--- a/data/raw/copas_y_torneos.xlsx
+++ b/data/raw/copas_y_torneos.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Projects\gateball\kantokeando-data\data\raw\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FB842DD0-6F67-42C3-80E1-9713BC04467E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3245F3C1-A9DF-49E7-A0FF-F7AF9FF244BB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -5079,7 +5079,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="15">
+  <cellXfs count="16">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -5099,6 +5099,7 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="164" fontId="6" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Hipervínculo" xfId="1" builtinId="8"/>
@@ -9255,7 +9256,7 @@
       <c r="D136" t="s">
         <v>282</v>
       </c>
-      <c r="E136" s="13">
+      <c r="E136" s="15">
         <v>42106</v>
       </c>
       <c r="F136" s="13"/>
@@ -28441,7 +28442,7 @@
         <v>1255</v>
       </c>
       <c r="E785" s="5">
-        <v>45579</v>
+        <v>45578</v>
       </c>
       <c r="G785" s="9" t="s">
         <v>71</v>
@@ -28470,7 +28471,7 @@
         <v>1255</v>
       </c>
       <c r="E786" s="5">
-        <v>45580</v>
+        <v>45578</v>
       </c>
       <c r="G786" s="9" t="s">
         <v>71</v>
@@ -28499,7 +28500,7 @@
         <v>1255</v>
       </c>
       <c r="E787" s="5">
-        <v>45581</v>
+        <v>45578</v>
       </c>
       <c r="G787" s="9" t="s">
         <v>71</v>
@@ -28528,7 +28529,7 @@
         <v>1255</v>
       </c>
       <c r="E788" s="5">
-        <v>45582</v>
+        <v>45578</v>
       </c>
       <c r="G788" s="9" t="s">
         <v>71</v>
@@ -28557,7 +28558,7 @@
         <v>1255</v>
       </c>
       <c r="E789" s="5">
-        <v>45583</v>
+        <v>45578</v>
       </c>
       <c r="G789" s="9" t="s">
         <v>71</v>
@@ -28586,7 +28587,7 @@
         <v>1255</v>
       </c>
       <c r="E790" s="5">
-        <v>45584</v>
+        <v>45578</v>
       </c>
       <c r="G790" s="9" t="s">
         <v>71</v>
@@ -29920,7 +29921,7 @@
         <v>303</v>
       </c>
       <c r="E837" s="5">
-        <v>45369</v>
+        <v>45368</v>
       </c>
       <c r="G837" s="9" t="s">
         <v>71</v>
@@ -29949,7 +29950,7 @@
         <v>303</v>
       </c>
       <c r="E838" s="5">
-        <v>45370</v>
+        <v>45368</v>
       </c>
       <c r="G838" s="9" t="s">
         <v>71</v>
@@ -29978,7 +29979,7 @@
         <v>303</v>
       </c>
       <c r="E839" s="5">
-        <v>45371</v>
+        <v>45368</v>
       </c>
       <c r="G839" s="9" t="s">
         <v>71</v>
@@ -30007,7 +30008,7 @@
         <v>303</v>
       </c>
       <c r="E840" s="5">
-        <v>45372</v>
+        <v>45368</v>
       </c>
       <c r="G840" s="9" t="s">
         <v>71</v>
@@ -32121,7 +32122,7 @@
         <v>1443</v>
       </c>
       <c r="E916" s="5">
-        <v>45852</v>
+        <v>45851</v>
       </c>
       <c r="G916" t="s">
         <v>15</v>
@@ -32147,7 +32148,7 @@
         <v>1443</v>
       </c>
       <c r="E917" s="5">
-        <v>45853</v>
+        <v>45851</v>
       </c>
       <c r="G917" t="s">
         <v>15</v>
@@ -32173,7 +32174,7 @@
         <v>1443</v>
       </c>
       <c r="E918" s="5">
-        <v>45854</v>
+        <v>45851</v>
       </c>
       <c r="G918" t="s">
         <v>15</v>
@@ -32199,7 +32200,7 @@
         <v>1443</v>
       </c>
       <c r="E919" s="5">
-        <v>45855</v>
+        <v>45851</v>
       </c>
       <c r="G919" t="s">
         <v>15</v>
@@ -32225,7 +32226,7 @@
         <v>1443</v>
       </c>
       <c r="E920" s="5">
-        <v>45856</v>
+        <v>45851</v>
       </c>
       <c r="G920" t="s">
         <v>15</v>
@@ -32251,7 +32252,7 @@
         <v>1443</v>
       </c>
       <c r="E921" s="5">
-        <v>45857</v>
+        <v>45851</v>
       </c>
       <c r="G921" t="s">
         <v>15</v>
@@ -32277,7 +32278,7 @@
         <v>1443</v>
       </c>
       <c r="E922" s="5">
-        <v>45858</v>
+        <v>45851</v>
       </c>
       <c r="G922" t="s">
         <v>15</v>

--- a/data/raw/copas_y_torneos.xlsx
+++ b/data/raw/copas_y_torneos.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Projects\gateball\kantokeando-data\data\raw\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3245F3C1-A9DF-49E7-A0FF-F7AF9FF244BB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2A9BFE27-584D-4730-A304-2BE655ACE4C7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -47,7 +47,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7061" uniqueCount="1638">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7071" uniqueCount="1638">
   <si>
     <t>id_torneo</t>
   </si>
@@ -5079,7 +5079,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="16">
+  <cellXfs count="15">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -5099,7 +5099,6 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="164" fontId="6" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Hipervínculo" xfId="1" builtinId="8"/>
@@ -5403,6 +5402,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+  <sheetPr filterMode="1"/>
   <dimension ref="A1:M1041"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.88671875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
@@ -5461,7 +5461,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="2" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="A2" s="6" t="s">
         <v>13</v>
       </c>
@@ -5494,7 +5494,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="3" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="A3" s="6"/>
       <c r="B3" s="6"/>
       <c r="C3" s="6"/>
@@ -5525,7 +5525,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="4" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="A4" s="6"/>
       <c r="B4" s="6"/>
       <c r="C4" s="6"/>
@@ -5556,7 +5556,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="5" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="D5" s="6" t="s">
         <v>14</v>
       </c>
@@ -5583,7 +5583,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="6" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="C6" t="s">
         <v>27</v>
       </c>
@@ -5613,7 +5613,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="7" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="C7" t="s">
         <v>27</v>
       </c>
@@ -5643,7 +5643,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="8" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="C8" t="s">
         <v>27</v>
       </c>
@@ -5673,7 +5673,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="9" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="C9" t="s">
         <v>27</v>
       </c>
@@ -5703,7 +5703,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="10" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="C10" t="s">
         <v>27</v>
       </c>
@@ -5733,7 +5733,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="11" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="C11" t="s">
         <v>27</v>
       </c>
@@ -5763,7 +5763,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="12" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="C12" t="s">
         <v>27</v>
       </c>
@@ -5793,7 +5793,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="13" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="C13" t="s">
         <v>27</v>
       </c>
@@ -5823,7 +5823,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="14" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="C14" t="s">
         <v>45</v>
       </c>
@@ -5853,7 +5853,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="15" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="C15" t="s">
         <v>45</v>
       </c>
@@ -5883,7 +5883,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="16" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="C16" t="s">
         <v>45</v>
       </c>
@@ -5913,7 +5913,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="17" spans="3:13" x14ac:dyDescent="0.3">
+    <row r="17" spans="3:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="C17" t="s">
         <v>45</v>
       </c>
@@ -5943,7 +5943,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="18" spans="3:13" x14ac:dyDescent="0.3">
+    <row r="18" spans="3:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="C18" t="s">
         <v>45</v>
       </c>
@@ -5973,7 +5973,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="19" spans="3:13" x14ac:dyDescent="0.3">
+    <row r="19" spans="3:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="C19" t="s">
         <v>45</v>
       </c>
@@ -6003,7 +6003,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="20" spans="3:13" x14ac:dyDescent="0.3">
+    <row r="20" spans="3:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="C20" t="s">
         <v>59</v>
       </c>
@@ -6030,7 +6030,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="21" spans="3:13" x14ac:dyDescent="0.3">
+    <row r="21" spans="3:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="C21" t="s">
         <v>59</v>
       </c>
@@ -6057,7 +6057,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="22" spans="3:13" x14ac:dyDescent="0.3">
+    <row r="22" spans="3:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="C22" t="s">
         <v>59</v>
       </c>
@@ -6084,7 +6084,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="23" spans="3:13" x14ac:dyDescent="0.3">
+    <row r="23" spans="3:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="C23" t="s">
         <v>59</v>
       </c>
@@ -6111,7 +6111,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="24" spans="3:13" x14ac:dyDescent="0.3">
+    <row r="24" spans="3:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="C24" t="s">
         <v>69</v>
       </c>
@@ -6138,7 +6138,7 @@
         <v>74</v>
       </c>
     </row>
-    <row r="25" spans="3:13" x14ac:dyDescent="0.3">
+    <row r="25" spans="3:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="C25" t="s">
         <v>69</v>
       </c>
@@ -6165,7 +6165,7 @@
         <v>74</v>
       </c>
     </row>
-    <row r="26" spans="3:13" x14ac:dyDescent="0.3">
+    <row r="26" spans="3:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="C26" t="s">
         <v>69</v>
       </c>
@@ -6192,7 +6192,7 @@
         <v>74</v>
       </c>
     </row>
-    <row r="27" spans="3:13" x14ac:dyDescent="0.3">
+    <row r="27" spans="3:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="C27" t="s">
         <v>69</v>
       </c>
@@ -6219,7 +6219,7 @@
         <v>74</v>
       </c>
     </row>
-    <row r="28" spans="3:13" x14ac:dyDescent="0.3">
+    <row r="28" spans="3:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="C28" t="s">
         <v>79</v>
       </c>
@@ -6246,7 +6246,7 @@
         <v>83</v>
       </c>
     </row>
-    <row r="29" spans="3:13" x14ac:dyDescent="0.3">
+    <row r="29" spans="3:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="C29" t="s">
         <v>79</v>
       </c>
@@ -6273,7 +6273,7 @@
         <v>83</v>
       </c>
     </row>
-    <row r="30" spans="3:13" x14ac:dyDescent="0.3">
+    <row r="30" spans="3:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="C30" t="s">
         <v>79</v>
       </c>
@@ -6300,7 +6300,7 @@
         <v>83</v>
       </c>
     </row>
-    <row r="31" spans="3:13" x14ac:dyDescent="0.3">
+    <row r="31" spans="3:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="C31" t="s">
         <v>79</v>
       </c>
@@ -6327,7 +6327,7 @@
         <v>83</v>
       </c>
     </row>
-    <row r="32" spans="3:13" x14ac:dyDescent="0.3">
+    <row r="32" spans="3:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="C32" t="s">
         <v>90</v>
       </c>
@@ -6354,7 +6354,7 @@
         <v>94</v>
       </c>
     </row>
-    <row r="33" spans="3:13" x14ac:dyDescent="0.3">
+    <row r="33" spans="3:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="C33" t="s">
         <v>90</v>
       </c>
@@ -6381,7 +6381,7 @@
         <v>94</v>
       </c>
     </row>
-    <row r="34" spans="3:13" x14ac:dyDescent="0.3">
+    <row r="34" spans="3:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="C34" t="s">
         <v>90</v>
       </c>
@@ -6408,7 +6408,7 @@
         <v>94</v>
       </c>
     </row>
-    <row r="35" spans="3:13" x14ac:dyDescent="0.3">
+    <row r="35" spans="3:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="C35" t="s">
         <v>90</v>
       </c>
@@ -6435,7 +6435,7 @@
         <v>94</v>
       </c>
     </row>
-    <row r="36" spans="3:13" x14ac:dyDescent="0.3">
+    <row r="36" spans="3:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="C36" t="s">
         <v>101</v>
       </c>
@@ -6462,7 +6462,7 @@
         <v>105</v>
       </c>
     </row>
-    <row r="37" spans="3:13" x14ac:dyDescent="0.3">
+    <row r="37" spans="3:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="C37" t="s">
         <v>101</v>
       </c>
@@ -6489,7 +6489,7 @@
         <v>105</v>
       </c>
     </row>
-    <row r="38" spans="3:13" x14ac:dyDescent="0.3">
+    <row r="38" spans="3:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="C38" t="s">
         <v>101</v>
       </c>
@@ -6516,7 +6516,7 @@
         <v>105</v>
       </c>
     </row>
-    <row r="39" spans="3:13" x14ac:dyDescent="0.3">
+    <row r="39" spans="3:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="C39" t="s">
         <v>101</v>
       </c>
@@ -6543,7 +6543,7 @@
         <v>105</v>
       </c>
     </row>
-    <row r="40" spans="3:13" x14ac:dyDescent="0.3">
+    <row r="40" spans="3:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="C40" t="s">
         <v>110</v>
       </c>
@@ -6570,7 +6570,7 @@
         <v>114</v>
       </c>
     </row>
-    <row r="41" spans="3:13" x14ac:dyDescent="0.3">
+    <row r="41" spans="3:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="C41" t="s">
         <v>110</v>
       </c>
@@ -6597,7 +6597,7 @@
         <v>114</v>
       </c>
     </row>
-    <row r="42" spans="3:13" x14ac:dyDescent="0.3">
+    <row r="42" spans="3:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="C42" t="s">
         <v>110</v>
       </c>
@@ -6624,7 +6624,7 @@
         <v>114</v>
       </c>
     </row>
-    <row r="43" spans="3:13" x14ac:dyDescent="0.3">
+    <row r="43" spans="3:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="C43" t="s">
         <v>110</v>
       </c>
@@ -6651,7 +6651,7 @@
         <v>114</v>
       </c>
     </row>
-    <row r="44" spans="3:13" x14ac:dyDescent="0.3">
+    <row r="44" spans="3:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="C44" t="s">
         <v>110</v>
       </c>
@@ -6678,7 +6678,7 @@
         <v>124</v>
       </c>
     </row>
-    <row r="45" spans="3:13" x14ac:dyDescent="0.3">
+    <row r="45" spans="3:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="C45" t="s">
         <v>110</v>
       </c>
@@ -6705,7 +6705,7 @@
         <v>124</v>
       </c>
     </row>
-    <row r="46" spans="3:13" x14ac:dyDescent="0.3">
+    <row r="46" spans="3:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="C46" t="s">
         <v>110</v>
       </c>
@@ -6732,7 +6732,7 @@
         <v>124</v>
       </c>
     </row>
-    <row r="47" spans="3:13" x14ac:dyDescent="0.3">
+    <row r="47" spans="3:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="C47" t="s">
         <v>110</v>
       </c>
@@ -6759,7 +6759,7 @@
         <v>124</v>
       </c>
     </row>
-    <row r="48" spans="3:13" x14ac:dyDescent="0.3">
+    <row r="48" spans="3:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="C48" t="s">
         <v>129</v>
       </c>
@@ -6786,7 +6786,7 @@
         <v>132</v>
       </c>
     </row>
-    <row r="49" spans="2:13" x14ac:dyDescent="0.3">
+    <row r="49" spans="2:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="C49" t="s">
         <v>129</v>
       </c>
@@ -6813,7 +6813,7 @@
         <v>132</v>
       </c>
     </row>
-    <row r="50" spans="2:13" x14ac:dyDescent="0.3">
+    <row r="50" spans="2:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="C50" t="s">
         <v>129</v>
       </c>
@@ -6840,7 +6840,7 @@
         <v>132</v>
       </c>
     </row>
-    <row r="51" spans="2:13" x14ac:dyDescent="0.3">
+    <row r="51" spans="2:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="C51" t="s">
         <v>129</v>
       </c>
@@ -6867,7 +6867,7 @@
         <v>132</v>
       </c>
     </row>
-    <row r="52" spans="2:13" x14ac:dyDescent="0.3">
+    <row r="52" spans="2:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="B52" t="s">
         <v>137</v>
       </c>
@@ -6894,7 +6894,7 @@
         <v>141</v>
       </c>
     </row>
-    <row r="53" spans="2:13" x14ac:dyDescent="0.3">
+    <row r="53" spans="2:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="B53" t="s">
         <v>137</v>
       </c>
@@ -6921,7 +6921,7 @@
         <v>141</v>
       </c>
     </row>
-    <row r="54" spans="2:13" x14ac:dyDescent="0.3">
+    <row r="54" spans="2:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="B54" t="s">
         <v>137</v>
       </c>
@@ -6948,7 +6948,7 @@
         <v>147</v>
       </c>
     </row>
-    <row r="55" spans="2:13" x14ac:dyDescent="0.3">
+    <row r="55" spans="2:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="B55" t="s">
         <v>137</v>
       </c>
@@ -6975,7 +6975,7 @@
         <v>147</v>
       </c>
     </row>
-    <row r="56" spans="2:13" x14ac:dyDescent="0.3">
+    <row r="56" spans="2:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="C56" t="s">
         <v>150</v>
       </c>
@@ -7002,7 +7002,7 @@
         <v>153</v>
       </c>
     </row>
-    <row r="57" spans="2:13" x14ac:dyDescent="0.3">
+    <row r="57" spans="2:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="C57" t="s">
         <v>154</v>
       </c>
@@ -7029,7 +7029,7 @@
         <v>157</v>
       </c>
     </row>
-    <row r="58" spans="2:13" x14ac:dyDescent="0.3">
+    <row r="58" spans="2:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="C58" t="s">
         <v>154</v>
       </c>
@@ -7056,7 +7056,7 @@
         <v>157</v>
       </c>
     </row>
-    <row r="59" spans="2:13" x14ac:dyDescent="0.3">
+    <row r="59" spans="2:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="C59" t="s">
         <v>154</v>
       </c>
@@ -7083,7 +7083,7 @@
         <v>157</v>
       </c>
     </row>
-    <row r="60" spans="2:13" x14ac:dyDescent="0.3">
+    <row r="60" spans="2:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="C60" t="s">
         <v>154</v>
       </c>
@@ -7110,7 +7110,7 @@
         <v>157</v>
       </c>
     </row>
-    <row r="61" spans="2:13" x14ac:dyDescent="0.3">
+    <row r="61" spans="2:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="B61" t="s">
         <v>162</v>
       </c>
@@ -7140,7 +7140,7 @@
         <v>167</v>
       </c>
     </row>
-    <row r="62" spans="2:13" x14ac:dyDescent="0.3">
+    <row r="62" spans="2:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="B62" t="s">
         <v>162</v>
       </c>
@@ -7170,7 +7170,7 @@
         <v>167</v>
       </c>
     </row>
-    <row r="63" spans="2:13" x14ac:dyDescent="0.3">
+    <row r="63" spans="2:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="B63" t="s">
         <v>162</v>
       </c>
@@ -7200,7 +7200,7 @@
         <v>167</v>
       </c>
     </row>
-    <row r="64" spans="2:13" x14ac:dyDescent="0.3">
+    <row r="64" spans="2:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="B64" t="s">
         <v>162</v>
       </c>
@@ -7230,7 +7230,7 @@
         <v>167</v>
       </c>
     </row>
-    <row r="65" spans="2:13" x14ac:dyDescent="0.3">
+    <row r="65" spans="2:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="B65" t="s">
         <v>162</v>
       </c>
@@ -7260,7 +7260,7 @@
         <v>167</v>
       </c>
     </row>
-    <row r="66" spans="2:13" x14ac:dyDescent="0.3">
+    <row r="66" spans="2:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="B66" t="s">
         <v>162</v>
       </c>
@@ -7290,7 +7290,7 @@
         <v>167</v>
       </c>
     </row>
-    <row r="67" spans="2:13" x14ac:dyDescent="0.3">
+    <row r="67" spans="2:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="B67" t="s">
         <v>162</v>
       </c>
@@ -7320,7 +7320,7 @@
         <v>167</v>
       </c>
     </row>
-    <row r="68" spans="2:13" x14ac:dyDescent="0.3">
+    <row r="68" spans="2:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="B68" t="s">
         <v>162</v>
       </c>
@@ -7350,7 +7350,7 @@
         <v>167</v>
       </c>
     </row>
-    <row r="69" spans="2:13" x14ac:dyDescent="0.3">
+    <row r="69" spans="2:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="B69" t="s">
         <v>162</v>
       </c>
@@ -7380,7 +7380,7 @@
         <v>167</v>
       </c>
     </row>
-    <row r="70" spans="2:13" x14ac:dyDescent="0.3">
+    <row r="70" spans="2:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="B70" t="s">
         <v>162</v>
       </c>
@@ -7410,7 +7410,7 @@
         <v>184</v>
       </c>
     </row>
-    <row r="71" spans="2:13" x14ac:dyDescent="0.3">
+    <row r="71" spans="2:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="B71" t="s">
         <v>162</v>
       </c>
@@ -7440,7 +7440,7 @@
         <v>184</v>
       </c>
     </row>
-    <row r="72" spans="2:13" x14ac:dyDescent="0.3">
+    <row r="72" spans="2:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="B72" t="s">
         <v>162</v>
       </c>
@@ -7470,7 +7470,7 @@
         <v>184</v>
       </c>
     </row>
-    <row r="73" spans="2:13" x14ac:dyDescent="0.3">
+    <row r="73" spans="2:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="B73" t="s">
         <v>162</v>
       </c>
@@ -7500,7 +7500,7 @@
         <v>184</v>
       </c>
     </row>
-    <row r="74" spans="2:13" x14ac:dyDescent="0.3">
+    <row r="74" spans="2:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="B74" t="s">
         <v>162</v>
       </c>
@@ -7530,7 +7530,7 @@
         <v>184</v>
       </c>
     </row>
-    <row r="75" spans="2:13" x14ac:dyDescent="0.3">
+    <row r="75" spans="2:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="B75" t="s">
         <v>162</v>
       </c>
@@ -7560,7 +7560,7 @@
         <v>184</v>
       </c>
     </row>
-    <row r="76" spans="2:13" x14ac:dyDescent="0.3">
+    <row r="76" spans="2:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="B76" t="s">
         <v>162</v>
       </c>
@@ -7590,7 +7590,7 @@
         <v>184</v>
       </c>
     </row>
-    <row r="77" spans="2:13" x14ac:dyDescent="0.3">
+    <row r="77" spans="2:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="B77" t="s">
         <v>162</v>
       </c>
@@ -7620,7 +7620,7 @@
         <v>184</v>
       </c>
     </row>
-    <row r="78" spans="2:13" x14ac:dyDescent="0.3">
+    <row r="78" spans="2:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="B78" t="s">
         <v>162</v>
       </c>
@@ -7650,7 +7650,7 @@
         <v>184</v>
       </c>
     </row>
-    <row r="79" spans="2:13" x14ac:dyDescent="0.3">
+    <row r="79" spans="2:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="C79" t="s">
         <v>79</v>
       </c>
@@ -7677,7 +7677,7 @@
         <v>198</v>
       </c>
     </row>
-    <row r="80" spans="2:13" x14ac:dyDescent="0.3">
+    <row r="80" spans="2:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="C80" t="s">
         <v>79</v>
       </c>
@@ -7704,7 +7704,7 @@
         <v>198</v>
       </c>
     </row>
-    <row r="81" spans="3:13" x14ac:dyDescent="0.3">
+    <row r="81" spans="3:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="C81" t="s">
         <v>79</v>
       </c>
@@ -7731,7 +7731,7 @@
         <v>198</v>
       </c>
     </row>
-    <row r="82" spans="3:13" x14ac:dyDescent="0.3">
+    <row r="82" spans="3:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="C82" t="s">
         <v>79</v>
       </c>
@@ -7758,7 +7758,7 @@
         <v>198</v>
       </c>
     </row>
-    <row r="83" spans="3:13" x14ac:dyDescent="0.3">
+    <row r="83" spans="3:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="C83" t="s">
         <v>45</v>
       </c>
@@ -7788,7 +7788,7 @@
         <v>207</v>
       </c>
     </row>
-    <row r="84" spans="3:13" x14ac:dyDescent="0.3">
+    <row r="84" spans="3:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="C84" t="s">
         <v>45</v>
       </c>
@@ -7818,7 +7818,7 @@
         <v>207</v>
       </c>
     </row>
-    <row r="85" spans="3:13" x14ac:dyDescent="0.3">
+    <row r="85" spans="3:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="C85" t="s">
         <v>45</v>
       </c>
@@ -7848,7 +7848,7 @@
         <v>207</v>
       </c>
     </row>
-    <row r="86" spans="3:13" x14ac:dyDescent="0.3">
+    <row r="86" spans="3:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="C86" t="s">
         <v>45</v>
       </c>
@@ -7878,7 +7878,7 @@
         <v>207</v>
       </c>
     </row>
-    <row r="87" spans="3:13" x14ac:dyDescent="0.3">
+    <row r="87" spans="3:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="C87" t="s">
         <v>45</v>
       </c>
@@ -7908,7 +7908,7 @@
         <v>207</v>
       </c>
     </row>
-    <row r="88" spans="3:13" x14ac:dyDescent="0.3">
+    <row r="88" spans="3:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="C88" t="s">
         <v>45</v>
       </c>
@@ -7938,7 +7938,7 @@
         <v>207</v>
       </c>
     </row>
-    <row r="89" spans="3:13" x14ac:dyDescent="0.3">
+    <row r="89" spans="3:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="C89" t="s">
         <v>59</v>
       </c>
@@ -7965,7 +7965,7 @@
         <v>214</v>
       </c>
     </row>
-    <row r="90" spans="3:13" x14ac:dyDescent="0.3">
+    <row r="90" spans="3:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="C90" t="s">
         <v>59</v>
       </c>
@@ -7992,7 +7992,7 @@
         <v>214</v>
       </c>
     </row>
-    <row r="91" spans="3:13" x14ac:dyDescent="0.3">
+    <row r="91" spans="3:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="C91" t="s">
         <v>59</v>
       </c>
@@ -8019,7 +8019,7 @@
         <v>214</v>
       </c>
     </row>
-    <row r="92" spans="3:13" x14ac:dyDescent="0.3">
+    <row r="92" spans="3:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="C92" t="s">
         <v>59</v>
       </c>
@@ -8046,7 +8046,7 @@
         <v>214</v>
       </c>
     </row>
-    <row r="93" spans="3:13" x14ac:dyDescent="0.3">
+    <row r="93" spans="3:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="C93" t="s">
         <v>69</v>
       </c>
@@ -8073,7 +8073,7 @@
         <v>219</v>
       </c>
     </row>
-    <row r="94" spans="3:13" x14ac:dyDescent="0.3">
+    <row r="94" spans="3:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="C94" t="s">
         <v>69</v>
       </c>
@@ -8100,7 +8100,7 @@
         <v>219</v>
       </c>
     </row>
-    <row r="95" spans="3:13" x14ac:dyDescent="0.3">
+    <row r="95" spans="3:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="C95" t="s">
         <v>69</v>
       </c>
@@ -8127,7 +8127,7 @@
         <v>219</v>
       </c>
     </row>
-    <row r="96" spans="3:13" x14ac:dyDescent="0.3">
+    <row r="96" spans="3:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="C96" t="s">
         <v>69</v>
       </c>
@@ -8154,7 +8154,7 @@
         <v>219</v>
       </c>
     </row>
-    <row r="97" spans="2:13" x14ac:dyDescent="0.3">
+    <row r="97" spans="2:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="B97" t="s">
         <v>137</v>
       </c>
@@ -8184,7 +8184,7 @@
         <v>229</v>
       </c>
     </row>
-    <row r="98" spans="2:13" x14ac:dyDescent="0.3">
+    <row r="98" spans="2:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="B98" t="s">
         <v>137</v>
       </c>
@@ -8214,7 +8214,7 @@
         <v>229</v>
       </c>
     </row>
-    <row r="99" spans="2:13" x14ac:dyDescent="0.3">
+    <row r="99" spans="2:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="B99" t="s">
         <v>137</v>
       </c>
@@ -8244,7 +8244,7 @@
         <v>229</v>
       </c>
     </row>
-    <row r="100" spans="2:13" x14ac:dyDescent="0.3">
+    <row r="100" spans="2:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="B100" t="s">
         <v>162</v>
       </c>
@@ -8274,7 +8274,7 @@
         <v>237</v>
       </c>
     </row>
-    <row r="101" spans="2:13" x14ac:dyDescent="0.3">
+    <row r="101" spans="2:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="B101" t="s">
         <v>162</v>
       </c>
@@ -8301,7 +8301,7 @@
         <v>237</v>
       </c>
     </row>
-    <row r="102" spans="2:13" x14ac:dyDescent="0.3">
+    <row r="102" spans="2:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="B102" t="s">
         <v>162</v>
       </c>
@@ -8328,7 +8328,7 @@
         <v>237</v>
       </c>
     </row>
-    <row r="103" spans="2:13" x14ac:dyDescent="0.3">
+    <row r="103" spans="2:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="B103" t="s">
         <v>162</v>
       </c>
@@ -8358,7 +8358,7 @@
         <v>237</v>
       </c>
     </row>
-    <row r="104" spans="2:13" x14ac:dyDescent="0.3">
+    <row r="104" spans="2:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="B104" t="s">
         <v>162</v>
       </c>
@@ -8385,7 +8385,7 @@
         <v>237</v>
       </c>
     </row>
-    <row r="105" spans="2:13" x14ac:dyDescent="0.3">
+    <row r="105" spans="2:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="B105" t="s">
         <v>162</v>
       </c>
@@ -8412,7 +8412,7 @@
         <v>237</v>
       </c>
     </row>
-    <row r="106" spans="2:13" x14ac:dyDescent="0.3">
+    <row r="106" spans="2:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="B106" t="s">
         <v>162</v>
       </c>
@@ -8439,7 +8439,7 @@
         <v>237</v>
       </c>
     </row>
-    <row r="107" spans="2:13" x14ac:dyDescent="0.3">
+    <row r="107" spans="2:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="B107" t="s">
         <v>162</v>
       </c>
@@ -8466,7 +8466,7 @@
         <v>237</v>
       </c>
     </row>
-    <row r="108" spans="2:13" x14ac:dyDescent="0.3">
+    <row r="108" spans="2:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="B108" t="s">
         <v>162</v>
       </c>
@@ -8493,7 +8493,7 @@
         <v>237</v>
       </c>
     </row>
-    <row r="109" spans="2:13" x14ac:dyDescent="0.3">
+    <row r="109" spans="2:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="B109" t="s">
         <v>162</v>
       </c>
@@ -8520,7 +8520,7 @@
         <v>237</v>
       </c>
     </row>
-    <row r="110" spans="2:13" x14ac:dyDescent="0.3">
+    <row r="110" spans="2:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="B110" t="s">
         <v>162</v>
       </c>
@@ -8547,7 +8547,7 @@
         <v>237</v>
       </c>
     </row>
-    <row r="111" spans="2:13" x14ac:dyDescent="0.3">
+    <row r="111" spans="2:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="B111" t="s">
         <v>162</v>
       </c>
@@ -8574,7 +8574,7 @@
         <v>237</v>
       </c>
     </row>
-    <row r="112" spans="2:13" x14ac:dyDescent="0.3">
+    <row r="112" spans="2:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="C112" t="s">
         <v>90</v>
       </c>
@@ -8601,7 +8601,7 @@
         <v>247</v>
       </c>
     </row>
-    <row r="113" spans="2:13" x14ac:dyDescent="0.3">
+    <row r="113" spans="2:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="C113" t="s">
         <v>90</v>
       </c>
@@ -8628,7 +8628,7 @@
         <v>247</v>
       </c>
     </row>
-    <row r="114" spans="2:13" x14ac:dyDescent="0.3">
+    <row r="114" spans="2:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="C114" t="s">
         <v>90</v>
       </c>
@@ -8655,7 +8655,7 @@
         <v>247</v>
       </c>
     </row>
-    <row r="115" spans="2:13" x14ac:dyDescent="0.3">
+    <row r="115" spans="2:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="C115" t="s">
         <v>90</v>
       </c>
@@ -8682,7 +8682,7 @@
         <v>247</v>
       </c>
     </row>
-    <row r="116" spans="2:13" x14ac:dyDescent="0.3">
+    <row r="116" spans="2:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="B116" t="s">
         <v>137</v>
       </c>
@@ -8709,7 +8709,7 @@
         <v>255</v>
       </c>
     </row>
-    <row r="117" spans="2:13" x14ac:dyDescent="0.3">
+    <row r="117" spans="2:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="B117" t="s">
         <v>137</v>
       </c>
@@ -8736,7 +8736,7 @@
         <v>255</v>
       </c>
     </row>
-    <row r="118" spans="2:13" x14ac:dyDescent="0.3">
+    <row r="118" spans="2:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="B118" t="s">
         <v>137</v>
       </c>
@@ -8763,7 +8763,7 @@
         <v>255</v>
       </c>
     </row>
-    <row r="119" spans="2:13" x14ac:dyDescent="0.3">
+    <row r="119" spans="2:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="B119" t="s">
         <v>137</v>
       </c>
@@ -8790,7 +8790,7 @@
         <v>255</v>
       </c>
     </row>
-    <row r="120" spans="2:13" x14ac:dyDescent="0.3">
+    <row r="120" spans="2:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="B120" t="s">
         <v>137</v>
       </c>
@@ -8817,7 +8817,7 @@
         <v>265</v>
       </c>
     </row>
-    <row r="121" spans="2:13" x14ac:dyDescent="0.3">
+    <row r="121" spans="2:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="B121" t="s">
         <v>137</v>
       </c>
@@ -8844,7 +8844,7 @@
         <v>265</v>
       </c>
     </row>
-    <row r="122" spans="2:13" x14ac:dyDescent="0.3">
+    <row r="122" spans="2:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="B122" t="s">
         <v>137</v>
       </c>
@@ -8871,7 +8871,7 @@
         <v>265</v>
       </c>
     </row>
-    <row r="123" spans="2:13" x14ac:dyDescent="0.3">
+    <row r="123" spans="2:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="B123" t="s">
         <v>137</v>
       </c>
@@ -8898,7 +8898,7 @@
         <v>265</v>
       </c>
     </row>
-    <row r="124" spans="2:13" x14ac:dyDescent="0.3">
+    <row r="124" spans="2:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="B124" t="s">
         <v>162</v>
       </c>
@@ -8928,7 +8928,7 @@
         <v>273</v>
       </c>
     </row>
-    <row r="125" spans="2:13" x14ac:dyDescent="0.3">
+    <row r="125" spans="2:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="B125" t="s">
         <v>162</v>
       </c>
@@ -8958,7 +8958,7 @@
         <v>273</v>
       </c>
     </row>
-    <row r="126" spans="2:13" x14ac:dyDescent="0.3">
+    <row r="126" spans="2:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="B126" t="s">
         <v>162</v>
       </c>
@@ -8988,7 +8988,7 @@
         <v>273</v>
       </c>
     </row>
-    <row r="127" spans="2:13" x14ac:dyDescent="0.3">
+    <row r="127" spans="2:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="B127" t="s">
         <v>162</v>
       </c>
@@ -9018,7 +9018,7 @@
         <v>273</v>
       </c>
     </row>
-    <row r="128" spans="2:13" x14ac:dyDescent="0.3">
+    <row r="128" spans="2:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="B128" t="s">
         <v>162</v>
       </c>
@@ -9048,7 +9048,7 @@
         <v>273</v>
       </c>
     </row>
-    <row r="129" spans="2:13" x14ac:dyDescent="0.3">
+    <row r="129" spans="2:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="B129" t="s">
         <v>162</v>
       </c>
@@ -9078,7 +9078,7 @@
         <v>273</v>
       </c>
     </row>
-    <row r="130" spans="2:13" x14ac:dyDescent="0.3">
+    <row r="130" spans="2:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="B130" t="s">
         <v>162</v>
       </c>
@@ -9108,7 +9108,7 @@
         <v>273</v>
       </c>
     </row>
-    <row r="131" spans="2:13" x14ac:dyDescent="0.3">
+    <row r="131" spans="2:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="B131" t="s">
         <v>162</v>
       </c>
@@ -9138,7 +9138,7 @@
         <v>273</v>
       </c>
     </row>
-    <row r="132" spans="2:13" x14ac:dyDescent="0.3">
+    <row r="132" spans="2:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="B132" t="s">
         <v>162</v>
       </c>
@@ -9168,7 +9168,7 @@
         <v>273</v>
       </c>
     </row>
-    <row r="133" spans="2:13" x14ac:dyDescent="0.3">
+    <row r="133" spans="2:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="C133" t="s">
         <v>129</v>
       </c>
@@ -9195,7 +9195,7 @@
         <v>284</v>
       </c>
     </row>
-    <row r="134" spans="2:13" x14ac:dyDescent="0.3">
+    <row r="134" spans="2:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="C134" t="s">
         <v>129</v>
       </c>
@@ -9222,7 +9222,7 @@
         <v>284</v>
       </c>
     </row>
-    <row r="135" spans="2:13" x14ac:dyDescent="0.3">
+    <row r="135" spans="2:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="C135" t="s">
         <v>129</v>
       </c>
@@ -9249,14 +9249,14 @@
         <v>284</v>
       </c>
     </row>
-    <row r="136" spans="2:13" x14ac:dyDescent="0.3">
+    <row r="136" spans="2:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="C136" t="s">
         <v>129</v>
       </c>
       <c r="D136" t="s">
         <v>282</v>
       </c>
-      <c r="E136" s="15">
+      <c r="E136" s="10">
         <v>42106</v>
       </c>
       <c r="F136" s="13"/>
@@ -9276,7 +9276,7 @@
         <v>284</v>
       </c>
     </row>
-    <row r="137" spans="2:13" x14ac:dyDescent="0.3">
+    <row r="137" spans="2:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="C137" t="s">
         <v>150</v>
       </c>
@@ -9303,7 +9303,7 @@
         <v>290</v>
       </c>
     </row>
-    <row r="138" spans="2:13" x14ac:dyDescent="0.3">
+    <row r="138" spans="2:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="C138" t="s">
         <v>150</v>
       </c>
@@ -9330,7 +9330,7 @@
         <v>290</v>
       </c>
     </row>
-    <row r="139" spans="2:13" x14ac:dyDescent="0.3">
+    <row r="139" spans="2:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="C139" t="s">
         <v>150</v>
       </c>
@@ -9357,7 +9357,7 @@
         <v>290</v>
       </c>
     </row>
-    <row r="140" spans="2:13" x14ac:dyDescent="0.3">
+    <row r="140" spans="2:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="C140" t="s">
         <v>150</v>
       </c>
@@ -9384,7 +9384,7 @@
         <v>290</v>
       </c>
     </row>
-    <row r="141" spans="2:13" x14ac:dyDescent="0.3">
+    <row r="141" spans="2:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="C141" t="s">
         <v>294</v>
       </c>
@@ -9414,7 +9414,7 @@
         <v>297</v>
       </c>
     </row>
-    <row r="142" spans="2:13" x14ac:dyDescent="0.3">
+    <row r="142" spans="2:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="C142" t="s">
         <v>294</v>
       </c>
@@ -9444,7 +9444,7 @@
         <v>297</v>
       </c>
     </row>
-    <row r="143" spans="2:13" x14ac:dyDescent="0.3">
+    <row r="143" spans="2:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="C143" t="s">
         <v>294</v>
       </c>
@@ -9474,7 +9474,7 @@
         <v>297</v>
       </c>
     </row>
-    <row r="144" spans="2:13" x14ac:dyDescent="0.3">
+    <row r="144" spans="2:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="C144" t="s">
         <v>294</v>
       </c>
@@ -9504,7 +9504,7 @@
         <v>297</v>
       </c>
     </row>
-    <row r="145" spans="2:13" x14ac:dyDescent="0.3">
+    <row r="145" spans="2:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="B145" t="s">
         <v>302</v>
       </c>
@@ -9534,7 +9534,7 @@
         <v>307</v>
       </c>
     </row>
-    <row r="146" spans="2:13" x14ac:dyDescent="0.3">
+    <row r="146" spans="2:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="B146" t="s">
         <v>302</v>
       </c>
@@ -9564,7 +9564,7 @@
         <v>307</v>
       </c>
     </row>
-    <row r="147" spans="2:13" x14ac:dyDescent="0.3">
+    <row r="147" spans="2:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="B147" t="s">
         <v>302</v>
       </c>
@@ -9594,7 +9594,7 @@
         <v>307</v>
       </c>
     </row>
-    <row r="148" spans="2:13" x14ac:dyDescent="0.3">
+    <row r="148" spans="2:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="B148" t="s">
         <v>302</v>
       </c>
@@ -9624,7 +9624,7 @@
         <v>307</v>
       </c>
     </row>
-    <row r="149" spans="2:13" x14ac:dyDescent="0.3">
+    <row r="149" spans="2:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="D149" t="s">
         <v>312</v>
       </c>
@@ -9651,7 +9651,7 @@
         <v>314</v>
       </c>
     </row>
-    <row r="150" spans="2:13" x14ac:dyDescent="0.3">
+    <row r="150" spans="2:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="D150" t="s">
         <v>312</v>
       </c>
@@ -9678,7 +9678,7 @@
         <v>314</v>
       </c>
     </row>
-    <row r="151" spans="2:13" x14ac:dyDescent="0.3">
+    <row r="151" spans="2:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="D151" t="s">
         <v>312</v>
       </c>
@@ -9705,7 +9705,7 @@
         <v>314</v>
       </c>
     </row>
-    <row r="152" spans="2:13" x14ac:dyDescent="0.3">
+    <row r="152" spans="2:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="D152" t="s">
         <v>312</v>
       </c>
@@ -9732,7 +9732,7 @@
         <v>314</v>
       </c>
     </row>
-    <row r="153" spans="2:13" x14ac:dyDescent="0.3">
+    <row r="153" spans="2:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="D153" t="s">
         <v>312</v>
       </c>
@@ -9786,7 +9786,7 @@
         <v>314</v>
       </c>
     </row>
-    <row r="155" spans="2:13" x14ac:dyDescent="0.3">
+    <row r="155" spans="2:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="C155" t="s">
         <v>27</v>
       </c>
@@ -9816,7 +9816,7 @@
         <v>327</v>
       </c>
     </row>
-    <row r="156" spans="2:13" x14ac:dyDescent="0.3">
+    <row r="156" spans="2:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="C156" t="s">
         <v>27</v>
       </c>
@@ -9846,7 +9846,7 @@
         <v>327</v>
       </c>
     </row>
-    <row r="157" spans="2:13" x14ac:dyDescent="0.3">
+    <row r="157" spans="2:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="C157" t="s">
         <v>27</v>
       </c>
@@ -9876,7 +9876,7 @@
         <v>327</v>
       </c>
     </row>
-    <row r="158" spans="2:13" x14ac:dyDescent="0.3">
+    <row r="158" spans="2:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="C158" t="s">
         <v>27</v>
       </c>
@@ -9906,7 +9906,7 @@
         <v>327</v>
       </c>
     </row>
-    <row r="159" spans="2:13" x14ac:dyDescent="0.3">
+    <row r="159" spans="2:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="C159" t="s">
         <v>27</v>
       </c>
@@ -9936,7 +9936,7 @@
         <v>327</v>
       </c>
     </row>
-    <row r="160" spans="2:13" x14ac:dyDescent="0.3">
+    <row r="160" spans="2:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="C160" t="s">
         <v>27</v>
       </c>
@@ -9966,7 +9966,7 @@
         <v>327</v>
       </c>
     </row>
-    <row r="161" spans="3:13" x14ac:dyDescent="0.3">
+    <row r="161" spans="3:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="C161" t="s">
         <v>27</v>
       </c>
@@ -9996,7 +9996,7 @@
         <v>327</v>
       </c>
     </row>
-    <row r="162" spans="3:13" x14ac:dyDescent="0.3">
+    <row r="162" spans="3:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="C162" t="s">
         <v>27</v>
       </c>
@@ -10026,7 +10026,7 @@
         <v>327</v>
       </c>
     </row>
-    <row r="163" spans="3:13" x14ac:dyDescent="0.3">
+    <row r="163" spans="3:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="C163" t="s">
         <v>45</v>
       </c>
@@ -10056,7 +10056,7 @@
         <v>339</v>
       </c>
     </row>
-    <row r="164" spans="3:13" x14ac:dyDescent="0.3">
+    <row r="164" spans="3:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="C164" t="s">
         <v>45</v>
       </c>
@@ -10086,7 +10086,7 @@
         <v>339</v>
       </c>
     </row>
-    <row r="165" spans="3:13" x14ac:dyDescent="0.3">
+    <row r="165" spans="3:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="C165" t="s">
         <v>45</v>
       </c>
@@ -10116,7 +10116,7 @@
         <v>339</v>
       </c>
     </row>
-    <row r="166" spans="3:13" x14ac:dyDescent="0.3">
+    <row r="166" spans="3:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="C166" t="s">
         <v>45</v>
       </c>
@@ -10146,7 +10146,7 @@
         <v>339</v>
       </c>
     </row>
-    <row r="167" spans="3:13" x14ac:dyDescent="0.3">
+    <row r="167" spans="3:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="C167" t="s">
         <v>45</v>
       </c>
@@ -10176,7 +10176,7 @@
         <v>339</v>
       </c>
     </row>
-    <row r="168" spans="3:13" x14ac:dyDescent="0.3">
+    <row r="168" spans="3:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="C168" t="s">
         <v>45</v>
       </c>
@@ -10206,7 +10206,7 @@
         <v>339</v>
       </c>
     </row>
-    <row r="169" spans="3:13" x14ac:dyDescent="0.3">
+    <row r="169" spans="3:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="C169" t="s">
         <v>79</v>
       </c>
@@ -10236,7 +10236,7 @@
         <v>347</v>
       </c>
     </row>
-    <row r="170" spans="3:13" x14ac:dyDescent="0.3">
+    <row r="170" spans="3:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="C170" t="s">
         <v>79</v>
       </c>
@@ -10266,7 +10266,7 @@
         <v>347</v>
       </c>
     </row>
-    <row r="171" spans="3:13" x14ac:dyDescent="0.3">
+    <row r="171" spans="3:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="C171" t="s">
         <v>79</v>
       </c>
@@ -10296,7 +10296,7 @@
         <v>347</v>
       </c>
     </row>
-    <row r="172" spans="3:13" x14ac:dyDescent="0.3">
+    <row r="172" spans="3:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="C172" t="s">
         <v>79</v>
       </c>
@@ -10326,7 +10326,7 @@
         <v>347</v>
       </c>
     </row>
-    <row r="173" spans="3:13" x14ac:dyDescent="0.3">
+    <row r="173" spans="3:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="C173" t="s">
         <v>69</v>
       </c>
@@ -10356,7 +10356,7 @@
         <v>354</v>
       </c>
     </row>
-    <row r="174" spans="3:13" x14ac:dyDescent="0.3">
+    <row r="174" spans="3:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="C174" t="s">
         <v>69</v>
       </c>
@@ -10386,7 +10386,7 @@
         <v>354</v>
       </c>
     </row>
-    <row r="175" spans="3:13" x14ac:dyDescent="0.3">
+    <row r="175" spans="3:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="C175" t="s">
         <v>69</v>
       </c>
@@ -10416,7 +10416,7 @@
         <v>354</v>
       </c>
     </row>
-    <row r="176" spans="3:13" x14ac:dyDescent="0.3">
+    <row r="176" spans="3:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="C176" t="s">
         <v>69</v>
       </c>
@@ -10446,7 +10446,7 @@
         <v>354</v>
       </c>
     </row>
-    <row r="177" spans="2:13" x14ac:dyDescent="0.3">
+    <row r="177" spans="2:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="B177" t="s">
         <v>162</v>
       </c>
@@ -10476,7 +10476,7 @@
         <v>358</v>
       </c>
     </row>
-    <row r="178" spans="2:13" x14ac:dyDescent="0.3">
+    <row r="178" spans="2:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="B178" t="s">
         <v>162</v>
       </c>
@@ -10506,7 +10506,7 @@
         <v>358</v>
       </c>
     </row>
-    <row r="179" spans="2:13" x14ac:dyDescent="0.3">
+    <row r="179" spans="2:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="B179" t="s">
         <v>162</v>
       </c>
@@ -10536,7 +10536,7 @@
         <v>358</v>
       </c>
     </row>
-    <row r="180" spans="2:13" x14ac:dyDescent="0.3">
+    <row r="180" spans="2:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="B180" t="s">
         <v>162</v>
       </c>
@@ -10566,7 +10566,7 @@
         <v>358</v>
       </c>
     </row>
-    <row r="181" spans="2:13" x14ac:dyDescent="0.3">
+    <row r="181" spans="2:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="B181" t="s">
         <v>162</v>
       </c>
@@ -10596,7 +10596,7 @@
         <v>358</v>
       </c>
     </row>
-    <row r="182" spans="2:13" x14ac:dyDescent="0.3">
+    <row r="182" spans="2:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="B182" t="s">
         <v>162</v>
       </c>
@@ -10626,7 +10626,7 @@
         <v>358</v>
       </c>
     </row>
-    <row r="183" spans="2:13" x14ac:dyDescent="0.3">
+    <row r="183" spans="2:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="B183" t="s">
         <v>162</v>
       </c>
@@ -10656,7 +10656,7 @@
         <v>358</v>
       </c>
     </row>
-    <row r="184" spans="2:13" x14ac:dyDescent="0.3">
+    <row r="184" spans="2:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="B184" t="s">
         <v>162</v>
       </c>
@@ -10686,7 +10686,7 @@
         <v>358</v>
       </c>
     </row>
-    <row r="185" spans="2:13" x14ac:dyDescent="0.3">
+    <row r="185" spans="2:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="B185" t="s">
         <v>162</v>
       </c>
@@ -10716,7 +10716,7 @@
         <v>358</v>
       </c>
     </row>
-    <row r="186" spans="2:13" x14ac:dyDescent="0.3">
+    <row r="186" spans="2:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="B186" t="s">
         <v>162</v>
       </c>
@@ -10746,7 +10746,7 @@
         <v>358</v>
       </c>
     </row>
-    <row r="187" spans="2:13" x14ac:dyDescent="0.3">
+    <row r="187" spans="2:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="B187" t="s">
         <v>162</v>
       </c>
@@ -10776,7 +10776,7 @@
         <v>358</v>
       </c>
     </row>
-    <row r="188" spans="2:13" x14ac:dyDescent="0.3">
+    <row r="188" spans="2:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="B188" t="s">
         <v>162</v>
       </c>
@@ -10806,7 +10806,7 @@
         <v>358</v>
       </c>
     </row>
-    <row r="189" spans="2:13" x14ac:dyDescent="0.3">
+    <row r="189" spans="2:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="C189" t="s">
         <v>372</v>
       </c>
@@ -10833,7 +10833,7 @@
         <v>375</v>
       </c>
     </row>
-    <row r="190" spans="2:13" x14ac:dyDescent="0.3">
+    <row r="190" spans="2:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="C190" t="s">
         <v>372</v>
       </c>
@@ -10860,7 +10860,7 @@
         <v>375</v>
       </c>
     </row>
-    <row r="191" spans="2:13" x14ac:dyDescent="0.3">
+    <row r="191" spans="2:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="C191" t="s">
         <v>372</v>
       </c>
@@ -10887,7 +10887,7 @@
         <v>375</v>
       </c>
     </row>
-    <row r="192" spans="2:13" x14ac:dyDescent="0.3">
+    <row r="192" spans="2:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="C192" t="s">
         <v>372</v>
       </c>
@@ -10914,7 +10914,7 @@
         <v>375</v>
       </c>
     </row>
-    <row r="193" spans="3:13" x14ac:dyDescent="0.3">
+    <row r="193" spans="3:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="C193" t="s">
         <v>101</v>
       </c>
@@ -10941,7 +10941,7 @@
         <v>380</v>
       </c>
     </row>
-    <row r="194" spans="3:13" x14ac:dyDescent="0.3">
+    <row r="194" spans="3:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="C194" t="s">
         <v>101</v>
       </c>
@@ -10968,7 +10968,7 @@
         <v>380</v>
       </c>
     </row>
-    <row r="195" spans="3:13" x14ac:dyDescent="0.3">
+    <row r="195" spans="3:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="C195" t="s">
         <v>101</v>
       </c>
@@ -10995,7 +10995,7 @@
         <v>380</v>
       </c>
     </row>
-    <row r="196" spans="3:13" x14ac:dyDescent="0.3">
+    <row r="196" spans="3:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="C196" t="s">
         <v>101</v>
       </c>
@@ -11022,7 +11022,7 @@
         <v>380</v>
       </c>
     </row>
-    <row r="197" spans="3:13" x14ac:dyDescent="0.3">
+    <row r="197" spans="3:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="C197" t="s">
         <v>382</v>
       </c>
@@ -11052,7 +11052,7 @@
         <v>386</v>
       </c>
     </row>
-    <row r="198" spans="3:13" x14ac:dyDescent="0.3">
+    <row r="198" spans="3:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="C198" t="s">
         <v>382</v>
       </c>
@@ -11082,7 +11082,7 @@
         <v>386</v>
       </c>
     </row>
-    <row r="199" spans="3:13" x14ac:dyDescent="0.3">
+    <row r="199" spans="3:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="C199" t="s">
         <v>382</v>
       </c>
@@ -11112,7 +11112,7 @@
         <v>386</v>
       </c>
     </row>
-    <row r="200" spans="3:13" x14ac:dyDescent="0.3">
+    <row r="200" spans="3:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="C200" t="s">
         <v>382</v>
       </c>
@@ -11142,7 +11142,7 @@
         <v>386</v>
       </c>
     </row>
-    <row r="201" spans="3:13" x14ac:dyDescent="0.3">
+    <row r="201" spans="3:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="C201" t="s">
         <v>382</v>
       </c>
@@ -11172,7 +11172,7 @@
         <v>386</v>
       </c>
     </row>
-    <row r="202" spans="3:13" x14ac:dyDescent="0.3">
+    <row r="202" spans="3:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="C202" t="s">
         <v>110</v>
       </c>
@@ -11199,7 +11199,7 @@
         <v>396</v>
       </c>
     </row>
-    <row r="203" spans="3:13" x14ac:dyDescent="0.3">
+    <row r="203" spans="3:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="C203" t="s">
         <v>110</v>
       </c>
@@ -11226,7 +11226,7 @@
         <v>396</v>
       </c>
     </row>
-    <row r="204" spans="3:13" x14ac:dyDescent="0.3">
+    <row r="204" spans="3:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="C204" t="s">
         <v>110</v>
       </c>
@@ -11253,7 +11253,7 @@
         <v>396</v>
       </c>
     </row>
-    <row r="205" spans="3:13" x14ac:dyDescent="0.3">
+    <row r="205" spans="3:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="C205" t="s">
         <v>110</v>
       </c>
@@ -11280,7 +11280,7 @@
         <v>396</v>
       </c>
     </row>
-    <row r="206" spans="3:13" x14ac:dyDescent="0.3">
+    <row r="206" spans="3:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="C206" t="s">
         <v>399</v>
       </c>
@@ -11307,7 +11307,7 @@
         <v>402</v>
       </c>
     </row>
-    <row r="207" spans="3:13" x14ac:dyDescent="0.3">
+    <row r="207" spans="3:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="C207" t="s">
         <v>399</v>
       </c>
@@ -11334,7 +11334,7 @@
         <v>402</v>
       </c>
     </row>
-    <row r="208" spans="3:13" x14ac:dyDescent="0.3">
+    <row r="208" spans="3:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="C208" t="s">
         <v>399</v>
       </c>
@@ -11361,7 +11361,7 @@
         <v>402</v>
       </c>
     </row>
-    <row r="209" spans="2:13" x14ac:dyDescent="0.3">
+    <row r="209" spans="2:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="C209" t="s">
         <v>399</v>
       </c>
@@ -11388,7 +11388,7 @@
         <v>402</v>
       </c>
     </row>
-    <row r="210" spans="2:13" x14ac:dyDescent="0.3">
+    <row r="210" spans="2:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="B210" t="s">
         <v>162</v>
       </c>
@@ -11418,7 +11418,7 @@
         <v>407</v>
       </c>
     </row>
-    <row r="211" spans="2:13" x14ac:dyDescent="0.3">
+    <row r="211" spans="2:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="B211" t="s">
         <v>162</v>
       </c>
@@ -11448,7 +11448,7 @@
         <v>407</v>
       </c>
     </row>
-    <row r="212" spans="2:13" x14ac:dyDescent="0.3">
+    <row r="212" spans="2:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="B212" t="s">
         <v>162</v>
       </c>
@@ -11475,7 +11475,7 @@
         <v>407</v>
       </c>
     </row>
-    <row r="213" spans="2:13" x14ac:dyDescent="0.3">
+    <row r="213" spans="2:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="B213" t="s">
         <v>162</v>
       </c>
@@ -11505,7 +11505,7 @@
         <v>407</v>
       </c>
     </row>
-    <row r="214" spans="2:13" x14ac:dyDescent="0.3">
+    <row r="214" spans="2:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="B214" t="s">
         <v>162</v>
       </c>
@@ -11532,7 +11532,7 @@
         <v>407</v>
       </c>
     </row>
-    <row r="215" spans="2:13" x14ac:dyDescent="0.3">
+    <row r="215" spans="2:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="B215" t="s">
         <v>162</v>
       </c>
@@ -11562,7 +11562,7 @@
         <v>407</v>
       </c>
     </row>
-    <row r="216" spans="2:13" x14ac:dyDescent="0.3">
+    <row r="216" spans="2:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="B216" t="s">
         <v>162</v>
       </c>
@@ -11589,7 +11589,7 @@
         <v>407</v>
       </c>
     </row>
-    <row r="217" spans="2:13" x14ac:dyDescent="0.3">
+    <row r="217" spans="2:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="B217" t="s">
         <v>162</v>
       </c>
@@ -11616,7 +11616,7 @@
         <v>407</v>
       </c>
     </row>
-    <row r="218" spans="2:13" x14ac:dyDescent="0.3">
+    <row r="218" spans="2:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="B218" t="s">
         <v>162</v>
       </c>
@@ -11646,7 +11646,7 @@
         <v>407</v>
       </c>
     </row>
-    <row r="219" spans="2:13" x14ac:dyDescent="0.3">
+    <row r="219" spans="2:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="B219" t="s">
         <v>162</v>
       </c>
@@ -11673,7 +11673,7 @@
         <v>407</v>
       </c>
     </row>
-    <row r="220" spans="2:13" x14ac:dyDescent="0.3">
+    <row r="220" spans="2:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="B220" t="s">
         <v>162</v>
       </c>
@@ -11703,7 +11703,7 @@
         <v>407</v>
       </c>
     </row>
-    <row r="221" spans="2:13" x14ac:dyDescent="0.3">
+    <row r="221" spans="2:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="B221" t="s">
         <v>162</v>
       </c>
@@ -11733,7 +11733,7 @@
         <v>407</v>
       </c>
     </row>
-    <row r="222" spans="2:13" x14ac:dyDescent="0.3">
+    <row r="222" spans="2:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="C222" t="s">
         <v>129</v>
       </c>
@@ -11760,7 +11760,7 @@
         <v>412</v>
       </c>
     </row>
-    <row r="223" spans="2:13" x14ac:dyDescent="0.3">
+    <row r="223" spans="2:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="C223" t="s">
         <v>129</v>
       </c>
@@ -11787,7 +11787,7 @@
         <v>412</v>
       </c>
     </row>
-    <row r="224" spans="2:13" x14ac:dyDescent="0.3">
+    <row r="224" spans="2:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="C224" t="s">
         <v>129</v>
       </c>
@@ -11814,7 +11814,7 @@
         <v>412</v>
       </c>
     </row>
-    <row r="225" spans="2:13" x14ac:dyDescent="0.3">
+    <row r="225" spans="2:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="C225" t="s">
         <v>129</v>
       </c>
@@ -11841,7 +11841,7 @@
         <v>412</v>
       </c>
     </row>
-    <row r="226" spans="2:13" x14ac:dyDescent="0.3">
+    <row r="226" spans="2:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="B226" t="s">
         <v>137</v>
       </c>
@@ -11871,7 +11871,7 @@
         <v>420</v>
       </c>
     </row>
-    <row r="227" spans="2:13" x14ac:dyDescent="0.3">
+    <row r="227" spans="2:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="B227" t="s">
         <v>137</v>
       </c>
@@ -11901,7 +11901,7 @@
         <v>420</v>
       </c>
     </row>
-    <row r="228" spans="2:13" x14ac:dyDescent="0.3">
+    <row r="228" spans="2:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="C228" t="s">
         <v>150</v>
       </c>
@@ -11928,7 +11928,7 @@
         <v>425</v>
       </c>
     </row>
-    <row r="229" spans="2:13" x14ac:dyDescent="0.3">
+    <row r="229" spans="2:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="C229" t="s">
         <v>150</v>
       </c>
@@ -11955,7 +11955,7 @@
         <v>425</v>
       </c>
     </row>
-    <row r="230" spans="2:13" x14ac:dyDescent="0.3">
+    <row r="230" spans="2:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="C230" t="s">
         <v>150</v>
       </c>
@@ -11982,7 +11982,7 @@
         <v>425</v>
       </c>
     </row>
-    <row r="231" spans="2:13" x14ac:dyDescent="0.3">
+    <row r="231" spans="2:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="C231" t="s">
         <v>150</v>
       </c>
@@ -12009,7 +12009,7 @@
         <v>425</v>
       </c>
     </row>
-    <row r="232" spans="2:13" x14ac:dyDescent="0.3">
+    <row r="232" spans="2:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="C232" t="s">
         <v>294</v>
       </c>
@@ -12039,7 +12039,7 @@
         <v>432</v>
       </c>
     </row>
-    <row r="233" spans="2:13" x14ac:dyDescent="0.3">
+    <row r="233" spans="2:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="C233" t="s">
         <v>294</v>
       </c>
@@ -12069,7 +12069,7 @@
         <v>432</v>
       </c>
     </row>
-    <row r="234" spans="2:13" x14ac:dyDescent="0.3">
+    <row r="234" spans="2:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="C234" t="s">
         <v>294</v>
       </c>
@@ -12099,7 +12099,7 @@
         <v>432</v>
       </c>
     </row>
-    <row r="235" spans="2:13" x14ac:dyDescent="0.3">
+    <row r="235" spans="2:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="C235" t="s">
         <v>294</v>
       </c>
@@ -12129,7 +12129,7 @@
         <v>432</v>
       </c>
     </row>
-    <row r="236" spans="2:13" x14ac:dyDescent="0.3">
+    <row r="236" spans="2:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="B236" t="s">
         <v>302</v>
       </c>
@@ -12159,7 +12159,7 @@
         <v>439</v>
       </c>
     </row>
-    <row r="237" spans="2:13" x14ac:dyDescent="0.3">
+    <row r="237" spans="2:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="B237" t="s">
         <v>302</v>
       </c>
@@ -12189,7 +12189,7 @@
         <v>439</v>
       </c>
     </row>
-    <row r="238" spans="2:13" x14ac:dyDescent="0.3">
+    <row r="238" spans="2:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="B238" t="s">
         <v>302</v>
       </c>
@@ -12219,7 +12219,7 @@
         <v>439</v>
       </c>
     </row>
-    <row r="239" spans="2:13" x14ac:dyDescent="0.3">
+    <row r="239" spans="2:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="B239" t="s">
         <v>302</v>
       </c>
@@ -12249,7 +12249,7 @@
         <v>439</v>
       </c>
     </row>
-    <row r="240" spans="2:13" x14ac:dyDescent="0.3">
+    <row r="240" spans="2:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="B240" t="s">
         <v>137</v>
       </c>
@@ -12279,7 +12279,7 @@
         <v>448</v>
       </c>
     </row>
-    <row r="241" spans="2:13" x14ac:dyDescent="0.3">
+    <row r="241" spans="2:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="B241" t="s">
         <v>137</v>
       </c>
@@ -12309,7 +12309,7 @@
         <v>448</v>
       </c>
     </row>
-    <row r="242" spans="2:13" x14ac:dyDescent="0.3">
+    <row r="242" spans="2:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="B242" t="s">
         <v>137</v>
       </c>
@@ -12339,7 +12339,7 @@
         <v>448</v>
       </c>
     </row>
-    <row r="243" spans="2:13" x14ac:dyDescent="0.3">
+    <row r="243" spans="2:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="B243" t="s">
         <v>137</v>
       </c>
@@ -12369,7 +12369,7 @@
         <v>448</v>
       </c>
     </row>
-    <row r="244" spans="2:13" x14ac:dyDescent="0.3">
+    <row r="244" spans="2:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="C244" t="s">
         <v>27</v>
       </c>
@@ -12399,7 +12399,7 @@
         <v>455</v>
       </c>
     </row>
-    <row r="245" spans="2:13" x14ac:dyDescent="0.3">
+    <row r="245" spans="2:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="C245" t="s">
         <v>27</v>
       </c>
@@ -12429,7 +12429,7 @@
         <v>455</v>
       </c>
     </row>
-    <row r="246" spans="2:13" x14ac:dyDescent="0.3">
+    <row r="246" spans="2:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="C246" t="s">
         <v>27</v>
       </c>
@@ -12459,7 +12459,7 @@
         <v>455</v>
       </c>
     </row>
-    <row r="247" spans="2:13" x14ac:dyDescent="0.3">
+    <row r="247" spans="2:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="C247" t="s">
         <v>27</v>
       </c>
@@ -12489,7 +12489,7 @@
         <v>455</v>
       </c>
     </row>
-    <row r="248" spans="2:13" x14ac:dyDescent="0.3">
+    <row r="248" spans="2:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="C248" t="s">
         <v>45</v>
       </c>
@@ -12519,7 +12519,7 @@
         <v>460</v>
       </c>
     </row>
-    <row r="249" spans="2:13" x14ac:dyDescent="0.3">
+    <row r="249" spans="2:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="C249" t="s">
         <v>45</v>
       </c>
@@ -12549,7 +12549,7 @@
         <v>460</v>
       </c>
     </row>
-    <row r="250" spans="2:13" x14ac:dyDescent="0.3">
+    <row r="250" spans="2:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="C250" t="s">
         <v>45</v>
       </c>
@@ -12579,7 +12579,7 @@
         <v>460</v>
       </c>
     </row>
-    <row r="251" spans="2:13" x14ac:dyDescent="0.3">
+    <row r="251" spans="2:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="C251" t="s">
         <v>45</v>
       </c>
@@ -12609,7 +12609,7 @@
         <v>460</v>
       </c>
     </row>
-    <row r="252" spans="2:13" x14ac:dyDescent="0.3">
+    <row r="252" spans="2:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="C252" t="s">
         <v>45</v>
       </c>
@@ -12639,7 +12639,7 @@
         <v>460</v>
       </c>
     </row>
-    <row r="253" spans="2:13" x14ac:dyDescent="0.3">
+    <row r="253" spans="2:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="C253" t="s">
         <v>45</v>
       </c>
@@ -12669,7 +12669,7 @@
         <v>460</v>
       </c>
     </row>
-    <row r="254" spans="2:13" x14ac:dyDescent="0.3">
+    <row r="254" spans="2:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="B254" t="s">
         <v>137</v>
       </c>
@@ -12699,7 +12699,7 @@
         <v>470</v>
       </c>
     </row>
-    <row r="255" spans="2:13" x14ac:dyDescent="0.3">
+    <row r="255" spans="2:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="B255" t="s">
         <v>137</v>
       </c>
@@ -12729,7 +12729,7 @@
         <v>470</v>
       </c>
     </row>
-    <row r="256" spans="2:13" x14ac:dyDescent="0.3">
+    <row r="256" spans="2:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="B256" t="s">
         <v>137</v>
       </c>
@@ -12759,7 +12759,7 @@
         <v>470</v>
       </c>
     </row>
-    <row r="257" spans="2:13" x14ac:dyDescent="0.3">
+    <row r="257" spans="2:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="B257" t="s">
         <v>137</v>
       </c>
@@ -12789,7 +12789,7 @@
         <v>470</v>
       </c>
     </row>
-    <row r="258" spans="2:13" x14ac:dyDescent="0.3">
+    <row r="258" spans="2:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="B258" t="s">
         <v>137</v>
       </c>
@@ -12819,7 +12819,7 @@
         <v>470</v>
       </c>
     </row>
-    <row r="259" spans="2:13" x14ac:dyDescent="0.3">
+    <row r="259" spans="2:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="C259" t="s">
         <v>69</v>
       </c>
@@ -12849,7 +12849,7 @@
         <v>483</v>
       </c>
     </row>
-    <row r="260" spans="2:13" x14ac:dyDescent="0.3">
+    <row r="260" spans="2:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="C260" t="s">
         <v>69</v>
       </c>
@@ -12879,7 +12879,7 @@
         <v>483</v>
       </c>
     </row>
-    <row r="261" spans="2:13" x14ac:dyDescent="0.3">
+    <row r="261" spans="2:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="C261" t="s">
         <v>69</v>
       </c>
@@ -12909,7 +12909,7 @@
         <v>483</v>
       </c>
     </row>
-    <row r="262" spans="2:13" x14ac:dyDescent="0.3">
+    <row r="262" spans="2:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="C262" t="s">
         <v>69</v>
       </c>
@@ -12939,7 +12939,7 @@
         <v>483</v>
       </c>
     </row>
-    <row r="263" spans="2:13" x14ac:dyDescent="0.3">
+    <row r="263" spans="2:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="C263" t="s">
         <v>69</v>
       </c>
@@ -12969,7 +12969,7 @@
         <v>483</v>
       </c>
     </row>
-    <row r="264" spans="2:13" x14ac:dyDescent="0.3">
+    <row r="264" spans="2:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="C264" t="s">
         <v>69</v>
       </c>
@@ -12999,7 +12999,7 @@
         <v>483</v>
       </c>
     </row>
-    <row r="265" spans="2:13" x14ac:dyDescent="0.3">
+    <row r="265" spans="2:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="C265" t="s">
         <v>69</v>
       </c>
@@ -13029,7 +13029,7 @@
         <v>483</v>
       </c>
     </row>
-    <row r="266" spans="2:13" x14ac:dyDescent="0.3">
+    <row r="266" spans="2:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="C266" t="s">
         <v>69</v>
       </c>
@@ -13059,7 +13059,7 @@
         <v>483</v>
       </c>
     </row>
-    <row r="267" spans="2:13" x14ac:dyDescent="0.3">
+    <row r="267" spans="2:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="B267" t="s">
         <v>162</v>
       </c>
@@ -13089,7 +13089,7 @@
         <v>493</v>
       </c>
     </row>
-    <row r="268" spans="2:13" x14ac:dyDescent="0.3">
+    <row r="268" spans="2:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="B268" t="s">
         <v>162</v>
       </c>
@@ -13119,7 +13119,7 @@
         <v>493</v>
       </c>
     </row>
-    <row r="269" spans="2:13" x14ac:dyDescent="0.3">
+    <row r="269" spans="2:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="B269" t="s">
         <v>162</v>
       </c>
@@ -13149,7 +13149,7 @@
         <v>493</v>
       </c>
     </row>
-    <row r="270" spans="2:13" x14ac:dyDescent="0.3">
+    <row r="270" spans="2:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="B270" t="s">
         <v>162</v>
       </c>
@@ -13179,7 +13179,7 @@
         <v>493</v>
       </c>
     </row>
-    <row r="271" spans="2:13" x14ac:dyDescent="0.3">
+    <row r="271" spans="2:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="B271" t="s">
         <v>162</v>
       </c>
@@ -13209,7 +13209,7 @@
         <v>493</v>
       </c>
     </row>
-    <row r="272" spans="2:13" x14ac:dyDescent="0.3">
+    <row r="272" spans="2:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="B272" t="s">
         <v>162</v>
       </c>
@@ -13239,7 +13239,7 @@
         <v>493</v>
       </c>
     </row>
-    <row r="273" spans="2:13" x14ac:dyDescent="0.3">
+    <row r="273" spans="2:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="B273" t="s">
         <v>162</v>
       </c>
@@ -13269,7 +13269,7 @@
         <v>493</v>
       </c>
     </row>
-    <row r="274" spans="2:13" x14ac:dyDescent="0.3">
+    <row r="274" spans="2:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="B274" t="s">
         <v>162</v>
       </c>
@@ -13299,7 +13299,7 @@
         <v>493</v>
       </c>
     </row>
-    <row r="275" spans="2:13" x14ac:dyDescent="0.3">
+    <row r="275" spans="2:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="B275" t="s">
         <v>162</v>
       </c>
@@ -13329,7 +13329,7 @@
         <v>493</v>
       </c>
     </row>
-    <row r="276" spans="2:13" x14ac:dyDescent="0.3">
+    <row r="276" spans="2:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="B276" t="s">
         <v>162</v>
       </c>
@@ -13359,7 +13359,7 @@
         <v>493</v>
       </c>
     </row>
-    <row r="277" spans="2:13" x14ac:dyDescent="0.3">
+    <row r="277" spans="2:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="B277" t="s">
         <v>162</v>
       </c>
@@ -13389,7 +13389,7 @@
         <v>493</v>
       </c>
     </row>
-    <row r="278" spans="2:13" x14ac:dyDescent="0.3">
+    <row r="278" spans="2:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="B278" t="s">
         <v>162</v>
       </c>
@@ -13419,7 +13419,7 @@
         <v>493</v>
       </c>
     </row>
-    <row r="279" spans="2:13" x14ac:dyDescent="0.3">
+    <row r="279" spans="2:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="C279" t="s">
         <v>90</v>
       </c>
@@ -13449,7 +13449,7 @@
         <v>507</v>
       </c>
     </row>
-    <row r="280" spans="2:13" x14ac:dyDescent="0.3">
+    <row r="280" spans="2:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="C280" t="s">
         <v>90</v>
       </c>
@@ -13479,7 +13479,7 @@
         <v>507</v>
       </c>
     </row>
-    <row r="281" spans="2:13" x14ac:dyDescent="0.3">
+    <row r="281" spans="2:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="C281" t="s">
         <v>90</v>
       </c>
@@ -13509,7 +13509,7 @@
         <v>507</v>
       </c>
     </row>
-    <row r="282" spans="2:13" x14ac:dyDescent="0.3">
+    <row r="282" spans="2:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="C282" t="s">
         <v>90</v>
       </c>
@@ -13539,7 +13539,7 @@
         <v>507</v>
       </c>
     </row>
-    <row r="283" spans="2:13" x14ac:dyDescent="0.3">
+    <row r="283" spans="2:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="C283" t="s">
         <v>90</v>
       </c>
@@ -13569,7 +13569,7 @@
         <v>507</v>
       </c>
     </row>
-    <row r="284" spans="2:13" x14ac:dyDescent="0.3">
+    <row r="284" spans="2:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="C284" t="s">
         <v>90</v>
       </c>
@@ -13599,7 +13599,7 @@
         <v>507</v>
       </c>
     </row>
-    <row r="285" spans="2:13" x14ac:dyDescent="0.3">
+    <row r="285" spans="2:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="C285" t="s">
         <v>90</v>
       </c>
@@ -13629,7 +13629,7 @@
         <v>507</v>
       </c>
     </row>
-    <row r="286" spans="2:13" x14ac:dyDescent="0.3">
+    <row r="286" spans="2:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="C286" t="s">
         <v>90</v>
       </c>
@@ -13659,7 +13659,7 @@
         <v>507</v>
       </c>
     </row>
-    <row r="287" spans="2:13" x14ac:dyDescent="0.3">
+    <row r="287" spans="2:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="C287" t="s">
         <v>516</v>
       </c>
@@ -13689,7 +13689,7 @@
         <v>520</v>
       </c>
     </row>
-    <row r="288" spans="2:13" x14ac:dyDescent="0.3">
+    <row r="288" spans="2:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="C288" t="s">
         <v>516</v>
       </c>
@@ -13719,7 +13719,7 @@
         <v>520</v>
       </c>
     </row>
-    <row r="289" spans="3:13" x14ac:dyDescent="0.3">
+    <row r="289" spans="3:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="C289" t="s">
         <v>516</v>
       </c>
@@ -13749,7 +13749,7 @@
         <v>520</v>
       </c>
     </row>
-    <row r="290" spans="3:13" x14ac:dyDescent="0.3">
+    <row r="290" spans="3:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="C290" t="s">
         <v>516</v>
       </c>
@@ -13779,7 +13779,7 @@
         <v>520</v>
       </c>
     </row>
-    <row r="291" spans="3:13" x14ac:dyDescent="0.3">
+    <row r="291" spans="3:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="C291" t="s">
         <v>516</v>
       </c>
@@ -13809,7 +13809,7 @@
         <v>520</v>
       </c>
     </row>
-    <row r="292" spans="3:13" x14ac:dyDescent="0.3">
+    <row r="292" spans="3:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="C292" t="s">
         <v>516</v>
       </c>
@@ -13839,7 +13839,7 @@
         <v>520</v>
       </c>
     </row>
-    <row r="293" spans="3:13" x14ac:dyDescent="0.3">
+    <row r="293" spans="3:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="C293" t="s">
         <v>516</v>
       </c>
@@ -13869,7 +13869,7 @@
         <v>520</v>
       </c>
     </row>
-    <row r="294" spans="3:13" x14ac:dyDescent="0.3">
+    <row r="294" spans="3:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="C294" t="s">
         <v>516</v>
       </c>
@@ -13899,7 +13899,7 @@
         <v>520</v>
       </c>
     </row>
-    <row r="295" spans="3:13" x14ac:dyDescent="0.3">
+    <row r="295" spans="3:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="C295" t="s">
         <v>101</v>
       </c>
@@ -13929,7 +13929,7 @@
         <v>537</v>
       </c>
     </row>
-    <row r="296" spans="3:13" x14ac:dyDescent="0.3">
+    <row r="296" spans="3:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="C296" t="s">
         <v>101</v>
       </c>
@@ -13959,7 +13959,7 @@
         <v>537</v>
       </c>
     </row>
-    <row r="297" spans="3:13" x14ac:dyDescent="0.3">
+    <row r="297" spans="3:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="C297" t="s">
         <v>101</v>
       </c>
@@ -13989,7 +13989,7 @@
         <v>537</v>
       </c>
     </row>
-    <row r="298" spans="3:13" x14ac:dyDescent="0.3">
+    <row r="298" spans="3:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="C298" t="s">
         <v>101</v>
       </c>
@@ -14019,7 +14019,7 @@
         <v>537</v>
       </c>
     </row>
-    <row r="299" spans="3:13" x14ac:dyDescent="0.3">
+    <row r="299" spans="3:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="C299" t="s">
         <v>110</v>
       </c>
@@ -14049,7 +14049,7 @@
         <v>543</v>
       </c>
     </row>
-    <row r="300" spans="3:13" x14ac:dyDescent="0.3">
+    <row r="300" spans="3:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="C300" t="s">
         <v>110</v>
       </c>
@@ -14079,7 +14079,7 @@
         <v>543</v>
       </c>
     </row>
-    <row r="301" spans="3:13" x14ac:dyDescent="0.3">
+    <row r="301" spans="3:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="C301" t="s">
         <v>110</v>
       </c>
@@ -14109,7 +14109,7 @@
         <v>543</v>
       </c>
     </row>
-    <row r="302" spans="3:13" x14ac:dyDescent="0.3">
+    <row r="302" spans="3:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="C302" t="s">
         <v>110</v>
       </c>
@@ -14139,7 +14139,7 @@
         <v>543</v>
       </c>
     </row>
-    <row r="303" spans="3:13" x14ac:dyDescent="0.3">
+    <row r="303" spans="3:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="C303" t="s">
         <v>399</v>
       </c>
@@ -14169,7 +14169,7 @@
         <v>548</v>
       </c>
     </row>
-    <row r="304" spans="3:13" x14ac:dyDescent="0.3">
+    <row r="304" spans="3:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="C304" t="s">
         <v>399</v>
       </c>
@@ -14199,7 +14199,7 @@
         <v>548</v>
       </c>
     </row>
-    <row r="305" spans="2:13" x14ac:dyDescent="0.3">
+    <row r="305" spans="2:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="C305" t="s">
         <v>399</v>
       </c>
@@ -14229,7 +14229,7 @@
         <v>548</v>
       </c>
     </row>
-    <row r="306" spans="2:13" x14ac:dyDescent="0.3">
+    <row r="306" spans="2:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="C306" t="s">
         <v>399</v>
       </c>
@@ -14259,7 +14259,7 @@
         <v>548</v>
       </c>
     </row>
-    <row r="307" spans="2:13" x14ac:dyDescent="0.3">
+    <row r="307" spans="2:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="B307" t="s">
         <v>162</v>
       </c>
@@ -14289,7 +14289,7 @@
         <v>553</v>
       </c>
     </row>
-    <row r="308" spans="2:13" x14ac:dyDescent="0.3">
+    <row r="308" spans="2:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="B308" t="s">
         <v>162</v>
       </c>
@@ -14319,7 +14319,7 @@
         <v>553</v>
       </c>
     </row>
-    <row r="309" spans="2:13" x14ac:dyDescent="0.3">
+    <row r="309" spans="2:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="B309" t="s">
         <v>162</v>
       </c>
@@ -14349,7 +14349,7 @@
         <v>553</v>
       </c>
     </row>
-    <row r="310" spans="2:13" x14ac:dyDescent="0.3">
+    <row r="310" spans="2:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="B310" t="s">
         <v>162</v>
       </c>
@@ -14379,7 +14379,7 @@
         <v>553</v>
       </c>
     </row>
-    <row r="311" spans="2:13" x14ac:dyDescent="0.3">
+    <row r="311" spans="2:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="B311" t="s">
         <v>162</v>
       </c>
@@ -14409,7 +14409,7 @@
         <v>553</v>
       </c>
     </row>
-    <row r="312" spans="2:13" x14ac:dyDescent="0.3">
+    <row r="312" spans="2:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="B312" t="s">
         <v>162</v>
       </c>
@@ -14439,7 +14439,7 @@
         <v>553</v>
       </c>
     </row>
-    <row r="313" spans="2:13" x14ac:dyDescent="0.3">
+    <row r="313" spans="2:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="B313" t="s">
         <v>162</v>
       </c>
@@ -14469,7 +14469,7 @@
         <v>553</v>
       </c>
     </row>
-    <row r="314" spans="2:13" x14ac:dyDescent="0.3">
+    <row r="314" spans="2:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="B314" t="s">
         <v>162</v>
       </c>
@@ -14499,7 +14499,7 @@
         <v>553</v>
       </c>
     </row>
-    <row r="315" spans="2:13" x14ac:dyDescent="0.3">
+    <row r="315" spans="2:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="B315" t="s">
         <v>162</v>
       </c>
@@ -14529,7 +14529,7 @@
         <v>553</v>
       </c>
     </row>
-    <row r="316" spans="2:13" x14ac:dyDescent="0.3">
+    <row r="316" spans="2:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="B316" t="s">
         <v>162</v>
       </c>
@@ -14559,7 +14559,7 @@
         <v>553</v>
       </c>
     </row>
-    <row r="317" spans="2:13" x14ac:dyDescent="0.3">
+    <row r="317" spans="2:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="B317" t="s">
         <v>162</v>
       </c>
@@ -14589,7 +14589,7 @@
         <v>553</v>
       </c>
     </row>
-    <row r="318" spans="2:13" x14ac:dyDescent="0.3">
+    <row r="318" spans="2:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="B318" t="s">
         <v>162</v>
       </c>
@@ -14619,7 +14619,7 @@
         <v>553</v>
       </c>
     </row>
-    <row r="319" spans="2:13" x14ac:dyDescent="0.3">
+    <row r="319" spans="2:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="C319" t="s">
         <v>129</v>
       </c>
@@ -14649,7 +14649,7 @@
         <v>568</v>
       </c>
     </row>
-    <row r="320" spans="2:13" x14ac:dyDescent="0.3">
+    <row r="320" spans="2:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="C320" t="s">
         <v>129</v>
       </c>
@@ -14679,7 +14679,7 @@
         <v>568</v>
       </c>
     </row>
-    <row r="321" spans="2:13" x14ac:dyDescent="0.3">
+    <row r="321" spans="2:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="C321" t="s">
         <v>129</v>
       </c>
@@ -14709,7 +14709,7 @@
         <v>568</v>
       </c>
     </row>
-    <row r="322" spans="2:13" x14ac:dyDescent="0.3">
+    <row r="322" spans="2:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="C322" t="s">
         <v>129</v>
       </c>
@@ -14739,7 +14739,7 @@
         <v>568</v>
       </c>
     </row>
-    <row r="323" spans="2:13" x14ac:dyDescent="0.3">
+    <row r="323" spans="2:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="C323" t="s">
         <v>154</v>
       </c>
@@ -14759,6 +14759,9 @@
       <c r="I323">
         <v>3</v>
       </c>
+      <c r="J323" t="s">
+        <v>1066</v>
+      </c>
       <c r="K323" s="9" t="s">
         <v>575</v>
       </c>
@@ -14769,7 +14772,7 @@
         <v>577</v>
       </c>
     </row>
-    <row r="324" spans="2:13" x14ac:dyDescent="0.3">
+    <row r="324" spans="2:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="C324" t="s">
         <v>154</v>
       </c>
@@ -14799,7 +14802,7 @@
         <v>577</v>
       </c>
     </row>
-    <row r="325" spans="2:13" x14ac:dyDescent="0.3">
+    <row r="325" spans="2:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="C325" t="s">
         <v>154</v>
       </c>
@@ -14819,6 +14822,9 @@
       <c r="I325">
         <v>2</v>
       </c>
+      <c r="J325" t="s">
+        <v>1066</v>
+      </c>
       <c r="K325" s="9" t="s">
         <v>580</v>
       </c>
@@ -14829,7 +14835,7 @@
         <v>577</v>
       </c>
     </row>
-    <row r="326" spans="2:13" x14ac:dyDescent="0.3">
+    <row r="326" spans="2:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="C326" t="s">
         <v>154</v>
       </c>
@@ -14859,7 +14865,7 @@
         <v>577</v>
       </c>
     </row>
-    <row r="327" spans="2:13" x14ac:dyDescent="0.3">
+    <row r="327" spans="2:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="C327" t="s">
         <v>154</v>
       </c>
@@ -14879,6 +14885,9 @@
       <c r="I327">
         <v>3</v>
       </c>
+      <c r="J327" t="s">
+        <v>1066</v>
+      </c>
       <c r="K327" s="9" t="s">
         <v>584</v>
       </c>
@@ -14889,7 +14898,7 @@
         <v>577</v>
       </c>
     </row>
-    <row r="328" spans="2:13" x14ac:dyDescent="0.3">
+    <row r="328" spans="2:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="C328" t="s">
         <v>154</v>
       </c>
@@ -14909,6 +14918,9 @@
       <c r="I328">
         <v>3</v>
       </c>
+      <c r="J328" t="s">
+        <v>1066</v>
+      </c>
       <c r="K328" s="9" t="s">
         <v>586</v>
       </c>
@@ -14919,7 +14931,7 @@
         <v>577</v>
       </c>
     </row>
-    <row r="329" spans="2:13" x14ac:dyDescent="0.3">
+    <row r="329" spans="2:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="C329" t="s">
         <v>154</v>
       </c>
@@ -14939,6 +14951,9 @@
       <c r="I329">
         <v>2</v>
       </c>
+      <c r="J329" t="s">
+        <v>1066</v>
+      </c>
       <c r="K329" s="9" t="s">
         <v>588</v>
       </c>
@@ -14949,7 +14964,7 @@
         <v>577</v>
       </c>
     </row>
-    <row r="330" spans="2:13" x14ac:dyDescent="0.3">
+    <row r="330" spans="2:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="C330" t="s">
         <v>154</v>
       </c>
@@ -14979,7 +14994,7 @@
         <v>577</v>
       </c>
     </row>
-    <row r="331" spans="2:13" x14ac:dyDescent="0.3">
+    <row r="331" spans="2:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="B331" t="s">
         <v>592</v>
       </c>
@@ -15002,6 +15017,9 @@
       <c r="I331">
         <v>3</v>
       </c>
+      <c r="J331" t="s">
+        <v>1066</v>
+      </c>
       <c r="K331" s="9" t="s">
         <v>586</v>
       </c>
@@ -15012,7 +15030,7 @@
         <v>596</v>
       </c>
     </row>
-    <row r="332" spans="2:13" x14ac:dyDescent="0.3">
+    <row r="332" spans="2:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="B332" t="s">
         <v>592</v>
       </c>
@@ -15035,6 +15053,9 @@
       <c r="I332">
         <v>3</v>
       </c>
+      <c r="J332" t="s">
+        <v>1066</v>
+      </c>
       <c r="K332" s="9" t="s">
         <v>597</v>
       </c>
@@ -15045,7 +15066,7 @@
         <v>596</v>
       </c>
     </row>
-    <row r="333" spans="2:13" x14ac:dyDescent="0.3">
+    <row r="333" spans="2:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="B333" t="s">
         <v>592</v>
       </c>
@@ -15078,7 +15099,7 @@
         <v>596</v>
       </c>
     </row>
-    <row r="334" spans="2:13" x14ac:dyDescent="0.3">
+    <row r="334" spans="2:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="B334" t="s">
         <v>592</v>
       </c>
@@ -15101,6 +15122,9 @@
       <c r="I334">
         <v>1</v>
       </c>
+      <c r="J334" t="s">
+        <v>1066</v>
+      </c>
       <c r="K334" s="9" t="s">
         <v>601</v>
       </c>
@@ -15111,7 +15135,7 @@
         <v>596</v>
       </c>
     </row>
-    <row r="335" spans="2:13" x14ac:dyDescent="0.3">
+    <row r="335" spans="2:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="B335" t="s">
         <v>592</v>
       </c>
@@ -15134,6 +15158,9 @@
       <c r="I335">
         <v>3</v>
       </c>
+      <c r="J335" t="s">
+        <v>1066</v>
+      </c>
       <c r="K335" s="9" t="s">
         <v>603</v>
       </c>
@@ -15144,7 +15171,7 @@
         <v>596</v>
       </c>
     </row>
-    <row r="336" spans="2:13" x14ac:dyDescent="0.3">
+    <row r="336" spans="2:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="B336" t="s">
         <v>592</v>
       </c>
@@ -15167,6 +15194,9 @@
       <c r="I336">
         <v>3</v>
       </c>
+      <c r="J336" t="s">
+        <v>1066</v>
+      </c>
       <c r="K336" s="9" t="s">
         <v>605</v>
       </c>
@@ -15177,7 +15207,7 @@
         <v>596</v>
       </c>
     </row>
-    <row r="337" spans="2:13" x14ac:dyDescent="0.3">
+    <row r="337" spans="2:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="B337" t="s">
         <v>592</v>
       </c>
@@ -15210,7 +15240,7 @@
         <v>596</v>
       </c>
     </row>
-    <row r="338" spans="2:13" x14ac:dyDescent="0.3">
+    <row r="338" spans="2:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="B338" t="s">
         <v>592</v>
       </c>
@@ -15243,7 +15273,7 @@
         <v>596</v>
       </c>
     </row>
-    <row r="339" spans="2:13" x14ac:dyDescent="0.3">
+    <row r="339" spans="2:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="C339" t="s">
         <v>150</v>
       </c>
@@ -15273,7 +15303,7 @@
         <v>612</v>
       </c>
     </row>
-    <row r="340" spans="2:13" x14ac:dyDescent="0.3">
+    <row r="340" spans="2:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="C340" t="s">
         <v>150</v>
       </c>
@@ -15303,7 +15333,7 @@
         <v>612</v>
       </c>
     </row>
-    <row r="341" spans="2:13" x14ac:dyDescent="0.3">
+    <row r="341" spans="2:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="C341" t="s">
         <v>150</v>
       </c>
@@ -15333,7 +15363,7 @@
         <v>612</v>
       </c>
     </row>
-    <row r="342" spans="2:13" x14ac:dyDescent="0.3">
+    <row r="342" spans="2:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="C342" t="s">
         <v>150</v>
       </c>
@@ -15363,7 +15393,7 @@
         <v>612</v>
       </c>
     </row>
-    <row r="343" spans="2:13" x14ac:dyDescent="0.3">
+    <row r="343" spans="2:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="B343" t="s">
         <v>302</v>
       </c>
@@ -15393,7 +15423,7 @@
         <v>618</v>
       </c>
     </row>
-    <row r="344" spans="2:13" x14ac:dyDescent="0.3">
+    <row r="344" spans="2:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="B344" t="s">
         <v>302</v>
       </c>
@@ -15423,7 +15453,7 @@
         <v>618</v>
       </c>
     </row>
-    <row r="345" spans="2:13" x14ac:dyDescent="0.3">
+    <row r="345" spans="2:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="B345" t="s">
         <v>302</v>
       </c>
@@ -15453,7 +15483,7 @@
         <v>618</v>
       </c>
     </row>
-    <row r="346" spans="2:13" x14ac:dyDescent="0.3">
+    <row r="346" spans="2:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="B346" t="s">
         <v>302</v>
       </c>
@@ -15483,7 +15513,7 @@
         <v>618</v>
       </c>
     </row>
-    <row r="347" spans="2:13" x14ac:dyDescent="0.3">
+    <row r="347" spans="2:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="C347" t="s">
         <v>154</v>
       </c>
@@ -15513,7 +15543,7 @@
         <v>626</v>
       </c>
     </row>
-    <row r="348" spans="2:13" x14ac:dyDescent="0.3">
+    <row r="348" spans="2:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="C348" t="s">
         <v>154</v>
       </c>
@@ -15543,7 +15573,7 @@
         <v>626</v>
       </c>
     </row>
-    <row r="349" spans="2:13" x14ac:dyDescent="0.3">
+    <row r="349" spans="2:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="C349" t="s">
         <v>154</v>
       </c>
@@ -15573,7 +15603,7 @@
         <v>626</v>
       </c>
     </row>
-    <row r="350" spans="2:13" x14ac:dyDescent="0.3">
+    <row r="350" spans="2:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="C350" t="s">
         <v>154</v>
       </c>
@@ -15603,7 +15633,7 @@
         <v>626</v>
       </c>
     </row>
-    <row r="351" spans="2:13" x14ac:dyDescent="0.3">
+    <row r="351" spans="2:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="C351" t="s">
         <v>154</v>
       </c>
@@ -15633,7 +15663,7 @@
         <v>626</v>
       </c>
     </row>
-    <row r="352" spans="2:13" x14ac:dyDescent="0.3">
+    <row r="352" spans="2:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="C352" t="s">
         <v>154</v>
       </c>
@@ -15663,7 +15693,7 @@
         <v>626</v>
       </c>
     </row>
-    <row r="353" spans="3:13" x14ac:dyDescent="0.3">
+    <row r="353" spans="3:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="C353" t="s">
         <v>154</v>
       </c>
@@ -15693,7 +15723,7 @@
         <v>626</v>
       </c>
     </row>
-    <row r="354" spans="3:13" x14ac:dyDescent="0.3">
+    <row r="354" spans="3:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="C354" t="s">
         <v>154</v>
       </c>
@@ -15723,7 +15753,7 @@
         <v>626</v>
       </c>
     </row>
-    <row r="355" spans="3:13" x14ac:dyDescent="0.3">
+    <row r="355" spans="3:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="C355" t="s">
         <v>634</v>
       </c>
@@ -15753,7 +15783,7 @@
         <v>637</v>
       </c>
     </row>
-    <row r="356" spans="3:13" x14ac:dyDescent="0.3">
+    <row r="356" spans="3:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="C356" t="s">
         <v>634</v>
       </c>
@@ -15783,7 +15813,7 @@
         <v>637</v>
       </c>
     </row>
-    <row r="357" spans="3:13" x14ac:dyDescent="0.3">
+    <row r="357" spans="3:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="C357" t="s">
         <v>634</v>
       </c>
@@ -15813,7 +15843,7 @@
         <v>637</v>
       </c>
     </row>
-    <row r="358" spans="3:13" x14ac:dyDescent="0.3">
+    <row r="358" spans="3:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="C358" t="s">
         <v>634</v>
       </c>
@@ -15843,7 +15873,7 @@
         <v>637</v>
       </c>
     </row>
-    <row r="359" spans="3:13" x14ac:dyDescent="0.3">
+    <row r="359" spans="3:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="C359" t="s">
         <v>516</v>
       </c>
@@ -15870,7 +15900,7 @@
         <v>644</v>
       </c>
     </row>
-    <row r="360" spans="3:13" x14ac:dyDescent="0.3">
+    <row r="360" spans="3:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="C360" t="s">
         <v>516</v>
       </c>
@@ -15897,7 +15927,7 @@
         <v>644</v>
       </c>
     </row>
-    <row r="361" spans="3:13" x14ac:dyDescent="0.3">
+    <row r="361" spans="3:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="C361" t="s">
         <v>516</v>
       </c>
@@ -15924,7 +15954,7 @@
         <v>644</v>
       </c>
     </row>
-    <row r="362" spans="3:13" x14ac:dyDescent="0.3">
+    <row r="362" spans="3:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="C362" t="s">
         <v>516</v>
       </c>
@@ -15951,7 +15981,7 @@
         <v>644</v>
       </c>
     </row>
-    <row r="363" spans="3:13" x14ac:dyDescent="0.3">
+    <row r="363" spans="3:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="C363" t="s">
         <v>27</v>
       </c>
@@ -15981,7 +16011,7 @@
         <v>652</v>
       </c>
     </row>
-    <row r="364" spans="3:13" x14ac:dyDescent="0.3">
+    <row r="364" spans="3:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="C364" t="s">
         <v>27</v>
       </c>
@@ -16011,7 +16041,7 @@
         <v>652</v>
       </c>
     </row>
-    <row r="365" spans="3:13" x14ac:dyDescent="0.3">
+    <row r="365" spans="3:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="C365" t="s">
         <v>27</v>
       </c>
@@ -16041,7 +16071,7 @@
         <v>652</v>
       </c>
     </row>
-    <row r="366" spans="3:13" x14ac:dyDescent="0.3">
+    <row r="366" spans="3:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="C366" t="s">
         <v>27</v>
       </c>
@@ -16071,7 +16101,7 @@
         <v>652</v>
       </c>
     </row>
-    <row r="367" spans="3:13" x14ac:dyDescent="0.3">
+    <row r="367" spans="3:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="C367" t="s">
         <v>45</v>
       </c>
@@ -16101,7 +16131,7 @@
         <v>658</v>
       </c>
     </row>
-    <row r="368" spans="3:13" x14ac:dyDescent="0.3">
+    <row r="368" spans="3:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="C368" t="s">
         <v>45</v>
       </c>
@@ -16131,7 +16161,7 @@
         <v>658</v>
       </c>
     </row>
-    <row r="369" spans="3:13" x14ac:dyDescent="0.3">
+    <row r="369" spans="3:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="C369" t="s">
         <v>45</v>
       </c>
@@ -16161,7 +16191,7 @@
         <v>658</v>
       </c>
     </row>
-    <row r="370" spans="3:13" x14ac:dyDescent="0.3">
+    <row r="370" spans="3:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="C370" t="s">
         <v>45</v>
       </c>
@@ -16191,7 +16221,7 @@
         <v>658</v>
       </c>
     </row>
-    <row r="371" spans="3:13" x14ac:dyDescent="0.3">
+    <row r="371" spans="3:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="C371" t="s">
         <v>45</v>
       </c>
@@ -16221,7 +16251,7 @@
         <v>658</v>
       </c>
     </row>
-    <row r="372" spans="3:13" x14ac:dyDescent="0.3">
+    <row r="372" spans="3:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="C372" t="s">
         <v>45</v>
       </c>
@@ -16251,7 +16281,7 @@
         <v>658</v>
       </c>
     </row>
-    <row r="373" spans="3:13" x14ac:dyDescent="0.3">
+    <row r="373" spans="3:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="C373" t="s">
         <v>69</v>
       </c>
@@ -16281,7 +16311,7 @@
         <v>665</v>
       </c>
     </row>
-    <row r="374" spans="3:13" x14ac:dyDescent="0.3">
+    <row r="374" spans="3:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="C374" t="s">
         <v>69</v>
       </c>
@@ -16311,7 +16341,7 @@
         <v>665</v>
       </c>
     </row>
-    <row r="375" spans="3:13" x14ac:dyDescent="0.3">
+    <row r="375" spans="3:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="C375" t="s">
         <v>69</v>
       </c>
@@ -16341,7 +16371,7 @@
         <v>665</v>
       </c>
     </row>
-    <row r="376" spans="3:13" x14ac:dyDescent="0.3">
+    <row r="376" spans="3:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="C376" t="s">
         <v>69</v>
       </c>
@@ -16371,7 +16401,7 @@
         <v>665</v>
       </c>
     </row>
-    <row r="377" spans="3:13" x14ac:dyDescent="0.3">
+    <row r="377" spans="3:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="C377" t="s">
         <v>669</v>
       </c>
@@ -16401,7 +16431,7 @@
         <v>672</v>
       </c>
     </row>
-    <row r="378" spans="3:13" x14ac:dyDescent="0.3">
+    <row r="378" spans="3:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="C378" t="s">
         <v>669</v>
       </c>
@@ -16431,7 +16461,7 @@
         <v>672</v>
       </c>
     </row>
-    <row r="379" spans="3:13" x14ac:dyDescent="0.3">
+    <row r="379" spans="3:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="C379" t="s">
         <v>669</v>
       </c>
@@ -16461,7 +16491,7 @@
         <v>672</v>
       </c>
     </row>
-    <row r="380" spans="3:13" x14ac:dyDescent="0.3">
+    <row r="380" spans="3:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="C380" t="s">
         <v>669</v>
       </c>
@@ -16491,7 +16521,7 @@
         <v>672</v>
       </c>
     </row>
-    <row r="381" spans="3:13" x14ac:dyDescent="0.3">
+    <row r="381" spans="3:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="C381" t="s">
         <v>90</v>
       </c>
@@ -16521,7 +16551,7 @@
         <v>678</v>
       </c>
     </row>
-    <row r="382" spans="3:13" x14ac:dyDescent="0.3">
+    <row r="382" spans="3:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="C382" t="s">
         <v>90</v>
       </c>
@@ -16551,7 +16581,7 @@
         <v>678</v>
       </c>
     </row>
-    <row r="383" spans="3:13" x14ac:dyDescent="0.3">
+    <row r="383" spans="3:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="C383" t="s">
         <v>90</v>
       </c>
@@ -16581,7 +16611,7 @@
         <v>678</v>
       </c>
     </row>
-    <row r="384" spans="3:13" x14ac:dyDescent="0.3">
+    <row r="384" spans="3:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="C384" t="s">
         <v>90</v>
       </c>
@@ -16611,7 +16641,7 @@
         <v>678</v>
       </c>
     </row>
-    <row r="385" spans="2:13" x14ac:dyDescent="0.3">
+    <row r="385" spans="2:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="C385" t="s">
         <v>90</v>
       </c>
@@ -16641,7 +16671,7 @@
         <v>678</v>
       </c>
     </row>
-    <row r="386" spans="2:13" x14ac:dyDescent="0.3">
+    <row r="386" spans="2:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="C386" t="s">
         <v>90</v>
       </c>
@@ -16671,7 +16701,7 @@
         <v>678</v>
       </c>
     </row>
-    <row r="387" spans="2:13" x14ac:dyDescent="0.3">
+    <row r="387" spans="2:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="C387" t="s">
         <v>90</v>
       </c>
@@ -16701,7 +16731,7 @@
         <v>678</v>
       </c>
     </row>
-    <row r="388" spans="2:13" x14ac:dyDescent="0.3">
+    <row r="388" spans="2:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="C388" t="s">
         <v>90</v>
       </c>
@@ -16731,7 +16761,7 @@
         <v>678</v>
       </c>
     </row>
-    <row r="389" spans="2:13" x14ac:dyDescent="0.3">
+    <row r="389" spans="2:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="B389" t="s">
         <v>162</v>
       </c>
@@ -16761,7 +16791,7 @@
         <v>685</v>
       </c>
     </row>
-    <row r="390" spans="2:13" x14ac:dyDescent="0.3">
+    <row r="390" spans="2:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="B390" t="s">
         <v>162</v>
       </c>
@@ -16791,7 +16821,7 @@
         <v>685</v>
       </c>
     </row>
-    <row r="391" spans="2:13" x14ac:dyDescent="0.3">
+    <row r="391" spans="2:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="B391" t="s">
         <v>162</v>
       </c>
@@ -16821,7 +16851,7 @@
         <v>685</v>
       </c>
     </row>
-    <row r="392" spans="2:13" x14ac:dyDescent="0.3">
+    <row r="392" spans="2:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="B392" t="s">
         <v>162</v>
       </c>
@@ -16851,7 +16881,7 @@
         <v>685</v>
       </c>
     </row>
-    <row r="393" spans="2:13" x14ac:dyDescent="0.3">
+    <row r="393" spans="2:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="B393" t="s">
         <v>162</v>
       </c>
@@ -16881,7 +16911,7 @@
         <v>685</v>
       </c>
     </row>
-    <row r="394" spans="2:13" x14ac:dyDescent="0.3">
+    <row r="394" spans="2:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="B394" t="s">
         <v>162</v>
       </c>
@@ -16911,7 +16941,7 @@
         <v>685</v>
       </c>
     </row>
-    <row r="395" spans="2:13" x14ac:dyDescent="0.3">
+    <row r="395" spans="2:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="B395" t="s">
         <v>162</v>
       </c>
@@ -16941,7 +16971,7 @@
         <v>685</v>
       </c>
     </row>
-    <row r="396" spans="2:13" x14ac:dyDescent="0.3">
+    <row r="396" spans="2:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="B396" t="s">
         <v>162</v>
       </c>
@@ -16971,7 +17001,7 @@
         <v>685</v>
       </c>
     </row>
-    <row r="397" spans="2:13" x14ac:dyDescent="0.3">
+    <row r="397" spans="2:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="B397" t="s">
         <v>162</v>
       </c>
@@ -17001,7 +17031,7 @@
         <v>685</v>
       </c>
     </row>
-    <row r="398" spans="2:13" x14ac:dyDescent="0.3">
+    <row r="398" spans="2:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="B398" t="s">
         <v>162</v>
       </c>
@@ -17031,7 +17061,7 @@
         <v>685</v>
       </c>
     </row>
-    <row r="399" spans="2:13" x14ac:dyDescent="0.3">
+    <row r="399" spans="2:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="B399" t="s">
         <v>162</v>
       </c>
@@ -17061,7 +17091,7 @@
         <v>685</v>
       </c>
     </row>
-    <row r="400" spans="2:13" x14ac:dyDescent="0.3">
+    <row r="400" spans="2:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="B400" t="s">
         <v>162</v>
       </c>
@@ -17091,7 +17121,7 @@
         <v>685</v>
       </c>
     </row>
-    <row r="401" spans="2:13" x14ac:dyDescent="0.3">
+    <row r="401" spans="2:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="C401" t="s">
         <v>101</v>
       </c>
@@ -17121,7 +17151,7 @@
         <v>697</v>
       </c>
     </row>
-    <row r="402" spans="2:13" x14ac:dyDescent="0.3">
+    <row r="402" spans="2:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="C402" t="s">
         <v>101</v>
       </c>
@@ -17151,7 +17181,7 @@
         <v>697</v>
       </c>
     </row>
-    <row r="403" spans="2:13" x14ac:dyDescent="0.3">
+    <row r="403" spans="2:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="C403" t="s">
         <v>101</v>
       </c>
@@ -17181,7 +17211,7 @@
         <v>697</v>
       </c>
     </row>
-    <row r="404" spans="2:13" x14ac:dyDescent="0.3">
+    <row r="404" spans="2:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="C404" t="s">
         <v>101</v>
       </c>
@@ -17211,7 +17241,7 @@
         <v>697</v>
       </c>
     </row>
-    <row r="405" spans="2:13" x14ac:dyDescent="0.3">
+    <row r="405" spans="2:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="C405" t="s">
         <v>110</v>
       </c>
@@ -17241,7 +17271,7 @@
         <v>702</v>
       </c>
     </row>
-    <row r="406" spans="2:13" x14ac:dyDescent="0.3">
+    <row r="406" spans="2:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="C406" t="s">
         <v>110</v>
       </c>
@@ -17271,7 +17301,7 @@
         <v>702</v>
       </c>
     </row>
-    <row r="407" spans="2:13" x14ac:dyDescent="0.3">
+    <row r="407" spans="2:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="C407" t="s">
         <v>110</v>
       </c>
@@ -17301,7 +17331,7 @@
         <v>702</v>
       </c>
     </row>
-    <row r="408" spans="2:13" x14ac:dyDescent="0.3">
+    <row r="408" spans="2:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="C408" t="s">
         <v>110</v>
       </c>
@@ -17331,7 +17361,7 @@
         <v>702</v>
       </c>
     </row>
-    <row r="409" spans="2:13" x14ac:dyDescent="0.3">
+    <row r="409" spans="2:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="B409" t="s">
         <v>162</v>
       </c>
@@ -17361,7 +17391,7 @@
         <v>707</v>
       </c>
     </row>
-    <row r="410" spans="2:13" x14ac:dyDescent="0.3">
+    <row r="410" spans="2:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="B410" t="s">
         <v>162</v>
       </c>
@@ -17391,7 +17421,7 @@
         <v>707</v>
       </c>
     </row>
-    <row r="411" spans="2:13" x14ac:dyDescent="0.3">
+    <row r="411" spans="2:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="B411" t="s">
         <v>162</v>
       </c>
@@ -17421,7 +17451,7 @@
         <v>707</v>
       </c>
     </row>
-    <row r="412" spans="2:13" x14ac:dyDescent="0.3">
+    <row r="412" spans="2:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="B412" t="s">
         <v>162</v>
       </c>
@@ -17451,7 +17481,7 @@
         <v>707</v>
       </c>
     </row>
-    <row r="413" spans="2:13" x14ac:dyDescent="0.3">
+    <row r="413" spans="2:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="B413" t="s">
         <v>162</v>
       </c>
@@ -17481,7 +17511,7 @@
         <v>707</v>
       </c>
     </row>
-    <row r="414" spans="2:13" x14ac:dyDescent="0.3">
+    <row r="414" spans="2:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="B414" t="s">
         <v>162</v>
       </c>
@@ -17511,7 +17541,7 @@
         <v>707</v>
       </c>
     </row>
-    <row r="415" spans="2:13" x14ac:dyDescent="0.3">
+    <row r="415" spans="2:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="B415" t="s">
         <v>162</v>
       </c>
@@ -17541,7 +17571,7 @@
         <v>707</v>
       </c>
     </row>
-    <row r="416" spans="2:13" x14ac:dyDescent="0.3">
+    <row r="416" spans="2:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="B416" t="s">
         <v>162</v>
       </c>
@@ -17571,7 +17601,7 @@
         <v>707</v>
       </c>
     </row>
-    <row r="417" spans="2:13" x14ac:dyDescent="0.3">
+    <row r="417" spans="2:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="B417" t="s">
         <v>162</v>
       </c>
@@ -17601,7 +17631,7 @@
         <v>707</v>
       </c>
     </row>
-    <row r="418" spans="2:13" x14ac:dyDescent="0.3">
+    <row r="418" spans="2:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="B418" t="s">
         <v>162</v>
       </c>
@@ -17631,7 +17661,7 @@
         <v>707</v>
       </c>
     </row>
-    <row r="419" spans="2:13" x14ac:dyDescent="0.3">
+    <row r="419" spans="2:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="B419" t="s">
         <v>162</v>
       </c>
@@ -17661,7 +17691,7 @@
         <v>707</v>
       </c>
     </row>
-    <row r="420" spans="2:13" x14ac:dyDescent="0.3">
+    <row r="420" spans="2:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="B420" t="s">
         <v>162</v>
       </c>
@@ -17721,7 +17751,7 @@
         <v>723</v>
       </c>
     </row>
-    <row r="422" spans="2:13" x14ac:dyDescent="0.3">
+    <row r="422" spans="2:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="C422" t="s">
         <v>719</v>
       </c>
@@ -17751,7 +17781,7 @@
         <v>723</v>
       </c>
     </row>
-    <row r="423" spans="2:13" x14ac:dyDescent="0.3">
+    <row r="423" spans="2:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="C423" t="s">
         <v>719</v>
       </c>
@@ -17781,7 +17811,7 @@
         <v>723</v>
       </c>
     </row>
-    <row r="424" spans="2:13" x14ac:dyDescent="0.3">
+    <row r="424" spans="2:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="C424" t="s">
         <v>719</v>
       </c>
@@ -17811,7 +17841,7 @@
         <v>723</v>
       </c>
     </row>
-    <row r="425" spans="2:13" x14ac:dyDescent="0.3">
+    <row r="425" spans="2:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="C425" t="s">
         <v>129</v>
       </c>
@@ -17841,7 +17871,7 @@
         <v>728</v>
       </c>
     </row>
-    <row r="426" spans="2:13" x14ac:dyDescent="0.3">
+    <row r="426" spans="2:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="C426" t="s">
         <v>129</v>
       </c>
@@ -17871,7 +17901,7 @@
         <v>728</v>
       </c>
     </row>
-    <row r="427" spans="2:13" x14ac:dyDescent="0.3">
+    <row r="427" spans="2:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="C427" t="s">
         <v>129</v>
       </c>
@@ -17901,7 +17931,7 @@
         <v>728</v>
       </c>
     </row>
-    <row r="428" spans="2:13" x14ac:dyDescent="0.3">
+    <row r="428" spans="2:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="C428" t="s">
         <v>129</v>
       </c>
@@ -17931,7 +17961,7 @@
         <v>728</v>
       </c>
     </row>
-    <row r="429" spans="2:13" x14ac:dyDescent="0.3">
+    <row r="429" spans="2:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="C429" t="s">
         <v>150</v>
       </c>
@@ -17961,7 +17991,7 @@
         <v>734</v>
       </c>
     </row>
-    <row r="430" spans="2:13" x14ac:dyDescent="0.3">
+    <row r="430" spans="2:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="C430" t="s">
         <v>150</v>
       </c>
@@ -17991,7 +18021,7 @@
         <v>734</v>
       </c>
     </row>
-    <row r="431" spans="2:13" x14ac:dyDescent="0.3">
+    <row r="431" spans="2:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="C431" t="s">
         <v>150</v>
       </c>
@@ -18021,7 +18051,7 @@
         <v>734</v>
       </c>
     </row>
-    <row r="432" spans="2:13" x14ac:dyDescent="0.3">
+    <row r="432" spans="2:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="C432" t="s">
         <v>150</v>
       </c>
@@ -18051,7 +18081,7 @@
         <v>734</v>
       </c>
     </row>
-    <row r="433" spans="3:13" x14ac:dyDescent="0.3">
+    <row r="433" spans="3:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="C433" t="s">
         <v>303</v>
       </c>
@@ -18078,7 +18108,7 @@
         <v>740</v>
       </c>
     </row>
-    <row r="434" spans="3:13" x14ac:dyDescent="0.3">
+    <row r="434" spans="3:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="C434" t="s">
         <v>303</v>
       </c>
@@ -18105,7 +18135,7 @@
         <v>740</v>
       </c>
     </row>
-    <row r="435" spans="3:13" x14ac:dyDescent="0.3">
+    <row r="435" spans="3:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="C435" t="s">
         <v>303</v>
       </c>
@@ -18132,7 +18162,7 @@
         <v>740</v>
       </c>
     </row>
-    <row r="436" spans="3:13" x14ac:dyDescent="0.3">
+    <row r="436" spans="3:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="C436" t="s">
         <v>303</v>
       </c>
@@ -18159,7 +18189,7 @@
         <v>740</v>
       </c>
     </row>
-    <row r="437" spans="3:13" x14ac:dyDescent="0.3">
+    <row r="437" spans="3:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="C437" t="s">
         <v>746</v>
       </c>
@@ -18186,7 +18216,7 @@
         <v>750</v>
       </c>
     </row>
-    <row r="438" spans="3:13" x14ac:dyDescent="0.3">
+    <row r="438" spans="3:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="C438" t="s">
         <v>746</v>
       </c>
@@ -18213,7 +18243,7 @@
         <v>750</v>
       </c>
     </row>
-    <row r="439" spans="3:13" x14ac:dyDescent="0.3">
+    <row r="439" spans="3:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="C439" t="s">
         <v>746</v>
       </c>
@@ -18240,7 +18270,7 @@
         <v>750</v>
       </c>
     </row>
-    <row r="440" spans="3:13" x14ac:dyDescent="0.3">
+    <row r="440" spans="3:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="C440" t="s">
         <v>746</v>
       </c>
@@ -18267,7 +18297,7 @@
         <v>750</v>
       </c>
     </row>
-    <row r="441" spans="3:13" x14ac:dyDescent="0.3">
+    <row r="441" spans="3:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="C441" t="s">
         <v>746</v>
       </c>
@@ -18294,7 +18324,7 @@
         <v>750</v>
       </c>
     </row>
-    <row r="442" spans="3:13" x14ac:dyDescent="0.3">
+    <row r="442" spans="3:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="C442" t="s">
         <v>746</v>
       </c>
@@ -18321,7 +18351,7 @@
         <v>750</v>
       </c>
     </row>
-    <row r="443" spans="3:13" x14ac:dyDescent="0.3">
+    <row r="443" spans="3:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="C443" t="s">
         <v>746</v>
       </c>
@@ -18348,7 +18378,7 @@
         <v>750</v>
       </c>
     </row>
-    <row r="444" spans="3:13" x14ac:dyDescent="0.3">
+    <row r="444" spans="3:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="C444" t="s">
         <v>746</v>
       </c>
@@ -18375,7 +18405,7 @@
         <v>750</v>
       </c>
     </row>
-    <row r="445" spans="3:13" x14ac:dyDescent="0.3">
+    <row r="445" spans="3:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="C445" t="s">
         <v>746</v>
       </c>
@@ -18402,7 +18432,7 @@
         <v>750</v>
       </c>
     </row>
-    <row r="446" spans="3:13" x14ac:dyDescent="0.3">
+    <row r="446" spans="3:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="C446" t="s">
         <v>746</v>
       </c>
@@ -18429,7 +18459,7 @@
         <v>750</v>
       </c>
     </row>
-    <row r="447" spans="3:13" x14ac:dyDescent="0.3">
+    <row r="447" spans="3:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="C447" t="s">
         <v>746</v>
       </c>
@@ -18456,7 +18486,7 @@
         <v>750</v>
       </c>
     </row>
-    <row r="448" spans="3:13" x14ac:dyDescent="0.3">
+    <row r="448" spans="3:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="C448" t="s">
         <v>746</v>
       </c>
@@ -18483,7 +18513,7 @@
         <v>750</v>
       </c>
     </row>
-    <row r="449" spans="3:13" x14ac:dyDescent="0.3">
+    <row r="449" spans="3:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="C449" t="s">
         <v>746</v>
       </c>
@@ -18510,7 +18540,7 @@
         <v>750</v>
       </c>
     </row>
-    <row r="450" spans="3:13" x14ac:dyDescent="0.3">
+    <row r="450" spans="3:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="C450" t="s">
         <v>746</v>
       </c>
@@ -18537,7 +18567,7 @@
         <v>750</v>
       </c>
     </row>
-    <row r="451" spans="3:13" x14ac:dyDescent="0.3">
+    <row r="451" spans="3:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="C451" t="s">
         <v>746</v>
       </c>
@@ -18564,7 +18594,7 @@
         <v>750</v>
       </c>
     </row>
-    <row r="452" spans="3:13" x14ac:dyDescent="0.3">
+    <row r="452" spans="3:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="C452" t="s">
         <v>154</v>
       </c>
@@ -18594,7 +18624,7 @@
         <v>768</v>
       </c>
     </row>
-    <row r="453" spans="3:13" x14ac:dyDescent="0.3">
+    <row r="453" spans="3:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="C453" t="s">
         <v>154</v>
       </c>
@@ -18624,7 +18654,7 @@
         <v>768</v>
       </c>
     </row>
-    <row r="454" spans="3:13" x14ac:dyDescent="0.3">
+    <row r="454" spans="3:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="C454" t="s">
         <v>154</v>
       </c>
@@ -18654,7 +18684,7 @@
         <v>768</v>
       </c>
     </row>
-    <row r="455" spans="3:13" x14ac:dyDescent="0.3">
+    <row r="455" spans="3:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="C455" t="s">
         <v>154</v>
       </c>
@@ -18684,7 +18714,7 @@
         <v>768</v>
       </c>
     </row>
-    <row r="456" spans="3:13" x14ac:dyDescent="0.3">
+    <row r="456" spans="3:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="C456" t="s">
         <v>154</v>
       </c>
@@ -18714,7 +18744,7 @@
         <v>768</v>
       </c>
     </row>
-    <row r="457" spans="3:13" x14ac:dyDescent="0.3">
+    <row r="457" spans="3:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="C457" t="s">
         <v>154</v>
       </c>
@@ -18744,7 +18774,7 @@
         <v>768</v>
       </c>
     </row>
-    <row r="458" spans="3:13" x14ac:dyDescent="0.3">
+    <row r="458" spans="3:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="C458" t="s">
         <v>154</v>
       </c>
@@ -18774,7 +18804,7 @@
         <v>768</v>
       </c>
     </row>
-    <row r="459" spans="3:13" x14ac:dyDescent="0.3">
+    <row r="459" spans="3:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="C459" t="s">
         <v>154</v>
       </c>
@@ -18804,7 +18834,7 @@
         <v>768</v>
       </c>
     </row>
-    <row r="460" spans="3:13" x14ac:dyDescent="0.3">
+    <row r="460" spans="3:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="C460" t="s">
         <v>27</v>
       </c>
@@ -18834,7 +18864,7 @@
         <v>778</v>
       </c>
     </row>
-    <row r="461" spans="3:13" x14ac:dyDescent="0.3">
+    <row r="461" spans="3:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="C461" t="s">
         <v>27</v>
       </c>
@@ -18864,7 +18894,7 @@
         <v>778</v>
       </c>
     </row>
-    <row r="462" spans="3:13" x14ac:dyDescent="0.3">
+    <row r="462" spans="3:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="C462" t="s">
         <v>27</v>
       </c>
@@ -18894,7 +18924,7 @@
         <v>778</v>
       </c>
     </row>
-    <row r="463" spans="3:13" x14ac:dyDescent="0.3">
+    <row r="463" spans="3:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="C463" t="s">
         <v>27</v>
       </c>
@@ -18924,7 +18954,7 @@
         <v>778</v>
       </c>
     </row>
-    <row r="464" spans="3:13" x14ac:dyDescent="0.3">
+    <row r="464" spans="3:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="C464" t="s">
         <v>45</v>
       </c>
@@ -18954,7 +18984,7 @@
         <v>784</v>
       </c>
     </row>
-    <row r="465" spans="3:13" x14ac:dyDescent="0.3">
+    <row r="465" spans="3:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="C465" t="s">
         <v>45</v>
       </c>
@@ -18984,7 +19014,7 @@
         <v>784</v>
       </c>
     </row>
-    <row r="466" spans="3:13" x14ac:dyDescent="0.3">
+    <row r="466" spans="3:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="C466" t="s">
         <v>45</v>
       </c>
@@ -19014,7 +19044,7 @@
         <v>784</v>
       </c>
     </row>
-    <row r="467" spans="3:13" x14ac:dyDescent="0.3">
+    <row r="467" spans="3:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="C467" t="s">
         <v>45</v>
       </c>
@@ -19044,7 +19074,7 @@
         <v>784</v>
       </c>
     </row>
-    <row r="468" spans="3:13" x14ac:dyDescent="0.3">
+    <row r="468" spans="3:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="C468" t="s">
         <v>69</v>
       </c>
@@ -19074,7 +19104,7 @@
         <v>789</v>
       </c>
     </row>
-    <row r="469" spans="3:13" x14ac:dyDescent="0.3">
+    <row r="469" spans="3:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="C469" t="s">
         <v>69</v>
       </c>
@@ -19104,7 +19134,7 @@
         <v>789</v>
       </c>
     </row>
-    <row r="470" spans="3:13" x14ac:dyDescent="0.3">
+    <row r="470" spans="3:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="C470" t="s">
         <v>69</v>
       </c>
@@ -19134,7 +19164,7 @@
         <v>789</v>
       </c>
     </row>
-    <row r="471" spans="3:13" x14ac:dyDescent="0.3">
+    <row r="471" spans="3:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="C471" t="s">
         <v>69</v>
       </c>
@@ -19164,7 +19194,7 @@
         <v>789</v>
       </c>
     </row>
-    <row r="472" spans="3:13" x14ac:dyDescent="0.3">
+    <row r="472" spans="3:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="C472" t="s">
         <v>69</v>
       </c>
@@ -19194,7 +19224,7 @@
         <v>789</v>
       </c>
     </row>
-    <row r="473" spans="3:13" x14ac:dyDescent="0.3">
+    <row r="473" spans="3:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="C473" t="s">
         <v>69</v>
       </c>
@@ -19224,7 +19254,7 @@
         <v>789</v>
       </c>
     </row>
-    <row r="474" spans="3:13" x14ac:dyDescent="0.3">
+    <row r="474" spans="3:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="C474" t="s">
         <v>69</v>
       </c>
@@ -19254,7 +19284,7 @@
         <v>789</v>
       </c>
     </row>
-    <row r="475" spans="3:13" x14ac:dyDescent="0.3">
+    <row r="475" spans="3:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="C475" t="s">
         <v>69</v>
       </c>
@@ -19284,7 +19314,7 @@
         <v>789</v>
       </c>
     </row>
-    <row r="476" spans="3:13" x14ac:dyDescent="0.3">
+    <row r="476" spans="3:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="C476" t="s">
         <v>669</v>
       </c>
@@ -19314,7 +19344,7 @@
         <v>800</v>
       </c>
     </row>
-    <row r="477" spans="3:13" x14ac:dyDescent="0.3">
+    <row r="477" spans="3:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="C477" t="s">
         <v>669</v>
       </c>
@@ -19344,7 +19374,7 @@
         <v>800</v>
       </c>
     </row>
-    <row r="478" spans="3:13" x14ac:dyDescent="0.3">
+    <row r="478" spans="3:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="C478" t="s">
         <v>669</v>
       </c>
@@ -19374,7 +19404,7 @@
         <v>800</v>
       </c>
     </row>
-    <row r="479" spans="3:13" x14ac:dyDescent="0.3">
+    <row r="479" spans="3:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="C479" t="s">
         <v>669</v>
       </c>
@@ -19404,7 +19434,7 @@
         <v>800</v>
       </c>
     </row>
-    <row r="480" spans="3:13" x14ac:dyDescent="0.3">
+    <row r="480" spans="3:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="C480" t="s">
         <v>669</v>
       </c>
@@ -19434,7 +19464,7 @@
         <v>800</v>
       </c>
     </row>
-    <row r="481" spans="2:13" x14ac:dyDescent="0.3">
+    <row r="481" spans="2:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="C481" t="s">
         <v>669</v>
       </c>
@@ -19464,7 +19494,7 @@
         <v>800</v>
       </c>
     </row>
-    <row r="482" spans="2:13" x14ac:dyDescent="0.3">
+    <row r="482" spans="2:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="C482" t="s">
         <v>669</v>
       </c>
@@ -19494,7 +19524,7 @@
         <v>800</v>
       </c>
     </row>
-    <row r="483" spans="2:13" x14ac:dyDescent="0.3">
+    <row r="483" spans="2:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="C483" t="s">
         <v>669</v>
       </c>
@@ -19524,7 +19554,7 @@
         <v>800</v>
       </c>
     </row>
-    <row r="484" spans="2:13" x14ac:dyDescent="0.3">
+    <row r="484" spans="2:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="B484" t="s">
         <v>162</v>
       </c>
@@ -19554,7 +19584,7 @@
         <v>809</v>
       </c>
     </row>
-    <row r="485" spans="2:13" x14ac:dyDescent="0.3">
+    <row r="485" spans="2:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="B485" t="s">
         <v>162</v>
       </c>
@@ -19584,7 +19614,7 @@
         <v>809</v>
       </c>
     </row>
-    <row r="486" spans="2:13" x14ac:dyDescent="0.3">
+    <row r="486" spans="2:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="B486" t="s">
         <v>162</v>
       </c>
@@ -19614,7 +19644,7 @@
         <v>809</v>
       </c>
     </row>
-    <row r="487" spans="2:13" x14ac:dyDescent="0.3">
+    <row r="487" spans="2:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="B487" t="s">
         <v>162</v>
       </c>
@@ -19644,7 +19674,7 @@
         <v>809</v>
       </c>
     </row>
-    <row r="488" spans="2:13" x14ac:dyDescent="0.3">
+    <row r="488" spans="2:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="B488" t="s">
         <v>162</v>
       </c>
@@ -19674,7 +19704,7 @@
         <v>809</v>
       </c>
     </row>
-    <row r="489" spans="2:13" x14ac:dyDescent="0.3">
+    <row r="489" spans="2:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="B489" t="s">
         <v>162</v>
       </c>
@@ -19704,7 +19734,7 @@
         <v>809</v>
       </c>
     </row>
-    <row r="490" spans="2:13" x14ac:dyDescent="0.3">
+    <row r="490" spans="2:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="B490" t="s">
         <v>162</v>
       </c>
@@ -19734,7 +19764,7 @@
         <v>809</v>
       </c>
     </row>
-    <row r="491" spans="2:13" x14ac:dyDescent="0.3">
+    <row r="491" spans="2:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="B491" t="s">
         <v>162</v>
       </c>
@@ -19764,7 +19794,7 @@
         <v>809</v>
       </c>
     </row>
-    <row r="492" spans="2:13" x14ac:dyDescent="0.3">
+    <row r="492" spans="2:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="B492" t="s">
         <v>162</v>
       </c>
@@ -19794,7 +19824,7 @@
         <v>809</v>
       </c>
     </row>
-    <row r="493" spans="2:13" x14ac:dyDescent="0.3">
+    <row r="493" spans="2:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="B493" t="s">
         <v>162</v>
       </c>
@@ -19824,7 +19854,7 @@
         <v>809</v>
       </c>
     </row>
-    <row r="494" spans="2:13" x14ac:dyDescent="0.3">
+    <row r="494" spans="2:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="B494" t="s">
         <v>162</v>
       </c>
@@ -19854,7 +19884,7 @@
         <v>809</v>
       </c>
     </row>
-    <row r="495" spans="2:13" x14ac:dyDescent="0.3">
+    <row r="495" spans="2:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="B495" t="s">
         <v>162</v>
       </c>
@@ -19884,7 +19914,7 @@
         <v>809</v>
       </c>
     </row>
-    <row r="496" spans="2:13" x14ac:dyDescent="0.3">
+    <row r="496" spans="2:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="C496" t="s">
         <v>101</v>
       </c>
@@ -19914,7 +19944,7 @@
         <v>823</v>
       </c>
     </row>
-    <row r="497" spans="2:13" x14ac:dyDescent="0.3">
+    <row r="497" spans="2:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="C497" t="s">
         <v>101</v>
       </c>
@@ -19944,7 +19974,7 @@
         <v>823</v>
       </c>
     </row>
-    <row r="498" spans="2:13" x14ac:dyDescent="0.3">
+    <row r="498" spans="2:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="C498" t="s">
         <v>101</v>
       </c>
@@ -19974,7 +20004,7 @@
         <v>823</v>
       </c>
     </row>
-    <row r="499" spans="2:13" x14ac:dyDescent="0.3">
+    <row r="499" spans="2:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="C499" t="s">
         <v>101</v>
       </c>
@@ -20004,7 +20034,7 @@
         <v>823</v>
       </c>
     </row>
-    <row r="500" spans="2:13" x14ac:dyDescent="0.3">
+    <row r="500" spans="2:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="C500" t="s">
         <v>101</v>
       </c>
@@ -20034,7 +20064,7 @@
         <v>823</v>
       </c>
     </row>
-    <row r="501" spans="2:13" x14ac:dyDescent="0.3">
+    <row r="501" spans="2:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="C501" t="s">
         <v>101</v>
       </c>
@@ -20064,7 +20094,7 @@
         <v>823</v>
       </c>
     </row>
-    <row r="502" spans="2:13" x14ac:dyDescent="0.3">
+    <row r="502" spans="2:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="C502" t="s">
         <v>110</v>
       </c>
@@ -20094,7 +20124,7 @@
         <v>830</v>
       </c>
     </row>
-    <row r="503" spans="2:13" x14ac:dyDescent="0.3">
+    <row r="503" spans="2:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="C503" t="s">
         <v>110</v>
       </c>
@@ -20124,7 +20154,7 @@
         <v>830</v>
       </c>
     </row>
-    <row r="504" spans="2:13" x14ac:dyDescent="0.3">
+    <row r="504" spans="2:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="C504" t="s">
         <v>110</v>
       </c>
@@ -20154,7 +20184,7 @@
         <v>830</v>
       </c>
     </row>
-    <row r="505" spans="2:13" x14ac:dyDescent="0.3">
+    <row r="505" spans="2:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="C505" t="s">
         <v>110</v>
       </c>
@@ -20184,7 +20214,7 @@
         <v>830</v>
       </c>
     </row>
-    <row r="506" spans="2:13" x14ac:dyDescent="0.3">
+    <row r="506" spans="2:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="C506" t="s">
         <v>110</v>
       </c>
@@ -20214,7 +20244,7 @@
         <v>835</v>
       </c>
     </row>
-    <row r="507" spans="2:13" x14ac:dyDescent="0.3">
+    <row r="507" spans="2:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="C507" t="s">
         <v>110</v>
       </c>
@@ -20244,7 +20274,7 @@
         <v>835</v>
       </c>
     </row>
-    <row r="508" spans="2:13" x14ac:dyDescent="0.3">
+    <row r="508" spans="2:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="C508" t="s">
         <v>110</v>
       </c>
@@ -20274,7 +20304,7 @@
         <v>835</v>
       </c>
     </row>
-    <row r="509" spans="2:13" x14ac:dyDescent="0.3">
+    <row r="509" spans="2:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="C509" t="s">
         <v>110</v>
       </c>
@@ -20304,7 +20334,7 @@
         <v>835</v>
       </c>
     </row>
-    <row r="510" spans="2:13" x14ac:dyDescent="0.3">
+    <row r="510" spans="2:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="B510" t="s">
         <v>162</v>
       </c>
@@ -20334,7 +20364,7 @@
         <v>840</v>
       </c>
     </row>
-    <row r="511" spans="2:13" x14ac:dyDescent="0.3">
+    <row r="511" spans="2:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="B511" t="s">
         <v>162</v>
       </c>
@@ -20364,7 +20394,7 @@
         <v>840</v>
       </c>
     </row>
-    <row r="512" spans="2:13" x14ac:dyDescent="0.3">
+    <row r="512" spans="2:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="B512" t="s">
         <v>162</v>
       </c>
@@ -20394,7 +20424,7 @@
         <v>840</v>
       </c>
     </row>
-    <row r="513" spans="2:13" x14ac:dyDescent="0.3">
+    <row r="513" spans="2:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="B513" t="s">
         <v>162</v>
       </c>
@@ -20424,7 +20454,7 @@
         <v>840</v>
       </c>
     </row>
-    <row r="514" spans="2:13" x14ac:dyDescent="0.3">
+    <row r="514" spans="2:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="B514" t="s">
         <v>162</v>
       </c>
@@ -20454,7 +20484,7 @@
         <v>840</v>
       </c>
     </row>
-    <row r="515" spans="2:13" x14ac:dyDescent="0.3">
+    <row r="515" spans="2:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="B515" t="s">
         <v>162</v>
       </c>
@@ -20484,7 +20514,7 @@
         <v>840</v>
       </c>
     </row>
-    <row r="516" spans="2:13" x14ac:dyDescent="0.3">
+    <row r="516" spans="2:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="B516" t="s">
         <v>162</v>
       </c>
@@ -20514,7 +20544,7 @@
         <v>840</v>
       </c>
     </row>
-    <row r="517" spans="2:13" x14ac:dyDescent="0.3">
+    <row r="517" spans="2:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="B517" t="s">
         <v>162</v>
       </c>
@@ -20544,7 +20574,7 @@
         <v>840</v>
       </c>
     </row>
-    <row r="518" spans="2:13" x14ac:dyDescent="0.3">
+    <row r="518" spans="2:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="B518" t="s">
         <v>162</v>
       </c>
@@ -20574,7 +20604,7 @@
         <v>840</v>
       </c>
     </row>
-    <row r="519" spans="2:13" x14ac:dyDescent="0.3">
+    <row r="519" spans="2:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="B519" t="s">
         <v>162</v>
       </c>
@@ -20604,7 +20634,7 @@
         <v>840</v>
       </c>
     </row>
-    <row r="520" spans="2:13" x14ac:dyDescent="0.3">
+    <row r="520" spans="2:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="B520" t="s">
         <v>162</v>
       </c>
@@ -20634,7 +20664,7 @@
         <v>840</v>
       </c>
     </row>
-    <row r="521" spans="2:13" x14ac:dyDescent="0.3">
+    <row r="521" spans="2:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="B521" t="s">
         <v>162</v>
       </c>
@@ -20664,7 +20694,7 @@
         <v>840</v>
       </c>
     </row>
-    <row r="522" spans="2:13" x14ac:dyDescent="0.3">
+    <row r="522" spans="2:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="C522" t="s">
         <v>746</v>
       </c>
@@ -20691,7 +20721,7 @@
         <v>854</v>
       </c>
     </row>
-    <row r="523" spans="2:13" x14ac:dyDescent="0.3">
+    <row r="523" spans="2:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="C523" t="s">
         <v>746</v>
       </c>
@@ -20718,7 +20748,7 @@
         <v>854</v>
       </c>
     </row>
-    <row r="524" spans="2:13" x14ac:dyDescent="0.3">
+    <row r="524" spans="2:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="C524" t="s">
         <v>746</v>
       </c>
@@ -20745,7 +20775,7 @@
         <v>854</v>
       </c>
     </row>
-    <row r="525" spans="2:13" x14ac:dyDescent="0.3">
+    <row r="525" spans="2:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="C525" t="s">
         <v>746</v>
       </c>
@@ -20772,7 +20802,7 @@
         <v>854</v>
       </c>
     </row>
-    <row r="526" spans="2:13" x14ac:dyDescent="0.3">
+    <row r="526" spans="2:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="C526" t="s">
         <v>746</v>
       </c>
@@ -20799,7 +20829,7 @@
         <v>854</v>
       </c>
     </row>
-    <row r="527" spans="2:13" x14ac:dyDescent="0.3">
+    <row r="527" spans="2:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="C527" t="s">
         <v>746</v>
       </c>
@@ -20826,7 +20856,7 @@
         <v>854</v>
       </c>
     </row>
-    <row r="528" spans="2:13" x14ac:dyDescent="0.3">
+    <row r="528" spans="2:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="C528" t="s">
         <v>746</v>
       </c>
@@ -20853,7 +20883,7 @@
         <v>854</v>
       </c>
     </row>
-    <row r="529" spans="2:13" x14ac:dyDescent="0.3">
+    <row r="529" spans="2:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="C529" t="s">
         <v>746</v>
       </c>
@@ -20880,7 +20910,7 @@
         <v>854</v>
       </c>
     </row>
-    <row r="530" spans="2:13" x14ac:dyDescent="0.3">
+    <row r="530" spans="2:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="C530" t="s">
         <v>746</v>
       </c>
@@ -20907,7 +20937,7 @@
         <v>854</v>
       </c>
     </row>
-    <row r="531" spans="2:13" x14ac:dyDescent="0.3">
+    <row r="531" spans="2:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="C531" t="s">
         <v>746</v>
       </c>
@@ -20934,7 +20964,7 @@
         <v>854</v>
       </c>
     </row>
-    <row r="532" spans="2:13" x14ac:dyDescent="0.3">
+    <row r="532" spans="2:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="C532" t="s">
         <v>746</v>
       </c>
@@ -20961,7 +20991,7 @@
         <v>854</v>
       </c>
     </row>
-    <row r="533" spans="2:13" x14ac:dyDescent="0.3">
+    <row r="533" spans="2:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="C533" t="s">
         <v>746</v>
       </c>
@@ -20988,7 +21018,7 @@
         <v>854</v>
       </c>
     </row>
-    <row r="534" spans="2:13" x14ac:dyDescent="0.3">
+    <row r="534" spans="2:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="C534" t="s">
         <v>746</v>
       </c>
@@ -21015,7 +21045,7 @@
         <v>854</v>
       </c>
     </row>
-    <row r="535" spans="2:13" x14ac:dyDescent="0.3">
+    <row r="535" spans="2:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="C535" t="s">
         <v>746</v>
       </c>
@@ -21042,7 +21072,7 @@
         <v>854</v>
       </c>
     </row>
-    <row r="536" spans="2:13" x14ac:dyDescent="0.3">
+    <row r="536" spans="2:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="C536" t="s">
         <v>746</v>
       </c>
@@ -21069,7 +21099,7 @@
         <v>854</v>
       </c>
     </row>
-    <row r="537" spans="2:13" x14ac:dyDescent="0.3">
+    <row r="537" spans="2:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="C537" t="s">
         <v>746</v>
       </c>
@@ -21096,7 +21126,7 @@
         <v>854</v>
       </c>
     </row>
-    <row r="538" spans="2:13" x14ac:dyDescent="0.3">
+    <row r="538" spans="2:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="C538" t="s">
         <v>746</v>
       </c>
@@ -21123,7 +21153,7 @@
         <v>854</v>
       </c>
     </row>
-    <row r="539" spans="2:13" x14ac:dyDescent="0.3">
+    <row r="539" spans="2:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="C539" t="s">
         <v>746</v>
       </c>
@@ -21150,7 +21180,7 @@
         <v>854</v>
       </c>
     </row>
-    <row r="540" spans="2:13" x14ac:dyDescent="0.3">
+    <row r="540" spans="2:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="C540" t="s">
         <v>746</v>
       </c>
@@ -21177,7 +21207,7 @@
         <v>854</v>
       </c>
     </row>
-    <row r="541" spans="2:13" x14ac:dyDescent="0.3">
+    <row r="541" spans="2:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="C541" t="s">
         <v>746</v>
       </c>
@@ -21204,7 +21234,7 @@
         <v>854</v>
       </c>
     </row>
-    <row r="542" spans="2:13" x14ac:dyDescent="0.3">
+    <row r="542" spans="2:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="B542" t="s">
         <v>137</v>
       </c>
@@ -21234,7 +21264,7 @@
         <v>876</v>
       </c>
     </row>
-    <row r="543" spans="2:13" x14ac:dyDescent="0.3">
+    <row r="543" spans="2:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="B543" t="s">
         <v>137</v>
       </c>
@@ -21264,7 +21294,7 @@
         <v>876</v>
       </c>
     </row>
-    <row r="544" spans="2:13" x14ac:dyDescent="0.3">
+    <row r="544" spans="2:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="B544" t="s">
         <v>137</v>
       </c>
@@ -21294,7 +21324,7 @@
         <v>876</v>
       </c>
     </row>
-    <row r="545" spans="2:13" x14ac:dyDescent="0.3">
+    <row r="545" spans="2:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="B545" t="s">
         <v>137</v>
       </c>
@@ -21324,7 +21354,7 @@
         <v>876</v>
       </c>
     </row>
-    <row r="546" spans="2:13" x14ac:dyDescent="0.3">
+    <row r="546" spans="2:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="C546" t="s">
         <v>150</v>
       </c>
@@ -21354,7 +21384,7 @@
         <v>884</v>
       </c>
     </row>
-    <row r="547" spans="2:13" x14ac:dyDescent="0.3">
+    <row r="547" spans="2:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="C547" t="s">
         <v>150</v>
       </c>
@@ -21384,7 +21414,7 @@
         <v>884</v>
       </c>
     </row>
-    <row r="548" spans="2:13" x14ac:dyDescent="0.3">
+    <row r="548" spans="2:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="C548" t="s">
         <v>150</v>
       </c>
@@ -21414,7 +21444,7 @@
         <v>884</v>
       </c>
     </row>
-    <row r="549" spans="2:13" x14ac:dyDescent="0.3">
+    <row r="549" spans="2:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="C549" t="s">
         <v>150</v>
       </c>
@@ -21444,7 +21474,7 @@
         <v>884</v>
       </c>
     </row>
-    <row r="550" spans="2:13" x14ac:dyDescent="0.3">
+    <row r="550" spans="2:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="C550" t="s">
         <v>303</v>
       </c>
@@ -21471,7 +21501,7 @@
         <v>889</v>
       </c>
     </row>
-    <row r="551" spans="2:13" x14ac:dyDescent="0.3">
+    <row r="551" spans="2:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="C551" t="s">
         <v>303</v>
       </c>
@@ -21498,7 +21528,7 @@
         <v>889</v>
       </c>
     </row>
-    <row r="552" spans="2:13" x14ac:dyDescent="0.3">
+    <row r="552" spans="2:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="C552" t="s">
         <v>303</v>
       </c>
@@ -21525,7 +21555,7 @@
         <v>889</v>
       </c>
     </row>
-    <row r="553" spans="2:13" x14ac:dyDescent="0.3">
+    <row r="553" spans="2:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="B553" t="s">
         <v>137</v>
       </c>
@@ -21555,7 +21585,7 @@
         <v>895</v>
       </c>
     </row>
-    <row r="554" spans="2:13" x14ac:dyDescent="0.3">
+    <row r="554" spans="2:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="B554" t="s">
         <v>137</v>
       </c>
@@ -21585,7 +21615,7 @@
         <v>895</v>
       </c>
     </row>
-    <row r="555" spans="2:13" x14ac:dyDescent="0.3">
+    <row r="555" spans="2:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="B555" t="s">
         <v>137</v>
       </c>
@@ -21615,7 +21645,7 @@
         <v>895</v>
       </c>
     </row>
-    <row r="556" spans="2:13" x14ac:dyDescent="0.3">
+    <row r="556" spans="2:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="B556" t="s">
         <v>137</v>
       </c>
@@ -21645,7 +21675,7 @@
         <v>895</v>
       </c>
     </row>
-    <row r="557" spans="2:13" x14ac:dyDescent="0.3">
+    <row r="557" spans="2:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="B557" t="s">
         <v>137</v>
       </c>
@@ -21675,7 +21705,7 @@
         <v>904</v>
       </c>
     </row>
-    <row r="558" spans="2:13" x14ac:dyDescent="0.3">
+    <row r="558" spans="2:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="B558" t="s">
         <v>137</v>
       </c>
@@ -21705,7 +21735,7 @@
         <v>904</v>
       </c>
     </row>
-    <row r="559" spans="2:13" x14ac:dyDescent="0.3">
+    <row r="559" spans="2:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="B559" t="s">
         <v>137</v>
       </c>
@@ -21735,7 +21765,7 @@
         <v>904</v>
       </c>
     </row>
-    <row r="560" spans="2:13" x14ac:dyDescent="0.3">
+    <row r="560" spans="2:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="B560" t="s">
         <v>137</v>
       </c>
@@ -21765,7 +21795,7 @@
         <v>904</v>
       </c>
     </row>
-    <row r="561" spans="2:13" x14ac:dyDescent="0.3">
+    <row r="561" spans="2:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="C561" t="s">
         <v>154</v>
       </c>
@@ -21795,7 +21825,7 @@
         <v>912</v>
       </c>
     </row>
-    <row r="562" spans="2:13" x14ac:dyDescent="0.3">
+    <row r="562" spans="2:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="C562" t="s">
         <v>154</v>
       </c>
@@ -21825,7 +21855,7 @@
         <v>912</v>
       </c>
     </row>
-    <row r="563" spans="2:13" x14ac:dyDescent="0.3">
+    <row r="563" spans="2:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="C563" t="s">
         <v>154</v>
       </c>
@@ -21855,7 +21885,7 @@
         <v>912</v>
       </c>
     </row>
-    <row r="564" spans="2:13" x14ac:dyDescent="0.3">
+    <row r="564" spans="2:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="C564" t="s">
         <v>154</v>
       </c>
@@ -21885,7 +21915,7 @@
         <v>912</v>
       </c>
     </row>
-    <row r="565" spans="2:13" x14ac:dyDescent="0.3">
+    <row r="565" spans="2:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="C565" t="s">
         <v>154</v>
       </c>
@@ -21915,7 +21945,7 @@
         <v>912</v>
       </c>
     </row>
-    <row r="566" spans="2:13" x14ac:dyDescent="0.3">
+    <row r="566" spans="2:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="C566" t="s">
         <v>154</v>
       </c>
@@ -21945,7 +21975,7 @@
         <v>912</v>
       </c>
     </row>
-    <row r="567" spans="2:13" x14ac:dyDescent="0.3">
+    <row r="567" spans="2:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="C567" t="s">
         <v>154</v>
       </c>
@@ -21975,7 +22005,7 @@
         <v>912</v>
       </c>
     </row>
-    <row r="568" spans="2:13" x14ac:dyDescent="0.3">
+    <row r="568" spans="2:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="C568" t="s">
         <v>154</v>
       </c>
@@ -22005,7 +22035,7 @@
         <v>912</v>
       </c>
     </row>
-    <row r="569" spans="2:13" x14ac:dyDescent="0.3">
+    <row r="569" spans="2:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="C569" t="s">
         <v>45</v>
       </c>
@@ -22035,7 +22065,7 @@
         <v>923</v>
       </c>
     </row>
-    <row r="570" spans="2:13" x14ac:dyDescent="0.3">
+    <row r="570" spans="2:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="C570" t="s">
         <v>45</v>
       </c>
@@ -22065,7 +22095,7 @@
         <v>923</v>
       </c>
     </row>
-    <row r="571" spans="2:13" x14ac:dyDescent="0.3">
+    <row r="571" spans="2:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="C571" t="s">
         <v>45</v>
       </c>
@@ -22095,7 +22125,7 @@
         <v>923</v>
       </c>
     </row>
-    <row r="572" spans="2:13" x14ac:dyDescent="0.3">
+    <row r="572" spans="2:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="C572" t="s">
         <v>45</v>
       </c>
@@ -22125,7 +22155,7 @@
         <v>923</v>
       </c>
     </row>
-    <row r="573" spans="2:13" x14ac:dyDescent="0.3">
+    <row r="573" spans="2:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="B573" t="s">
         <v>137</v>
       </c>
@@ -22155,7 +22185,7 @@
         <v>929</v>
       </c>
     </row>
-    <row r="574" spans="2:13" x14ac:dyDescent="0.3">
+    <row r="574" spans="2:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="B574" t="s">
         <v>137</v>
       </c>
@@ -22185,7 +22215,7 @@
         <v>929</v>
       </c>
     </row>
-    <row r="575" spans="2:13" x14ac:dyDescent="0.3">
+    <row r="575" spans="2:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="B575" t="s">
         <v>137</v>
       </c>
@@ -22215,7 +22245,7 @@
         <v>935</v>
       </c>
     </row>
-    <row r="576" spans="2:13" x14ac:dyDescent="0.3">
+    <row r="576" spans="2:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="B576" t="s">
         <v>137</v>
       </c>
@@ -22245,7 +22275,7 @@
         <v>935</v>
       </c>
     </row>
-    <row r="577" spans="2:13" x14ac:dyDescent="0.3">
+    <row r="577" spans="2:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="B577" t="s">
         <v>137</v>
       </c>
@@ -22275,7 +22305,7 @@
         <v>941</v>
       </c>
     </row>
-    <row r="578" spans="2:13" x14ac:dyDescent="0.3">
+    <row r="578" spans="2:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="B578" t="s">
         <v>137</v>
       </c>
@@ -22305,7 +22335,7 @@
         <v>941</v>
       </c>
     </row>
-    <row r="579" spans="2:13" x14ac:dyDescent="0.3">
+    <row r="579" spans="2:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="B579" t="s">
         <v>137</v>
       </c>
@@ -22335,7 +22365,7 @@
         <v>946</v>
       </c>
     </row>
-    <row r="580" spans="2:13" x14ac:dyDescent="0.3">
+    <row r="580" spans="2:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="B580" t="s">
         <v>137</v>
       </c>
@@ -22365,7 +22395,7 @@
         <v>946</v>
       </c>
     </row>
-    <row r="581" spans="2:13" x14ac:dyDescent="0.3">
+    <row r="581" spans="2:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="B581" t="s">
         <v>137</v>
       </c>
@@ -22395,7 +22425,7 @@
         <v>946</v>
       </c>
     </row>
-    <row r="582" spans="2:13" x14ac:dyDescent="0.3">
+    <row r="582" spans="2:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="C582" t="s">
         <v>154</v>
       </c>
@@ -22425,7 +22455,7 @@
         <v>953</v>
       </c>
     </row>
-    <row r="583" spans="2:13" x14ac:dyDescent="0.3">
+    <row r="583" spans="2:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="C583" t="s">
         <v>154</v>
       </c>
@@ -22455,7 +22485,7 @@
         <v>953</v>
       </c>
     </row>
-    <row r="584" spans="2:13" x14ac:dyDescent="0.3">
+    <row r="584" spans="2:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="C584" t="s">
         <v>154</v>
       </c>
@@ -22485,7 +22515,7 @@
         <v>953</v>
       </c>
     </row>
-    <row r="585" spans="2:13" x14ac:dyDescent="0.3">
+    <row r="585" spans="2:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="C585" t="s">
         <v>154</v>
       </c>
@@ -22515,7 +22545,7 @@
         <v>953</v>
       </c>
     </row>
-    <row r="586" spans="2:13" x14ac:dyDescent="0.3">
+    <row r="586" spans="2:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="C586" t="s">
         <v>27</v>
       </c>
@@ -22545,7 +22575,7 @@
         <v>959</v>
       </c>
     </row>
-    <row r="587" spans="2:13" x14ac:dyDescent="0.3">
+    <row r="587" spans="2:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="C587" t="s">
         <v>27</v>
       </c>
@@ -22575,7 +22605,7 @@
         <v>959</v>
       </c>
     </row>
-    <row r="588" spans="2:13" x14ac:dyDescent="0.3">
+    <row r="588" spans="2:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="C588" t="s">
         <v>27</v>
       </c>
@@ -22605,7 +22635,7 @@
         <v>959</v>
       </c>
     </row>
-    <row r="589" spans="2:13" x14ac:dyDescent="0.3">
+    <row r="589" spans="2:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="C589" t="s">
         <v>27</v>
       </c>
@@ -22635,7 +22665,7 @@
         <v>959</v>
       </c>
     </row>
-    <row r="590" spans="2:13" x14ac:dyDescent="0.3">
+    <row r="590" spans="2:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="C590" t="s">
         <v>45</v>
       </c>
@@ -22665,7 +22695,7 @@
         <v>965</v>
       </c>
     </row>
-    <row r="591" spans="2:13" x14ac:dyDescent="0.3">
+    <row r="591" spans="2:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="C591" t="s">
         <v>45</v>
       </c>
@@ -22695,7 +22725,7 @@
         <v>965</v>
       </c>
     </row>
-    <row r="592" spans="2:13" x14ac:dyDescent="0.3">
+    <row r="592" spans="2:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="C592" t="s">
         <v>45</v>
       </c>
@@ -22725,7 +22755,7 @@
         <v>965</v>
       </c>
     </row>
-    <row r="593" spans="2:13" x14ac:dyDescent="0.3">
+    <row r="593" spans="2:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="C593" t="s">
         <v>45</v>
       </c>
@@ -22755,7 +22785,7 @@
         <v>965</v>
       </c>
     </row>
-    <row r="594" spans="2:13" x14ac:dyDescent="0.3">
+    <row r="594" spans="2:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="C594" t="s">
         <v>69</v>
       </c>
@@ -22785,7 +22815,7 @@
         <v>970</v>
       </c>
     </row>
-    <row r="595" spans="2:13" x14ac:dyDescent="0.3">
+    <row r="595" spans="2:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="C595" t="s">
         <v>69</v>
       </c>
@@ -22815,7 +22845,7 @@
         <v>970</v>
       </c>
     </row>
-    <row r="596" spans="2:13" x14ac:dyDescent="0.3">
+    <row r="596" spans="2:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="C596" t="s">
         <v>69</v>
       </c>
@@ -22845,7 +22875,7 @@
         <v>970</v>
       </c>
     </row>
-    <row r="597" spans="2:13" x14ac:dyDescent="0.3">
+    <row r="597" spans="2:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="C597" t="s">
         <v>69</v>
       </c>
@@ -22875,7 +22905,7 @@
         <v>970</v>
       </c>
     </row>
-    <row r="598" spans="2:13" x14ac:dyDescent="0.3">
+    <row r="598" spans="2:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="C598" t="s">
         <v>69</v>
       </c>
@@ -22905,7 +22935,7 @@
         <v>970</v>
       </c>
     </row>
-    <row r="599" spans="2:13" x14ac:dyDescent="0.3">
+    <row r="599" spans="2:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="C599" t="s">
         <v>69</v>
       </c>
@@ -22935,7 +22965,7 @@
         <v>970</v>
       </c>
     </row>
-    <row r="600" spans="2:13" x14ac:dyDescent="0.3">
+    <row r="600" spans="2:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="C600" t="s">
         <v>69</v>
       </c>
@@ -22965,7 +22995,7 @@
         <v>970</v>
       </c>
     </row>
-    <row r="601" spans="2:13" x14ac:dyDescent="0.3">
+    <row r="601" spans="2:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="C601" t="s">
         <v>69</v>
       </c>
@@ -22995,7 +23025,7 @@
         <v>970</v>
       </c>
     </row>
-    <row r="602" spans="2:13" x14ac:dyDescent="0.3">
+    <row r="602" spans="2:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="C602" t="s">
         <v>90</v>
       </c>
@@ -23025,7 +23055,7 @@
         <v>979</v>
       </c>
     </row>
-    <row r="603" spans="2:13" x14ac:dyDescent="0.3">
+    <row r="603" spans="2:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="C603" t="s">
         <v>90</v>
       </c>
@@ -23055,7 +23085,7 @@
         <v>979</v>
       </c>
     </row>
-    <row r="604" spans="2:13" x14ac:dyDescent="0.3">
+    <row r="604" spans="2:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="C604" t="s">
         <v>90</v>
       </c>
@@ -23085,7 +23115,7 @@
         <v>979</v>
       </c>
     </row>
-    <row r="605" spans="2:13" x14ac:dyDescent="0.3">
+    <row r="605" spans="2:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="C605" t="s">
         <v>90</v>
       </c>
@@ -23115,7 +23145,7 @@
         <v>979</v>
       </c>
     </row>
-    <row r="606" spans="2:13" x14ac:dyDescent="0.3">
+    <row r="606" spans="2:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="B606" t="s">
         <v>162</v>
       </c>
@@ -23145,7 +23175,7 @@
         <v>984</v>
       </c>
     </row>
-    <row r="607" spans="2:13" x14ac:dyDescent="0.3">
+    <row r="607" spans="2:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="B607" t="s">
         <v>162</v>
       </c>
@@ -23175,7 +23205,7 @@
         <v>984</v>
       </c>
     </row>
-    <row r="608" spans="2:13" x14ac:dyDescent="0.3">
+    <row r="608" spans="2:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="B608" t="s">
         <v>162</v>
       </c>
@@ -23205,7 +23235,7 @@
         <v>984</v>
       </c>
     </row>
-    <row r="609" spans="2:13" x14ac:dyDescent="0.3">
+    <row r="609" spans="2:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="B609" t="s">
         <v>162</v>
       </c>
@@ -23235,7 +23265,7 @@
         <v>984</v>
       </c>
     </row>
-    <row r="610" spans="2:13" x14ac:dyDescent="0.3">
+    <row r="610" spans="2:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="B610" t="s">
         <v>162</v>
       </c>
@@ -23265,7 +23295,7 @@
         <v>984</v>
       </c>
     </row>
-    <row r="611" spans="2:13" x14ac:dyDescent="0.3">
+    <row r="611" spans="2:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="B611" t="s">
         <v>162</v>
       </c>
@@ -23295,7 +23325,7 @@
         <v>984</v>
       </c>
     </row>
-    <row r="612" spans="2:13" x14ac:dyDescent="0.3">
+    <row r="612" spans="2:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="B612" t="s">
         <v>162</v>
       </c>
@@ -23325,7 +23355,7 @@
         <v>984</v>
       </c>
     </row>
-    <row r="613" spans="2:13" x14ac:dyDescent="0.3">
+    <row r="613" spans="2:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="B613" t="s">
         <v>162</v>
       </c>
@@ -23355,7 +23385,7 @@
         <v>984</v>
       </c>
     </row>
-    <row r="614" spans="2:13" x14ac:dyDescent="0.3">
+    <row r="614" spans="2:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="B614" t="s">
         <v>162</v>
       </c>
@@ -23385,7 +23415,7 @@
         <v>984</v>
       </c>
     </row>
-    <row r="615" spans="2:13" x14ac:dyDescent="0.3">
+    <row r="615" spans="2:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="C615" t="s">
         <v>516</v>
       </c>
@@ -23415,7 +23445,7 @@
         <v>995</v>
       </c>
     </row>
-    <row r="616" spans="2:13" x14ac:dyDescent="0.3">
+    <row r="616" spans="2:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="C616" t="s">
         <v>516</v>
       </c>
@@ -23445,7 +23475,7 @@
         <v>995</v>
       </c>
     </row>
-    <row r="617" spans="2:13" x14ac:dyDescent="0.3">
+    <row r="617" spans="2:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="C617" t="s">
         <v>516</v>
       </c>
@@ -23475,7 +23505,7 @@
         <v>995</v>
       </c>
     </row>
-    <row r="618" spans="2:13" x14ac:dyDescent="0.3">
+    <row r="618" spans="2:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="C618" t="s">
         <v>516</v>
       </c>
@@ -23505,7 +23535,7 @@
         <v>995</v>
       </c>
     </row>
-    <row r="619" spans="2:13" x14ac:dyDescent="0.3">
+    <row r="619" spans="2:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="C619" t="s">
         <v>516</v>
       </c>
@@ -23535,7 +23565,7 @@
         <v>995</v>
       </c>
     </row>
-    <row r="620" spans="2:13" x14ac:dyDescent="0.3">
+    <row r="620" spans="2:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="C620" t="s">
         <v>516</v>
       </c>
@@ -23565,7 +23595,7 @@
         <v>995</v>
       </c>
     </row>
-    <row r="621" spans="2:13" x14ac:dyDescent="0.3">
+    <row r="621" spans="2:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="C621" t="s">
         <v>101</v>
       </c>
@@ -23595,7 +23625,7 @@
         <v>1008</v>
       </c>
     </row>
-    <row r="622" spans="2:13" x14ac:dyDescent="0.3">
+    <row r="622" spans="2:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="C622" t="s">
         <v>101</v>
       </c>
@@ -23625,7 +23655,7 @@
         <v>1008</v>
       </c>
     </row>
-    <row r="623" spans="2:13" x14ac:dyDescent="0.3">
+    <row r="623" spans="2:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="C623" t="s">
         <v>101</v>
       </c>
@@ -23655,7 +23685,7 @@
         <v>1008</v>
       </c>
     </row>
-    <row r="624" spans="2:13" x14ac:dyDescent="0.3">
+    <row r="624" spans="2:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="C624" t="s">
         <v>101</v>
       </c>
@@ -23685,7 +23715,7 @@
         <v>1008</v>
       </c>
     </row>
-    <row r="625" spans="2:13" x14ac:dyDescent="0.3">
+    <row r="625" spans="2:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="C625" t="s">
         <v>101</v>
       </c>
@@ -23715,7 +23745,7 @@
         <v>1008</v>
       </c>
     </row>
-    <row r="626" spans="2:13" x14ac:dyDescent="0.3">
+    <row r="626" spans="2:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="C626" t="s">
         <v>101</v>
       </c>
@@ -23745,7 +23775,7 @@
         <v>1008</v>
       </c>
     </row>
-    <row r="627" spans="2:13" x14ac:dyDescent="0.3">
+    <row r="627" spans="2:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="D627" t="s">
         <v>893</v>
       </c>
@@ -23772,7 +23802,7 @@
         <v>1015</v>
       </c>
     </row>
-    <row r="628" spans="2:13" x14ac:dyDescent="0.3">
+    <row r="628" spans="2:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="D628" t="s">
         <v>893</v>
       </c>
@@ -23799,7 +23829,7 @@
         <v>1015</v>
       </c>
     </row>
-    <row r="629" spans="2:13" x14ac:dyDescent="0.3">
+    <row r="629" spans="2:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="C629" t="s">
         <v>399</v>
       </c>
@@ -23829,7 +23859,7 @@
         <v>1020</v>
       </c>
     </row>
-    <row r="630" spans="2:13" x14ac:dyDescent="0.3">
+    <row r="630" spans="2:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="C630" t="s">
         <v>399</v>
       </c>
@@ -23859,7 +23889,7 @@
         <v>1020</v>
       </c>
     </row>
-    <row r="631" spans="2:13" x14ac:dyDescent="0.3">
+    <row r="631" spans="2:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="B631" t="s">
         <v>162</v>
       </c>
@@ -23889,7 +23919,7 @@
         <v>1024</v>
       </c>
     </row>
-    <row r="632" spans="2:13" x14ac:dyDescent="0.3">
+    <row r="632" spans="2:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="B632" t="s">
         <v>162</v>
       </c>
@@ -23919,7 +23949,7 @@
         <v>1024</v>
       </c>
     </row>
-    <row r="633" spans="2:13" x14ac:dyDescent="0.3">
+    <row r="633" spans="2:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="B633" t="s">
         <v>162</v>
       </c>
@@ -23949,7 +23979,7 @@
         <v>1024</v>
       </c>
     </row>
-    <row r="634" spans="2:13" x14ac:dyDescent="0.3">
+    <row r="634" spans="2:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="B634" t="s">
         <v>162</v>
       </c>
@@ -23979,7 +24009,7 @@
         <v>1024</v>
       </c>
     </row>
-    <row r="635" spans="2:13" x14ac:dyDescent="0.3">
+    <row r="635" spans="2:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="B635" t="s">
         <v>162</v>
       </c>
@@ -24009,7 +24039,7 @@
         <v>1024</v>
       </c>
     </row>
-    <row r="636" spans="2:13" x14ac:dyDescent="0.3">
+    <row r="636" spans="2:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="B636" t="s">
         <v>162</v>
       </c>
@@ -24039,7 +24069,7 @@
         <v>1024</v>
       </c>
     </row>
-    <row r="637" spans="2:13" x14ac:dyDescent="0.3">
+    <row r="637" spans="2:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="B637" t="s">
         <v>162</v>
       </c>
@@ -24069,7 +24099,7 @@
         <v>1024</v>
       </c>
     </row>
-    <row r="638" spans="2:13" x14ac:dyDescent="0.3">
+    <row r="638" spans="2:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="B638" t="s">
         <v>162</v>
       </c>
@@ -24099,7 +24129,7 @@
         <v>1024</v>
       </c>
     </row>
-    <row r="639" spans="2:13" x14ac:dyDescent="0.3">
+    <row r="639" spans="2:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="B639" t="s">
         <v>162</v>
       </c>
@@ -24129,7 +24159,7 @@
         <v>1024</v>
       </c>
     </row>
-    <row r="640" spans="2:13" x14ac:dyDescent="0.3">
+    <row r="640" spans="2:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="C640" t="s">
         <v>129</v>
       </c>
@@ -24159,7 +24189,7 @@
         <v>1032</v>
       </c>
     </row>
-    <row r="641" spans="2:13" x14ac:dyDescent="0.3">
+    <row r="641" spans="2:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="C641" t="s">
         <v>129</v>
       </c>
@@ -24189,7 +24219,7 @@
         <v>1032</v>
       </c>
     </row>
-    <row r="642" spans="2:13" x14ac:dyDescent="0.3">
+    <row r="642" spans="2:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="C642" t="s">
         <v>129</v>
       </c>
@@ -24219,7 +24249,7 @@
         <v>1032</v>
       </c>
     </row>
-    <row r="643" spans="2:13" x14ac:dyDescent="0.3">
+    <row r="643" spans="2:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="C643" t="s">
         <v>129</v>
       </c>
@@ -24249,7 +24279,7 @@
         <v>1032</v>
       </c>
     </row>
-    <row r="644" spans="2:13" x14ac:dyDescent="0.3">
+    <row r="644" spans="2:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="D644" t="s">
         <v>1035</v>
       </c>
@@ -24276,7 +24306,7 @@
         <v>1037</v>
       </c>
     </row>
-    <row r="645" spans="2:13" x14ac:dyDescent="0.3">
+    <row r="645" spans="2:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="D645" t="s">
         <v>1035</v>
       </c>
@@ -24303,7 +24333,7 @@
         <v>1037</v>
       </c>
     </row>
-    <row r="646" spans="2:13" x14ac:dyDescent="0.3">
+    <row r="646" spans="2:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="D646" t="s">
         <v>1035</v>
       </c>
@@ -24330,7 +24360,7 @@
         <v>1037</v>
       </c>
     </row>
-    <row r="647" spans="2:13" x14ac:dyDescent="0.3">
+    <row r="647" spans="2:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="D647" t="s">
         <v>1035</v>
       </c>
@@ -24357,7 +24387,7 @@
         <v>1037</v>
       </c>
     </row>
-    <row r="648" spans="2:13" x14ac:dyDescent="0.3">
+    <row r="648" spans="2:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="C648" t="s">
         <v>746</v>
       </c>
@@ -24384,7 +24414,7 @@
         <v>1044</v>
       </c>
     </row>
-    <row r="649" spans="2:13" x14ac:dyDescent="0.3">
+    <row r="649" spans="2:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="C649" t="s">
         <v>746</v>
       </c>
@@ -24411,7 +24441,7 @@
         <v>1044</v>
       </c>
     </row>
-    <row r="650" spans="2:13" x14ac:dyDescent="0.3">
+    <row r="650" spans="2:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="C650" t="s">
         <v>154</v>
       </c>
@@ -24441,7 +24471,7 @@
         <v>1049</v>
       </c>
     </row>
-    <row r="651" spans="2:13" x14ac:dyDescent="0.3">
+    <row r="651" spans="2:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="C651" t="s">
         <v>154</v>
       </c>
@@ -24471,7 +24501,7 @@
         <v>1049</v>
       </c>
     </row>
-    <row r="652" spans="2:13" x14ac:dyDescent="0.3">
+    <row r="652" spans="2:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="C652" t="s">
         <v>154</v>
       </c>
@@ -24501,7 +24531,7 @@
         <v>1049</v>
       </c>
     </row>
-    <row r="653" spans="2:13" x14ac:dyDescent="0.3">
+    <row r="653" spans="2:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="C653" t="s">
         <v>154</v>
       </c>
@@ -24531,7 +24561,7 @@
         <v>1049</v>
       </c>
     </row>
-    <row r="654" spans="2:13" x14ac:dyDescent="0.3">
+    <row r="654" spans="2:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="B654" t="s">
         <v>137</v>
       </c>
@@ -24558,7 +24588,7 @@
         <v>1055</v>
       </c>
     </row>
-    <row r="655" spans="2:13" x14ac:dyDescent="0.3">
+    <row r="655" spans="2:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="B655" t="s">
         <v>137</v>
       </c>
@@ -24588,7 +24618,7 @@
         <v>1055</v>
       </c>
     </row>
-    <row r="656" spans="2:13" x14ac:dyDescent="0.3">
+    <row r="656" spans="2:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="B656" t="s">
         <v>137</v>
       </c>
@@ -24618,7 +24648,7 @@
         <v>1055</v>
       </c>
     </row>
-    <row r="657" spans="2:13" x14ac:dyDescent="0.3">
+    <row r="657" spans="2:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="C657" t="s">
         <v>45</v>
       </c>
@@ -24648,7 +24678,7 @@
         <v>1063</v>
       </c>
     </row>
-    <row r="658" spans="2:13" x14ac:dyDescent="0.3">
+    <row r="658" spans="2:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="C658" t="s">
         <v>45</v>
       </c>
@@ -24678,7 +24708,7 @@
         <v>1063</v>
       </c>
     </row>
-    <row r="659" spans="2:13" x14ac:dyDescent="0.3">
+    <row r="659" spans="2:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="C659" t="s">
         <v>45</v>
       </c>
@@ -24711,7 +24741,7 @@
         <v>1063</v>
       </c>
     </row>
-    <row r="660" spans="2:13" x14ac:dyDescent="0.3">
+    <row r="660" spans="2:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="C660" t="s">
         <v>45</v>
       </c>
@@ -24741,7 +24771,7 @@
         <v>1063</v>
       </c>
     </row>
-    <row r="661" spans="2:13" x14ac:dyDescent="0.3">
+    <row r="661" spans="2:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="B661" t="s">
         <v>592</v>
       </c>
@@ -24774,7 +24804,7 @@
         <v>1072</v>
       </c>
     </row>
-    <row r="662" spans="2:13" x14ac:dyDescent="0.3">
+    <row r="662" spans="2:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="B662" t="s">
         <v>592</v>
       </c>
@@ -24807,7 +24837,7 @@
         <v>1072</v>
       </c>
     </row>
-    <row r="663" spans="2:13" x14ac:dyDescent="0.3">
+    <row r="663" spans="2:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="B663" t="s">
         <v>592</v>
       </c>
@@ -24840,7 +24870,7 @@
         <v>1072</v>
       </c>
     </row>
-    <row r="664" spans="2:13" x14ac:dyDescent="0.3">
+    <row r="664" spans="2:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="B664" t="s">
         <v>592</v>
       </c>
@@ -24876,7 +24906,7 @@
         <v>1072</v>
       </c>
     </row>
-    <row r="665" spans="2:13" x14ac:dyDescent="0.3">
+    <row r="665" spans="2:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="B665" t="s">
         <v>592</v>
       </c>
@@ -24909,7 +24939,7 @@
         <v>1072</v>
       </c>
     </row>
-    <row r="666" spans="2:13" x14ac:dyDescent="0.3">
+    <row r="666" spans="2:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="B666" t="s">
         <v>592</v>
       </c>
@@ -24945,7 +24975,7 @@
         <v>1072</v>
       </c>
     </row>
-    <row r="667" spans="2:13" x14ac:dyDescent="0.3">
+    <row r="667" spans="2:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="B667" t="s">
         <v>592</v>
       </c>
@@ -24981,7 +25011,7 @@
         <v>1072</v>
       </c>
     </row>
-    <row r="668" spans="2:13" x14ac:dyDescent="0.3">
+    <row r="668" spans="2:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="B668" t="s">
         <v>592</v>
       </c>
@@ -25014,7 +25044,7 @@
         <v>1072</v>
       </c>
     </row>
-    <row r="669" spans="2:13" x14ac:dyDescent="0.3">
+    <row r="669" spans="2:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="D669" t="s">
         <v>1083</v>
       </c>
@@ -25041,7 +25071,7 @@
         <v>1085</v>
       </c>
     </row>
-    <row r="670" spans="2:13" x14ac:dyDescent="0.3">
+    <row r="670" spans="2:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="D670" t="s">
         <v>1083</v>
       </c>
@@ -25068,7 +25098,7 @@
         <v>1085</v>
       </c>
     </row>
-    <row r="671" spans="2:13" x14ac:dyDescent="0.3">
+    <row r="671" spans="2:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="D671" t="s">
         <v>1083</v>
       </c>
@@ -25095,7 +25125,7 @@
         <v>1085</v>
       </c>
     </row>
-    <row r="672" spans="2:13" x14ac:dyDescent="0.3">
+    <row r="672" spans="2:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="D672" t="s">
         <v>1083</v>
       </c>
@@ -25122,7 +25152,7 @@
         <v>1085</v>
       </c>
     </row>
-    <row r="673" spans="3:13" x14ac:dyDescent="0.3">
+    <row r="673" spans="3:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="C673" t="s">
         <v>1089</v>
       </c>
@@ -25152,7 +25182,7 @@
         <v>1091</v>
       </c>
     </row>
-    <row r="674" spans="3:13" x14ac:dyDescent="0.3">
+    <row r="674" spans="3:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="C674" t="s">
         <v>1089</v>
       </c>
@@ -25182,7 +25212,7 @@
         <v>1091</v>
       </c>
     </row>
-    <row r="675" spans="3:13" x14ac:dyDescent="0.3">
+    <row r="675" spans="3:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="C675" t="s">
         <v>1089</v>
       </c>
@@ -25212,7 +25242,7 @@
         <v>1091</v>
       </c>
     </row>
-    <row r="676" spans="3:13" x14ac:dyDescent="0.3">
+    <row r="676" spans="3:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="C676" t="s">
         <v>1089</v>
       </c>
@@ -25242,7 +25272,7 @@
         <v>1091</v>
       </c>
     </row>
-    <row r="677" spans="3:13" x14ac:dyDescent="0.3">
+    <row r="677" spans="3:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="C677" t="s">
         <v>1089</v>
       </c>
@@ -25272,7 +25302,7 @@
         <v>1091</v>
       </c>
     </row>
-    <row r="678" spans="3:13" x14ac:dyDescent="0.3">
+    <row r="678" spans="3:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="C678" t="s">
         <v>1089</v>
       </c>
@@ -25302,7 +25332,7 @@
         <v>1091</v>
       </c>
     </row>
-    <row r="679" spans="3:13" x14ac:dyDescent="0.3">
+    <row r="679" spans="3:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="C679" t="s">
         <v>1089</v>
       </c>
@@ -25332,7 +25362,7 @@
         <v>1091</v>
       </c>
     </row>
-    <row r="680" spans="3:13" x14ac:dyDescent="0.3">
+    <row r="680" spans="3:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="C680" t="s">
         <v>1089</v>
       </c>
@@ -25362,7 +25392,7 @@
         <v>1091</v>
       </c>
     </row>
-    <row r="681" spans="3:13" x14ac:dyDescent="0.3">
+    <row r="681" spans="3:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="C681" t="s">
         <v>69</v>
       </c>
@@ -25392,7 +25422,7 @@
         <v>1100</v>
       </c>
     </row>
-    <row r="682" spans="3:13" x14ac:dyDescent="0.3">
+    <row r="682" spans="3:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="C682" t="s">
         <v>69</v>
       </c>
@@ -25422,7 +25452,7 @@
         <v>1100</v>
       </c>
     </row>
-    <row r="683" spans="3:13" x14ac:dyDescent="0.3">
+    <row r="683" spans="3:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="C683" t="s">
         <v>69</v>
       </c>
@@ -25452,7 +25482,7 @@
         <v>1100</v>
       </c>
     </row>
-    <row r="684" spans="3:13" x14ac:dyDescent="0.3">
+    <row r="684" spans="3:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="C684" t="s">
         <v>69</v>
       </c>
@@ -25482,7 +25512,7 @@
         <v>1100</v>
       </c>
     </row>
-    <row r="685" spans="3:13" x14ac:dyDescent="0.3">
+    <row r="685" spans="3:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="C685" t="s">
         <v>69</v>
       </c>
@@ -25512,7 +25542,7 @@
         <v>1100</v>
       </c>
     </row>
-    <row r="686" spans="3:13" x14ac:dyDescent="0.3">
+    <row r="686" spans="3:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="C686" t="s">
         <v>69</v>
       </c>
@@ -25542,7 +25572,7 @@
         <v>1100</v>
       </c>
     </row>
-    <row r="687" spans="3:13" x14ac:dyDescent="0.3">
+    <row r="687" spans="3:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="C687" t="s">
         <v>69</v>
       </c>
@@ -25572,7 +25602,7 @@
         <v>1100</v>
       </c>
     </row>
-    <row r="688" spans="3:13" x14ac:dyDescent="0.3">
+    <row r="688" spans="3:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="C688" t="s">
         <v>69</v>
       </c>
@@ -25602,7 +25632,7 @@
         <v>1100</v>
       </c>
     </row>
-    <row r="689" spans="2:13" x14ac:dyDescent="0.3">
+    <row r="689" spans="2:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="B689" t="s">
         <v>162</v>
       </c>
@@ -25632,7 +25662,7 @@
         <v>1110</v>
       </c>
     </row>
-    <row r="690" spans="2:13" x14ac:dyDescent="0.3">
+    <row r="690" spans="2:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="B690" t="s">
         <v>162</v>
       </c>
@@ -25662,7 +25692,7 @@
         <v>1110</v>
       </c>
     </row>
-    <row r="691" spans="2:13" x14ac:dyDescent="0.3">
+    <row r="691" spans="2:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="B691" t="s">
         <v>162</v>
       </c>
@@ -25692,7 +25722,7 @@
         <v>1110</v>
       </c>
     </row>
-    <row r="692" spans="2:13" x14ac:dyDescent="0.3">
+    <row r="692" spans="2:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="B692" t="s">
         <v>162</v>
       </c>
@@ -25722,7 +25752,7 @@
         <v>1110</v>
       </c>
     </row>
-    <row r="693" spans="2:13" x14ac:dyDescent="0.3">
+    <row r="693" spans="2:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="B693" t="s">
         <v>162</v>
       </c>
@@ -25752,7 +25782,7 @@
         <v>1110</v>
       </c>
     </row>
-    <row r="694" spans="2:13" x14ac:dyDescent="0.3">
+    <row r="694" spans="2:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="B694" t="s">
         <v>162</v>
       </c>
@@ -25782,7 +25812,7 @@
         <v>1110</v>
       </c>
     </row>
-    <row r="695" spans="2:13" x14ac:dyDescent="0.3">
+    <row r="695" spans="2:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="B695" t="s">
         <v>162</v>
       </c>
@@ -25812,7 +25842,7 @@
         <v>1110</v>
       </c>
     </row>
-    <row r="696" spans="2:13" x14ac:dyDescent="0.3">
+    <row r="696" spans="2:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="B696" t="s">
         <v>162</v>
       </c>
@@ -25842,7 +25872,7 @@
         <v>1110</v>
       </c>
     </row>
-    <row r="697" spans="2:13" x14ac:dyDescent="0.3">
+    <row r="697" spans="2:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="B697" t="s">
         <v>162</v>
       </c>
@@ -25872,7 +25902,7 @@
         <v>1110</v>
       </c>
     </row>
-    <row r="698" spans="2:13" x14ac:dyDescent="0.3">
+    <row r="698" spans="2:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="C698" t="s">
         <v>516</v>
       </c>
@@ -25902,7 +25932,7 @@
         <v>1120</v>
       </c>
     </row>
-    <row r="699" spans="2:13" x14ac:dyDescent="0.3">
+    <row r="699" spans="2:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="C699" t="s">
         <v>516</v>
       </c>
@@ -25932,7 +25962,7 @@
         <v>1120</v>
       </c>
     </row>
-    <row r="700" spans="2:13" x14ac:dyDescent="0.3">
+    <row r="700" spans="2:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="C700" t="s">
         <v>516</v>
       </c>
@@ -25962,7 +25992,7 @@
         <v>1120</v>
       </c>
     </row>
-    <row r="701" spans="2:13" x14ac:dyDescent="0.3">
+    <row r="701" spans="2:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="C701" t="s">
         <v>516</v>
       </c>
@@ -25992,7 +26022,7 @@
         <v>1120</v>
       </c>
     </row>
-    <row r="702" spans="2:13" x14ac:dyDescent="0.3">
+    <row r="702" spans="2:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="C702" t="s">
         <v>516</v>
       </c>
@@ -26022,7 +26052,7 @@
         <v>1120</v>
       </c>
     </row>
-    <row r="703" spans="2:13" x14ac:dyDescent="0.3">
+    <row r="703" spans="2:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="C703" t="s">
         <v>516</v>
       </c>
@@ -26052,7 +26082,7 @@
         <v>1120</v>
       </c>
     </row>
-    <row r="704" spans="2:13" x14ac:dyDescent="0.3">
+    <row r="704" spans="2:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="C704" t="s">
         <v>101</v>
       </c>
@@ -26082,7 +26112,7 @@
         <v>1131</v>
       </c>
     </row>
-    <row r="705" spans="2:13" x14ac:dyDescent="0.3">
+    <row r="705" spans="2:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="C705" t="s">
         <v>101</v>
       </c>
@@ -26112,7 +26142,7 @@
         <v>1131</v>
       </c>
     </row>
-    <row r="706" spans="2:13" x14ac:dyDescent="0.3">
+    <row r="706" spans="2:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="C706" t="s">
         <v>101</v>
       </c>
@@ -26142,7 +26172,7 @@
         <v>1131</v>
       </c>
     </row>
-    <row r="707" spans="2:13" x14ac:dyDescent="0.3">
+    <row r="707" spans="2:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="C707" t="s">
         <v>101</v>
       </c>
@@ -26172,7 +26202,7 @@
         <v>1131</v>
       </c>
     </row>
-    <row r="708" spans="2:13" x14ac:dyDescent="0.3">
+    <row r="708" spans="2:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="C708" t="s">
         <v>101</v>
       </c>
@@ -26202,7 +26232,7 @@
         <v>1131</v>
       </c>
     </row>
-    <row r="709" spans="2:13" x14ac:dyDescent="0.3">
+    <row r="709" spans="2:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="C709" t="s">
         <v>101</v>
       </c>
@@ -26232,7 +26262,7 @@
         <v>1131</v>
       </c>
     </row>
-    <row r="710" spans="2:13" x14ac:dyDescent="0.3">
+    <row r="710" spans="2:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="C710" t="s">
         <v>399</v>
       </c>
@@ -26262,7 +26292,7 @@
         <v>1139</v>
       </c>
     </row>
-    <row r="711" spans="2:13" x14ac:dyDescent="0.3">
+    <row r="711" spans="2:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="C711" t="s">
         <v>399</v>
       </c>
@@ -26292,7 +26322,7 @@
         <v>1139</v>
       </c>
     </row>
-    <row r="712" spans="2:13" x14ac:dyDescent="0.3">
+    <row r="712" spans="2:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="B712" t="s">
         <v>162</v>
       </c>
@@ -26322,7 +26352,7 @@
         <v>1143</v>
       </c>
     </row>
-    <row r="713" spans="2:13" x14ac:dyDescent="0.3">
+    <row r="713" spans="2:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="B713" t="s">
         <v>162</v>
       </c>
@@ -26352,7 +26382,7 @@
         <v>1143</v>
       </c>
     </row>
-    <row r="714" spans="2:13" x14ac:dyDescent="0.3">
+    <row r="714" spans="2:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="B714" t="s">
         <v>162</v>
       </c>
@@ -26382,7 +26412,7 @@
         <v>1143</v>
       </c>
     </row>
-    <row r="715" spans="2:13" x14ac:dyDescent="0.3">
+    <row r="715" spans="2:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="B715" t="s">
         <v>162</v>
       </c>
@@ -26412,7 +26442,7 @@
         <v>1143</v>
       </c>
     </row>
-    <row r="716" spans="2:13" x14ac:dyDescent="0.3">
+    <row r="716" spans="2:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="B716" t="s">
         <v>162</v>
       </c>
@@ -26442,7 +26472,7 @@
         <v>1143</v>
       </c>
     </row>
-    <row r="717" spans="2:13" x14ac:dyDescent="0.3">
+    <row r="717" spans="2:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="B717" t="s">
         <v>162</v>
       </c>
@@ -26472,7 +26502,7 @@
         <v>1143</v>
       </c>
     </row>
-    <row r="718" spans="2:13" x14ac:dyDescent="0.3">
+    <row r="718" spans="2:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="B718" t="s">
         <v>162</v>
       </c>
@@ -26502,7 +26532,7 @@
         <v>1143</v>
       </c>
     </row>
-    <row r="719" spans="2:13" x14ac:dyDescent="0.3">
+    <row r="719" spans="2:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="B719" t="s">
         <v>162</v>
       </c>
@@ -26532,7 +26562,7 @@
         <v>1143</v>
       </c>
     </row>
-    <row r="720" spans="2:13" x14ac:dyDescent="0.3">
+    <row r="720" spans="2:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="B720" t="s">
         <v>162</v>
       </c>
@@ -26562,7 +26592,7 @@
         <v>1143</v>
       </c>
     </row>
-    <row r="721" spans="2:13" x14ac:dyDescent="0.3">
+    <row r="721" spans="2:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="C721" t="s">
         <v>129</v>
       </c>
@@ -26592,7 +26622,7 @@
         <v>1153</v>
       </c>
     </row>
-    <row r="722" spans="2:13" x14ac:dyDescent="0.3">
+    <row r="722" spans="2:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="C722" t="s">
         <v>129</v>
       </c>
@@ -26622,7 +26652,7 @@
         <v>1153</v>
       </c>
     </row>
-    <row r="723" spans="2:13" x14ac:dyDescent="0.3">
+    <row r="723" spans="2:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="C723" t="s">
         <v>129</v>
       </c>
@@ -26652,7 +26682,7 @@
         <v>1153</v>
       </c>
     </row>
-    <row r="724" spans="2:13" x14ac:dyDescent="0.3">
+    <row r="724" spans="2:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="C724" t="s">
         <v>129</v>
       </c>
@@ -26682,7 +26712,7 @@
         <v>1153</v>
       </c>
     </row>
-    <row r="725" spans="2:13" x14ac:dyDescent="0.3">
+    <row r="725" spans="2:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="C725" t="s">
         <v>129</v>
       </c>
@@ -26712,7 +26742,7 @@
         <v>1153</v>
       </c>
     </row>
-    <row r="726" spans="2:13" x14ac:dyDescent="0.3">
+    <row r="726" spans="2:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="C726" t="s">
         <v>129</v>
       </c>
@@ -26742,7 +26772,7 @@
         <v>1153</v>
       </c>
     </row>
-    <row r="727" spans="2:13" x14ac:dyDescent="0.3">
+    <row r="727" spans="2:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="C727" t="s">
         <v>129</v>
       </c>
@@ -26772,7 +26802,7 @@
         <v>1153</v>
       </c>
     </row>
-    <row r="728" spans="2:13" x14ac:dyDescent="0.3">
+    <row r="728" spans="2:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="C728" t="s">
         <v>129</v>
       </c>
@@ -26802,7 +26832,7 @@
         <v>1153</v>
       </c>
     </row>
-    <row r="729" spans="2:13" x14ac:dyDescent="0.3">
+    <row r="729" spans="2:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="B729" t="s">
         <v>137</v>
       </c>
@@ -26832,7 +26862,7 @@
         <v>1162</v>
       </c>
     </row>
-    <row r="730" spans="2:13" x14ac:dyDescent="0.3">
+    <row r="730" spans="2:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="B730" t="s">
         <v>137</v>
       </c>
@@ -26862,7 +26892,7 @@
         <v>1162</v>
       </c>
     </row>
-    <row r="731" spans="2:13" x14ac:dyDescent="0.3">
+    <row r="731" spans="2:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="B731" t="s">
         <v>137</v>
       </c>
@@ -26892,7 +26922,7 @@
         <v>1162</v>
       </c>
     </row>
-    <row r="732" spans="2:13" x14ac:dyDescent="0.3">
+    <row r="732" spans="2:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="B732" t="s">
         <v>137</v>
       </c>
@@ -26919,7 +26949,7 @@
         <v>1170</v>
       </c>
     </row>
-    <row r="733" spans="2:13" x14ac:dyDescent="0.3">
+    <row r="733" spans="2:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="B733" t="s">
         <v>137</v>
       </c>
@@ -26946,7 +26976,7 @@
         <v>1170</v>
       </c>
     </row>
-    <row r="734" spans="2:13" x14ac:dyDescent="0.3">
+    <row r="734" spans="2:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="C734" t="s">
         <v>150</v>
       </c>
@@ -26976,7 +27006,7 @@
         <v>1174</v>
       </c>
     </row>
-    <row r="735" spans="2:13" x14ac:dyDescent="0.3">
+    <row r="735" spans="2:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="C735" t="s">
         <v>150</v>
       </c>
@@ -27006,7 +27036,7 @@
         <v>1174</v>
       </c>
     </row>
-    <row r="736" spans="2:13" x14ac:dyDescent="0.3">
+    <row r="736" spans="2:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="C736" t="s">
         <v>150</v>
       </c>
@@ -27036,7 +27066,7 @@
         <v>1174</v>
       </c>
     </row>
-    <row r="737" spans="2:13" x14ac:dyDescent="0.3">
+    <row r="737" spans="2:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="C737" t="s">
         <v>150</v>
       </c>
@@ -27066,7 +27096,7 @@
         <v>1174</v>
       </c>
     </row>
-    <row r="738" spans="2:13" x14ac:dyDescent="0.3">
+    <row r="738" spans="2:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="C738" t="s">
         <v>303</v>
       </c>
@@ -27096,7 +27126,7 @@
         <v>1180</v>
       </c>
     </row>
-    <row r="739" spans="2:13" x14ac:dyDescent="0.3">
+    <row r="739" spans="2:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="C739" t="s">
         <v>303</v>
       </c>
@@ -27126,7 +27156,7 @@
         <v>1180</v>
       </c>
     </row>
-    <row r="740" spans="2:13" x14ac:dyDescent="0.3">
+    <row r="740" spans="2:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="C740" t="s">
         <v>303</v>
       </c>
@@ -27156,7 +27186,7 @@
         <v>1180</v>
       </c>
     </row>
-    <row r="741" spans="2:13" x14ac:dyDescent="0.3">
+    <row r="741" spans="2:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="C741" t="s">
         <v>303</v>
       </c>
@@ -27186,7 +27216,7 @@
         <v>1180</v>
       </c>
     </row>
-    <row r="742" spans="2:13" x14ac:dyDescent="0.3">
+    <row r="742" spans="2:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="C742" t="s">
         <v>634</v>
       </c>
@@ -27216,7 +27246,7 @@
         <v>1187</v>
       </c>
     </row>
-    <row r="743" spans="2:13" x14ac:dyDescent="0.3">
+    <row r="743" spans="2:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="C743" t="s">
         <v>634</v>
       </c>
@@ -27246,7 +27276,7 @@
         <v>1187</v>
       </c>
     </row>
-    <row r="744" spans="2:13" x14ac:dyDescent="0.3">
+    <row r="744" spans="2:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="C744" t="s">
         <v>634</v>
       </c>
@@ -27276,7 +27306,7 @@
         <v>1187</v>
       </c>
     </row>
-    <row r="745" spans="2:13" x14ac:dyDescent="0.3">
+    <row r="745" spans="2:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="C745" t="s">
         <v>634</v>
       </c>
@@ -27306,7 +27336,7 @@
         <v>1187</v>
       </c>
     </row>
-    <row r="746" spans="2:13" x14ac:dyDescent="0.3">
+    <row r="746" spans="2:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="B746" t="s">
         <v>592</v>
       </c>
@@ -27367,7 +27397,7 @@
         <v>1187</v>
       </c>
     </row>
-    <row r="748" spans="2:13" x14ac:dyDescent="0.3">
+    <row r="748" spans="2:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="B748" t="s">
         <v>592</v>
       </c>
@@ -27399,7 +27429,7 @@
         <v>1187</v>
       </c>
     </row>
-    <row r="749" spans="2:13" x14ac:dyDescent="0.3">
+    <row r="749" spans="2:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="B749" t="s">
         <v>592</v>
       </c>
@@ -27431,7 +27461,7 @@
         <v>1187</v>
       </c>
     </row>
-    <row r="750" spans="2:13" x14ac:dyDescent="0.3">
+    <row r="750" spans="2:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="C750" t="s">
         <v>1201</v>
       </c>
@@ -27460,7 +27490,7 @@
         <v>1204</v>
       </c>
     </row>
-    <row r="751" spans="2:13" x14ac:dyDescent="0.3">
+    <row r="751" spans="2:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="C751" t="s">
         <v>1201</v>
       </c>
@@ -27489,7 +27519,7 @@
         <v>1204</v>
       </c>
     </row>
-    <row r="752" spans="2:13" x14ac:dyDescent="0.3">
+    <row r="752" spans="2:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="C752" t="s">
         <v>1201</v>
       </c>
@@ -27518,7 +27548,7 @@
         <v>1204</v>
       </c>
     </row>
-    <row r="753" spans="3:13" x14ac:dyDescent="0.3">
+    <row r="753" spans="3:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="C753" t="s">
         <v>1201</v>
       </c>
@@ -27547,7 +27577,7 @@
         <v>1204</v>
       </c>
     </row>
-    <row r="754" spans="3:13" x14ac:dyDescent="0.3">
+    <row r="754" spans="3:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="C754" t="s">
         <v>1201</v>
       </c>
@@ -27576,7 +27606,7 @@
         <v>1204</v>
       </c>
     </row>
-    <row r="755" spans="3:13" x14ac:dyDescent="0.3">
+    <row r="755" spans="3:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="C755" t="s">
         <v>1201</v>
       </c>
@@ -27605,7 +27635,7 @@
         <v>1204</v>
       </c>
     </row>
-    <row r="756" spans="3:13" x14ac:dyDescent="0.3">
+    <row r="756" spans="3:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="C756" t="s">
         <v>154</v>
       </c>
@@ -27634,7 +27664,7 @@
         <v>1214</v>
       </c>
     </row>
-    <row r="757" spans="3:13" x14ac:dyDescent="0.3">
+    <row r="757" spans="3:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="C757" t="s">
         <v>154</v>
       </c>
@@ -27663,7 +27693,7 @@
         <v>1214</v>
       </c>
     </row>
-    <row r="758" spans="3:13" x14ac:dyDescent="0.3">
+    <row r="758" spans="3:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="C758" t="s">
         <v>154</v>
       </c>
@@ -27692,7 +27722,7 @@
         <v>1214</v>
       </c>
     </row>
-    <row r="759" spans="3:13" x14ac:dyDescent="0.3">
+    <row r="759" spans="3:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="C759" t="s">
         <v>154</v>
       </c>
@@ -27721,7 +27751,7 @@
         <v>1214</v>
       </c>
     </row>
-    <row r="760" spans="3:13" x14ac:dyDescent="0.3">
+    <row r="760" spans="3:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="C760" t="s">
         <v>516</v>
       </c>
@@ -27747,7 +27777,7 @@
         <v>1221</v>
       </c>
     </row>
-    <row r="761" spans="3:13" x14ac:dyDescent="0.3">
+    <row r="761" spans="3:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="C761" t="s">
         <v>516</v>
       </c>
@@ -27773,7 +27803,7 @@
         <v>1221</v>
       </c>
     </row>
-    <row r="762" spans="3:13" x14ac:dyDescent="0.3">
+    <row r="762" spans="3:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="C762" t="s">
         <v>516</v>
       </c>
@@ -27799,7 +27829,7 @@
         <v>1221</v>
       </c>
     </row>
-    <row r="763" spans="3:13" x14ac:dyDescent="0.3">
+    <row r="763" spans="3:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="C763" t="s">
         <v>516</v>
       </c>
@@ -27825,7 +27855,7 @@
         <v>1221</v>
       </c>
     </row>
-    <row r="764" spans="3:13" x14ac:dyDescent="0.3">
+    <row r="764" spans="3:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="C764" t="s">
         <v>27</v>
       </c>
@@ -27854,7 +27884,7 @@
         <v>1230</v>
       </c>
     </row>
-    <row r="765" spans="3:13" x14ac:dyDescent="0.3">
+    <row r="765" spans="3:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="C765" t="s">
         <v>27</v>
       </c>
@@ -27883,7 +27913,7 @@
         <v>1230</v>
       </c>
     </row>
-    <row r="766" spans="3:13" x14ac:dyDescent="0.3">
+    <row r="766" spans="3:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="C766" t="s">
         <v>27</v>
       </c>
@@ -27912,7 +27942,7 @@
         <v>1230</v>
       </c>
     </row>
-    <row r="767" spans="3:13" x14ac:dyDescent="0.3">
+    <row r="767" spans="3:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="C767" t="s">
         <v>27</v>
       </c>
@@ -27941,7 +27971,7 @@
         <v>1230</v>
       </c>
     </row>
-    <row r="768" spans="3:13" x14ac:dyDescent="0.3">
+    <row r="768" spans="3:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="C768" t="s">
         <v>45</v>
       </c>
@@ -27970,7 +28000,7 @@
         <v>1237</v>
       </c>
     </row>
-    <row r="769" spans="3:13" x14ac:dyDescent="0.3">
+    <row r="769" spans="3:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="C769" t="s">
         <v>45</v>
       </c>
@@ -27999,7 +28029,7 @@
         <v>1237</v>
       </c>
     </row>
-    <row r="770" spans="3:13" x14ac:dyDescent="0.3">
+    <row r="770" spans="3:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="C770" t="s">
         <v>45</v>
       </c>
@@ -28028,7 +28058,7 @@
         <v>1237</v>
       </c>
     </row>
-    <row r="771" spans="3:13" x14ac:dyDescent="0.3">
+    <row r="771" spans="3:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="C771" t="s">
         <v>45</v>
       </c>
@@ -28057,7 +28087,7 @@
         <v>1237</v>
       </c>
     </row>
-    <row r="772" spans="3:13" x14ac:dyDescent="0.3">
+    <row r="772" spans="3:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="C772" t="s">
         <v>634</v>
       </c>
@@ -28086,7 +28116,7 @@
         <v>1242</v>
       </c>
     </row>
-    <row r="773" spans="3:13" x14ac:dyDescent="0.3">
+    <row r="773" spans="3:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="C773" t="s">
         <v>634</v>
       </c>
@@ -28115,7 +28145,7 @@
         <v>1242</v>
       </c>
     </row>
-    <row r="774" spans="3:13" x14ac:dyDescent="0.3">
+    <row r="774" spans="3:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="C774" t="s">
         <v>634</v>
       </c>
@@ -28144,7 +28174,7 @@
         <v>1242</v>
       </c>
     </row>
-    <row r="775" spans="3:13" x14ac:dyDescent="0.3">
+    <row r="775" spans="3:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="C775" t="s">
         <v>634</v>
       </c>
@@ -28173,7 +28203,7 @@
         <v>1242</v>
       </c>
     </row>
-    <row r="776" spans="3:13" x14ac:dyDescent="0.3">
+    <row r="776" spans="3:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="C776" t="s">
         <v>90</v>
       </c>
@@ -28202,7 +28232,7 @@
         <v>1247</v>
       </c>
     </row>
-    <row r="777" spans="3:13" x14ac:dyDescent="0.3">
+    <row r="777" spans="3:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="C777" t="s">
         <v>90</v>
       </c>
@@ -28231,7 +28261,7 @@
         <v>1247</v>
       </c>
     </row>
-    <row r="778" spans="3:13" x14ac:dyDescent="0.3">
+    <row r="778" spans="3:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="C778" t="s">
         <v>90</v>
       </c>
@@ -28260,7 +28290,7 @@
         <v>1247</v>
       </c>
     </row>
-    <row r="779" spans="3:13" x14ac:dyDescent="0.3">
+    <row r="779" spans="3:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="C779" t="s">
         <v>90</v>
       </c>
@@ -28289,7 +28319,7 @@
         <v>1247</v>
       </c>
     </row>
-    <row r="780" spans="3:13" x14ac:dyDescent="0.3">
+    <row r="780" spans="3:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="C780" t="s">
         <v>90</v>
       </c>
@@ -28318,7 +28348,7 @@
         <v>1247</v>
       </c>
     </row>
-    <row r="781" spans="3:13" x14ac:dyDescent="0.3">
+    <row r="781" spans="3:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="C781" t="s">
         <v>90</v>
       </c>
@@ -28347,7 +28377,7 @@
         <v>1247</v>
       </c>
     </row>
-    <row r="782" spans="3:13" x14ac:dyDescent="0.3">
+    <row r="782" spans="3:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="C782" t="s">
         <v>90</v>
       </c>
@@ -28376,7 +28406,7 @@
         <v>1247</v>
       </c>
     </row>
-    <row r="783" spans="3:13" x14ac:dyDescent="0.3">
+    <row r="783" spans="3:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="C783" t="s">
         <v>90</v>
       </c>
@@ -28405,7 +28435,7 @@
         <v>1247</v>
       </c>
     </row>
-    <row r="784" spans="3:13" x14ac:dyDescent="0.3">
+    <row r="784" spans="3:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="C784" t="s">
         <v>69</v>
       </c>
@@ -28434,7 +28464,7 @@
         <v>1257</v>
       </c>
     </row>
-    <row r="785" spans="2:13" x14ac:dyDescent="0.3">
+    <row r="785" spans="2:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="C785" t="s">
         <v>69</v>
       </c>
@@ -28463,7 +28493,7 @@
         <v>1257</v>
       </c>
     </row>
-    <row r="786" spans="2:13" x14ac:dyDescent="0.3">
+    <row r="786" spans="2:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="C786" t="s">
         <v>69</v>
       </c>
@@ -28492,7 +28522,7 @@
         <v>1257</v>
       </c>
     </row>
-    <row r="787" spans="2:13" x14ac:dyDescent="0.3">
+    <row r="787" spans="2:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="C787" t="s">
         <v>69</v>
       </c>
@@ -28521,7 +28551,7 @@
         <v>1257</v>
       </c>
     </row>
-    <row r="788" spans="2:13" x14ac:dyDescent="0.3">
+    <row r="788" spans="2:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="C788" t="s">
         <v>69</v>
       </c>
@@ -28550,7 +28580,7 @@
         <v>1257</v>
       </c>
     </row>
-    <row r="789" spans="2:13" x14ac:dyDescent="0.3">
+    <row r="789" spans="2:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="C789" t="s">
         <v>69</v>
       </c>
@@ -28579,7 +28609,7 @@
         <v>1257</v>
       </c>
     </row>
-    <row r="790" spans="2:13" x14ac:dyDescent="0.3">
+    <row r="790" spans="2:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="C790" t="s">
         <v>69</v>
       </c>
@@ -28608,7 +28638,7 @@
         <v>1257</v>
       </c>
     </row>
-    <row r="791" spans="2:13" x14ac:dyDescent="0.3">
+    <row r="791" spans="2:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="C791" t="s">
         <v>372</v>
       </c>
@@ -28637,7 +28667,7 @@
         <v>1266</v>
       </c>
     </row>
-    <row r="792" spans="2:13" x14ac:dyDescent="0.3">
+    <row r="792" spans="2:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="C792" t="s">
         <v>372</v>
       </c>
@@ -28666,7 +28696,7 @@
         <v>1266</v>
       </c>
     </row>
-    <row r="793" spans="2:13" x14ac:dyDescent="0.3">
+    <row r="793" spans="2:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="C793" t="s">
         <v>372</v>
       </c>
@@ -28695,7 +28725,7 @@
         <v>1266</v>
       </c>
     </row>
-    <row r="794" spans="2:13" x14ac:dyDescent="0.3">
+    <row r="794" spans="2:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="C794" t="s">
         <v>372</v>
       </c>
@@ -28724,7 +28754,7 @@
         <v>1266</v>
       </c>
     </row>
-    <row r="795" spans="2:13" x14ac:dyDescent="0.3">
+    <row r="795" spans="2:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="C795" t="s">
         <v>1270</v>
       </c>
@@ -28753,7 +28783,7 @@
         <v>1273</v>
       </c>
     </row>
-    <row r="796" spans="2:13" x14ac:dyDescent="0.3">
+    <row r="796" spans="2:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="C796" t="s">
         <v>1270</v>
       </c>
@@ -28782,7 +28812,7 @@
         <v>1273</v>
       </c>
     </row>
-    <row r="797" spans="2:13" x14ac:dyDescent="0.3">
+    <row r="797" spans="2:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="B797" t="s">
         <v>162</v>
       </c>
@@ -28811,7 +28841,7 @@
         <v>1276</v>
       </c>
     </row>
-    <row r="798" spans="2:13" x14ac:dyDescent="0.3">
+    <row r="798" spans="2:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="B798" t="s">
         <v>162</v>
       </c>
@@ -28840,7 +28870,7 @@
         <v>1276</v>
       </c>
     </row>
-    <row r="799" spans="2:13" x14ac:dyDescent="0.3">
+    <row r="799" spans="2:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="B799" t="s">
         <v>162</v>
       </c>
@@ -28869,7 +28899,7 @@
         <v>1276</v>
       </c>
     </row>
-    <row r="800" spans="2:13" x14ac:dyDescent="0.3">
+    <row r="800" spans="2:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="B800" t="s">
         <v>162</v>
       </c>
@@ -28898,7 +28928,7 @@
         <v>1276</v>
       </c>
     </row>
-    <row r="801" spans="2:13" x14ac:dyDescent="0.3">
+    <row r="801" spans="2:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="B801" t="s">
         <v>162</v>
       </c>
@@ -28927,7 +28957,7 @@
         <v>1276</v>
       </c>
     </row>
-    <row r="802" spans="2:13" x14ac:dyDescent="0.3">
+    <row r="802" spans="2:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="B802" t="s">
         <v>162</v>
       </c>
@@ -28956,7 +28986,7 @@
         <v>1276</v>
       </c>
     </row>
-    <row r="803" spans="2:13" x14ac:dyDescent="0.3">
+    <row r="803" spans="2:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="D803" t="s">
         <v>893</v>
       </c>
@@ -28982,7 +29012,7 @@
         <v>1284</v>
       </c>
     </row>
-    <row r="804" spans="2:13" x14ac:dyDescent="0.3">
+    <row r="804" spans="2:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="D804" t="s">
         <v>893</v>
       </c>
@@ -29008,7 +29038,7 @@
         <v>1284</v>
       </c>
     </row>
-    <row r="805" spans="2:13" x14ac:dyDescent="0.3">
+    <row r="805" spans="2:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="D805" t="s">
         <v>893</v>
       </c>
@@ -29032,7 +29062,7 @@
         <v>1284</v>
       </c>
     </row>
-    <row r="806" spans="2:13" x14ac:dyDescent="0.3">
+    <row r="806" spans="2:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="C806" t="s">
         <v>101</v>
       </c>
@@ -29061,7 +29091,7 @@
         <v>1291</v>
       </c>
     </row>
-    <row r="807" spans="2:13" x14ac:dyDescent="0.3">
+    <row r="807" spans="2:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="C807" t="s">
         <v>101</v>
       </c>
@@ -29090,7 +29120,7 @@
         <v>1291</v>
       </c>
     </row>
-    <row r="808" spans="2:13" x14ac:dyDescent="0.3">
+    <row r="808" spans="2:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="C808" t="s">
         <v>101</v>
       </c>
@@ -29119,7 +29149,7 @@
         <v>1291</v>
       </c>
     </row>
-    <row r="809" spans="2:13" x14ac:dyDescent="0.3">
+    <row r="809" spans="2:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="C809" t="s">
         <v>101</v>
       </c>
@@ -29148,7 +29178,7 @@
         <v>1291</v>
       </c>
     </row>
-    <row r="810" spans="2:13" x14ac:dyDescent="0.3">
+    <row r="810" spans="2:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="C810" t="s">
         <v>101</v>
       </c>
@@ -29177,7 +29207,7 @@
         <v>1291</v>
       </c>
     </row>
-    <row r="811" spans="2:13" x14ac:dyDescent="0.3">
+    <row r="811" spans="2:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="C811" t="s">
         <v>101</v>
       </c>
@@ -29206,7 +29236,7 @@
         <v>1291</v>
       </c>
     </row>
-    <row r="812" spans="2:13" x14ac:dyDescent="0.3">
+    <row r="812" spans="2:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="C812" t="s">
         <v>399</v>
       </c>
@@ -29235,7 +29265,7 @@
         <v>1300</v>
       </c>
     </row>
-    <row r="813" spans="2:13" x14ac:dyDescent="0.3">
+    <row r="813" spans="2:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="C813" t="s">
         <v>399</v>
       </c>
@@ -29264,7 +29294,7 @@
         <v>1300</v>
       </c>
     </row>
-    <row r="814" spans="2:13" x14ac:dyDescent="0.3">
+    <row r="814" spans="2:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="C814" t="s">
         <v>180</v>
       </c>
@@ -29290,7 +29320,7 @@
         <v>1304</v>
       </c>
     </row>
-    <row r="815" spans="2:13" x14ac:dyDescent="0.3">
+    <row r="815" spans="2:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="C815" t="s">
         <v>180</v>
       </c>
@@ -29316,7 +29346,7 @@
         <v>1304</v>
       </c>
     </row>
-    <row r="816" spans="2:13" x14ac:dyDescent="0.3">
+    <row r="816" spans="2:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="C816" t="s">
         <v>180</v>
       </c>
@@ -29342,7 +29372,7 @@
         <v>1304</v>
       </c>
     </row>
-    <row r="817" spans="3:13" x14ac:dyDescent="0.3">
+    <row r="817" spans="3:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="C817" t="s">
         <v>180</v>
       </c>
@@ -29368,7 +29398,7 @@
         <v>1304</v>
       </c>
     </row>
-    <row r="818" spans="3:13" x14ac:dyDescent="0.3">
+    <row r="818" spans="3:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="C818" t="s">
         <v>180</v>
       </c>
@@ -29394,7 +29424,7 @@
         <v>1304</v>
       </c>
     </row>
-    <row r="819" spans="3:13" x14ac:dyDescent="0.3">
+    <row r="819" spans="3:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="C819" t="s">
         <v>180</v>
       </c>
@@ -29420,7 +29450,7 @@
         <v>1304</v>
       </c>
     </row>
-    <row r="820" spans="3:13" x14ac:dyDescent="0.3">
+    <row r="820" spans="3:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="C820" t="s">
         <v>27</v>
       </c>
@@ -29449,7 +29479,7 @@
         <v>1312</v>
       </c>
     </row>
-    <row r="821" spans="3:13" x14ac:dyDescent="0.3">
+    <row r="821" spans="3:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="C821" t="s">
         <v>27</v>
       </c>
@@ -29478,7 +29508,7 @@
         <v>1312</v>
       </c>
     </row>
-    <row r="822" spans="3:13" x14ac:dyDescent="0.3">
+    <row r="822" spans="3:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="C822" t="s">
         <v>27</v>
       </c>
@@ -29507,7 +29537,7 @@
         <v>1312</v>
       </c>
     </row>
-    <row r="823" spans="3:13" x14ac:dyDescent="0.3">
+    <row r="823" spans="3:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="C823" t="s">
         <v>27</v>
       </c>
@@ -29536,7 +29566,7 @@
         <v>1312</v>
       </c>
     </row>
-    <row r="824" spans="3:13" x14ac:dyDescent="0.3">
+    <row r="824" spans="3:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="C824" t="s">
         <v>27</v>
       </c>
@@ -29565,7 +29595,7 @@
         <v>1312</v>
       </c>
     </row>
-    <row r="825" spans="3:13" x14ac:dyDescent="0.3">
+    <row r="825" spans="3:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="C825" t="s">
         <v>27</v>
       </c>
@@ -29594,7 +29624,7 @@
         <v>1312</v>
       </c>
     </row>
-    <row r="826" spans="3:13" x14ac:dyDescent="0.3">
+    <row r="826" spans="3:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="C826" t="s">
         <v>27</v>
       </c>
@@ -29623,7 +29653,7 @@
         <v>1312</v>
       </c>
     </row>
-    <row r="827" spans="3:13" x14ac:dyDescent="0.3">
+    <row r="827" spans="3:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="C827" t="s">
         <v>27</v>
       </c>
@@ -29652,7 +29682,7 @@
         <v>1312</v>
       </c>
     </row>
-    <row r="828" spans="3:13" x14ac:dyDescent="0.3">
+    <row r="828" spans="3:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="C828" t="s">
         <v>150</v>
       </c>
@@ -29681,7 +29711,7 @@
         <v>1321</v>
       </c>
     </row>
-    <row r="829" spans="3:13" x14ac:dyDescent="0.3">
+    <row r="829" spans="3:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="C829" t="s">
         <v>150</v>
       </c>
@@ -29710,7 +29740,7 @@
         <v>1321</v>
       </c>
     </row>
-    <row r="830" spans="3:13" x14ac:dyDescent="0.3">
+    <row r="830" spans="3:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="C830" t="s">
         <v>150</v>
       </c>
@@ -29739,7 +29769,7 @@
         <v>1321</v>
       </c>
     </row>
-    <row r="831" spans="3:13" x14ac:dyDescent="0.3">
+    <row r="831" spans="3:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="C831" t="s">
         <v>150</v>
       </c>
@@ -29768,7 +29798,7 @@
         <v>1321</v>
       </c>
     </row>
-    <row r="832" spans="3:13" x14ac:dyDescent="0.3">
+    <row r="832" spans="3:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="C832" t="s">
         <v>150</v>
       </c>
@@ -29797,7 +29827,7 @@
         <v>1321</v>
       </c>
     </row>
-    <row r="833" spans="3:13" x14ac:dyDescent="0.3">
+    <row r="833" spans="3:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="C833" t="s">
         <v>150</v>
       </c>
@@ -29826,7 +29856,7 @@
         <v>1321</v>
       </c>
     </row>
-    <row r="834" spans="3:13" x14ac:dyDescent="0.3">
+    <row r="834" spans="3:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="C834" t="s">
         <v>150</v>
       </c>
@@ -29855,7 +29885,7 @@
         <v>1321</v>
       </c>
     </row>
-    <row r="835" spans="3:13" x14ac:dyDescent="0.3">
+    <row r="835" spans="3:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="C835" t="s">
         <v>150</v>
       </c>
@@ -29884,7 +29914,7 @@
         <v>1321</v>
       </c>
     </row>
-    <row r="836" spans="3:13" x14ac:dyDescent="0.3">
+    <row r="836" spans="3:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="C836" t="s">
         <v>303</v>
       </c>
@@ -29913,7 +29943,7 @@
         <v>1332</v>
       </c>
     </row>
-    <row r="837" spans="3:13" x14ac:dyDescent="0.3">
+    <row r="837" spans="3:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="C837" t="s">
         <v>303</v>
       </c>
@@ -29942,7 +29972,7 @@
         <v>1332</v>
       </c>
     </row>
-    <row r="838" spans="3:13" x14ac:dyDescent="0.3">
+    <row r="838" spans="3:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="C838" t="s">
         <v>303</v>
       </c>
@@ -29971,7 +30001,7 @@
         <v>1332</v>
       </c>
     </row>
-    <row r="839" spans="3:13" x14ac:dyDescent="0.3">
+    <row r="839" spans="3:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="C839" t="s">
         <v>303</v>
       </c>
@@ -30000,7 +30030,7 @@
         <v>1332</v>
       </c>
     </row>
-    <row r="840" spans="3:13" x14ac:dyDescent="0.3">
+    <row r="840" spans="3:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="C840" t="s">
         <v>303</v>
       </c>
@@ -30029,7 +30059,7 @@
         <v>1332</v>
       </c>
     </row>
-    <row r="841" spans="3:13" x14ac:dyDescent="0.3">
+    <row r="841" spans="3:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="D841" t="s">
         <v>1339</v>
       </c>
@@ -30052,7 +30082,7 @@
         <v>1342</v>
       </c>
     </row>
-    <row r="842" spans="3:13" x14ac:dyDescent="0.3">
+    <row r="842" spans="3:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="D842" t="s">
         <v>1339</v>
       </c>
@@ -30075,7 +30105,7 @@
         <v>1342</v>
       </c>
     </row>
-    <row r="843" spans="3:13" x14ac:dyDescent="0.3">
+    <row r="843" spans="3:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="D843" t="s">
         <v>1339</v>
       </c>
@@ -30098,7 +30128,7 @@
         <v>1342</v>
       </c>
     </row>
-    <row r="844" spans="3:13" x14ac:dyDescent="0.3">
+    <row r="844" spans="3:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="D844" t="s">
         <v>1339</v>
       </c>
@@ -30121,7 +30151,7 @@
         <v>1342</v>
       </c>
     </row>
-    <row r="845" spans="3:13" x14ac:dyDescent="0.3">
+    <row r="845" spans="3:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="D845" t="s">
         <v>1339</v>
       </c>
@@ -30144,7 +30174,7 @@
         <v>1342</v>
       </c>
     </row>
-    <row r="846" spans="3:13" x14ac:dyDescent="0.3">
+    <row r="846" spans="3:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="D846" t="s">
         <v>1339</v>
       </c>
@@ -30167,7 +30197,7 @@
         <v>1342</v>
       </c>
     </row>
-    <row r="847" spans="3:13" x14ac:dyDescent="0.3">
+    <row r="847" spans="3:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="C847" t="s">
         <v>154</v>
       </c>
@@ -30196,7 +30226,7 @@
         <v>1350</v>
       </c>
     </row>
-    <row r="848" spans="3:13" x14ac:dyDescent="0.3">
+    <row r="848" spans="3:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="C848" t="s">
         <v>154</v>
       </c>
@@ -30225,7 +30255,7 @@
         <v>1350</v>
       </c>
     </row>
-    <row r="849" spans="3:13" x14ac:dyDescent="0.3">
+    <row r="849" spans="3:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="C849" t="s">
         <v>154</v>
       </c>
@@ -30254,7 +30284,7 @@
         <v>1350</v>
       </c>
     </row>
-    <row r="850" spans="3:13" x14ac:dyDescent="0.3">
+    <row r="850" spans="3:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="C850" t="s">
         <v>154</v>
       </c>
@@ -30283,7 +30313,7 @@
         <v>1350</v>
       </c>
     </row>
-    <row r="851" spans="3:13" x14ac:dyDescent="0.3">
+    <row r="851" spans="3:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="D851" t="s">
         <v>1353</v>
       </c>
@@ -30309,7 +30339,7 @@
         <v>1356</v>
       </c>
     </row>
-    <row r="852" spans="3:13" x14ac:dyDescent="0.3">
+    <row r="852" spans="3:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="D852" t="s">
         <v>1353</v>
       </c>
@@ -30335,7 +30365,7 @@
         <v>1356</v>
       </c>
     </row>
-    <row r="853" spans="3:13" x14ac:dyDescent="0.3">
+    <row r="853" spans="3:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="C853" t="s">
         <v>27</v>
       </c>
@@ -30364,7 +30394,7 @@
         <v>1361</v>
       </c>
     </row>
-    <row r="854" spans="3:13" x14ac:dyDescent="0.3">
+    <row r="854" spans="3:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="C854" t="s">
         <v>27</v>
       </c>
@@ -30393,7 +30423,7 @@
         <v>1361</v>
       </c>
     </row>
-    <row r="855" spans="3:13" x14ac:dyDescent="0.3">
+    <row r="855" spans="3:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="C855" t="s">
         <v>27</v>
       </c>
@@ -30422,7 +30452,7 @@
         <v>1361</v>
       </c>
     </row>
-    <row r="856" spans="3:13" x14ac:dyDescent="0.3">
+    <row r="856" spans="3:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="C856" t="s">
         <v>27</v>
       </c>
@@ -30451,7 +30481,7 @@
         <v>1361</v>
       </c>
     </row>
-    <row r="857" spans="3:13" x14ac:dyDescent="0.3">
+    <row r="857" spans="3:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="C857" t="s">
         <v>45</v>
       </c>
@@ -30480,7 +30510,7 @@
         <v>1367</v>
       </c>
     </row>
-    <row r="858" spans="3:13" x14ac:dyDescent="0.3">
+    <row r="858" spans="3:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="C858" t="s">
         <v>45</v>
       </c>
@@ -30509,7 +30539,7 @@
         <v>1367</v>
       </c>
     </row>
-    <row r="859" spans="3:13" x14ac:dyDescent="0.3">
+    <row r="859" spans="3:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="C859" t="s">
         <v>45</v>
       </c>
@@ -30538,7 +30568,7 @@
         <v>1367</v>
       </c>
     </row>
-    <row r="860" spans="3:13" x14ac:dyDescent="0.3">
+    <row r="860" spans="3:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="C860" t="s">
         <v>45</v>
       </c>
@@ -30567,7 +30597,7 @@
         <v>1367</v>
       </c>
     </row>
-    <row r="861" spans="3:13" x14ac:dyDescent="0.3">
+    <row r="861" spans="3:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="C861" t="s">
         <v>1371</v>
       </c>
@@ -30593,7 +30623,7 @@
         <v>1373</v>
       </c>
     </row>
-    <row r="862" spans="3:13" x14ac:dyDescent="0.3">
+    <row r="862" spans="3:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="C862" t="s">
         <v>1371</v>
       </c>
@@ -30619,7 +30649,7 @@
         <v>1373</v>
       </c>
     </row>
-    <row r="863" spans="3:13" x14ac:dyDescent="0.3">
+    <row r="863" spans="3:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="C863" t="s">
         <v>1371</v>
       </c>
@@ -30645,7 +30675,7 @@
         <v>1373</v>
       </c>
     </row>
-    <row r="864" spans="3:13" x14ac:dyDescent="0.3">
+    <row r="864" spans="3:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="C864" t="s">
         <v>1371</v>
       </c>
@@ -30671,7 +30701,7 @@
         <v>1373</v>
       </c>
     </row>
-    <row r="865" spans="3:13" x14ac:dyDescent="0.3">
+    <row r="865" spans="3:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="C865" t="s">
         <v>1371</v>
       </c>
@@ -30697,7 +30727,7 @@
         <v>1373</v>
       </c>
     </row>
-    <row r="866" spans="3:13" x14ac:dyDescent="0.3">
+    <row r="866" spans="3:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="C866" t="s">
         <v>1371</v>
       </c>
@@ -30723,7 +30753,7 @@
         <v>1373</v>
       </c>
     </row>
-    <row r="867" spans="3:13" x14ac:dyDescent="0.3">
+    <row r="867" spans="3:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="C867" t="s">
         <v>90</v>
       </c>
@@ -30752,7 +30782,7 @@
         <v>1376</v>
       </c>
     </row>
-    <row r="868" spans="3:13" x14ac:dyDescent="0.3">
+    <row r="868" spans="3:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="C868" t="s">
         <v>90</v>
       </c>
@@ -30781,7 +30811,7 @@
         <v>1376</v>
       </c>
     </row>
-    <row r="869" spans="3:13" x14ac:dyDescent="0.3">
+    <row r="869" spans="3:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="C869" t="s">
         <v>90</v>
       </c>
@@ -30810,7 +30840,7 @@
         <v>1376</v>
       </c>
     </row>
-    <row r="870" spans="3:13" x14ac:dyDescent="0.3">
+    <row r="870" spans="3:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="C870" t="s">
         <v>90</v>
       </c>
@@ -30839,7 +30869,7 @@
         <v>1376</v>
       </c>
     </row>
-    <row r="871" spans="3:13" x14ac:dyDescent="0.3">
+    <row r="871" spans="3:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="C871" t="s">
         <v>90</v>
       </c>
@@ -30868,7 +30898,7 @@
         <v>1376</v>
       </c>
     </row>
-    <row r="872" spans="3:13" x14ac:dyDescent="0.3">
+    <row r="872" spans="3:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="C872" t="s">
         <v>90</v>
       </c>
@@ -30897,7 +30927,7 @@
         <v>1376</v>
       </c>
     </row>
-    <row r="873" spans="3:13" x14ac:dyDescent="0.3">
+    <row r="873" spans="3:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="C873" t="s">
         <v>90</v>
       </c>
@@ -30926,7 +30956,7 @@
         <v>1376</v>
       </c>
     </row>
-    <row r="874" spans="3:13" x14ac:dyDescent="0.3">
+    <row r="874" spans="3:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="C874" t="s">
         <v>90</v>
       </c>
@@ -30955,7 +30985,7 @@
         <v>1376</v>
       </c>
     </row>
-    <row r="875" spans="3:13" x14ac:dyDescent="0.3">
+    <row r="875" spans="3:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="D875" t="s">
         <v>1383</v>
       </c>
@@ -30978,7 +31008,7 @@
         <v>1385</v>
       </c>
     </row>
-    <row r="876" spans="3:13" x14ac:dyDescent="0.3">
+    <row r="876" spans="3:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="D876" t="s">
         <v>1383</v>
       </c>
@@ -31001,7 +31031,7 @@
         <v>1385</v>
       </c>
     </row>
-    <row r="877" spans="3:13" x14ac:dyDescent="0.3">
+    <row r="877" spans="3:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="D877" t="s">
         <v>1383</v>
       </c>
@@ -31024,7 +31054,7 @@
         <v>1385</v>
       </c>
     </row>
-    <row r="878" spans="3:13" x14ac:dyDescent="0.3">
+    <row r="878" spans="3:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="D878" t="s">
         <v>1383</v>
       </c>
@@ -31047,7 +31077,7 @@
         <v>1385</v>
       </c>
     </row>
-    <row r="879" spans="3:13" x14ac:dyDescent="0.3">
+    <row r="879" spans="3:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="C879" t="s">
         <v>69</v>
       </c>
@@ -31076,7 +31106,7 @@
         <v>1394</v>
       </c>
     </row>
-    <row r="880" spans="3:13" x14ac:dyDescent="0.3">
+    <row r="880" spans="3:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="C880" t="s">
         <v>69</v>
       </c>
@@ -31105,7 +31135,7 @@
         <v>1394</v>
       </c>
     </row>
-    <row r="881" spans="2:13" x14ac:dyDescent="0.3">
+    <row r="881" spans="2:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="C881" t="s">
         <v>69</v>
       </c>
@@ -31134,7 +31164,7 @@
         <v>1394</v>
       </c>
     </row>
-    <row r="882" spans="2:13" x14ac:dyDescent="0.3">
+    <row r="882" spans="2:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="C882" t="s">
         <v>69</v>
       </c>
@@ -31163,7 +31193,7 @@
         <v>1394</v>
       </c>
     </row>
-    <row r="883" spans="2:13" x14ac:dyDescent="0.3">
+    <row r="883" spans="2:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="C883" t="s">
         <v>69</v>
       </c>
@@ -31192,7 +31222,7 @@
         <v>1394</v>
       </c>
     </row>
-    <row r="884" spans="2:13" x14ac:dyDescent="0.3">
+    <row r="884" spans="2:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="C884" t="s">
         <v>69</v>
       </c>
@@ -31221,7 +31251,7 @@
         <v>1394</v>
       </c>
     </row>
-    <row r="885" spans="2:13" x14ac:dyDescent="0.3">
+    <row r="885" spans="2:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="B885" t="s">
         <v>162</v>
       </c>
@@ -31250,7 +31280,7 @@
         <v>1402</v>
       </c>
     </row>
-    <row r="886" spans="2:13" x14ac:dyDescent="0.3">
+    <row r="886" spans="2:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="B886" t="s">
         <v>162</v>
       </c>
@@ -31279,7 +31309,7 @@
         <v>1402</v>
       </c>
     </row>
-    <row r="887" spans="2:13" x14ac:dyDescent="0.3">
+    <row r="887" spans="2:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="B887" t="s">
         <v>162</v>
       </c>
@@ -31308,7 +31338,7 @@
         <v>1402</v>
       </c>
     </row>
-    <row r="888" spans="2:13" x14ac:dyDescent="0.3">
+    <row r="888" spans="2:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="B888" t="s">
         <v>162</v>
       </c>
@@ -31337,7 +31367,7 @@
         <v>1402</v>
       </c>
     </row>
-    <row r="889" spans="2:13" x14ac:dyDescent="0.3">
+    <row r="889" spans="2:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="B889" t="s">
         <v>162</v>
       </c>
@@ -31366,7 +31396,7 @@
         <v>1402</v>
       </c>
     </row>
-    <row r="890" spans="2:13" x14ac:dyDescent="0.3">
+    <row r="890" spans="2:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="B890" t="s">
         <v>162</v>
       </c>
@@ -31395,7 +31425,7 @@
         <v>1402</v>
       </c>
     </row>
-    <row r="891" spans="2:13" x14ac:dyDescent="0.3">
+    <row r="891" spans="2:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="C891" t="s">
         <v>1408</v>
       </c>
@@ -31424,7 +31454,7 @@
         <v>1411</v>
       </c>
     </row>
-    <row r="892" spans="2:13" x14ac:dyDescent="0.3">
+    <row r="892" spans="2:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="C892" t="s">
         <v>1408</v>
       </c>
@@ -31453,7 +31483,7 @@
         <v>1411</v>
       </c>
     </row>
-    <row r="893" spans="2:13" x14ac:dyDescent="0.3">
+    <row r="893" spans="2:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="C893" t="s">
         <v>1408</v>
       </c>
@@ -31482,7 +31512,7 @@
         <v>1411</v>
       </c>
     </row>
-    <row r="894" spans="2:13" x14ac:dyDescent="0.3">
+    <row r="894" spans="2:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="C894" t="s">
         <v>1408</v>
       </c>
@@ -31511,7 +31541,7 @@
         <v>1411</v>
       </c>
     </row>
-    <row r="895" spans="2:13" x14ac:dyDescent="0.3">
+    <row r="895" spans="2:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="C895" t="s">
         <v>1408</v>
       </c>
@@ -31540,7 +31570,7 @@
         <v>1411</v>
       </c>
     </row>
-    <row r="896" spans="2:13" x14ac:dyDescent="0.3">
+    <row r="896" spans="2:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="C896" t="s">
         <v>1408</v>
       </c>
@@ -31569,7 +31599,7 @@
         <v>1411</v>
       </c>
     </row>
-    <row r="897" spans="3:13" x14ac:dyDescent="0.3">
+    <row r="897" spans="3:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="C897" t="s">
         <v>1408</v>
       </c>
@@ -31598,7 +31628,7 @@
         <v>1411</v>
       </c>
     </row>
-    <row r="898" spans="3:13" x14ac:dyDescent="0.3">
+    <row r="898" spans="3:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="C898" t="s">
         <v>1408</v>
       </c>
@@ -31627,7 +31657,7 @@
         <v>1411</v>
       </c>
     </row>
-    <row r="899" spans="3:13" x14ac:dyDescent="0.3">
+    <row r="899" spans="3:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="C899" t="s">
         <v>1420</v>
       </c>
@@ -31656,7 +31686,7 @@
         <v>1423</v>
       </c>
     </row>
-    <row r="900" spans="3:13" x14ac:dyDescent="0.3">
+    <row r="900" spans="3:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="C900" t="s">
         <v>1420</v>
       </c>
@@ -31685,7 +31715,7 @@
         <v>1423</v>
       </c>
     </row>
-    <row r="901" spans="3:13" x14ac:dyDescent="0.3">
+    <row r="901" spans="3:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="C901" t="s">
         <v>1420</v>
       </c>
@@ -31714,7 +31744,7 @@
         <v>1423</v>
       </c>
     </row>
-    <row r="902" spans="3:13" x14ac:dyDescent="0.3">
+    <row r="902" spans="3:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="C902" t="s">
         <v>1420</v>
       </c>
@@ -31743,7 +31773,7 @@
         <v>1423</v>
       </c>
     </row>
-    <row r="903" spans="3:13" x14ac:dyDescent="0.3">
+    <row r="903" spans="3:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="C903" t="s">
         <v>1420</v>
       </c>
@@ -31772,7 +31802,7 @@
         <v>1423</v>
       </c>
     </row>
-    <row r="904" spans="3:13" x14ac:dyDescent="0.3">
+    <row r="904" spans="3:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="C904" t="s">
         <v>1420</v>
       </c>
@@ -31801,7 +31831,7 @@
         <v>1423</v>
       </c>
     </row>
-    <row r="905" spans="3:13" x14ac:dyDescent="0.3">
+    <row r="905" spans="3:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="C905" t="s">
         <v>1420</v>
       </c>
@@ -31830,7 +31860,7 @@
         <v>1423</v>
       </c>
     </row>
-    <row r="906" spans="3:13" x14ac:dyDescent="0.3">
+    <row r="906" spans="3:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="C906" t="s">
         <v>1420</v>
       </c>
@@ -31859,7 +31889,7 @@
         <v>1423</v>
       </c>
     </row>
-    <row r="907" spans="3:13" x14ac:dyDescent="0.3">
+    <row r="907" spans="3:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="C907" t="s">
         <v>101</v>
       </c>
@@ -31888,7 +31918,7 @@
         <v>1433</v>
       </c>
     </row>
-    <row r="908" spans="3:13" x14ac:dyDescent="0.3">
+    <row r="908" spans="3:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="C908" t="s">
         <v>101</v>
       </c>
@@ -31917,7 +31947,7 @@
         <v>1433</v>
       </c>
     </row>
-    <row r="909" spans="3:13" x14ac:dyDescent="0.3">
+    <row r="909" spans="3:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="C909" t="s">
         <v>101</v>
       </c>
@@ -31946,7 +31976,7 @@
         <v>1433</v>
       </c>
     </row>
-    <row r="910" spans="3:13" x14ac:dyDescent="0.3">
+    <row r="910" spans="3:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="C910" t="s">
         <v>101</v>
       </c>
@@ -31975,7 +32005,7 @@
         <v>1433</v>
       </c>
     </row>
-    <row r="911" spans="3:13" x14ac:dyDescent="0.3">
+    <row r="911" spans="3:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="C911" t="s">
         <v>101</v>
       </c>
@@ -32004,7 +32034,7 @@
         <v>1433</v>
       </c>
     </row>
-    <row r="912" spans="3:13" x14ac:dyDescent="0.3">
+    <row r="912" spans="3:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="C912" t="s">
         <v>101</v>
       </c>
@@ -32033,7 +32063,7 @@
         <v>1433</v>
       </c>
     </row>
-    <row r="913" spans="2:13" x14ac:dyDescent="0.3">
+    <row r="913" spans="2:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="C913" t="s">
         <v>399</v>
       </c>
@@ -32062,7 +32092,7 @@
         <v>1441</v>
       </c>
     </row>
-    <row r="914" spans="2:13" x14ac:dyDescent="0.3">
+    <row r="914" spans="2:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="C914" t="s">
         <v>399</v>
       </c>
@@ -32091,7 +32121,7 @@
         <v>1441</v>
       </c>
     </row>
-    <row r="915" spans="2:13" x14ac:dyDescent="0.3">
+    <row r="915" spans="2:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="D915" t="s">
         <v>1443</v>
       </c>
@@ -32117,7 +32147,7 @@
         <v>1445</v>
       </c>
     </row>
-    <row r="916" spans="2:13" x14ac:dyDescent="0.3">
+    <row r="916" spans="2:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="D916" t="s">
         <v>1443</v>
       </c>
@@ -32143,7 +32173,7 @@
         <v>1445</v>
       </c>
     </row>
-    <row r="917" spans="2:13" x14ac:dyDescent="0.3">
+    <row r="917" spans="2:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="D917" t="s">
         <v>1443</v>
       </c>
@@ -32169,7 +32199,7 @@
         <v>1445</v>
       </c>
     </row>
-    <row r="918" spans="2:13" x14ac:dyDescent="0.3">
+    <row r="918" spans="2:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="D918" t="s">
         <v>1443</v>
       </c>
@@ -32195,7 +32225,7 @@
         <v>1445</v>
       </c>
     </row>
-    <row r="919" spans="2:13" x14ac:dyDescent="0.3">
+    <row r="919" spans="2:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="D919" t="s">
         <v>1443</v>
       </c>
@@ -32221,7 +32251,7 @@
         <v>1445</v>
       </c>
     </row>
-    <row r="920" spans="2:13" x14ac:dyDescent="0.3">
+    <row r="920" spans="2:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="D920" t="s">
         <v>1443</v>
       </c>
@@ -32247,7 +32277,7 @@
         <v>1445</v>
       </c>
     </row>
-    <row r="921" spans="2:13" x14ac:dyDescent="0.3">
+    <row r="921" spans="2:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="D921" t="s">
         <v>1443</v>
       </c>
@@ -32273,7 +32303,7 @@
         <v>1445</v>
       </c>
     </row>
-    <row r="922" spans="2:13" x14ac:dyDescent="0.3">
+    <row r="922" spans="2:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="D922" t="s">
         <v>1443</v>
       </c>
@@ -32299,7 +32329,7 @@
         <v>1445</v>
       </c>
     </row>
-    <row r="923" spans="2:13" x14ac:dyDescent="0.3">
+    <row r="923" spans="2:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="B923" t="s">
         <v>162</v>
       </c>
@@ -32328,7 +32358,7 @@
         <v>1456</v>
       </c>
     </row>
-    <row r="924" spans="2:13" x14ac:dyDescent="0.3">
+    <row r="924" spans="2:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="B924" t="s">
         <v>162</v>
       </c>
@@ -32357,7 +32387,7 @@
         <v>1456</v>
       </c>
     </row>
-    <row r="925" spans="2:13" x14ac:dyDescent="0.3">
+    <row r="925" spans="2:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="B925" t="s">
         <v>162</v>
       </c>
@@ -32386,7 +32416,7 @@
         <v>1456</v>
       </c>
     </row>
-    <row r="926" spans="2:13" x14ac:dyDescent="0.3">
+    <row r="926" spans="2:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="B926" t="s">
         <v>162</v>
       </c>
@@ -32415,7 +32445,7 @@
         <v>1456</v>
       </c>
     </row>
-    <row r="927" spans="2:13" x14ac:dyDescent="0.3">
+    <row r="927" spans="2:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="B927" t="s">
         <v>162</v>
       </c>
@@ -32444,7 +32474,7 @@
         <v>1456</v>
       </c>
     </row>
-    <row r="928" spans="2:13" x14ac:dyDescent="0.3">
+    <row r="928" spans="2:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="B928" t="s">
         <v>162</v>
       </c>
@@ -32473,7 +32503,7 @@
         <v>1456</v>
       </c>
     </row>
-    <row r="929" spans="2:13" x14ac:dyDescent="0.3">
+    <row r="929" spans="2:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="B929" t="s">
         <v>592</v>
       </c>
@@ -32508,7 +32538,7 @@
         <v>1471</v>
       </c>
     </row>
-    <row r="930" spans="2:13" x14ac:dyDescent="0.3">
+    <row r="930" spans="2:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="B930" t="s">
         <v>592</v>
       </c>
@@ -32546,7 +32576,7 @@
         <v>1471</v>
       </c>
     </row>
-    <row r="931" spans="2:13" x14ac:dyDescent="0.3">
+    <row r="931" spans="2:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="B931" t="s">
         <v>592</v>
       </c>
@@ -32584,7 +32614,7 @@
         <v>1471</v>
       </c>
     </row>
-    <row r="932" spans="2:13" x14ac:dyDescent="0.3">
+    <row r="932" spans="2:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="B932" t="s">
         <v>592</v>
       </c>
@@ -32622,7 +32652,7 @@
         <v>1471</v>
       </c>
     </row>
-    <row r="933" spans="2:13" x14ac:dyDescent="0.3">
+    <row r="933" spans="2:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="B933" t="s">
         <v>592</v>
       </c>
@@ -32657,7 +32687,7 @@
         <v>1471</v>
       </c>
     </row>
-    <row r="934" spans="2:13" x14ac:dyDescent="0.3">
+    <row r="934" spans="2:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="B934" t="s">
         <v>592</v>
       </c>
@@ -32695,7 +32725,7 @@
         <v>1471</v>
       </c>
     </row>
-    <row r="935" spans="2:13" x14ac:dyDescent="0.3">
+    <row r="935" spans="2:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="B935" t="s">
         <v>592</v>
       </c>
@@ -32730,7 +32760,7 @@
         <v>1471</v>
       </c>
     </row>
-    <row r="936" spans="2:13" x14ac:dyDescent="0.3">
+    <row r="936" spans="2:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="B936" t="s">
         <v>592</v>
       </c>
@@ -32768,7 +32798,7 @@
         <v>1471</v>
       </c>
     </row>
-    <row r="937" spans="2:13" x14ac:dyDescent="0.3">
+    <row r="937" spans="2:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="C937" t="s">
         <v>150</v>
       </c>
@@ -32797,7 +32827,7 @@
         <v>1487</v>
       </c>
     </row>
-    <row r="938" spans="2:13" x14ac:dyDescent="0.3">
+    <row r="938" spans="2:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="C938" t="s">
         <v>150</v>
       </c>
@@ -32826,7 +32856,7 @@
         <v>1487</v>
       </c>
     </row>
-    <row r="939" spans="2:13" x14ac:dyDescent="0.3">
+    <row r="939" spans="2:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="C939" t="s">
         <v>150</v>
       </c>
@@ -32855,7 +32885,7 @@
         <v>1487</v>
       </c>
     </row>
-    <row r="940" spans="2:13" x14ac:dyDescent="0.3">
+    <row r="940" spans="2:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="C940" t="s">
         <v>150</v>
       </c>
@@ -32884,7 +32914,7 @@
         <v>1487</v>
       </c>
     </row>
-    <row r="941" spans="2:13" x14ac:dyDescent="0.3">
+    <row r="941" spans="2:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="C941" t="s">
         <v>150</v>
       </c>
@@ -32913,7 +32943,7 @@
         <v>1487</v>
       </c>
     </row>
-    <row r="942" spans="2:13" x14ac:dyDescent="0.3">
+    <row r="942" spans="2:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="C942" t="s">
         <v>150</v>
       </c>
@@ -32942,7 +32972,7 @@
         <v>1487</v>
       </c>
     </row>
-    <row r="943" spans="2:13" x14ac:dyDescent="0.3">
+    <row r="943" spans="2:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="C943" t="s">
         <v>150</v>
       </c>
@@ -32971,7 +33001,7 @@
         <v>1487</v>
       </c>
     </row>
-    <row r="944" spans="2:13" x14ac:dyDescent="0.3">
+    <row r="944" spans="2:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="C944" t="s">
         <v>150</v>
       </c>
@@ -33000,7 +33030,7 @@
         <v>1487</v>
       </c>
     </row>
-    <row r="945" spans="2:13" x14ac:dyDescent="0.3">
+    <row r="945" spans="2:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="C945" t="s">
         <v>129</v>
       </c>
@@ -33029,7 +33059,7 @@
         <v>1499</v>
       </c>
     </row>
-    <row r="946" spans="2:13" x14ac:dyDescent="0.3">
+    <row r="946" spans="2:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="C946" t="s">
         <v>129</v>
       </c>
@@ -33058,7 +33088,7 @@
         <v>1499</v>
       </c>
     </row>
-    <row r="947" spans="2:13" x14ac:dyDescent="0.3">
+    <row r="947" spans="2:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="C947" t="s">
         <v>129</v>
       </c>
@@ -33087,7 +33117,7 @@
         <v>1499</v>
       </c>
     </row>
-    <row r="948" spans="2:13" x14ac:dyDescent="0.3">
+    <row r="948" spans="2:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="C948" t="s">
         <v>129</v>
       </c>
@@ -33116,7 +33146,7 @@
         <v>1499</v>
       </c>
     </row>
-    <row r="949" spans="2:13" x14ac:dyDescent="0.3">
+    <row r="949" spans="2:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="C949" t="s">
         <v>129</v>
       </c>
@@ -33145,7 +33175,7 @@
         <v>1499</v>
       </c>
     </row>
-    <row r="950" spans="2:13" x14ac:dyDescent="0.3">
+    <row r="950" spans="2:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="C950" t="s">
         <v>129</v>
       </c>
@@ -33174,7 +33204,7 @@
         <v>1499</v>
       </c>
     </row>
-    <row r="951" spans="2:13" x14ac:dyDescent="0.3">
+    <row r="951" spans="2:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="C951" t="s">
         <v>129</v>
       </c>
@@ -33203,7 +33233,7 @@
         <v>1499</v>
       </c>
     </row>
-    <row r="952" spans="2:13" x14ac:dyDescent="0.3">
+    <row r="952" spans="2:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="C952" t="s">
         <v>129</v>
       </c>
@@ -33232,7 +33262,7 @@
         <v>1499</v>
       </c>
     </row>
-    <row r="953" spans="2:13" x14ac:dyDescent="0.3">
+    <row r="953" spans="2:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="C953" t="s">
         <v>303</v>
       </c>
@@ -33258,7 +33288,7 @@
         <v>1509</v>
       </c>
     </row>
-    <row r="954" spans="2:13" x14ac:dyDescent="0.3">
+    <row r="954" spans="2:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="C954" t="s">
         <v>303</v>
       </c>
@@ -33284,7 +33314,7 @@
         <v>1509</v>
       </c>
     </row>
-    <row r="955" spans="2:13" x14ac:dyDescent="0.3">
+    <row r="955" spans="2:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="C955" t="s">
         <v>303</v>
       </c>
@@ -33310,7 +33340,7 @@
         <v>1509</v>
       </c>
     </row>
-    <row r="956" spans="2:13" x14ac:dyDescent="0.3">
+    <row r="956" spans="2:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="C956" t="s">
         <v>303</v>
       </c>
@@ -33336,7 +33366,7 @@
         <v>1509</v>
       </c>
     </row>
-    <row r="957" spans="2:13" x14ac:dyDescent="0.3">
+    <row r="957" spans="2:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="B957" t="s">
         <v>592</v>
       </c>
@@ -33365,7 +33395,7 @@
         <v>1516</v>
       </c>
     </row>
-    <row r="958" spans="2:13" x14ac:dyDescent="0.3">
+    <row r="958" spans="2:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="B958" t="s">
         <v>592</v>
       </c>
@@ -33394,7 +33424,7 @@
         <v>1516</v>
       </c>
     </row>
-    <row r="959" spans="2:13" x14ac:dyDescent="0.3">
+    <row r="959" spans="2:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="B959" t="s">
         <v>592</v>
       </c>
@@ -33423,7 +33453,7 @@
         <v>1516</v>
       </c>
     </row>
-    <row r="960" spans="2:13" x14ac:dyDescent="0.3">
+    <row r="960" spans="2:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="B960" t="s">
         <v>592</v>
       </c>
@@ -33452,7 +33482,7 @@
         <v>1516</v>
       </c>
     </row>
-    <row r="961" spans="2:13" x14ac:dyDescent="0.3">
+    <row r="961" spans="2:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="B961" t="s">
         <v>592</v>
       </c>
@@ -33481,7 +33511,7 @@
         <v>1516</v>
       </c>
     </row>
-    <row r="962" spans="2:13" x14ac:dyDescent="0.3">
+    <row r="962" spans="2:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="B962" t="s">
         <v>592</v>
       </c>
@@ -33510,7 +33540,7 @@
         <v>1516</v>
       </c>
     </row>
-    <row r="963" spans="2:13" x14ac:dyDescent="0.3">
+    <row r="963" spans="2:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="B963" t="s">
         <v>592</v>
       </c>
@@ -33542,7 +33572,7 @@
         <v>1516</v>
       </c>
     </row>
-    <row r="964" spans="2:13" x14ac:dyDescent="0.3">
+    <row r="964" spans="2:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="B964" t="s">
         <v>592</v>
       </c>
@@ -33574,7 +33604,7 @@
         <v>1516</v>
       </c>
     </row>
-    <row r="965" spans="2:13" x14ac:dyDescent="0.3">
+    <row r="965" spans="2:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="B965" t="s">
         <v>592</v>
       </c>
@@ -33609,7 +33639,7 @@
         <v>1531</v>
       </c>
     </row>
-    <row r="966" spans="2:13" x14ac:dyDescent="0.3">
+    <row r="966" spans="2:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="C966" t="s">
         <v>1532</v>
       </c>
@@ -33638,7 +33668,7 @@
         <v>1536</v>
       </c>
     </row>
-    <row r="967" spans="2:13" x14ac:dyDescent="0.3">
+    <row r="967" spans="2:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="C967" t="s">
         <v>1532</v>
       </c>
@@ -33696,7 +33726,7 @@
         <v>1536</v>
       </c>
     </row>
-    <row r="969" spans="2:13" x14ac:dyDescent="0.3">
+    <row r="969" spans="2:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="C969" t="s">
         <v>1532</v>
       </c>
@@ -33725,7 +33755,7 @@
         <v>1536</v>
       </c>
     </row>
-    <row r="970" spans="2:13" x14ac:dyDescent="0.3">
+    <row r="970" spans="2:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="C970" t="s">
         <v>1532</v>
       </c>
@@ -33754,7 +33784,7 @@
         <v>1536</v>
       </c>
     </row>
-    <row r="971" spans="2:13" x14ac:dyDescent="0.3">
+    <row r="971" spans="2:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="C971" t="s">
         <v>1532</v>
       </c>
@@ -33783,7 +33813,7 @@
         <v>1536</v>
       </c>
     </row>
-    <row r="972" spans="2:13" x14ac:dyDescent="0.3">
+    <row r="972" spans="2:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="C972" t="s">
         <v>1532</v>
       </c>
@@ -33812,7 +33842,7 @@
         <v>1536</v>
       </c>
     </row>
-    <row r="973" spans="2:13" x14ac:dyDescent="0.3">
+    <row r="973" spans="2:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="C973" t="s">
         <v>1532</v>
       </c>
@@ -33841,7 +33871,7 @@
         <v>1536</v>
       </c>
     </row>
-    <row r="974" spans="2:13" x14ac:dyDescent="0.3">
+    <row r="974" spans="2:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="C974" t="s">
         <v>1532</v>
       </c>
@@ -33899,7 +33929,7 @@
         <v>1548</v>
       </c>
     </row>
-    <row r="976" spans="2:13" x14ac:dyDescent="0.3">
+    <row r="976" spans="2:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="C976" t="s">
         <v>1408</v>
       </c>
@@ -33928,7 +33958,7 @@
         <v>1548</v>
       </c>
     </row>
-    <row r="977" spans="3:13" x14ac:dyDescent="0.3">
+    <row r="977" spans="3:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="C977" t="s">
         <v>1408</v>
       </c>
@@ -33957,7 +33987,7 @@
         <v>1548</v>
       </c>
     </row>
-    <row r="978" spans="3:13" x14ac:dyDescent="0.3">
+    <row r="978" spans="3:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="C978" t="s">
         <v>1408</v>
       </c>
@@ -33986,7 +34016,7 @@
         <v>1548</v>
       </c>
     </row>
-    <row r="979" spans="3:13" x14ac:dyDescent="0.3">
+    <row r="979" spans="3:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="C979" t="s">
         <v>1408</v>
       </c>
@@ -34015,7 +34045,7 @@
         <v>1548</v>
       </c>
     </row>
-    <row r="980" spans="3:13" x14ac:dyDescent="0.3">
+    <row r="980" spans="3:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="C980" t="s">
         <v>1408</v>
       </c>
@@ -34044,7 +34074,7 @@
         <v>1548</v>
       </c>
     </row>
-    <row r="981" spans="3:13" x14ac:dyDescent="0.3">
+    <row r="981" spans="3:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="D981" t="s">
         <v>1554</v>
       </c>
@@ -34067,7 +34097,7 @@
         <v>1557</v>
       </c>
     </row>
-    <row r="982" spans="3:13" x14ac:dyDescent="0.3">
+    <row r="982" spans="3:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="D982" t="s">
         <v>1554</v>
       </c>
@@ -34090,7 +34120,7 @@
         <v>1557</v>
       </c>
     </row>
-    <row r="983" spans="3:13" x14ac:dyDescent="0.3">
+    <row r="983" spans="3:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="D983" t="s">
         <v>1554</v>
       </c>
@@ -34113,7 +34143,7 @@
         <v>1557</v>
       </c>
     </row>
-    <row r="984" spans="3:13" x14ac:dyDescent="0.3">
+    <row r="984" spans="3:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="D984" t="s">
         <v>1554</v>
       </c>
@@ -34136,7 +34166,7 @@
         <v>1557</v>
       </c>
     </row>
-    <row r="985" spans="3:13" x14ac:dyDescent="0.3">
+    <row r="985" spans="3:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="D985" t="s">
         <v>1554</v>
       </c>
@@ -34159,7 +34189,7 @@
         <v>1557</v>
       </c>
     </row>
-    <row r="986" spans="3:13" x14ac:dyDescent="0.3">
+    <row r="986" spans="3:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="C986" t="s">
         <v>101</v>
       </c>
@@ -34188,7 +34218,7 @@
         <v>1565</v>
       </c>
     </row>
-    <row r="987" spans="3:13" x14ac:dyDescent="0.3">
+    <row r="987" spans="3:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="C987" t="s">
         <v>101</v>
       </c>
@@ -34217,7 +34247,7 @@
         <v>1565</v>
       </c>
     </row>
-    <row r="988" spans="3:13" x14ac:dyDescent="0.3">
+    <row r="988" spans="3:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="C988" t="s">
         <v>101</v>
       </c>
@@ -34246,7 +34276,7 @@
         <v>1565</v>
       </c>
     </row>
-    <row r="989" spans="3:13" x14ac:dyDescent="0.3">
+    <row r="989" spans="3:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="C989" t="s">
         <v>101</v>
       </c>
@@ -34275,7 +34305,7 @@
         <v>1565</v>
       </c>
     </row>
-    <row r="990" spans="3:13" x14ac:dyDescent="0.3">
+    <row r="990" spans="3:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="C990" t="s">
         <v>101</v>
       </c>
@@ -34304,7 +34334,7 @@
         <v>1565</v>
       </c>
     </row>
-    <row r="991" spans="3:13" x14ac:dyDescent="0.3">
+    <row r="991" spans="3:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="C991" t="s">
         <v>101</v>
       </c>
@@ -34333,7 +34363,7 @@
         <v>1565</v>
       </c>
     </row>
-    <row r="992" spans="3:13" x14ac:dyDescent="0.3">
+    <row r="992" spans="3:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="C992" t="s">
         <v>101</v>
       </c>
@@ -34362,7 +34392,7 @@
         <v>1565</v>
       </c>
     </row>
-    <row r="993" spans="3:13" x14ac:dyDescent="0.3">
+    <row r="993" spans="3:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="C993" t="s">
         <v>101</v>
       </c>
@@ -34391,7 +34421,7 @@
         <v>1565</v>
       </c>
     </row>
-    <row r="994" spans="3:13" x14ac:dyDescent="0.3">
+    <row r="994" spans="3:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="C994" t="s">
         <v>399</v>
       </c>
@@ -34420,7 +34450,7 @@
         <v>1577</v>
       </c>
     </row>
-    <row r="995" spans="3:13" x14ac:dyDescent="0.3">
+    <row r="995" spans="3:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="C995" t="s">
         <v>399</v>
       </c>
@@ -34449,7 +34479,7 @@
         <v>1577</v>
       </c>
     </row>
-    <row r="996" spans="3:13" x14ac:dyDescent="0.3">
+    <row r="996" spans="3:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="C996" t="s">
         <v>399</v>
       </c>
@@ -34478,7 +34508,7 @@
         <v>1577</v>
       </c>
     </row>
-    <row r="997" spans="3:13" x14ac:dyDescent="0.3">
+    <row r="997" spans="3:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="C997" t="s">
         <v>719</v>
       </c>
@@ -34507,7 +34537,7 @@
         <v>1583</v>
       </c>
     </row>
-    <row r="998" spans="3:13" x14ac:dyDescent="0.3">
+    <row r="998" spans="3:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="C998" t="s">
         <v>719</v>
       </c>
@@ -34565,7 +34595,7 @@
         <v>1583</v>
       </c>
     </row>
-    <row r="1000" spans="3:13" x14ac:dyDescent="0.3">
+    <row r="1000" spans="3:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="C1000" t="s">
         <v>719</v>
       </c>
@@ -34594,7 +34624,7 @@
         <v>1583</v>
       </c>
     </row>
-    <row r="1001" spans="3:13" x14ac:dyDescent="0.3">
+    <row r="1001" spans="3:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="C1001" t="s">
         <v>719</v>
       </c>
@@ -34623,7 +34653,7 @@
         <v>1583</v>
       </c>
     </row>
-    <row r="1002" spans="3:13" x14ac:dyDescent="0.3">
+    <row r="1002" spans="3:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="C1002" t="s">
         <v>719</v>
       </c>
@@ -34652,7 +34682,7 @@
         <v>1583</v>
       </c>
     </row>
-    <row r="1003" spans="3:13" x14ac:dyDescent="0.3">
+    <row r="1003" spans="3:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="C1003" t="s">
         <v>719</v>
       </c>
@@ -34681,7 +34711,7 @@
         <v>1583</v>
       </c>
     </row>
-    <row r="1004" spans="3:13" x14ac:dyDescent="0.3">
+    <row r="1004" spans="3:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="C1004" t="s">
         <v>719</v>
       </c>
@@ -34710,7 +34740,7 @@
         <v>1583</v>
       </c>
     </row>
-    <row r="1005" spans="3:13" x14ac:dyDescent="0.3">
+    <row r="1005" spans="3:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="C1005" t="s">
         <v>719</v>
       </c>
@@ -34739,7 +34769,7 @@
         <v>1583</v>
       </c>
     </row>
-    <row r="1006" spans="3:13" x14ac:dyDescent="0.3">
+    <row r="1006" spans="3:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="C1006" t="s">
         <v>180</v>
       </c>
@@ -34765,7 +34795,7 @@
         <v>1594</v>
       </c>
     </row>
-    <row r="1007" spans="3:13" x14ac:dyDescent="0.3">
+    <row r="1007" spans="3:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="C1007" t="s">
         <v>180</v>
       </c>
@@ -34791,7 +34821,7 @@
         <v>1594</v>
       </c>
     </row>
-    <row r="1008" spans="3:13" x14ac:dyDescent="0.3">
+    <row r="1008" spans="3:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="C1008" t="s">
         <v>180</v>
       </c>
@@ -34817,7 +34847,7 @@
         <v>1594</v>
       </c>
     </row>
-    <row r="1009" spans="3:13" x14ac:dyDescent="0.3">
+    <row r="1009" spans="3:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="C1009" t="s">
         <v>180</v>
       </c>
@@ -34843,7 +34873,7 @@
         <v>1594</v>
       </c>
     </row>
-    <row r="1010" spans="3:13" x14ac:dyDescent="0.3">
+    <row r="1010" spans="3:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="C1010" t="s">
         <v>180</v>
       </c>
@@ -34869,7 +34899,7 @@
         <v>1594</v>
       </c>
     </row>
-    <row r="1011" spans="3:13" x14ac:dyDescent="0.3">
+    <row r="1011" spans="3:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="C1011" t="s">
         <v>180</v>
       </c>
@@ -34895,7 +34925,7 @@
         <v>1594</v>
       </c>
     </row>
-    <row r="1012" spans="3:13" x14ac:dyDescent="0.3">
+    <row r="1012" spans="3:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="C1012" t="s">
         <v>180</v>
       </c>
@@ -34921,7 +34951,7 @@
         <v>1594</v>
       </c>
     </row>
-    <row r="1013" spans="3:13" x14ac:dyDescent="0.3">
+    <row r="1013" spans="3:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="C1013" t="s">
         <v>180</v>
       </c>
@@ -34947,7 +34977,7 @@
         <v>1594</v>
       </c>
     </row>
-    <row r="1014" spans="3:13" x14ac:dyDescent="0.3">
+    <row r="1014" spans="3:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="C1014" t="s">
         <v>180</v>
       </c>
@@ -34973,7 +35003,7 @@
         <v>1594</v>
       </c>
     </row>
-    <row r="1015" spans="3:13" x14ac:dyDescent="0.3">
+    <row r="1015" spans="3:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="C1015" t="s">
         <v>1420</v>
       </c>
@@ -34999,7 +35029,7 @@
         <v>1594</v>
       </c>
     </row>
-    <row r="1016" spans="3:13" x14ac:dyDescent="0.3">
+    <row r="1016" spans="3:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="C1016" t="s">
         <v>1420</v>
       </c>
@@ -35025,7 +35055,7 @@
         <v>1594</v>
       </c>
     </row>
-    <row r="1017" spans="3:13" x14ac:dyDescent="0.3">
+    <row r="1017" spans="3:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="C1017" t="s">
         <v>1420</v>
       </c>
@@ -35051,7 +35081,7 @@
         <v>1594</v>
       </c>
     </row>
-    <row r="1018" spans="3:13" x14ac:dyDescent="0.3">
+    <row r="1018" spans="3:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="C1018" t="s">
         <v>150</v>
       </c>
@@ -35080,7 +35110,7 @@
         <v>1612</v>
       </c>
     </row>
-    <row r="1019" spans="3:13" x14ac:dyDescent="0.3">
+    <row r="1019" spans="3:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="C1019" t="s">
         <v>150</v>
       </c>
@@ -35109,7 +35139,7 @@
         <v>1612</v>
       </c>
     </row>
-    <row r="1020" spans="3:13" x14ac:dyDescent="0.3">
+    <row r="1020" spans="3:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="C1020" t="s">
         <v>150</v>
       </c>
@@ -35138,7 +35168,7 @@
         <v>1612</v>
       </c>
     </row>
-    <row r="1021" spans="3:13" x14ac:dyDescent="0.3">
+    <row r="1021" spans="3:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="C1021" t="s">
         <v>150</v>
       </c>
@@ -35167,7 +35197,7 @@
         <v>1612</v>
       </c>
     </row>
-    <row r="1022" spans="3:13" x14ac:dyDescent="0.3">
+    <row r="1022" spans="3:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="C1022" t="s">
         <v>150</v>
       </c>
@@ -35196,7 +35226,7 @@
         <v>1612</v>
       </c>
     </row>
-    <row r="1023" spans="3:13" x14ac:dyDescent="0.3">
+    <row r="1023" spans="3:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="C1023" t="s">
         <v>150</v>
       </c>
@@ -35225,7 +35255,7 @@
         <v>1612</v>
       </c>
     </row>
-    <row r="1024" spans="3:13" x14ac:dyDescent="0.3">
+    <row r="1024" spans="3:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="C1024" t="s">
         <v>150</v>
       </c>
@@ -35254,7 +35284,7 @@
         <v>1612</v>
       </c>
     </row>
-    <row r="1025" spans="3:13" x14ac:dyDescent="0.3">
+    <row r="1025" spans="3:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="C1025" t="s">
         <v>150</v>
       </c>
@@ -35283,7 +35313,7 @@
         <v>1612</v>
       </c>
     </row>
-    <row r="1026" spans="3:13" x14ac:dyDescent="0.3">
+    <row r="1026" spans="3:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="D1026" t="s">
         <v>1621</v>
       </c>
@@ -35306,7 +35336,7 @@
         <v>1624</v>
       </c>
     </row>
-    <row r="1027" spans="3:13" x14ac:dyDescent="0.3">
+    <row r="1027" spans="3:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="D1027" t="s">
         <v>1621</v>
       </c>
@@ -35329,7 +35359,7 @@
         <v>1624</v>
       </c>
     </row>
-    <row r="1028" spans="3:13" x14ac:dyDescent="0.3">
+    <row r="1028" spans="3:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="D1028" t="s">
         <v>1621</v>
       </c>
@@ -35349,7 +35379,7 @@
         <v>1624</v>
       </c>
     </row>
-    <row r="1029" spans="3:13" x14ac:dyDescent="0.3">
+    <row r="1029" spans="3:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="D1029" t="s">
         <v>1621</v>
       </c>
@@ -35369,7 +35399,7 @@
         <v>1624</v>
       </c>
     </row>
-    <row r="1030" spans="3:13" x14ac:dyDescent="0.3">
+    <row r="1030" spans="3:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="C1030" t="s">
         <v>129</v>
       </c>
@@ -35395,7 +35425,7 @@
         <v>1628</v>
       </c>
     </row>
-    <row r="1031" spans="3:13" x14ac:dyDescent="0.3">
+    <row r="1031" spans="3:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="C1031" t="s">
         <v>129</v>
       </c>
@@ -35421,7 +35451,7 @@
         <v>1628</v>
       </c>
     </row>
-    <row r="1032" spans="3:13" x14ac:dyDescent="0.3">
+    <row r="1032" spans="3:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="C1032" t="s">
         <v>129</v>
       </c>
@@ -35447,7 +35477,7 @@
         <v>1628</v>
       </c>
     </row>
-    <row r="1033" spans="3:13" x14ac:dyDescent="0.3">
+    <row r="1033" spans="3:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="C1033" t="s">
         <v>129</v>
       </c>
@@ -35473,7 +35503,7 @@
         <v>1628</v>
       </c>
     </row>
-    <row r="1034" spans="3:13" x14ac:dyDescent="0.3">
+    <row r="1034" spans="3:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="C1034" t="s">
         <v>129</v>
       </c>
@@ -35499,7 +35529,7 @@
         <v>1628</v>
       </c>
     </row>
-    <row r="1035" spans="3:13" x14ac:dyDescent="0.3">
+    <row r="1035" spans="3:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="C1035" t="s">
         <v>129</v>
       </c>
@@ -35525,7 +35555,7 @@
         <v>1628</v>
       </c>
     </row>
-    <row r="1036" spans="3:13" x14ac:dyDescent="0.3">
+    <row r="1036" spans="3:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="C1036" t="s">
         <v>129</v>
       </c>
@@ -35551,7 +35581,7 @@
         <v>1628</v>
       </c>
     </row>
-    <row r="1037" spans="3:13" x14ac:dyDescent="0.3">
+    <row r="1037" spans="3:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="C1037" t="s">
         <v>129</v>
       </c>
@@ -35577,7 +35607,7 @@
         <v>1628</v>
       </c>
     </row>
-    <row r="1038" spans="3:13" x14ac:dyDescent="0.3">
+    <row r="1038" spans="3:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="C1038" t="s">
         <v>303</v>
       </c>
@@ -35603,7 +35633,7 @@
         <v>1630</v>
       </c>
     </row>
-    <row r="1039" spans="3:13" x14ac:dyDescent="0.3">
+    <row r="1039" spans="3:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="C1039" t="s">
         <v>303</v>
       </c>
@@ -35629,7 +35659,7 @@
         <v>1630</v>
       </c>
     </row>
-    <row r="1040" spans="3:13" x14ac:dyDescent="0.3">
+    <row r="1040" spans="3:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="C1040" t="s">
         <v>303</v>
       </c>
@@ -35655,7 +35685,7 @@
         <v>1630</v>
       </c>
     </row>
-    <row r="1041" spans="3:13" x14ac:dyDescent="0.3">
+    <row r="1041" spans="3:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="C1041" t="s">
         <v>303</v>
       </c>
@@ -35682,7 +35712,15 @@
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:M1041" xr:uid="{00000000-0009-0000-0000-000000000000}"/>
+  <autoFilter ref="A1:M1041" xr:uid="{00000000-0009-0000-0000-000000000000}">
+    <filterColumn colId="10">
+      <filters>
+        <filter val="Sakura"/>
+        <filter val="Sakura A"/>
+        <filter val="Sakura C"/>
+      </filters>
+    </filterColumn>
+  </autoFilter>
   <hyperlinks>
     <hyperlink ref="M14" r:id="rId1" xr:uid="{00000000-0004-0000-0000-000000000000}"/>
     <hyperlink ref="M15" r:id="rId2" xr:uid="{00000000-0004-0000-0000-000001000000}"/>

--- a/data/raw/copas_y_torneos.xlsx
+++ b/data/raw/copas_y_torneos.xlsx
@@ -526,7 +526,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr filterMode="1">
+  <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
@@ -614,7 +614,7 @@
         </is>
       </c>
     </row>
-    <row r="2" hidden="1">
+    <row r="2">
       <c r="A2" s="6" t="inlineStr">
         <is>
           <t>2024-11-18-CopaAELU</t>
@@ -661,7 +661,7 @@
         </is>
       </c>
     </row>
-    <row r="3" hidden="1">
+    <row r="3">
       <c r="A3" s="6" t="n"/>
       <c r="B3" s="6" t="n"/>
       <c r="C3" s="6" t="n"/>
@@ -704,7 +704,7 @@
         </is>
       </c>
     </row>
-    <row r="4" hidden="1">
+    <row r="4">
       <c r="A4" s="6" t="n"/>
       <c r="B4" s="6" t="n"/>
       <c r="C4" s="6" t="n"/>
@@ -747,7 +747,7 @@
         </is>
       </c>
     </row>
-    <row r="5" hidden="1">
+    <row r="5">
       <c r="D5" s="6" t="inlineStr">
         <is>
           <t>Copa "José Watanabe Kaway"</t>
@@ -786,7 +786,7 @@
         </is>
       </c>
     </row>
-    <row r="6" hidden="1">
+    <row r="6">
       <c r="C6" t="inlineStr">
         <is>
           <t>Torneo AELU</t>
@@ -830,7 +830,7 @@
         </is>
       </c>
     </row>
-    <row r="7" hidden="1">
+    <row r="7">
       <c r="C7" t="inlineStr">
         <is>
           <t>Torneo AELU</t>
@@ -874,7 +874,7 @@
         </is>
       </c>
     </row>
-    <row r="8" hidden="1">
+    <row r="8">
       <c r="C8" t="inlineStr">
         <is>
           <t>Torneo AELU</t>
@@ -918,7 +918,7 @@
         </is>
       </c>
     </row>
-    <row r="9" hidden="1">
+    <row r="9">
       <c r="C9" t="inlineStr">
         <is>
           <t>Torneo AELU</t>
@@ -962,7 +962,7 @@
         </is>
       </c>
     </row>
-    <row r="10" hidden="1">
+    <row r="10">
       <c r="C10" t="inlineStr">
         <is>
           <t>Torneo AELU</t>
@@ -1006,7 +1006,7 @@
         </is>
       </c>
     </row>
-    <row r="11" hidden="1">
+    <row r="11">
       <c r="C11" t="inlineStr">
         <is>
           <t>Torneo AELU</t>
@@ -1050,7 +1050,7 @@
         </is>
       </c>
     </row>
-    <row r="12" hidden="1">
+    <row r="12">
       <c r="C12" t="inlineStr">
         <is>
           <t>Torneo AELU</t>
@@ -1094,7 +1094,7 @@
         </is>
       </c>
     </row>
-    <row r="13" hidden="1">
+    <row r="13">
       <c r="C13" t="inlineStr">
         <is>
           <t>Torneo AELU</t>
@@ -1138,7 +1138,7 @@
         </is>
       </c>
     </row>
-    <row r="14" hidden="1">
+    <row r="14">
       <c r="C14" t="inlineStr">
         <is>
           <t>Torneo Copa Embajada</t>
@@ -1182,7 +1182,7 @@
         </is>
       </c>
     </row>
-    <row r="15" hidden="1">
+    <row r="15">
       <c r="C15" t="inlineStr">
         <is>
           <t>Torneo Copa Embajada</t>
@@ -1226,7 +1226,7 @@
         </is>
       </c>
     </row>
-    <row r="16" hidden="1">
+    <row r="16">
       <c r="C16" t="inlineStr">
         <is>
           <t>Torneo Copa Embajada</t>
@@ -1270,7 +1270,7 @@
         </is>
       </c>
     </row>
-    <row r="17" hidden="1">
+    <row r="17">
       <c r="C17" t="inlineStr">
         <is>
           <t>Torneo Copa Embajada</t>
@@ -1314,7 +1314,7 @@
         </is>
       </c>
     </row>
-    <row r="18" hidden="1">
+    <row r="18">
       <c r="C18" t="inlineStr">
         <is>
           <t>Torneo Copa Embajada</t>
@@ -1358,7 +1358,7 @@
         </is>
       </c>
     </row>
-    <row r="19" hidden="1">
+    <row r="19">
       <c r="C19" t="inlineStr">
         <is>
           <t>Torneo Copa Embajada</t>
@@ -1402,7 +1402,7 @@
         </is>
       </c>
     </row>
-    <row r="20" hidden="1">
+    <row r="20">
       <c r="C20" t="inlineStr">
         <is>
           <t>Torneo Emmanuel</t>
@@ -1441,7 +1441,7 @@
         </is>
       </c>
     </row>
-    <row r="21" hidden="1">
+    <row r="21">
       <c r="C21" t="inlineStr">
         <is>
           <t>Torneo Emmanuel</t>
@@ -1480,7 +1480,7 @@
         </is>
       </c>
     </row>
-    <row r="22" hidden="1">
+    <row r="22">
       <c r="C22" t="inlineStr">
         <is>
           <t>Torneo Emmanuel</t>
@@ -1519,7 +1519,7 @@
         </is>
       </c>
     </row>
-    <row r="23" hidden="1">
+    <row r="23">
       <c r="C23" t="inlineStr">
         <is>
           <t>Torneo Emmanuel</t>
@@ -1558,7 +1558,7 @@
         </is>
       </c>
     </row>
-    <row r="24" hidden="1">
+    <row r="24">
       <c r="C24" t="inlineStr">
         <is>
           <t>Torneo AOPCOOP</t>
@@ -1597,7 +1597,7 @@
         </is>
       </c>
     </row>
-    <row r="25" hidden="1">
+    <row r="25">
       <c r="C25" t="inlineStr">
         <is>
           <t>Torneo AOPCOOP</t>
@@ -1636,7 +1636,7 @@
         </is>
       </c>
     </row>
-    <row r="26" hidden="1">
+    <row r="26">
       <c r="C26" t="inlineStr">
         <is>
           <t>Torneo AOPCOOP</t>
@@ -1675,7 +1675,7 @@
         </is>
       </c>
     </row>
-    <row r="27" hidden="1">
+    <row r="27">
       <c r="C27" t="inlineStr">
         <is>
           <t>Torneo AOPCOOP</t>
@@ -1714,7 +1714,7 @@
         </is>
       </c>
     </row>
-    <row r="28" hidden="1">
+    <row r="28">
       <c r="C28" t="inlineStr">
         <is>
           <t>Torneo Chatan</t>
@@ -1753,7 +1753,7 @@
         </is>
       </c>
     </row>
-    <row r="29" hidden="1">
+    <row r="29">
       <c r="C29" t="inlineStr">
         <is>
           <t>Torneo Chatan</t>
@@ -1792,7 +1792,7 @@
         </is>
       </c>
     </row>
-    <row r="30" hidden="1">
+    <row r="30">
       <c r="C30" t="inlineStr">
         <is>
           <t>Torneo Chatan</t>
@@ -1831,7 +1831,7 @@
         </is>
       </c>
     </row>
-    <row r="31" hidden="1">
+    <row r="31">
       <c r="C31" t="inlineStr">
         <is>
           <t>Torneo Chatan</t>
@@ -1870,7 +1870,7 @@
         </is>
       </c>
     </row>
-    <row r="32" hidden="1">
+    <row r="32">
       <c r="C32" t="inlineStr">
         <is>
           <t>Torneo Okinawa Kenjinkai</t>
@@ -1909,7 +1909,7 @@
         </is>
       </c>
     </row>
-    <row r="33" hidden="1">
+    <row r="33">
       <c r="C33" t="inlineStr">
         <is>
           <t>Torneo Okinawa Kenjinkai</t>
@@ -1948,7 +1948,7 @@
         </is>
       </c>
     </row>
-    <row r="34" hidden="1">
+    <row r="34">
       <c r="C34" t="inlineStr">
         <is>
           <t>Torneo Okinawa Kenjinkai</t>
@@ -1987,7 +1987,7 @@
         </is>
       </c>
     </row>
-    <row r="35" hidden="1">
+    <row r="35">
       <c r="C35" t="inlineStr">
         <is>
           <t>Torneo Okinawa Kenjinkai</t>
@@ -2026,7 +2026,7 @@
         </is>
       </c>
     </row>
-    <row r="36" hidden="1">
+    <row r="36">
       <c r="C36" t="inlineStr">
         <is>
           <t>Torneo Nikkei Fujinkai</t>
@@ -2065,7 +2065,7 @@
         </is>
       </c>
     </row>
-    <row r="37" hidden="1">
+    <row r="37">
       <c r="C37" t="inlineStr">
         <is>
           <t>Torneo Nikkei Fujinkai</t>
@@ -2104,7 +2104,7 @@
         </is>
       </c>
     </row>
-    <row r="38" hidden="1">
+    <row r="38">
       <c r="C38" t="inlineStr">
         <is>
           <t>Torneo Nikkei Fujinkai</t>
@@ -2143,7 +2143,7 @@
         </is>
       </c>
     </row>
-    <row r="39" hidden="1">
+    <row r="39">
       <c r="C39" t="inlineStr">
         <is>
           <t>Torneo Nikkei Fujinkai</t>
@@ -2182,7 +2182,7 @@
         </is>
       </c>
     </row>
-    <row r="40" hidden="1">
+    <row r="40">
       <c r="C40" t="inlineStr">
         <is>
           <t>Torneo Kumamoto Kenjinkai</t>
@@ -2221,7 +2221,7 @@
         </is>
       </c>
     </row>
-    <row r="41" hidden="1">
+    <row r="41">
       <c r="C41" t="inlineStr">
         <is>
           <t>Torneo Kumamoto Kenjinkai</t>
@@ -2260,7 +2260,7 @@
         </is>
       </c>
     </row>
-    <row r="42" hidden="1">
+    <row r="42">
       <c r="C42" t="inlineStr">
         <is>
           <t>Torneo Kumamoto Kenjinkai</t>
@@ -2299,7 +2299,7 @@
         </is>
       </c>
     </row>
-    <row r="43" hidden="1">
+    <row r="43">
       <c r="C43" t="inlineStr">
         <is>
           <t>Torneo Kumamoto Kenjinkai</t>
@@ -2338,7 +2338,7 @@
         </is>
       </c>
     </row>
-    <row r="44" hidden="1">
+    <row r="44">
       <c r="C44" t="inlineStr">
         <is>
           <t>Torneo Kumamoto Kenjinkai</t>
@@ -2377,7 +2377,7 @@
         </is>
       </c>
     </row>
-    <row r="45" hidden="1">
+    <row r="45">
       <c r="C45" t="inlineStr">
         <is>
           <t>Torneo Kumamoto Kenjinkai</t>
@@ -2416,7 +2416,7 @@
         </is>
       </c>
     </row>
-    <row r="46" hidden="1">
+    <row r="46">
       <c r="C46" t="inlineStr">
         <is>
           <t>Torneo Kumamoto Kenjinkai</t>
@@ -2455,7 +2455,7 @@
         </is>
       </c>
     </row>
-    <row r="47" hidden="1">
+    <row r="47">
       <c r="C47" t="inlineStr">
         <is>
           <t>Torneo Kumamoto Kenjinkai</t>
@@ -2494,7 +2494,7 @@
         </is>
       </c>
     </row>
-    <row r="48" hidden="1">
+    <row r="48">
       <c r="C48" t="inlineStr">
         <is>
           <t>Torneo Club Aikokai</t>
@@ -2533,7 +2533,7 @@
         </is>
       </c>
     </row>
-    <row r="49" hidden="1">
+    <row r="49">
       <c r="C49" t="inlineStr">
         <is>
           <t>Torneo Club Aikokai</t>
@@ -2572,7 +2572,7 @@
         </is>
       </c>
     </row>
-    <row r="50" hidden="1">
+    <row r="50">
       <c r="C50" t="inlineStr">
         <is>
           <t>Torneo Club Aikokai</t>
@@ -2611,7 +2611,7 @@
         </is>
       </c>
     </row>
-    <row r="51" hidden="1">
+    <row r="51">
       <c r="C51" t="inlineStr">
         <is>
           <t>Torneo Club Aikokai</t>
@@ -2650,7 +2650,7 @@
         </is>
       </c>
     </row>
-    <row r="52" hidden="1">
+    <row r="52">
       <c r="B52" t="inlineStr">
         <is>
           <t>Confraternidad/Integración</t>
@@ -2689,7 +2689,7 @@
         </is>
       </c>
     </row>
-    <row r="53" hidden="1">
+    <row r="53">
       <c r="B53" t="inlineStr">
         <is>
           <t>Confraternidad/Integración</t>
@@ -2728,7 +2728,7 @@
         </is>
       </c>
     </row>
-    <row r="54" hidden="1">
+    <row r="54">
       <c r="B54" t="inlineStr">
         <is>
           <t>Confraternidad/Integración</t>
@@ -2767,7 +2767,7 @@
         </is>
       </c>
     </row>
-    <row r="55" hidden="1">
+    <row r="55">
       <c r="B55" t="inlineStr">
         <is>
           <t>Confraternidad/Integración</t>
@@ -2806,7 +2806,7 @@
         </is>
       </c>
     </row>
-    <row r="56" hidden="1">
+    <row r="56">
       <c r="C56" t="inlineStr">
         <is>
           <t>Torneo Okinawa Fujinkai</t>
@@ -2845,7 +2845,7 @@
         </is>
       </c>
     </row>
-    <row r="57" hidden="1">
+    <row r="57">
       <c r="C57" t="inlineStr">
         <is>
           <t>Torneo APG</t>
@@ -2884,7 +2884,7 @@
         </is>
       </c>
     </row>
-    <row r="58" hidden="1">
+    <row r="58">
       <c r="C58" t="inlineStr">
         <is>
           <t>Torneo APG</t>
@@ -2923,7 +2923,7 @@
         </is>
       </c>
     </row>
-    <row r="59" hidden="1">
+    <row r="59">
       <c r="C59" t="inlineStr">
         <is>
           <t>Torneo APG</t>
@@ -2962,7 +2962,7 @@
         </is>
       </c>
     </row>
-    <row r="60" hidden="1">
+    <row r="60">
       <c r="C60" t="inlineStr">
         <is>
           <t>Torneo APG</t>
@@ -3001,7 +3001,7 @@
         </is>
       </c>
     </row>
-    <row r="61" hidden="1">
+    <row r="61">
       <c r="B61" t="inlineStr">
         <is>
           <t>Campeonato Oficial</t>
@@ -3045,7 +3045,7 @@
         </is>
       </c>
     </row>
-    <row r="62" hidden="1">
+    <row r="62">
       <c r="B62" t="inlineStr">
         <is>
           <t>Campeonato Oficial</t>
@@ -3089,7 +3089,7 @@
         </is>
       </c>
     </row>
-    <row r="63" hidden="1">
+    <row r="63">
       <c r="B63" t="inlineStr">
         <is>
           <t>Campeonato Oficial</t>
@@ -3133,7 +3133,7 @@
         </is>
       </c>
     </row>
-    <row r="64" hidden="1">
+    <row r="64">
       <c r="B64" t="inlineStr">
         <is>
           <t>Campeonato Oficial</t>
@@ -3177,7 +3177,7 @@
         </is>
       </c>
     </row>
-    <row r="65" hidden="1">
+    <row r="65">
       <c r="B65" t="inlineStr">
         <is>
           <t>Campeonato Oficial</t>
@@ -3221,7 +3221,7 @@
         </is>
       </c>
     </row>
-    <row r="66" hidden="1">
+    <row r="66">
       <c r="B66" t="inlineStr">
         <is>
           <t>Campeonato Oficial</t>
@@ -3265,7 +3265,7 @@
         </is>
       </c>
     </row>
-    <row r="67" hidden="1">
+    <row r="67">
       <c r="B67" t="inlineStr">
         <is>
           <t>Campeonato Oficial</t>
@@ -3309,7 +3309,7 @@
         </is>
       </c>
     </row>
-    <row r="68" hidden="1">
+    <row r="68">
       <c r="B68" t="inlineStr">
         <is>
           <t>Campeonato Oficial</t>
@@ -3353,7 +3353,7 @@
         </is>
       </c>
     </row>
-    <row r="69" hidden="1">
+    <row r="69">
       <c r="B69" t="inlineStr">
         <is>
           <t>Campeonato Oficial</t>
@@ -3397,7 +3397,7 @@
         </is>
       </c>
     </row>
-    <row r="70" hidden="1">
+    <row r="70">
       <c r="B70" t="inlineStr">
         <is>
           <t>Campeonato Oficial</t>
@@ -3441,7 +3441,7 @@
         </is>
       </c>
     </row>
-    <row r="71" hidden="1">
+    <row r="71">
       <c r="B71" t="inlineStr">
         <is>
           <t>Campeonato Oficial</t>
@@ -3485,7 +3485,7 @@
         </is>
       </c>
     </row>
-    <row r="72" hidden="1">
+    <row r="72">
       <c r="B72" t="inlineStr">
         <is>
           <t>Campeonato Oficial</t>
@@ -3529,7 +3529,7 @@
         </is>
       </c>
     </row>
-    <row r="73" hidden="1">
+    <row r="73">
       <c r="B73" t="inlineStr">
         <is>
           <t>Campeonato Oficial</t>
@@ -3573,7 +3573,7 @@
         </is>
       </c>
     </row>
-    <row r="74" hidden="1">
+    <row r="74">
       <c r="B74" t="inlineStr">
         <is>
           <t>Campeonato Oficial</t>
@@ -3617,7 +3617,7 @@
         </is>
       </c>
     </row>
-    <row r="75" hidden="1">
+    <row r="75">
       <c r="B75" t="inlineStr">
         <is>
           <t>Campeonato Oficial</t>
@@ -3661,7 +3661,7 @@
         </is>
       </c>
     </row>
-    <row r="76" hidden="1">
+    <row r="76">
       <c r="B76" t="inlineStr">
         <is>
           <t>Campeonato Oficial</t>
@@ -3705,7 +3705,7 @@
         </is>
       </c>
     </row>
-    <row r="77" hidden="1">
+    <row r="77">
       <c r="B77" t="inlineStr">
         <is>
           <t>Campeonato Oficial</t>
@@ -3749,7 +3749,7 @@
         </is>
       </c>
     </row>
-    <row r="78" hidden="1">
+    <row r="78">
       <c r="B78" t="inlineStr">
         <is>
           <t>Campeonato Oficial</t>
@@ -3793,7 +3793,7 @@
         </is>
       </c>
     </row>
-    <row r="79" hidden="1">
+    <row r="79">
       <c r="C79" t="inlineStr">
         <is>
           <t>Torneo Chatan</t>
@@ -3832,7 +3832,7 @@
         </is>
       </c>
     </row>
-    <row r="80" hidden="1">
+    <row r="80">
       <c r="C80" t="inlineStr">
         <is>
           <t>Torneo Chatan</t>
@@ -3871,7 +3871,7 @@
         </is>
       </c>
     </row>
-    <row r="81" hidden="1">
+    <row r="81">
       <c r="C81" t="inlineStr">
         <is>
           <t>Torneo Chatan</t>
@@ -3910,7 +3910,7 @@
         </is>
       </c>
     </row>
-    <row r="82" hidden="1">
+    <row r="82">
       <c r="C82" t="inlineStr">
         <is>
           <t>Torneo Chatan</t>
@@ -3949,7 +3949,7 @@
         </is>
       </c>
     </row>
-    <row r="83" hidden="1">
+    <row r="83">
       <c r="C83" t="inlineStr">
         <is>
           <t>Torneo Copa Embajada</t>
@@ -3993,7 +3993,7 @@
         </is>
       </c>
     </row>
-    <row r="84" hidden="1">
+    <row r="84">
       <c r="C84" t="inlineStr">
         <is>
           <t>Torneo Copa Embajada</t>
@@ -4037,7 +4037,7 @@
         </is>
       </c>
     </row>
-    <row r="85" hidden="1">
+    <row r="85">
       <c r="C85" t="inlineStr">
         <is>
           <t>Torneo Copa Embajada</t>
@@ -4081,7 +4081,7 @@
         </is>
       </c>
     </row>
-    <row r="86" hidden="1">
+    <row r="86">
       <c r="C86" t="inlineStr">
         <is>
           <t>Torneo Copa Embajada</t>
@@ -4125,7 +4125,7 @@
         </is>
       </c>
     </row>
-    <row r="87" hidden="1">
+    <row r="87">
       <c r="C87" t="inlineStr">
         <is>
           <t>Torneo Copa Embajada</t>
@@ -4169,7 +4169,7 @@
         </is>
       </c>
     </row>
-    <row r="88" hidden="1">
+    <row r="88">
       <c r="C88" t="inlineStr">
         <is>
           <t>Torneo Copa Embajada</t>
@@ -4213,7 +4213,7 @@
         </is>
       </c>
     </row>
-    <row r="89" hidden="1">
+    <row r="89">
       <c r="C89" t="inlineStr">
         <is>
           <t>Torneo Emmanuel</t>
@@ -4252,7 +4252,7 @@
         </is>
       </c>
     </row>
-    <row r="90" hidden="1">
+    <row r="90">
       <c r="C90" t="inlineStr">
         <is>
           <t>Torneo Emmanuel</t>
@@ -4291,7 +4291,7 @@
         </is>
       </c>
     </row>
-    <row r="91" hidden="1">
+    <row r="91">
       <c r="C91" t="inlineStr">
         <is>
           <t>Torneo Emmanuel</t>
@@ -4330,7 +4330,7 @@
         </is>
       </c>
     </row>
-    <row r="92" hidden="1">
+    <row r="92">
       <c r="C92" t="inlineStr">
         <is>
           <t>Torneo Emmanuel</t>
@@ -4369,7 +4369,7 @@
         </is>
       </c>
     </row>
-    <row r="93" hidden="1">
+    <row r="93">
       <c r="C93" t="inlineStr">
         <is>
           <t>Torneo AOPCOOP</t>
@@ -4408,7 +4408,7 @@
         </is>
       </c>
     </row>
-    <row r="94" hidden="1">
+    <row r="94">
       <c r="C94" t="inlineStr">
         <is>
           <t>Torneo AOPCOOP</t>
@@ -4447,7 +4447,7 @@
         </is>
       </c>
     </row>
-    <row r="95" hidden="1">
+    <row r="95">
       <c r="C95" t="inlineStr">
         <is>
           <t>Torneo AOPCOOP</t>
@@ -4486,7 +4486,7 @@
         </is>
       </c>
     </row>
-    <row r="96" hidden="1">
+    <row r="96">
       <c r="C96" t="inlineStr">
         <is>
           <t>Torneo AOPCOOP</t>
@@ -4525,7 +4525,7 @@
         </is>
       </c>
     </row>
-    <row r="97" hidden="1">
+    <row r="97">
       <c r="B97" t="inlineStr">
         <is>
           <t>Confraternidad/Integración</t>
@@ -4569,7 +4569,7 @@
         </is>
       </c>
     </row>
-    <row r="98" hidden="1">
+    <row r="98">
       <c r="B98" t="inlineStr">
         <is>
           <t>Confraternidad/Integración</t>
@@ -4613,7 +4613,7 @@
         </is>
       </c>
     </row>
-    <row r="99" hidden="1">
+    <row r="99">
       <c r="B99" t="inlineStr">
         <is>
           <t>Confraternidad/Integración</t>
@@ -4657,7 +4657,7 @@
         </is>
       </c>
     </row>
-    <row r="100" hidden="1">
+    <row r="100">
       <c r="B100" t="inlineStr">
         <is>
           <t>Campeonato Oficial</t>
@@ -4701,7 +4701,7 @@
         </is>
       </c>
     </row>
-    <row r="101" hidden="1">
+    <row r="101">
       <c r="B101" t="inlineStr">
         <is>
           <t>Campeonato Oficial</t>
@@ -4740,7 +4740,7 @@
         </is>
       </c>
     </row>
-    <row r="102" hidden="1">
+    <row r="102">
       <c r="B102" t="inlineStr">
         <is>
           <t>Campeonato Oficial</t>
@@ -4779,7 +4779,7 @@
         </is>
       </c>
     </row>
-    <row r="103" hidden="1">
+    <row r="103">
       <c r="B103" t="inlineStr">
         <is>
           <t>Campeonato Oficial</t>
@@ -4823,7 +4823,7 @@
         </is>
       </c>
     </row>
-    <row r="104" hidden="1">
+    <row r="104">
       <c r="B104" t="inlineStr">
         <is>
           <t>Campeonato Oficial</t>
@@ -4862,7 +4862,7 @@
         </is>
       </c>
     </row>
-    <row r="105" hidden="1">
+    <row r="105">
       <c r="B105" t="inlineStr">
         <is>
           <t>Campeonato Oficial</t>
@@ -4901,7 +4901,7 @@
         </is>
       </c>
     </row>
-    <row r="106" hidden="1">
+    <row r="106">
       <c r="B106" t="inlineStr">
         <is>
           <t>Campeonato Oficial</t>
@@ -4940,7 +4940,7 @@
         </is>
       </c>
     </row>
-    <row r="107" hidden="1">
+    <row r="107">
       <c r="B107" t="inlineStr">
         <is>
           <t>Campeonato Oficial</t>
@@ -4979,7 +4979,7 @@
         </is>
       </c>
     </row>
-    <row r="108" hidden="1">
+    <row r="108">
       <c r="B108" t="inlineStr">
         <is>
           <t>Campeonato Oficial</t>
@@ -5018,7 +5018,7 @@
         </is>
       </c>
     </row>
-    <row r="109" hidden="1">
+    <row r="109">
       <c r="B109" t="inlineStr">
         <is>
           <t>Campeonato Oficial</t>
@@ -5057,7 +5057,7 @@
         </is>
       </c>
     </row>
-    <row r="110" hidden="1">
+    <row r="110">
       <c r="B110" t="inlineStr">
         <is>
           <t>Campeonato Oficial</t>
@@ -5096,7 +5096,7 @@
         </is>
       </c>
     </row>
-    <row r="111" hidden="1">
+    <row r="111">
       <c r="B111" t="inlineStr">
         <is>
           <t>Campeonato Oficial</t>
@@ -5135,7 +5135,7 @@
         </is>
       </c>
     </row>
-    <row r="112" hidden="1">
+    <row r="112">
       <c r="C112" t="inlineStr">
         <is>
           <t>Torneo Okinawa Kenjinkai</t>
@@ -5174,7 +5174,7 @@
         </is>
       </c>
     </row>
-    <row r="113" hidden="1">
+    <row r="113">
       <c r="C113" t="inlineStr">
         <is>
           <t>Torneo Okinawa Kenjinkai</t>
@@ -5213,7 +5213,7 @@
         </is>
       </c>
     </row>
-    <row r="114" hidden="1">
+    <row r="114">
       <c r="C114" t="inlineStr">
         <is>
           <t>Torneo Okinawa Kenjinkai</t>
@@ -5252,7 +5252,7 @@
         </is>
       </c>
     </row>
-    <row r="115" hidden="1">
+    <row r="115">
       <c r="C115" t="inlineStr">
         <is>
           <t>Torneo Okinawa Kenjinkai</t>
@@ -5291,7 +5291,7 @@
         </is>
       </c>
     </row>
-    <row r="116" hidden="1">
+    <row r="116">
       <c r="B116" t="inlineStr">
         <is>
           <t>Confraternidad/Integración</t>
@@ -5330,7 +5330,7 @@
         </is>
       </c>
     </row>
-    <row r="117" hidden="1">
+    <row r="117">
       <c r="B117" t="inlineStr">
         <is>
           <t>Confraternidad/Integración</t>
@@ -5369,7 +5369,7 @@
         </is>
       </c>
     </row>
-    <row r="118" hidden="1">
+    <row r="118">
       <c r="B118" t="inlineStr">
         <is>
           <t>Confraternidad/Integración</t>
@@ -5408,7 +5408,7 @@
         </is>
       </c>
     </row>
-    <row r="119" hidden="1">
+    <row r="119">
       <c r="B119" t="inlineStr">
         <is>
           <t>Confraternidad/Integración</t>
@@ -5447,7 +5447,7 @@
         </is>
       </c>
     </row>
-    <row r="120" hidden="1">
+    <row r="120">
       <c r="B120" t="inlineStr">
         <is>
           <t>Confraternidad/Integración</t>
@@ -5486,7 +5486,7 @@
         </is>
       </c>
     </row>
-    <row r="121" hidden="1">
+    <row r="121">
       <c r="B121" t="inlineStr">
         <is>
           <t>Confraternidad/Integración</t>
@@ -5525,7 +5525,7 @@
         </is>
       </c>
     </row>
-    <row r="122" hidden="1">
+    <row r="122">
       <c r="B122" t="inlineStr">
         <is>
           <t>Confraternidad/Integración</t>
@@ -5564,7 +5564,7 @@
         </is>
       </c>
     </row>
-    <row r="123" hidden="1">
+    <row r="123">
       <c r="B123" t="inlineStr">
         <is>
           <t>Confraternidad/Integración</t>
@@ -5603,7 +5603,7 @@
         </is>
       </c>
     </row>
-    <row r="124" hidden="1">
+    <row r="124">
       <c r="B124" t="inlineStr">
         <is>
           <t>Campeonato Oficial</t>
@@ -5647,7 +5647,7 @@
         </is>
       </c>
     </row>
-    <row r="125" hidden="1">
+    <row r="125">
       <c r="B125" t="inlineStr">
         <is>
           <t>Campeonato Oficial</t>
@@ -5691,7 +5691,7 @@
         </is>
       </c>
     </row>
-    <row r="126" hidden="1">
+    <row r="126">
       <c r="B126" t="inlineStr">
         <is>
           <t>Campeonato Oficial</t>
@@ -5735,7 +5735,7 @@
         </is>
       </c>
     </row>
-    <row r="127" hidden="1">
+    <row r="127">
       <c r="B127" t="inlineStr">
         <is>
           <t>Campeonato Oficial</t>
@@ -5779,7 +5779,7 @@
         </is>
       </c>
     </row>
-    <row r="128" hidden="1">
+    <row r="128">
       <c r="B128" t="inlineStr">
         <is>
           <t>Campeonato Oficial</t>
@@ -5823,7 +5823,7 @@
         </is>
       </c>
     </row>
-    <row r="129" hidden="1">
+    <row r="129">
       <c r="B129" t="inlineStr">
         <is>
           <t>Campeonato Oficial</t>
@@ -5867,7 +5867,7 @@
         </is>
       </c>
     </row>
-    <row r="130" hidden="1">
+    <row r="130">
       <c r="B130" t="inlineStr">
         <is>
           <t>Campeonato Oficial</t>
@@ -5911,7 +5911,7 @@
         </is>
       </c>
     </row>
-    <row r="131" hidden="1">
+    <row r="131">
       <c r="B131" t="inlineStr">
         <is>
           <t>Campeonato Oficial</t>
@@ -5955,7 +5955,7 @@
         </is>
       </c>
     </row>
-    <row r="132" hidden="1">
+    <row r="132">
       <c r="B132" t="inlineStr">
         <is>
           <t>Campeonato Oficial</t>
@@ -5999,7 +5999,7 @@
         </is>
       </c>
     </row>
-    <row r="133" hidden="1">
+    <row r="133">
       <c r="C133" t="inlineStr">
         <is>
           <t>Torneo Club Aikokai</t>
@@ -6038,7 +6038,7 @@
         </is>
       </c>
     </row>
-    <row r="134" hidden="1">
+    <row r="134">
       <c r="C134" t="inlineStr">
         <is>
           <t>Torneo Club Aikokai</t>
@@ -6077,7 +6077,7 @@
         </is>
       </c>
     </row>
-    <row r="135" hidden="1">
+    <row r="135">
       <c r="C135" t="inlineStr">
         <is>
           <t>Torneo Club Aikokai</t>
@@ -6116,7 +6116,7 @@
         </is>
       </c>
     </row>
-    <row r="136" hidden="1">
+    <row r="136">
       <c r="C136" t="inlineStr">
         <is>
           <t>Torneo Club Aikokai</t>
@@ -6155,7 +6155,7 @@
         </is>
       </c>
     </row>
-    <row r="137" hidden="1">
+    <row r="137">
       <c r="C137" t="inlineStr">
         <is>
           <t>Torneo Okinawa Fujinkai</t>
@@ -6194,7 +6194,7 @@
         </is>
       </c>
     </row>
-    <row r="138" hidden="1">
+    <row r="138">
       <c r="C138" t="inlineStr">
         <is>
           <t>Torneo Okinawa Fujinkai</t>
@@ -6233,7 +6233,7 @@
         </is>
       </c>
     </row>
-    <row r="139" hidden="1">
+    <row r="139">
       <c r="C139" t="inlineStr">
         <is>
           <t>Torneo Okinawa Fujinkai</t>
@@ -6272,7 +6272,7 @@
         </is>
       </c>
     </row>
-    <row r="140" hidden="1">
+    <row r="140">
       <c r="C140" t="inlineStr">
         <is>
           <t>Torneo Okinawa Fujinkai</t>
@@ -6311,7 +6311,7 @@
         </is>
       </c>
     </row>
-    <row r="141" hidden="1">
+    <row r="141">
       <c r="C141" t="inlineStr">
         <is>
           <t>Torneo Den Omori</t>
@@ -6355,7 +6355,7 @@
         </is>
       </c>
     </row>
-    <row r="142" hidden="1">
+    <row r="142">
       <c r="C142" t="inlineStr">
         <is>
           <t>Torneo Den Omori</t>
@@ -6399,7 +6399,7 @@
         </is>
       </c>
     </row>
-    <row r="143" hidden="1">
+    <row r="143">
       <c r="C143" t="inlineStr">
         <is>
           <t>Torneo Den Omori</t>
@@ -6443,7 +6443,7 @@
         </is>
       </c>
     </row>
-    <row r="144" hidden="1">
+    <row r="144">
       <c r="C144" t="inlineStr">
         <is>
           <t>Torneo Den Omori</t>
@@ -6487,7 +6487,7 @@
         </is>
       </c>
     </row>
-    <row r="145" hidden="1">
+    <row r="145">
       <c r="B145" t="inlineStr">
         <is>
           <t>SHI-CHO-SON</t>
@@ -6531,7 +6531,7 @@
         </is>
       </c>
     </row>
-    <row r="146" hidden="1">
+    <row r="146">
       <c r="B146" t="inlineStr">
         <is>
           <t>SHI-CHO-SON</t>
@@ -6575,7 +6575,7 @@
         </is>
       </c>
     </row>
-    <row r="147" hidden="1">
+    <row r="147">
       <c r="B147" t="inlineStr">
         <is>
           <t>SHI-CHO-SON</t>
@@ -6619,7 +6619,7 @@
         </is>
       </c>
     </row>
-    <row r="148" hidden="1">
+    <row r="148">
       <c r="B148" t="inlineStr">
         <is>
           <t>SHI-CHO-SON</t>
@@ -6663,7 +6663,7 @@
         </is>
       </c>
     </row>
-    <row r="149" hidden="1">
+    <row r="149">
       <c r="D149" t="inlineStr">
         <is>
           <t>III TORNEO INTERCLUBES AELU DE GATEBALL</t>
@@ -6702,7 +6702,7 @@
         </is>
       </c>
     </row>
-    <row r="150" hidden="1">
+    <row r="150">
       <c r="D150" t="inlineStr">
         <is>
           <t>III TORNEO INTERCLUBES AELU DE GATEBALL</t>
@@ -6741,7 +6741,7 @@
         </is>
       </c>
     </row>
-    <row r="151" hidden="1">
+    <row r="151">
       <c r="D151" t="inlineStr">
         <is>
           <t>III TORNEO INTERCLUBES AELU DE GATEBALL</t>
@@ -6780,7 +6780,7 @@
         </is>
       </c>
     </row>
-    <row r="152" hidden="1">
+    <row r="152">
       <c r="D152" t="inlineStr">
         <is>
           <t>III TORNEO INTERCLUBES AELU DE GATEBALL</t>
@@ -6819,7 +6819,7 @@
         </is>
       </c>
     </row>
-    <row r="153" hidden="1">
+    <row r="153">
       <c r="D153" t="inlineStr">
         <is>
           <t>III TORNEO INTERCLUBES AELU DE GATEBALL</t>
@@ -6858,7 +6858,7 @@
         </is>
       </c>
     </row>
-    <row r="154" hidden="1">
+    <row r="154">
       <c r="D154" t="inlineStr">
         <is>
           <t>III TORNEO INTERCLUBES AELU DE GATEBALL</t>
@@ -6897,7 +6897,7 @@
         </is>
       </c>
     </row>
-    <row r="155" hidden="1">
+    <row r="155">
       <c r="C155" t="inlineStr">
         <is>
           <t>Torneo AELU</t>
@@ -6932,7 +6932,7 @@
       </c>
       <c r="L155" t="inlineStr">
         <is>
-          <t>Tamayoshi Setsuko, Miyahira Take, Higashionna Chioko, Yamamoto Mistuko, Unten Shigueko y Uehara Nobuko</t>
+          <t>Tamayoshi Setsuko, Miyahira Take, Higashionna Chioko, Yamamoto Mitsuko, Unten Shigueko y Uehara Nobuko</t>
         </is>
       </c>
       <c r="M155" s="3" t="inlineStr">
@@ -6941,7 +6941,7 @@
         </is>
       </c>
     </row>
-    <row r="156" hidden="1">
+    <row r="156">
       <c r="C156" t="inlineStr">
         <is>
           <t>Torneo AELU</t>
@@ -6985,7 +6985,7 @@
         </is>
       </c>
     </row>
-    <row r="157" hidden="1">
+    <row r="157">
       <c r="C157" t="inlineStr">
         <is>
           <t>Torneo AELU</t>
@@ -7029,7 +7029,7 @@
         </is>
       </c>
     </row>
-    <row r="158" hidden="1">
+    <row r="158">
       <c r="C158" t="inlineStr">
         <is>
           <t>Torneo AELU</t>
@@ -7073,7 +7073,7 @@
         </is>
       </c>
     </row>
-    <row r="159" hidden="1">
+    <row r="159">
       <c r="C159" t="inlineStr">
         <is>
           <t>Torneo AELU</t>
@@ -7117,7 +7117,7 @@
         </is>
       </c>
     </row>
-    <row r="160" hidden="1">
+    <row r="160">
       <c r="C160" t="inlineStr">
         <is>
           <t>Torneo AELU</t>
@@ -7161,7 +7161,7 @@
         </is>
       </c>
     </row>
-    <row r="161" hidden="1">
+    <row r="161">
       <c r="C161" t="inlineStr">
         <is>
           <t>Torneo AELU</t>
@@ -7205,7 +7205,7 @@
         </is>
       </c>
     </row>
-    <row r="162" hidden="1">
+    <row r="162">
       <c r="C162" t="inlineStr">
         <is>
           <t>Torneo AELU</t>
@@ -7249,7 +7249,7 @@
         </is>
       </c>
     </row>
-    <row r="163" hidden="1">
+    <row r="163">
       <c r="C163" t="inlineStr">
         <is>
           <t>Torneo Copa Embajada</t>
@@ -7293,7 +7293,7 @@
         </is>
       </c>
     </row>
-    <row r="164" hidden="1">
+    <row r="164">
       <c r="C164" t="inlineStr">
         <is>
           <t>Torneo Copa Embajada</t>
@@ -7337,7 +7337,7 @@
         </is>
       </c>
     </row>
-    <row r="165" hidden="1">
+    <row r="165">
       <c r="C165" t="inlineStr">
         <is>
           <t>Torneo Copa Embajada</t>
@@ -7381,7 +7381,7 @@
         </is>
       </c>
     </row>
-    <row r="166" hidden="1">
+    <row r="166">
       <c r="C166" t="inlineStr">
         <is>
           <t>Torneo Copa Embajada</t>
@@ -7425,7 +7425,7 @@
         </is>
       </c>
     </row>
-    <row r="167" hidden="1">
+    <row r="167">
       <c r="C167" t="inlineStr">
         <is>
           <t>Torneo Copa Embajada</t>
@@ -7469,7 +7469,7 @@
         </is>
       </c>
     </row>
-    <row r="168" hidden="1">
+    <row r="168">
       <c r="C168" t="inlineStr">
         <is>
           <t>Torneo Copa Embajada</t>
@@ -7513,7 +7513,7 @@
         </is>
       </c>
     </row>
-    <row r="169" hidden="1">
+    <row r="169">
       <c r="C169" t="inlineStr">
         <is>
           <t>Torneo Chatan</t>
@@ -7557,7 +7557,7 @@
         </is>
       </c>
     </row>
-    <row r="170" hidden="1">
+    <row r="170">
       <c r="C170" t="inlineStr">
         <is>
           <t>Torneo Chatan</t>
@@ -7601,7 +7601,7 @@
         </is>
       </c>
     </row>
-    <row r="171" hidden="1">
+    <row r="171">
       <c r="C171" t="inlineStr">
         <is>
           <t>Torneo Chatan</t>
@@ -7645,7 +7645,7 @@
         </is>
       </c>
     </row>
-    <row r="172" hidden="1">
+    <row r="172">
       <c r="C172" t="inlineStr">
         <is>
           <t>Torneo Chatan</t>
@@ -7689,7 +7689,7 @@
         </is>
       </c>
     </row>
-    <row r="173" hidden="1">
+    <row r="173">
       <c r="C173" t="inlineStr">
         <is>
           <t>Torneo AOPCOOP</t>
@@ -7733,7 +7733,7 @@
         </is>
       </c>
     </row>
-    <row r="174" hidden="1">
+    <row r="174">
       <c r="C174" t="inlineStr">
         <is>
           <t>Torneo AOPCOOP</t>
@@ -7777,7 +7777,7 @@
         </is>
       </c>
     </row>
-    <row r="175" hidden="1">
+    <row r="175">
       <c r="C175" t="inlineStr">
         <is>
           <t>Torneo AOPCOOP</t>
@@ -7821,7 +7821,7 @@
         </is>
       </c>
     </row>
-    <row r="176" hidden="1">
+    <row r="176">
       <c r="C176" t="inlineStr">
         <is>
           <t>Torneo AOPCOOP</t>
@@ -7865,7 +7865,7 @@
         </is>
       </c>
     </row>
-    <row r="177" hidden="1">
+    <row r="177">
       <c r="B177" t="inlineStr">
         <is>
           <t>Campeonato Oficial</t>
@@ -7909,7 +7909,7 @@
         </is>
       </c>
     </row>
-    <row r="178" hidden="1">
+    <row r="178">
       <c r="B178" t="inlineStr">
         <is>
           <t>Campeonato Oficial</t>
@@ -7953,7 +7953,7 @@
         </is>
       </c>
     </row>
-    <row r="179" hidden="1">
+    <row r="179">
       <c r="B179" t="inlineStr">
         <is>
           <t>Campeonato Oficial</t>
@@ -7997,7 +7997,7 @@
         </is>
       </c>
     </row>
-    <row r="180" hidden="1">
+    <row r="180">
       <c r="B180" t="inlineStr">
         <is>
           <t>Campeonato Oficial</t>
@@ -8041,7 +8041,7 @@
         </is>
       </c>
     </row>
-    <row r="181" hidden="1">
+    <row r="181">
       <c r="B181" t="inlineStr">
         <is>
           <t>Campeonato Oficial</t>
@@ -8085,7 +8085,7 @@
         </is>
       </c>
     </row>
-    <row r="182" hidden="1">
+    <row r="182">
       <c r="B182" t="inlineStr">
         <is>
           <t>Campeonato Oficial</t>
@@ -8129,7 +8129,7 @@
         </is>
       </c>
     </row>
-    <row r="183" hidden="1">
+    <row r="183">
       <c r="B183" t="inlineStr">
         <is>
           <t>Campeonato Oficial</t>
@@ -8173,7 +8173,7 @@
         </is>
       </c>
     </row>
-    <row r="184" hidden="1">
+    <row r="184">
       <c r="B184" t="inlineStr">
         <is>
           <t>Campeonato Oficial</t>
@@ -8217,7 +8217,7 @@
         </is>
       </c>
     </row>
-    <row r="185" hidden="1">
+    <row r="185">
       <c r="B185" t="inlineStr">
         <is>
           <t>Campeonato Oficial</t>
@@ -8261,7 +8261,7 @@
         </is>
       </c>
     </row>
-    <row r="186" hidden="1">
+    <row r="186">
       <c r="B186" t="inlineStr">
         <is>
           <t>Campeonato Oficial</t>
@@ -8305,7 +8305,7 @@
         </is>
       </c>
     </row>
-    <row r="187" hidden="1">
+    <row r="187">
       <c r="B187" t="inlineStr">
         <is>
           <t>Campeonato Oficial</t>
@@ -8349,7 +8349,7 @@
         </is>
       </c>
     </row>
-    <row r="188" hidden="1">
+    <row r="188">
       <c r="B188" t="inlineStr">
         <is>
           <t>Campeonato Oficial</t>
@@ -8393,7 +8393,7 @@
         </is>
       </c>
     </row>
-    <row r="189" hidden="1">
+    <row r="189">
       <c r="C189" t="inlineStr">
         <is>
           <t>Torneo Inmigración Japonesa</t>
@@ -8432,7 +8432,7 @@
         </is>
       </c>
     </row>
-    <row r="190" hidden="1">
+    <row r="190">
       <c r="C190" t="inlineStr">
         <is>
           <t>Torneo Inmigración Japonesa</t>
@@ -8471,7 +8471,7 @@
         </is>
       </c>
     </row>
-    <row r="191" hidden="1">
+    <row r="191">
       <c r="C191" t="inlineStr">
         <is>
           <t>Torneo Inmigración Japonesa</t>
@@ -8510,7 +8510,7 @@
         </is>
       </c>
     </row>
-    <row r="192" hidden="1">
+    <row r="192">
       <c r="C192" t="inlineStr">
         <is>
           <t>Torneo Inmigración Japonesa</t>
@@ -8549,7 +8549,7 @@
         </is>
       </c>
     </row>
-    <row r="193" hidden="1">
+    <row r="193">
       <c r="C193" t="inlineStr">
         <is>
           <t>Torneo Nikkei Fujinkai</t>
@@ -8588,7 +8588,7 @@
         </is>
       </c>
     </row>
-    <row r="194" hidden="1">
+    <row r="194">
       <c r="C194" t="inlineStr">
         <is>
           <t>Torneo Nikkei Fujinkai</t>
@@ -8627,7 +8627,7 @@
         </is>
       </c>
     </row>
-    <row r="195" hidden="1">
+    <row r="195">
       <c r="C195" t="inlineStr">
         <is>
           <t>Torneo Nikkei Fujinkai</t>
@@ -8666,7 +8666,7 @@
         </is>
       </c>
     </row>
-    <row r="196" hidden="1">
+    <row r="196">
       <c r="C196" t="inlineStr">
         <is>
           <t>Torneo Nikkei Fujinkai</t>
@@ -8705,7 +8705,7 @@
         </is>
       </c>
     </row>
-    <row r="197" hidden="1">
+    <row r="197">
       <c r="C197" t="inlineStr">
         <is>
           <t>Torne Kagoshima Kenjinkai</t>
@@ -8749,7 +8749,7 @@
         </is>
       </c>
     </row>
-    <row r="198" hidden="1">
+    <row r="198">
       <c r="C198" t="inlineStr">
         <is>
           <t>Torne Kagoshima Kenjinkai</t>
@@ -8793,7 +8793,7 @@
         </is>
       </c>
     </row>
-    <row r="199" hidden="1">
+    <row r="199">
       <c r="C199" t="inlineStr">
         <is>
           <t>Torne Kagoshima Kenjinkai</t>
@@ -8837,7 +8837,7 @@
         </is>
       </c>
     </row>
-    <row r="200" hidden="1">
+    <row r="200">
       <c r="C200" t="inlineStr">
         <is>
           <t>Torne Kagoshima Kenjinkai</t>
@@ -8881,7 +8881,7 @@
         </is>
       </c>
     </row>
-    <row r="201" hidden="1">
+    <row r="201">
       <c r="C201" t="inlineStr">
         <is>
           <t>Torne Kagoshima Kenjinkai</t>
@@ -8925,7 +8925,7 @@
         </is>
       </c>
     </row>
-    <row r="202" hidden="1">
+    <row r="202">
       <c r="C202" t="inlineStr">
         <is>
           <t>Torneo Kumamoto Kenjinkai</t>
@@ -8964,7 +8964,7 @@
         </is>
       </c>
     </row>
-    <row r="203" hidden="1">
+    <row r="203">
       <c r="C203" t="inlineStr">
         <is>
           <t>Torneo Kumamoto Kenjinkai</t>
@@ -9003,7 +9003,7 @@
         </is>
       </c>
     </row>
-    <row r="204" hidden="1">
+    <row r="204">
       <c r="C204" t="inlineStr">
         <is>
           <t>Torneo Kumamoto Kenjinkai</t>
@@ -9042,7 +9042,7 @@
         </is>
       </c>
     </row>
-    <row r="205" hidden="1">
+    <row r="205">
       <c r="C205" t="inlineStr">
         <is>
           <t>Torneo Kumamoto Kenjinkai</t>
@@ -9081,7 +9081,7 @@
         </is>
       </c>
     </row>
-    <row r="206" hidden="1">
+    <row r="206">
       <c r="C206" t="inlineStr">
         <is>
           <t>Torneo Yamanashi Shimbokukai</t>
@@ -9120,7 +9120,7 @@
         </is>
       </c>
     </row>
-    <row r="207" hidden="1">
+    <row r="207">
       <c r="C207" t="inlineStr">
         <is>
           <t>Torneo Yamanashi Shimbokukai</t>
@@ -9159,7 +9159,7 @@
         </is>
       </c>
     </row>
-    <row r="208" hidden="1">
+    <row r="208">
       <c r="C208" t="inlineStr">
         <is>
           <t>Torneo Yamanashi Shimbokukai</t>
@@ -9198,7 +9198,7 @@
         </is>
       </c>
     </row>
-    <row r="209" hidden="1">
+    <row r="209">
       <c r="C209" t="inlineStr">
         <is>
           <t>Torneo Yamanashi Shimbokukai</t>
@@ -9237,7 +9237,7 @@
         </is>
       </c>
     </row>
-    <row r="210" hidden="1">
+    <row r="210">
       <c r="B210" t="inlineStr">
         <is>
           <t>Campeonato Oficial</t>
@@ -9281,7 +9281,7 @@
         </is>
       </c>
     </row>
-    <row r="211" hidden="1">
+    <row r="211">
       <c r="B211" t="inlineStr">
         <is>
           <t>Campeonato Oficial</t>
@@ -9325,7 +9325,7 @@
         </is>
       </c>
     </row>
-    <row r="212" hidden="1">
+    <row r="212">
       <c r="B212" t="inlineStr">
         <is>
           <t>Campeonato Oficial</t>
@@ -9364,7 +9364,7 @@
         </is>
       </c>
     </row>
-    <row r="213" hidden="1">
+    <row r="213">
       <c r="B213" t="inlineStr">
         <is>
           <t>Campeonato Oficial</t>
@@ -9408,7 +9408,7 @@
         </is>
       </c>
     </row>
-    <row r="214" hidden="1">
+    <row r="214">
       <c r="B214" t="inlineStr">
         <is>
           <t>Campeonato Oficial</t>
@@ -9447,7 +9447,7 @@
         </is>
       </c>
     </row>
-    <row r="215" hidden="1">
+    <row r="215">
       <c r="B215" t="inlineStr">
         <is>
           <t>Campeonato Oficial</t>
@@ -9491,7 +9491,7 @@
         </is>
       </c>
     </row>
-    <row r="216" hidden="1">
+    <row r="216">
       <c r="B216" t="inlineStr">
         <is>
           <t>Campeonato Oficial</t>
@@ -9530,7 +9530,7 @@
         </is>
       </c>
     </row>
-    <row r="217" hidden="1">
+    <row r="217">
       <c r="B217" t="inlineStr">
         <is>
           <t>Campeonato Oficial</t>
@@ -9569,7 +9569,7 @@
         </is>
       </c>
     </row>
-    <row r="218" hidden="1">
+    <row r="218">
       <c r="B218" t="inlineStr">
         <is>
           <t>Campeonato Oficial</t>
@@ -9613,7 +9613,7 @@
         </is>
       </c>
     </row>
-    <row r="219" hidden="1">
+    <row r="219">
       <c r="B219" t="inlineStr">
         <is>
           <t>Campeonato Oficial</t>
@@ -9652,7 +9652,7 @@
         </is>
       </c>
     </row>
-    <row r="220" hidden="1">
+    <row r="220">
       <c r="B220" t="inlineStr">
         <is>
           <t>Campeonato Oficial</t>
@@ -9696,7 +9696,7 @@
         </is>
       </c>
     </row>
-    <row r="221" hidden="1">
+    <row r="221">
       <c r="B221" t="inlineStr">
         <is>
           <t>Campeonato Oficial</t>
@@ -9740,7 +9740,7 @@
         </is>
       </c>
     </row>
-    <row r="222" hidden="1">
+    <row r="222">
       <c r="C222" t="inlineStr">
         <is>
           <t>Torneo Club Aikokai</t>
@@ -9779,7 +9779,7 @@
         </is>
       </c>
     </row>
-    <row r="223" hidden="1">
+    <row r="223">
       <c r="C223" t="inlineStr">
         <is>
           <t>Torneo Club Aikokai</t>
@@ -9818,7 +9818,7 @@
         </is>
       </c>
     </row>
-    <row r="224" hidden="1">
+    <row r="224">
       <c r="C224" t="inlineStr">
         <is>
           <t>Torneo Club Aikokai</t>
@@ -9857,7 +9857,7 @@
         </is>
       </c>
     </row>
-    <row r="225" hidden="1">
+    <row r="225">
       <c r="C225" t="inlineStr">
         <is>
           <t>Torneo Club Aikokai</t>
@@ -9896,7 +9896,7 @@
         </is>
       </c>
     </row>
-    <row r="226" hidden="1">
+    <row r="226">
       <c r="B226" t="inlineStr">
         <is>
           <t>Confraternidad/Integración</t>
@@ -9940,7 +9940,7 @@
         </is>
       </c>
     </row>
-    <row r="227" hidden="1">
+    <row r="227">
       <c r="B227" t="inlineStr">
         <is>
           <t>Confraternidad/Integración</t>
@@ -9984,7 +9984,7 @@
         </is>
       </c>
     </row>
-    <row r="228" hidden="1">
+    <row r="228">
       <c r="C228" t="inlineStr">
         <is>
           <t>Torneo Okinawa Fujinkai</t>
@@ -10023,7 +10023,7 @@
         </is>
       </c>
     </row>
-    <row r="229" hidden="1">
+    <row r="229">
       <c r="C229" t="inlineStr">
         <is>
           <t>Torneo Okinawa Fujinkai</t>
@@ -10062,7 +10062,7 @@
         </is>
       </c>
     </row>
-    <row r="230" hidden="1">
+    <row r="230">
       <c r="C230" t="inlineStr">
         <is>
           <t>Torneo Okinawa Fujinkai</t>
@@ -10101,7 +10101,7 @@
         </is>
       </c>
     </row>
-    <row r="231" hidden="1">
+    <row r="231">
       <c r="C231" t="inlineStr">
         <is>
           <t>Torneo Okinawa Fujinkai</t>
@@ -10140,7 +10140,7 @@
         </is>
       </c>
     </row>
-    <row r="232" hidden="1">
+    <row r="232">
       <c r="C232" t="inlineStr">
         <is>
           <t>Torneo Den Omori</t>
@@ -10184,7 +10184,7 @@
         </is>
       </c>
     </row>
-    <row r="233" hidden="1">
+    <row r="233">
       <c r="C233" t="inlineStr">
         <is>
           <t>Torneo Den Omori</t>
@@ -10228,7 +10228,7 @@
         </is>
       </c>
     </row>
-    <row r="234" hidden="1">
+    <row r="234">
       <c r="C234" t="inlineStr">
         <is>
           <t>Torneo Den Omori</t>
@@ -10272,7 +10272,7 @@
         </is>
       </c>
     </row>
-    <row r="235" hidden="1">
+    <row r="235">
       <c r="C235" t="inlineStr">
         <is>
           <t>Torneo Den Omori</t>
@@ -10316,7 +10316,7 @@
         </is>
       </c>
     </row>
-    <row r="236" hidden="1">
+    <row r="236">
       <c r="B236" t="inlineStr">
         <is>
           <t>SHI-CHO-SON</t>
@@ -10360,7 +10360,7 @@
         </is>
       </c>
     </row>
-    <row r="237" hidden="1">
+    <row r="237">
       <c r="B237" t="inlineStr">
         <is>
           <t>SHI-CHO-SON</t>
@@ -10404,7 +10404,7 @@
         </is>
       </c>
     </row>
-    <row r="238" hidden="1">
+    <row r="238">
       <c r="B238" t="inlineStr">
         <is>
           <t>SHI-CHO-SON</t>
@@ -10448,7 +10448,7 @@
         </is>
       </c>
     </row>
-    <row r="239" hidden="1">
+    <row r="239">
       <c r="B239" t="inlineStr">
         <is>
           <t>SHI-CHO-SON</t>
@@ -10492,7 +10492,7 @@
         </is>
       </c>
     </row>
-    <row r="240" hidden="1">
+    <row r="240">
       <c r="B240" t="inlineStr">
         <is>
           <t>Confraternidad/Integración</t>
@@ -10536,7 +10536,7 @@
         </is>
       </c>
     </row>
-    <row r="241" hidden="1">
+    <row r="241">
       <c r="B241" t="inlineStr">
         <is>
           <t>Confraternidad/Integración</t>
@@ -10580,7 +10580,7 @@
         </is>
       </c>
     </row>
-    <row r="242" hidden="1">
+    <row r="242">
       <c r="B242" t="inlineStr">
         <is>
           <t>Confraternidad/Integración</t>
@@ -10624,7 +10624,7 @@
         </is>
       </c>
     </row>
-    <row r="243" hidden="1">
+    <row r="243">
       <c r="B243" t="inlineStr">
         <is>
           <t>Confraternidad/Integración</t>
@@ -10668,7 +10668,7 @@
         </is>
       </c>
     </row>
-    <row r="244" hidden="1">
+    <row r="244">
       <c r="C244" t="inlineStr">
         <is>
           <t>Torneo AELU</t>
@@ -10712,7 +10712,7 @@
         </is>
       </c>
     </row>
-    <row r="245" hidden="1">
+    <row r="245">
       <c r="C245" t="inlineStr">
         <is>
           <t>Torneo AELU</t>
@@ -10756,7 +10756,7 @@
         </is>
       </c>
     </row>
-    <row r="246" hidden="1">
+    <row r="246">
       <c r="C246" t="inlineStr">
         <is>
           <t>Torneo AELU</t>
@@ -10800,7 +10800,7 @@
         </is>
       </c>
     </row>
-    <row r="247" hidden="1">
+    <row r="247">
       <c r="C247" t="inlineStr">
         <is>
           <t>Torneo AELU</t>
@@ -10844,7 +10844,7 @@
         </is>
       </c>
     </row>
-    <row r="248" hidden="1">
+    <row r="248">
       <c r="C248" t="inlineStr">
         <is>
           <t>Torneo Copa Embajada</t>
@@ -10888,7 +10888,7 @@
         </is>
       </c>
     </row>
-    <row r="249" hidden="1">
+    <row r="249">
       <c r="C249" t="inlineStr">
         <is>
           <t>Torneo Copa Embajada</t>
@@ -10932,7 +10932,7 @@
         </is>
       </c>
     </row>
-    <row r="250" hidden="1">
+    <row r="250">
       <c r="C250" t="inlineStr">
         <is>
           <t>Torneo Copa Embajada</t>
@@ -10976,7 +10976,7 @@
         </is>
       </c>
     </row>
-    <row r="251" hidden="1">
+    <row r="251">
       <c r="C251" t="inlineStr">
         <is>
           <t>Torneo Copa Embajada</t>
@@ -11020,7 +11020,7 @@
         </is>
       </c>
     </row>
-    <row r="252" hidden="1">
+    <row r="252">
       <c r="C252" t="inlineStr">
         <is>
           <t>Torneo Copa Embajada</t>
@@ -11064,7 +11064,7 @@
         </is>
       </c>
     </row>
-    <row r="253" hidden="1">
+    <row r="253">
       <c r="C253" t="inlineStr">
         <is>
           <t>Torneo Copa Embajada</t>
@@ -11108,7 +11108,7 @@
         </is>
       </c>
     </row>
-    <row r="254" hidden="1">
+    <row r="254">
       <c r="B254" t="inlineStr">
         <is>
           <t>Confraternidad/Integración</t>
@@ -11152,7 +11152,7 @@
         </is>
       </c>
     </row>
-    <row r="255" hidden="1">
+    <row r="255">
       <c r="B255" t="inlineStr">
         <is>
           <t>Confraternidad/Integración</t>
@@ -11196,7 +11196,7 @@
         </is>
       </c>
     </row>
-    <row r="256" hidden="1">
+    <row r="256">
       <c r="B256" t="inlineStr">
         <is>
           <t>Confraternidad/Integración</t>
@@ -11240,7 +11240,7 @@
         </is>
       </c>
     </row>
-    <row r="257" hidden="1">
+    <row r="257">
       <c r="B257" t="inlineStr">
         <is>
           <t>Confraternidad/Integración</t>
@@ -11284,7 +11284,7 @@
         </is>
       </c>
     </row>
-    <row r="258" hidden="1">
+    <row r="258">
       <c r="B258" t="inlineStr">
         <is>
           <t>Confraternidad/Integración</t>
@@ -11328,7 +11328,7 @@
         </is>
       </c>
     </row>
-    <row r="259" hidden="1">
+    <row r="259">
       <c r="C259" t="inlineStr">
         <is>
           <t>Torneo AOPCOOP</t>
@@ -11372,7 +11372,7 @@
         </is>
       </c>
     </row>
-    <row r="260" hidden="1">
+    <row r="260">
       <c r="C260" t="inlineStr">
         <is>
           <t>Torneo AOPCOOP</t>
@@ -11416,7 +11416,7 @@
         </is>
       </c>
     </row>
-    <row r="261" hidden="1">
+    <row r="261">
       <c r="C261" t="inlineStr">
         <is>
           <t>Torneo AOPCOOP</t>
@@ -11460,7 +11460,7 @@
         </is>
       </c>
     </row>
-    <row r="262" hidden="1">
+    <row r="262">
       <c r="C262" t="inlineStr">
         <is>
           <t>Torneo AOPCOOP</t>
@@ -11504,7 +11504,7 @@
         </is>
       </c>
     </row>
-    <row r="263" hidden="1">
+    <row r="263">
       <c r="C263" t="inlineStr">
         <is>
           <t>Torneo AOPCOOP</t>
@@ -11548,7 +11548,7 @@
         </is>
       </c>
     </row>
-    <row r="264" hidden="1">
+    <row r="264">
       <c r="C264" t="inlineStr">
         <is>
           <t>Torneo AOPCOOP</t>
@@ -11592,7 +11592,7 @@
         </is>
       </c>
     </row>
-    <row r="265" hidden="1">
+    <row r="265">
       <c r="C265" t="inlineStr">
         <is>
           <t>Torneo AOPCOOP</t>
@@ -11636,7 +11636,7 @@
         </is>
       </c>
     </row>
-    <row r="266" hidden="1">
+    <row r="266">
       <c r="C266" t="inlineStr">
         <is>
           <t>Torneo AOPCOOP</t>
@@ -11680,7 +11680,7 @@
         </is>
       </c>
     </row>
-    <row r="267" hidden="1">
+    <row r="267">
       <c r="B267" t="inlineStr">
         <is>
           <t>Campeonato Oficial</t>
@@ -11724,7 +11724,7 @@
         </is>
       </c>
     </row>
-    <row r="268" hidden="1">
+    <row r="268">
       <c r="B268" t="inlineStr">
         <is>
           <t>Campeonato Oficial</t>
@@ -11768,7 +11768,7 @@
         </is>
       </c>
     </row>
-    <row r="269" hidden="1">
+    <row r="269">
       <c r="B269" t="inlineStr">
         <is>
           <t>Campeonato Oficial</t>
@@ -11812,7 +11812,7 @@
         </is>
       </c>
     </row>
-    <row r="270" hidden="1">
+    <row r="270">
       <c r="B270" t="inlineStr">
         <is>
           <t>Campeonato Oficial</t>
@@ -11856,7 +11856,7 @@
         </is>
       </c>
     </row>
-    <row r="271" hidden="1">
+    <row r="271">
       <c r="B271" t="inlineStr">
         <is>
           <t>Campeonato Oficial</t>
@@ -11900,7 +11900,7 @@
         </is>
       </c>
     </row>
-    <row r="272" hidden="1">
+    <row r="272">
       <c r="B272" t="inlineStr">
         <is>
           <t>Campeonato Oficial</t>
@@ -11944,7 +11944,7 @@
         </is>
       </c>
     </row>
-    <row r="273" hidden="1">
+    <row r="273">
       <c r="B273" t="inlineStr">
         <is>
           <t>Campeonato Oficial</t>
@@ -11988,7 +11988,7 @@
         </is>
       </c>
     </row>
-    <row r="274" hidden="1">
+    <row r="274">
       <c r="B274" t="inlineStr">
         <is>
           <t>Campeonato Oficial</t>
@@ -12032,7 +12032,7 @@
         </is>
       </c>
     </row>
-    <row r="275" hidden="1">
+    <row r="275">
       <c r="B275" t="inlineStr">
         <is>
           <t>Campeonato Oficial</t>
@@ -12076,7 +12076,7 @@
         </is>
       </c>
     </row>
-    <row r="276" hidden="1">
+    <row r="276">
       <c r="B276" t="inlineStr">
         <is>
           <t>Campeonato Oficial</t>
@@ -12120,7 +12120,7 @@
         </is>
       </c>
     </row>
-    <row r="277" hidden="1">
+    <row r="277">
       <c r="B277" t="inlineStr">
         <is>
           <t>Campeonato Oficial</t>
@@ -12164,7 +12164,7 @@
         </is>
       </c>
     </row>
-    <row r="278" hidden="1">
+    <row r="278">
       <c r="B278" t="inlineStr">
         <is>
           <t>Campeonato Oficial</t>
@@ -12208,7 +12208,7 @@
         </is>
       </c>
     </row>
-    <row r="279" hidden="1">
+    <row r="279">
       <c r="C279" t="inlineStr">
         <is>
           <t>Torneo Okinawa Kenjinkai</t>
@@ -12252,7 +12252,7 @@
         </is>
       </c>
     </row>
-    <row r="280" hidden="1">
+    <row r="280">
       <c r="C280" t="inlineStr">
         <is>
           <t>Torneo Okinawa Kenjinkai</t>
@@ -12296,7 +12296,7 @@
         </is>
       </c>
     </row>
-    <row r="281" hidden="1">
+    <row r="281">
       <c r="C281" t="inlineStr">
         <is>
           <t>Torneo Okinawa Kenjinkai</t>
@@ -12340,7 +12340,7 @@
         </is>
       </c>
     </row>
-    <row r="282" hidden="1">
+    <row r="282">
       <c r="C282" t="inlineStr">
         <is>
           <t>Torneo Okinawa Kenjinkai</t>
@@ -12384,7 +12384,7 @@
         </is>
       </c>
     </row>
-    <row r="283" hidden="1">
+    <row r="283">
       <c r="C283" t="inlineStr">
         <is>
           <t>Torneo Okinawa Kenjinkai</t>
@@ -12428,7 +12428,7 @@
         </is>
       </c>
     </row>
-    <row r="284" hidden="1">
+    <row r="284">
       <c r="C284" t="inlineStr">
         <is>
           <t>Torneo Okinawa Kenjinkai</t>
@@ -12472,7 +12472,7 @@
         </is>
       </c>
     </row>
-    <row r="285" hidden="1">
+    <row r="285">
       <c r="C285" t="inlineStr">
         <is>
           <t>Torneo Okinawa Kenjinkai</t>
@@ -12516,7 +12516,7 @@
         </is>
       </c>
     </row>
-    <row r="286" hidden="1">
+    <row r="286">
       <c r="C286" t="inlineStr">
         <is>
           <t>Torneo Okinawa Kenjinkai</t>
@@ -12952,7 +12952,7 @@
         </is>
       </c>
     </row>
-    <row r="295" hidden="1">
+    <row r="295">
       <c r="C295" t="inlineStr">
         <is>
           <t>Torneo Nikkei Fujinkai</t>
@@ -12996,7 +12996,7 @@
         </is>
       </c>
     </row>
-    <row r="296" hidden="1">
+    <row r="296">
       <c r="C296" t="inlineStr">
         <is>
           <t>Torneo Nikkei Fujinkai</t>
@@ -13040,7 +13040,7 @@
         </is>
       </c>
     </row>
-    <row r="297" hidden="1">
+    <row r="297">
       <c r="C297" t="inlineStr">
         <is>
           <t>Torneo Nikkei Fujinkai</t>
@@ -13084,7 +13084,7 @@
         </is>
       </c>
     </row>
-    <row r="298" hidden="1">
+    <row r="298">
       <c r="C298" t="inlineStr">
         <is>
           <t>Torneo Nikkei Fujinkai</t>
@@ -13128,7 +13128,7 @@
         </is>
       </c>
     </row>
-    <row r="299" hidden="1">
+    <row r="299">
       <c r="C299" t="inlineStr">
         <is>
           <t>Torneo Kumamoto Kenjinkai</t>
@@ -13172,7 +13172,7 @@
         </is>
       </c>
     </row>
-    <row r="300" hidden="1">
+    <row r="300">
       <c r="C300" t="inlineStr">
         <is>
           <t>Torneo Kumamoto Kenjinkai</t>
@@ -13216,7 +13216,7 @@
         </is>
       </c>
     </row>
-    <row r="301" hidden="1">
+    <row r="301">
       <c r="C301" t="inlineStr">
         <is>
           <t>Torneo Kumamoto Kenjinkai</t>
@@ -13260,7 +13260,7 @@
         </is>
       </c>
     </row>
-    <row r="302" hidden="1">
+    <row r="302">
       <c r="C302" t="inlineStr">
         <is>
           <t>Torneo Kumamoto Kenjinkai</t>
@@ -13304,7 +13304,7 @@
         </is>
       </c>
     </row>
-    <row r="303" hidden="1">
+    <row r="303">
       <c r="C303" t="inlineStr">
         <is>
           <t>Torneo Yamanashi Shimbokukai</t>
@@ -13348,7 +13348,7 @@
         </is>
       </c>
     </row>
-    <row r="304" hidden="1">
+    <row r="304">
       <c r="C304" t="inlineStr">
         <is>
           <t>Torneo Yamanashi Shimbokukai</t>
@@ -13392,7 +13392,7 @@
         </is>
       </c>
     </row>
-    <row r="305" hidden="1">
+    <row r="305">
       <c r="C305" t="inlineStr">
         <is>
           <t>Torneo Yamanashi Shimbokukai</t>
@@ -13436,7 +13436,7 @@
         </is>
       </c>
     </row>
-    <row r="306" hidden="1">
+    <row r="306">
       <c r="C306" t="inlineStr">
         <is>
           <t>Torneo Yamanashi Shimbokukai</t>
@@ -13480,7 +13480,7 @@
         </is>
       </c>
     </row>
-    <row r="307" hidden="1">
+    <row r="307">
       <c r="B307" t="inlineStr">
         <is>
           <t>Campeonato Oficial</t>
@@ -13524,7 +13524,7 @@
         </is>
       </c>
     </row>
-    <row r="308" hidden="1">
+    <row r="308">
       <c r="B308" t="inlineStr">
         <is>
           <t>Campeonato Oficial</t>
@@ -13568,7 +13568,7 @@
         </is>
       </c>
     </row>
-    <row r="309" hidden="1">
+    <row r="309">
       <c r="B309" t="inlineStr">
         <is>
           <t>Campeonato Oficial</t>
@@ -13612,7 +13612,7 @@
         </is>
       </c>
     </row>
-    <row r="310" hidden="1">
+    <row r="310">
       <c r="B310" t="inlineStr">
         <is>
           <t>Campeonato Oficial</t>
@@ -13656,7 +13656,7 @@
         </is>
       </c>
     </row>
-    <row r="311" hidden="1">
+    <row r="311">
       <c r="B311" t="inlineStr">
         <is>
           <t>Campeonato Oficial</t>
@@ -13700,7 +13700,7 @@
         </is>
       </c>
     </row>
-    <row r="312" hidden="1">
+    <row r="312">
       <c r="B312" t="inlineStr">
         <is>
           <t>Campeonato Oficial</t>
@@ -13744,7 +13744,7 @@
         </is>
       </c>
     </row>
-    <row r="313" hidden="1">
+    <row r="313">
       <c r="B313" t="inlineStr">
         <is>
           <t>Campeonato Oficial</t>
@@ -13788,7 +13788,7 @@
         </is>
       </c>
     </row>
-    <row r="314" hidden="1">
+    <row r="314">
       <c r="B314" t="inlineStr">
         <is>
           <t>Campeonato Oficial</t>
@@ -13832,7 +13832,7 @@
         </is>
       </c>
     </row>
-    <row r="315" hidden="1">
+    <row r="315">
       <c r="B315" t="inlineStr">
         <is>
           <t>Campeonato Oficial</t>
@@ -13876,7 +13876,7 @@
         </is>
       </c>
     </row>
-    <row r="316" hidden="1">
+    <row r="316">
       <c r="B316" t="inlineStr">
         <is>
           <t>Campeonato Oficial</t>
@@ -13920,7 +13920,7 @@
         </is>
       </c>
     </row>
-    <row r="317" hidden="1">
+    <row r="317">
       <c r="B317" t="inlineStr">
         <is>
           <t>Campeonato Oficial</t>
@@ -13964,7 +13964,7 @@
         </is>
       </c>
     </row>
-    <row r="318" hidden="1">
+    <row r="318">
       <c r="B318" t="inlineStr">
         <is>
           <t>Campeonato Oficial</t>
@@ -14008,7 +14008,7 @@
         </is>
       </c>
     </row>
-    <row r="319" hidden="1">
+    <row r="319">
       <c r="C319" t="inlineStr">
         <is>
           <t>Torneo Club Aikokai</t>
@@ -14052,7 +14052,7 @@
         </is>
       </c>
     </row>
-    <row r="320" hidden="1">
+    <row r="320">
       <c r="C320" t="inlineStr">
         <is>
           <t>Torneo Club Aikokai</t>
@@ -14096,7 +14096,7 @@
         </is>
       </c>
     </row>
-    <row r="321" hidden="1">
+    <row r="321">
       <c r="C321" t="inlineStr">
         <is>
           <t>Torneo Club Aikokai</t>
@@ -14140,7 +14140,7 @@
         </is>
       </c>
     </row>
-    <row r="322" hidden="1">
+    <row r="322">
       <c r="C322" t="inlineStr">
         <is>
           <t>Torneo Club Aikokai</t>
@@ -14184,7 +14184,7 @@
         </is>
       </c>
     </row>
-    <row r="323" hidden="1">
+    <row r="323">
       <c r="C323" t="inlineStr">
         <is>
           <t>Torneo APG</t>
@@ -14233,7 +14233,7 @@
         </is>
       </c>
     </row>
-    <row r="324" hidden="1">
+    <row r="324">
       <c r="C324" t="inlineStr">
         <is>
           <t>Torneo APG</t>
@@ -14277,7 +14277,7 @@
         </is>
       </c>
     </row>
-    <row r="325" hidden="1">
+    <row r="325">
       <c r="C325" t="inlineStr">
         <is>
           <t>Torneo APG</t>
@@ -14326,7 +14326,7 @@
         </is>
       </c>
     </row>
-    <row r="326" hidden="1">
+    <row r="326">
       <c r="C326" t="inlineStr">
         <is>
           <t>Torneo APG</t>
@@ -14370,7 +14370,7 @@
         </is>
       </c>
     </row>
-    <row r="327" hidden="1">
+    <row r="327">
       <c r="C327" t="inlineStr">
         <is>
           <t>Torneo APG</t>
@@ -14419,7 +14419,7 @@
         </is>
       </c>
     </row>
-    <row r="328" hidden="1">
+    <row r="328">
       <c r="C328" t="inlineStr">
         <is>
           <t>Torneo APG</t>
@@ -14468,7 +14468,7 @@
         </is>
       </c>
     </row>
-    <row r="329" hidden="1">
+    <row r="329">
       <c r="C329" t="inlineStr">
         <is>
           <t>Torneo APG</t>
@@ -14517,7 +14517,7 @@
         </is>
       </c>
     </row>
-    <row r="330" hidden="1">
+    <row r="330">
       <c r="C330" t="inlineStr">
         <is>
           <t>Torneo APG</t>
@@ -14561,7 +14561,7 @@
         </is>
       </c>
     </row>
-    <row r="331" hidden="1">
+    <row r="331">
       <c r="B331" t="inlineStr">
         <is>
           <t>Campeonato Internacional</t>
@@ -14615,7 +14615,7 @@
         </is>
       </c>
     </row>
-    <row r="332" hidden="1">
+    <row r="332">
       <c r="B332" t="inlineStr">
         <is>
           <t>Campeonato Internacional</t>
@@ -14669,7 +14669,7 @@
         </is>
       </c>
     </row>
-    <row r="333" hidden="1">
+    <row r="333">
       <c r="B333" t="inlineStr">
         <is>
           <t>Campeonato Internacional</t>
@@ -14718,7 +14718,7 @@
         </is>
       </c>
     </row>
-    <row r="334" hidden="1">
+    <row r="334">
       <c r="B334" t="inlineStr">
         <is>
           <t>Campeonato Internacional</t>
@@ -14772,7 +14772,7 @@
         </is>
       </c>
     </row>
-    <row r="335" hidden="1">
+    <row r="335">
       <c r="B335" t="inlineStr">
         <is>
           <t>Campeonato Internacional</t>
@@ -14826,7 +14826,7 @@
         </is>
       </c>
     </row>
-    <row r="336" hidden="1">
+    <row r="336">
       <c r="B336" t="inlineStr">
         <is>
           <t>Campeonato Internacional</t>
@@ -14880,7 +14880,7 @@
         </is>
       </c>
     </row>
-    <row r="337" hidden="1">
+    <row r="337">
       <c r="B337" t="inlineStr">
         <is>
           <t>Campeonato Internacional</t>
@@ -14929,7 +14929,7 @@
         </is>
       </c>
     </row>
-    <row r="338" hidden="1">
+    <row r="338">
       <c r="B338" t="inlineStr">
         <is>
           <t>Campeonato Internacional</t>
@@ -14969,7 +14969,7 @@
       </c>
       <c r="L338" t="inlineStr">
         <is>
-          <t>Nakasone Juan, Kanashiro Carlos, Arakaki Bryan, Miyasato Andrés, Higa Ricardo y Vidal Alfredo</t>
+          <t>Nakasone Juan, Kanashiro Gabo, Arakaki Bryan, Miyasato Andrés, Higa Ricardo y Vidal Alfredo</t>
         </is>
       </c>
       <c r="M338" t="inlineStr">
@@ -14978,7 +14978,7 @@
         </is>
       </c>
     </row>
-    <row r="339" hidden="1">
+    <row r="339">
       <c r="C339" t="inlineStr">
         <is>
           <t>Torneo Okinawa Fujinkai</t>
@@ -15022,7 +15022,7 @@
         </is>
       </c>
     </row>
-    <row r="340" hidden="1">
+    <row r="340">
       <c r="C340" t="inlineStr">
         <is>
           <t>Torneo Okinawa Fujinkai</t>
@@ -15066,7 +15066,7 @@
         </is>
       </c>
     </row>
-    <row r="341" hidden="1">
+    <row r="341">
       <c r="C341" t="inlineStr">
         <is>
           <t>Torneo Okinawa Fujinkai</t>
@@ -15110,7 +15110,7 @@
         </is>
       </c>
     </row>
-    <row r="342" hidden="1">
+    <row r="342">
       <c r="C342" t="inlineStr">
         <is>
           <t>Torneo Okinawa Fujinkai</t>
@@ -15154,7 +15154,7 @@
         </is>
       </c>
     </row>
-    <row r="343" hidden="1">
+    <row r="343">
       <c r="B343" t="inlineStr">
         <is>
           <t>SHI-CHO-SON</t>
@@ -15198,7 +15198,7 @@
         </is>
       </c>
     </row>
-    <row r="344" hidden="1">
+    <row r="344">
       <c r="B344" t="inlineStr">
         <is>
           <t>SHI-CHO-SON</t>
@@ -15242,7 +15242,7 @@
         </is>
       </c>
     </row>
-    <row r="345" hidden="1">
+    <row r="345">
       <c r="B345" t="inlineStr">
         <is>
           <t>SHI-CHO-SON</t>
@@ -15286,7 +15286,7 @@
         </is>
       </c>
     </row>
-    <row r="346" hidden="1">
+    <row r="346">
       <c r="B346" t="inlineStr">
         <is>
           <t>SHI-CHO-SON</t>
@@ -15330,7 +15330,7 @@
         </is>
       </c>
     </row>
-    <row r="347" hidden="1">
+    <row r="347">
       <c r="C347" t="inlineStr">
         <is>
           <t>Torneo APG</t>
@@ -15374,7 +15374,7 @@
         </is>
       </c>
     </row>
-    <row r="348" hidden="1">
+    <row r="348">
       <c r="C348" t="inlineStr">
         <is>
           <t>Torneo APG</t>
@@ -15418,7 +15418,7 @@
         </is>
       </c>
     </row>
-    <row r="349" hidden="1">
+    <row r="349">
       <c r="C349" t="inlineStr">
         <is>
           <t>Torneo APG</t>
@@ -15462,7 +15462,7 @@
         </is>
       </c>
     </row>
-    <row r="350" hidden="1">
+    <row r="350">
       <c r="C350" t="inlineStr">
         <is>
           <t>Torneo APG</t>
@@ -15506,7 +15506,7 @@
         </is>
       </c>
     </row>
-    <row r="351" hidden="1">
+    <row r="351">
       <c r="C351" t="inlineStr">
         <is>
           <t>Torneo APG</t>
@@ -15550,7 +15550,7 @@
         </is>
       </c>
     </row>
-    <row r="352" hidden="1">
+    <row r="352">
       <c r="C352" t="inlineStr">
         <is>
           <t>Torneo APG</t>
@@ -15594,7 +15594,7 @@
         </is>
       </c>
     </row>
-    <row r="353" hidden="1">
+    <row r="353">
       <c r="C353" t="inlineStr">
         <is>
           <t>Torneo APG</t>
@@ -15638,7 +15638,7 @@
         </is>
       </c>
     </row>
-    <row r="354" hidden="1">
+    <row r="354">
       <c r="C354" t="inlineStr">
         <is>
           <t>Torneo APG</t>
@@ -15682,7 +15682,7 @@
         </is>
       </c>
     </row>
-    <row r="355" hidden="1">
+    <row r="355">
       <c r="C355" t="inlineStr">
         <is>
           <t>Torneo Leoncio Prado</t>
@@ -15726,7 +15726,7 @@
         </is>
       </c>
     </row>
-    <row r="356" hidden="1">
+    <row r="356">
       <c r="C356" t="inlineStr">
         <is>
           <t>Torneo Leoncio Prado</t>
@@ -15770,7 +15770,7 @@
         </is>
       </c>
     </row>
-    <row r="357" hidden="1">
+    <row r="357">
       <c r="C357" t="inlineStr">
         <is>
           <t>Torneo Leoncio Prado</t>
@@ -15814,7 +15814,7 @@
         </is>
       </c>
     </row>
-    <row r="358" hidden="1">
+    <row r="358">
       <c r="C358" t="inlineStr">
         <is>
           <t>Torneo Leoncio Prado</t>
@@ -16034,7 +16034,7 @@
         </is>
       </c>
     </row>
-    <row r="363" hidden="1">
+    <row r="363">
       <c r="C363" t="inlineStr">
         <is>
           <t>Torneo AELU</t>
@@ -16078,7 +16078,7 @@
         </is>
       </c>
     </row>
-    <row r="364" hidden="1">
+    <row r="364">
       <c r="C364" t="inlineStr">
         <is>
           <t>Torneo AELU</t>
@@ -16122,7 +16122,7 @@
         </is>
       </c>
     </row>
-    <row r="365" hidden="1">
+    <row r="365">
       <c r="C365" t="inlineStr">
         <is>
           <t>Torneo AELU</t>
@@ -16166,7 +16166,7 @@
         </is>
       </c>
     </row>
-    <row r="366" hidden="1">
+    <row r="366">
       <c r="C366" t="inlineStr">
         <is>
           <t>Torneo AELU</t>
@@ -16210,7 +16210,7 @@
         </is>
       </c>
     </row>
-    <row r="367" hidden="1">
+    <row r="367">
       <c r="C367" t="inlineStr">
         <is>
           <t>Torneo Copa Embajada</t>
@@ -16254,7 +16254,7 @@
         </is>
       </c>
     </row>
-    <row r="368" hidden="1">
+    <row r="368">
       <c r="C368" t="inlineStr">
         <is>
           <t>Torneo Copa Embajada</t>
@@ -16298,7 +16298,7 @@
         </is>
       </c>
     </row>
-    <row r="369" hidden="1">
+    <row r="369">
       <c r="C369" t="inlineStr">
         <is>
           <t>Torneo Copa Embajada</t>
@@ -16342,7 +16342,7 @@
         </is>
       </c>
     </row>
-    <row r="370" hidden="1">
+    <row r="370">
       <c r="C370" t="inlineStr">
         <is>
           <t>Torneo Copa Embajada</t>
@@ -16386,7 +16386,7 @@
         </is>
       </c>
     </row>
-    <row r="371" hidden="1">
+    <row r="371">
       <c r="C371" t="inlineStr">
         <is>
           <t>Torneo Copa Embajada</t>
@@ -16430,7 +16430,7 @@
         </is>
       </c>
     </row>
-    <row r="372" hidden="1">
+    <row r="372">
       <c r="C372" t="inlineStr">
         <is>
           <t>Torneo Copa Embajada</t>
@@ -16474,7 +16474,7 @@
         </is>
       </c>
     </row>
-    <row r="373" hidden="1">
+    <row r="373">
       <c r="C373" t="inlineStr">
         <is>
           <t>Torneo AOPCOOP</t>
@@ -16518,7 +16518,7 @@
         </is>
       </c>
     </row>
-    <row r="374" hidden="1">
+    <row r="374">
       <c r="C374" t="inlineStr">
         <is>
           <t>Torneo AOPCOOP</t>
@@ -16562,7 +16562,7 @@
         </is>
       </c>
     </row>
-    <row r="375" hidden="1">
+    <row r="375">
       <c r="C375" t="inlineStr">
         <is>
           <t>Torneo AOPCOOP</t>
@@ -16606,7 +16606,7 @@
         </is>
       </c>
     </row>
-    <row r="376" hidden="1">
+    <row r="376">
       <c r="C376" t="inlineStr">
         <is>
           <t>Torneo AOPCOOP</t>
@@ -16650,7 +16650,7 @@
         </is>
       </c>
     </row>
-    <row r="377" hidden="1">
+    <row r="377">
       <c r="C377" t="inlineStr">
         <is>
           <t>Torneo ABACO</t>
@@ -16694,7 +16694,7 @@
         </is>
       </c>
     </row>
-    <row r="378" hidden="1">
+    <row r="378">
       <c r="C378" t="inlineStr">
         <is>
           <t>Torneo ABACO</t>
@@ -16738,7 +16738,7 @@
         </is>
       </c>
     </row>
-    <row r="379" hidden="1">
+    <row r="379">
       <c r="C379" t="inlineStr">
         <is>
           <t>Torneo ABACO</t>
@@ -16782,7 +16782,7 @@
         </is>
       </c>
     </row>
-    <row r="380" hidden="1">
+    <row r="380">
       <c r="C380" t="inlineStr">
         <is>
           <t>Torneo ABACO</t>
@@ -16817,7 +16817,7 @@
       </c>
       <c r="L380" t="inlineStr">
         <is>
-          <t>Alfredo Vidal, Carlos Kanashiro, Bryan Arakaki, Andrés Miyasato, Hiko Nakasone, Rubén Sugano y José Kanashiro</t>
+          <t>Alfredo Vidal, Gabo Kanashiro, Bryan Arakaki, Andrés Miyasato, Hiko Nakasone, Rubén Sugano y José Kanashiro</t>
         </is>
       </c>
       <c r="M380" t="inlineStr">
@@ -16826,7 +16826,7 @@
         </is>
       </c>
     </row>
-    <row r="381" hidden="1">
+    <row r="381">
       <c r="C381" t="inlineStr">
         <is>
           <t>Torneo Okinawa Kenjinkai</t>
@@ -16870,7 +16870,7 @@
         </is>
       </c>
     </row>
-    <row r="382" hidden="1">
+    <row r="382">
       <c r="C382" t="inlineStr">
         <is>
           <t>Torneo Okinawa Kenjinkai</t>
@@ -16914,7 +16914,7 @@
         </is>
       </c>
     </row>
-    <row r="383" hidden="1">
+    <row r="383">
       <c r="C383" t="inlineStr">
         <is>
           <t>Torneo Okinawa Kenjinkai</t>
@@ -16958,7 +16958,7 @@
         </is>
       </c>
     </row>
-    <row r="384" hidden="1">
+    <row r="384">
       <c r="C384" t="inlineStr">
         <is>
           <t>Torneo Okinawa Kenjinkai</t>
@@ -17002,7 +17002,7 @@
         </is>
       </c>
     </row>
-    <row r="385" hidden="1">
+    <row r="385">
       <c r="C385" t="inlineStr">
         <is>
           <t>Torneo Okinawa Kenjinkai</t>
@@ -17046,7 +17046,7 @@
         </is>
       </c>
     </row>
-    <row r="386" hidden="1">
+    <row r="386">
       <c r="C386" t="inlineStr">
         <is>
           <t>Torneo Okinawa Kenjinkai</t>
@@ -17090,7 +17090,7 @@
         </is>
       </c>
     </row>
-    <row r="387" hidden="1">
+    <row r="387">
       <c r="C387" t="inlineStr">
         <is>
           <t>Torneo Okinawa Kenjinkai</t>
@@ -17134,7 +17134,7 @@
         </is>
       </c>
     </row>
-    <row r="388" hidden="1">
+    <row r="388">
       <c r="C388" t="inlineStr">
         <is>
           <t>Torneo Okinawa Kenjinkai</t>
@@ -17169,7 +17169,7 @@
       </c>
       <c r="L388" t="inlineStr">
         <is>
-          <t>José Kanashiro, Bryan Arakaki, Andrés Miyasato, Rubén Sugano y Carlos Kanashiro</t>
+          <t>José Kanashiro, Bryan Arakaki, Andrés Miyasato, Rubén Sugano y Gabo Kanashiro</t>
         </is>
       </c>
       <c r="M388" t="inlineStr">
@@ -17178,7 +17178,7 @@
         </is>
       </c>
     </row>
-    <row r="389" hidden="1">
+    <row r="389">
       <c r="B389" t="inlineStr">
         <is>
           <t>Campeonato Oficial</t>
@@ -17222,7 +17222,7 @@
         </is>
       </c>
     </row>
-    <row r="390" hidden="1">
+    <row r="390">
       <c r="B390" t="inlineStr">
         <is>
           <t>Campeonato Oficial</t>
@@ -17266,7 +17266,7 @@
         </is>
       </c>
     </row>
-    <row r="391" hidden="1">
+    <row r="391">
       <c r="B391" t="inlineStr">
         <is>
           <t>Campeonato Oficial</t>
@@ -17310,7 +17310,7 @@
         </is>
       </c>
     </row>
-    <row r="392" hidden="1">
+    <row r="392">
       <c r="B392" t="inlineStr">
         <is>
           <t>Campeonato Oficial</t>
@@ -17354,7 +17354,7 @@
         </is>
       </c>
     </row>
-    <row r="393" hidden="1">
+    <row r="393">
       <c r="B393" t="inlineStr">
         <is>
           <t>Campeonato Oficial</t>
@@ -17398,7 +17398,7 @@
         </is>
       </c>
     </row>
-    <row r="394" hidden="1">
+    <row r="394">
       <c r="B394" t="inlineStr">
         <is>
           <t>Campeonato Oficial</t>
@@ -17442,7 +17442,7 @@
         </is>
       </c>
     </row>
-    <row r="395" hidden="1">
+    <row r="395">
       <c r="B395" t="inlineStr">
         <is>
           <t>Campeonato Oficial</t>
@@ -17486,7 +17486,7 @@
         </is>
       </c>
     </row>
-    <row r="396" hidden="1">
+    <row r="396">
       <c r="B396" t="inlineStr">
         <is>
           <t>Campeonato Oficial</t>
@@ -17530,7 +17530,7 @@
         </is>
       </c>
     </row>
-    <row r="397" hidden="1">
+    <row r="397">
       <c r="B397" t="inlineStr">
         <is>
           <t>Campeonato Oficial</t>
@@ -17574,7 +17574,7 @@
         </is>
       </c>
     </row>
-    <row r="398" hidden="1">
+    <row r="398">
       <c r="B398" t="inlineStr">
         <is>
           <t>Campeonato Oficial</t>
@@ -17618,7 +17618,7 @@
         </is>
       </c>
     </row>
-    <row r="399" hidden="1">
+    <row r="399">
       <c r="B399" t="inlineStr">
         <is>
           <t>Campeonato Oficial</t>
@@ -17662,7 +17662,7 @@
         </is>
       </c>
     </row>
-    <row r="400" hidden="1">
+    <row r="400">
       <c r="B400" t="inlineStr">
         <is>
           <t>Campeonato Oficial</t>
@@ -17706,7 +17706,7 @@
         </is>
       </c>
     </row>
-    <row r="401" hidden="1">
+    <row r="401">
       <c r="C401" t="inlineStr">
         <is>
           <t>Torneo Nikkei Fujinkai</t>
@@ -17750,7 +17750,7 @@
         </is>
       </c>
     </row>
-    <row r="402" hidden="1">
+    <row r="402">
       <c r="C402" t="inlineStr">
         <is>
           <t>Torneo Nikkei Fujinkai</t>
@@ -17794,7 +17794,7 @@
         </is>
       </c>
     </row>
-    <row r="403" hidden="1">
+    <row r="403">
       <c r="C403" t="inlineStr">
         <is>
           <t>Torneo Nikkei Fujinkai</t>
@@ -17838,7 +17838,7 @@
         </is>
       </c>
     </row>
-    <row r="404" hidden="1">
+    <row r="404">
       <c r="C404" t="inlineStr">
         <is>
           <t>Torneo Nikkei Fujinkai</t>
@@ -17882,7 +17882,7 @@
         </is>
       </c>
     </row>
-    <row r="405" hidden="1">
+    <row r="405">
       <c r="C405" t="inlineStr">
         <is>
           <t>Torneo Kumamoto Kenjinkai</t>
@@ -17926,7 +17926,7 @@
         </is>
       </c>
     </row>
-    <row r="406" hidden="1">
+    <row r="406">
       <c r="C406" t="inlineStr">
         <is>
           <t>Torneo Kumamoto Kenjinkai</t>
@@ -17970,7 +17970,7 @@
         </is>
       </c>
     </row>
-    <row r="407" hidden="1">
+    <row r="407">
       <c r="C407" t="inlineStr">
         <is>
           <t>Torneo Kumamoto Kenjinkai</t>
@@ -18014,7 +18014,7 @@
         </is>
       </c>
     </row>
-    <row r="408" hidden="1">
+    <row r="408">
       <c r="C408" t="inlineStr">
         <is>
           <t>Torneo Kumamoto Kenjinkai</t>
@@ -18058,7 +18058,7 @@
         </is>
       </c>
     </row>
-    <row r="409" hidden="1">
+    <row r="409">
       <c r="B409" t="inlineStr">
         <is>
           <t>Campeonato Oficial</t>
@@ -18102,7 +18102,7 @@
         </is>
       </c>
     </row>
-    <row r="410" hidden="1">
+    <row r="410">
       <c r="B410" t="inlineStr">
         <is>
           <t>Campeonato Oficial</t>
@@ -18137,7 +18137,7 @@
       </c>
       <c r="L410" t="inlineStr">
         <is>
-          <t>Oshiro Yoneko, Tamashiro Sachiko, Salazar Kimi, Ginoza Sumiko, Shimabukuro Mistuko y Yoza Mitsue</t>
+          <t>Oshiro Yoneko, Tamashiro Sachiko, Salazar Kimi, Ginoza Sumiko, Shimabukuro Mitsuko y Yoza Mitsue</t>
         </is>
       </c>
       <c r="M410" t="inlineStr">
@@ -18146,7 +18146,7 @@
         </is>
       </c>
     </row>
-    <row r="411" hidden="1">
+    <row r="411">
       <c r="B411" t="inlineStr">
         <is>
           <t>Campeonato Oficial</t>
@@ -18190,7 +18190,7 @@
         </is>
       </c>
     </row>
-    <row r="412" hidden="1">
+    <row r="412">
       <c r="B412" t="inlineStr">
         <is>
           <t>Campeonato Oficial</t>
@@ -18234,7 +18234,7 @@
         </is>
       </c>
     </row>
-    <row r="413" hidden="1">
+    <row r="413">
       <c r="B413" t="inlineStr">
         <is>
           <t>Campeonato Oficial</t>
@@ -18278,7 +18278,7 @@
         </is>
       </c>
     </row>
-    <row r="414" hidden="1">
+    <row r="414">
       <c r="B414" t="inlineStr">
         <is>
           <t>Campeonato Oficial</t>
@@ -18322,7 +18322,7 @@
         </is>
       </c>
     </row>
-    <row r="415" hidden="1">
+    <row r="415">
       <c r="B415" t="inlineStr">
         <is>
           <t>Campeonato Oficial</t>
@@ -18366,7 +18366,7 @@
         </is>
       </c>
     </row>
-    <row r="416" hidden="1">
+    <row r="416">
       <c r="B416" t="inlineStr">
         <is>
           <t>Campeonato Oficial</t>
@@ -18410,7 +18410,7 @@
         </is>
       </c>
     </row>
-    <row r="417" hidden="1">
+    <row r="417">
       <c r="B417" t="inlineStr">
         <is>
           <t>Campeonato Oficial</t>
@@ -18454,7 +18454,7 @@
         </is>
       </c>
     </row>
-    <row r="418" hidden="1">
+    <row r="418">
       <c r="B418" t="inlineStr">
         <is>
           <t>Campeonato Oficial</t>
@@ -18498,7 +18498,7 @@
         </is>
       </c>
     </row>
-    <row r="419" hidden="1">
+    <row r="419">
       <c r="B419" t="inlineStr">
         <is>
           <t>Campeonato Oficial</t>
@@ -18542,7 +18542,7 @@
         </is>
       </c>
     </row>
-    <row r="420" hidden="1">
+    <row r="420">
       <c r="B420" t="inlineStr">
         <is>
           <t>Campeonato Oficial</t>
@@ -18577,7 +18577,7 @@
       </c>
       <c r="L420" t="inlineStr">
         <is>
-          <t>Nakasone Hiko, Miyasato Andrés, Sugano Rubén, Vidal Alfredo, Kanashiro José, Arakaki Bryan y Kanashiro Carlos</t>
+          <t>Nakasone Hiko, Miyasato Andrés, Sugano Rubén, Vidal Alfredo, Kanashiro José, Arakaki Bryan y Kanashiro Gabo</t>
         </is>
       </c>
       <c r="M420" t="inlineStr">
@@ -18586,7 +18586,7 @@
         </is>
       </c>
     </row>
-    <row r="421" hidden="1">
+    <row r="421">
       <c r="C421" t="inlineStr">
         <is>
           <t>Torneo Sakura</t>
@@ -18630,7 +18630,7 @@
         </is>
       </c>
     </row>
-    <row r="422" hidden="1">
+    <row r="422">
       <c r="C422" t="inlineStr">
         <is>
           <t>Torneo Sakura</t>
@@ -18674,7 +18674,7 @@
         </is>
       </c>
     </row>
-    <row r="423" hidden="1">
+    <row r="423">
       <c r="C423" t="inlineStr">
         <is>
           <t>Torneo Sakura</t>
@@ -18718,7 +18718,7 @@
         </is>
       </c>
     </row>
-    <row r="424" hidden="1">
+    <row r="424">
       <c r="C424" t="inlineStr">
         <is>
           <t>Torneo Sakura</t>
@@ -18762,7 +18762,7 @@
         </is>
       </c>
     </row>
-    <row r="425" hidden="1">
+    <row r="425">
       <c r="C425" t="inlineStr">
         <is>
           <t>Torneo Club Aikokai</t>
@@ -18806,7 +18806,7 @@
         </is>
       </c>
     </row>
-    <row r="426" hidden="1">
+    <row r="426">
       <c r="C426" t="inlineStr">
         <is>
           <t>Torneo Club Aikokai</t>
@@ -18850,7 +18850,7 @@
         </is>
       </c>
     </row>
-    <row r="427" hidden="1">
+    <row r="427">
       <c r="C427" t="inlineStr">
         <is>
           <t>Torneo Club Aikokai</t>
@@ -18894,7 +18894,7 @@
         </is>
       </c>
     </row>
-    <row r="428" hidden="1">
+    <row r="428">
       <c r="C428" t="inlineStr">
         <is>
           <t>Torneo Club Aikokai</t>
@@ -18938,7 +18938,7 @@
         </is>
       </c>
     </row>
-    <row r="429" hidden="1">
+    <row r="429">
       <c r="C429" t="inlineStr">
         <is>
           <t>Torneo Okinawa Fujinkai</t>
@@ -18982,7 +18982,7 @@
         </is>
       </c>
     </row>
-    <row r="430" hidden="1">
+    <row r="430">
       <c r="C430" t="inlineStr">
         <is>
           <t>Torneo Okinawa Fujinkai</t>
@@ -19026,7 +19026,7 @@
         </is>
       </c>
     </row>
-    <row r="431" hidden="1">
+    <row r="431">
       <c r="C431" t="inlineStr">
         <is>
           <t>Torneo Okinawa Fujinkai</t>
@@ -19070,7 +19070,7 @@
         </is>
       </c>
     </row>
-    <row r="432" hidden="1">
+    <row r="432">
       <c r="C432" t="inlineStr">
         <is>
           <t>Torneo Okinawa Fujinkai</t>
@@ -19114,7 +19114,7 @@
         </is>
       </c>
     </row>
-    <row r="433" hidden="1">
+    <row r="433">
       <c r="C433" t="inlineStr">
         <is>
           <t>Juegos de Integración Nikkei</t>
@@ -19153,7 +19153,7 @@
         </is>
       </c>
     </row>
-    <row r="434" hidden="1">
+    <row r="434">
       <c r="C434" t="inlineStr">
         <is>
           <t>Juegos de Integración Nikkei</t>
@@ -19192,7 +19192,7 @@
         </is>
       </c>
     </row>
-    <row r="435" hidden="1">
+    <row r="435">
       <c r="C435" t="inlineStr">
         <is>
           <t>Juegos de Integración Nikkei</t>
@@ -19231,7 +19231,7 @@
         </is>
       </c>
     </row>
-    <row r="436" hidden="1">
+    <row r="436">
       <c r="C436" t="inlineStr">
         <is>
           <t>Juegos de Integración Nikkei</t>
@@ -19270,7 +19270,7 @@
         </is>
       </c>
     </row>
-    <row r="437" hidden="1">
+    <row r="437">
       <c r="C437" t="inlineStr">
         <is>
           <t>Torneo Konomi</t>
@@ -19309,7 +19309,7 @@
         </is>
       </c>
     </row>
-    <row r="438" hidden="1">
+    <row r="438">
       <c r="C438" t="inlineStr">
         <is>
           <t>Torneo Konomi</t>
@@ -19348,7 +19348,7 @@
         </is>
       </c>
     </row>
-    <row r="439" hidden="1">
+    <row r="439">
       <c r="C439" t="inlineStr">
         <is>
           <t>Torneo Konomi</t>
@@ -19387,7 +19387,7 @@
         </is>
       </c>
     </row>
-    <row r="440" hidden="1">
+    <row r="440">
       <c r="C440" t="inlineStr">
         <is>
           <t>Torneo Konomi</t>
@@ -19426,7 +19426,7 @@
         </is>
       </c>
     </row>
-    <row r="441" hidden="1">
+    <row r="441">
       <c r="C441" t="inlineStr">
         <is>
           <t>Torneo Konomi</t>
@@ -19465,7 +19465,7 @@
         </is>
       </c>
     </row>
-    <row r="442" hidden="1">
+    <row r="442">
       <c r="C442" t="inlineStr">
         <is>
           <t>Torneo Konomi</t>
@@ -19504,7 +19504,7 @@
         </is>
       </c>
     </row>
-    <row r="443" hidden="1">
+    <row r="443">
       <c r="C443" t="inlineStr">
         <is>
           <t>Torneo Konomi</t>
@@ -19543,7 +19543,7 @@
         </is>
       </c>
     </row>
-    <row r="444" hidden="1">
+    <row r="444">
       <c r="C444" t="inlineStr">
         <is>
           <t>Torneo Konomi</t>
@@ -19582,7 +19582,7 @@
         </is>
       </c>
     </row>
-    <row r="445" hidden="1">
+    <row r="445">
       <c r="C445" t="inlineStr">
         <is>
           <t>Torneo Konomi</t>
@@ -19621,7 +19621,7 @@
         </is>
       </c>
     </row>
-    <row r="446" hidden="1">
+    <row r="446">
       <c r="C446" t="inlineStr">
         <is>
           <t>Torneo Konomi</t>
@@ -19660,7 +19660,7 @@
         </is>
       </c>
     </row>
-    <row r="447" hidden="1">
+    <row r="447">
       <c r="C447" t="inlineStr">
         <is>
           <t>Torneo Konomi</t>
@@ -19699,7 +19699,7 @@
         </is>
       </c>
     </row>
-    <row r="448" hidden="1">
+    <row r="448">
       <c r="C448" t="inlineStr">
         <is>
           <t>Torneo Konomi</t>
@@ -19738,7 +19738,7 @@
         </is>
       </c>
     </row>
-    <row r="449" hidden="1">
+    <row r="449">
       <c r="C449" t="inlineStr">
         <is>
           <t>Torneo Konomi</t>
@@ -19777,7 +19777,7 @@
         </is>
       </c>
     </row>
-    <row r="450" hidden="1">
+    <row r="450">
       <c r="C450" t="inlineStr">
         <is>
           <t>Torneo Konomi</t>
@@ -19816,7 +19816,7 @@
         </is>
       </c>
     </row>
-    <row r="451" hidden="1">
+    <row r="451">
       <c r="C451" t="inlineStr">
         <is>
           <t>Torneo Konomi</t>
@@ -19855,7 +19855,7 @@
         </is>
       </c>
     </row>
-    <row r="452" hidden="1">
+    <row r="452">
       <c r="C452" t="inlineStr">
         <is>
           <t>Torneo APG</t>
@@ -19899,7 +19899,7 @@
         </is>
       </c>
     </row>
-    <row r="453" hidden="1">
+    <row r="453">
       <c r="C453" t="inlineStr">
         <is>
           <t>Torneo APG</t>
@@ -19943,7 +19943,7 @@
         </is>
       </c>
     </row>
-    <row r="454" hidden="1">
+    <row r="454">
       <c r="C454" t="inlineStr">
         <is>
           <t>Torneo APG</t>
@@ -19987,7 +19987,7 @@
         </is>
       </c>
     </row>
-    <row r="455" hidden="1">
+    <row r="455">
       <c r="C455" t="inlineStr">
         <is>
           <t>Torneo APG</t>
@@ -20031,7 +20031,7 @@
         </is>
       </c>
     </row>
-    <row r="456" hidden="1">
+    <row r="456">
       <c r="C456" t="inlineStr">
         <is>
           <t>Torneo APG</t>
@@ -20075,7 +20075,7 @@
         </is>
       </c>
     </row>
-    <row r="457" hidden="1">
+    <row r="457">
       <c r="C457" t="inlineStr">
         <is>
           <t>Torneo APG</t>
@@ -20119,7 +20119,7 @@
         </is>
       </c>
     </row>
-    <row r="458" hidden="1">
+    <row r="458">
       <c r="C458" t="inlineStr">
         <is>
           <t>Torneo APG</t>
@@ -20163,7 +20163,7 @@
         </is>
       </c>
     </row>
-    <row r="459" hidden="1">
+    <row r="459">
       <c r="C459" t="inlineStr">
         <is>
           <t>Torneo APG</t>
@@ -20207,7 +20207,7 @@
         </is>
       </c>
     </row>
-    <row r="460" hidden="1">
+    <row r="460">
       <c r="C460" t="inlineStr">
         <is>
           <t>Torneo AELU</t>
@@ -20251,7 +20251,7 @@
         </is>
       </c>
     </row>
-    <row r="461" hidden="1">
+    <row r="461">
       <c r="C461" t="inlineStr">
         <is>
           <t>Torneo AELU</t>
@@ -20295,7 +20295,7 @@
         </is>
       </c>
     </row>
-    <row r="462" hidden="1">
+    <row r="462">
       <c r="C462" t="inlineStr">
         <is>
           <t>Torneo AELU</t>
@@ -20339,7 +20339,7 @@
         </is>
       </c>
     </row>
-    <row r="463" hidden="1">
+    <row r="463">
       <c r="C463" t="inlineStr">
         <is>
           <t>Torneo AELU</t>
@@ -20383,7 +20383,7 @@
         </is>
       </c>
     </row>
-    <row r="464" hidden="1">
+    <row r="464">
       <c r="C464" t="inlineStr">
         <is>
           <t>Torneo Copa Embajada</t>
@@ -20427,7 +20427,7 @@
         </is>
       </c>
     </row>
-    <row r="465" hidden="1">
+    <row r="465">
       <c r="C465" t="inlineStr">
         <is>
           <t>Torneo Copa Embajada</t>
@@ -20471,7 +20471,7 @@
         </is>
       </c>
     </row>
-    <row r="466" hidden="1">
+    <row r="466">
       <c r="C466" t="inlineStr">
         <is>
           <t>Torneo Copa Embajada</t>
@@ -20515,7 +20515,7 @@
         </is>
       </c>
     </row>
-    <row r="467" hidden="1">
+    <row r="467">
       <c r="C467" t="inlineStr">
         <is>
           <t>Torneo Copa Embajada</t>
@@ -20559,7 +20559,7 @@
         </is>
       </c>
     </row>
-    <row r="468" hidden="1">
+    <row r="468">
       <c r="C468" t="inlineStr">
         <is>
           <t>Torneo AOPCOOP</t>
@@ -20603,7 +20603,7 @@
         </is>
       </c>
     </row>
-    <row r="469" hidden="1">
+    <row r="469">
       <c r="C469" t="inlineStr">
         <is>
           <t>Torneo AOPCOOP</t>
@@ -20647,7 +20647,7 @@
         </is>
       </c>
     </row>
-    <row r="470" hidden="1">
+    <row r="470">
       <c r="C470" t="inlineStr">
         <is>
           <t>Torneo AOPCOOP</t>
@@ -20691,7 +20691,7 @@
         </is>
       </c>
     </row>
-    <row r="471" hidden="1">
+    <row r="471">
       <c r="C471" t="inlineStr">
         <is>
           <t>Torneo AOPCOOP</t>
@@ -20735,7 +20735,7 @@
         </is>
       </c>
     </row>
-    <row r="472" hidden="1">
+    <row r="472">
       <c r="C472" t="inlineStr">
         <is>
           <t>Torneo AOPCOOP</t>
@@ -20779,7 +20779,7 @@
         </is>
       </c>
     </row>
-    <row r="473" hidden="1">
+    <row r="473">
       <c r="C473" t="inlineStr">
         <is>
           <t>Torneo AOPCOOP</t>
@@ -20823,7 +20823,7 @@
         </is>
       </c>
     </row>
-    <row r="474" hidden="1">
+    <row r="474">
       <c r="C474" t="inlineStr">
         <is>
           <t>Torneo AOPCOOP</t>
@@ -20867,7 +20867,7 @@
         </is>
       </c>
     </row>
-    <row r="475" hidden="1">
+    <row r="475">
       <c r="C475" t="inlineStr">
         <is>
           <t>Torneo AOPCOOP</t>
@@ -20911,7 +20911,7 @@
         </is>
       </c>
     </row>
-    <row r="476" hidden="1">
+    <row r="476">
       <c r="C476" t="inlineStr">
         <is>
           <t>Torneo ABACO</t>
@@ -20955,7 +20955,7 @@
         </is>
       </c>
     </row>
-    <row r="477" hidden="1">
+    <row r="477">
       <c r="C477" t="inlineStr">
         <is>
           <t>Torneo ABACO</t>
@@ -20999,7 +20999,7 @@
         </is>
       </c>
     </row>
-    <row r="478" hidden="1">
+    <row r="478">
       <c r="C478" t="inlineStr">
         <is>
           <t>Torneo ABACO</t>
@@ -21043,7 +21043,7 @@
         </is>
       </c>
     </row>
-    <row r="479" hidden="1">
+    <row r="479">
       <c r="C479" t="inlineStr">
         <is>
           <t>Torneo ABACO</t>
@@ -21087,7 +21087,7 @@
         </is>
       </c>
     </row>
-    <row r="480" hidden="1">
+    <row r="480">
       <c r="C480" t="inlineStr">
         <is>
           <t>Torneo ABACO</t>
@@ -21131,7 +21131,7 @@
         </is>
       </c>
     </row>
-    <row r="481" hidden="1">
+    <row r="481">
       <c r="C481" t="inlineStr">
         <is>
           <t>Torneo ABACO</t>
@@ -21175,7 +21175,7 @@
         </is>
       </c>
     </row>
-    <row r="482" hidden="1">
+    <row r="482">
       <c r="C482" t="inlineStr">
         <is>
           <t>Torneo ABACO</t>
@@ -21219,7 +21219,7 @@
         </is>
       </c>
     </row>
-    <row r="483" hidden="1">
+    <row r="483">
       <c r="C483" t="inlineStr">
         <is>
           <t>Torneo ABACO</t>
@@ -21263,7 +21263,7 @@
         </is>
       </c>
     </row>
-    <row r="484" hidden="1">
+    <row r="484">
       <c r="B484" t="inlineStr">
         <is>
           <t>Campeonato Oficial</t>
@@ -21307,7 +21307,7 @@
         </is>
       </c>
     </row>
-    <row r="485" hidden="1">
+    <row r="485">
       <c r="B485" t="inlineStr">
         <is>
           <t>Campeonato Oficial</t>
@@ -21351,7 +21351,7 @@
         </is>
       </c>
     </row>
-    <row r="486" hidden="1">
+    <row r="486">
       <c r="B486" t="inlineStr">
         <is>
           <t>Campeonato Oficial</t>
@@ -21395,7 +21395,7 @@
         </is>
       </c>
     </row>
-    <row r="487" hidden="1">
+    <row r="487">
       <c r="B487" t="inlineStr">
         <is>
           <t>Campeonato Oficial</t>
@@ -21439,7 +21439,7 @@
         </is>
       </c>
     </row>
-    <row r="488" hidden="1">
+    <row r="488">
       <c r="B488" t="inlineStr">
         <is>
           <t>Campeonato Oficial</t>
@@ -21483,7 +21483,7 @@
         </is>
       </c>
     </row>
-    <row r="489" hidden="1">
+    <row r="489">
       <c r="B489" t="inlineStr">
         <is>
           <t>Campeonato Oficial</t>
@@ -21527,7 +21527,7 @@
         </is>
       </c>
     </row>
-    <row r="490" hidden="1">
+    <row r="490">
       <c r="B490" t="inlineStr">
         <is>
           <t>Campeonato Oficial</t>
@@ -21571,7 +21571,7 @@
         </is>
       </c>
     </row>
-    <row r="491" hidden="1">
+    <row r="491">
       <c r="B491" t="inlineStr">
         <is>
           <t>Campeonato Oficial</t>
@@ -21615,7 +21615,7 @@
         </is>
       </c>
     </row>
-    <row r="492" hidden="1">
+    <row r="492">
       <c r="B492" t="inlineStr">
         <is>
           <t>Campeonato Oficial</t>
@@ -21659,7 +21659,7 @@
         </is>
       </c>
     </row>
-    <row r="493" hidden="1">
+    <row r="493">
       <c r="B493" t="inlineStr">
         <is>
           <t>Campeonato Oficial</t>
@@ -21703,7 +21703,7 @@
         </is>
       </c>
     </row>
-    <row r="494" hidden="1">
+    <row r="494">
       <c r="B494" t="inlineStr">
         <is>
           <t>Campeonato Oficial</t>
@@ -21747,7 +21747,7 @@
         </is>
       </c>
     </row>
-    <row r="495" hidden="1">
+    <row r="495">
       <c r="B495" t="inlineStr">
         <is>
           <t>Campeonato Oficial</t>
@@ -21791,7 +21791,7 @@
         </is>
       </c>
     </row>
-    <row r="496" hidden="1">
+    <row r="496">
       <c r="C496" t="inlineStr">
         <is>
           <t>Torneo Nikkei Fujinkai</t>
@@ -21835,7 +21835,7 @@
         </is>
       </c>
     </row>
-    <row r="497" hidden="1">
+    <row r="497">
       <c r="C497" t="inlineStr">
         <is>
           <t>Torneo Nikkei Fujinkai</t>
@@ -21879,7 +21879,7 @@
         </is>
       </c>
     </row>
-    <row r="498" hidden="1">
+    <row r="498">
       <c r="C498" t="inlineStr">
         <is>
           <t>Torneo Nikkei Fujinkai</t>
@@ -21923,7 +21923,7 @@
         </is>
       </c>
     </row>
-    <row r="499" hidden="1">
+    <row r="499">
       <c r="C499" t="inlineStr">
         <is>
           <t>Torneo Nikkei Fujinkai</t>
@@ -21967,7 +21967,7 @@
         </is>
       </c>
     </row>
-    <row r="500" hidden="1">
+    <row r="500">
       <c r="C500" t="inlineStr">
         <is>
           <t>Torneo Nikkei Fujinkai</t>
@@ -22011,7 +22011,7 @@
         </is>
       </c>
     </row>
-    <row r="501" hidden="1">
+    <row r="501">
       <c r="C501" t="inlineStr">
         <is>
           <t>Torneo Nikkei Fujinkai</t>
@@ -22055,7 +22055,7 @@
         </is>
       </c>
     </row>
-    <row r="502" hidden="1">
+    <row r="502">
       <c r="C502" t="inlineStr">
         <is>
           <t>Torneo Kumamoto Kenjinkai</t>
@@ -22099,7 +22099,7 @@
         </is>
       </c>
     </row>
-    <row r="503" hidden="1">
+    <row r="503">
       <c r="C503" t="inlineStr">
         <is>
           <t>Torneo Kumamoto Kenjinkai</t>
@@ -22143,7 +22143,7 @@
         </is>
       </c>
     </row>
-    <row r="504" hidden="1">
+    <row r="504">
       <c r="C504" t="inlineStr">
         <is>
           <t>Torneo Kumamoto Kenjinkai</t>
@@ -22187,7 +22187,7 @@
         </is>
       </c>
     </row>
-    <row r="505" hidden="1">
+    <row r="505">
       <c r="C505" t="inlineStr">
         <is>
           <t>Torneo Kumamoto Kenjinkai</t>
@@ -22231,7 +22231,7 @@
         </is>
       </c>
     </row>
-    <row r="506" hidden="1">
+    <row r="506">
       <c r="C506" t="inlineStr">
         <is>
           <t>Torneo Kumamoto Kenjinkai</t>
@@ -22275,7 +22275,7 @@
         </is>
       </c>
     </row>
-    <row r="507" hidden="1">
+    <row r="507">
       <c r="C507" t="inlineStr">
         <is>
           <t>Torneo Kumamoto Kenjinkai</t>
@@ -22319,7 +22319,7 @@
         </is>
       </c>
     </row>
-    <row r="508" hidden="1">
+    <row r="508">
       <c r="C508" t="inlineStr">
         <is>
           <t>Torneo Kumamoto Kenjinkai</t>
@@ -22363,7 +22363,7 @@
         </is>
       </c>
     </row>
-    <row r="509" hidden="1">
+    <row r="509">
       <c r="C509" t="inlineStr">
         <is>
           <t>Torneo Kumamoto Kenjinkai</t>
@@ -22407,7 +22407,7 @@
         </is>
       </c>
     </row>
-    <row r="510" hidden="1">
+    <row r="510">
       <c r="B510" t="inlineStr">
         <is>
           <t>Campeonato Oficial</t>
@@ -22451,7 +22451,7 @@
         </is>
       </c>
     </row>
-    <row r="511" hidden="1">
+    <row r="511">
       <c r="B511" t="inlineStr">
         <is>
           <t>Campeonato Oficial</t>
@@ -22495,7 +22495,7 @@
         </is>
       </c>
     </row>
-    <row r="512" hidden="1">
+    <row r="512">
       <c r="B512" t="inlineStr">
         <is>
           <t>Campeonato Oficial</t>
@@ -22539,7 +22539,7 @@
         </is>
       </c>
     </row>
-    <row r="513" hidden="1">
+    <row r="513">
       <c r="B513" t="inlineStr">
         <is>
           <t>Campeonato Oficial</t>
@@ -22583,7 +22583,7 @@
         </is>
       </c>
     </row>
-    <row r="514" hidden="1">
+    <row r="514">
       <c r="B514" t="inlineStr">
         <is>
           <t>Campeonato Oficial</t>
@@ -22627,7 +22627,7 @@
         </is>
       </c>
     </row>
-    <row r="515" hidden="1">
+    <row r="515">
       <c r="B515" t="inlineStr">
         <is>
           <t>Campeonato Oficial</t>
@@ -22671,7 +22671,7 @@
         </is>
       </c>
     </row>
-    <row r="516" hidden="1">
+    <row r="516">
       <c r="B516" t="inlineStr">
         <is>
           <t>Campeonato Oficial</t>
@@ -22715,7 +22715,7 @@
         </is>
       </c>
     </row>
-    <row r="517" hidden="1">
+    <row r="517">
       <c r="B517" t="inlineStr">
         <is>
           <t>Campeonato Oficial</t>
@@ -22759,7 +22759,7 @@
         </is>
       </c>
     </row>
-    <row r="518" hidden="1">
+    <row r="518">
       <c r="B518" t="inlineStr">
         <is>
           <t>Campeonato Oficial</t>
@@ -22803,7 +22803,7 @@
         </is>
       </c>
     </row>
-    <row r="519" hidden="1">
+    <row r="519">
       <c r="B519" t="inlineStr">
         <is>
           <t>Campeonato Oficial</t>
@@ -22847,7 +22847,7 @@
         </is>
       </c>
     </row>
-    <row r="520" hidden="1">
+    <row r="520">
       <c r="B520" t="inlineStr">
         <is>
           <t>Campeonato Oficial</t>
@@ -22891,7 +22891,7 @@
         </is>
       </c>
     </row>
-    <row r="521" hidden="1">
+    <row r="521">
       <c r="B521" t="inlineStr">
         <is>
           <t>Campeonato Oficial</t>
@@ -22935,7 +22935,7 @@
         </is>
       </c>
     </row>
-    <row r="522" hidden="1">
+    <row r="522">
       <c r="C522" t="inlineStr">
         <is>
           <t>Torneo Konomi</t>
@@ -22974,7 +22974,7 @@
         </is>
       </c>
     </row>
-    <row r="523" hidden="1">
+    <row r="523">
       <c r="C523" t="inlineStr">
         <is>
           <t>Torneo Konomi</t>
@@ -23013,7 +23013,7 @@
         </is>
       </c>
     </row>
-    <row r="524" hidden="1">
+    <row r="524">
       <c r="C524" t="inlineStr">
         <is>
           <t>Torneo Konomi</t>
@@ -23052,7 +23052,7 @@
         </is>
       </c>
     </row>
-    <row r="525" hidden="1">
+    <row r="525">
       <c r="C525" t="inlineStr">
         <is>
           <t>Torneo Konomi</t>
@@ -23091,7 +23091,7 @@
         </is>
       </c>
     </row>
-    <row r="526" hidden="1">
+    <row r="526">
       <c r="C526" t="inlineStr">
         <is>
           <t>Torneo Konomi</t>
@@ -23130,7 +23130,7 @@
         </is>
       </c>
     </row>
-    <row r="527" hidden="1">
+    <row r="527">
       <c r="C527" t="inlineStr">
         <is>
           <t>Torneo Konomi</t>
@@ -23169,7 +23169,7 @@
         </is>
       </c>
     </row>
-    <row r="528" hidden="1">
+    <row r="528">
       <c r="C528" t="inlineStr">
         <is>
           <t>Torneo Konomi</t>
@@ -23208,7 +23208,7 @@
         </is>
       </c>
     </row>
-    <row r="529" hidden="1">
+    <row r="529">
       <c r="C529" t="inlineStr">
         <is>
           <t>Torneo Konomi</t>
@@ -23247,7 +23247,7 @@
         </is>
       </c>
     </row>
-    <row r="530" hidden="1">
+    <row r="530">
       <c r="C530" t="inlineStr">
         <is>
           <t>Torneo Konomi</t>
@@ -23286,7 +23286,7 @@
         </is>
       </c>
     </row>
-    <row r="531" hidden="1">
+    <row r="531">
       <c r="C531" t="inlineStr">
         <is>
           <t>Torneo Konomi</t>
@@ -23325,7 +23325,7 @@
         </is>
       </c>
     </row>
-    <row r="532" hidden="1">
+    <row r="532">
       <c r="C532" t="inlineStr">
         <is>
           <t>Torneo Konomi</t>
@@ -23364,7 +23364,7 @@
         </is>
       </c>
     </row>
-    <row r="533" hidden="1">
+    <row r="533">
       <c r="C533" t="inlineStr">
         <is>
           <t>Torneo Konomi</t>
@@ -23403,7 +23403,7 @@
         </is>
       </c>
     </row>
-    <row r="534" hidden="1">
+    <row r="534">
       <c r="C534" t="inlineStr">
         <is>
           <t>Torneo Konomi</t>
@@ -23442,7 +23442,7 @@
         </is>
       </c>
     </row>
-    <row r="535" hidden="1">
+    <row r="535">
       <c r="C535" t="inlineStr">
         <is>
           <t>Torneo Konomi</t>
@@ -23481,7 +23481,7 @@
         </is>
       </c>
     </row>
-    <row r="536" hidden="1">
+    <row r="536">
       <c r="C536" t="inlineStr">
         <is>
           <t>Torneo Konomi</t>
@@ -23520,7 +23520,7 @@
         </is>
       </c>
     </row>
-    <row r="537" hidden="1">
+    <row r="537">
       <c r="C537" t="inlineStr">
         <is>
           <t>Torneo Konomi</t>
@@ -23559,7 +23559,7 @@
         </is>
       </c>
     </row>
-    <row r="538" hidden="1">
+    <row r="538">
       <c r="C538" t="inlineStr">
         <is>
           <t>Torneo Konomi</t>
@@ -23598,7 +23598,7 @@
         </is>
       </c>
     </row>
-    <row r="539" hidden="1">
+    <row r="539">
       <c r="C539" t="inlineStr">
         <is>
           <t>Torneo Konomi</t>
@@ -23637,7 +23637,7 @@
         </is>
       </c>
     </row>
-    <row r="540" hidden="1">
+    <row r="540">
       <c r="C540" t="inlineStr">
         <is>
           <t>Torneo Konomi</t>
@@ -23676,7 +23676,7 @@
         </is>
       </c>
     </row>
-    <row r="541" hidden="1">
+    <row r="541">
       <c r="C541" t="inlineStr">
         <is>
           <t>Torneo Konomi</t>
@@ -23715,7 +23715,7 @@
         </is>
       </c>
     </row>
-    <row r="542" hidden="1">
+    <row r="542">
       <c r="B542" t="inlineStr">
         <is>
           <t>Confraternidad/Integración</t>
@@ -23759,7 +23759,7 @@
         </is>
       </c>
     </row>
-    <row r="543" hidden="1">
+    <row r="543">
       <c r="B543" t="inlineStr">
         <is>
           <t>Confraternidad/Integración</t>
@@ -23803,7 +23803,7 @@
         </is>
       </c>
     </row>
-    <row r="544" hidden="1">
+    <row r="544">
       <c r="B544" t="inlineStr">
         <is>
           <t>Confraternidad/Integración</t>
@@ -23847,7 +23847,7 @@
         </is>
       </c>
     </row>
-    <row r="545" hidden="1">
+    <row r="545">
       <c r="B545" t="inlineStr">
         <is>
           <t>Confraternidad/Integración</t>
@@ -23891,7 +23891,7 @@
         </is>
       </c>
     </row>
-    <row r="546" hidden="1">
+    <row r="546">
       <c r="C546" t="inlineStr">
         <is>
           <t>Torneo Okinawa Fujinkai</t>
@@ -23935,7 +23935,7 @@
         </is>
       </c>
     </row>
-    <row r="547" hidden="1">
+    <row r="547">
       <c r="C547" t="inlineStr">
         <is>
           <t>Torneo Okinawa Fujinkai</t>
@@ -23979,7 +23979,7 @@
         </is>
       </c>
     </row>
-    <row r="548" hidden="1">
+    <row r="548">
       <c r="C548" t="inlineStr">
         <is>
           <t>Torneo Okinawa Fujinkai</t>
@@ -24023,7 +24023,7 @@
         </is>
       </c>
     </row>
-    <row r="549" hidden="1">
+    <row r="549">
       <c r="C549" t="inlineStr">
         <is>
           <t>Torneo Okinawa Fujinkai</t>
@@ -24067,7 +24067,7 @@
         </is>
       </c>
     </row>
-    <row r="550" hidden="1">
+    <row r="550">
       <c r="C550" t="inlineStr">
         <is>
           <t>Juegos de Integración Nikkei</t>
@@ -24106,7 +24106,7 @@
         </is>
       </c>
     </row>
-    <row r="551" hidden="1">
+    <row r="551">
       <c r="C551" t="inlineStr">
         <is>
           <t>Juegos de Integración Nikkei</t>
@@ -24145,7 +24145,7 @@
         </is>
       </c>
     </row>
-    <row r="552" hidden="1">
+    <row r="552">
       <c r="C552" t="inlineStr">
         <is>
           <t>Juegos de Integración Nikkei</t>
@@ -24184,7 +24184,7 @@
         </is>
       </c>
     </row>
-    <row r="553" hidden="1">
+    <row r="553">
       <c r="B553" t="inlineStr">
         <is>
           <t>Confraternidad/Integración</t>
@@ -24228,7 +24228,7 @@
         </is>
       </c>
     </row>
-    <row r="554" hidden="1">
+    <row r="554">
       <c r="B554" t="inlineStr">
         <is>
           <t>Confraternidad/Integración</t>
@@ -24272,7 +24272,7 @@
         </is>
       </c>
     </row>
-    <row r="555" hidden="1">
+    <row r="555">
       <c r="B555" t="inlineStr">
         <is>
           <t>Confraternidad/Integración</t>
@@ -24316,7 +24316,7 @@
         </is>
       </c>
     </row>
-    <row r="556" hidden="1">
+    <row r="556">
       <c r="B556" t="inlineStr">
         <is>
           <t>Confraternidad/Integración</t>
@@ -24360,7 +24360,7 @@
         </is>
       </c>
     </row>
-    <row r="557" hidden="1">
+    <row r="557">
       <c r="B557" t="inlineStr">
         <is>
           <t>Confraternidad/Integración</t>
@@ -24404,7 +24404,7 @@
         </is>
       </c>
     </row>
-    <row r="558" hidden="1">
+    <row r="558">
       <c r="B558" t="inlineStr">
         <is>
           <t>Confraternidad/Integración</t>
@@ -24448,7 +24448,7 @@
         </is>
       </c>
     </row>
-    <row r="559" hidden="1">
+    <row r="559">
       <c r="B559" t="inlineStr">
         <is>
           <t>Confraternidad/Integración</t>
@@ -24492,7 +24492,7 @@
         </is>
       </c>
     </row>
-    <row r="560" hidden="1">
+    <row r="560">
       <c r="B560" t="inlineStr">
         <is>
           <t>Confraternidad/Integración</t>
@@ -24536,7 +24536,7 @@
         </is>
       </c>
     </row>
-    <row r="561" hidden="1">
+    <row r="561">
       <c r="C561" t="inlineStr">
         <is>
           <t>Torneo APG</t>
@@ -24580,7 +24580,7 @@
         </is>
       </c>
     </row>
-    <row r="562" hidden="1">
+    <row r="562">
       <c r="C562" t="inlineStr">
         <is>
           <t>Torneo APG</t>
@@ -24624,7 +24624,7 @@
         </is>
       </c>
     </row>
-    <row r="563" hidden="1">
+    <row r="563">
       <c r="C563" t="inlineStr">
         <is>
           <t>Torneo APG</t>
@@ -24668,7 +24668,7 @@
         </is>
       </c>
     </row>
-    <row r="564" hidden="1">
+    <row r="564">
       <c r="C564" t="inlineStr">
         <is>
           <t>Torneo APG</t>
@@ -24712,7 +24712,7 @@
         </is>
       </c>
     </row>
-    <row r="565" hidden="1">
+    <row r="565">
       <c r="C565" t="inlineStr">
         <is>
           <t>Torneo APG</t>
@@ -24756,7 +24756,7 @@
         </is>
       </c>
     </row>
-    <row r="566" hidden="1">
+    <row r="566">
       <c r="C566" t="inlineStr">
         <is>
           <t>Torneo APG</t>
@@ -24800,7 +24800,7 @@
         </is>
       </c>
     </row>
-    <row r="567" hidden="1">
+    <row r="567">
       <c r="C567" t="inlineStr">
         <is>
           <t>Torneo APG</t>
@@ -24844,7 +24844,7 @@
         </is>
       </c>
     </row>
-    <row r="568" hidden="1">
+    <row r="568">
       <c r="C568" t="inlineStr">
         <is>
           <t>Torneo APG</t>
@@ -24888,7 +24888,7 @@
         </is>
       </c>
     </row>
-    <row r="569" hidden="1">
+    <row r="569">
       <c r="C569" t="inlineStr">
         <is>
           <t>Torneo Copa Embajada</t>
@@ -24932,7 +24932,7 @@
         </is>
       </c>
     </row>
-    <row r="570" hidden="1">
+    <row r="570">
       <c r="C570" t="inlineStr">
         <is>
           <t>Torneo Copa Embajada</t>
@@ -24976,7 +24976,7 @@
         </is>
       </c>
     </row>
-    <row r="571" hidden="1">
+    <row r="571">
       <c r="C571" t="inlineStr">
         <is>
           <t>Torneo Copa Embajada</t>
@@ -25020,7 +25020,7 @@
         </is>
       </c>
     </row>
-    <row r="572" hidden="1">
+    <row r="572">
       <c r="C572" t="inlineStr">
         <is>
           <t>Torneo Copa Embajada</t>
@@ -25064,7 +25064,7 @@
         </is>
       </c>
     </row>
-    <row r="573" hidden="1">
+    <row r="573">
       <c r="B573" t="inlineStr">
         <is>
           <t>Confraternidad/Integración</t>
@@ -25108,7 +25108,7 @@
         </is>
       </c>
     </row>
-    <row r="574" hidden="1">
+    <row r="574">
       <c r="B574" t="inlineStr">
         <is>
           <t>Confraternidad/Integración</t>
@@ -25152,7 +25152,7 @@
         </is>
       </c>
     </row>
-    <row r="575" hidden="1">
+    <row r="575">
       <c r="B575" t="inlineStr">
         <is>
           <t>Confraternidad/Integración</t>
@@ -25196,7 +25196,7 @@
         </is>
       </c>
     </row>
-    <row r="576" hidden="1">
+    <row r="576">
       <c r="B576" t="inlineStr">
         <is>
           <t>Confraternidad/Integración</t>
@@ -25240,7 +25240,7 @@
         </is>
       </c>
     </row>
-    <row r="577" hidden="1">
+    <row r="577">
       <c r="B577" t="inlineStr">
         <is>
           <t>Confraternidad/Integración</t>
@@ -25284,7 +25284,7 @@
         </is>
       </c>
     </row>
-    <row r="578" hidden="1">
+    <row r="578">
       <c r="B578" t="inlineStr">
         <is>
           <t>Confraternidad/Integración</t>
@@ -25328,7 +25328,7 @@
         </is>
       </c>
     </row>
-    <row r="579" hidden="1">
+    <row r="579">
       <c r="B579" t="inlineStr">
         <is>
           <t>Confraternidad/Integración</t>
@@ -25372,7 +25372,7 @@
         </is>
       </c>
     </row>
-    <row r="580" hidden="1">
+    <row r="580">
       <c r="B580" t="inlineStr">
         <is>
           <t>Confraternidad/Integración</t>
@@ -25416,7 +25416,7 @@
         </is>
       </c>
     </row>
-    <row r="581" hidden="1">
+    <row r="581">
       <c r="B581" t="inlineStr">
         <is>
           <t>Confraternidad/Integración</t>
@@ -25460,7 +25460,7 @@
         </is>
       </c>
     </row>
-    <row r="582" hidden="1">
+    <row r="582">
       <c r="C582" t="inlineStr">
         <is>
           <t>Torneo APG</t>
@@ -25504,7 +25504,7 @@
         </is>
       </c>
     </row>
-    <row r="583" hidden="1">
+    <row r="583">
       <c r="C583" t="inlineStr">
         <is>
           <t>Torneo APG</t>
@@ -25548,7 +25548,7 @@
         </is>
       </c>
     </row>
-    <row r="584" hidden="1">
+    <row r="584">
       <c r="C584" t="inlineStr">
         <is>
           <t>Torneo APG</t>
@@ -25592,7 +25592,7 @@
         </is>
       </c>
     </row>
-    <row r="585" hidden="1">
+    <row r="585">
       <c r="C585" t="inlineStr">
         <is>
           <t>Torneo APG</t>
@@ -25636,7 +25636,7 @@
         </is>
       </c>
     </row>
-    <row r="586" hidden="1">
+    <row r="586">
       <c r="C586" t="inlineStr">
         <is>
           <t>Torneo AELU</t>
@@ -25680,7 +25680,7 @@
         </is>
       </c>
     </row>
-    <row r="587" hidden="1">
+    <row r="587">
       <c r="C587" t="inlineStr">
         <is>
           <t>Torneo AELU</t>
@@ -25724,7 +25724,7 @@
         </is>
       </c>
     </row>
-    <row r="588" hidden="1">
+    <row r="588">
       <c r="C588" t="inlineStr">
         <is>
           <t>Torneo AELU</t>
@@ -25768,7 +25768,7 @@
         </is>
       </c>
     </row>
-    <row r="589" hidden="1">
+    <row r="589">
       <c r="C589" t="inlineStr">
         <is>
           <t>Torneo AELU</t>
@@ -25812,7 +25812,7 @@
         </is>
       </c>
     </row>
-    <row r="590" hidden="1">
+    <row r="590">
       <c r="C590" t="inlineStr">
         <is>
           <t>Torneo Copa Embajada</t>
@@ -25856,7 +25856,7 @@
         </is>
       </c>
     </row>
-    <row r="591" hidden="1">
+    <row r="591">
       <c r="C591" t="inlineStr">
         <is>
           <t>Torneo Copa Embajada</t>
@@ -25900,7 +25900,7 @@
         </is>
       </c>
     </row>
-    <row r="592" hidden="1">
+    <row r="592">
       <c r="C592" t="inlineStr">
         <is>
           <t>Torneo Copa Embajada</t>
@@ -25944,7 +25944,7 @@
         </is>
       </c>
     </row>
-    <row r="593" hidden="1">
+    <row r="593">
       <c r="C593" t="inlineStr">
         <is>
           <t>Torneo Copa Embajada</t>
@@ -25988,7 +25988,7 @@
         </is>
       </c>
     </row>
-    <row r="594" hidden="1">
+    <row r="594">
       <c r="C594" t="inlineStr">
         <is>
           <t>Torneo AOPCOOP</t>
@@ -26032,7 +26032,7 @@
         </is>
       </c>
     </row>
-    <row r="595" hidden="1">
+    <row r="595">
       <c r="C595" t="inlineStr">
         <is>
           <t>Torneo AOPCOOP</t>
@@ -26076,7 +26076,7 @@
         </is>
       </c>
     </row>
-    <row r="596" hidden="1">
+    <row r="596">
       <c r="C596" t="inlineStr">
         <is>
           <t>Torneo AOPCOOP</t>
@@ -26120,7 +26120,7 @@
         </is>
       </c>
     </row>
-    <row r="597" hidden="1">
+    <row r="597">
       <c r="C597" t="inlineStr">
         <is>
           <t>Torneo AOPCOOP</t>
@@ -26164,7 +26164,7 @@
         </is>
       </c>
     </row>
-    <row r="598" hidden="1">
+    <row r="598">
       <c r="C598" t="inlineStr">
         <is>
           <t>Torneo AOPCOOP</t>
@@ -26208,7 +26208,7 @@
         </is>
       </c>
     </row>
-    <row r="599" hidden="1">
+    <row r="599">
       <c r="C599" t="inlineStr">
         <is>
           <t>Torneo AOPCOOP</t>
@@ -26252,7 +26252,7 @@
         </is>
       </c>
     </row>
-    <row r="600" hidden="1">
+    <row r="600">
       <c r="C600" t="inlineStr">
         <is>
           <t>Torneo AOPCOOP</t>
@@ -26296,7 +26296,7 @@
         </is>
       </c>
     </row>
-    <row r="601" hidden="1">
+    <row r="601">
       <c r="C601" t="inlineStr">
         <is>
           <t>Torneo AOPCOOP</t>
@@ -26340,7 +26340,7 @@
         </is>
       </c>
     </row>
-    <row r="602" hidden="1">
+    <row r="602">
       <c r="C602" t="inlineStr">
         <is>
           <t>Torneo Okinawa Kenjinkai</t>
@@ -26384,7 +26384,7 @@
         </is>
       </c>
     </row>
-    <row r="603" hidden="1">
+    <row r="603">
       <c r="C603" t="inlineStr">
         <is>
           <t>Torneo Okinawa Kenjinkai</t>
@@ -26428,7 +26428,7 @@
         </is>
       </c>
     </row>
-    <row r="604" hidden="1">
+    <row r="604">
       <c r="C604" t="inlineStr">
         <is>
           <t>Torneo Okinawa Kenjinkai</t>
@@ -26472,7 +26472,7 @@
         </is>
       </c>
     </row>
-    <row r="605" hidden="1">
+    <row r="605">
       <c r="C605" t="inlineStr">
         <is>
           <t>Torneo Okinawa Kenjinkai</t>
@@ -26516,7 +26516,7 @@
         </is>
       </c>
     </row>
-    <row r="606" hidden="1">
+    <row r="606">
       <c r="B606" t="inlineStr">
         <is>
           <t>Campeonato Oficial</t>
@@ -26560,7 +26560,7 @@
         </is>
       </c>
     </row>
-    <row r="607" hidden="1">
+    <row r="607">
       <c r="B607" t="inlineStr">
         <is>
           <t>Campeonato Oficial</t>
@@ -26604,7 +26604,7 @@
         </is>
       </c>
     </row>
-    <row r="608" hidden="1">
+    <row r="608">
       <c r="B608" t="inlineStr">
         <is>
           <t>Campeonato Oficial</t>
@@ -26648,7 +26648,7 @@
         </is>
       </c>
     </row>
-    <row r="609" hidden="1">
+    <row r="609">
       <c r="B609" t="inlineStr">
         <is>
           <t>Campeonato Oficial</t>
@@ -26692,7 +26692,7 @@
         </is>
       </c>
     </row>
-    <row r="610" hidden="1">
+    <row r="610">
       <c r="B610" t="inlineStr">
         <is>
           <t>Campeonato Oficial</t>
@@ -26736,7 +26736,7 @@
         </is>
       </c>
     </row>
-    <row r="611" hidden="1">
+    <row r="611">
       <c r="B611" t="inlineStr">
         <is>
           <t>Campeonato Oficial</t>
@@ -26780,7 +26780,7 @@
         </is>
       </c>
     </row>
-    <row r="612" hidden="1">
+    <row r="612">
       <c r="B612" t="inlineStr">
         <is>
           <t>Campeonato Oficial</t>
@@ -26824,7 +26824,7 @@
         </is>
       </c>
     </row>
-    <row r="613" hidden="1">
+    <row r="613">
       <c r="B613" t="inlineStr">
         <is>
           <t>Campeonato Oficial</t>
@@ -26868,7 +26868,7 @@
         </is>
       </c>
     </row>
-    <row r="614" hidden="1">
+    <row r="614">
       <c r="B614" t="inlineStr">
         <is>
           <t>Campeonato Oficial</t>
@@ -26898,7 +26898,7 @@
       </c>
       <c r="K614" t="inlineStr">
         <is>
-          <t>Primero</t>
+          <t>AELU 2</t>
         </is>
       </c>
       <c r="L614" t="inlineStr">
@@ -27206,7 +27206,7 @@
         </is>
       </c>
     </row>
-    <row r="621" hidden="1">
+    <row r="621">
       <c r="C621" t="inlineStr">
         <is>
           <t>Torneo Nikkei Fujinkai</t>
@@ -27250,7 +27250,7 @@
         </is>
       </c>
     </row>
-    <row r="622" hidden="1">
+    <row r="622">
       <c r="C622" t="inlineStr">
         <is>
           <t>Torneo Nikkei Fujinkai</t>
@@ -27294,7 +27294,7 @@
         </is>
       </c>
     </row>
-    <row r="623" hidden="1">
+    <row r="623">
       <c r="C623" t="inlineStr">
         <is>
           <t>Torneo Nikkei Fujinkai</t>
@@ -27338,7 +27338,7 @@
         </is>
       </c>
     </row>
-    <row r="624" hidden="1">
+    <row r="624">
       <c r="C624" t="inlineStr">
         <is>
           <t>Torneo Nikkei Fujinkai</t>
@@ -27382,7 +27382,7 @@
         </is>
       </c>
     </row>
-    <row r="625" hidden="1">
+    <row r="625">
       <c r="C625" t="inlineStr">
         <is>
           <t>Torneo Nikkei Fujinkai</t>
@@ -27426,7 +27426,7 @@
         </is>
       </c>
     </row>
-    <row r="626" hidden="1">
+    <row r="626">
       <c r="C626" t="inlineStr">
         <is>
           <t>Torneo Nikkei Fujinkai</t>
@@ -27470,7 +27470,7 @@
         </is>
       </c>
     </row>
-    <row r="627" hidden="1">
+    <row r="627">
       <c r="B627" t="inlineStr">
         <is>
           <t>Confraternidad/Integración</t>
@@ -27514,7 +27514,7 @@
         </is>
       </c>
     </row>
-    <row r="628" hidden="1">
+    <row r="628">
       <c r="B628" t="inlineStr">
         <is>
           <t>Confraternidad/Integración</t>
@@ -27558,7 +27558,7 @@
         </is>
       </c>
     </row>
-    <row r="629" hidden="1">
+    <row r="629">
       <c r="C629" t="inlineStr">
         <is>
           <t>Torneo Yamanashi Shimbokukai</t>
@@ -27602,7 +27602,7 @@
         </is>
       </c>
     </row>
-    <row r="630" hidden="1">
+    <row r="630">
       <c r="C630" t="inlineStr">
         <is>
           <t>Torneo Yamanashi Shimbokukai</t>
@@ -27646,7 +27646,7 @@
         </is>
       </c>
     </row>
-    <row r="631" hidden="1">
+    <row r="631">
       <c r="B631" t="inlineStr">
         <is>
           <t>Campeonato Oficial</t>
@@ -27690,7 +27690,7 @@
         </is>
       </c>
     </row>
-    <row r="632" hidden="1">
+    <row r="632">
       <c r="B632" t="inlineStr">
         <is>
           <t>Campeonato Oficial</t>
@@ -27734,7 +27734,7 @@
         </is>
       </c>
     </row>
-    <row r="633" hidden="1">
+    <row r="633">
       <c r="B633" t="inlineStr">
         <is>
           <t>Campeonato Oficial</t>
@@ -27778,7 +27778,7 @@
         </is>
       </c>
     </row>
-    <row r="634" hidden="1">
+    <row r="634">
       <c r="B634" t="inlineStr">
         <is>
           <t>Campeonato Oficial</t>
@@ -27822,7 +27822,7 @@
         </is>
       </c>
     </row>
-    <row r="635" hidden="1">
+    <row r="635">
       <c r="B635" t="inlineStr">
         <is>
           <t>Campeonato Oficial</t>
@@ -27866,7 +27866,7 @@
         </is>
       </c>
     </row>
-    <row r="636" hidden="1">
+    <row r="636">
       <c r="B636" t="inlineStr">
         <is>
           <t>Campeonato Oficial</t>
@@ -27910,7 +27910,7 @@
         </is>
       </c>
     </row>
-    <row r="637" hidden="1">
+    <row r="637">
       <c r="B637" t="inlineStr">
         <is>
           <t>Campeonato Oficial</t>
@@ -27954,7 +27954,7 @@
         </is>
       </c>
     </row>
-    <row r="638" hidden="1">
+    <row r="638">
       <c r="B638" t="inlineStr">
         <is>
           <t>Campeonato Oficial</t>
@@ -27998,7 +27998,7 @@
         </is>
       </c>
     </row>
-    <row r="639" hidden="1">
+    <row r="639">
       <c r="B639" t="inlineStr">
         <is>
           <t>Campeonato Oficial</t>
@@ -28042,7 +28042,7 @@
         </is>
       </c>
     </row>
-    <row r="640" hidden="1">
+    <row r="640">
       <c r="C640" t="inlineStr">
         <is>
           <t>Torneo Club Aikokai</t>
@@ -28086,7 +28086,7 @@
         </is>
       </c>
     </row>
-    <row r="641" hidden="1">
+    <row r="641">
       <c r="C641" t="inlineStr">
         <is>
           <t>Torneo Club Aikokai</t>
@@ -28130,7 +28130,7 @@
         </is>
       </c>
     </row>
-    <row r="642" hidden="1">
+    <row r="642">
       <c r="C642" t="inlineStr">
         <is>
           <t>Torneo Club Aikokai</t>
@@ -28174,7 +28174,7 @@
         </is>
       </c>
     </row>
-    <row r="643" hidden="1">
+    <row r="643">
       <c r="C643" t="inlineStr">
         <is>
           <t>Torneo Club Aikokai</t>
@@ -28218,7 +28218,7 @@
         </is>
       </c>
     </row>
-    <row r="644" hidden="1">
+    <row r="644">
       <c r="D644" t="inlineStr">
         <is>
           <t>Torneo de Verano APG</t>
@@ -28257,7 +28257,7 @@
         </is>
       </c>
     </row>
-    <row r="645" hidden="1">
+    <row r="645">
       <c r="D645" t="inlineStr">
         <is>
           <t>Torneo de Verano APG</t>
@@ -28296,7 +28296,7 @@
         </is>
       </c>
     </row>
-    <row r="646" hidden="1">
+    <row r="646">
       <c r="D646" t="inlineStr">
         <is>
           <t>Torneo de Verano APG</t>
@@ -28335,7 +28335,7 @@
         </is>
       </c>
     </row>
-    <row r="647" hidden="1">
+    <row r="647">
       <c r="D647" t="inlineStr">
         <is>
           <t>Torneo de Verano APG</t>
@@ -28374,7 +28374,12 @@
         </is>
       </c>
     </row>
-    <row r="648" hidden="1">
+    <row r="648">
+      <c r="B648" t="inlineStr">
+        <is>
+          <t>Confraternidad/Integración</t>
+        </is>
+      </c>
       <c r="C648" t="inlineStr">
         <is>
           <t>Torneo Konomi</t>
@@ -28413,7 +28418,12 @@
         </is>
       </c>
     </row>
-    <row r="649" hidden="1">
+    <row r="649">
+      <c r="B649" t="inlineStr">
+        <is>
+          <t>Confraternidad/Integración</t>
+        </is>
+      </c>
       <c r="C649" t="inlineStr">
         <is>
           <t>Torneo Konomi</t>
@@ -28452,7 +28462,7 @@
         </is>
       </c>
     </row>
-    <row r="650" hidden="1">
+    <row r="650">
       <c r="C650" t="inlineStr">
         <is>
           <t>Torneo APG</t>
@@ -28496,7 +28506,7 @@
         </is>
       </c>
     </row>
-    <row r="651" hidden="1">
+    <row r="651">
       <c r="C651" t="inlineStr">
         <is>
           <t>Torneo APG</t>
@@ -28540,7 +28550,7 @@
         </is>
       </c>
     </row>
-    <row r="652" hidden="1">
+    <row r="652">
       <c r="C652" t="inlineStr">
         <is>
           <t>Torneo APG</t>
@@ -28584,7 +28594,7 @@
         </is>
       </c>
     </row>
-    <row r="653" hidden="1">
+    <row r="653">
       <c r="C653" t="inlineStr">
         <is>
           <t>Torneo APG</t>
@@ -28628,7 +28638,7 @@
         </is>
       </c>
     </row>
-    <row r="654" hidden="1">
+    <row r="654">
       <c r="B654" t="inlineStr">
         <is>
           <t>Confraternidad/Integración</t>
@@ -28667,7 +28677,7 @@
         </is>
       </c>
     </row>
-    <row r="655" hidden="1">
+    <row r="655">
       <c r="B655" t="inlineStr">
         <is>
           <t>Confraternidad/Integración</t>
@@ -28711,7 +28721,7 @@
         </is>
       </c>
     </row>
-    <row r="656" hidden="1">
+    <row r="656">
       <c r="B656" t="inlineStr">
         <is>
           <t>Confraternidad/Integración</t>
@@ -28755,7 +28765,7 @@
         </is>
       </c>
     </row>
-    <row r="657" hidden="1">
+    <row r="657">
       <c r="C657" t="inlineStr">
         <is>
           <t>Torneo Copa Embajada</t>
@@ -28799,7 +28809,7 @@
         </is>
       </c>
     </row>
-    <row r="658" hidden="1">
+    <row r="658">
       <c r="C658" t="inlineStr">
         <is>
           <t>Torneo Copa Embajada</t>
@@ -28843,7 +28853,7 @@
         </is>
       </c>
     </row>
-    <row r="659" hidden="1">
+    <row r="659">
       <c r="C659" t="inlineStr">
         <is>
           <t>Torneo Copa Embajada</t>
@@ -28892,7 +28902,7 @@
         </is>
       </c>
     </row>
-    <row r="660" hidden="1">
+    <row r="660">
       <c r="C660" t="inlineStr">
         <is>
           <t>Torneo Copa Embajada</t>
@@ -28936,7 +28946,7 @@
         </is>
       </c>
     </row>
-    <row r="661" hidden="1">
+    <row r="661">
       <c r="B661" t="inlineStr">
         <is>
           <t>Campeonato Internacional</t>
@@ -28985,7 +28995,7 @@
         </is>
       </c>
     </row>
-    <row r="662" hidden="1">
+    <row r="662">
       <c r="B662" t="inlineStr">
         <is>
           <t>Campeonato Internacional</t>
@@ -29034,7 +29044,7 @@
         </is>
       </c>
     </row>
-    <row r="663" hidden="1">
+    <row r="663">
       <c r="B663" t="inlineStr">
         <is>
           <t>Campeonato Internacional</t>
@@ -29083,7 +29093,7 @@
         </is>
       </c>
     </row>
-    <row r="664" hidden="1">
+    <row r="664">
       <c r="B664" t="inlineStr">
         <is>
           <t>Campeonato Internacional</t>
@@ -29137,7 +29147,7 @@
         </is>
       </c>
     </row>
-    <row r="665" hidden="1">
+    <row r="665">
       <c r="B665" t="inlineStr">
         <is>
           <t>Campeonato Internacional</t>
@@ -29186,7 +29196,7 @@
         </is>
       </c>
     </row>
-    <row r="666" hidden="1">
+    <row r="666">
       <c r="B666" t="inlineStr">
         <is>
           <t>Campeonato Internacional</t>
@@ -29240,7 +29250,7 @@
         </is>
       </c>
     </row>
-    <row r="667" hidden="1">
+    <row r="667">
       <c r="B667" t="inlineStr">
         <is>
           <t>Campeonato Internacional</t>
@@ -29294,7 +29304,7 @@
         </is>
       </c>
     </row>
-    <row r="668" hidden="1">
+    <row r="668">
       <c r="B668" t="inlineStr">
         <is>
           <t>Campeonato Internacional</t>
@@ -29343,7 +29353,7 @@
         </is>
       </c>
     </row>
-    <row r="669" hidden="1">
+    <row r="669">
       <c r="D669" t="inlineStr">
         <is>
           <t>Torneo de Gateball - Otilia Akiyama &amp; Domingo Nakura</t>
@@ -29382,7 +29392,7 @@
         </is>
       </c>
     </row>
-    <row r="670" hidden="1">
+    <row r="670">
       <c r="D670" t="inlineStr">
         <is>
           <t>Torneo de Gateball - Otilia Akiyama &amp; Domingo Nakura</t>
@@ -29421,7 +29431,7 @@
         </is>
       </c>
     </row>
-    <row r="671" hidden="1">
+    <row r="671">
       <c r="D671" t="inlineStr">
         <is>
           <t>Torneo de Gateball - Otilia Akiyama &amp; Domingo Nakura</t>
@@ -29460,7 +29470,7 @@
         </is>
       </c>
     </row>
-    <row r="672" hidden="1">
+    <row r="672">
       <c r="D672" t="inlineStr">
         <is>
           <t>Torneo de Gateball - Otilia Akiyama &amp; Domingo Nakura</t>
@@ -29499,7 +29509,7 @@
         </is>
       </c>
     </row>
-    <row r="673" hidden="1">
+    <row r="673">
       <c r="C673" t="inlineStr">
         <is>
           <t xml:space="preserve">Torneo Okinawa Kenjinkai </t>
@@ -29543,7 +29553,7 @@
         </is>
       </c>
     </row>
-    <row r="674" hidden="1">
+    <row r="674">
       <c r="C674" t="inlineStr">
         <is>
           <t xml:space="preserve">Torneo Okinawa Kenjinkai </t>
@@ -29587,7 +29597,7 @@
         </is>
       </c>
     </row>
-    <row r="675" hidden="1">
+    <row r="675">
       <c r="C675" t="inlineStr">
         <is>
           <t xml:space="preserve">Torneo Okinawa Kenjinkai </t>
@@ -29631,7 +29641,7 @@
         </is>
       </c>
     </row>
-    <row r="676" hidden="1">
+    <row r="676">
       <c r="C676" t="inlineStr">
         <is>
           <t xml:space="preserve">Torneo Okinawa Kenjinkai </t>
@@ -29675,7 +29685,7 @@
         </is>
       </c>
     </row>
-    <row r="677" hidden="1">
+    <row r="677">
       <c r="C677" t="inlineStr">
         <is>
           <t xml:space="preserve">Torneo Okinawa Kenjinkai </t>
@@ -29719,7 +29729,7 @@
         </is>
       </c>
     </row>
-    <row r="678" hidden="1">
+    <row r="678">
       <c r="C678" t="inlineStr">
         <is>
           <t xml:space="preserve">Torneo Okinawa Kenjinkai </t>
@@ -29763,7 +29773,7 @@
         </is>
       </c>
     </row>
-    <row r="679" hidden="1">
+    <row r="679">
       <c r="C679" t="inlineStr">
         <is>
           <t xml:space="preserve">Torneo Okinawa Kenjinkai </t>
@@ -29807,7 +29817,7 @@
         </is>
       </c>
     </row>
-    <row r="680" hidden="1">
+    <row r="680">
       <c r="C680" t="inlineStr">
         <is>
           <t xml:space="preserve">Torneo Okinawa Kenjinkai </t>
@@ -29851,7 +29861,7 @@
         </is>
       </c>
     </row>
-    <row r="681" hidden="1">
+    <row r="681">
       <c r="C681" t="inlineStr">
         <is>
           <t>Torneo AOPCOOP</t>
@@ -29895,7 +29905,7 @@
         </is>
       </c>
     </row>
-    <row r="682" hidden="1">
+    <row r="682">
       <c r="C682" t="inlineStr">
         <is>
           <t>Torneo AOPCOOP</t>
@@ -29939,7 +29949,7 @@
         </is>
       </c>
     </row>
-    <row r="683" hidden="1">
+    <row r="683">
       <c r="C683" t="inlineStr">
         <is>
           <t>Torneo AOPCOOP</t>
@@ -29983,7 +29993,7 @@
         </is>
       </c>
     </row>
-    <row r="684" hidden="1">
+    <row r="684">
       <c r="C684" t="inlineStr">
         <is>
           <t>Torneo AOPCOOP</t>
@@ -30027,7 +30037,7 @@
         </is>
       </c>
     </row>
-    <row r="685" hidden="1">
+    <row r="685">
       <c r="C685" t="inlineStr">
         <is>
           <t>Torneo AOPCOOP</t>
@@ -30071,7 +30081,7 @@
         </is>
       </c>
     </row>
-    <row r="686" hidden="1">
+    <row r="686">
       <c r="C686" t="inlineStr">
         <is>
           <t>Torneo AOPCOOP</t>
@@ -30115,7 +30125,7 @@
         </is>
       </c>
     </row>
-    <row r="687" hidden="1">
+    <row r="687">
       <c r="C687" t="inlineStr">
         <is>
           <t>Torneo AOPCOOP</t>
@@ -30159,7 +30169,7 @@
         </is>
       </c>
     </row>
-    <row r="688" hidden="1">
+    <row r="688">
       <c r="C688" t="inlineStr">
         <is>
           <t>Torneo AOPCOOP</t>
@@ -30203,7 +30213,7 @@
         </is>
       </c>
     </row>
-    <row r="689" hidden="1">
+    <row r="689">
       <c r="B689" t="inlineStr">
         <is>
           <t>Campeonato Oficial</t>
@@ -30247,7 +30257,7 @@
         </is>
       </c>
     </row>
-    <row r="690" hidden="1">
+    <row r="690">
       <c r="B690" t="inlineStr">
         <is>
           <t>Campeonato Oficial</t>
@@ -30291,7 +30301,7 @@
         </is>
       </c>
     </row>
-    <row r="691" hidden="1">
+    <row r="691">
       <c r="B691" t="inlineStr">
         <is>
           <t>Campeonato Oficial</t>
@@ -30335,7 +30345,7 @@
         </is>
       </c>
     </row>
-    <row r="692" hidden="1">
+    <row r="692">
       <c r="B692" t="inlineStr">
         <is>
           <t>Campeonato Oficial</t>
@@ -30379,7 +30389,7 @@
         </is>
       </c>
     </row>
-    <row r="693" hidden="1">
+    <row r="693">
       <c r="B693" t="inlineStr">
         <is>
           <t>Campeonato Oficial</t>
@@ -30423,7 +30433,7 @@
         </is>
       </c>
     </row>
-    <row r="694" hidden="1">
+    <row r="694">
       <c r="B694" t="inlineStr">
         <is>
           <t>Campeonato Oficial</t>
@@ -30467,7 +30477,7 @@
         </is>
       </c>
     </row>
-    <row r="695" hidden="1">
+    <row r="695">
       <c r="B695" t="inlineStr">
         <is>
           <t>Campeonato Oficial</t>
@@ -30511,7 +30521,7 @@
         </is>
       </c>
     </row>
-    <row r="696" hidden="1">
+    <row r="696">
       <c r="B696" t="inlineStr">
         <is>
           <t>Campeonato Oficial</t>
@@ -30555,7 +30565,7 @@
         </is>
       </c>
     </row>
-    <row r="697" hidden="1">
+    <row r="697">
       <c r="B697" t="inlineStr">
         <is>
           <t>Campeonato Oficial</t>
@@ -30893,7 +30903,7 @@
         </is>
       </c>
     </row>
-    <row r="704" hidden="1">
+    <row r="704">
       <c r="C704" t="inlineStr">
         <is>
           <t>Torneo Nikkei Fujinkai</t>
@@ -30937,7 +30947,7 @@
         </is>
       </c>
     </row>
-    <row r="705" hidden="1">
+    <row r="705">
       <c r="C705" t="inlineStr">
         <is>
           <t>Torneo Nikkei Fujinkai</t>
@@ -30981,7 +30991,7 @@
         </is>
       </c>
     </row>
-    <row r="706" hidden="1">
+    <row r="706">
       <c r="C706" t="inlineStr">
         <is>
           <t>Torneo Nikkei Fujinkai</t>
@@ -31025,7 +31035,7 @@
         </is>
       </c>
     </row>
-    <row r="707" hidden="1">
+    <row r="707">
       <c r="C707" t="inlineStr">
         <is>
           <t>Torneo Nikkei Fujinkai</t>
@@ -31069,7 +31079,7 @@
         </is>
       </c>
     </row>
-    <row r="708" hidden="1">
+    <row r="708">
       <c r="C708" t="inlineStr">
         <is>
           <t>Torneo Nikkei Fujinkai</t>
@@ -31113,7 +31123,7 @@
         </is>
       </c>
     </row>
-    <row r="709" hidden="1">
+    <row r="709">
       <c r="C709" t="inlineStr">
         <is>
           <t>Torneo Nikkei Fujinkai</t>
@@ -31157,7 +31167,7 @@
         </is>
       </c>
     </row>
-    <row r="710" hidden="1">
+    <row r="710">
       <c r="C710" t="inlineStr">
         <is>
           <t>Torneo Yamanashi Shimbokukai</t>
@@ -31201,7 +31211,7 @@
         </is>
       </c>
     </row>
-    <row r="711" hidden="1">
+    <row r="711">
       <c r="C711" t="inlineStr">
         <is>
           <t>Torneo Yamanashi Shimbokukai</t>
@@ -31245,7 +31255,7 @@
         </is>
       </c>
     </row>
-    <row r="712" hidden="1">
+    <row r="712">
       <c r="B712" t="inlineStr">
         <is>
           <t>Campeonato Oficial</t>
@@ -31289,7 +31299,7 @@
         </is>
       </c>
     </row>
-    <row r="713" hidden="1">
+    <row r="713">
       <c r="B713" t="inlineStr">
         <is>
           <t>Campeonato Oficial</t>
@@ -31333,7 +31343,7 @@
         </is>
       </c>
     </row>
-    <row r="714" hidden="1">
+    <row r="714">
       <c r="B714" t="inlineStr">
         <is>
           <t>Campeonato Oficial</t>
@@ -31377,7 +31387,7 @@
         </is>
       </c>
     </row>
-    <row r="715" hidden="1">
+    <row r="715">
       <c r="B715" t="inlineStr">
         <is>
           <t>Campeonato Oficial</t>
@@ -31421,7 +31431,7 @@
         </is>
       </c>
     </row>
-    <row r="716" hidden="1">
+    <row r="716">
       <c r="B716" t="inlineStr">
         <is>
           <t>Campeonato Oficial</t>
@@ -31465,7 +31475,7 @@
         </is>
       </c>
     </row>
-    <row r="717" hidden="1">
+    <row r="717">
       <c r="B717" t="inlineStr">
         <is>
           <t>Campeonato Oficial</t>
@@ -31509,7 +31519,7 @@
         </is>
       </c>
     </row>
-    <row r="718" hidden="1">
+    <row r="718">
       <c r="B718" t="inlineStr">
         <is>
           <t>Campeonato Oficial</t>
@@ -31553,7 +31563,7 @@
         </is>
       </c>
     </row>
-    <row r="719" hidden="1">
+    <row r="719">
       <c r="B719" t="inlineStr">
         <is>
           <t>Campeonato Oficial</t>
@@ -31597,7 +31607,7 @@
         </is>
       </c>
     </row>
-    <row r="720" hidden="1">
+    <row r="720">
       <c r="B720" t="inlineStr">
         <is>
           <t>Campeonato Oficial</t>
@@ -31641,7 +31651,7 @@
         </is>
       </c>
     </row>
-    <row r="721" hidden="1">
+    <row r="721">
       <c r="C721" t="inlineStr">
         <is>
           <t>Torneo Club Aikokai</t>
@@ -31685,7 +31695,7 @@
         </is>
       </c>
     </row>
-    <row r="722" hidden="1">
+    <row r="722">
       <c r="C722" t="inlineStr">
         <is>
           <t>Torneo Club Aikokai</t>
@@ -31729,7 +31739,7 @@
         </is>
       </c>
     </row>
-    <row r="723" hidden="1">
+    <row r="723">
       <c r="C723" t="inlineStr">
         <is>
           <t>Torneo Club Aikokai</t>
@@ -31773,7 +31783,7 @@
         </is>
       </c>
     </row>
-    <row r="724" hidden="1">
+    <row r="724">
       <c r="C724" t="inlineStr">
         <is>
           <t>Torneo Club Aikokai</t>
@@ -31817,7 +31827,7 @@
         </is>
       </c>
     </row>
-    <row r="725" hidden="1">
+    <row r="725">
       <c r="C725" t="inlineStr">
         <is>
           <t>Torneo Club Aikokai</t>
@@ -31861,7 +31871,7 @@
         </is>
       </c>
     </row>
-    <row r="726" hidden="1">
+    <row r="726">
       <c r="C726" t="inlineStr">
         <is>
           <t>Torneo Club Aikokai</t>
@@ -31905,7 +31915,7 @@
         </is>
       </c>
     </row>
-    <row r="727" hidden="1">
+    <row r="727">
       <c r="C727" t="inlineStr">
         <is>
           <t>Torneo Club Aikokai</t>
@@ -31949,7 +31959,7 @@
         </is>
       </c>
     </row>
-    <row r="728" hidden="1">
+    <row r="728">
       <c r="C728" t="inlineStr">
         <is>
           <t>Torneo Club Aikokai</t>
@@ -31993,7 +32003,7 @@
         </is>
       </c>
     </row>
-    <row r="729" hidden="1">
+    <row r="729">
       <c r="B729" t="inlineStr">
         <is>
           <t>Confraternidad/Integración</t>
@@ -32037,7 +32047,7 @@
         </is>
       </c>
     </row>
-    <row r="730" hidden="1">
+    <row r="730">
       <c r="B730" t="inlineStr">
         <is>
           <t>Confraternidad/Integración</t>
@@ -32081,7 +32091,7 @@
         </is>
       </c>
     </row>
-    <row r="731" hidden="1">
+    <row r="731">
       <c r="B731" t="inlineStr">
         <is>
           <t>Confraternidad/Integración</t>
@@ -32125,7 +32135,7 @@
         </is>
       </c>
     </row>
-    <row r="732" hidden="1">
+    <row r="732">
       <c r="B732" t="inlineStr">
         <is>
           <t>Confraternidad/Integración</t>
@@ -32164,7 +32174,7 @@
         </is>
       </c>
     </row>
-    <row r="733" hidden="1">
+    <row r="733">
       <c r="B733" t="inlineStr">
         <is>
           <t>Confraternidad/Integración</t>
@@ -32203,7 +32213,7 @@
         </is>
       </c>
     </row>
-    <row r="734" hidden="1">
+    <row r="734">
       <c r="C734" t="inlineStr">
         <is>
           <t>Torneo Okinawa Fujinkai</t>
@@ -32247,7 +32257,7 @@
         </is>
       </c>
     </row>
-    <row r="735" hidden="1">
+    <row r="735">
       <c r="C735" t="inlineStr">
         <is>
           <t>Torneo Okinawa Fujinkai</t>
@@ -32291,7 +32301,7 @@
         </is>
       </c>
     </row>
-    <row r="736" hidden="1">
+    <row r="736">
       <c r="C736" t="inlineStr">
         <is>
           <t>Torneo Okinawa Fujinkai</t>
@@ -32335,7 +32345,7 @@
         </is>
       </c>
     </row>
-    <row r="737" hidden="1">
+    <row r="737">
       <c r="C737" t="inlineStr">
         <is>
           <t>Torneo Okinawa Fujinkai</t>
@@ -32379,7 +32389,7 @@
         </is>
       </c>
     </row>
-    <row r="738" hidden="1">
+    <row r="738">
       <c r="C738" t="inlineStr">
         <is>
           <t>Juegos de Integración Nikkei</t>
@@ -32423,7 +32433,7 @@
         </is>
       </c>
     </row>
-    <row r="739" hidden="1">
+    <row r="739">
       <c r="C739" t="inlineStr">
         <is>
           <t>Juegos de Integración Nikkei</t>
@@ -32467,7 +32477,7 @@
         </is>
       </c>
     </row>
-    <row r="740" hidden="1">
+    <row r="740">
       <c r="C740" t="inlineStr">
         <is>
           <t>Juegos de Integración Nikkei</t>
@@ -32511,7 +32521,7 @@
         </is>
       </c>
     </row>
-    <row r="741" hidden="1">
+    <row r="741">
       <c r="C741" t="inlineStr">
         <is>
           <t>Juegos de Integración Nikkei</t>
@@ -32555,7 +32565,7 @@
         </is>
       </c>
     </row>
-    <row r="742" hidden="1">
+    <row r="742">
       <c r="C742" t="inlineStr">
         <is>
           <t>Torneo Leoncio Prado</t>
@@ -32599,7 +32609,7 @@
         </is>
       </c>
     </row>
-    <row r="743" hidden="1">
+    <row r="743">
       <c r="C743" t="inlineStr">
         <is>
           <t>Torneo Leoncio Prado</t>
@@ -32643,7 +32653,7 @@
         </is>
       </c>
     </row>
-    <row r="744" hidden="1">
+    <row r="744">
       <c r="C744" t="inlineStr">
         <is>
           <t>Torneo Leoncio Prado</t>
@@ -32687,7 +32697,7 @@
         </is>
       </c>
     </row>
-    <row r="745" hidden="1">
+    <row r="745">
       <c r="C745" t="inlineStr">
         <is>
           <t>Torneo Leoncio Prado</t>
@@ -32731,7 +32741,7 @@
         </is>
       </c>
     </row>
-    <row r="746" hidden="1">
+    <row r="746">
       <c r="B746" t="inlineStr">
         <is>
           <t>Campeonato Internacional</t>
@@ -32774,7 +32784,7 @@
         </is>
       </c>
     </row>
-    <row r="747" hidden="1">
+    <row r="747">
       <c r="B747" t="inlineStr">
         <is>
           <t>Campeonato Internacional</t>
@@ -32822,7 +32832,7 @@
         </is>
       </c>
     </row>
-    <row r="748" hidden="1">
+    <row r="748">
       <c r="B748" t="inlineStr">
         <is>
           <t>Campeonato Internacional</t>
@@ -32870,7 +32880,7 @@
         </is>
       </c>
     </row>
-    <row r="749" hidden="1">
+    <row r="749">
       <c r="B749" t="inlineStr">
         <is>
           <t>Campeonato Internacional</t>
@@ -32918,7 +32928,7 @@
         </is>
       </c>
     </row>
-    <row r="750" hidden="1">
+    <row r="750">
       <c r="C750" t="inlineStr">
         <is>
           <t>Torneo Unión Pacífico</t>
@@ -32961,7 +32971,7 @@
         </is>
       </c>
     </row>
-    <row r="751" hidden="1">
+    <row r="751">
       <c r="C751" t="inlineStr">
         <is>
           <t>Torneo Unión Pacífico</t>
@@ -33004,7 +33014,7 @@
         </is>
       </c>
     </row>
-    <row r="752" hidden="1">
+    <row r="752">
       <c r="C752" t="inlineStr">
         <is>
           <t>Torneo Unión Pacífico</t>
@@ -33047,7 +33057,7 @@
         </is>
       </c>
     </row>
-    <row r="753" hidden="1">
+    <row r="753">
       <c r="C753" t="inlineStr">
         <is>
           <t>Torneo Unión Pacífico</t>
@@ -33090,7 +33100,7 @@
         </is>
       </c>
     </row>
-    <row r="754" hidden="1">
+    <row r="754">
       <c r="C754" t="inlineStr">
         <is>
           <t>Torneo Unión Pacífico</t>
@@ -33133,7 +33143,7 @@
         </is>
       </c>
     </row>
-    <row r="755" hidden="1">
+    <row r="755">
       <c r="C755" t="inlineStr">
         <is>
           <t>Torneo Unión Pacífico</t>
@@ -33176,7 +33186,7 @@
         </is>
       </c>
     </row>
-    <row r="756" hidden="1">
+    <row r="756">
       <c r="C756" t="inlineStr">
         <is>
           <t>Torneo APG</t>
@@ -33219,7 +33229,7 @@
         </is>
       </c>
     </row>
-    <row r="757" hidden="1">
+    <row r="757">
       <c r="C757" t="inlineStr">
         <is>
           <t>Torneo APG</t>
@@ -33262,7 +33272,7 @@
         </is>
       </c>
     </row>
-    <row r="758" hidden="1">
+    <row r="758">
       <c r="C758" t="inlineStr">
         <is>
           <t>Torneo APG</t>
@@ -33305,7 +33315,7 @@
         </is>
       </c>
     </row>
-    <row r="759" hidden="1">
+    <row r="759">
       <c r="C759" t="inlineStr">
         <is>
           <t>Torneo APG</t>
@@ -33520,7 +33530,7 @@
         </is>
       </c>
     </row>
-    <row r="764" hidden="1">
+    <row r="764">
       <c r="C764" t="inlineStr">
         <is>
           <t>Torneo AELU</t>
@@ -33563,7 +33573,7 @@
         </is>
       </c>
     </row>
-    <row r="765" hidden="1">
+    <row r="765">
       <c r="C765" t="inlineStr">
         <is>
           <t>Torneo AELU</t>
@@ -33606,7 +33616,7 @@
         </is>
       </c>
     </row>
-    <row r="766" hidden="1">
+    <row r="766">
       <c r="C766" t="inlineStr">
         <is>
           <t>Torneo AELU</t>
@@ -33649,7 +33659,7 @@
         </is>
       </c>
     </row>
-    <row r="767" hidden="1">
+    <row r="767">
       <c r="C767" t="inlineStr">
         <is>
           <t>Torneo AELU</t>
@@ -33692,7 +33702,7 @@
         </is>
       </c>
     </row>
-    <row r="768" hidden="1">
+    <row r="768">
       <c r="C768" t="inlineStr">
         <is>
           <t>Torneo Copa Embajada</t>
@@ -33735,7 +33745,7 @@
         </is>
       </c>
     </row>
-    <row r="769" hidden="1">
+    <row r="769">
       <c r="C769" t="inlineStr">
         <is>
           <t>Torneo Copa Embajada</t>
@@ -33778,7 +33788,7 @@
         </is>
       </c>
     </row>
-    <row r="770" hidden="1">
+    <row r="770">
       <c r="C770" t="inlineStr">
         <is>
           <t>Torneo Copa Embajada</t>
@@ -33821,7 +33831,7 @@
         </is>
       </c>
     </row>
-    <row r="771" hidden="1">
+    <row r="771">
       <c r="C771" t="inlineStr">
         <is>
           <t>Torneo Copa Embajada</t>
@@ -33864,7 +33874,7 @@
         </is>
       </c>
     </row>
-    <row r="772" hidden="1">
+    <row r="772">
       <c r="C772" t="inlineStr">
         <is>
           <t>Torneo Leoncio Prado</t>
@@ -33907,7 +33917,7 @@
         </is>
       </c>
     </row>
-    <row r="773" hidden="1">
+    <row r="773">
       <c r="C773" t="inlineStr">
         <is>
           <t>Torneo Leoncio Prado</t>
@@ -33950,7 +33960,7 @@
         </is>
       </c>
     </row>
-    <row r="774" hidden="1">
+    <row r="774">
       <c r="C774" t="inlineStr">
         <is>
           <t>Torneo Leoncio Prado</t>
@@ -33993,7 +34003,7 @@
         </is>
       </c>
     </row>
-    <row r="775" hidden="1">
+    <row r="775">
       <c r="C775" t="inlineStr">
         <is>
           <t>Torneo Leoncio Prado</t>
@@ -34036,7 +34046,7 @@
         </is>
       </c>
     </row>
-    <row r="776" hidden="1">
+    <row r="776">
       <c r="C776" t="inlineStr">
         <is>
           <t>Torneo Okinawa Kenjinkai</t>
@@ -34079,7 +34089,7 @@
         </is>
       </c>
     </row>
-    <row r="777" hidden="1">
+    <row r="777">
       <c r="C777" t="inlineStr">
         <is>
           <t>Torneo Okinawa Kenjinkai</t>
@@ -34122,7 +34132,7 @@
         </is>
       </c>
     </row>
-    <row r="778" hidden="1">
+    <row r="778">
       <c r="C778" t="inlineStr">
         <is>
           <t>Torneo Okinawa Kenjinkai</t>
@@ -34165,7 +34175,7 @@
         </is>
       </c>
     </row>
-    <row r="779" hidden="1">
+    <row r="779">
       <c r="C779" t="inlineStr">
         <is>
           <t>Torneo Okinawa Kenjinkai</t>
@@ -34208,7 +34218,7 @@
         </is>
       </c>
     </row>
-    <row r="780" hidden="1">
+    <row r="780">
       <c r="C780" t="inlineStr">
         <is>
           <t>Torneo Okinawa Kenjinkai</t>
@@ -34251,7 +34261,7 @@
         </is>
       </c>
     </row>
-    <row r="781" hidden="1">
+    <row r="781">
       <c r="C781" t="inlineStr">
         <is>
           <t>Torneo Okinawa Kenjinkai</t>
@@ -34294,7 +34304,7 @@
         </is>
       </c>
     </row>
-    <row r="782" hidden="1">
+    <row r="782">
       <c r="C782" t="inlineStr">
         <is>
           <t>Torneo Okinawa Kenjinkai</t>
@@ -34337,7 +34347,7 @@
         </is>
       </c>
     </row>
-    <row r="783" hidden="1">
+    <row r="783">
       <c r="C783" t="inlineStr">
         <is>
           <t>Torneo Okinawa Kenjinkai</t>
@@ -34380,7 +34390,7 @@
         </is>
       </c>
     </row>
-    <row r="784" hidden="1">
+    <row r="784">
       <c r="C784" t="inlineStr">
         <is>
           <t>Torneo AOPCOOP</t>
@@ -34423,7 +34433,7 @@
         </is>
       </c>
     </row>
-    <row r="785" hidden="1">
+    <row r="785">
       <c r="C785" t="inlineStr">
         <is>
           <t>Torneo AOPCOOP</t>
@@ -34466,7 +34476,7 @@
         </is>
       </c>
     </row>
-    <row r="786" hidden="1">
+    <row r="786">
       <c r="C786" t="inlineStr">
         <is>
           <t>Torneo AOPCOOP</t>
@@ -34509,7 +34519,7 @@
         </is>
       </c>
     </row>
-    <row r="787" hidden="1">
+    <row r="787">
       <c r="C787" t="inlineStr">
         <is>
           <t>Torneo AOPCOOP</t>
@@ -34552,7 +34562,7 @@
         </is>
       </c>
     </row>
-    <row r="788" hidden="1">
+    <row r="788">
       <c r="C788" t="inlineStr">
         <is>
           <t>Torneo AOPCOOP</t>
@@ -34595,7 +34605,7 @@
         </is>
       </c>
     </row>
-    <row r="789" hidden="1">
+    <row r="789">
       <c r="C789" t="inlineStr">
         <is>
           <t>Torneo AOPCOOP</t>
@@ -34638,7 +34648,7 @@
         </is>
       </c>
     </row>
-    <row r="790" hidden="1">
+    <row r="790">
       <c r="C790" t="inlineStr">
         <is>
           <t>Torneo AOPCOOP</t>
@@ -34681,7 +34691,7 @@
         </is>
       </c>
     </row>
-    <row r="791" hidden="1">
+    <row r="791">
       <c r="C791" t="inlineStr">
         <is>
           <t>Torneo Inmigración Japonesa</t>
@@ -34724,7 +34734,7 @@
         </is>
       </c>
     </row>
-    <row r="792" hidden="1">
+    <row r="792">
       <c r="C792" t="inlineStr">
         <is>
           <t>Torneo Inmigración Japonesa</t>
@@ -34767,7 +34777,7 @@
         </is>
       </c>
     </row>
-    <row r="793" hidden="1">
+    <row r="793">
       <c r="C793" t="inlineStr">
         <is>
           <t>Torneo Inmigración Japonesa</t>
@@ -34810,7 +34820,7 @@
         </is>
       </c>
     </row>
-    <row r="794" hidden="1">
+    <row r="794">
       <c r="C794" t="inlineStr">
         <is>
           <t>Torneo Inmigración Japonesa</t>
@@ -34853,7 +34863,7 @@
         </is>
       </c>
     </row>
-    <row r="795" hidden="1">
+    <row r="795">
       <c r="C795" t="inlineStr">
         <is>
           <t>Torneo Nishihara Chojinkai</t>
@@ -34896,7 +34906,7 @@
         </is>
       </c>
     </row>
-    <row r="796" hidden="1">
+    <row r="796">
       <c r="C796" t="inlineStr">
         <is>
           <t>Torneo Nishihara Chojinkai</t>
@@ -34939,7 +34949,7 @@
         </is>
       </c>
     </row>
-    <row r="797" hidden="1">
+    <row r="797">
       <c r="B797" t="inlineStr">
         <is>
           <t>Campeonato Oficial</t>
@@ -34982,7 +34992,7 @@
         </is>
       </c>
     </row>
-    <row r="798" hidden="1">
+    <row r="798">
       <c r="B798" t="inlineStr">
         <is>
           <t>Campeonato Oficial</t>
@@ -35025,7 +35035,7 @@
         </is>
       </c>
     </row>
-    <row r="799" hidden="1">
+    <row r="799">
       <c r="B799" t="inlineStr">
         <is>
           <t>Campeonato Oficial</t>
@@ -35068,7 +35078,7 @@
         </is>
       </c>
     </row>
-    <row r="800" hidden="1">
+    <row r="800">
       <c r="B800" t="inlineStr">
         <is>
           <t>Campeonato Oficial</t>
@@ -35111,7 +35121,7 @@
         </is>
       </c>
     </row>
-    <row r="801" hidden="1">
+    <row r="801">
       <c r="B801" t="inlineStr">
         <is>
           <t>Campeonato Oficial</t>
@@ -35154,7 +35164,7 @@
         </is>
       </c>
     </row>
-    <row r="802" hidden="1">
+    <row r="802">
       <c r="B802" t="inlineStr">
         <is>
           <t>Campeonato Oficial</t>
@@ -35197,7 +35207,12 @@
         </is>
       </c>
     </row>
-    <row r="803" hidden="1">
+    <row r="803">
+      <c r="B803" t="inlineStr">
+        <is>
+          <t>Confraternidad/Integración</t>
+        </is>
+      </c>
       <c r="D803" t="inlineStr">
         <is>
           <t>Torneo Confraternidad AELU</t>
@@ -35235,7 +35250,12 @@
         </is>
       </c>
     </row>
-    <row r="804" hidden="1">
+    <row r="804">
+      <c r="B804" t="inlineStr">
+        <is>
+          <t>Confraternidad/Integración</t>
+        </is>
+      </c>
       <c r="D804" t="inlineStr">
         <is>
           <t>Torneo Confraternidad AELU</t>
@@ -35273,7 +35293,12 @@
         </is>
       </c>
     </row>
-    <row r="805" hidden="1">
+    <row r="805">
+      <c r="B805" t="inlineStr">
+        <is>
+          <t>Confraternidad/Integración</t>
+        </is>
+      </c>
       <c r="D805" t="inlineStr">
         <is>
           <t>Torneo Confraternidad AELU</t>
@@ -35307,7 +35332,7 @@
         </is>
       </c>
     </row>
-    <row r="806" hidden="1">
+    <row r="806">
       <c r="C806" t="inlineStr">
         <is>
           <t>Torneo Nikkei Fujinkai</t>
@@ -35350,7 +35375,7 @@
         </is>
       </c>
     </row>
-    <row r="807" hidden="1">
+    <row r="807">
       <c r="C807" t="inlineStr">
         <is>
           <t>Torneo Nikkei Fujinkai</t>
@@ -35393,7 +35418,7 @@
         </is>
       </c>
     </row>
-    <row r="808" hidden="1">
+    <row r="808">
       <c r="C808" t="inlineStr">
         <is>
           <t>Torneo Nikkei Fujinkai</t>
@@ -35436,7 +35461,7 @@
         </is>
       </c>
     </row>
-    <row r="809" hidden="1">
+    <row r="809">
       <c r="C809" t="inlineStr">
         <is>
           <t>Torneo Nikkei Fujinkai</t>
@@ -35479,7 +35504,7 @@
         </is>
       </c>
     </row>
-    <row r="810" hidden="1">
+    <row r="810">
       <c r="C810" t="inlineStr">
         <is>
           <t>Torneo Nikkei Fujinkai</t>
@@ -35522,7 +35547,7 @@
         </is>
       </c>
     </row>
-    <row r="811" hidden="1">
+    <row r="811">
       <c r="C811" t="inlineStr">
         <is>
           <t>Torneo Nikkei Fujinkai</t>
@@ -35565,7 +35590,7 @@
         </is>
       </c>
     </row>
-    <row r="812" hidden="1">
+    <row r="812">
       <c r="C812" t="inlineStr">
         <is>
           <t>Torneo Yamanashi Shimbokukai</t>
@@ -35608,7 +35633,7 @@
         </is>
       </c>
     </row>
-    <row r="813" hidden="1">
+    <row r="813">
       <c r="C813" t="inlineStr">
         <is>
           <t>Torneo Yamanashi Shimbokukai</t>
@@ -35651,7 +35676,7 @@
         </is>
       </c>
     </row>
-    <row r="814" hidden="1">
+    <row r="814">
       <c r="C814" t="inlineStr">
         <is>
           <t>Campeonato Mario Akamine</t>
@@ -35689,7 +35714,7 @@
         </is>
       </c>
     </row>
-    <row r="815" hidden="1">
+    <row r="815">
       <c r="C815" t="inlineStr">
         <is>
           <t>Campeonato Mario Akamine</t>
@@ -35727,7 +35752,7 @@
         </is>
       </c>
     </row>
-    <row r="816" hidden="1">
+    <row r="816">
       <c r="C816" t="inlineStr">
         <is>
           <t>Campeonato Mario Akamine</t>
@@ -35765,7 +35790,7 @@
         </is>
       </c>
     </row>
-    <row r="817" hidden="1">
+    <row r="817">
       <c r="C817" t="inlineStr">
         <is>
           <t>Campeonato Mario Akamine</t>
@@ -35803,7 +35828,7 @@
         </is>
       </c>
     </row>
-    <row r="818" hidden="1">
+    <row r="818">
       <c r="C818" t="inlineStr">
         <is>
           <t>Campeonato Mario Akamine</t>
@@ -35841,7 +35866,7 @@
         </is>
       </c>
     </row>
-    <row r="819" hidden="1">
+    <row r="819">
       <c r="C819" t="inlineStr">
         <is>
           <t>Campeonato Mario Akamine</t>
@@ -35879,7 +35904,7 @@
         </is>
       </c>
     </row>
-    <row r="820" hidden="1">
+    <row r="820">
       <c r="C820" t="inlineStr">
         <is>
           <t>Torneo AELU</t>
@@ -35922,7 +35947,7 @@
         </is>
       </c>
     </row>
-    <row r="821" hidden="1">
+    <row r="821">
       <c r="C821" t="inlineStr">
         <is>
           <t>Torneo AELU</t>
@@ -35965,7 +35990,7 @@
         </is>
       </c>
     </row>
-    <row r="822" hidden="1">
+    <row r="822">
       <c r="C822" t="inlineStr">
         <is>
           <t>Torneo AELU</t>
@@ -36008,7 +36033,7 @@
         </is>
       </c>
     </row>
-    <row r="823" hidden="1">
+    <row r="823">
       <c r="C823" t="inlineStr">
         <is>
           <t>Torneo AELU</t>
@@ -36051,7 +36076,7 @@
         </is>
       </c>
     </row>
-    <row r="824" hidden="1">
+    <row r="824">
       <c r="C824" t="inlineStr">
         <is>
           <t>Torneo AELU</t>
@@ -36094,7 +36119,7 @@
         </is>
       </c>
     </row>
-    <row r="825" hidden="1">
+    <row r="825">
       <c r="C825" t="inlineStr">
         <is>
           <t>Torneo AELU</t>
@@ -36137,7 +36162,7 @@
         </is>
       </c>
     </row>
-    <row r="826" hidden="1">
+    <row r="826">
       <c r="C826" t="inlineStr">
         <is>
           <t>Torneo AELU</t>
@@ -36180,7 +36205,7 @@
         </is>
       </c>
     </row>
-    <row r="827" hidden="1">
+    <row r="827">
       <c r="C827" t="inlineStr">
         <is>
           <t>Torneo AELU</t>
@@ -36223,7 +36248,7 @@
         </is>
       </c>
     </row>
-    <row r="828" hidden="1">
+    <row r="828">
       <c r="C828" t="inlineStr">
         <is>
           <t>Torneo Okinawa Fujinkai</t>
@@ -36266,7 +36291,7 @@
         </is>
       </c>
     </row>
-    <row r="829" hidden="1">
+    <row r="829">
       <c r="C829" t="inlineStr">
         <is>
           <t>Torneo Okinawa Fujinkai</t>
@@ -36309,7 +36334,7 @@
         </is>
       </c>
     </row>
-    <row r="830" hidden="1">
+    <row r="830">
       <c r="C830" t="inlineStr">
         <is>
           <t>Torneo Okinawa Fujinkai</t>
@@ -36352,7 +36377,7 @@
         </is>
       </c>
     </row>
-    <row r="831" hidden="1">
+    <row r="831">
       <c r="C831" t="inlineStr">
         <is>
           <t>Torneo Okinawa Fujinkai</t>
@@ -36395,7 +36420,7 @@
         </is>
       </c>
     </row>
-    <row r="832" hidden="1">
+    <row r="832">
       <c r="C832" t="inlineStr">
         <is>
           <t>Torneo Okinawa Fujinkai</t>
@@ -36438,7 +36463,7 @@
         </is>
       </c>
     </row>
-    <row r="833" hidden="1">
+    <row r="833">
       <c r="C833" t="inlineStr">
         <is>
           <t>Torneo Okinawa Fujinkai</t>
@@ -36481,7 +36506,7 @@
         </is>
       </c>
     </row>
-    <row r="834" hidden="1">
+    <row r="834">
       <c r="C834" t="inlineStr">
         <is>
           <t>Torneo Okinawa Fujinkai</t>
@@ -36524,7 +36549,7 @@
         </is>
       </c>
     </row>
-    <row r="835" hidden="1">
+    <row r="835">
       <c r="C835" t="inlineStr">
         <is>
           <t>Torneo Okinawa Fujinkai</t>
@@ -36567,7 +36592,7 @@
         </is>
       </c>
     </row>
-    <row r="836" hidden="1">
+    <row r="836">
       <c r="C836" t="inlineStr">
         <is>
           <t>Juegos de Integración Nikkei</t>
@@ -36610,7 +36635,7 @@
         </is>
       </c>
     </row>
-    <row r="837" hidden="1">
+    <row r="837">
       <c r="C837" t="inlineStr">
         <is>
           <t>Juegos de Integración Nikkei</t>
@@ -36653,7 +36678,7 @@
         </is>
       </c>
     </row>
-    <row r="838" hidden="1">
+    <row r="838">
       <c r="C838" t="inlineStr">
         <is>
           <t>Juegos de Integración Nikkei</t>
@@ -36696,7 +36721,7 @@
         </is>
       </c>
     </row>
-    <row r="839" hidden="1">
+    <row r="839">
       <c r="C839" t="inlineStr">
         <is>
           <t>Juegos de Integración Nikkei</t>
@@ -36739,7 +36764,7 @@
         </is>
       </c>
     </row>
-    <row r="840" hidden="1">
+    <row r="840">
       <c r="C840" t="inlineStr">
         <is>
           <t>Juegos de Integración Nikkei</t>
@@ -36782,7 +36807,7 @@
         </is>
       </c>
     </row>
-    <row r="841" hidden="1">
+    <row r="841">
       <c r="D841" t="inlineStr">
         <is>
           <t>Torneo Nocturno de Verano</t>
@@ -36815,7 +36840,7 @@
         </is>
       </c>
     </row>
-    <row r="842" hidden="1">
+    <row r="842">
       <c r="D842" t="inlineStr">
         <is>
           <t>Torneo Nocturno de Verano</t>
@@ -36848,7 +36873,7 @@
         </is>
       </c>
     </row>
-    <row r="843" hidden="1">
+    <row r="843">
       <c r="D843" t="inlineStr">
         <is>
           <t>Torneo Nocturno de Verano</t>
@@ -36881,7 +36906,7 @@
         </is>
       </c>
     </row>
-    <row r="844" hidden="1">
+    <row r="844">
       <c r="D844" t="inlineStr">
         <is>
           <t>Torneo Nocturno de Verano</t>
@@ -36914,7 +36939,7 @@
         </is>
       </c>
     </row>
-    <row r="845" hidden="1">
+    <row r="845">
       <c r="D845" t="inlineStr">
         <is>
           <t>Torneo Nocturno de Verano</t>
@@ -36947,7 +36972,7 @@
         </is>
       </c>
     </row>
-    <row r="846" hidden="1">
+    <row r="846">
       <c r="D846" t="inlineStr">
         <is>
           <t>Torneo Nocturno de Verano</t>
@@ -36980,7 +37005,7 @@
         </is>
       </c>
     </row>
-    <row r="847" hidden="1">
+    <row r="847">
       <c r="C847" t="inlineStr">
         <is>
           <t>Torneo APG</t>
@@ -37023,7 +37048,7 @@
         </is>
       </c>
     </row>
-    <row r="848" hidden="1">
+    <row r="848">
       <c r="C848" t="inlineStr">
         <is>
           <t>Torneo APG</t>
@@ -37066,7 +37091,7 @@
         </is>
       </c>
     </row>
-    <row r="849" hidden="1">
+    <row r="849">
       <c r="C849" t="inlineStr">
         <is>
           <t>Torneo APG</t>
@@ -37109,7 +37134,7 @@
         </is>
       </c>
     </row>
-    <row r="850" hidden="1">
+    <row r="850">
       <c r="C850" t="inlineStr">
         <is>
           <t>Torneo APG</t>
@@ -37152,7 +37177,12 @@
         </is>
       </c>
     </row>
-    <row r="851" hidden="1">
+    <row r="851">
+      <c r="B851" t="inlineStr">
+        <is>
+          <t>Confraternidad/Integración</t>
+        </is>
+      </c>
       <c r="D851" t="inlineStr">
         <is>
           <t>Torneo de Integración "Nuevos Valores"</t>
@@ -37190,7 +37220,12 @@
         </is>
       </c>
     </row>
-    <row r="852" hidden="1">
+    <row r="852">
+      <c r="B852" t="inlineStr">
+        <is>
+          <t>Confraternidad/Integración</t>
+        </is>
+      </c>
       <c r="D852" t="inlineStr">
         <is>
           <t>Torneo de Integración "Nuevos Valores"</t>
@@ -37228,7 +37263,7 @@
         </is>
       </c>
     </row>
-    <row r="853" hidden="1">
+    <row r="853">
       <c r="C853" t="inlineStr">
         <is>
           <t>Torneo AELU</t>
@@ -37271,7 +37306,7 @@
         </is>
       </c>
     </row>
-    <row r="854" hidden="1">
+    <row r="854">
       <c r="C854" t="inlineStr">
         <is>
           <t>Torneo AELU</t>
@@ -37314,7 +37349,7 @@
         </is>
       </c>
     </row>
-    <row r="855" hidden="1">
+    <row r="855">
       <c r="C855" t="inlineStr">
         <is>
           <t>Torneo AELU</t>
@@ -37357,7 +37392,7 @@
         </is>
       </c>
     </row>
-    <row r="856" hidden="1">
+    <row r="856">
       <c r="C856" t="inlineStr">
         <is>
           <t>Torneo AELU</t>
@@ -37400,7 +37435,7 @@
         </is>
       </c>
     </row>
-    <row r="857" hidden="1">
+    <row r="857">
       <c r="C857" t="inlineStr">
         <is>
           <t>Torneo Copa Embajada</t>
@@ -37443,7 +37478,7 @@
         </is>
       </c>
     </row>
-    <row r="858" hidden="1">
+    <row r="858">
       <c r="C858" t="inlineStr">
         <is>
           <t>Torneo Copa Embajada</t>
@@ -37486,7 +37521,7 @@
         </is>
       </c>
     </row>
-    <row r="859" hidden="1">
+    <row r="859">
       <c r="C859" t="inlineStr">
         <is>
           <t>Torneo Copa Embajada</t>
@@ -37529,7 +37564,7 @@
         </is>
       </c>
     </row>
-    <row r="860" hidden="1">
+    <row r="860">
       <c r="C860" t="inlineStr">
         <is>
           <t>Torneo Copa Embajada</t>
@@ -37572,7 +37607,7 @@
         </is>
       </c>
     </row>
-    <row r="861" hidden="1">
+    <row r="861">
       <c r="C861" t="inlineStr">
         <is>
           <t>Torneo Shizuoka Kenjinkai</t>
@@ -37610,7 +37645,7 @@
         </is>
       </c>
     </row>
-    <row r="862" hidden="1">
+    <row r="862">
       <c r="C862" t="inlineStr">
         <is>
           <t>Torneo Shizuoka Kenjinkai</t>
@@ -37648,7 +37683,7 @@
         </is>
       </c>
     </row>
-    <row r="863" hidden="1">
+    <row r="863">
       <c r="C863" t="inlineStr">
         <is>
           <t>Torneo Shizuoka Kenjinkai</t>
@@ -37686,7 +37721,7 @@
         </is>
       </c>
     </row>
-    <row r="864" hidden="1">
+    <row r="864">
       <c r="C864" t="inlineStr">
         <is>
           <t>Torneo Shizuoka Kenjinkai</t>
@@ -37724,7 +37759,7 @@
         </is>
       </c>
     </row>
-    <row r="865" hidden="1">
+    <row r="865">
       <c r="C865" t="inlineStr">
         <is>
           <t>Torneo Shizuoka Kenjinkai</t>
@@ -37762,7 +37797,7 @@
         </is>
       </c>
     </row>
-    <row r="866" hidden="1">
+    <row r="866">
       <c r="C866" t="inlineStr">
         <is>
           <t>Torneo Shizuoka Kenjinkai</t>
@@ -37800,7 +37835,7 @@
         </is>
       </c>
     </row>
-    <row r="867" hidden="1">
+    <row r="867">
       <c r="C867" t="inlineStr">
         <is>
           <t>Torneo Okinawa Kenjinkai</t>
@@ -37843,7 +37878,7 @@
         </is>
       </c>
     </row>
-    <row r="868" hidden="1">
+    <row r="868">
       <c r="C868" t="inlineStr">
         <is>
           <t>Torneo Okinawa Kenjinkai</t>
@@ -37886,7 +37921,7 @@
         </is>
       </c>
     </row>
-    <row r="869" hidden="1">
+    <row r="869">
       <c r="C869" t="inlineStr">
         <is>
           <t>Torneo Okinawa Kenjinkai</t>
@@ -37929,7 +37964,7 @@
         </is>
       </c>
     </row>
-    <row r="870" hidden="1">
+    <row r="870">
       <c r="C870" t="inlineStr">
         <is>
           <t>Torneo Okinawa Kenjinkai</t>
@@ -37972,7 +38007,7 @@
         </is>
       </c>
     </row>
-    <row r="871" hidden="1">
+    <row r="871">
       <c r="C871" t="inlineStr">
         <is>
           <t>Torneo Okinawa Kenjinkai</t>
@@ -38015,7 +38050,7 @@
         </is>
       </c>
     </row>
-    <row r="872" hidden="1">
+    <row r="872">
       <c r="C872" t="inlineStr">
         <is>
           <t>Torneo Okinawa Kenjinkai</t>
@@ -38058,7 +38093,7 @@
         </is>
       </c>
     </row>
-    <row r="873" hidden="1">
+    <row r="873">
       <c r="C873" t="inlineStr">
         <is>
           <t>Torneo Okinawa Kenjinkai</t>
@@ -38101,7 +38136,7 @@
         </is>
       </c>
     </row>
-    <row r="874" hidden="1">
+    <row r="874">
       <c r="C874" t="inlineStr">
         <is>
           <t>Torneo Okinawa Kenjinkai</t>
@@ -38144,7 +38179,7 @@
         </is>
       </c>
     </row>
-    <row r="875" hidden="1">
+    <row r="875">
       <c r="B875" t="inlineStr">
         <is>
           <t>Confraternidad/Integración</t>
@@ -38182,7 +38217,7 @@
         </is>
       </c>
     </row>
-    <row r="876" hidden="1">
+    <row r="876">
       <c r="B876" t="inlineStr">
         <is>
           <t>Confraternidad/Integración</t>
@@ -38220,7 +38255,7 @@
         </is>
       </c>
     </row>
-    <row r="877" hidden="1">
+    <row r="877">
       <c r="B877" t="inlineStr">
         <is>
           <t>Confraternidad/Integración</t>
@@ -38258,7 +38293,7 @@
         </is>
       </c>
     </row>
-    <row r="878" hidden="1">
+    <row r="878">
       <c r="B878" t="inlineStr">
         <is>
           <t>Confraternidad/Integración</t>
@@ -38296,7 +38331,7 @@
         </is>
       </c>
     </row>
-    <row r="879" hidden="1">
+    <row r="879">
       <c r="C879" t="inlineStr">
         <is>
           <t>Torneo AOPCOOP</t>
@@ -38339,7 +38374,7 @@
         </is>
       </c>
     </row>
-    <row r="880" hidden="1">
+    <row r="880">
       <c r="C880" t="inlineStr">
         <is>
           <t>Torneo AOPCOOP</t>
@@ -38382,7 +38417,7 @@
         </is>
       </c>
     </row>
-    <row r="881" hidden="1">
+    <row r="881">
       <c r="C881" t="inlineStr">
         <is>
           <t>Torneo AOPCOOP</t>
@@ -38425,7 +38460,7 @@
         </is>
       </c>
     </row>
-    <row r="882" hidden="1">
+    <row r="882">
       <c r="C882" t="inlineStr">
         <is>
           <t>Torneo AOPCOOP</t>
@@ -38468,7 +38503,7 @@
         </is>
       </c>
     </row>
-    <row r="883" hidden="1">
+    <row r="883">
       <c r="C883" t="inlineStr">
         <is>
           <t>Torneo AOPCOOP</t>
@@ -38511,7 +38546,7 @@
         </is>
       </c>
     </row>
-    <row r="884" hidden="1">
+    <row r="884">
       <c r="C884" t="inlineStr">
         <is>
           <t>Torneo AOPCOOP</t>
@@ -38554,7 +38589,7 @@
         </is>
       </c>
     </row>
-    <row r="885" hidden="1">
+    <row r="885">
       <c r="B885" t="inlineStr">
         <is>
           <t>Campeonato Oficial</t>
@@ -38597,7 +38632,7 @@
         </is>
       </c>
     </row>
-    <row r="886" hidden="1">
+    <row r="886">
       <c r="B886" t="inlineStr">
         <is>
           <t>Campeonato Oficial</t>
@@ -38640,7 +38675,7 @@
         </is>
       </c>
     </row>
-    <row r="887" hidden="1">
+    <row r="887">
       <c r="B887" t="inlineStr">
         <is>
           <t>Campeonato Oficial</t>
@@ -38683,7 +38718,7 @@
         </is>
       </c>
     </row>
-    <row r="888" hidden="1">
+    <row r="888">
       <c r="B888" t="inlineStr">
         <is>
           <t>Campeonato Oficial</t>
@@ -38726,7 +38761,7 @@
         </is>
       </c>
     </row>
-    <row r="889" hidden="1">
+    <row r="889">
       <c r="B889" t="inlineStr">
         <is>
           <t>Campeonato Oficial</t>
@@ -38769,7 +38804,7 @@
         </is>
       </c>
     </row>
-    <row r="890" hidden="1">
+    <row r="890">
       <c r="B890" t="inlineStr">
         <is>
           <t>Campeonato Oficial</t>
@@ -38812,7 +38847,7 @@
         </is>
       </c>
     </row>
-    <row r="891" hidden="1">
+    <row r="891">
       <c r="C891" t="inlineStr">
         <is>
           <t>Torneo Odawara</t>
@@ -38855,7 +38890,7 @@
         </is>
       </c>
     </row>
-    <row r="892" hidden="1">
+    <row r="892">
       <c r="C892" t="inlineStr">
         <is>
           <t>Torneo Odawara</t>
@@ -38898,7 +38933,7 @@
         </is>
       </c>
     </row>
-    <row r="893" hidden="1">
+    <row r="893">
       <c r="C893" t="inlineStr">
         <is>
           <t>Torneo Odawara</t>
@@ -38941,7 +38976,7 @@
         </is>
       </c>
     </row>
-    <row r="894" hidden="1">
+    <row r="894">
       <c r="C894" t="inlineStr">
         <is>
           <t>Torneo Odawara</t>
@@ -38984,7 +39019,7 @@
         </is>
       </c>
     </row>
-    <row r="895" hidden="1">
+    <row r="895">
       <c r="C895" t="inlineStr">
         <is>
           <t>Torneo Odawara</t>
@@ -39027,7 +39062,7 @@
         </is>
       </c>
     </row>
-    <row r="896" hidden="1">
+    <row r="896">
       <c r="C896" t="inlineStr">
         <is>
           <t>Torneo Odawara</t>
@@ -39070,7 +39105,7 @@
         </is>
       </c>
     </row>
-    <row r="897" hidden="1">
+    <row r="897">
       <c r="C897" t="inlineStr">
         <is>
           <t>Torneo Odawara</t>
@@ -39113,7 +39148,7 @@
         </is>
       </c>
     </row>
-    <row r="898" hidden="1">
+    <row r="898">
       <c r="C898" t="inlineStr">
         <is>
           <t>Torneo Odawara</t>
@@ -39156,7 +39191,7 @@
         </is>
       </c>
     </row>
-    <row r="899" hidden="1">
+    <row r="899">
       <c r="C899" t="inlineStr">
         <is>
           <t>Torneo Kyodai</t>
@@ -39199,7 +39234,7 @@
         </is>
       </c>
     </row>
-    <row r="900" hidden="1">
+    <row r="900">
       <c r="C900" t="inlineStr">
         <is>
           <t>Torneo Kyodai</t>
@@ -39242,7 +39277,7 @@
         </is>
       </c>
     </row>
-    <row r="901" hidden="1">
+    <row r="901">
       <c r="C901" t="inlineStr">
         <is>
           <t>Torneo Kyodai</t>
@@ -39285,7 +39320,7 @@
         </is>
       </c>
     </row>
-    <row r="902" hidden="1">
+    <row r="902">
       <c r="C902" t="inlineStr">
         <is>
           <t>Torneo Kyodai</t>
@@ -39328,7 +39363,7 @@
         </is>
       </c>
     </row>
-    <row r="903" hidden="1">
+    <row r="903">
       <c r="C903" t="inlineStr">
         <is>
           <t>Torneo Kyodai</t>
@@ -39371,7 +39406,7 @@
         </is>
       </c>
     </row>
-    <row r="904" hidden="1">
+    <row r="904">
       <c r="C904" t="inlineStr">
         <is>
           <t>Torneo Kyodai</t>
@@ -39414,7 +39449,7 @@
         </is>
       </c>
     </row>
-    <row r="905" hidden="1">
+    <row r="905">
       <c r="C905" t="inlineStr">
         <is>
           <t>Torneo Kyodai</t>
@@ -39457,7 +39492,7 @@
         </is>
       </c>
     </row>
-    <row r="906" hidden="1">
+    <row r="906">
       <c r="C906" t="inlineStr">
         <is>
           <t>Torneo Kyodai</t>
@@ -39500,7 +39535,7 @@
         </is>
       </c>
     </row>
-    <row r="907" hidden="1">
+    <row r="907">
       <c r="C907" t="inlineStr">
         <is>
           <t>Torneo Nikkei Fujinkai</t>
@@ -39543,7 +39578,7 @@
         </is>
       </c>
     </row>
-    <row r="908" hidden="1">
+    <row r="908">
       <c r="C908" t="inlineStr">
         <is>
           <t>Torneo Nikkei Fujinkai</t>
@@ -39586,7 +39621,7 @@
         </is>
       </c>
     </row>
-    <row r="909" hidden="1">
+    <row r="909">
       <c r="C909" t="inlineStr">
         <is>
           <t>Torneo Nikkei Fujinkai</t>
@@ -39629,7 +39664,7 @@
         </is>
       </c>
     </row>
-    <row r="910" hidden="1">
+    <row r="910">
       <c r="C910" t="inlineStr">
         <is>
           <t>Torneo Nikkei Fujinkai</t>
@@ -39672,7 +39707,7 @@
         </is>
       </c>
     </row>
-    <row r="911" hidden="1">
+    <row r="911">
       <c r="C911" t="inlineStr">
         <is>
           <t>Torneo Nikkei Fujinkai</t>
@@ -39715,7 +39750,7 @@
         </is>
       </c>
     </row>
-    <row r="912" hidden="1">
+    <row r="912">
       <c r="C912" t="inlineStr">
         <is>
           <t>Torneo Nikkei Fujinkai</t>
@@ -39758,7 +39793,7 @@
         </is>
       </c>
     </row>
-    <row r="913" hidden="1">
+    <row r="913">
       <c r="C913" t="inlineStr">
         <is>
           <t>Torneo Yamanashi Shimbokukai</t>
@@ -39801,7 +39836,7 @@
         </is>
       </c>
     </row>
-    <row r="914" hidden="1">
+    <row r="914">
       <c r="C914" t="inlineStr">
         <is>
           <t>Torneo Yamanashi Shimbokukai</t>
@@ -39844,7 +39879,7 @@
         </is>
       </c>
     </row>
-    <row r="915" hidden="1">
+    <row r="915">
       <c r="D915" t="inlineStr">
         <is>
           <t>Torneo Día de Pa &amp; Ma</t>
@@ -39882,7 +39917,7 @@
         </is>
       </c>
     </row>
-    <row r="916" hidden="1">
+    <row r="916">
       <c r="D916" t="inlineStr">
         <is>
           <t>Torneo Día de Pa &amp; Ma</t>
@@ -39920,7 +39955,7 @@
         </is>
       </c>
     </row>
-    <row r="917" hidden="1">
+    <row r="917">
       <c r="D917" t="inlineStr">
         <is>
           <t>Torneo Día de Pa &amp; Ma</t>
@@ -39958,7 +39993,7 @@
         </is>
       </c>
     </row>
-    <row r="918" hidden="1">
+    <row r="918">
       <c r="D918" t="inlineStr">
         <is>
           <t>Torneo Día de Pa &amp; Ma</t>
@@ -39996,7 +40031,7 @@
         </is>
       </c>
     </row>
-    <row r="919" hidden="1">
+    <row r="919">
       <c r="D919" t="inlineStr">
         <is>
           <t>Torneo Día de Pa &amp; Ma</t>
@@ -40034,7 +40069,7 @@
         </is>
       </c>
     </row>
-    <row r="920" hidden="1">
+    <row r="920">
       <c r="D920" t="inlineStr">
         <is>
           <t>Torneo Día de Pa &amp; Ma</t>
@@ -40072,7 +40107,7 @@
         </is>
       </c>
     </row>
-    <row r="921" hidden="1">
+    <row r="921">
       <c r="D921" t="inlineStr">
         <is>
           <t>Torneo Día de Pa &amp; Ma</t>
@@ -40110,7 +40145,7 @@
         </is>
       </c>
     </row>
-    <row r="922" hidden="1">
+    <row r="922">
       <c r="D922" t="inlineStr">
         <is>
           <t>Torneo Día de Pa &amp; Ma</t>
@@ -40148,7 +40183,7 @@
         </is>
       </c>
     </row>
-    <row r="923" hidden="1">
+    <row r="923">
       <c r="B923" t="inlineStr">
         <is>
           <t>Campeonato Oficial</t>
@@ -40191,7 +40226,7 @@
         </is>
       </c>
     </row>
-    <row r="924" hidden="1">
+    <row r="924">
       <c r="B924" t="inlineStr">
         <is>
           <t>Campeonato Oficial</t>
@@ -40234,7 +40269,7 @@
         </is>
       </c>
     </row>
-    <row r="925" hidden="1">
+    <row r="925">
       <c r="B925" t="inlineStr">
         <is>
           <t>Campeonato Oficial</t>
@@ -40277,7 +40312,7 @@
         </is>
       </c>
     </row>
-    <row r="926" hidden="1">
+    <row r="926">
       <c r="B926" t="inlineStr">
         <is>
           <t>Campeonato Oficial</t>
@@ -40320,7 +40355,7 @@
         </is>
       </c>
     </row>
-    <row r="927" hidden="1">
+    <row r="927">
       <c r="B927" t="inlineStr">
         <is>
           <t>Campeonato Oficial</t>
@@ -40363,7 +40398,7 @@
         </is>
       </c>
     </row>
-    <row r="928" hidden="1">
+    <row r="928">
       <c r="B928" t="inlineStr">
         <is>
           <t>Campeonato Oficial</t>
@@ -40406,7 +40441,7 @@
         </is>
       </c>
     </row>
-    <row r="929" hidden="1">
+    <row r="929">
       <c r="B929" t="inlineStr">
         <is>
           <t>Campeonato Internacional</t>
@@ -40459,7 +40494,7 @@
         </is>
       </c>
     </row>
-    <row r="930" hidden="1">
+    <row r="930">
       <c r="B930" t="inlineStr">
         <is>
           <t>Campeonato Internacional</t>
@@ -40517,7 +40552,7 @@
         </is>
       </c>
     </row>
-    <row r="931" hidden="1">
+    <row r="931">
       <c r="B931" t="inlineStr">
         <is>
           <t>Campeonato Internacional</t>
@@ -40575,7 +40610,7 @@
         </is>
       </c>
     </row>
-    <row r="932" hidden="1">
+    <row r="932">
       <c r="B932" t="inlineStr">
         <is>
           <t>Campeonato Internacional</t>
@@ -40633,7 +40668,7 @@
         </is>
       </c>
     </row>
-    <row r="933" hidden="1">
+    <row r="933">
       <c r="B933" t="inlineStr">
         <is>
           <t>Campeonato Internacional</t>
@@ -40686,7 +40721,7 @@
         </is>
       </c>
     </row>
-    <row r="934" hidden="1">
+    <row r="934">
       <c r="B934" t="inlineStr">
         <is>
           <t>Campeonato Internacional</t>
@@ -40744,7 +40779,7 @@
         </is>
       </c>
     </row>
-    <row r="935" hidden="1">
+    <row r="935">
       <c r="B935" t="inlineStr">
         <is>
           <t>Campeonato Internacional</t>
@@ -40797,7 +40832,7 @@
         </is>
       </c>
     </row>
-    <row r="936" hidden="1">
+    <row r="936">
       <c r="B936" t="inlineStr">
         <is>
           <t>Campeonato Internacional</t>
@@ -40855,7 +40890,7 @@
         </is>
       </c>
     </row>
-    <row r="937" hidden="1">
+    <row r="937">
       <c r="C937" t="inlineStr">
         <is>
           <t>Torneo Okinawa Fujinkai</t>
@@ -40898,7 +40933,7 @@
         </is>
       </c>
     </row>
-    <row r="938" hidden="1">
+    <row r="938">
       <c r="C938" t="inlineStr">
         <is>
           <t>Torneo Okinawa Fujinkai</t>
@@ -40941,7 +40976,7 @@
         </is>
       </c>
     </row>
-    <row r="939" hidden="1">
+    <row r="939">
       <c r="C939" t="inlineStr">
         <is>
           <t>Torneo Okinawa Fujinkai</t>
@@ -40984,7 +41019,7 @@
         </is>
       </c>
     </row>
-    <row r="940" hidden="1">
+    <row r="940">
       <c r="C940" t="inlineStr">
         <is>
           <t>Torneo Okinawa Fujinkai</t>
@@ -41027,7 +41062,7 @@
         </is>
       </c>
     </row>
-    <row r="941" hidden="1">
+    <row r="941">
       <c r="C941" t="inlineStr">
         <is>
           <t>Torneo Okinawa Fujinkai</t>
@@ -41070,7 +41105,7 @@
         </is>
       </c>
     </row>
-    <row r="942" hidden="1">
+    <row r="942">
       <c r="C942" t="inlineStr">
         <is>
           <t>Torneo Okinawa Fujinkai</t>
@@ -41113,7 +41148,7 @@
         </is>
       </c>
     </row>
-    <row r="943" hidden="1">
+    <row r="943">
       <c r="C943" t="inlineStr">
         <is>
           <t>Torneo Okinawa Fujinkai</t>
@@ -41156,7 +41191,7 @@
         </is>
       </c>
     </row>
-    <row r="944" hidden="1">
+    <row r="944">
       <c r="C944" t="inlineStr">
         <is>
           <t>Torneo Okinawa Fujinkai</t>
@@ -41199,7 +41234,7 @@
         </is>
       </c>
     </row>
-    <row r="945" hidden="1">
+    <row r="945">
       <c r="C945" t="inlineStr">
         <is>
           <t>Torneo Club Aikokai</t>
@@ -41242,7 +41277,7 @@
         </is>
       </c>
     </row>
-    <row r="946" hidden="1">
+    <row r="946">
       <c r="C946" t="inlineStr">
         <is>
           <t>Torneo Club Aikokai</t>
@@ -41285,7 +41320,7 @@
         </is>
       </c>
     </row>
-    <row r="947" hidden="1">
+    <row r="947">
       <c r="C947" t="inlineStr">
         <is>
           <t>Torneo Club Aikokai</t>
@@ -41328,7 +41363,7 @@
         </is>
       </c>
     </row>
-    <row r="948" hidden="1">
+    <row r="948">
       <c r="C948" t="inlineStr">
         <is>
           <t>Torneo Club Aikokai</t>
@@ -41371,7 +41406,7 @@
         </is>
       </c>
     </row>
-    <row r="949" hidden="1">
+    <row r="949">
       <c r="C949" t="inlineStr">
         <is>
           <t>Torneo Club Aikokai</t>
@@ -41414,7 +41449,7 @@
         </is>
       </c>
     </row>
-    <row r="950" hidden="1">
+    <row r="950">
       <c r="C950" t="inlineStr">
         <is>
           <t>Torneo Club Aikokai</t>
@@ -41457,7 +41492,7 @@
         </is>
       </c>
     </row>
-    <row r="951" hidden="1">
+    <row r="951">
       <c r="C951" t="inlineStr">
         <is>
           <t>Torneo Club Aikokai</t>
@@ -41500,7 +41535,7 @@
         </is>
       </c>
     </row>
-    <row r="952" hidden="1">
+    <row r="952">
       <c r="C952" t="inlineStr">
         <is>
           <t>Torneo Club Aikokai</t>
@@ -41543,7 +41578,7 @@
         </is>
       </c>
     </row>
-    <row r="953" hidden="1">
+    <row r="953">
       <c r="C953" t="inlineStr">
         <is>
           <t>Juegos de Integración Nikkei</t>
@@ -41581,7 +41616,7 @@
         </is>
       </c>
     </row>
-    <row r="954" hidden="1">
+    <row r="954">
       <c r="C954" t="inlineStr">
         <is>
           <t>Juegos de Integración Nikkei</t>
@@ -41619,7 +41654,7 @@
         </is>
       </c>
     </row>
-    <row r="955" hidden="1">
+    <row r="955">
       <c r="C955" t="inlineStr">
         <is>
           <t>Juegos de Integración Nikkei</t>
@@ -41657,7 +41692,7 @@
         </is>
       </c>
     </row>
-    <row r="956" hidden="1">
+    <row r="956">
       <c r="C956" t="inlineStr">
         <is>
           <t>Juegos de Integración Nikkei</t>
@@ -41695,7 +41730,7 @@
         </is>
       </c>
     </row>
-    <row r="957" hidden="1">
+    <row r="957">
       <c r="B957" t="inlineStr">
         <is>
           <t>Campeonato Internacional</t>
@@ -41738,7 +41773,7 @@
         </is>
       </c>
     </row>
-    <row r="958" hidden="1">
+    <row r="958">
       <c r="B958" t="inlineStr">
         <is>
           <t>Campeonato Internacional</t>
@@ -41781,7 +41816,7 @@
         </is>
       </c>
     </row>
-    <row r="959" hidden="1">
+    <row r="959">
       <c r="B959" t="inlineStr">
         <is>
           <t>Campeonato Internacional</t>
@@ -41824,7 +41859,7 @@
         </is>
       </c>
     </row>
-    <row r="960" hidden="1">
+    <row r="960">
       <c r="B960" t="inlineStr">
         <is>
           <t>Campeonato Internacional</t>
@@ -41867,7 +41902,7 @@
         </is>
       </c>
     </row>
-    <row r="961" hidden="1">
+    <row r="961">
       <c r="B961" t="inlineStr">
         <is>
           <t>Campeonato Internacional</t>
@@ -41910,7 +41945,7 @@
         </is>
       </c>
     </row>
-    <row r="962" hidden="1">
+    <row r="962">
       <c r="B962" t="inlineStr">
         <is>
           <t>Campeonato Internacional</t>
@@ -41953,7 +41988,7 @@
         </is>
       </c>
     </row>
-    <row r="963" hidden="1">
+    <row r="963">
       <c r="B963" t="inlineStr">
         <is>
           <t>Campeonato Internacional</t>
@@ -42001,7 +42036,7 @@
         </is>
       </c>
     </row>
-    <row r="964" hidden="1">
+    <row r="964">
       <c r="B964" t="inlineStr">
         <is>
           <t>Campeonato Internacional</t>
@@ -42049,7 +42084,7 @@
         </is>
       </c>
     </row>
-    <row r="965" hidden="1">
+    <row r="965">
       <c r="B965" t="inlineStr">
         <is>
           <t>Campeonato Internacional</t>
@@ -42102,7 +42137,7 @@
         </is>
       </c>
     </row>
-    <row r="966" hidden="1">
+    <row r="966">
       <c r="C966" t="inlineStr">
         <is>
           <t>Torneo Physia</t>
@@ -42145,7 +42180,7 @@
         </is>
       </c>
     </row>
-    <row r="967" hidden="1">
+    <row r="967">
       <c r="C967" t="inlineStr">
         <is>
           <t>Torneo Physia</t>
@@ -42188,7 +42223,7 @@
         </is>
       </c>
     </row>
-    <row r="968" hidden="1">
+    <row r="968">
       <c r="C968" t="inlineStr">
         <is>
           <t>Torneo Physia</t>
@@ -42231,7 +42266,7 @@
         </is>
       </c>
     </row>
-    <row r="969" hidden="1">
+    <row r="969">
       <c r="C969" t="inlineStr">
         <is>
           <t>Torneo Physia</t>
@@ -42274,7 +42309,7 @@
         </is>
       </c>
     </row>
-    <row r="970" hidden="1">
+    <row r="970">
       <c r="C970" t="inlineStr">
         <is>
           <t>Torneo Physia</t>
@@ -42317,7 +42352,7 @@
         </is>
       </c>
     </row>
-    <row r="971" hidden="1">
+    <row r="971">
       <c r="C971" t="inlineStr">
         <is>
           <t>Torneo Physia</t>
@@ -42360,7 +42395,7 @@
         </is>
       </c>
     </row>
-    <row r="972" hidden="1">
+    <row r="972">
       <c r="C972" t="inlineStr">
         <is>
           <t>Torneo Physia</t>
@@ -42403,7 +42438,7 @@
         </is>
       </c>
     </row>
-    <row r="973" hidden="1">
+    <row r="973">
       <c r="C973" t="inlineStr">
         <is>
           <t>Torneo Physia</t>
@@ -42446,7 +42481,7 @@
         </is>
       </c>
     </row>
-    <row r="974" hidden="1">
+    <row r="974">
       <c r="C974" t="inlineStr">
         <is>
           <t>Torneo Physia</t>
@@ -42489,7 +42524,7 @@
         </is>
       </c>
     </row>
-    <row r="975" hidden="1">
+    <row r="975">
       <c r="C975" t="inlineStr">
         <is>
           <t>Torneo Odawara</t>
@@ -42523,7 +42558,7 @@
       </c>
       <c r="L975" t="inlineStr">
         <is>
-          <t>Tere Oshiro, Andy Yzena, Mari Uezoga, Carlos Teran y Jacky Matsufuji</t>
+          <t>Tere Oshiro, Andy Yzena, Mary Uezyoga, Carlos Teran y Jacky Matsufuji</t>
         </is>
       </c>
       <c r="M975" s="3" t="inlineStr">
@@ -42532,7 +42567,7 @@
         </is>
       </c>
     </row>
-    <row r="976" hidden="1">
+    <row r="976">
       <c r="C976" t="inlineStr">
         <is>
           <t>Torneo Odawara</t>
@@ -42575,7 +42610,7 @@
         </is>
       </c>
     </row>
-    <row r="977" hidden="1">
+    <row r="977">
       <c r="C977" t="inlineStr">
         <is>
           <t>Torneo Odawara</t>
@@ -42618,7 +42653,7 @@
         </is>
       </c>
     </row>
-    <row r="978" hidden="1">
+    <row r="978">
       <c r="C978" t="inlineStr">
         <is>
           <t>Torneo Odawara</t>
@@ -42661,7 +42696,7 @@
         </is>
       </c>
     </row>
-    <row r="979" hidden="1">
+    <row r="979">
       <c r="C979" t="inlineStr">
         <is>
           <t>Torneo Odawara</t>
@@ -42704,7 +42739,7 @@
         </is>
       </c>
     </row>
-    <row r="980" hidden="1">
+    <row r="980">
       <c r="C980" t="inlineStr">
         <is>
           <t>Torneo Odawara</t>
@@ -42747,7 +42782,12 @@
         </is>
       </c>
     </row>
-    <row r="981" hidden="1">
+    <row r="981">
+      <c r="B981" t="inlineStr">
+        <is>
+          <t>Confraternidad/Integración</t>
+        </is>
+      </c>
       <c r="D981" t="inlineStr">
         <is>
           <t>Torneo de la Academia de Gateball</t>
@@ -42780,7 +42820,12 @@
         </is>
       </c>
     </row>
-    <row r="982" hidden="1">
+    <row r="982">
+      <c r="B982" t="inlineStr">
+        <is>
+          <t>Confraternidad/Integración</t>
+        </is>
+      </c>
       <c r="D982" t="inlineStr">
         <is>
           <t>Torneo de la Academia de Gateball</t>
@@ -42813,7 +42858,12 @@
         </is>
       </c>
     </row>
-    <row r="983" hidden="1">
+    <row r="983">
+      <c r="B983" t="inlineStr">
+        <is>
+          <t>Confraternidad/Integración</t>
+        </is>
+      </c>
       <c r="D983" t="inlineStr">
         <is>
           <t>Torneo de la Academia de Gateball</t>
@@ -42846,7 +42896,12 @@
         </is>
       </c>
     </row>
-    <row r="984" hidden="1">
+    <row r="984">
+      <c r="B984" t="inlineStr">
+        <is>
+          <t>Confraternidad/Integración</t>
+        </is>
+      </c>
       <c r="D984" t="inlineStr">
         <is>
           <t>Torneo de la Academia de Gateball</t>
@@ -42879,7 +42934,12 @@
         </is>
       </c>
     </row>
-    <row r="985" hidden="1">
+    <row r="985">
+      <c r="B985" t="inlineStr">
+        <is>
+          <t>Confraternidad/Integración</t>
+        </is>
+      </c>
       <c r="D985" t="inlineStr">
         <is>
           <t>Torneo de la Academia de Gateball</t>
@@ -42912,7 +42972,7 @@
         </is>
       </c>
     </row>
-    <row r="986" hidden="1">
+    <row r="986">
       <c r="C986" t="inlineStr">
         <is>
           <t>Torneo Nikkei Fujinkai</t>
@@ -42955,7 +43015,7 @@
         </is>
       </c>
     </row>
-    <row r="987" hidden="1">
+    <row r="987">
       <c r="C987" t="inlineStr">
         <is>
           <t>Torneo Nikkei Fujinkai</t>
@@ -42998,7 +43058,7 @@
         </is>
       </c>
     </row>
-    <row r="988" hidden="1">
+    <row r="988">
       <c r="C988" t="inlineStr">
         <is>
           <t>Torneo Nikkei Fujinkai</t>
@@ -43041,7 +43101,7 @@
         </is>
       </c>
     </row>
-    <row r="989" hidden="1">
+    <row r="989">
       <c r="C989" t="inlineStr">
         <is>
           <t>Torneo Nikkei Fujinkai</t>
@@ -43084,7 +43144,7 @@
         </is>
       </c>
     </row>
-    <row r="990" hidden="1">
+    <row r="990">
       <c r="C990" t="inlineStr">
         <is>
           <t>Torneo Nikkei Fujinkai</t>
@@ -43127,7 +43187,7 @@
         </is>
       </c>
     </row>
-    <row r="991" hidden="1">
+    <row r="991">
       <c r="C991" t="inlineStr">
         <is>
           <t>Torneo Nikkei Fujinkai</t>
@@ -43170,7 +43230,7 @@
         </is>
       </c>
     </row>
-    <row r="992" hidden="1">
+    <row r="992">
       <c r="C992" t="inlineStr">
         <is>
           <t>Torneo Nikkei Fujinkai</t>
@@ -43213,7 +43273,7 @@
         </is>
       </c>
     </row>
-    <row r="993" hidden="1">
+    <row r="993">
       <c r="C993" t="inlineStr">
         <is>
           <t>Torneo Nikkei Fujinkai</t>
@@ -43256,7 +43316,7 @@
         </is>
       </c>
     </row>
-    <row r="994" hidden="1">
+    <row r="994">
       <c r="C994" t="inlineStr">
         <is>
           <t>Torneo Yamanashi Shimbokukai</t>
@@ -43299,7 +43359,7 @@
         </is>
       </c>
     </row>
-    <row r="995" hidden="1">
+    <row r="995">
       <c r="C995" t="inlineStr">
         <is>
           <t>Torneo Yamanashi Shimbokukai</t>
@@ -43342,7 +43402,7 @@
         </is>
       </c>
     </row>
-    <row r="996" hidden="1">
+    <row r="996">
       <c r="C996" t="inlineStr">
         <is>
           <t>Torneo Yamanashi Shimbokukai</t>
@@ -43385,7 +43445,7 @@
         </is>
       </c>
     </row>
-    <row r="997" hidden="1">
+    <row r="997">
       <c r="C997" t="inlineStr">
         <is>
           <t>Torneo Sakura</t>
@@ -43428,7 +43488,7 @@
         </is>
       </c>
     </row>
-    <row r="998" hidden="1">
+    <row r="998">
       <c r="C998" t="inlineStr">
         <is>
           <t>Torneo Sakura</t>
@@ -43471,7 +43531,7 @@
         </is>
       </c>
     </row>
-    <row r="999" hidden="1">
+    <row r="999">
       <c r="C999" t="inlineStr">
         <is>
           <t>Torneo Sakura</t>
@@ -43505,7 +43565,7 @@
       </c>
       <c r="L999" t="inlineStr">
         <is>
-          <t>Andy Yzena, Mari Uezoga, Nancy Higaonna, Johnny Taira y Mabo Tsukahoshi</t>
+          <t>Andy Yzena, Mary Uezyoga, Nancy Higaonna, Johnny Taira y Mabo Tsukahoshi</t>
         </is>
       </c>
       <c r="M999" t="inlineStr">
@@ -43514,7 +43574,7 @@
         </is>
       </c>
     </row>
-    <row r="1000" hidden="1">
+    <row r="1000">
       <c r="C1000" t="inlineStr">
         <is>
           <t>Torneo Sakura</t>
@@ -43557,7 +43617,7 @@
         </is>
       </c>
     </row>
-    <row r="1001" hidden="1">
+    <row r="1001">
       <c r="C1001" t="inlineStr">
         <is>
           <t>Torneo Sakura</t>
@@ -43600,7 +43660,7 @@
         </is>
       </c>
     </row>
-    <row r="1002" hidden="1">
+    <row r="1002">
       <c r="C1002" t="inlineStr">
         <is>
           <t>Torneo Sakura</t>
@@ -43643,7 +43703,7 @@
         </is>
       </c>
     </row>
-    <row r="1003" hidden="1">
+    <row r="1003">
       <c r="C1003" t="inlineStr">
         <is>
           <t>Torneo Sakura</t>
@@ -43686,7 +43746,7 @@
         </is>
       </c>
     </row>
-    <row r="1004" hidden="1">
+    <row r="1004">
       <c r="C1004" t="inlineStr">
         <is>
           <t>Torneo Sakura</t>
@@ -43729,7 +43789,7 @@
         </is>
       </c>
     </row>
-    <row r="1005" hidden="1">
+    <row r="1005">
       <c r="C1005" t="inlineStr">
         <is>
           <t>Torneo Sakura</t>
@@ -43772,7 +43832,7 @@
         </is>
       </c>
     </row>
-    <row r="1006" hidden="1">
+    <row r="1006">
       <c r="C1006" t="inlineStr">
         <is>
           <t>Campeonato Mario Akamine</t>
@@ -43810,7 +43870,7 @@
         </is>
       </c>
     </row>
-    <row r="1007" hidden="1">
+    <row r="1007">
       <c r="C1007" t="inlineStr">
         <is>
           <t>Campeonato Mario Akamine</t>
@@ -43848,7 +43908,7 @@
         </is>
       </c>
     </row>
-    <row r="1008" hidden="1">
+    <row r="1008">
       <c r="C1008" t="inlineStr">
         <is>
           <t>Campeonato Mario Akamine</t>
@@ -43886,7 +43946,7 @@
         </is>
       </c>
     </row>
-    <row r="1009" hidden="1">
+    <row r="1009">
       <c r="C1009" t="inlineStr">
         <is>
           <t>Campeonato Mario Akamine</t>
@@ -43924,7 +43984,7 @@
         </is>
       </c>
     </row>
-    <row r="1010" hidden="1">
+    <row r="1010">
       <c r="C1010" t="inlineStr">
         <is>
           <t>Campeonato Mario Akamine</t>
@@ -43962,7 +44022,7 @@
         </is>
       </c>
     </row>
-    <row r="1011" hidden="1">
+    <row r="1011">
       <c r="C1011" t="inlineStr">
         <is>
           <t>Campeonato Mario Akamine</t>
@@ -44000,7 +44060,7 @@
         </is>
       </c>
     </row>
-    <row r="1012" hidden="1">
+    <row r="1012">
       <c r="C1012" t="inlineStr">
         <is>
           <t>Campeonato Mario Akamine</t>
@@ -44038,7 +44098,7 @@
         </is>
       </c>
     </row>
-    <row r="1013" hidden="1">
+    <row r="1013">
       <c r="C1013" t="inlineStr">
         <is>
           <t>Campeonato Mario Akamine</t>
@@ -44076,7 +44136,7 @@
         </is>
       </c>
     </row>
-    <row r="1014" hidden="1">
+    <row r="1014">
       <c r="C1014" t="inlineStr">
         <is>
           <t>Campeonato Mario Akamine</t>
@@ -44114,7 +44174,12 @@
         </is>
       </c>
     </row>
-    <row r="1015" hidden="1">
+    <row r="1015">
+      <c r="B1015" t="inlineStr">
+        <is>
+          <t>Confraternidad/Integración</t>
+        </is>
+      </c>
       <c r="C1015" t="inlineStr">
         <is>
           <t>Torneo Kyodai</t>
@@ -44152,7 +44217,12 @@
         </is>
       </c>
     </row>
-    <row r="1016" hidden="1">
+    <row r="1016">
+      <c r="B1016" t="inlineStr">
+        <is>
+          <t>Confraternidad/Integración</t>
+        </is>
+      </c>
       <c r="C1016" t="inlineStr">
         <is>
           <t>Torneo Kyodai</t>
@@ -44190,7 +44260,12 @@
         </is>
       </c>
     </row>
-    <row r="1017" hidden="1">
+    <row r="1017">
+      <c r="B1017" t="inlineStr">
+        <is>
+          <t>Confraternidad/Integración</t>
+        </is>
+      </c>
       <c r="C1017" t="inlineStr">
         <is>
           <t>Torneo Kyodai</t>
@@ -44228,7 +44303,7 @@
         </is>
       </c>
     </row>
-    <row r="1018" hidden="1">
+    <row r="1018">
       <c r="C1018" t="inlineStr">
         <is>
           <t>Torneo Okinawa Fujinkai</t>
@@ -44271,7 +44346,7 @@
         </is>
       </c>
     </row>
-    <row r="1019" hidden="1">
+    <row r="1019">
       <c r="C1019" t="inlineStr">
         <is>
           <t>Torneo Okinawa Fujinkai</t>
@@ -44314,7 +44389,7 @@
         </is>
       </c>
     </row>
-    <row r="1020" hidden="1">
+    <row r="1020">
       <c r="C1020" t="inlineStr">
         <is>
           <t>Torneo Okinawa Fujinkai</t>
@@ -44357,7 +44432,7 @@
         </is>
       </c>
     </row>
-    <row r="1021" hidden="1">
+    <row r="1021">
       <c r="C1021" t="inlineStr">
         <is>
           <t>Torneo Okinawa Fujinkai</t>
@@ -44400,7 +44475,7 @@
         </is>
       </c>
     </row>
-    <row r="1022" hidden="1">
+    <row r="1022">
       <c r="C1022" t="inlineStr">
         <is>
           <t>Torneo Okinawa Fujinkai</t>
@@ -44443,7 +44518,7 @@
         </is>
       </c>
     </row>
-    <row r="1023" hidden="1">
+    <row r="1023">
       <c r="C1023" t="inlineStr">
         <is>
           <t>Torneo Okinawa Fujinkai</t>
@@ -44486,7 +44561,7 @@
         </is>
       </c>
     </row>
-    <row r="1024" hidden="1">
+    <row r="1024">
       <c r="C1024" t="inlineStr">
         <is>
           <t>Torneo Okinawa Fujinkai</t>
@@ -44529,7 +44604,7 @@
         </is>
       </c>
     </row>
-    <row r="1025" hidden="1">
+    <row r="1025">
       <c r="C1025" t="inlineStr">
         <is>
           <t>Torneo Okinawa Fujinkai</t>
@@ -44572,7 +44647,7 @@
         </is>
       </c>
     </row>
-    <row r="1026" hidden="1">
+    <row r="1026">
       <c r="D1026" t="inlineStr">
         <is>
           <t>I Torneo Incentivo de Gateball</t>
@@ -44605,7 +44680,7 @@
         </is>
       </c>
     </row>
-    <row r="1027" hidden="1">
+    <row r="1027">
       <c r="D1027" t="inlineStr">
         <is>
           <t>I Torneo Incentivo de Gateball</t>
@@ -44638,7 +44713,7 @@
         </is>
       </c>
     </row>
-    <row r="1028" hidden="1">
+    <row r="1028">
       <c r="D1028" t="inlineStr">
         <is>
           <t>I Torneo Incentivo de Gateball</t>
@@ -44666,7 +44741,7 @@
         </is>
       </c>
     </row>
-    <row r="1029" hidden="1">
+    <row r="1029">
       <c r="D1029" t="inlineStr">
         <is>
           <t>I Torneo Incentivo de Gateball</t>
@@ -44694,7 +44769,7 @@
         </is>
       </c>
     </row>
-    <row r="1030" hidden="1">
+    <row r="1030">
       <c r="C1030" t="inlineStr">
         <is>
           <t>Torneo Club Aikokai</t>
@@ -44732,7 +44807,7 @@
         </is>
       </c>
     </row>
-    <row r="1031" hidden="1">
+    <row r="1031">
       <c r="C1031" t="inlineStr">
         <is>
           <t>Torneo Club Aikokai</t>
@@ -44770,7 +44845,7 @@
         </is>
       </c>
     </row>
-    <row r="1032" hidden="1">
+    <row r="1032">
       <c r="C1032" t="inlineStr">
         <is>
           <t>Torneo Club Aikokai</t>
@@ -44808,7 +44883,7 @@
         </is>
       </c>
     </row>
-    <row r="1033" hidden="1">
+    <row r="1033">
       <c r="C1033" t="inlineStr">
         <is>
           <t>Torneo Club Aikokai</t>
@@ -44846,7 +44921,7 @@
         </is>
       </c>
     </row>
-    <row r="1034" hidden="1">
+    <row r="1034">
       <c r="C1034" t="inlineStr">
         <is>
           <t>Torneo Club Aikokai</t>
@@ -44884,7 +44959,7 @@
         </is>
       </c>
     </row>
-    <row r="1035" hidden="1">
+    <row r="1035">
       <c r="C1035" t="inlineStr">
         <is>
           <t>Torneo Club Aikokai</t>
@@ -44922,7 +44997,7 @@
         </is>
       </c>
     </row>
-    <row r="1036" hidden="1">
+    <row r="1036">
       <c r="C1036" t="inlineStr">
         <is>
           <t>Torneo Club Aikokai</t>
@@ -44960,7 +45035,7 @@
         </is>
       </c>
     </row>
-    <row r="1037" hidden="1">
+    <row r="1037">
       <c r="C1037" t="inlineStr">
         <is>
           <t>Torneo Club Aikokai</t>
@@ -44998,7 +45073,7 @@
         </is>
       </c>
     </row>
-    <row r="1038" hidden="1">
+    <row r="1038">
       <c r="C1038" t="inlineStr">
         <is>
           <t>Juegos de Integración Nikkei</t>
@@ -45036,7 +45111,7 @@
         </is>
       </c>
     </row>
-    <row r="1039" hidden="1">
+    <row r="1039">
       <c r="C1039" t="inlineStr">
         <is>
           <t>Juegos de Integración Nikkei</t>
@@ -45074,7 +45149,7 @@
         </is>
       </c>
     </row>
-    <row r="1040" hidden="1">
+    <row r="1040">
       <c r="C1040" t="inlineStr">
         <is>
           <t>Juegos de Integración Nikkei</t>
@@ -45112,7 +45187,7 @@
         </is>
       </c>
     </row>
-    <row r="1041" hidden="1">
+    <row r="1041">
       <c r="C1041" t="inlineStr">
         <is>
           <t>Juegos de Integración Nikkei</t>
@@ -45151,13 +45226,7 @@
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:M1041">
-    <filterColumn colId="2" hiddenButton="0" showButton="1">
-      <filters>
-        <filter val="Torneo Jinnai"/>
-      </filters>
-    </filterColumn>
-  </autoFilter>
+  <autoFilter ref="A1:M1041"/>
   <hyperlinks>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M14" r:id="rId1"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M15" r:id="rId2"/>

--- a/data/raw/copas_y_torneos.xlsx
+++ b/data/raw/copas_y_torneos.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Projects\gateball\kantokeando-data\data\raw\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{767C59F6-0244-4F03-8AFF-562892B3321B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CE30C624-6B90-4945-826B-BF3E52E8DFB2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Resultados" sheetId="1" r:id="rId1"/>
@@ -29836,7 +29836,7 @@
     </row>
     <row r="820" spans="3:13" x14ac:dyDescent="0.3">
       <c r="C820" t="s">
-        <v>27</v>
+        <v>129</v>
       </c>
       <c r="D820" t="s">
         <v>1313</v>
@@ -29865,7 +29865,7 @@
     </row>
     <row r="821" spans="3:13" x14ac:dyDescent="0.3">
       <c r="C821" t="s">
-        <v>27</v>
+        <v>129</v>
       </c>
       <c r="D821" t="s">
         <v>1313</v>
@@ -29894,7 +29894,7 @@
     </row>
     <row r="822" spans="3:13" x14ac:dyDescent="0.3">
       <c r="C822" t="s">
-        <v>27</v>
+        <v>129</v>
       </c>
       <c r="D822" t="s">
         <v>1313</v>
@@ -29923,7 +29923,7 @@
     </row>
     <row r="823" spans="3:13" x14ac:dyDescent="0.3">
       <c r="C823" t="s">
-        <v>27</v>
+        <v>129</v>
       </c>
       <c r="D823" t="s">
         <v>1313</v>
@@ -29952,7 +29952,7 @@
     </row>
     <row r="824" spans="3:13" x14ac:dyDescent="0.3">
       <c r="C824" t="s">
-        <v>27</v>
+        <v>129</v>
       </c>
       <c r="D824" t="s">
         <v>1313</v>
@@ -29981,7 +29981,7 @@
     </row>
     <row r="825" spans="3:13" x14ac:dyDescent="0.3">
       <c r="C825" t="s">
-        <v>27</v>
+        <v>129</v>
       </c>
       <c r="D825" t="s">
         <v>1313</v>
@@ -30010,7 +30010,7 @@
     </row>
     <row r="826" spans="3:13" x14ac:dyDescent="0.3">
       <c r="C826" t="s">
-        <v>27</v>
+        <v>129</v>
       </c>
       <c r="D826" t="s">
         <v>1313</v>
@@ -30039,7 +30039,7 @@
     </row>
     <row r="827" spans="3:13" x14ac:dyDescent="0.3">
       <c r="C827" t="s">
-        <v>27</v>
+        <v>129</v>
       </c>
       <c r="D827" t="s">
         <v>1313</v>

--- a/data/raw/copas_y_torneos.xlsx
+++ b/data/raw/copas_y_torneos.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Projects\gateball\kantokeando-data\data\raw\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CE30C624-6B90-4945-826B-BF3E52E8DFB2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E0CAEA86-BCB6-4C24-93E9-BD85E359A4B7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -17,7 +17,7 @@
     <sheet name="Posiciones" sheetId="2" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Resultados!$A$1:$M$1041</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Resultados!$A$1:$M$1046</definedName>
   </definedNames>
   <calcPr calcId="0"/>
 </workbook>
@@ -48,7 +48,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="8153" uniqueCount="1688">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="8190" uniqueCount="1700">
   <si>
     <t>id_torneo</t>
   </si>
@@ -5112,6 +5112,42 @@
   </si>
   <si>
     <t>En curso</t>
+  </si>
+  <si>
+    <t>IV Torneo Kyodai "La Academia"</t>
+  </si>
+  <si>
+    <t>Muralla China</t>
+  </si>
+  <si>
+    <t>Yoshi Furugen, Aiko Tamashiro, Nelly Kina, Nobu Shimabukuro y Ceci Paniagua.</t>
+  </si>
+  <si>
+    <t>https://kantokeando.blogspot.com/2026/10/sabado-03-de-octubre-se-realizo-el-iv.html</t>
+  </si>
+  <si>
+    <t>Pirámide de Giza</t>
+  </si>
+  <si>
+    <t>Mirtha Miura, Yoshi Yamauchi, Harumi Ikemiyashiro, Hanae Pretell y Carmen Teruya.</t>
+  </si>
+  <si>
+    <t>Jugadores destacados</t>
+  </si>
+  <si>
+    <t>Mejores kantokus</t>
+  </si>
+  <si>
+    <t>Nelly Kina, Roberto Higa</t>
+  </si>
+  <si>
+    <t>Torneo de supakus</t>
+  </si>
+  <si>
+    <t>Yoshi Yamauchi</t>
+  </si>
+  <si>
+    <t>Mary Uezyoga, Julia Enobi</t>
   </si>
 </sst>
 </file>
@@ -5304,9 +5340,10 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="2">
+  <cellStyleXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
   <cellXfs count="29">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
@@ -5367,8 +5404,9 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
-  <cellStyles count="2">
+  <cellStyles count="3">
     <cellStyle name="Hipervínculo" xfId="1" builtinId="8"/>
+    <cellStyle name="Hipervínculo 2" xfId="2" xr:uid="{82920A91-9945-4A80-8BAF-D08F14AFCD25}"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="1">
@@ -5682,7 +5720,8 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:M1041"/>
+  <sheetPr filterMode="1"/>
+  <dimension ref="A1:M1046"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.88671875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="20" customWidth="1"/>
@@ -5740,7 +5779,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="2" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="A2" s="6" t="s">
         <v>13</v>
       </c>
@@ -5773,7 +5812,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="3" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="A3" s="6"/>
       <c r="B3" s="6"/>
       <c r="C3" s="6"/>
@@ -5804,7 +5843,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="4" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="A4" s="6"/>
       <c r="B4" s="6"/>
       <c r="C4" s="6"/>
@@ -5835,7 +5874,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="5" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="D5" s="6" t="s">
         <v>14</v>
       </c>
@@ -5862,7 +5901,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="6" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="C6" t="s">
         <v>27</v>
       </c>
@@ -5892,7 +5931,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="7" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="C7" t="s">
         <v>27</v>
       </c>
@@ -5922,7 +5961,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="8" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="C8" t="s">
         <v>27</v>
       </c>
@@ -5952,7 +5991,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="9" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="C9" t="s">
         <v>27</v>
       </c>
@@ -5982,7 +6021,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="10" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="C10" t="s">
         <v>27</v>
       </c>
@@ -6012,7 +6051,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="11" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="C11" t="s">
         <v>27</v>
       </c>
@@ -6042,7 +6081,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="12" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="C12" t="s">
         <v>27</v>
       </c>
@@ -6072,7 +6111,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="13" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="C13" t="s">
         <v>27</v>
       </c>
@@ -6102,7 +6141,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="14" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="C14" t="s">
         <v>45</v>
       </c>
@@ -6132,7 +6171,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="15" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="C15" t="s">
         <v>45</v>
       </c>
@@ -6162,7 +6201,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="16" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="C16" t="s">
         <v>45</v>
       </c>
@@ -6192,7 +6231,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="17" spans="3:13" x14ac:dyDescent="0.3">
+    <row r="17" spans="3:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="C17" t="s">
         <v>45</v>
       </c>
@@ -6222,7 +6261,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="18" spans="3:13" x14ac:dyDescent="0.3">
+    <row r="18" spans="3:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="C18" t="s">
         <v>45</v>
       </c>
@@ -6252,7 +6291,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="19" spans="3:13" x14ac:dyDescent="0.3">
+    <row r="19" spans="3:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="C19" t="s">
         <v>45</v>
       </c>
@@ -6282,7 +6321,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="20" spans="3:13" x14ac:dyDescent="0.3">
+    <row r="20" spans="3:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="C20" t="s">
         <v>59</v>
       </c>
@@ -6309,7 +6348,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="21" spans="3:13" x14ac:dyDescent="0.3">
+    <row r="21" spans="3:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="C21" t="s">
         <v>59</v>
       </c>
@@ -6336,7 +6375,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="22" spans="3:13" x14ac:dyDescent="0.3">
+    <row r="22" spans="3:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="C22" t="s">
         <v>59</v>
       </c>
@@ -6363,7 +6402,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="23" spans="3:13" x14ac:dyDescent="0.3">
+    <row r="23" spans="3:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="C23" t="s">
         <v>59</v>
       </c>
@@ -6390,7 +6429,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="24" spans="3:13" x14ac:dyDescent="0.3">
+    <row r="24" spans="3:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="C24" t="s">
         <v>69</v>
       </c>
@@ -6417,7 +6456,7 @@
         <v>74</v>
       </c>
     </row>
-    <row r="25" spans="3:13" x14ac:dyDescent="0.3">
+    <row r="25" spans="3:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="C25" t="s">
         <v>69</v>
       </c>
@@ -6444,7 +6483,7 @@
         <v>74</v>
       </c>
     </row>
-    <row r="26" spans="3:13" x14ac:dyDescent="0.3">
+    <row r="26" spans="3:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="C26" t="s">
         <v>69</v>
       </c>
@@ -6471,7 +6510,7 @@
         <v>74</v>
       </c>
     </row>
-    <row r="27" spans="3:13" x14ac:dyDescent="0.3">
+    <row r="27" spans="3:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="C27" t="s">
         <v>69</v>
       </c>
@@ -6498,7 +6537,7 @@
         <v>74</v>
       </c>
     </row>
-    <row r="28" spans="3:13" x14ac:dyDescent="0.3">
+    <row r="28" spans="3:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="C28" t="s">
         <v>79</v>
       </c>
@@ -6525,7 +6564,7 @@
         <v>83</v>
       </c>
     </row>
-    <row r="29" spans="3:13" x14ac:dyDescent="0.3">
+    <row r="29" spans="3:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="C29" t="s">
         <v>79</v>
       </c>
@@ -6552,7 +6591,7 @@
         <v>83</v>
       </c>
     </row>
-    <row r="30" spans="3:13" x14ac:dyDescent="0.3">
+    <row r="30" spans="3:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="C30" t="s">
         <v>79</v>
       </c>
@@ -6579,7 +6618,7 @@
         <v>83</v>
       </c>
     </row>
-    <row r="31" spans="3:13" x14ac:dyDescent="0.3">
+    <row r="31" spans="3:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="C31" t="s">
         <v>79</v>
       </c>
@@ -6606,7 +6645,7 @@
         <v>83</v>
       </c>
     </row>
-    <row r="32" spans="3:13" x14ac:dyDescent="0.3">
+    <row r="32" spans="3:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="C32" t="s">
         <v>90</v>
       </c>
@@ -6633,7 +6672,7 @@
         <v>94</v>
       </c>
     </row>
-    <row r="33" spans="3:13" x14ac:dyDescent="0.3">
+    <row r="33" spans="3:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="C33" t="s">
         <v>90</v>
       </c>
@@ -6660,7 +6699,7 @@
         <v>94</v>
       </c>
     </row>
-    <row r="34" spans="3:13" x14ac:dyDescent="0.3">
+    <row r="34" spans="3:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="C34" t="s">
         <v>90</v>
       </c>
@@ -6687,7 +6726,7 @@
         <v>94</v>
       </c>
     </row>
-    <row r="35" spans="3:13" x14ac:dyDescent="0.3">
+    <row r="35" spans="3:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="C35" t="s">
         <v>90</v>
       </c>
@@ -6714,7 +6753,7 @@
         <v>94</v>
       </c>
     </row>
-    <row r="36" spans="3:13" x14ac:dyDescent="0.3">
+    <row r="36" spans="3:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="C36" t="s">
         <v>101</v>
       </c>
@@ -6741,7 +6780,7 @@
         <v>105</v>
       </c>
     </row>
-    <row r="37" spans="3:13" x14ac:dyDescent="0.3">
+    <row r="37" spans="3:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="C37" t="s">
         <v>101</v>
       </c>
@@ -6768,7 +6807,7 @@
         <v>105</v>
       </c>
     </row>
-    <row r="38" spans="3:13" x14ac:dyDescent="0.3">
+    <row r="38" spans="3:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="C38" t="s">
         <v>101</v>
       </c>
@@ -6795,7 +6834,7 @@
         <v>105</v>
       </c>
     </row>
-    <row r="39" spans="3:13" x14ac:dyDescent="0.3">
+    <row r="39" spans="3:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="C39" t="s">
         <v>101</v>
       </c>
@@ -6822,7 +6861,7 @@
         <v>105</v>
       </c>
     </row>
-    <row r="40" spans="3:13" x14ac:dyDescent="0.3">
+    <row r="40" spans="3:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="C40" t="s">
         <v>110</v>
       </c>
@@ -6849,7 +6888,7 @@
         <v>114</v>
       </c>
     </row>
-    <row r="41" spans="3:13" x14ac:dyDescent="0.3">
+    <row r="41" spans="3:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="C41" t="s">
         <v>110</v>
       </c>
@@ -6876,7 +6915,7 @@
         <v>114</v>
       </c>
     </row>
-    <row r="42" spans="3:13" x14ac:dyDescent="0.3">
+    <row r="42" spans="3:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="C42" t="s">
         <v>110</v>
       </c>
@@ -6903,7 +6942,7 @@
         <v>114</v>
       </c>
     </row>
-    <row r="43" spans="3:13" x14ac:dyDescent="0.3">
+    <row r="43" spans="3:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="C43" t="s">
         <v>110</v>
       </c>
@@ -6930,7 +6969,7 @@
         <v>114</v>
       </c>
     </row>
-    <row r="44" spans="3:13" x14ac:dyDescent="0.3">
+    <row r="44" spans="3:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="C44" t="s">
         <v>110</v>
       </c>
@@ -6957,7 +6996,7 @@
         <v>124</v>
       </c>
     </row>
-    <row r="45" spans="3:13" x14ac:dyDescent="0.3">
+    <row r="45" spans="3:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="C45" t="s">
         <v>110</v>
       </c>
@@ -6984,7 +7023,7 @@
         <v>124</v>
       </c>
     </row>
-    <row r="46" spans="3:13" x14ac:dyDescent="0.3">
+    <row r="46" spans="3:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="C46" t="s">
         <v>110</v>
       </c>
@@ -7011,7 +7050,7 @@
         <v>124</v>
       </c>
     </row>
-    <row r="47" spans="3:13" x14ac:dyDescent="0.3">
+    <row r="47" spans="3:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="C47" t="s">
         <v>110</v>
       </c>
@@ -7038,7 +7077,7 @@
         <v>124</v>
       </c>
     </row>
-    <row r="48" spans="3:13" x14ac:dyDescent="0.3">
+    <row r="48" spans="3:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="C48" t="s">
         <v>129</v>
       </c>
@@ -7065,7 +7104,7 @@
         <v>132</v>
       </c>
     </row>
-    <row r="49" spans="2:13" x14ac:dyDescent="0.3">
+    <row r="49" spans="2:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="C49" t="s">
         <v>129</v>
       </c>
@@ -7092,7 +7131,7 @@
         <v>132</v>
       </c>
     </row>
-    <row r="50" spans="2:13" x14ac:dyDescent="0.3">
+    <row r="50" spans="2:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="C50" t="s">
         <v>129</v>
       </c>
@@ -7119,7 +7158,7 @@
         <v>132</v>
       </c>
     </row>
-    <row r="51" spans="2:13" x14ac:dyDescent="0.3">
+    <row r="51" spans="2:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="C51" t="s">
         <v>129</v>
       </c>
@@ -7146,7 +7185,7 @@
         <v>132</v>
       </c>
     </row>
-    <row r="52" spans="2:13" x14ac:dyDescent="0.3">
+    <row r="52" spans="2:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="B52" t="s">
         <v>137</v>
       </c>
@@ -7173,7 +7212,7 @@
         <v>141</v>
       </c>
     </row>
-    <row r="53" spans="2:13" x14ac:dyDescent="0.3">
+    <row r="53" spans="2:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="B53" t="s">
         <v>137</v>
       </c>
@@ -7200,7 +7239,7 @@
         <v>141</v>
       </c>
     </row>
-    <row r="54" spans="2:13" x14ac:dyDescent="0.3">
+    <row r="54" spans="2:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="B54" t="s">
         <v>137</v>
       </c>
@@ -7227,7 +7266,7 @@
         <v>147</v>
       </c>
     </row>
-    <row r="55" spans="2:13" x14ac:dyDescent="0.3">
+    <row r="55" spans="2:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="B55" t="s">
         <v>137</v>
       </c>
@@ -7254,7 +7293,7 @@
         <v>147</v>
       </c>
     </row>
-    <row r="56" spans="2:13" x14ac:dyDescent="0.3">
+    <row r="56" spans="2:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="C56" t="s">
         <v>150</v>
       </c>
@@ -7281,7 +7320,7 @@
         <v>153</v>
       </c>
     </row>
-    <row r="57" spans="2:13" x14ac:dyDescent="0.3">
+    <row r="57" spans="2:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="C57" t="s">
         <v>154</v>
       </c>
@@ -7308,7 +7347,7 @@
         <v>157</v>
       </c>
     </row>
-    <row r="58" spans="2:13" x14ac:dyDescent="0.3">
+    <row r="58" spans="2:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="C58" t="s">
         <v>154</v>
       </c>
@@ -7335,7 +7374,7 @@
         <v>157</v>
       </c>
     </row>
-    <row r="59" spans="2:13" x14ac:dyDescent="0.3">
+    <row r="59" spans="2:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="C59" t="s">
         <v>154</v>
       </c>
@@ -7362,7 +7401,7 @@
         <v>157</v>
       </c>
     </row>
-    <row r="60" spans="2:13" x14ac:dyDescent="0.3">
+    <row r="60" spans="2:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="C60" t="s">
         <v>154</v>
       </c>
@@ -7389,7 +7428,7 @@
         <v>157</v>
       </c>
     </row>
-    <row r="61" spans="2:13" x14ac:dyDescent="0.3">
+    <row r="61" spans="2:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="B61" t="s">
         <v>162</v>
       </c>
@@ -7419,7 +7458,7 @@
         <v>167</v>
       </c>
     </row>
-    <row r="62" spans="2:13" x14ac:dyDescent="0.3">
+    <row r="62" spans="2:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="B62" t="s">
         <v>162</v>
       </c>
@@ -7449,7 +7488,7 @@
         <v>167</v>
       </c>
     </row>
-    <row r="63" spans="2:13" x14ac:dyDescent="0.3">
+    <row r="63" spans="2:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="B63" t="s">
         <v>162</v>
       </c>
@@ -7479,7 +7518,7 @@
         <v>167</v>
       </c>
     </row>
-    <row r="64" spans="2:13" x14ac:dyDescent="0.3">
+    <row r="64" spans="2:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="B64" t="s">
         <v>162</v>
       </c>
@@ -7509,7 +7548,7 @@
         <v>167</v>
       </c>
     </row>
-    <row r="65" spans="2:13" x14ac:dyDescent="0.3">
+    <row r="65" spans="2:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="B65" t="s">
         <v>162</v>
       </c>
@@ -7539,7 +7578,7 @@
         <v>167</v>
       </c>
     </row>
-    <row r="66" spans="2:13" x14ac:dyDescent="0.3">
+    <row r="66" spans="2:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="B66" t="s">
         <v>162</v>
       </c>
@@ -7569,7 +7608,7 @@
         <v>167</v>
       </c>
     </row>
-    <row r="67" spans="2:13" x14ac:dyDescent="0.3">
+    <row r="67" spans="2:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="B67" t="s">
         <v>162</v>
       </c>
@@ -7599,7 +7638,7 @@
         <v>167</v>
       </c>
     </row>
-    <row r="68" spans="2:13" x14ac:dyDescent="0.3">
+    <row r="68" spans="2:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="B68" t="s">
         <v>162</v>
       </c>
@@ -7629,7 +7668,7 @@
         <v>167</v>
       </c>
     </row>
-    <row r="69" spans="2:13" x14ac:dyDescent="0.3">
+    <row r="69" spans="2:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="B69" t="s">
         <v>162</v>
       </c>
@@ -7659,7 +7698,7 @@
         <v>167</v>
       </c>
     </row>
-    <row r="70" spans="2:13" x14ac:dyDescent="0.3">
+    <row r="70" spans="2:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="B70" t="s">
         <v>162</v>
       </c>
@@ -7689,7 +7728,7 @@
         <v>184</v>
       </c>
     </row>
-    <row r="71" spans="2:13" x14ac:dyDescent="0.3">
+    <row r="71" spans="2:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="B71" t="s">
         <v>162</v>
       </c>
@@ -7719,7 +7758,7 @@
         <v>184</v>
       </c>
     </row>
-    <row r="72" spans="2:13" x14ac:dyDescent="0.3">
+    <row r="72" spans="2:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="B72" t="s">
         <v>162</v>
       </c>
@@ -7749,7 +7788,7 @@
         <v>184</v>
       </c>
     </row>
-    <row r="73" spans="2:13" x14ac:dyDescent="0.3">
+    <row r="73" spans="2:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="B73" t="s">
         <v>162</v>
       </c>
@@ -7779,7 +7818,7 @@
         <v>184</v>
       </c>
     </row>
-    <row r="74" spans="2:13" x14ac:dyDescent="0.3">
+    <row r="74" spans="2:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="B74" t="s">
         <v>162</v>
       </c>
@@ -7809,7 +7848,7 @@
         <v>184</v>
       </c>
     </row>
-    <row r="75" spans="2:13" x14ac:dyDescent="0.3">
+    <row r="75" spans="2:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="B75" t="s">
         <v>162</v>
       </c>
@@ -7839,7 +7878,7 @@
         <v>184</v>
       </c>
     </row>
-    <row r="76" spans="2:13" x14ac:dyDescent="0.3">
+    <row r="76" spans="2:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="B76" t="s">
         <v>162</v>
       </c>
@@ -7869,7 +7908,7 @@
         <v>184</v>
       </c>
     </row>
-    <row r="77" spans="2:13" x14ac:dyDescent="0.3">
+    <row r="77" spans="2:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="B77" t="s">
         <v>162</v>
       </c>
@@ -7899,7 +7938,7 @@
         <v>184</v>
       </c>
     </row>
-    <row r="78" spans="2:13" x14ac:dyDescent="0.3">
+    <row r="78" spans="2:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="B78" t="s">
         <v>162</v>
       </c>
@@ -7929,7 +7968,7 @@
         <v>184</v>
       </c>
     </row>
-    <row r="79" spans="2:13" x14ac:dyDescent="0.3">
+    <row r="79" spans="2:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="C79" t="s">
         <v>79</v>
       </c>
@@ -7956,7 +7995,7 @@
         <v>198</v>
       </c>
     </row>
-    <row r="80" spans="2:13" x14ac:dyDescent="0.3">
+    <row r="80" spans="2:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="C80" t="s">
         <v>79</v>
       </c>
@@ -7983,7 +8022,7 @@
         <v>198</v>
       </c>
     </row>
-    <row r="81" spans="3:13" x14ac:dyDescent="0.3">
+    <row r="81" spans="3:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="C81" t="s">
         <v>79</v>
       </c>
@@ -8010,7 +8049,7 @@
         <v>198</v>
       </c>
     </row>
-    <row r="82" spans="3:13" x14ac:dyDescent="0.3">
+    <row r="82" spans="3:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="C82" t="s">
         <v>79</v>
       </c>
@@ -8037,7 +8076,7 @@
         <v>198</v>
       </c>
     </row>
-    <row r="83" spans="3:13" x14ac:dyDescent="0.3">
+    <row r="83" spans="3:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="C83" t="s">
         <v>45</v>
       </c>
@@ -8067,7 +8106,7 @@
         <v>207</v>
       </c>
     </row>
-    <row r="84" spans="3:13" x14ac:dyDescent="0.3">
+    <row r="84" spans="3:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="C84" t="s">
         <v>45</v>
       </c>
@@ -8097,7 +8136,7 @@
         <v>207</v>
       </c>
     </row>
-    <row r="85" spans="3:13" x14ac:dyDescent="0.3">
+    <row r="85" spans="3:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="C85" t="s">
         <v>45</v>
       </c>
@@ -8127,7 +8166,7 @@
         <v>207</v>
       </c>
     </row>
-    <row r="86" spans="3:13" x14ac:dyDescent="0.3">
+    <row r="86" spans="3:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="C86" t="s">
         <v>45</v>
       </c>
@@ -8157,7 +8196,7 @@
         <v>207</v>
       </c>
     </row>
-    <row r="87" spans="3:13" x14ac:dyDescent="0.3">
+    <row r="87" spans="3:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="C87" t="s">
         <v>45</v>
       </c>
@@ -8187,7 +8226,7 @@
         <v>207</v>
       </c>
     </row>
-    <row r="88" spans="3:13" x14ac:dyDescent="0.3">
+    <row r="88" spans="3:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="C88" t="s">
         <v>45</v>
       </c>
@@ -8217,7 +8256,7 @@
         <v>207</v>
       </c>
     </row>
-    <row r="89" spans="3:13" x14ac:dyDescent="0.3">
+    <row r="89" spans="3:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="C89" t="s">
         <v>59</v>
       </c>
@@ -8244,7 +8283,7 @@
         <v>214</v>
       </c>
     </row>
-    <row r="90" spans="3:13" x14ac:dyDescent="0.3">
+    <row r="90" spans="3:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="C90" t="s">
         <v>59</v>
       </c>
@@ -8271,7 +8310,7 @@
         <v>214</v>
       </c>
     </row>
-    <row r="91" spans="3:13" x14ac:dyDescent="0.3">
+    <row r="91" spans="3:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="C91" t="s">
         <v>59</v>
       </c>
@@ -8298,7 +8337,7 @@
         <v>214</v>
       </c>
     </row>
-    <row r="92" spans="3:13" x14ac:dyDescent="0.3">
+    <row r="92" spans="3:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="C92" t="s">
         <v>59</v>
       </c>
@@ -8325,7 +8364,7 @@
         <v>214</v>
       </c>
     </row>
-    <row r="93" spans="3:13" x14ac:dyDescent="0.3">
+    <row r="93" spans="3:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="C93" t="s">
         <v>69</v>
       </c>
@@ -8352,7 +8391,7 @@
         <v>219</v>
       </c>
     </row>
-    <row r="94" spans="3:13" x14ac:dyDescent="0.3">
+    <row r="94" spans="3:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="C94" t="s">
         <v>69</v>
       </c>
@@ -8379,7 +8418,7 @@
         <v>219</v>
       </c>
     </row>
-    <row r="95" spans="3:13" x14ac:dyDescent="0.3">
+    <row r="95" spans="3:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="C95" t="s">
         <v>69</v>
       </c>
@@ -8406,7 +8445,7 @@
         <v>219</v>
       </c>
     </row>
-    <row r="96" spans="3:13" x14ac:dyDescent="0.3">
+    <row r="96" spans="3:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="C96" t="s">
         <v>69</v>
       </c>
@@ -8433,7 +8472,7 @@
         <v>219</v>
       </c>
     </row>
-    <row r="97" spans="2:13" x14ac:dyDescent="0.3">
+    <row r="97" spans="2:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="B97" t="s">
         <v>137</v>
       </c>
@@ -8463,7 +8502,7 @@
         <v>229</v>
       </c>
     </row>
-    <row r="98" spans="2:13" x14ac:dyDescent="0.3">
+    <row r="98" spans="2:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="B98" t="s">
         <v>137</v>
       </c>
@@ -8493,7 +8532,7 @@
         <v>229</v>
       </c>
     </row>
-    <row r="99" spans="2:13" x14ac:dyDescent="0.3">
+    <row r="99" spans="2:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="B99" t="s">
         <v>137</v>
       </c>
@@ -8523,7 +8562,7 @@
         <v>229</v>
       </c>
     </row>
-    <row r="100" spans="2:13" x14ac:dyDescent="0.3">
+    <row r="100" spans="2:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="B100" t="s">
         <v>162</v>
       </c>
@@ -8553,7 +8592,7 @@
         <v>237</v>
       </c>
     </row>
-    <row r="101" spans="2:13" x14ac:dyDescent="0.3">
+    <row r="101" spans="2:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="B101" t="s">
         <v>162</v>
       </c>
@@ -8580,7 +8619,7 @@
         <v>237</v>
       </c>
     </row>
-    <row r="102" spans="2:13" x14ac:dyDescent="0.3">
+    <row r="102" spans="2:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="B102" t="s">
         <v>162</v>
       </c>
@@ -8607,7 +8646,7 @@
         <v>237</v>
       </c>
     </row>
-    <row r="103" spans="2:13" x14ac:dyDescent="0.3">
+    <row r="103" spans="2:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="B103" t="s">
         <v>162</v>
       </c>
@@ -8637,7 +8676,7 @@
         <v>237</v>
       </c>
     </row>
-    <row r="104" spans="2:13" x14ac:dyDescent="0.3">
+    <row r="104" spans="2:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="B104" t="s">
         <v>162</v>
       </c>
@@ -8664,7 +8703,7 @@
         <v>237</v>
       </c>
     </row>
-    <row r="105" spans="2:13" x14ac:dyDescent="0.3">
+    <row r="105" spans="2:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="B105" t="s">
         <v>162</v>
       </c>
@@ -8691,7 +8730,7 @@
         <v>237</v>
       </c>
     </row>
-    <row r="106" spans="2:13" x14ac:dyDescent="0.3">
+    <row r="106" spans="2:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="B106" t="s">
         <v>162</v>
       </c>
@@ -8718,7 +8757,7 @@
         <v>237</v>
       </c>
     </row>
-    <row r="107" spans="2:13" x14ac:dyDescent="0.3">
+    <row r="107" spans="2:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="B107" t="s">
         <v>162</v>
       </c>
@@ -8745,7 +8784,7 @@
         <v>237</v>
       </c>
     </row>
-    <row r="108" spans="2:13" x14ac:dyDescent="0.3">
+    <row r="108" spans="2:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="B108" t="s">
         <v>162</v>
       </c>
@@ -8772,7 +8811,7 @@
         <v>237</v>
       </c>
     </row>
-    <row r="109" spans="2:13" x14ac:dyDescent="0.3">
+    <row r="109" spans="2:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="B109" t="s">
         <v>162</v>
       </c>
@@ -8799,7 +8838,7 @@
         <v>237</v>
       </c>
     </row>
-    <row r="110" spans="2:13" x14ac:dyDescent="0.3">
+    <row r="110" spans="2:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="B110" t="s">
         <v>162</v>
       </c>
@@ -8826,7 +8865,7 @@
         <v>237</v>
       </c>
     </row>
-    <row r="111" spans="2:13" x14ac:dyDescent="0.3">
+    <row r="111" spans="2:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="B111" t="s">
         <v>162</v>
       </c>
@@ -8853,7 +8892,7 @@
         <v>237</v>
       </c>
     </row>
-    <row r="112" spans="2:13" x14ac:dyDescent="0.3">
+    <row r="112" spans="2:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="C112" t="s">
         <v>90</v>
       </c>
@@ -8880,7 +8919,7 @@
         <v>247</v>
       </c>
     </row>
-    <row r="113" spans="2:13" x14ac:dyDescent="0.3">
+    <row r="113" spans="2:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="C113" t="s">
         <v>90</v>
       </c>
@@ -8907,7 +8946,7 @@
         <v>247</v>
       </c>
     </row>
-    <row r="114" spans="2:13" x14ac:dyDescent="0.3">
+    <row r="114" spans="2:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="C114" t="s">
         <v>90</v>
       </c>
@@ -8934,7 +8973,7 @@
         <v>247</v>
       </c>
     </row>
-    <row r="115" spans="2:13" x14ac:dyDescent="0.3">
+    <row r="115" spans="2:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="C115" t="s">
         <v>90</v>
       </c>
@@ -8961,7 +9000,7 @@
         <v>247</v>
       </c>
     </row>
-    <row r="116" spans="2:13" x14ac:dyDescent="0.3">
+    <row r="116" spans="2:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="B116" t="s">
         <v>137</v>
       </c>
@@ -8988,7 +9027,7 @@
         <v>255</v>
       </c>
     </row>
-    <row r="117" spans="2:13" x14ac:dyDescent="0.3">
+    <row r="117" spans="2:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="B117" t="s">
         <v>137</v>
       </c>
@@ -9015,7 +9054,7 @@
         <v>255</v>
       </c>
     </row>
-    <row r="118" spans="2:13" x14ac:dyDescent="0.3">
+    <row r="118" spans="2:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="B118" t="s">
         <v>137</v>
       </c>
@@ -9042,7 +9081,7 @@
         <v>255</v>
       </c>
     </row>
-    <row r="119" spans="2:13" x14ac:dyDescent="0.3">
+    <row r="119" spans="2:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="B119" t="s">
         <v>137</v>
       </c>
@@ -9069,7 +9108,7 @@
         <v>255</v>
       </c>
     </row>
-    <row r="120" spans="2:13" x14ac:dyDescent="0.3">
+    <row r="120" spans="2:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="B120" t="s">
         <v>137</v>
       </c>
@@ -9096,7 +9135,7 @@
         <v>265</v>
       </c>
     </row>
-    <row r="121" spans="2:13" x14ac:dyDescent="0.3">
+    <row r="121" spans="2:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="B121" t="s">
         <v>137</v>
       </c>
@@ -9123,7 +9162,7 @@
         <v>265</v>
       </c>
     </row>
-    <row r="122" spans="2:13" x14ac:dyDescent="0.3">
+    <row r="122" spans="2:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="B122" t="s">
         <v>137</v>
       </c>
@@ -9150,7 +9189,7 @@
         <v>265</v>
       </c>
     </row>
-    <row r="123" spans="2:13" x14ac:dyDescent="0.3">
+    <row r="123" spans="2:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="B123" t="s">
         <v>137</v>
       </c>
@@ -9177,7 +9216,7 @@
         <v>265</v>
       </c>
     </row>
-    <row r="124" spans="2:13" x14ac:dyDescent="0.3">
+    <row r="124" spans="2:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="B124" t="s">
         <v>162</v>
       </c>
@@ -9207,7 +9246,7 @@
         <v>273</v>
       </c>
     </row>
-    <row r="125" spans="2:13" x14ac:dyDescent="0.3">
+    <row r="125" spans="2:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="B125" t="s">
         <v>162</v>
       </c>
@@ -9237,7 +9276,7 @@
         <v>273</v>
       </c>
     </row>
-    <row r="126" spans="2:13" x14ac:dyDescent="0.3">
+    <row r="126" spans="2:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="B126" t="s">
         <v>162</v>
       </c>
@@ -9267,7 +9306,7 @@
         <v>273</v>
       </c>
     </row>
-    <row r="127" spans="2:13" x14ac:dyDescent="0.3">
+    <row r="127" spans="2:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="B127" t="s">
         <v>162</v>
       </c>
@@ -9297,7 +9336,7 @@
         <v>273</v>
       </c>
     </row>
-    <row r="128" spans="2:13" x14ac:dyDescent="0.3">
+    <row r="128" spans="2:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="B128" t="s">
         <v>162</v>
       </c>
@@ -9327,7 +9366,7 @@
         <v>273</v>
       </c>
     </row>
-    <row r="129" spans="2:13" x14ac:dyDescent="0.3">
+    <row r="129" spans="2:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="B129" t="s">
         <v>162</v>
       </c>
@@ -9357,7 +9396,7 @@
         <v>273</v>
       </c>
     </row>
-    <row r="130" spans="2:13" x14ac:dyDescent="0.3">
+    <row r="130" spans="2:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="B130" t="s">
         <v>162</v>
       </c>
@@ -9387,7 +9426,7 @@
         <v>273</v>
       </c>
     </row>
-    <row r="131" spans="2:13" x14ac:dyDescent="0.3">
+    <row r="131" spans="2:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="B131" t="s">
         <v>162</v>
       </c>
@@ -9417,7 +9456,7 @@
         <v>273</v>
       </c>
     </row>
-    <row r="132" spans="2:13" x14ac:dyDescent="0.3">
+    <row r="132" spans="2:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="B132" t="s">
         <v>162</v>
       </c>
@@ -9447,7 +9486,7 @@
         <v>273</v>
       </c>
     </row>
-    <row r="133" spans="2:13" x14ac:dyDescent="0.3">
+    <row r="133" spans="2:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="C133" t="s">
         <v>129</v>
       </c>
@@ -9474,7 +9513,7 @@
         <v>284</v>
       </c>
     </row>
-    <row r="134" spans="2:13" x14ac:dyDescent="0.3">
+    <row r="134" spans="2:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="C134" t="s">
         <v>129</v>
       </c>
@@ -9501,7 +9540,7 @@
         <v>284</v>
       </c>
     </row>
-    <row r="135" spans="2:13" x14ac:dyDescent="0.3">
+    <row r="135" spans="2:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="C135" t="s">
         <v>129</v>
       </c>
@@ -9528,7 +9567,7 @@
         <v>284</v>
       </c>
     </row>
-    <row r="136" spans="2:13" x14ac:dyDescent="0.3">
+    <row r="136" spans="2:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="C136" t="s">
         <v>129</v>
       </c>
@@ -9555,7 +9594,7 @@
         <v>284</v>
       </c>
     </row>
-    <row r="137" spans="2:13" x14ac:dyDescent="0.3">
+    <row r="137" spans="2:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="C137" t="s">
         <v>150</v>
       </c>
@@ -9582,7 +9621,7 @@
         <v>290</v>
       </c>
     </row>
-    <row r="138" spans="2:13" x14ac:dyDescent="0.3">
+    <row r="138" spans="2:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="C138" t="s">
         <v>150</v>
       </c>
@@ -9609,7 +9648,7 @@
         <v>290</v>
       </c>
     </row>
-    <row r="139" spans="2:13" x14ac:dyDescent="0.3">
+    <row r="139" spans="2:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="C139" t="s">
         <v>150</v>
       </c>
@@ -9636,7 +9675,7 @@
         <v>290</v>
       </c>
     </row>
-    <row r="140" spans="2:13" x14ac:dyDescent="0.3">
+    <row r="140" spans="2:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="C140" t="s">
         <v>150</v>
       </c>
@@ -9663,7 +9702,7 @@
         <v>290</v>
       </c>
     </row>
-    <row r="141" spans="2:13" x14ac:dyDescent="0.3">
+    <row r="141" spans="2:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="C141" t="s">
         <v>294</v>
       </c>
@@ -9693,7 +9732,7 @@
         <v>297</v>
       </c>
     </row>
-    <row r="142" spans="2:13" x14ac:dyDescent="0.3">
+    <row r="142" spans="2:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="C142" t="s">
         <v>294</v>
       </c>
@@ -9723,7 +9762,7 @@
         <v>297</v>
       </c>
     </row>
-    <row r="143" spans="2:13" x14ac:dyDescent="0.3">
+    <row r="143" spans="2:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="C143" t="s">
         <v>294</v>
       </c>
@@ -9753,7 +9792,7 @@
         <v>297</v>
       </c>
     </row>
-    <row r="144" spans="2:13" x14ac:dyDescent="0.3">
+    <row r="144" spans="2:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="C144" t="s">
         <v>294</v>
       </c>
@@ -9783,7 +9822,7 @@
         <v>297</v>
       </c>
     </row>
-    <row r="145" spans="2:13" x14ac:dyDescent="0.3">
+    <row r="145" spans="2:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="B145" t="s">
         <v>302</v>
       </c>
@@ -9813,7 +9852,7 @@
         <v>307</v>
       </c>
     </row>
-    <row r="146" spans="2:13" x14ac:dyDescent="0.3">
+    <row r="146" spans="2:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="B146" t="s">
         <v>302</v>
       </c>
@@ -9843,7 +9882,7 @@
         <v>307</v>
       </c>
     </row>
-    <row r="147" spans="2:13" x14ac:dyDescent="0.3">
+    <row r="147" spans="2:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="B147" t="s">
         <v>302</v>
       </c>
@@ -9873,7 +9912,7 @@
         <v>307</v>
       </c>
     </row>
-    <row r="148" spans="2:13" x14ac:dyDescent="0.3">
+    <row r="148" spans="2:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="B148" t="s">
         <v>302</v>
       </c>
@@ -9903,7 +9942,7 @@
         <v>307</v>
       </c>
     </row>
-    <row r="149" spans="2:13" x14ac:dyDescent="0.3">
+    <row r="149" spans="2:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="D149" t="s">
         <v>312</v>
       </c>
@@ -9930,7 +9969,7 @@
         <v>314</v>
       </c>
     </row>
-    <row r="150" spans="2:13" x14ac:dyDescent="0.3">
+    <row r="150" spans="2:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="D150" t="s">
         <v>312</v>
       </c>
@@ -9957,7 +9996,7 @@
         <v>314</v>
       </c>
     </row>
-    <row r="151" spans="2:13" x14ac:dyDescent="0.3">
+    <row r="151" spans="2:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="D151" t="s">
         <v>312</v>
       </c>
@@ -9984,7 +10023,7 @@
         <v>314</v>
       </c>
     </row>
-    <row r="152" spans="2:13" x14ac:dyDescent="0.3">
+    <row r="152" spans="2:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="D152" t="s">
         <v>312</v>
       </c>
@@ -10011,7 +10050,7 @@
         <v>314</v>
       </c>
     </row>
-    <row r="153" spans="2:13" x14ac:dyDescent="0.3">
+    <row r="153" spans="2:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="D153" t="s">
         <v>312</v>
       </c>
@@ -10038,7 +10077,7 @@
         <v>314</v>
       </c>
     </row>
-    <row r="154" spans="2:13" x14ac:dyDescent="0.3">
+    <row r="154" spans="2:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="D154" t="s">
         <v>312</v>
       </c>
@@ -10065,7 +10104,7 @@
         <v>314</v>
       </c>
     </row>
-    <row r="155" spans="2:13" x14ac:dyDescent="0.3">
+    <row r="155" spans="2:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="C155" t="s">
         <v>27</v>
       </c>
@@ -10095,7 +10134,7 @@
         <v>327</v>
       </c>
     </row>
-    <row r="156" spans="2:13" x14ac:dyDescent="0.3">
+    <row r="156" spans="2:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="C156" t="s">
         <v>27</v>
       </c>
@@ -10125,7 +10164,7 @@
         <v>327</v>
       </c>
     </row>
-    <row r="157" spans="2:13" x14ac:dyDescent="0.3">
+    <row r="157" spans="2:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="C157" t="s">
         <v>27</v>
       </c>
@@ -10155,7 +10194,7 @@
         <v>327</v>
       </c>
     </row>
-    <row r="158" spans="2:13" x14ac:dyDescent="0.3">
+    <row r="158" spans="2:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="C158" t="s">
         <v>27</v>
       </c>
@@ -10185,7 +10224,7 @@
         <v>327</v>
       </c>
     </row>
-    <row r="159" spans="2:13" x14ac:dyDescent="0.3">
+    <row r="159" spans="2:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="C159" t="s">
         <v>27</v>
       </c>
@@ -10215,7 +10254,7 @@
         <v>327</v>
       </c>
     </row>
-    <row r="160" spans="2:13" x14ac:dyDescent="0.3">
+    <row r="160" spans="2:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="C160" t="s">
         <v>27</v>
       </c>
@@ -10245,7 +10284,7 @@
         <v>327</v>
       </c>
     </row>
-    <row r="161" spans="3:13" x14ac:dyDescent="0.3">
+    <row r="161" spans="3:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="C161" t="s">
         <v>27</v>
       </c>
@@ -10275,7 +10314,7 @@
         <v>327</v>
       </c>
     </row>
-    <row r="162" spans="3:13" x14ac:dyDescent="0.3">
+    <row r="162" spans="3:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="C162" t="s">
         <v>27</v>
       </c>
@@ -10305,7 +10344,7 @@
         <v>327</v>
       </c>
     </row>
-    <row r="163" spans="3:13" x14ac:dyDescent="0.3">
+    <row r="163" spans="3:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="C163" t="s">
         <v>45</v>
       </c>
@@ -10335,7 +10374,7 @@
         <v>339</v>
       </c>
     </row>
-    <row r="164" spans="3:13" x14ac:dyDescent="0.3">
+    <row r="164" spans="3:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="C164" t="s">
         <v>45</v>
       </c>
@@ -10365,7 +10404,7 @@
         <v>339</v>
       </c>
     </row>
-    <row r="165" spans="3:13" x14ac:dyDescent="0.3">
+    <row r="165" spans="3:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="C165" t="s">
         <v>45</v>
       </c>
@@ -10395,7 +10434,7 @@
         <v>339</v>
       </c>
     </row>
-    <row r="166" spans="3:13" x14ac:dyDescent="0.3">
+    <row r="166" spans="3:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="C166" t="s">
         <v>45</v>
       </c>
@@ -10425,7 +10464,7 @@
         <v>339</v>
       </c>
     </row>
-    <row r="167" spans="3:13" x14ac:dyDescent="0.3">
+    <row r="167" spans="3:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="C167" t="s">
         <v>45</v>
       </c>
@@ -10455,7 +10494,7 @@
         <v>339</v>
       </c>
     </row>
-    <row r="168" spans="3:13" x14ac:dyDescent="0.3">
+    <row r="168" spans="3:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="C168" t="s">
         <v>45</v>
       </c>
@@ -10485,7 +10524,7 @@
         <v>339</v>
       </c>
     </row>
-    <row r="169" spans="3:13" x14ac:dyDescent="0.3">
+    <row r="169" spans="3:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="C169" t="s">
         <v>79</v>
       </c>
@@ -10515,7 +10554,7 @@
         <v>347</v>
       </c>
     </row>
-    <row r="170" spans="3:13" x14ac:dyDescent="0.3">
+    <row r="170" spans="3:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="C170" t="s">
         <v>79</v>
       </c>
@@ -10545,7 +10584,7 @@
         <v>347</v>
       </c>
     </row>
-    <row r="171" spans="3:13" x14ac:dyDescent="0.3">
+    <row r="171" spans="3:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="C171" t="s">
         <v>79</v>
       </c>
@@ -10575,7 +10614,7 @@
         <v>347</v>
       </c>
     </row>
-    <row r="172" spans="3:13" x14ac:dyDescent="0.3">
+    <row r="172" spans="3:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="C172" t="s">
         <v>79</v>
       </c>
@@ -10605,7 +10644,7 @@
         <v>347</v>
       </c>
     </row>
-    <row r="173" spans="3:13" x14ac:dyDescent="0.3">
+    <row r="173" spans="3:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="C173" t="s">
         <v>69</v>
       </c>
@@ -10635,7 +10674,7 @@
         <v>354</v>
       </c>
     </row>
-    <row r="174" spans="3:13" x14ac:dyDescent="0.3">
+    <row r="174" spans="3:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="C174" t="s">
         <v>69</v>
       </c>
@@ -10665,7 +10704,7 @@
         <v>354</v>
       </c>
     </row>
-    <row r="175" spans="3:13" x14ac:dyDescent="0.3">
+    <row r="175" spans="3:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="C175" t="s">
         <v>69</v>
       </c>
@@ -10695,7 +10734,7 @@
         <v>354</v>
       </c>
     </row>
-    <row r="176" spans="3:13" x14ac:dyDescent="0.3">
+    <row r="176" spans="3:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="C176" t="s">
         <v>69</v>
       </c>
@@ -10725,7 +10764,7 @@
         <v>354</v>
       </c>
     </row>
-    <row r="177" spans="2:13" x14ac:dyDescent="0.3">
+    <row r="177" spans="2:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="B177" t="s">
         <v>162</v>
       </c>
@@ -10755,7 +10794,7 @@
         <v>358</v>
       </c>
     </row>
-    <row r="178" spans="2:13" x14ac:dyDescent="0.3">
+    <row r="178" spans="2:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="B178" t="s">
         <v>162</v>
       </c>
@@ -10785,7 +10824,7 @@
         <v>358</v>
       </c>
     </row>
-    <row r="179" spans="2:13" x14ac:dyDescent="0.3">
+    <row r="179" spans="2:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="B179" t="s">
         <v>162</v>
       </c>
@@ -10815,7 +10854,7 @@
         <v>358</v>
       </c>
     </row>
-    <row r="180" spans="2:13" x14ac:dyDescent="0.3">
+    <row r="180" spans="2:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="B180" t="s">
         <v>162</v>
       </c>
@@ -10845,7 +10884,7 @@
         <v>358</v>
       </c>
     </row>
-    <row r="181" spans="2:13" x14ac:dyDescent="0.3">
+    <row r="181" spans="2:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="B181" t="s">
         <v>162</v>
       </c>
@@ -10875,7 +10914,7 @@
         <v>358</v>
       </c>
     </row>
-    <row r="182" spans="2:13" x14ac:dyDescent="0.3">
+    <row r="182" spans="2:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="B182" t="s">
         <v>162</v>
       </c>
@@ -10905,7 +10944,7 @@
         <v>358</v>
       </c>
     </row>
-    <row r="183" spans="2:13" x14ac:dyDescent="0.3">
+    <row r="183" spans="2:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="B183" t="s">
         <v>162</v>
       </c>
@@ -10935,7 +10974,7 @@
         <v>358</v>
       </c>
     </row>
-    <row r="184" spans="2:13" x14ac:dyDescent="0.3">
+    <row r="184" spans="2:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="B184" t="s">
         <v>162</v>
       </c>
@@ -10965,7 +11004,7 @@
         <v>358</v>
       </c>
     </row>
-    <row r="185" spans="2:13" x14ac:dyDescent="0.3">
+    <row r="185" spans="2:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="B185" t="s">
         <v>162</v>
       </c>
@@ -10995,7 +11034,7 @@
         <v>358</v>
       </c>
     </row>
-    <row r="186" spans="2:13" x14ac:dyDescent="0.3">
+    <row r="186" spans="2:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="B186" t="s">
         <v>162</v>
       </c>
@@ -11025,7 +11064,7 @@
         <v>358</v>
       </c>
     </row>
-    <row r="187" spans="2:13" x14ac:dyDescent="0.3">
+    <row r="187" spans="2:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="B187" t="s">
         <v>162</v>
       </c>
@@ -11055,7 +11094,7 @@
         <v>358</v>
       </c>
     </row>
-    <row r="188" spans="2:13" x14ac:dyDescent="0.3">
+    <row r="188" spans="2:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="B188" t="s">
         <v>162</v>
       </c>
@@ -11085,7 +11124,7 @@
         <v>358</v>
       </c>
     </row>
-    <row r="189" spans="2:13" x14ac:dyDescent="0.3">
+    <row r="189" spans="2:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="C189" t="s">
         <v>372</v>
       </c>
@@ -11112,7 +11151,7 @@
         <v>375</v>
       </c>
     </row>
-    <row r="190" spans="2:13" x14ac:dyDescent="0.3">
+    <row r="190" spans="2:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="C190" t="s">
         <v>372</v>
       </c>
@@ -11139,7 +11178,7 @@
         <v>375</v>
       </c>
     </row>
-    <row r="191" spans="2:13" x14ac:dyDescent="0.3">
+    <row r="191" spans="2:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="C191" t="s">
         <v>372</v>
       </c>
@@ -11166,7 +11205,7 @@
         <v>375</v>
       </c>
     </row>
-    <row r="192" spans="2:13" x14ac:dyDescent="0.3">
+    <row r="192" spans="2:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="C192" t="s">
         <v>372</v>
       </c>
@@ -11193,7 +11232,7 @@
         <v>375</v>
       </c>
     </row>
-    <row r="193" spans="3:13" x14ac:dyDescent="0.3">
+    <row r="193" spans="3:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="C193" t="s">
         <v>101</v>
       </c>
@@ -11220,7 +11259,7 @@
         <v>380</v>
       </c>
     </row>
-    <row r="194" spans="3:13" x14ac:dyDescent="0.3">
+    <row r="194" spans="3:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="C194" t="s">
         <v>101</v>
       </c>
@@ -11247,7 +11286,7 @@
         <v>380</v>
       </c>
     </row>
-    <row r="195" spans="3:13" x14ac:dyDescent="0.3">
+    <row r="195" spans="3:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="C195" t="s">
         <v>101</v>
       </c>
@@ -11274,7 +11313,7 @@
         <v>380</v>
       </c>
     </row>
-    <row r="196" spans="3:13" x14ac:dyDescent="0.3">
+    <row r="196" spans="3:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="C196" t="s">
         <v>101</v>
       </c>
@@ -11301,7 +11340,7 @@
         <v>380</v>
       </c>
     </row>
-    <row r="197" spans="3:13" x14ac:dyDescent="0.3">
+    <row r="197" spans="3:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="C197" t="s">
         <v>382</v>
       </c>
@@ -11331,7 +11370,7 @@
         <v>386</v>
       </c>
     </row>
-    <row r="198" spans="3:13" x14ac:dyDescent="0.3">
+    <row r="198" spans="3:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="C198" t="s">
         <v>382</v>
       </c>
@@ -11361,7 +11400,7 @@
         <v>386</v>
       </c>
     </row>
-    <row r="199" spans="3:13" x14ac:dyDescent="0.3">
+    <row r="199" spans="3:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="C199" t="s">
         <v>382</v>
       </c>
@@ -11391,7 +11430,7 @@
         <v>386</v>
       </c>
     </row>
-    <row r="200" spans="3:13" x14ac:dyDescent="0.3">
+    <row r="200" spans="3:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="C200" t="s">
         <v>382</v>
       </c>
@@ -11421,7 +11460,7 @@
         <v>386</v>
       </c>
     </row>
-    <row r="201" spans="3:13" x14ac:dyDescent="0.3">
+    <row r="201" spans="3:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="C201" t="s">
         <v>382</v>
       </c>
@@ -11451,7 +11490,7 @@
         <v>386</v>
       </c>
     </row>
-    <row r="202" spans="3:13" x14ac:dyDescent="0.3">
+    <row r="202" spans="3:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="C202" t="s">
         <v>110</v>
       </c>
@@ -11478,7 +11517,7 @@
         <v>396</v>
       </c>
     </row>
-    <row r="203" spans="3:13" x14ac:dyDescent="0.3">
+    <row r="203" spans="3:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="C203" t="s">
         <v>110</v>
       </c>
@@ -11505,7 +11544,7 @@
         <v>396</v>
       </c>
     </row>
-    <row r="204" spans="3:13" x14ac:dyDescent="0.3">
+    <row r="204" spans="3:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="C204" t="s">
         <v>110</v>
       </c>
@@ -11532,7 +11571,7 @@
         <v>396</v>
       </c>
     </row>
-    <row r="205" spans="3:13" x14ac:dyDescent="0.3">
+    <row r="205" spans="3:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="C205" t="s">
         <v>110</v>
       </c>
@@ -11559,7 +11598,7 @@
         <v>396</v>
       </c>
     </row>
-    <row r="206" spans="3:13" x14ac:dyDescent="0.3">
+    <row r="206" spans="3:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="C206" t="s">
         <v>399</v>
       </c>
@@ -11586,7 +11625,7 @@
         <v>402</v>
       </c>
     </row>
-    <row r="207" spans="3:13" x14ac:dyDescent="0.3">
+    <row r="207" spans="3:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="C207" t="s">
         <v>399</v>
       </c>
@@ -11613,7 +11652,7 @@
         <v>402</v>
       </c>
     </row>
-    <row r="208" spans="3:13" x14ac:dyDescent="0.3">
+    <row r="208" spans="3:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="C208" t="s">
         <v>399</v>
       </c>
@@ -11640,7 +11679,7 @@
         <v>402</v>
       </c>
     </row>
-    <row r="209" spans="2:13" x14ac:dyDescent="0.3">
+    <row r="209" spans="2:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="C209" t="s">
         <v>399</v>
       </c>
@@ -11667,7 +11706,7 @@
         <v>402</v>
       </c>
     </row>
-    <row r="210" spans="2:13" x14ac:dyDescent="0.3">
+    <row r="210" spans="2:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="B210" t="s">
         <v>162</v>
       </c>
@@ -11697,7 +11736,7 @@
         <v>407</v>
       </c>
     </row>
-    <row r="211" spans="2:13" x14ac:dyDescent="0.3">
+    <row r="211" spans="2:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="B211" t="s">
         <v>162</v>
       </c>
@@ -11727,7 +11766,7 @@
         <v>407</v>
       </c>
     </row>
-    <row r="212" spans="2:13" x14ac:dyDescent="0.3">
+    <row r="212" spans="2:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="B212" t="s">
         <v>162</v>
       </c>
@@ -11754,7 +11793,7 @@
         <v>407</v>
       </c>
     </row>
-    <row r="213" spans="2:13" x14ac:dyDescent="0.3">
+    <row r="213" spans="2:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="B213" t="s">
         <v>162</v>
       </c>
@@ -11784,7 +11823,7 @@
         <v>407</v>
       </c>
     </row>
-    <row r="214" spans="2:13" x14ac:dyDescent="0.3">
+    <row r="214" spans="2:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="B214" t="s">
         <v>162</v>
       </c>
@@ -11811,7 +11850,7 @@
         <v>407</v>
       </c>
     </row>
-    <row r="215" spans="2:13" x14ac:dyDescent="0.3">
+    <row r="215" spans="2:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="B215" t="s">
         <v>162</v>
       </c>
@@ -11841,7 +11880,7 @@
         <v>407</v>
       </c>
     </row>
-    <row r="216" spans="2:13" x14ac:dyDescent="0.3">
+    <row r="216" spans="2:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="B216" t="s">
         <v>162</v>
       </c>
@@ -11868,7 +11907,7 @@
         <v>407</v>
       </c>
     </row>
-    <row r="217" spans="2:13" x14ac:dyDescent="0.3">
+    <row r="217" spans="2:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="B217" t="s">
         <v>162</v>
       </c>
@@ -11895,7 +11934,7 @@
         <v>407</v>
       </c>
     </row>
-    <row r="218" spans="2:13" x14ac:dyDescent="0.3">
+    <row r="218" spans="2:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="B218" t="s">
         <v>162</v>
       </c>
@@ -11925,7 +11964,7 @@
         <v>407</v>
       </c>
     </row>
-    <row r="219" spans="2:13" x14ac:dyDescent="0.3">
+    <row r="219" spans="2:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="B219" t="s">
         <v>162</v>
       </c>
@@ -11952,7 +11991,7 @@
         <v>407</v>
       </c>
     </row>
-    <row r="220" spans="2:13" x14ac:dyDescent="0.3">
+    <row r="220" spans="2:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="B220" t="s">
         <v>162</v>
       </c>
@@ -11982,7 +12021,7 @@
         <v>407</v>
       </c>
     </row>
-    <row r="221" spans="2:13" x14ac:dyDescent="0.3">
+    <row r="221" spans="2:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="B221" t="s">
         <v>162</v>
       </c>
@@ -12012,7 +12051,7 @@
         <v>407</v>
       </c>
     </row>
-    <row r="222" spans="2:13" x14ac:dyDescent="0.3">
+    <row r="222" spans="2:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="C222" t="s">
         <v>129</v>
       </c>
@@ -12039,7 +12078,7 @@
         <v>412</v>
       </c>
     </row>
-    <row r="223" spans="2:13" x14ac:dyDescent="0.3">
+    <row r="223" spans="2:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="C223" t="s">
         <v>129</v>
       </c>
@@ -12066,7 +12105,7 @@
         <v>412</v>
       </c>
     </row>
-    <row r="224" spans="2:13" x14ac:dyDescent="0.3">
+    <row r="224" spans="2:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="C224" t="s">
         <v>129</v>
       </c>
@@ -12093,7 +12132,7 @@
         <v>412</v>
       </c>
     </row>
-    <row r="225" spans="2:13" x14ac:dyDescent="0.3">
+    <row r="225" spans="2:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="C225" t="s">
         <v>129</v>
       </c>
@@ -12120,7 +12159,7 @@
         <v>412</v>
       </c>
     </row>
-    <row r="226" spans="2:13" x14ac:dyDescent="0.3">
+    <row r="226" spans="2:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="B226" t="s">
         <v>137</v>
       </c>
@@ -12150,7 +12189,7 @@
         <v>420</v>
       </c>
     </row>
-    <row r="227" spans="2:13" x14ac:dyDescent="0.3">
+    <row r="227" spans="2:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="B227" t="s">
         <v>137</v>
       </c>
@@ -12180,7 +12219,7 @@
         <v>420</v>
       </c>
     </row>
-    <row r="228" spans="2:13" x14ac:dyDescent="0.3">
+    <row r="228" spans="2:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="C228" t="s">
         <v>150</v>
       </c>
@@ -12207,7 +12246,7 @@
         <v>425</v>
       </c>
     </row>
-    <row r="229" spans="2:13" x14ac:dyDescent="0.3">
+    <row r="229" spans="2:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="C229" t="s">
         <v>150</v>
       </c>
@@ -12234,7 +12273,7 @@
         <v>425</v>
       </c>
     </row>
-    <row r="230" spans="2:13" x14ac:dyDescent="0.3">
+    <row r="230" spans="2:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="C230" t="s">
         <v>150</v>
       </c>
@@ -12261,7 +12300,7 @@
         <v>425</v>
       </c>
     </row>
-    <row r="231" spans="2:13" x14ac:dyDescent="0.3">
+    <row r="231" spans="2:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="C231" t="s">
         <v>150</v>
       </c>
@@ -12288,7 +12327,7 @@
         <v>425</v>
       </c>
     </row>
-    <row r="232" spans="2:13" x14ac:dyDescent="0.3">
+    <row r="232" spans="2:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="C232" t="s">
         <v>294</v>
       </c>
@@ -12318,7 +12357,7 @@
         <v>432</v>
       </c>
     </row>
-    <row r="233" spans="2:13" x14ac:dyDescent="0.3">
+    <row r="233" spans="2:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="C233" t="s">
         <v>294</v>
       </c>
@@ -12348,7 +12387,7 @@
         <v>432</v>
       </c>
     </row>
-    <row r="234" spans="2:13" x14ac:dyDescent="0.3">
+    <row r="234" spans="2:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="C234" t="s">
         <v>294</v>
       </c>
@@ -12378,7 +12417,7 @@
         <v>432</v>
       </c>
     </row>
-    <row r="235" spans="2:13" x14ac:dyDescent="0.3">
+    <row r="235" spans="2:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="C235" t="s">
         <v>294</v>
       </c>
@@ -12408,7 +12447,7 @@
         <v>432</v>
       </c>
     </row>
-    <row r="236" spans="2:13" x14ac:dyDescent="0.3">
+    <row r="236" spans="2:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="B236" t="s">
         <v>302</v>
       </c>
@@ -12438,7 +12477,7 @@
         <v>439</v>
       </c>
     </row>
-    <row r="237" spans="2:13" x14ac:dyDescent="0.3">
+    <row r="237" spans="2:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="B237" t="s">
         <v>302</v>
       </c>
@@ -12468,7 +12507,7 @@
         <v>439</v>
       </c>
     </row>
-    <row r="238" spans="2:13" x14ac:dyDescent="0.3">
+    <row r="238" spans="2:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="B238" t="s">
         <v>302</v>
       </c>
@@ -12498,7 +12537,7 @@
         <v>439</v>
       </c>
     </row>
-    <row r="239" spans="2:13" x14ac:dyDescent="0.3">
+    <row r="239" spans="2:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="B239" t="s">
         <v>302</v>
       </c>
@@ -12528,7 +12567,7 @@
         <v>439</v>
       </c>
     </row>
-    <row r="240" spans="2:13" x14ac:dyDescent="0.3">
+    <row r="240" spans="2:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="B240" t="s">
         <v>137</v>
       </c>
@@ -12558,7 +12597,7 @@
         <v>448</v>
       </c>
     </row>
-    <row r="241" spans="2:13" x14ac:dyDescent="0.3">
+    <row r="241" spans="2:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="B241" t="s">
         <v>137</v>
       </c>
@@ -12588,7 +12627,7 @@
         <v>448</v>
       </c>
     </row>
-    <row r="242" spans="2:13" x14ac:dyDescent="0.3">
+    <row r="242" spans="2:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="B242" t="s">
         <v>137</v>
       </c>
@@ -12618,7 +12657,7 @@
         <v>448</v>
       </c>
     </row>
-    <row r="243" spans="2:13" x14ac:dyDescent="0.3">
+    <row r="243" spans="2:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="B243" t="s">
         <v>137</v>
       </c>
@@ -12648,7 +12687,7 @@
         <v>448</v>
       </c>
     </row>
-    <row r="244" spans="2:13" x14ac:dyDescent="0.3">
+    <row r="244" spans="2:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="C244" t="s">
         <v>27</v>
       </c>
@@ -12678,7 +12717,7 @@
         <v>455</v>
       </c>
     </row>
-    <row r="245" spans="2:13" x14ac:dyDescent="0.3">
+    <row r="245" spans="2:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="C245" t="s">
         <v>27</v>
       </c>
@@ -12708,7 +12747,7 @@
         <v>455</v>
       </c>
     </row>
-    <row r="246" spans="2:13" x14ac:dyDescent="0.3">
+    <row r="246" spans="2:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="C246" t="s">
         <v>27</v>
       </c>
@@ -12738,7 +12777,7 @@
         <v>455</v>
       </c>
     </row>
-    <row r="247" spans="2:13" x14ac:dyDescent="0.3">
+    <row r="247" spans="2:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="C247" t="s">
         <v>27</v>
       </c>
@@ -12768,7 +12807,7 @@
         <v>455</v>
       </c>
     </row>
-    <row r="248" spans="2:13" x14ac:dyDescent="0.3">
+    <row r="248" spans="2:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="C248" t="s">
         <v>45</v>
       </c>
@@ -12798,7 +12837,7 @@
         <v>460</v>
       </c>
     </row>
-    <row r="249" spans="2:13" x14ac:dyDescent="0.3">
+    <row r="249" spans="2:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="C249" t="s">
         <v>45</v>
       </c>
@@ -12828,7 +12867,7 @@
         <v>460</v>
       </c>
     </row>
-    <row r="250" spans="2:13" x14ac:dyDescent="0.3">
+    <row r="250" spans="2:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="C250" t="s">
         <v>45</v>
       </c>
@@ -12858,7 +12897,7 @@
         <v>460</v>
       </c>
     </row>
-    <row r="251" spans="2:13" x14ac:dyDescent="0.3">
+    <row r="251" spans="2:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="C251" t="s">
         <v>45</v>
       </c>
@@ -12888,7 +12927,7 @@
         <v>460</v>
       </c>
     </row>
-    <row r="252" spans="2:13" x14ac:dyDescent="0.3">
+    <row r="252" spans="2:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="C252" t="s">
         <v>45</v>
       </c>
@@ -12918,7 +12957,7 @@
         <v>460</v>
       </c>
     </row>
-    <row r="253" spans="2:13" x14ac:dyDescent="0.3">
+    <row r="253" spans="2:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="C253" t="s">
         <v>45</v>
       </c>
@@ -12948,7 +12987,7 @@
         <v>460</v>
       </c>
     </row>
-    <row r="254" spans="2:13" x14ac:dyDescent="0.3">
+    <row r="254" spans="2:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="B254" t="s">
         <v>137</v>
       </c>
@@ -12978,7 +13017,7 @@
         <v>470</v>
       </c>
     </row>
-    <row r="255" spans="2:13" x14ac:dyDescent="0.3">
+    <row r="255" spans="2:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="B255" t="s">
         <v>137</v>
       </c>
@@ -13008,7 +13047,7 @@
         <v>470</v>
       </c>
     </row>
-    <row r="256" spans="2:13" x14ac:dyDescent="0.3">
+    <row r="256" spans="2:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="B256" t="s">
         <v>137</v>
       </c>
@@ -13038,7 +13077,7 @@
         <v>470</v>
       </c>
     </row>
-    <row r="257" spans="2:13" x14ac:dyDescent="0.3">
+    <row r="257" spans="2:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="B257" t="s">
         <v>137</v>
       </c>
@@ -13068,7 +13107,7 @@
         <v>470</v>
       </c>
     </row>
-    <row r="258" spans="2:13" x14ac:dyDescent="0.3">
+    <row r="258" spans="2:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="B258" t="s">
         <v>137</v>
       </c>
@@ -13098,7 +13137,7 @@
         <v>470</v>
       </c>
     </row>
-    <row r="259" spans="2:13" x14ac:dyDescent="0.3">
+    <row r="259" spans="2:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="C259" t="s">
         <v>69</v>
       </c>
@@ -13128,7 +13167,7 @@
         <v>483</v>
       </c>
     </row>
-    <row r="260" spans="2:13" x14ac:dyDescent="0.3">
+    <row r="260" spans="2:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="C260" t="s">
         <v>69</v>
       </c>
@@ -13158,7 +13197,7 @@
         <v>483</v>
       </c>
     </row>
-    <row r="261" spans="2:13" x14ac:dyDescent="0.3">
+    <row r="261" spans="2:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="C261" t="s">
         <v>69</v>
       </c>
@@ -13188,7 +13227,7 @@
         <v>483</v>
       </c>
     </row>
-    <row r="262" spans="2:13" x14ac:dyDescent="0.3">
+    <row r="262" spans="2:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="C262" t="s">
         <v>69</v>
       </c>
@@ -13218,7 +13257,7 @@
         <v>483</v>
       </c>
     </row>
-    <row r="263" spans="2:13" x14ac:dyDescent="0.3">
+    <row r="263" spans="2:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="C263" t="s">
         <v>69</v>
       </c>
@@ -13248,7 +13287,7 @@
         <v>483</v>
       </c>
     </row>
-    <row r="264" spans="2:13" x14ac:dyDescent="0.3">
+    <row r="264" spans="2:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="C264" t="s">
         <v>69</v>
       </c>
@@ -13278,7 +13317,7 @@
         <v>483</v>
       </c>
     </row>
-    <row r="265" spans="2:13" x14ac:dyDescent="0.3">
+    <row r="265" spans="2:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="C265" t="s">
         <v>69</v>
       </c>
@@ -13308,7 +13347,7 @@
         <v>483</v>
       </c>
     </row>
-    <row r="266" spans="2:13" x14ac:dyDescent="0.3">
+    <row r="266" spans="2:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="C266" t="s">
         <v>69</v>
       </c>
@@ -13338,7 +13377,7 @@
         <v>483</v>
       </c>
     </row>
-    <row r="267" spans="2:13" x14ac:dyDescent="0.3">
+    <row r="267" spans="2:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="B267" t="s">
         <v>162</v>
       </c>
@@ -13368,7 +13407,7 @@
         <v>493</v>
       </c>
     </row>
-    <row r="268" spans="2:13" x14ac:dyDescent="0.3">
+    <row r="268" spans="2:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="B268" t="s">
         <v>162</v>
       </c>
@@ -13398,7 +13437,7 @@
         <v>493</v>
       </c>
     </row>
-    <row r="269" spans="2:13" x14ac:dyDescent="0.3">
+    <row r="269" spans="2:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="B269" t="s">
         <v>162</v>
       </c>
@@ -13428,7 +13467,7 @@
         <v>493</v>
       </c>
     </row>
-    <row r="270" spans="2:13" x14ac:dyDescent="0.3">
+    <row r="270" spans="2:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="B270" t="s">
         <v>162</v>
       </c>
@@ -13458,7 +13497,7 @@
         <v>493</v>
       </c>
     </row>
-    <row r="271" spans="2:13" x14ac:dyDescent="0.3">
+    <row r="271" spans="2:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="B271" t="s">
         <v>162</v>
       </c>
@@ -13488,7 +13527,7 @@
         <v>493</v>
       </c>
     </row>
-    <row r="272" spans="2:13" x14ac:dyDescent="0.3">
+    <row r="272" spans="2:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="B272" t="s">
         <v>162</v>
       </c>
@@ -13518,7 +13557,7 @@
         <v>493</v>
       </c>
     </row>
-    <row r="273" spans="2:13" x14ac:dyDescent="0.3">
+    <row r="273" spans="2:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="B273" t="s">
         <v>162</v>
       </c>
@@ -13548,7 +13587,7 @@
         <v>493</v>
       </c>
     </row>
-    <row r="274" spans="2:13" x14ac:dyDescent="0.3">
+    <row r="274" spans="2:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="B274" t="s">
         <v>162</v>
       </c>
@@ -13578,7 +13617,7 @@
         <v>493</v>
       </c>
     </row>
-    <row r="275" spans="2:13" x14ac:dyDescent="0.3">
+    <row r="275" spans="2:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="B275" t="s">
         <v>162</v>
       </c>
@@ -13608,7 +13647,7 @@
         <v>493</v>
       </c>
     </row>
-    <row r="276" spans="2:13" x14ac:dyDescent="0.3">
+    <row r="276" spans="2:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="B276" t="s">
         <v>162</v>
       </c>
@@ -13638,7 +13677,7 @@
         <v>493</v>
       </c>
     </row>
-    <row r="277" spans="2:13" x14ac:dyDescent="0.3">
+    <row r="277" spans="2:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="B277" t="s">
         <v>162</v>
       </c>
@@ -13668,7 +13707,7 @@
         <v>493</v>
       </c>
     </row>
-    <row r="278" spans="2:13" x14ac:dyDescent="0.3">
+    <row r="278" spans="2:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="B278" t="s">
         <v>162</v>
       </c>
@@ -13698,7 +13737,7 @@
         <v>493</v>
       </c>
     </row>
-    <row r="279" spans="2:13" x14ac:dyDescent="0.3">
+    <row r="279" spans="2:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="C279" t="s">
         <v>90</v>
       </c>
@@ -13728,7 +13767,7 @@
         <v>507</v>
       </c>
     </row>
-    <row r="280" spans="2:13" x14ac:dyDescent="0.3">
+    <row r="280" spans="2:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="C280" t="s">
         <v>90</v>
       </c>
@@ -13758,7 +13797,7 @@
         <v>507</v>
       </c>
     </row>
-    <row r="281" spans="2:13" x14ac:dyDescent="0.3">
+    <row r="281" spans="2:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="C281" t="s">
         <v>90</v>
       </c>
@@ -13788,7 +13827,7 @@
         <v>507</v>
       </c>
     </row>
-    <row r="282" spans="2:13" x14ac:dyDescent="0.3">
+    <row r="282" spans="2:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="C282" t="s">
         <v>90</v>
       </c>
@@ -13818,7 +13857,7 @@
         <v>507</v>
       </c>
     </row>
-    <row r="283" spans="2:13" x14ac:dyDescent="0.3">
+    <row r="283" spans="2:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="C283" t="s">
         <v>90</v>
       </c>
@@ -13848,7 +13887,7 @@
         <v>507</v>
       </c>
     </row>
-    <row r="284" spans="2:13" x14ac:dyDescent="0.3">
+    <row r="284" spans="2:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="C284" t="s">
         <v>90</v>
       </c>
@@ -13878,7 +13917,7 @@
         <v>507</v>
       </c>
     </row>
-    <row r="285" spans="2:13" x14ac:dyDescent="0.3">
+    <row r="285" spans="2:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="C285" t="s">
         <v>90</v>
       </c>
@@ -13908,7 +13947,7 @@
         <v>507</v>
       </c>
     </row>
-    <row r="286" spans="2:13" x14ac:dyDescent="0.3">
+    <row r="286" spans="2:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="C286" t="s">
         <v>90</v>
       </c>
@@ -13938,7 +13977,7 @@
         <v>507</v>
       </c>
     </row>
-    <row r="287" spans="2:13" x14ac:dyDescent="0.3">
+    <row r="287" spans="2:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="B287" t="s">
         <v>137</v>
       </c>
@@ -13971,7 +14010,7 @@
         <v>520</v>
       </c>
     </row>
-    <row r="288" spans="2:13" x14ac:dyDescent="0.3">
+    <row r="288" spans="2:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="B288" t="s">
         <v>137</v>
       </c>
@@ -14004,7 +14043,7 @@
         <v>520</v>
       </c>
     </row>
-    <row r="289" spans="2:13" x14ac:dyDescent="0.3">
+    <row r="289" spans="2:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="B289" t="s">
         <v>137</v>
       </c>
@@ -14037,7 +14076,7 @@
         <v>520</v>
       </c>
     </row>
-    <row r="290" spans="2:13" x14ac:dyDescent="0.3">
+    <row r="290" spans="2:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="B290" t="s">
         <v>137</v>
       </c>
@@ -14070,7 +14109,7 @@
         <v>520</v>
       </c>
     </row>
-    <row r="291" spans="2:13" x14ac:dyDescent="0.3">
+    <row r="291" spans="2:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="B291" t="s">
         <v>137</v>
       </c>
@@ -14103,7 +14142,7 @@
         <v>520</v>
       </c>
     </row>
-    <row r="292" spans="2:13" x14ac:dyDescent="0.3">
+    <row r="292" spans="2:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="B292" t="s">
         <v>137</v>
       </c>
@@ -14136,7 +14175,7 @@
         <v>520</v>
       </c>
     </row>
-    <row r="293" spans="2:13" x14ac:dyDescent="0.3">
+    <row r="293" spans="2:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="B293" t="s">
         <v>137</v>
       </c>
@@ -14169,7 +14208,7 @@
         <v>520</v>
       </c>
     </row>
-    <row r="294" spans="2:13" x14ac:dyDescent="0.3">
+    <row r="294" spans="2:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="B294" t="s">
         <v>137</v>
       </c>
@@ -14202,7 +14241,7 @@
         <v>520</v>
       </c>
     </row>
-    <row r="295" spans="2:13" x14ac:dyDescent="0.3">
+    <row r="295" spans="2:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="C295" t="s">
         <v>101</v>
       </c>
@@ -14232,7 +14271,7 @@
         <v>537</v>
       </c>
     </row>
-    <row r="296" spans="2:13" x14ac:dyDescent="0.3">
+    <row r="296" spans="2:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="C296" t="s">
         <v>101</v>
       </c>
@@ -14262,7 +14301,7 @@
         <v>537</v>
       </c>
     </row>
-    <row r="297" spans="2:13" x14ac:dyDescent="0.3">
+    <row r="297" spans="2:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="C297" t="s">
         <v>101</v>
       </c>
@@ -14292,7 +14331,7 @@
         <v>537</v>
       </c>
     </row>
-    <row r="298" spans="2:13" x14ac:dyDescent="0.3">
+    <row r="298" spans="2:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="C298" t="s">
         <v>101</v>
       </c>
@@ -14322,7 +14361,7 @@
         <v>537</v>
       </c>
     </row>
-    <row r="299" spans="2:13" x14ac:dyDescent="0.3">
+    <row r="299" spans="2:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="C299" t="s">
         <v>110</v>
       </c>
@@ -14352,7 +14391,7 @@
         <v>543</v>
       </c>
     </row>
-    <row r="300" spans="2:13" x14ac:dyDescent="0.3">
+    <row r="300" spans="2:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="C300" t="s">
         <v>110</v>
       </c>
@@ -14382,7 +14421,7 @@
         <v>543</v>
       </c>
     </row>
-    <row r="301" spans="2:13" x14ac:dyDescent="0.3">
+    <row r="301" spans="2:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="C301" t="s">
         <v>110</v>
       </c>
@@ -14412,7 +14451,7 @@
         <v>543</v>
       </c>
     </row>
-    <row r="302" spans="2:13" x14ac:dyDescent="0.3">
+    <row r="302" spans="2:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="C302" t="s">
         <v>110</v>
       </c>
@@ -14442,7 +14481,7 @@
         <v>543</v>
       </c>
     </row>
-    <row r="303" spans="2:13" x14ac:dyDescent="0.3">
+    <row r="303" spans="2:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="C303" t="s">
         <v>399</v>
       </c>
@@ -14472,7 +14511,7 @@
         <v>548</v>
       </c>
     </row>
-    <row r="304" spans="2:13" x14ac:dyDescent="0.3">
+    <row r="304" spans="2:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="C304" t="s">
         <v>399</v>
       </c>
@@ -14502,7 +14541,7 @@
         <v>548</v>
       </c>
     </row>
-    <row r="305" spans="2:13" x14ac:dyDescent="0.3">
+    <row r="305" spans="2:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="C305" t="s">
         <v>399</v>
       </c>
@@ -14532,7 +14571,7 @@
         <v>548</v>
       </c>
     </row>
-    <row r="306" spans="2:13" x14ac:dyDescent="0.3">
+    <row r="306" spans="2:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="C306" t="s">
         <v>399</v>
       </c>
@@ -14562,7 +14601,7 @@
         <v>548</v>
       </c>
     </row>
-    <row r="307" spans="2:13" x14ac:dyDescent="0.3">
+    <row r="307" spans="2:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="B307" t="s">
         <v>162</v>
       </c>
@@ -14592,7 +14631,7 @@
         <v>553</v>
       </c>
     </row>
-    <row r="308" spans="2:13" x14ac:dyDescent="0.3">
+    <row r="308" spans="2:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="B308" t="s">
         <v>162</v>
       </c>
@@ -14622,7 +14661,7 @@
         <v>553</v>
       </c>
     </row>
-    <row r="309" spans="2:13" x14ac:dyDescent="0.3">
+    <row r="309" spans="2:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="B309" t="s">
         <v>162</v>
       </c>
@@ -14652,7 +14691,7 @@
         <v>553</v>
       </c>
     </row>
-    <row r="310" spans="2:13" x14ac:dyDescent="0.3">
+    <row r="310" spans="2:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="B310" t="s">
         <v>162</v>
       </c>
@@ -14682,7 +14721,7 @@
         <v>553</v>
       </c>
     </row>
-    <row r="311" spans="2:13" x14ac:dyDescent="0.3">
+    <row r="311" spans="2:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="B311" t="s">
         <v>162</v>
       </c>
@@ -14712,7 +14751,7 @@
         <v>553</v>
       </c>
     </row>
-    <row r="312" spans="2:13" x14ac:dyDescent="0.3">
+    <row r="312" spans="2:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="B312" t="s">
         <v>162</v>
       </c>
@@ -14742,7 +14781,7 @@
         <v>553</v>
       </c>
     </row>
-    <row r="313" spans="2:13" x14ac:dyDescent="0.3">
+    <row r="313" spans="2:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="B313" t="s">
         <v>162</v>
       </c>
@@ -14772,7 +14811,7 @@
         <v>553</v>
       </c>
     </row>
-    <row r="314" spans="2:13" x14ac:dyDescent="0.3">
+    <row r="314" spans="2:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="B314" t="s">
         <v>162</v>
       </c>
@@ -14802,7 +14841,7 @@
         <v>553</v>
       </c>
     </row>
-    <row r="315" spans="2:13" x14ac:dyDescent="0.3">
+    <row r="315" spans="2:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="B315" t="s">
         <v>162</v>
       </c>
@@ -14832,7 +14871,7 @@
         <v>553</v>
       </c>
     </row>
-    <row r="316" spans="2:13" x14ac:dyDescent="0.3">
+    <row r="316" spans="2:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="B316" t="s">
         <v>162</v>
       </c>
@@ -14862,7 +14901,7 @@
         <v>553</v>
       </c>
     </row>
-    <row r="317" spans="2:13" x14ac:dyDescent="0.3">
+    <row r="317" spans="2:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="B317" t="s">
         <v>162</v>
       </c>
@@ -14892,7 +14931,7 @@
         <v>553</v>
       </c>
     </row>
-    <row r="318" spans="2:13" x14ac:dyDescent="0.3">
+    <row r="318" spans="2:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="B318" t="s">
         <v>162</v>
       </c>
@@ -14922,7 +14961,7 @@
         <v>553</v>
       </c>
     </row>
-    <row r="319" spans="2:13" x14ac:dyDescent="0.3">
+    <row r="319" spans="2:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="C319" t="s">
         <v>129</v>
       </c>
@@ -14952,7 +14991,7 @@
         <v>568</v>
       </c>
     </row>
-    <row r="320" spans="2:13" x14ac:dyDescent="0.3">
+    <row r="320" spans="2:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="C320" t="s">
         <v>129</v>
       </c>
@@ -14982,7 +15021,7 @@
         <v>568</v>
       </c>
     </row>
-    <row r="321" spans="2:13" x14ac:dyDescent="0.3">
+    <row r="321" spans="2:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="C321" t="s">
         <v>129</v>
       </c>
@@ -15012,7 +15051,7 @@
         <v>568</v>
       </c>
     </row>
-    <row r="322" spans="2:13" x14ac:dyDescent="0.3">
+    <row r="322" spans="2:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="C322" t="s">
         <v>129</v>
       </c>
@@ -15042,7 +15081,7 @@
         <v>568</v>
       </c>
     </row>
-    <row r="323" spans="2:13" x14ac:dyDescent="0.3">
+    <row r="323" spans="2:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="C323" t="s">
         <v>154</v>
       </c>
@@ -15075,7 +15114,7 @@
         <v>578</v>
       </c>
     </row>
-    <row r="324" spans="2:13" x14ac:dyDescent="0.3">
+    <row r="324" spans="2:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="C324" t="s">
         <v>154</v>
       </c>
@@ -15105,7 +15144,7 @@
         <v>578</v>
       </c>
     </row>
-    <row r="325" spans="2:13" x14ac:dyDescent="0.3">
+    <row r="325" spans="2:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="C325" t="s">
         <v>154</v>
       </c>
@@ -15138,7 +15177,7 @@
         <v>578</v>
       </c>
     </row>
-    <row r="326" spans="2:13" x14ac:dyDescent="0.3">
+    <row r="326" spans="2:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="C326" t="s">
         <v>154</v>
       </c>
@@ -15168,7 +15207,7 @@
         <v>578</v>
       </c>
     </row>
-    <row r="327" spans="2:13" x14ac:dyDescent="0.3">
+    <row r="327" spans="2:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="C327" t="s">
         <v>154</v>
       </c>
@@ -15201,7 +15240,7 @@
         <v>578</v>
       </c>
     </row>
-    <row r="328" spans="2:13" x14ac:dyDescent="0.3">
+    <row r="328" spans="2:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="C328" t="s">
         <v>154</v>
       </c>
@@ -15234,7 +15273,7 @@
         <v>578</v>
       </c>
     </row>
-    <row r="329" spans="2:13" x14ac:dyDescent="0.3">
+    <row r="329" spans="2:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="C329" t="s">
         <v>154</v>
       </c>
@@ -15267,7 +15306,7 @@
         <v>578</v>
       </c>
     </row>
-    <row r="330" spans="2:13" x14ac:dyDescent="0.3">
+    <row r="330" spans="2:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="C330" t="s">
         <v>154</v>
       </c>
@@ -15297,7 +15336,7 @@
         <v>578</v>
       </c>
     </row>
-    <row r="331" spans="2:13" x14ac:dyDescent="0.3">
+    <row r="331" spans="2:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="B331" t="s">
         <v>593</v>
       </c>
@@ -15333,7 +15372,7 @@
         <v>597</v>
       </c>
     </row>
-    <row r="332" spans="2:13" x14ac:dyDescent="0.3">
+    <row r="332" spans="2:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="B332" t="s">
         <v>593</v>
       </c>
@@ -15369,7 +15408,7 @@
         <v>597</v>
       </c>
     </row>
-    <row r="333" spans="2:13" x14ac:dyDescent="0.3">
+    <row r="333" spans="2:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="B333" t="s">
         <v>593</v>
       </c>
@@ -15402,7 +15441,7 @@
         <v>597</v>
       </c>
     </row>
-    <row r="334" spans="2:13" x14ac:dyDescent="0.3">
+    <row r="334" spans="2:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="B334" t="s">
         <v>593</v>
       </c>
@@ -15438,7 +15477,7 @@
         <v>597</v>
       </c>
     </row>
-    <row r="335" spans="2:13" x14ac:dyDescent="0.3">
+    <row r="335" spans="2:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="B335" t="s">
         <v>593</v>
       </c>
@@ -15474,7 +15513,7 @@
         <v>597</v>
       </c>
     </row>
-    <row r="336" spans="2:13" x14ac:dyDescent="0.3">
+    <row r="336" spans="2:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="B336" t="s">
         <v>593</v>
       </c>
@@ -15510,7 +15549,7 @@
         <v>597</v>
       </c>
     </row>
-    <row r="337" spans="2:13" x14ac:dyDescent="0.3">
+    <row r="337" spans="2:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="B337" t="s">
         <v>593</v>
       </c>
@@ -15543,7 +15582,7 @@
         <v>597</v>
       </c>
     </row>
-    <row r="338" spans="2:13" x14ac:dyDescent="0.3">
+    <row r="338" spans="2:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="B338" t="s">
         <v>593</v>
       </c>
@@ -15576,7 +15615,7 @@
         <v>597</v>
       </c>
     </row>
-    <row r="339" spans="2:13" x14ac:dyDescent="0.3">
+    <row r="339" spans="2:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="C339" t="s">
         <v>150</v>
       </c>
@@ -15606,7 +15645,7 @@
         <v>613</v>
       </c>
     </row>
-    <row r="340" spans="2:13" x14ac:dyDescent="0.3">
+    <row r="340" spans="2:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="C340" t="s">
         <v>150</v>
       </c>
@@ -15636,7 +15675,7 @@
         <v>613</v>
       </c>
     </row>
-    <row r="341" spans="2:13" x14ac:dyDescent="0.3">
+    <row r="341" spans="2:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="C341" t="s">
         <v>150</v>
       </c>
@@ -15666,7 +15705,7 @@
         <v>613</v>
       </c>
     </row>
-    <row r="342" spans="2:13" x14ac:dyDescent="0.3">
+    <row r="342" spans="2:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="C342" t="s">
         <v>150</v>
       </c>
@@ -15696,7 +15735,7 @@
         <v>613</v>
       </c>
     </row>
-    <row r="343" spans="2:13" x14ac:dyDescent="0.3">
+    <row r="343" spans="2:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="B343" t="s">
         <v>302</v>
       </c>
@@ -15726,7 +15765,7 @@
         <v>619</v>
       </c>
     </row>
-    <row r="344" spans="2:13" x14ac:dyDescent="0.3">
+    <row r="344" spans="2:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="B344" t="s">
         <v>302</v>
       </c>
@@ -15756,7 +15795,7 @@
         <v>619</v>
       </c>
     </row>
-    <row r="345" spans="2:13" x14ac:dyDescent="0.3">
+    <row r="345" spans="2:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="B345" t="s">
         <v>302</v>
       </c>
@@ -15786,7 +15825,7 @@
         <v>619</v>
       </c>
     </row>
-    <row r="346" spans="2:13" x14ac:dyDescent="0.3">
+    <row r="346" spans="2:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="B346" t="s">
         <v>302</v>
       </c>
@@ -15816,7 +15855,7 @@
         <v>619</v>
       </c>
     </row>
-    <row r="347" spans="2:13" x14ac:dyDescent="0.3">
+    <row r="347" spans="2:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="C347" t="s">
         <v>154</v>
       </c>
@@ -15846,7 +15885,7 @@
         <v>627</v>
       </c>
     </row>
-    <row r="348" spans="2:13" x14ac:dyDescent="0.3">
+    <row r="348" spans="2:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="C348" t="s">
         <v>154</v>
       </c>
@@ -15876,7 +15915,7 @@
         <v>627</v>
       </c>
     </row>
-    <row r="349" spans="2:13" x14ac:dyDescent="0.3">
+    <row r="349" spans="2:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="C349" t="s">
         <v>154</v>
       </c>
@@ -15906,7 +15945,7 @@
         <v>627</v>
       </c>
     </row>
-    <row r="350" spans="2:13" x14ac:dyDescent="0.3">
+    <row r="350" spans="2:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="C350" t="s">
         <v>154</v>
       </c>
@@ -15936,7 +15975,7 @@
         <v>627</v>
       </c>
     </row>
-    <row r="351" spans="2:13" x14ac:dyDescent="0.3">
+    <row r="351" spans="2:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="C351" t="s">
         <v>154</v>
       </c>
@@ -15966,7 +16005,7 @@
         <v>627</v>
       </c>
     </row>
-    <row r="352" spans="2:13" x14ac:dyDescent="0.3">
+    <row r="352" spans="2:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="C352" t="s">
         <v>154</v>
       </c>
@@ -15996,7 +16035,7 @@
         <v>627</v>
       </c>
     </row>
-    <row r="353" spans="2:13" x14ac:dyDescent="0.3">
+    <row r="353" spans="2:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="C353" t="s">
         <v>154</v>
       </c>
@@ -16026,7 +16065,7 @@
         <v>627</v>
       </c>
     </row>
-    <row r="354" spans="2:13" x14ac:dyDescent="0.3">
+    <row r="354" spans="2:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="C354" t="s">
         <v>154</v>
       </c>
@@ -16056,7 +16095,7 @@
         <v>627</v>
       </c>
     </row>
-    <row r="355" spans="2:13" x14ac:dyDescent="0.3">
+    <row r="355" spans="2:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="C355" t="s">
         <v>635</v>
       </c>
@@ -16086,7 +16125,7 @@
         <v>638</v>
       </c>
     </row>
-    <row r="356" spans="2:13" x14ac:dyDescent="0.3">
+    <row r="356" spans="2:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="C356" t="s">
         <v>635</v>
       </c>
@@ -16116,7 +16155,7 @@
         <v>638</v>
       </c>
     </row>
-    <row r="357" spans="2:13" x14ac:dyDescent="0.3">
+    <row r="357" spans="2:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="C357" t="s">
         <v>635</v>
       </c>
@@ -16146,7 +16185,7 @@
         <v>638</v>
       </c>
     </row>
-    <row r="358" spans="2:13" x14ac:dyDescent="0.3">
+    <row r="358" spans="2:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="C358" t="s">
         <v>635</v>
       </c>
@@ -16176,7 +16215,7 @@
         <v>638</v>
       </c>
     </row>
-    <row r="359" spans="2:13" x14ac:dyDescent="0.3">
+    <row r="359" spans="2:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="B359" t="s">
         <v>137</v>
       </c>
@@ -16206,7 +16245,7 @@
         <v>645</v>
       </c>
     </row>
-    <row r="360" spans="2:13" x14ac:dyDescent="0.3">
+    <row r="360" spans="2:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="B360" t="s">
         <v>137</v>
       </c>
@@ -16236,7 +16275,7 @@
         <v>645</v>
       </c>
     </row>
-    <row r="361" spans="2:13" x14ac:dyDescent="0.3">
+    <row r="361" spans="2:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="B361" t="s">
         <v>137</v>
       </c>
@@ -16266,7 +16305,7 @@
         <v>645</v>
       </c>
     </row>
-    <row r="362" spans="2:13" x14ac:dyDescent="0.3">
+    <row r="362" spans="2:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="B362" t="s">
         <v>137</v>
       </c>
@@ -16296,7 +16335,7 @@
         <v>645</v>
       </c>
     </row>
-    <row r="363" spans="2:13" x14ac:dyDescent="0.3">
+    <row r="363" spans="2:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="C363" t="s">
         <v>27</v>
       </c>
@@ -16326,7 +16365,7 @@
         <v>653</v>
       </c>
     </row>
-    <row r="364" spans="2:13" x14ac:dyDescent="0.3">
+    <row r="364" spans="2:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="C364" t="s">
         <v>27</v>
       </c>
@@ -16356,7 +16395,7 @@
         <v>653</v>
       </c>
     </row>
-    <row r="365" spans="2:13" x14ac:dyDescent="0.3">
+    <row r="365" spans="2:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="C365" t="s">
         <v>27</v>
       </c>
@@ -16386,7 +16425,7 @@
         <v>653</v>
       </c>
     </row>
-    <row r="366" spans="2:13" x14ac:dyDescent="0.3">
+    <row r="366" spans="2:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="C366" t="s">
         <v>27</v>
       </c>
@@ -16416,7 +16455,7 @@
         <v>653</v>
       </c>
     </row>
-    <row r="367" spans="2:13" x14ac:dyDescent="0.3">
+    <row r="367" spans="2:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="C367" t="s">
         <v>45</v>
       </c>
@@ -16446,7 +16485,7 @@
         <v>659</v>
       </c>
     </row>
-    <row r="368" spans="2:13" x14ac:dyDescent="0.3">
+    <row r="368" spans="2:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="C368" t="s">
         <v>45</v>
       </c>
@@ -16476,7 +16515,7 @@
         <v>659</v>
       </c>
     </row>
-    <row r="369" spans="3:13" x14ac:dyDescent="0.3">
+    <row r="369" spans="3:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="C369" t="s">
         <v>45</v>
       </c>
@@ -16506,7 +16545,7 @@
         <v>659</v>
       </c>
     </row>
-    <row r="370" spans="3:13" x14ac:dyDescent="0.3">
+    <row r="370" spans="3:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="C370" t="s">
         <v>45</v>
       </c>
@@ -16536,7 +16575,7 @@
         <v>659</v>
       </c>
     </row>
-    <row r="371" spans="3:13" x14ac:dyDescent="0.3">
+    <row r="371" spans="3:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="C371" t="s">
         <v>45</v>
       </c>
@@ -16566,7 +16605,7 @@
         <v>659</v>
       </c>
     </row>
-    <row r="372" spans="3:13" x14ac:dyDescent="0.3">
+    <row r="372" spans="3:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="C372" t="s">
         <v>45</v>
       </c>
@@ -16596,7 +16635,7 @@
         <v>659</v>
       </c>
     </row>
-    <row r="373" spans="3:13" x14ac:dyDescent="0.3">
+    <row r="373" spans="3:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="C373" t="s">
         <v>69</v>
       </c>
@@ -16626,7 +16665,7 @@
         <v>666</v>
       </c>
     </row>
-    <row r="374" spans="3:13" x14ac:dyDescent="0.3">
+    <row r="374" spans="3:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="C374" t="s">
         <v>69</v>
       </c>
@@ -16656,7 +16695,7 @@
         <v>666</v>
       </c>
     </row>
-    <row r="375" spans="3:13" x14ac:dyDescent="0.3">
+    <row r="375" spans="3:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="C375" t="s">
         <v>69</v>
       </c>
@@ -16686,7 +16725,7 @@
         <v>666</v>
       </c>
     </row>
-    <row r="376" spans="3:13" x14ac:dyDescent="0.3">
+    <row r="376" spans="3:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="C376" t="s">
         <v>69</v>
       </c>
@@ -16716,7 +16755,7 @@
         <v>666</v>
       </c>
     </row>
-    <row r="377" spans="3:13" x14ac:dyDescent="0.3">
+    <row r="377" spans="3:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="C377" t="s">
         <v>670</v>
       </c>
@@ -16746,7 +16785,7 @@
         <v>673</v>
       </c>
     </row>
-    <row r="378" spans="3:13" x14ac:dyDescent="0.3">
+    <row r="378" spans="3:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="C378" t="s">
         <v>670</v>
       </c>
@@ -16776,7 +16815,7 @@
         <v>673</v>
       </c>
     </row>
-    <row r="379" spans="3:13" x14ac:dyDescent="0.3">
+    <row r="379" spans="3:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="C379" t="s">
         <v>670</v>
       </c>
@@ -16806,7 +16845,7 @@
         <v>673</v>
       </c>
     </row>
-    <row r="380" spans="3:13" x14ac:dyDescent="0.3">
+    <row r="380" spans="3:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="C380" t="s">
         <v>670</v>
       </c>
@@ -16836,7 +16875,7 @@
         <v>673</v>
       </c>
     </row>
-    <row r="381" spans="3:13" x14ac:dyDescent="0.3">
+    <row r="381" spans="3:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="C381" t="s">
         <v>90</v>
       </c>
@@ -16866,7 +16905,7 @@
         <v>679</v>
       </c>
     </row>
-    <row r="382" spans="3:13" x14ac:dyDescent="0.3">
+    <row r="382" spans="3:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="C382" t="s">
         <v>90</v>
       </c>
@@ -16896,7 +16935,7 @@
         <v>679</v>
       </c>
     </row>
-    <row r="383" spans="3:13" x14ac:dyDescent="0.3">
+    <row r="383" spans="3:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="C383" t="s">
         <v>90</v>
       </c>
@@ -16926,7 +16965,7 @@
         <v>679</v>
       </c>
     </row>
-    <row r="384" spans="3:13" x14ac:dyDescent="0.3">
+    <row r="384" spans="3:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="C384" t="s">
         <v>90</v>
       </c>
@@ -16956,7 +16995,7 @@
         <v>679</v>
       </c>
     </row>
-    <row r="385" spans="2:13" x14ac:dyDescent="0.3">
+    <row r="385" spans="2:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="C385" t="s">
         <v>90</v>
       </c>
@@ -16986,7 +17025,7 @@
         <v>679</v>
       </c>
     </row>
-    <row r="386" spans="2:13" x14ac:dyDescent="0.3">
+    <row r="386" spans="2:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="C386" t="s">
         <v>90</v>
       </c>
@@ -17016,7 +17055,7 @@
         <v>679</v>
       </c>
     </row>
-    <row r="387" spans="2:13" x14ac:dyDescent="0.3">
+    <row r="387" spans="2:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="C387" t="s">
         <v>90</v>
       </c>
@@ -17046,7 +17085,7 @@
         <v>679</v>
       </c>
     </row>
-    <row r="388" spans="2:13" x14ac:dyDescent="0.3">
+    <row r="388" spans="2:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="C388" t="s">
         <v>90</v>
       </c>
@@ -17076,7 +17115,7 @@
         <v>679</v>
       </c>
     </row>
-    <row r="389" spans="2:13" x14ac:dyDescent="0.3">
+    <row r="389" spans="2:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="B389" t="s">
         <v>162</v>
       </c>
@@ -17106,7 +17145,7 @@
         <v>687</v>
       </c>
     </row>
-    <row r="390" spans="2:13" x14ac:dyDescent="0.3">
+    <row r="390" spans="2:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="B390" t="s">
         <v>162</v>
       </c>
@@ -17136,7 +17175,7 @@
         <v>687</v>
       </c>
     </row>
-    <row r="391" spans="2:13" x14ac:dyDescent="0.3">
+    <row r="391" spans="2:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="B391" t="s">
         <v>162</v>
       </c>
@@ -17166,7 +17205,7 @@
         <v>687</v>
       </c>
     </row>
-    <row r="392" spans="2:13" x14ac:dyDescent="0.3">
+    <row r="392" spans="2:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="B392" t="s">
         <v>162</v>
       </c>
@@ -17196,7 +17235,7 @@
         <v>687</v>
       </c>
     </row>
-    <row r="393" spans="2:13" x14ac:dyDescent="0.3">
+    <row r="393" spans="2:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="B393" t="s">
         <v>162</v>
       </c>
@@ -17226,7 +17265,7 @@
         <v>687</v>
       </c>
     </row>
-    <row r="394" spans="2:13" x14ac:dyDescent="0.3">
+    <row r="394" spans="2:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="B394" t="s">
         <v>162</v>
       </c>
@@ -17256,7 +17295,7 @@
         <v>687</v>
       </c>
     </row>
-    <row r="395" spans="2:13" x14ac:dyDescent="0.3">
+    <row r="395" spans="2:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="B395" t="s">
         <v>162</v>
       </c>
@@ -17286,7 +17325,7 @@
         <v>687</v>
       </c>
     </row>
-    <row r="396" spans="2:13" x14ac:dyDescent="0.3">
+    <row r="396" spans="2:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="B396" t="s">
         <v>162</v>
       </c>
@@ -17316,7 +17355,7 @@
         <v>687</v>
       </c>
     </row>
-    <row r="397" spans="2:13" x14ac:dyDescent="0.3">
+    <row r="397" spans="2:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="B397" t="s">
         <v>162</v>
       </c>
@@ -17346,7 +17385,7 @@
         <v>687</v>
       </c>
     </row>
-    <row r="398" spans="2:13" x14ac:dyDescent="0.3">
+    <row r="398" spans="2:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="B398" t="s">
         <v>162</v>
       </c>
@@ -17376,7 +17415,7 @@
         <v>687</v>
       </c>
     </row>
-    <row r="399" spans="2:13" x14ac:dyDescent="0.3">
+    <row r="399" spans="2:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="B399" t="s">
         <v>162</v>
       </c>
@@ -17406,7 +17445,7 @@
         <v>687</v>
       </c>
     </row>
-    <row r="400" spans="2:13" x14ac:dyDescent="0.3">
+    <row r="400" spans="2:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="B400" t="s">
         <v>162</v>
       </c>
@@ -17436,7 +17475,7 @@
         <v>687</v>
       </c>
     </row>
-    <row r="401" spans="2:13" x14ac:dyDescent="0.3">
+    <row r="401" spans="2:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="C401" t="s">
         <v>101</v>
       </c>
@@ -17466,7 +17505,7 @@
         <v>699</v>
       </c>
     </row>
-    <row r="402" spans="2:13" x14ac:dyDescent="0.3">
+    <row r="402" spans="2:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="C402" t="s">
         <v>101</v>
       </c>
@@ -17496,7 +17535,7 @@
         <v>699</v>
       </c>
     </row>
-    <row r="403" spans="2:13" x14ac:dyDescent="0.3">
+    <row r="403" spans="2:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="C403" t="s">
         <v>101</v>
       </c>
@@ -17526,7 +17565,7 @@
         <v>699</v>
       </c>
     </row>
-    <row r="404" spans="2:13" x14ac:dyDescent="0.3">
+    <row r="404" spans="2:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="C404" t="s">
         <v>101</v>
       </c>
@@ -17556,7 +17595,7 @@
         <v>699</v>
       </c>
     </row>
-    <row r="405" spans="2:13" x14ac:dyDescent="0.3">
+    <row r="405" spans="2:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="C405" t="s">
         <v>110</v>
       </c>
@@ -17586,7 +17625,7 @@
         <v>704</v>
       </c>
     </row>
-    <row r="406" spans="2:13" x14ac:dyDescent="0.3">
+    <row r="406" spans="2:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="C406" t="s">
         <v>110</v>
       </c>
@@ -17616,7 +17655,7 @@
         <v>704</v>
       </c>
     </row>
-    <row r="407" spans="2:13" x14ac:dyDescent="0.3">
+    <row r="407" spans="2:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="C407" t="s">
         <v>110</v>
       </c>
@@ -17646,7 +17685,7 @@
         <v>704</v>
       </c>
     </row>
-    <row r="408" spans="2:13" x14ac:dyDescent="0.3">
+    <row r="408" spans="2:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="C408" t="s">
         <v>110</v>
       </c>
@@ -17676,7 +17715,7 @@
         <v>704</v>
       </c>
     </row>
-    <row r="409" spans="2:13" x14ac:dyDescent="0.3">
+    <row r="409" spans="2:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="B409" t="s">
         <v>162</v>
       </c>
@@ -17706,7 +17745,7 @@
         <v>709</v>
       </c>
     </row>
-    <row r="410" spans="2:13" x14ac:dyDescent="0.3">
+    <row r="410" spans="2:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="B410" t="s">
         <v>162</v>
       </c>
@@ -17736,7 +17775,7 @@
         <v>709</v>
       </c>
     </row>
-    <row r="411" spans="2:13" x14ac:dyDescent="0.3">
+    <row r="411" spans="2:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="B411" t="s">
         <v>162</v>
       </c>
@@ -17766,7 +17805,7 @@
         <v>709</v>
       </c>
     </row>
-    <row r="412" spans="2:13" x14ac:dyDescent="0.3">
+    <row r="412" spans="2:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="B412" t="s">
         <v>162</v>
       </c>
@@ -17796,7 +17835,7 @@
         <v>709</v>
       </c>
     </row>
-    <row r="413" spans="2:13" x14ac:dyDescent="0.3">
+    <row r="413" spans="2:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="B413" t="s">
         <v>162</v>
       </c>
@@ -17826,7 +17865,7 @@
         <v>709</v>
       </c>
     </row>
-    <row r="414" spans="2:13" x14ac:dyDescent="0.3">
+    <row r="414" spans="2:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="B414" t="s">
         <v>162</v>
       </c>
@@ -17856,7 +17895,7 @@
         <v>709</v>
       </c>
     </row>
-    <row r="415" spans="2:13" x14ac:dyDescent="0.3">
+    <row r="415" spans="2:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="B415" t="s">
         <v>162</v>
       </c>
@@ -17886,7 +17925,7 @@
         <v>709</v>
       </c>
     </row>
-    <row r="416" spans="2:13" x14ac:dyDescent="0.3">
+    <row r="416" spans="2:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="B416" t="s">
         <v>162</v>
       </c>
@@ -17916,7 +17955,7 @@
         <v>709</v>
       </c>
     </row>
-    <row r="417" spans="2:13" x14ac:dyDescent="0.3">
+    <row r="417" spans="2:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="B417" t="s">
         <v>162</v>
       </c>
@@ -17946,7 +17985,7 @@
         <v>709</v>
       </c>
     </row>
-    <row r="418" spans="2:13" x14ac:dyDescent="0.3">
+    <row r="418" spans="2:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="B418" t="s">
         <v>162</v>
       </c>
@@ -17976,7 +18015,7 @@
         <v>709</v>
       </c>
     </row>
-    <row r="419" spans="2:13" x14ac:dyDescent="0.3">
+    <row r="419" spans="2:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="B419" t="s">
         <v>162</v>
       </c>
@@ -18006,7 +18045,7 @@
         <v>709</v>
       </c>
     </row>
-    <row r="420" spans="2:13" x14ac:dyDescent="0.3">
+    <row r="420" spans="2:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="B420" t="s">
         <v>162</v>
       </c>
@@ -18036,7 +18075,7 @@
         <v>709</v>
       </c>
     </row>
-    <row r="421" spans="2:13" x14ac:dyDescent="0.3">
+    <row r="421" spans="2:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="C421" t="s">
         <v>721</v>
       </c>
@@ -18066,7 +18105,7 @@
         <v>725</v>
       </c>
     </row>
-    <row r="422" spans="2:13" x14ac:dyDescent="0.3">
+    <row r="422" spans="2:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="C422" t="s">
         <v>721</v>
       </c>
@@ -18096,7 +18135,7 @@
         <v>725</v>
       </c>
     </row>
-    <row r="423" spans="2:13" x14ac:dyDescent="0.3">
+    <row r="423" spans="2:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="C423" t="s">
         <v>721</v>
       </c>
@@ -18126,7 +18165,7 @@
         <v>725</v>
       </c>
     </row>
-    <row r="424" spans="2:13" x14ac:dyDescent="0.3">
+    <row r="424" spans="2:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="C424" t="s">
         <v>721</v>
       </c>
@@ -18156,7 +18195,7 @@
         <v>725</v>
       </c>
     </row>
-    <row r="425" spans="2:13" x14ac:dyDescent="0.3">
+    <row r="425" spans="2:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="C425" t="s">
         <v>129</v>
       </c>
@@ -18186,7 +18225,7 @@
         <v>730</v>
       </c>
     </row>
-    <row r="426" spans="2:13" x14ac:dyDescent="0.3">
+    <row r="426" spans="2:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="C426" t="s">
         <v>129</v>
       </c>
@@ -18216,7 +18255,7 @@
         <v>730</v>
       </c>
     </row>
-    <row r="427" spans="2:13" x14ac:dyDescent="0.3">
+    <row r="427" spans="2:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="C427" t="s">
         <v>129</v>
       </c>
@@ -18246,7 +18285,7 @@
         <v>730</v>
       </c>
     </row>
-    <row r="428" spans="2:13" x14ac:dyDescent="0.3">
+    <row r="428" spans="2:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="C428" t="s">
         <v>129</v>
       </c>
@@ -18276,7 +18315,7 @@
         <v>730</v>
       </c>
     </row>
-    <row r="429" spans="2:13" x14ac:dyDescent="0.3">
+    <row r="429" spans="2:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="C429" t="s">
         <v>150</v>
       </c>
@@ -18306,7 +18345,7 @@
         <v>736</v>
       </c>
     </row>
-    <row r="430" spans="2:13" x14ac:dyDescent="0.3">
+    <row r="430" spans="2:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="C430" t="s">
         <v>150</v>
       </c>
@@ -18336,7 +18375,7 @@
         <v>736</v>
       </c>
     </row>
-    <row r="431" spans="2:13" x14ac:dyDescent="0.3">
+    <row r="431" spans="2:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="C431" t="s">
         <v>150</v>
       </c>
@@ -18366,7 +18405,7 @@
         <v>736</v>
       </c>
     </row>
-    <row r="432" spans="2:13" x14ac:dyDescent="0.3">
+    <row r="432" spans="2:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="C432" t="s">
         <v>150</v>
       </c>
@@ -18396,7 +18435,7 @@
         <v>736</v>
       </c>
     </row>
-    <row r="433" spans="3:13" x14ac:dyDescent="0.3">
+    <row r="433" spans="3:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="C433" t="s">
         <v>303</v>
       </c>
@@ -18423,7 +18462,7 @@
         <v>742</v>
       </c>
     </row>
-    <row r="434" spans="3:13" x14ac:dyDescent="0.3">
+    <row r="434" spans="3:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="C434" t="s">
         <v>303</v>
       </c>
@@ -18450,7 +18489,7 @@
         <v>742</v>
       </c>
     </row>
-    <row r="435" spans="3:13" x14ac:dyDescent="0.3">
+    <row r="435" spans="3:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="C435" t="s">
         <v>303</v>
       </c>
@@ -18477,7 +18516,7 @@
         <v>742</v>
       </c>
     </row>
-    <row r="436" spans="3:13" x14ac:dyDescent="0.3">
+    <row r="436" spans="3:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="C436" t="s">
         <v>303</v>
       </c>
@@ -18522,7 +18561,7 @@
         <v>750</v>
       </c>
       <c r="I437">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L437" t="s">
         <v>751</v>
@@ -18549,7 +18588,7 @@
         <v>753</v>
       </c>
       <c r="I438">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L438" t="s">
         <v>754</v>
@@ -18576,7 +18615,7 @@
         <v>755</v>
       </c>
       <c r="I439">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L439" t="s">
         <v>756</v>
@@ -18603,7 +18642,7 @@
         <v>755</v>
       </c>
       <c r="I440">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L440" t="s">
         <v>757</v>
@@ -18630,7 +18669,7 @@
         <v>755</v>
       </c>
       <c r="I441">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L441" t="s">
         <v>758</v>
@@ -18657,7 +18696,7 @@
         <v>755</v>
       </c>
       <c r="I442">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L442" t="s">
         <v>759</v>
@@ -18684,7 +18723,7 @@
         <v>755</v>
       </c>
       <c r="I443">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L443" t="s">
         <v>760</v>
@@ -18711,7 +18750,7 @@
         <v>755</v>
       </c>
       <c r="I444">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L444" t="s">
         <v>761</v>
@@ -18909,7 +18948,7 @@
         <v>752</v>
       </c>
     </row>
-    <row r="452" spans="3:13" x14ac:dyDescent="0.3">
+    <row r="452" spans="3:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="C452" t="s">
         <v>154</v>
       </c>
@@ -18939,7 +18978,7 @@
         <v>770</v>
       </c>
     </row>
-    <row r="453" spans="3:13" x14ac:dyDescent="0.3">
+    <row r="453" spans="3:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="C453" t="s">
         <v>154</v>
       </c>
@@ -18969,7 +19008,7 @@
         <v>770</v>
       </c>
     </row>
-    <row r="454" spans="3:13" x14ac:dyDescent="0.3">
+    <row r="454" spans="3:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="C454" t="s">
         <v>154</v>
       </c>
@@ -18999,7 +19038,7 @@
         <v>770</v>
       </c>
     </row>
-    <row r="455" spans="3:13" x14ac:dyDescent="0.3">
+    <row r="455" spans="3:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="C455" t="s">
         <v>154</v>
       </c>
@@ -19029,7 +19068,7 @@
         <v>770</v>
       </c>
     </row>
-    <row r="456" spans="3:13" x14ac:dyDescent="0.3">
+    <row r="456" spans="3:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="C456" t="s">
         <v>154</v>
       </c>
@@ -19059,7 +19098,7 @@
         <v>770</v>
       </c>
     </row>
-    <row r="457" spans="3:13" x14ac:dyDescent="0.3">
+    <row r="457" spans="3:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="C457" t="s">
         <v>154</v>
       </c>
@@ -19089,7 +19128,7 @@
         <v>770</v>
       </c>
     </row>
-    <row r="458" spans="3:13" x14ac:dyDescent="0.3">
+    <row r="458" spans="3:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="C458" t="s">
         <v>154</v>
       </c>
@@ -19119,7 +19158,7 @@
         <v>770</v>
       </c>
     </row>
-    <row r="459" spans="3:13" x14ac:dyDescent="0.3">
+    <row r="459" spans="3:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="C459" t="s">
         <v>154</v>
       </c>
@@ -19149,7 +19188,7 @@
         <v>770</v>
       </c>
     </row>
-    <row r="460" spans="3:13" x14ac:dyDescent="0.3">
+    <row r="460" spans="3:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="C460" t="s">
         <v>27</v>
       </c>
@@ -19179,7 +19218,7 @@
         <v>780</v>
       </c>
     </row>
-    <row r="461" spans="3:13" x14ac:dyDescent="0.3">
+    <row r="461" spans="3:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="C461" t="s">
         <v>27</v>
       </c>
@@ -19209,7 +19248,7 @@
         <v>780</v>
       </c>
     </row>
-    <row r="462" spans="3:13" x14ac:dyDescent="0.3">
+    <row r="462" spans="3:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="C462" t="s">
         <v>27</v>
       </c>
@@ -19239,7 +19278,7 @@
         <v>780</v>
       </c>
     </row>
-    <row r="463" spans="3:13" x14ac:dyDescent="0.3">
+    <row r="463" spans="3:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="C463" t="s">
         <v>27</v>
       </c>
@@ -19269,7 +19308,7 @@
         <v>780</v>
       </c>
     </row>
-    <row r="464" spans="3:13" x14ac:dyDescent="0.3">
+    <row r="464" spans="3:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="C464" t="s">
         <v>45</v>
       </c>
@@ -19299,7 +19338,7 @@
         <v>786</v>
       </c>
     </row>
-    <row r="465" spans="3:13" x14ac:dyDescent="0.3">
+    <row r="465" spans="3:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="C465" t="s">
         <v>45</v>
       </c>
@@ -19329,7 +19368,7 @@
         <v>786</v>
       </c>
     </row>
-    <row r="466" spans="3:13" x14ac:dyDescent="0.3">
+    <row r="466" spans="3:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="C466" t="s">
         <v>45</v>
       </c>
@@ -19359,7 +19398,7 @@
         <v>786</v>
       </c>
     </row>
-    <row r="467" spans="3:13" x14ac:dyDescent="0.3">
+    <row r="467" spans="3:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="C467" t="s">
         <v>45</v>
       </c>
@@ -19389,7 +19428,7 @@
         <v>786</v>
       </c>
     </row>
-    <row r="468" spans="3:13" x14ac:dyDescent="0.3">
+    <row r="468" spans="3:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="C468" t="s">
         <v>69</v>
       </c>
@@ -19419,7 +19458,7 @@
         <v>791</v>
       </c>
     </row>
-    <row r="469" spans="3:13" x14ac:dyDescent="0.3">
+    <row r="469" spans="3:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="C469" t="s">
         <v>69</v>
       </c>
@@ -19449,7 +19488,7 @@
         <v>791</v>
       </c>
     </row>
-    <row r="470" spans="3:13" x14ac:dyDescent="0.3">
+    <row r="470" spans="3:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="C470" t="s">
         <v>69</v>
       </c>
@@ -19479,7 +19518,7 @@
         <v>791</v>
       </c>
     </row>
-    <row r="471" spans="3:13" x14ac:dyDescent="0.3">
+    <row r="471" spans="3:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="C471" t="s">
         <v>69</v>
       </c>
@@ -19509,7 +19548,7 @@
         <v>791</v>
       </c>
     </row>
-    <row r="472" spans="3:13" x14ac:dyDescent="0.3">
+    <row r="472" spans="3:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="C472" t="s">
         <v>69</v>
       </c>
@@ -19539,7 +19578,7 @@
         <v>791</v>
       </c>
     </row>
-    <row r="473" spans="3:13" x14ac:dyDescent="0.3">
+    <row r="473" spans="3:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="C473" t="s">
         <v>69</v>
       </c>
@@ -19569,7 +19608,7 @@
         <v>791</v>
       </c>
     </row>
-    <row r="474" spans="3:13" x14ac:dyDescent="0.3">
+    <row r="474" spans="3:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="C474" t="s">
         <v>69</v>
       </c>
@@ -19599,7 +19638,7 @@
         <v>791</v>
       </c>
     </row>
-    <row r="475" spans="3:13" x14ac:dyDescent="0.3">
+    <row r="475" spans="3:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="C475" t="s">
         <v>69</v>
       </c>
@@ -19629,7 +19668,7 @@
         <v>791</v>
       </c>
     </row>
-    <row r="476" spans="3:13" x14ac:dyDescent="0.3">
+    <row r="476" spans="3:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="C476" t="s">
         <v>670</v>
       </c>
@@ -19659,7 +19698,7 @@
         <v>802</v>
       </c>
     </row>
-    <row r="477" spans="3:13" x14ac:dyDescent="0.3">
+    <row r="477" spans="3:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="C477" t="s">
         <v>670</v>
       </c>
@@ -19689,7 +19728,7 @@
         <v>802</v>
       </c>
     </row>
-    <row r="478" spans="3:13" x14ac:dyDescent="0.3">
+    <row r="478" spans="3:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="C478" t="s">
         <v>670</v>
       </c>
@@ -19719,7 +19758,7 @@
         <v>802</v>
       </c>
     </row>
-    <row r="479" spans="3:13" x14ac:dyDescent="0.3">
+    <row r="479" spans="3:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="C479" t="s">
         <v>670</v>
       </c>
@@ -19749,7 +19788,7 @@
         <v>802</v>
       </c>
     </row>
-    <row r="480" spans="3:13" x14ac:dyDescent="0.3">
+    <row r="480" spans="3:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="C480" t="s">
         <v>670</v>
       </c>
@@ -19779,7 +19818,7 @@
         <v>802</v>
       </c>
     </row>
-    <row r="481" spans="2:13" x14ac:dyDescent="0.3">
+    <row r="481" spans="2:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="C481" t="s">
         <v>670</v>
       </c>
@@ -19809,7 +19848,7 @@
         <v>802</v>
       </c>
     </row>
-    <row r="482" spans="2:13" x14ac:dyDescent="0.3">
+    <row r="482" spans="2:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="C482" t="s">
         <v>670</v>
       </c>
@@ -19839,7 +19878,7 @@
         <v>802</v>
       </c>
     </row>
-    <row r="483" spans="2:13" x14ac:dyDescent="0.3">
+    <row r="483" spans="2:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="C483" t="s">
         <v>670</v>
       </c>
@@ -19869,7 +19908,7 @@
         <v>802</v>
       </c>
     </row>
-    <row r="484" spans="2:13" x14ac:dyDescent="0.3">
+    <row r="484" spans="2:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="B484" t="s">
         <v>162</v>
       </c>
@@ -19899,7 +19938,7 @@
         <v>811</v>
       </c>
     </row>
-    <row r="485" spans="2:13" x14ac:dyDescent="0.3">
+    <row r="485" spans="2:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="B485" t="s">
         <v>162</v>
       </c>
@@ -19929,7 +19968,7 @@
         <v>811</v>
       </c>
     </row>
-    <row r="486" spans="2:13" x14ac:dyDescent="0.3">
+    <row r="486" spans="2:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="B486" t="s">
         <v>162</v>
       </c>
@@ -19959,7 +19998,7 @@
         <v>811</v>
       </c>
     </row>
-    <row r="487" spans="2:13" x14ac:dyDescent="0.3">
+    <row r="487" spans="2:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="B487" t="s">
         <v>162</v>
       </c>
@@ -19989,7 +20028,7 @@
         <v>811</v>
       </c>
     </row>
-    <row r="488" spans="2:13" x14ac:dyDescent="0.3">
+    <row r="488" spans="2:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="B488" t="s">
         <v>162</v>
       </c>
@@ -20019,7 +20058,7 @@
         <v>811</v>
       </c>
     </row>
-    <row r="489" spans="2:13" x14ac:dyDescent="0.3">
+    <row r="489" spans="2:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="B489" t="s">
         <v>162</v>
       </c>
@@ -20049,7 +20088,7 @@
         <v>811</v>
       </c>
     </row>
-    <row r="490" spans="2:13" x14ac:dyDescent="0.3">
+    <row r="490" spans="2:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="B490" t="s">
         <v>162</v>
       </c>
@@ -20079,7 +20118,7 @@
         <v>811</v>
       </c>
     </row>
-    <row r="491" spans="2:13" x14ac:dyDescent="0.3">
+    <row r="491" spans="2:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="B491" t="s">
         <v>162</v>
       </c>
@@ -20109,7 +20148,7 @@
         <v>811</v>
       </c>
     </row>
-    <row r="492" spans="2:13" x14ac:dyDescent="0.3">
+    <row r="492" spans="2:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="B492" t="s">
         <v>162</v>
       </c>
@@ -20139,7 +20178,7 @@
         <v>811</v>
       </c>
     </row>
-    <row r="493" spans="2:13" x14ac:dyDescent="0.3">
+    <row r="493" spans="2:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="B493" t="s">
         <v>162</v>
       </c>
@@ -20169,7 +20208,7 @@
         <v>811</v>
       </c>
     </row>
-    <row r="494" spans="2:13" x14ac:dyDescent="0.3">
+    <row r="494" spans="2:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="B494" t="s">
         <v>162</v>
       </c>
@@ -20199,7 +20238,7 @@
         <v>811</v>
       </c>
     </row>
-    <row r="495" spans="2:13" x14ac:dyDescent="0.3">
+    <row r="495" spans="2:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="B495" t="s">
         <v>162</v>
       </c>
@@ -20229,7 +20268,7 @@
         <v>811</v>
       </c>
     </row>
-    <row r="496" spans="2:13" x14ac:dyDescent="0.3">
+    <row r="496" spans="2:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="C496" t="s">
         <v>101</v>
       </c>
@@ -20259,7 +20298,7 @@
         <v>825</v>
       </c>
     </row>
-    <row r="497" spans="2:13" x14ac:dyDescent="0.3">
+    <row r="497" spans="2:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="C497" t="s">
         <v>101</v>
       </c>
@@ -20289,7 +20328,7 @@
         <v>825</v>
       </c>
     </row>
-    <row r="498" spans="2:13" x14ac:dyDescent="0.3">
+    <row r="498" spans="2:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="C498" t="s">
         <v>101</v>
       </c>
@@ -20319,7 +20358,7 @@
         <v>825</v>
       </c>
     </row>
-    <row r="499" spans="2:13" x14ac:dyDescent="0.3">
+    <row r="499" spans="2:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="C499" t="s">
         <v>101</v>
       </c>
@@ -20349,7 +20388,7 @@
         <v>825</v>
       </c>
     </row>
-    <row r="500" spans="2:13" x14ac:dyDescent="0.3">
+    <row r="500" spans="2:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="C500" t="s">
         <v>101</v>
       </c>
@@ -20379,7 +20418,7 @@
         <v>825</v>
       </c>
     </row>
-    <row r="501" spans="2:13" x14ac:dyDescent="0.3">
+    <row r="501" spans="2:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="C501" t="s">
         <v>101</v>
       </c>
@@ -20409,7 +20448,7 @@
         <v>825</v>
       </c>
     </row>
-    <row r="502" spans="2:13" x14ac:dyDescent="0.3">
+    <row r="502" spans="2:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="C502" t="s">
         <v>110</v>
       </c>
@@ -20439,7 +20478,7 @@
         <v>832</v>
       </c>
     </row>
-    <row r="503" spans="2:13" x14ac:dyDescent="0.3">
+    <row r="503" spans="2:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="C503" t="s">
         <v>110</v>
       </c>
@@ -20469,7 +20508,7 @@
         <v>832</v>
       </c>
     </row>
-    <row r="504" spans="2:13" x14ac:dyDescent="0.3">
+    <row r="504" spans="2:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="C504" t="s">
         <v>110</v>
       </c>
@@ -20499,7 +20538,7 @@
         <v>832</v>
       </c>
     </row>
-    <row r="505" spans="2:13" x14ac:dyDescent="0.3">
+    <row r="505" spans="2:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="C505" t="s">
         <v>110</v>
       </c>
@@ -20529,7 +20568,7 @@
         <v>832</v>
       </c>
     </row>
-    <row r="506" spans="2:13" x14ac:dyDescent="0.3">
+    <row r="506" spans="2:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="C506" t="s">
         <v>110</v>
       </c>
@@ -20559,7 +20598,7 @@
         <v>837</v>
       </c>
     </row>
-    <row r="507" spans="2:13" x14ac:dyDescent="0.3">
+    <row r="507" spans="2:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="C507" t="s">
         <v>110</v>
       </c>
@@ -20589,7 +20628,7 @@
         <v>837</v>
       </c>
     </row>
-    <row r="508" spans="2:13" x14ac:dyDescent="0.3">
+    <row r="508" spans="2:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="C508" t="s">
         <v>110</v>
       </c>
@@ -20619,7 +20658,7 @@
         <v>837</v>
       </c>
     </row>
-    <row r="509" spans="2:13" x14ac:dyDescent="0.3">
+    <row r="509" spans="2:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="C509" t="s">
         <v>110</v>
       </c>
@@ -20649,7 +20688,7 @@
         <v>837</v>
       </c>
     </row>
-    <row r="510" spans="2:13" x14ac:dyDescent="0.3">
+    <row r="510" spans="2:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="B510" t="s">
         <v>162</v>
       </c>
@@ -20679,7 +20718,7 @@
         <v>842</v>
       </c>
     </row>
-    <row r="511" spans="2:13" x14ac:dyDescent="0.3">
+    <row r="511" spans="2:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="B511" t="s">
         <v>162</v>
       </c>
@@ -20709,7 +20748,7 @@
         <v>842</v>
       </c>
     </row>
-    <row r="512" spans="2:13" x14ac:dyDescent="0.3">
+    <row r="512" spans="2:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="B512" t="s">
         <v>162</v>
       </c>
@@ -20739,7 +20778,7 @@
         <v>842</v>
       </c>
     </row>
-    <row r="513" spans="2:13" x14ac:dyDescent="0.3">
+    <row r="513" spans="2:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="B513" t="s">
         <v>162</v>
       </c>
@@ -20769,7 +20808,7 @@
         <v>842</v>
       </c>
     </row>
-    <row r="514" spans="2:13" x14ac:dyDescent="0.3">
+    <row r="514" spans="2:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="B514" t="s">
         <v>162</v>
       </c>
@@ -20799,7 +20838,7 @@
         <v>842</v>
       </c>
     </row>
-    <row r="515" spans="2:13" x14ac:dyDescent="0.3">
+    <row r="515" spans="2:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="B515" t="s">
         <v>162</v>
       </c>
@@ -20829,7 +20868,7 @@
         <v>842</v>
       </c>
     </row>
-    <row r="516" spans="2:13" x14ac:dyDescent="0.3">
+    <row r="516" spans="2:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="B516" t="s">
         <v>162</v>
       </c>
@@ -20859,7 +20898,7 @@
         <v>842</v>
       </c>
     </row>
-    <row r="517" spans="2:13" x14ac:dyDescent="0.3">
+    <row r="517" spans="2:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="B517" t="s">
         <v>162</v>
       </c>
@@ -20889,7 +20928,7 @@
         <v>842</v>
       </c>
     </row>
-    <row r="518" spans="2:13" x14ac:dyDescent="0.3">
+    <row r="518" spans="2:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="B518" t="s">
         <v>162</v>
       </c>
@@ -20919,7 +20958,7 @@
         <v>842</v>
       </c>
     </row>
-    <row r="519" spans="2:13" x14ac:dyDescent="0.3">
+    <row r="519" spans="2:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="B519" t="s">
         <v>162</v>
       </c>
@@ -20949,7 +20988,7 @@
         <v>842</v>
       </c>
     </row>
-    <row r="520" spans="2:13" x14ac:dyDescent="0.3">
+    <row r="520" spans="2:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="B520" t="s">
         <v>162</v>
       </c>
@@ -20979,7 +21018,7 @@
         <v>842</v>
       </c>
     </row>
-    <row r="521" spans="2:13" x14ac:dyDescent="0.3">
+    <row r="521" spans="2:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="B521" t="s">
         <v>162</v>
       </c>
@@ -21027,7 +21066,7 @@
         <v>854</v>
       </c>
       <c r="I522">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L522" t="s">
         <v>855</v>
@@ -21054,7 +21093,7 @@
         <v>854</v>
       </c>
       <c r="I523">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L523" t="s">
         <v>857</v>
@@ -21081,7 +21120,7 @@
         <v>854</v>
       </c>
       <c r="I524">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L524" t="s">
         <v>757</v>
@@ -21108,7 +21147,7 @@
         <v>854</v>
       </c>
       <c r="I525">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L525" t="s">
         <v>768</v>
@@ -21135,7 +21174,7 @@
         <v>854</v>
       </c>
       <c r="I526">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L526" t="s">
         <v>756</v>
@@ -21162,7 +21201,7 @@
         <v>858</v>
       </c>
       <c r="I527">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L527" t="s">
         <v>859</v>
@@ -21189,7 +21228,7 @@
         <v>860</v>
       </c>
       <c r="I528">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L528" t="s">
         <v>861</v>
@@ -21216,7 +21255,7 @@
         <v>862</v>
       </c>
       <c r="I529">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L529" t="s">
         <v>761</v>
@@ -21243,7 +21282,7 @@
         <v>863</v>
       </c>
       <c r="I530">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L530" t="s">
         <v>864</v>
@@ -21270,7 +21309,7 @@
         <v>865</v>
       </c>
       <c r="I531">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L531" t="s">
         <v>866</v>
@@ -21297,7 +21336,7 @@
         <v>867</v>
       </c>
       <c r="I532">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L532" t="s">
         <v>868</v>
@@ -21324,7 +21363,7 @@
         <v>869</v>
       </c>
       <c r="I533">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L533" t="s">
         <v>870</v>
@@ -21432,7 +21471,7 @@
         <v>871</v>
       </c>
       <c r="I537">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="L537" t="s">
         <v>766</v>
@@ -21549,7 +21588,7 @@
         <v>856</v>
       </c>
     </row>
-    <row r="542" spans="2:13" x14ac:dyDescent="0.3">
+    <row r="542" spans="2:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="B542" t="s">
         <v>137</v>
       </c>
@@ -21579,7 +21618,7 @@
         <v>878</v>
       </c>
     </row>
-    <row r="543" spans="2:13" x14ac:dyDescent="0.3">
+    <row r="543" spans="2:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="B543" t="s">
         <v>137</v>
       </c>
@@ -21609,7 +21648,7 @@
         <v>878</v>
       </c>
     </row>
-    <row r="544" spans="2:13" x14ac:dyDescent="0.3">
+    <row r="544" spans="2:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="B544" t="s">
         <v>137</v>
       </c>
@@ -21639,7 +21678,7 @@
         <v>878</v>
       </c>
     </row>
-    <row r="545" spans="2:13" x14ac:dyDescent="0.3">
+    <row r="545" spans="2:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="B545" t="s">
         <v>137</v>
       </c>
@@ -21669,7 +21708,7 @@
         <v>878</v>
       </c>
     </row>
-    <row r="546" spans="2:13" x14ac:dyDescent="0.3">
+    <row r="546" spans="2:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="C546" t="s">
         <v>150</v>
       </c>
@@ -21699,7 +21738,7 @@
         <v>886</v>
       </c>
     </row>
-    <row r="547" spans="2:13" x14ac:dyDescent="0.3">
+    <row r="547" spans="2:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="C547" t="s">
         <v>150</v>
       </c>
@@ -21729,7 +21768,7 @@
         <v>886</v>
       </c>
     </row>
-    <row r="548" spans="2:13" x14ac:dyDescent="0.3">
+    <row r="548" spans="2:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="C548" t="s">
         <v>150</v>
       </c>
@@ -21759,7 +21798,7 @@
         <v>886</v>
       </c>
     </row>
-    <row r="549" spans="2:13" x14ac:dyDescent="0.3">
+    <row r="549" spans="2:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="C549" t="s">
         <v>150</v>
       </c>
@@ -21789,7 +21828,7 @@
         <v>886</v>
       </c>
     </row>
-    <row r="550" spans="2:13" x14ac:dyDescent="0.3">
+    <row r="550" spans="2:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="C550" t="s">
         <v>303</v>
       </c>
@@ -21816,7 +21855,7 @@
         <v>891</v>
       </c>
     </row>
-    <row r="551" spans="2:13" x14ac:dyDescent="0.3">
+    <row r="551" spans="2:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="C551" t="s">
         <v>303</v>
       </c>
@@ -21843,7 +21882,7 @@
         <v>891</v>
       </c>
     </row>
-    <row r="552" spans="2:13" x14ac:dyDescent="0.3">
+    <row r="552" spans="2:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="C552" t="s">
         <v>303</v>
       </c>
@@ -21870,7 +21909,7 @@
         <v>891</v>
       </c>
     </row>
-    <row r="553" spans="2:13" x14ac:dyDescent="0.3">
+    <row r="553" spans="2:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="B553" t="s">
         <v>137</v>
       </c>
@@ -21900,7 +21939,7 @@
         <v>897</v>
       </c>
     </row>
-    <row r="554" spans="2:13" x14ac:dyDescent="0.3">
+    <row r="554" spans="2:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="B554" t="s">
         <v>137</v>
       </c>
@@ -21930,7 +21969,7 @@
         <v>897</v>
       </c>
     </row>
-    <row r="555" spans="2:13" x14ac:dyDescent="0.3">
+    <row r="555" spans="2:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="B555" t="s">
         <v>137</v>
       </c>
@@ -21960,7 +21999,7 @@
         <v>897</v>
       </c>
     </row>
-    <row r="556" spans="2:13" x14ac:dyDescent="0.3">
+    <row r="556" spans="2:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="B556" t="s">
         <v>137</v>
       </c>
@@ -21990,7 +22029,7 @@
         <v>897</v>
       </c>
     </row>
-    <row r="557" spans="2:13" x14ac:dyDescent="0.3">
+    <row r="557" spans="2:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="B557" t="s">
         <v>137</v>
       </c>
@@ -22020,7 +22059,7 @@
         <v>906</v>
       </c>
     </row>
-    <row r="558" spans="2:13" x14ac:dyDescent="0.3">
+    <row r="558" spans="2:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="B558" t="s">
         <v>137</v>
       </c>
@@ -22050,7 +22089,7 @@
         <v>906</v>
       </c>
     </row>
-    <row r="559" spans="2:13" x14ac:dyDescent="0.3">
+    <row r="559" spans="2:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="B559" t="s">
         <v>137</v>
       </c>
@@ -22080,7 +22119,7 @@
         <v>906</v>
       </c>
     </row>
-    <row r="560" spans="2:13" x14ac:dyDescent="0.3">
+    <row r="560" spans="2:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="B560" t="s">
         <v>137</v>
       </c>
@@ -22110,7 +22149,7 @@
         <v>906</v>
       </c>
     </row>
-    <row r="561" spans="2:13" x14ac:dyDescent="0.3">
+    <row r="561" spans="2:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="C561" t="s">
         <v>154</v>
       </c>
@@ -22140,7 +22179,7 @@
         <v>914</v>
       </c>
     </row>
-    <row r="562" spans="2:13" x14ac:dyDescent="0.3">
+    <row r="562" spans="2:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="C562" t="s">
         <v>154</v>
       </c>
@@ -22170,7 +22209,7 @@
         <v>914</v>
       </c>
     </row>
-    <row r="563" spans="2:13" x14ac:dyDescent="0.3">
+    <row r="563" spans="2:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="C563" t="s">
         <v>154</v>
       </c>
@@ -22200,7 +22239,7 @@
         <v>914</v>
       </c>
     </row>
-    <row r="564" spans="2:13" x14ac:dyDescent="0.3">
+    <row r="564" spans="2:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="C564" t="s">
         <v>154</v>
       </c>
@@ -22230,7 +22269,7 @@
         <v>914</v>
       </c>
     </row>
-    <row r="565" spans="2:13" x14ac:dyDescent="0.3">
+    <row r="565" spans="2:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="C565" t="s">
         <v>154</v>
       </c>
@@ -22260,7 +22299,7 @@
         <v>914</v>
       </c>
     </row>
-    <row r="566" spans="2:13" x14ac:dyDescent="0.3">
+    <row r="566" spans="2:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="C566" t="s">
         <v>154</v>
       </c>
@@ -22290,7 +22329,7 @@
         <v>914</v>
       </c>
     </row>
-    <row r="567" spans="2:13" x14ac:dyDescent="0.3">
+    <row r="567" spans="2:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="C567" t="s">
         <v>154</v>
       </c>
@@ -22320,7 +22359,7 @@
         <v>914</v>
       </c>
     </row>
-    <row r="568" spans="2:13" x14ac:dyDescent="0.3">
+    <row r="568" spans="2:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="C568" t="s">
         <v>154</v>
       </c>
@@ -22350,7 +22389,7 @@
         <v>914</v>
       </c>
     </row>
-    <row r="569" spans="2:13" x14ac:dyDescent="0.3">
+    <row r="569" spans="2:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="C569" t="s">
         <v>45</v>
       </c>
@@ -22380,7 +22419,7 @@
         <v>925</v>
       </c>
     </row>
-    <row r="570" spans="2:13" x14ac:dyDescent="0.3">
+    <row r="570" spans="2:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="C570" t="s">
         <v>45</v>
       </c>
@@ -22410,7 +22449,7 @@
         <v>925</v>
       </c>
     </row>
-    <row r="571" spans="2:13" x14ac:dyDescent="0.3">
+    <row r="571" spans="2:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="C571" t="s">
         <v>45</v>
       </c>
@@ -22440,7 +22479,7 @@
         <v>925</v>
       </c>
     </row>
-    <row r="572" spans="2:13" x14ac:dyDescent="0.3">
+    <row r="572" spans="2:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="C572" t="s">
         <v>45</v>
       </c>
@@ -22470,7 +22509,7 @@
         <v>925</v>
       </c>
     </row>
-    <row r="573" spans="2:13" x14ac:dyDescent="0.3">
+    <row r="573" spans="2:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="B573" t="s">
         <v>137</v>
       </c>
@@ -22500,7 +22539,7 @@
         <v>931</v>
       </c>
     </row>
-    <row r="574" spans="2:13" x14ac:dyDescent="0.3">
+    <row r="574" spans="2:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="B574" t="s">
         <v>137</v>
       </c>
@@ -22530,7 +22569,7 @@
         <v>931</v>
       </c>
     </row>
-    <row r="575" spans="2:13" x14ac:dyDescent="0.3">
+    <row r="575" spans="2:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="B575" t="s">
         <v>137</v>
       </c>
@@ -22560,7 +22599,7 @@
         <v>937</v>
       </c>
     </row>
-    <row r="576" spans="2:13" x14ac:dyDescent="0.3">
+    <row r="576" spans="2:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="B576" t="s">
         <v>137</v>
       </c>
@@ -22590,7 +22629,7 @@
         <v>937</v>
       </c>
     </row>
-    <row r="577" spans="2:13" x14ac:dyDescent="0.3">
+    <row r="577" spans="2:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="B577" t="s">
         <v>137</v>
       </c>
@@ -22620,7 +22659,7 @@
         <v>943</v>
       </c>
     </row>
-    <row r="578" spans="2:13" x14ac:dyDescent="0.3">
+    <row r="578" spans="2:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="B578" t="s">
         <v>137</v>
       </c>
@@ -22650,7 +22689,7 @@
         <v>943</v>
       </c>
     </row>
-    <row r="579" spans="2:13" x14ac:dyDescent="0.3">
+    <row r="579" spans="2:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="B579" t="s">
         <v>137</v>
       </c>
@@ -22680,7 +22719,7 @@
         <v>948</v>
       </c>
     </row>
-    <row r="580" spans="2:13" x14ac:dyDescent="0.3">
+    <row r="580" spans="2:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="B580" t="s">
         <v>137</v>
       </c>
@@ -22710,7 +22749,7 @@
         <v>948</v>
       </c>
     </row>
-    <row r="581" spans="2:13" x14ac:dyDescent="0.3">
+    <row r="581" spans="2:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="B581" t="s">
         <v>137</v>
       </c>
@@ -22740,7 +22779,7 @@
         <v>948</v>
       </c>
     </row>
-    <row r="582" spans="2:13" x14ac:dyDescent="0.3">
+    <row r="582" spans="2:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="C582" t="s">
         <v>154</v>
       </c>
@@ -22770,7 +22809,7 @@
         <v>955</v>
       </c>
     </row>
-    <row r="583" spans="2:13" x14ac:dyDescent="0.3">
+    <row r="583" spans="2:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="C583" t="s">
         <v>154</v>
       </c>
@@ -22800,7 +22839,7 @@
         <v>955</v>
       </c>
     </row>
-    <row r="584" spans="2:13" x14ac:dyDescent="0.3">
+    <row r="584" spans="2:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="C584" t="s">
         <v>154</v>
       </c>
@@ -22830,7 +22869,7 @@
         <v>955</v>
       </c>
     </row>
-    <row r="585" spans="2:13" x14ac:dyDescent="0.3">
+    <row r="585" spans="2:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="C585" t="s">
         <v>154</v>
       </c>
@@ -22860,7 +22899,7 @@
         <v>955</v>
       </c>
     </row>
-    <row r="586" spans="2:13" x14ac:dyDescent="0.3">
+    <row r="586" spans="2:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="C586" t="s">
         <v>27</v>
       </c>
@@ -22890,7 +22929,7 @@
         <v>961</v>
       </c>
     </row>
-    <row r="587" spans="2:13" x14ac:dyDescent="0.3">
+    <row r="587" spans="2:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="C587" t="s">
         <v>27</v>
       </c>
@@ -22920,7 +22959,7 @@
         <v>961</v>
       </c>
     </row>
-    <row r="588" spans="2:13" x14ac:dyDescent="0.3">
+    <row r="588" spans="2:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="C588" t="s">
         <v>27</v>
       </c>
@@ -22950,7 +22989,7 @@
         <v>961</v>
       </c>
     </row>
-    <row r="589" spans="2:13" x14ac:dyDescent="0.3">
+    <row r="589" spans="2:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="C589" t="s">
         <v>27</v>
       </c>
@@ -22980,7 +23019,7 @@
         <v>961</v>
       </c>
     </row>
-    <row r="590" spans="2:13" x14ac:dyDescent="0.3">
+    <row r="590" spans="2:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="C590" t="s">
         <v>45</v>
       </c>
@@ -23010,7 +23049,7 @@
         <v>967</v>
       </c>
     </row>
-    <row r="591" spans="2:13" x14ac:dyDescent="0.3">
+    <row r="591" spans="2:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="C591" t="s">
         <v>45</v>
       </c>
@@ -23040,7 +23079,7 @@
         <v>967</v>
       </c>
     </row>
-    <row r="592" spans="2:13" x14ac:dyDescent="0.3">
+    <row r="592" spans="2:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="C592" t="s">
         <v>45</v>
       </c>
@@ -23070,7 +23109,7 @@
         <v>967</v>
       </c>
     </row>
-    <row r="593" spans="2:13" x14ac:dyDescent="0.3">
+    <row r="593" spans="2:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="C593" t="s">
         <v>45</v>
       </c>
@@ -23100,7 +23139,7 @@
         <v>967</v>
       </c>
     </row>
-    <row r="594" spans="2:13" x14ac:dyDescent="0.3">
+    <row r="594" spans="2:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="C594" t="s">
         <v>69</v>
       </c>
@@ -23130,7 +23169,7 @@
         <v>972</v>
       </c>
     </row>
-    <row r="595" spans="2:13" x14ac:dyDescent="0.3">
+    <row r="595" spans="2:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="C595" t="s">
         <v>69</v>
       </c>
@@ -23160,7 +23199,7 @@
         <v>972</v>
       </c>
     </row>
-    <row r="596" spans="2:13" x14ac:dyDescent="0.3">
+    <row r="596" spans="2:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="C596" t="s">
         <v>69</v>
       </c>
@@ -23190,7 +23229,7 @@
         <v>972</v>
       </c>
     </row>
-    <row r="597" spans="2:13" x14ac:dyDescent="0.3">
+    <row r="597" spans="2:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="C597" t="s">
         <v>69</v>
       </c>
@@ -23220,7 +23259,7 @@
         <v>972</v>
       </c>
     </row>
-    <row r="598" spans="2:13" x14ac:dyDescent="0.3">
+    <row r="598" spans="2:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="C598" t="s">
         <v>69</v>
       </c>
@@ -23250,7 +23289,7 @@
         <v>972</v>
       </c>
     </row>
-    <row r="599" spans="2:13" x14ac:dyDescent="0.3">
+    <row r="599" spans="2:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="C599" t="s">
         <v>69</v>
       </c>
@@ -23280,7 +23319,7 @@
         <v>972</v>
       </c>
     </row>
-    <row r="600" spans="2:13" x14ac:dyDescent="0.3">
+    <row r="600" spans="2:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="C600" t="s">
         <v>69</v>
       </c>
@@ -23310,7 +23349,7 @@
         <v>972</v>
       </c>
     </row>
-    <row r="601" spans="2:13" x14ac:dyDescent="0.3">
+    <row r="601" spans="2:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="C601" t="s">
         <v>69</v>
       </c>
@@ -23340,7 +23379,7 @@
         <v>972</v>
       </c>
     </row>
-    <row r="602" spans="2:13" x14ac:dyDescent="0.3">
+    <row r="602" spans="2:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="C602" t="s">
         <v>90</v>
       </c>
@@ -23370,7 +23409,7 @@
         <v>981</v>
       </c>
     </row>
-    <row r="603" spans="2:13" x14ac:dyDescent="0.3">
+    <row r="603" spans="2:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="C603" t="s">
         <v>90</v>
       </c>
@@ -23400,7 +23439,7 @@
         <v>981</v>
       </c>
     </row>
-    <row r="604" spans="2:13" x14ac:dyDescent="0.3">
+    <row r="604" spans="2:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="C604" t="s">
         <v>90</v>
       </c>
@@ -23430,7 +23469,7 @@
         <v>981</v>
       </c>
     </row>
-    <row r="605" spans="2:13" x14ac:dyDescent="0.3">
+    <row r="605" spans="2:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="C605" t="s">
         <v>90</v>
       </c>
@@ -23460,7 +23499,7 @@
         <v>981</v>
       </c>
     </row>
-    <row r="606" spans="2:13" x14ac:dyDescent="0.3">
+    <row r="606" spans="2:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="B606" t="s">
         <v>162</v>
       </c>
@@ -23490,7 +23529,7 @@
         <v>986</v>
       </c>
     </row>
-    <row r="607" spans="2:13" x14ac:dyDescent="0.3">
+    <row r="607" spans="2:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="B607" t="s">
         <v>162</v>
       </c>
@@ -23520,7 +23559,7 @@
         <v>986</v>
       </c>
     </row>
-    <row r="608" spans="2:13" x14ac:dyDescent="0.3">
+    <row r="608" spans="2:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="B608" t="s">
         <v>162</v>
       </c>
@@ -23550,7 +23589,7 @@
         <v>986</v>
       </c>
     </row>
-    <row r="609" spans="2:13" x14ac:dyDescent="0.3">
+    <row r="609" spans="2:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="B609" t="s">
         <v>162</v>
       </c>
@@ -23580,7 +23619,7 @@
         <v>986</v>
       </c>
     </row>
-    <row r="610" spans="2:13" x14ac:dyDescent="0.3">
+    <row r="610" spans="2:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="B610" t="s">
         <v>162</v>
       </c>
@@ -23610,7 +23649,7 @@
         <v>986</v>
       </c>
     </row>
-    <row r="611" spans="2:13" x14ac:dyDescent="0.3">
+    <row r="611" spans="2:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="B611" t="s">
         <v>162</v>
       </c>
@@ -23640,7 +23679,7 @@
         <v>986</v>
       </c>
     </row>
-    <row r="612" spans="2:13" x14ac:dyDescent="0.3">
+    <row r="612" spans="2:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="B612" t="s">
         <v>162</v>
       </c>
@@ -23670,7 +23709,7 @@
         <v>986</v>
       </c>
     </row>
-    <row r="613" spans="2:13" x14ac:dyDescent="0.3">
+    <row r="613" spans="2:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="B613" t="s">
         <v>162</v>
       </c>
@@ -23700,7 +23739,7 @@
         <v>986</v>
       </c>
     </row>
-    <row r="614" spans="2:13" x14ac:dyDescent="0.3">
+    <row r="614" spans="2:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="B614" t="s">
         <v>162</v>
       </c>
@@ -23730,7 +23769,7 @@
         <v>986</v>
       </c>
     </row>
-    <row r="615" spans="2:13" x14ac:dyDescent="0.3">
+    <row r="615" spans="2:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="B615" t="s">
         <v>137</v>
       </c>
@@ -23763,7 +23802,7 @@
         <v>997</v>
       </c>
     </row>
-    <row r="616" spans="2:13" x14ac:dyDescent="0.3">
+    <row r="616" spans="2:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="B616" t="s">
         <v>137</v>
       </c>
@@ -23796,7 +23835,7 @@
         <v>997</v>
       </c>
     </row>
-    <row r="617" spans="2:13" x14ac:dyDescent="0.3">
+    <row r="617" spans="2:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="B617" t="s">
         <v>137</v>
       </c>
@@ -23829,7 +23868,7 @@
         <v>997</v>
       </c>
     </row>
-    <row r="618" spans="2:13" x14ac:dyDescent="0.3">
+    <row r="618" spans="2:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="B618" t="s">
         <v>137</v>
       </c>
@@ -23862,7 +23901,7 @@
         <v>997</v>
       </c>
     </row>
-    <row r="619" spans="2:13" x14ac:dyDescent="0.3">
+    <row r="619" spans="2:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="B619" t="s">
         <v>137</v>
       </c>
@@ -23895,7 +23934,7 @@
         <v>997</v>
       </c>
     </row>
-    <row r="620" spans="2:13" x14ac:dyDescent="0.3">
+    <row r="620" spans="2:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="B620" t="s">
         <v>137</v>
       </c>
@@ -23928,7 +23967,7 @@
         <v>997</v>
       </c>
     </row>
-    <row r="621" spans="2:13" x14ac:dyDescent="0.3">
+    <row r="621" spans="2:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="C621" t="s">
         <v>101</v>
       </c>
@@ -23958,7 +23997,7 @@
         <v>1010</v>
       </c>
     </row>
-    <row r="622" spans="2:13" x14ac:dyDescent="0.3">
+    <row r="622" spans="2:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="C622" t="s">
         <v>101</v>
       </c>
@@ -23988,7 +24027,7 @@
         <v>1010</v>
       </c>
     </row>
-    <row r="623" spans="2:13" x14ac:dyDescent="0.3">
+    <row r="623" spans="2:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="C623" t="s">
         <v>101</v>
       </c>
@@ -24018,7 +24057,7 @@
         <v>1010</v>
       </c>
     </row>
-    <row r="624" spans="2:13" x14ac:dyDescent="0.3">
+    <row r="624" spans="2:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="C624" t="s">
         <v>101</v>
       </c>
@@ -24048,7 +24087,7 @@
         <v>1010</v>
       </c>
     </row>
-    <row r="625" spans="2:13" x14ac:dyDescent="0.3">
+    <row r="625" spans="2:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="C625" t="s">
         <v>101</v>
       </c>
@@ -24078,7 +24117,7 @@
         <v>1010</v>
       </c>
     </row>
-    <row r="626" spans="2:13" x14ac:dyDescent="0.3">
+    <row r="626" spans="2:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="C626" t="s">
         <v>101</v>
       </c>
@@ -24108,7 +24147,7 @@
         <v>1010</v>
       </c>
     </row>
-    <row r="627" spans="2:13" x14ac:dyDescent="0.3">
+    <row r="627" spans="2:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="B627" t="s">
         <v>137</v>
       </c>
@@ -24138,7 +24177,7 @@
         <v>1017</v>
       </c>
     </row>
-    <row r="628" spans="2:13" x14ac:dyDescent="0.3">
+    <row r="628" spans="2:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="B628" t="s">
         <v>137</v>
       </c>
@@ -24168,7 +24207,7 @@
         <v>1017</v>
       </c>
     </row>
-    <row r="629" spans="2:13" x14ac:dyDescent="0.3">
+    <row r="629" spans="2:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="C629" t="s">
         <v>399</v>
       </c>
@@ -24198,7 +24237,7 @@
         <v>1022</v>
       </c>
     </row>
-    <row r="630" spans="2:13" x14ac:dyDescent="0.3">
+    <row r="630" spans="2:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="C630" t="s">
         <v>399</v>
       </c>
@@ -24228,7 +24267,7 @@
         <v>1022</v>
       </c>
     </row>
-    <row r="631" spans="2:13" x14ac:dyDescent="0.3">
+    <row r="631" spans="2:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="B631" t="s">
         <v>162</v>
       </c>
@@ -24258,7 +24297,7 @@
         <v>1026</v>
       </c>
     </row>
-    <row r="632" spans="2:13" x14ac:dyDescent="0.3">
+    <row r="632" spans="2:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="B632" t="s">
         <v>162</v>
       </c>
@@ -24288,7 +24327,7 @@
         <v>1026</v>
       </c>
     </row>
-    <row r="633" spans="2:13" x14ac:dyDescent="0.3">
+    <row r="633" spans="2:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="B633" t="s">
         <v>162</v>
       </c>
@@ -24318,7 +24357,7 @@
         <v>1026</v>
       </c>
     </row>
-    <row r="634" spans="2:13" x14ac:dyDescent="0.3">
+    <row r="634" spans="2:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="B634" t="s">
         <v>162</v>
       </c>
@@ -24348,7 +24387,7 @@
         <v>1026</v>
       </c>
     </row>
-    <row r="635" spans="2:13" x14ac:dyDescent="0.3">
+    <row r="635" spans="2:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="B635" t="s">
         <v>162</v>
       </c>
@@ -24378,7 +24417,7 @@
         <v>1026</v>
       </c>
     </row>
-    <row r="636" spans="2:13" x14ac:dyDescent="0.3">
+    <row r="636" spans="2:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="B636" t="s">
         <v>162</v>
       </c>
@@ -24408,7 +24447,7 @@
         <v>1026</v>
       </c>
     </row>
-    <row r="637" spans="2:13" x14ac:dyDescent="0.3">
+    <row r="637" spans="2:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="B637" t="s">
         <v>162</v>
       </c>
@@ -24438,7 +24477,7 @@
         <v>1026</v>
       </c>
     </row>
-    <row r="638" spans="2:13" x14ac:dyDescent="0.3">
+    <row r="638" spans="2:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="B638" t="s">
         <v>162</v>
       </c>
@@ -24468,7 +24507,7 @@
         <v>1026</v>
       </c>
     </row>
-    <row r="639" spans="2:13" x14ac:dyDescent="0.3">
+    <row r="639" spans="2:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="B639" t="s">
         <v>162</v>
       </c>
@@ -24498,7 +24537,7 @@
         <v>1026</v>
       </c>
     </row>
-    <row r="640" spans="2:13" x14ac:dyDescent="0.3">
+    <row r="640" spans="2:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="C640" t="s">
         <v>129</v>
       </c>
@@ -24528,7 +24567,7 @@
         <v>1034</v>
       </c>
     </row>
-    <row r="641" spans="2:13" x14ac:dyDescent="0.3">
+    <row r="641" spans="2:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="C641" t="s">
         <v>129</v>
       </c>
@@ -24558,7 +24597,7 @@
         <v>1034</v>
       </c>
     </row>
-    <row r="642" spans="2:13" x14ac:dyDescent="0.3">
+    <row r="642" spans="2:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="C642" t="s">
         <v>129</v>
       </c>
@@ -24588,7 +24627,7 @@
         <v>1034</v>
       </c>
     </row>
-    <row r="643" spans="2:13" x14ac:dyDescent="0.3">
+    <row r="643" spans="2:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="C643" t="s">
         <v>129</v>
       </c>
@@ -24618,7 +24657,7 @@
         <v>1034</v>
       </c>
     </row>
-    <row r="644" spans="2:13" x14ac:dyDescent="0.3">
+    <row r="644" spans="2:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="D644" t="s">
         <v>1037</v>
       </c>
@@ -24645,7 +24684,7 @@
         <v>1039</v>
       </c>
     </row>
-    <row r="645" spans="2:13" x14ac:dyDescent="0.3">
+    <row r="645" spans="2:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="D645" t="s">
         <v>1037</v>
       </c>
@@ -24672,7 +24711,7 @@
         <v>1039</v>
       </c>
     </row>
-    <row r="646" spans="2:13" x14ac:dyDescent="0.3">
+    <row r="646" spans="2:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="D646" t="s">
         <v>1037</v>
       </c>
@@ -24699,7 +24738,7 @@
         <v>1039</v>
       </c>
     </row>
-    <row r="647" spans="2:13" x14ac:dyDescent="0.3">
+    <row r="647" spans="2:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="D647" t="s">
         <v>1037</v>
       </c>
@@ -24786,7 +24825,7 @@
         <v>1046</v>
       </c>
     </row>
-    <row r="650" spans="2:13" x14ac:dyDescent="0.3">
+    <row r="650" spans="2:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="C650" t="s">
         <v>154</v>
       </c>
@@ -24816,7 +24855,7 @@
         <v>1051</v>
       </c>
     </row>
-    <row r="651" spans="2:13" x14ac:dyDescent="0.3">
+    <row r="651" spans="2:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="C651" t="s">
         <v>154</v>
       </c>
@@ -24846,7 +24885,7 @@
         <v>1051</v>
       </c>
     </row>
-    <row r="652" spans="2:13" x14ac:dyDescent="0.3">
+    <row r="652" spans="2:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="C652" t="s">
         <v>154</v>
       </c>
@@ -24876,7 +24915,7 @@
         <v>1051</v>
       </c>
     </row>
-    <row r="653" spans="2:13" x14ac:dyDescent="0.3">
+    <row r="653" spans="2:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="C653" t="s">
         <v>154</v>
       </c>
@@ -24906,7 +24945,7 @@
         <v>1051</v>
       </c>
     </row>
-    <row r="654" spans="2:13" x14ac:dyDescent="0.3">
+    <row r="654" spans="2:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="B654" t="s">
         <v>137</v>
       </c>
@@ -24933,7 +24972,7 @@
         <v>1057</v>
       </c>
     </row>
-    <row r="655" spans="2:13" x14ac:dyDescent="0.3">
+    <row r="655" spans="2:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="B655" t="s">
         <v>137</v>
       </c>
@@ -24963,7 +25002,7 @@
         <v>1057</v>
       </c>
     </row>
-    <row r="656" spans="2:13" x14ac:dyDescent="0.3">
+    <row r="656" spans="2:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="B656" t="s">
         <v>137</v>
       </c>
@@ -24993,7 +25032,7 @@
         <v>1057</v>
       </c>
     </row>
-    <row r="657" spans="2:13" x14ac:dyDescent="0.3">
+    <row r="657" spans="2:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="C657" t="s">
         <v>45</v>
       </c>
@@ -25023,7 +25062,7 @@
         <v>1065</v>
       </c>
     </row>
-    <row r="658" spans="2:13" x14ac:dyDescent="0.3">
+    <row r="658" spans="2:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="C658" t="s">
         <v>45</v>
       </c>
@@ -25053,7 +25092,7 @@
         <v>1065</v>
       </c>
     </row>
-    <row r="659" spans="2:13" x14ac:dyDescent="0.3">
+    <row r="659" spans="2:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="C659" t="s">
         <v>45</v>
       </c>
@@ -25086,7 +25125,7 @@
         <v>1065</v>
       </c>
     </row>
-    <row r="660" spans="2:13" x14ac:dyDescent="0.3">
+    <row r="660" spans="2:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="C660" t="s">
         <v>45</v>
       </c>
@@ -25116,7 +25155,7 @@
         <v>1065</v>
       </c>
     </row>
-    <row r="661" spans="2:13" x14ac:dyDescent="0.3">
+    <row r="661" spans="2:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="B661" t="s">
         <v>593</v>
       </c>
@@ -25149,7 +25188,7 @@
         <v>1073</v>
       </c>
     </row>
-    <row r="662" spans="2:13" x14ac:dyDescent="0.3">
+    <row r="662" spans="2:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="B662" t="s">
         <v>593</v>
       </c>
@@ -25182,7 +25221,7 @@
         <v>1073</v>
       </c>
     </row>
-    <row r="663" spans="2:13" x14ac:dyDescent="0.3">
+    <row r="663" spans="2:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="B663" t="s">
         <v>593</v>
       </c>
@@ -25215,7 +25254,7 @@
         <v>1073</v>
       </c>
     </row>
-    <row r="664" spans="2:13" x14ac:dyDescent="0.3">
+    <row r="664" spans="2:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="B664" t="s">
         <v>593</v>
       </c>
@@ -25251,7 +25290,7 @@
         <v>1073</v>
       </c>
     </row>
-    <row r="665" spans="2:13" x14ac:dyDescent="0.3">
+    <row r="665" spans="2:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="B665" t="s">
         <v>593</v>
       </c>
@@ -25284,7 +25323,7 @@
         <v>1073</v>
       </c>
     </row>
-    <row r="666" spans="2:13" x14ac:dyDescent="0.3">
+    <row r="666" spans="2:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="B666" t="s">
         <v>593</v>
       </c>
@@ -25320,7 +25359,7 @@
         <v>1073</v>
       </c>
     </row>
-    <row r="667" spans="2:13" x14ac:dyDescent="0.3">
+    <row r="667" spans="2:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="B667" t="s">
         <v>593</v>
       </c>
@@ -25356,7 +25395,7 @@
         <v>1073</v>
       </c>
     </row>
-    <row r="668" spans="2:13" x14ac:dyDescent="0.3">
+    <row r="668" spans="2:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="B668" t="s">
         <v>593</v>
       </c>
@@ -25389,7 +25428,7 @@
         <v>1073</v>
       </c>
     </row>
-    <row r="669" spans="2:13" x14ac:dyDescent="0.3">
+    <row r="669" spans="2:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="D669" t="s">
         <v>1084</v>
       </c>
@@ -25416,7 +25455,7 @@
         <v>1086</v>
       </c>
     </row>
-    <row r="670" spans="2:13" x14ac:dyDescent="0.3">
+    <row r="670" spans="2:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="D670" t="s">
         <v>1084</v>
       </c>
@@ -25443,7 +25482,7 @@
         <v>1086</v>
       </c>
     </row>
-    <row r="671" spans="2:13" x14ac:dyDescent="0.3">
+    <row r="671" spans="2:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="D671" t="s">
         <v>1084</v>
       </c>
@@ -25470,7 +25509,7 @@
         <v>1086</v>
       </c>
     </row>
-    <row r="672" spans="2:13" x14ac:dyDescent="0.3">
+    <row r="672" spans="2:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="D672" t="s">
         <v>1084</v>
       </c>
@@ -25497,7 +25536,7 @@
         <v>1086</v>
       </c>
     </row>
-    <row r="673" spans="3:13" x14ac:dyDescent="0.3">
+    <row r="673" spans="3:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="C673" t="s">
         <v>1090</v>
       </c>
@@ -25527,7 +25566,7 @@
         <v>1092</v>
       </c>
     </row>
-    <row r="674" spans="3:13" x14ac:dyDescent="0.3">
+    <row r="674" spans="3:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="C674" t="s">
         <v>1090</v>
       </c>
@@ -25557,7 +25596,7 @@
         <v>1092</v>
       </c>
     </row>
-    <row r="675" spans="3:13" x14ac:dyDescent="0.3">
+    <row r="675" spans="3:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="C675" t="s">
         <v>1090</v>
       </c>
@@ -25587,7 +25626,7 @@
         <v>1092</v>
       </c>
     </row>
-    <row r="676" spans="3:13" x14ac:dyDescent="0.3">
+    <row r="676" spans="3:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="C676" t="s">
         <v>1090</v>
       </c>
@@ -25617,7 +25656,7 @@
         <v>1092</v>
       </c>
     </row>
-    <row r="677" spans="3:13" x14ac:dyDescent="0.3">
+    <row r="677" spans="3:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="C677" t="s">
         <v>1090</v>
       </c>
@@ -25647,7 +25686,7 @@
         <v>1092</v>
       </c>
     </row>
-    <row r="678" spans="3:13" x14ac:dyDescent="0.3">
+    <row r="678" spans="3:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="C678" t="s">
         <v>1090</v>
       </c>
@@ -25677,7 +25716,7 @@
         <v>1092</v>
       </c>
     </row>
-    <row r="679" spans="3:13" x14ac:dyDescent="0.3">
+    <row r="679" spans="3:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="C679" t="s">
         <v>1090</v>
       </c>
@@ -25707,7 +25746,7 @@
         <v>1092</v>
       </c>
     </row>
-    <row r="680" spans="3:13" x14ac:dyDescent="0.3">
+    <row r="680" spans="3:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="C680" t="s">
         <v>1090</v>
       </c>
@@ -25737,7 +25776,7 @@
         <v>1092</v>
       </c>
     </row>
-    <row r="681" spans="3:13" x14ac:dyDescent="0.3">
+    <row r="681" spans="3:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="C681" t="s">
         <v>69</v>
       </c>
@@ -25767,7 +25806,7 @@
         <v>1101</v>
       </c>
     </row>
-    <row r="682" spans="3:13" x14ac:dyDescent="0.3">
+    <row r="682" spans="3:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="C682" t="s">
         <v>69</v>
       </c>
@@ -25797,7 +25836,7 @@
         <v>1101</v>
       </c>
     </row>
-    <row r="683" spans="3:13" x14ac:dyDescent="0.3">
+    <row r="683" spans="3:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="C683" t="s">
         <v>69</v>
       </c>
@@ -25827,7 +25866,7 @@
         <v>1101</v>
       </c>
     </row>
-    <row r="684" spans="3:13" x14ac:dyDescent="0.3">
+    <row r="684" spans="3:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="C684" t="s">
         <v>69</v>
       </c>
@@ -25857,7 +25896,7 @@
         <v>1101</v>
       </c>
     </row>
-    <row r="685" spans="3:13" x14ac:dyDescent="0.3">
+    <row r="685" spans="3:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="C685" t="s">
         <v>69</v>
       </c>
@@ -25887,7 +25926,7 @@
         <v>1101</v>
       </c>
     </row>
-    <row r="686" spans="3:13" x14ac:dyDescent="0.3">
+    <row r="686" spans="3:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="C686" t="s">
         <v>69</v>
       </c>
@@ -25917,7 +25956,7 @@
         <v>1101</v>
       </c>
     </row>
-    <row r="687" spans="3:13" x14ac:dyDescent="0.3">
+    <row r="687" spans="3:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="C687" t="s">
         <v>69</v>
       </c>
@@ -25947,7 +25986,7 @@
         <v>1101</v>
       </c>
     </row>
-    <row r="688" spans="3:13" x14ac:dyDescent="0.3">
+    <row r="688" spans="3:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="C688" t="s">
         <v>69</v>
       </c>
@@ -25977,7 +26016,7 @@
         <v>1101</v>
       </c>
     </row>
-    <row r="689" spans="2:13" x14ac:dyDescent="0.3">
+    <row r="689" spans="2:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="B689" t="s">
         <v>162</v>
       </c>
@@ -26007,7 +26046,7 @@
         <v>1111</v>
       </c>
     </row>
-    <row r="690" spans="2:13" x14ac:dyDescent="0.3">
+    <row r="690" spans="2:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="B690" t="s">
         <v>162</v>
       </c>
@@ -26037,7 +26076,7 @@
         <v>1111</v>
       </c>
     </row>
-    <row r="691" spans="2:13" x14ac:dyDescent="0.3">
+    <row r="691" spans="2:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="B691" t="s">
         <v>162</v>
       </c>
@@ -26067,7 +26106,7 @@
         <v>1111</v>
       </c>
     </row>
-    <row r="692" spans="2:13" x14ac:dyDescent="0.3">
+    <row r="692" spans="2:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="B692" t="s">
         <v>162</v>
       </c>
@@ -26097,7 +26136,7 @@
         <v>1111</v>
       </c>
     </row>
-    <row r="693" spans="2:13" x14ac:dyDescent="0.3">
+    <row r="693" spans="2:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="B693" t="s">
         <v>162</v>
       </c>
@@ -26127,7 +26166,7 @@
         <v>1111</v>
       </c>
     </row>
-    <row r="694" spans="2:13" x14ac:dyDescent="0.3">
+    <row r="694" spans="2:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="B694" t="s">
         <v>162</v>
       </c>
@@ -26157,7 +26196,7 @@
         <v>1111</v>
       </c>
     </row>
-    <row r="695" spans="2:13" x14ac:dyDescent="0.3">
+    <row r="695" spans="2:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="B695" t="s">
         <v>162</v>
       </c>
@@ -26187,7 +26226,7 @@
         <v>1111</v>
       </c>
     </row>
-    <row r="696" spans="2:13" x14ac:dyDescent="0.3">
+    <row r="696" spans="2:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="B696" t="s">
         <v>162</v>
       </c>
@@ -26217,7 +26256,7 @@
         <v>1111</v>
       </c>
     </row>
-    <row r="697" spans="2:13" x14ac:dyDescent="0.3">
+    <row r="697" spans="2:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="B697" t="s">
         <v>162</v>
       </c>
@@ -26247,7 +26286,7 @@
         <v>1111</v>
       </c>
     </row>
-    <row r="698" spans="2:13" x14ac:dyDescent="0.3">
+    <row r="698" spans="2:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="B698" t="s">
         <v>137</v>
       </c>
@@ -26280,7 +26319,7 @@
         <v>1121</v>
       </c>
     </row>
-    <row r="699" spans="2:13" x14ac:dyDescent="0.3">
+    <row r="699" spans="2:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="B699" t="s">
         <v>137</v>
       </c>
@@ -26313,7 +26352,7 @@
         <v>1121</v>
       </c>
     </row>
-    <row r="700" spans="2:13" x14ac:dyDescent="0.3">
+    <row r="700" spans="2:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="B700" t="s">
         <v>137</v>
       </c>
@@ -26346,7 +26385,7 @@
         <v>1121</v>
       </c>
     </row>
-    <row r="701" spans="2:13" x14ac:dyDescent="0.3">
+    <row r="701" spans="2:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="B701" t="s">
         <v>137</v>
       </c>
@@ -26379,7 +26418,7 @@
         <v>1121</v>
       </c>
     </row>
-    <row r="702" spans="2:13" x14ac:dyDescent="0.3">
+    <row r="702" spans="2:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="B702" t="s">
         <v>137</v>
       </c>
@@ -26412,7 +26451,7 @@
         <v>1121</v>
       </c>
     </row>
-    <row r="703" spans="2:13" x14ac:dyDescent="0.3">
+    <row r="703" spans="2:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="B703" t="s">
         <v>137</v>
       </c>
@@ -26445,7 +26484,7 @@
         <v>1121</v>
       </c>
     </row>
-    <row r="704" spans="2:13" x14ac:dyDescent="0.3">
+    <row r="704" spans="2:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="C704" t="s">
         <v>101</v>
       </c>
@@ -26475,7 +26514,7 @@
         <v>1132</v>
       </c>
     </row>
-    <row r="705" spans="2:13" x14ac:dyDescent="0.3">
+    <row r="705" spans="2:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="C705" t="s">
         <v>101</v>
       </c>
@@ -26505,7 +26544,7 @@
         <v>1132</v>
       </c>
     </row>
-    <row r="706" spans="2:13" x14ac:dyDescent="0.3">
+    <row r="706" spans="2:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="C706" t="s">
         <v>101</v>
       </c>
@@ -26535,7 +26574,7 @@
         <v>1132</v>
       </c>
     </row>
-    <row r="707" spans="2:13" x14ac:dyDescent="0.3">
+    <row r="707" spans="2:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="C707" t="s">
         <v>101</v>
       </c>
@@ -26565,7 +26604,7 @@
         <v>1132</v>
       </c>
     </row>
-    <row r="708" spans="2:13" x14ac:dyDescent="0.3">
+    <row r="708" spans="2:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="C708" t="s">
         <v>101</v>
       </c>
@@ -26595,7 +26634,7 @@
         <v>1132</v>
       </c>
     </row>
-    <row r="709" spans="2:13" x14ac:dyDescent="0.3">
+    <row r="709" spans="2:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="C709" t="s">
         <v>101</v>
       </c>
@@ -26625,7 +26664,7 @@
         <v>1132</v>
       </c>
     </row>
-    <row r="710" spans="2:13" x14ac:dyDescent="0.3">
+    <row r="710" spans="2:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="C710" t="s">
         <v>399</v>
       </c>
@@ -26655,7 +26694,7 @@
         <v>1140</v>
       </c>
     </row>
-    <row r="711" spans="2:13" x14ac:dyDescent="0.3">
+    <row r="711" spans="2:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="C711" t="s">
         <v>399</v>
       </c>
@@ -26685,7 +26724,7 @@
         <v>1140</v>
       </c>
     </row>
-    <row r="712" spans="2:13" x14ac:dyDescent="0.3">
+    <row r="712" spans="2:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="B712" t="s">
         <v>162</v>
       </c>
@@ -26715,7 +26754,7 @@
         <v>1144</v>
       </c>
     </row>
-    <row r="713" spans="2:13" x14ac:dyDescent="0.3">
+    <row r="713" spans="2:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="B713" t="s">
         <v>162</v>
       </c>
@@ -26745,7 +26784,7 @@
         <v>1144</v>
       </c>
     </row>
-    <row r="714" spans="2:13" x14ac:dyDescent="0.3">
+    <row r="714" spans="2:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="B714" t="s">
         <v>162</v>
       </c>
@@ -26775,7 +26814,7 @@
         <v>1144</v>
       </c>
     </row>
-    <row r="715" spans="2:13" x14ac:dyDescent="0.3">
+    <row r="715" spans="2:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="B715" t="s">
         <v>162</v>
       </c>
@@ -26805,7 +26844,7 @@
         <v>1144</v>
       </c>
     </row>
-    <row r="716" spans="2:13" x14ac:dyDescent="0.3">
+    <row r="716" spans="2:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="B716" t="s">
         <v>162</v>
       </c>
@@ -26835,7 +26874,7 @@
         <v>1144</v>
       </c>
     </row>
-    <row r="717" spans="2:13" x14ac:dyDescent="0.3">
+    <row r="717" spans="2:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="B717" t="s">
         <v>162</v>
       </c>
@@ -26865,7 +26904,7 @@
         <v>1144</v>
       </c>
     </row>
-    <row r="718" spans="2:13" x14ac:dyDescent="0.3">
+    <row r="718" spans="2:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="B718" t="s">
         <v>162</v>
       </c>
@@ -26895,7 +26934,7 @@
         <v>1144</v>
       </c>
     </row>
-    <row r="719" spans="2:13" x14ac:dyDescent="0.3">
+    <row r="719" spans="2:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="B719" t="s">
         <v>162</v>
       </c>
@@ -26925,7 +26964,7 @@
         <v>1144</v>
       </c>
     </row>
-    <row r="720" spans="2:13" x14ac:dyDescent="0.3">
+    <row r="720" spans="2:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="B720" t="s">
         <v>162</v>
       </c>
@@ -26955,7 +26994,7 @@
         <v>1144</v>
       </c>
     </row>
-    <row r="721" spans="2:13" x14ac:dyDescent="0.3">
+    <row r="721" spans="2:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="C721" t="s">
         <v>129</v>
       </c>
@@ -26985,7 +27024,7 @@
         <v>1154</v>
       </c>
     </row>
-    <row r="722" spans="2:13" x14ac:dyDescent="0.3">
+    <row r="722" spans="2:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="C722" t="s">
         <v>129</v>
       </c>
@@ -27015,7 +27054,7 @@
         <v>1154</v>
       </c>
     </row>
-    <row r="723" spans="2:13" x14ac:dyDescent="0.3">
+    <row r="723" spans="2:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="C723" t="s">
         <v>129</v>
       </c>
@@ -27045,7 +27084,7 @@
         <v>1154</v>
       </c>
     </row>
-    <row r="724" spans="2:13" x14ac:dyDescent="0.3">
+    <row r="724" spans="2:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="C724" t="s">
         <v>129</v>
       </c>
@@ -27075,7 +27114,7 @@
         <v>1154</v>
       </c>
     </row>
-    <row r="725" spans="2:13" x14ac:dyDescent="0.3">
+    <row r="725" spans="2:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="C725" t="s">
         <v>129</v>
       </c>
@@ -27105,7 +27144,7 @@
         <v>1154</v>
       </c>
     </row>
-    <row r="726" spans="2:13" x14ac:dyDescent="0.3">
+    <row r="726" spans="2:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="C726" t="s">
         <v>129</v>
       </c>
@@ -27135,7 +27174,7 @@
         <v>1154</v>
       </c>
     </row>
-    <row r="727" spans="2:13" x14ac:dyDescent="0.3">
+    <row r="727" spans="2:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="C727" t="s">
         <v>129</v>
       </c>
@@ -27165,7 +27204,7 @@
         <v>1154</v>
       </c>
     </row>
-    <row r="728" spans="2:13" x14ac:dyDescent="0.3">
+    <row r="728" spans="2:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="C728" t="s">
         <v>129</v>
       </c>
@@ -27195,7 +27234,7 @@
         <v>1154</v>
       </c>
     </row>
-    <row r="729" spans="2:13" x14ac:dyDescent="0.3">
+    <row r="729" spans="2:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="B729" t="s">
         <v>137</v>
       </c>
@@ -27225,7 +27264,7 @@
         <v>1163</v>
       </c>
     </row>
-    <row r="730" spans="2:13" x14ac:dyDescent="0.3">
+    <row r="730" spans="2:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="B730" t="s">
         <v>137</v>
       </c>
@@ -27255,7 +27294,7 @@
         <v>1163</v>
       </c>
     </row>
-    <row r="731" spans="2:13" x14ac:dyDescent="0.3">
+    <row r="731" spans="2:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="B731" t="s">
         <v>137</v>
       </c>
@@ -27285,7 +27324,7 @@
         <v>1163</v>
       </c>
     </row>
-    <row r="732" spans="2:13" x14ac:dyDescent="0.3">
+    <row r="732" spans="2:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="B732" t="s">
         <v>137</v>
       </c>
@@ -27312,7 +27351,7 @@
         <v>1171</v>
       </c>
     </row>
-    <row r="733" spans="2:13" x14ac:dyDescent="0.3">
+    <row r="733" spans="2:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="B733" t="s">
         <v>137</v>
       </c>
@@ -27339,7 +27378,7 @@
         <v>1171</v>
       </c>
     </row>
-    <row r="734" spans="2:13" x14ac:dyDescent="0.3">
+    <row r="734" spans="2:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="C734" t="s">
         <v>150</v>
       </c>
@@ -27369,7 +27408,7 @@
         <v>1175</v>
       </c>
     </row>
-    <row r="735" spans="2:13" x14ac:dyDescent="0.3">
+    <row r="735" spans="2:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="C735" t="s">
         <v>150</v>
       </c>
@@ -27399,7 +27438,7 @@
         <v>1175</v>
       </c>
     </row>
-    <row r="736" spans="2:13" x14ac:dyDescent="0.3">
+    <row r="736" spans="2:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="C736" t="s">
         <v>150</v>
       </c>
@@ -27429,7 +27468,7 @@
         <v>1175</v>
       </c>
     </row>
-    <row r="737" spans="2:13" x14ac:dyDescent="0.3">
+    <row r="737" spans="2:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="C737" t="s">
         <v>150</v>
       </c>
@@ -27459,7 +27498,7 @@
         <v>1175</v>
       </c>
     </row>
-    <row r="738" spans="2:13" x14ac:dyDescent="0.3">
+    <row r="738" spans="2:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="C738" t="s">
         <v>303</v>
       </c>
@@ -27489,7 +27528,7 @@
         <v>1181</v>
       </c>
     </row>
-    <row r="739" spans="2:13" x14ac:dyDescent="0.3">
+    <row r="739" spans="2:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="C739" t="s">
         <v>303</v>
       </c>
@@ -27519,7 +27558,7 @@
         <v>1181</v>
       </c>
     </row>
-    <row r="740" spans="2:13" x14ac:dyDescent="0.3">
+    <row r="740" spans="2:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="C740" t="s">
         <v>303</v>
       </c>
@@ -27549,7 +27588,7 @@
         <v>1181</v>
       </c>
     </row>
-    <row r="741" spans="2:13" x14ac:dyDescent="0.3">
+    <row r="741" spans="2:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="C741" t="s">
         <v>303</v>
       </c>
@@ -27579,7 +27618,7 @@
         <v>1181</v>
       </c>
     </row>
-    <row r="742" spans="2:13" x14ac:dyDescent="0.3">
+    <row r="742" spans="2:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="C742" t="s">
         <v>635</v>
       </c>
@@ -27609,7 +27648,7 @@
         <v>1189</v>
       </c>
     </row>
-    <row r="743" spans="2:13" x14ac:dyDescent="0.3">
+    <row r="743" spans="2:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="C743" t="s">
         <v>635</v>
       </c>
@@ -27639,7 +27678,7 @@
         <v>1189</v>
       </c>
     </row>
-    <row r="744" spans="2:13" x14ac:dyDescent="0.3">
+    <row r="744" spans="2:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="C744" t="s">
         <v>635</v>
       </c>
@@ -27669,7 +27708,7 @@
         <v>1189</v>
       </c>
     </row>
-    <row r="745" spans="2:13" x14ac:dyDescent="0.3">
+    <row r="745" spans="2:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="C745" t="s">
         <v>635</v>
       </c>
@@ -27699,7 +27738,7 @@
         <v>1189</v>
       </c>
     </row>
-    <row r="746" spans="2:13" x14ac:dyDescent="0.3">
+    <row r="746" spans="2:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="B746" t="s">
         <v>593</v>
       </c>
@@ -27728,7 +27767,7 @@
         <v>1189</v>
       </c>
     </row>
-    <row r="747" spans="2:13" x14ac:dyDescent="0.3">
+    <row r="747" spans="2:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="B747" t="s">
         <v>593</v>
       </c>
@@ -27760,7 +27799,7 @@
         <v>1189</v>
       </c>
     </row>
-    <row r="748" spans="2:13" x14ac:dyDescent="0.3">
+    <row r="748" spans="2:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="B748" t="s">
         <v>593</v>
       </c>
@@ -27792,7 +27831,7 @@
         <v>1189</v>
       </c>
     </row>
-    <row r="749" spans="2:13" x14ac:dyDescent="0.3">
+    <row r="749" spans="2:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="B749" t="s">
         <v>593</v>
       </c>
@@ -27824,7 +27863,7 @@
         <v>1189</v>
       </c>
     </row>
-    <row r="750" spans="2:13" x14ac:dyDescent="0.3">
+    <row r="750" spans="2:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="C750" t="s">
         <v>1203</v>
       </c>
@@ -27853,7 +27892,7 @@
         <v>1206</v>
       </c>
     </row>
-    <row r="751" spans="2:13" x14ac:dyDescent="0.3">
+    <row r="751" spans="2:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="C751" t="s">
         <v>1203</v>
       </c>
@@ -27882,7 +27921,7 @@
         <v>1206</v>
       </c>
     </row>
-    <row r="752" spans="2:13" x14ac:dyDescent="0.3">
+    <row r="752" spans="2:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="C752" t="s">
         <v>1203</v>
       </c>
@@ -27911,7 +27950,7 @@
         <v>1206</v>
       </c>
     </row>
-    <row r="753" spans="2:13" x14ac:dyDescent="0.3">
+    <row r="753" spans="2:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="C753" t="s">
         <v>1203</v>
       </c>
@@ -27940,7 +27979,7 @@
         <v>1206</v>
       </c>
     </row>
-    <row r="754" spans="2:13" x14ac:dyDescent="0.3">
+    <row r="754" spans="2:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="C754" t="s">
         <v>1203</v>
       </c>
@@ -27969,7 +28008,7 @@
         <v>1206</v>
       </c>
     </row>
-    <row r="755" spans="2:13" x14ac:dyDescent="0.3">
+    <row r="755" spans="2:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="C755" t="s">
         <v>1203</v>
       </c>
@@ -27998,7 +28037,7 @@
         <v>1206</v>
       </c>
     </row>
-    <row r="756" spans="2:13" x14ac:dyDescent="0.3">
+    <row r="756" spans="2:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="C756" t="s">
         <v>154</v>
       </c>
@@ -28027,7 +28066,7 @@
         <v>1216</v>
       </c>
     </row>
-    <row r="757" spans="2:13" x14ac:dyDescent="0.3">
+    <row r="757" spans="2:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="C757" t="s">
         <v>154</v>
       </c>
@@ -28056,7 +28095,7 @@
         <v>1216</v>
       </c>
     </row>
-    <row r="758" spans="2:13" x14ac:dyDescent="0.3">
+    <row r="758" spans="2:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="C758" t="s">
         <v>154</v>
       </c>
@@ -28085,7 +28124,7 @@
         <v>1216</v>
       </c>
     </row>
-    <row r="759" spans="2:13" x14ac:dyDescent="0.3">
+    <row r="759" spans="2:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="C759" t="s">
         <v>154</v>
       </c>
@@ -28114,7 +28153,7 @@
         <v>1216</v>
       </c>
     </row>
-    <row r="760" spans="2:13" x14ac:dyDescent="0.3">
+    <row r="760" spans="2:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="B760" t="s">
         <v>137</v>
       </c>
@@ -28143,7 +28182,7 @@
         <v>1223</v>
       </c>
     </row>
-    <row r="761" spans="2:13" x14ac:dyDescent="0.3">
+    <row r="761" spans="2:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="B761" t="s">
         <v>137</v>
       </c>
@@ -28172,7 +28211,7 @@
         <v>1223</v>
       </c>
     </row>
-    <row r="762" spans="2:13" x14ac:dyDescent="0.3">
+    <row r="762" spans="2:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="B762" t="s">
         <v>137</v>
       </c>
@@ -28201,7 +28240,7 @@
         <v>1223</v>
       </c>
     </row>
-    <row r="763" spans="2:13" x14ac:dyDescent="0.3">
+    <row r="763" spans="2:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="B763" t="s">
         <v>137</v>
       </c>
@@ -28230,7 +28269,7 @@
         <v>1223</v>
       </c>
     </row>
-    <row r="764" spans="2:13" x14ac:dyDescent="0.3">
+    <row r="764" spans="2:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="C764" t="s">
         <v>27</v>
       </c>
@@ -28259,7 +28298,7 @@
         <v>1232</v>
       </c>
     </row>
-    <row r="765" spans="2:13" x14ac:dyDescent="0.3">
+    <row r="765" spans="2:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="C765" t="s">
         <v>27</v>
       </c>
@@ -28288,7 +28327,7 @@
         <v>1232</v>
       </c>
     </row>
-    <row r="766" spans="2:13" x14ac:dyDescent="0.3">
+    <row r="766" spans="2:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="C766" t="s">
         <v>27</v>
       </c>
@@ -28317,7 +28356,7 @@
         <v>1232</v>
       </c>
     </row>
-    <row r="767" spans="2:13" x14ac:dyDescent="0.3">
+    <row r="767" spans="2:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="C767" t="s">
         <v>27</v>
       </c>
@@ -28346,7 +28385,7 @@
         <v>1232</v>
       </c>
     </row>
-    <row r="768" spans="2:13" x14ac:dyDescent="0.3">
+    <row r="768" spans="2:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="C768" t="s">
         <v>45</v>
       </c>
@@ -28375,7 +28414,7 @@
         <v>1239</v>
       </c>
     </row>
-    <row r="769" spans="3:13" x14ac:dyDescent="0.3">
+    <row r="769" spans="3:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="C769" t="s">
         <v>45</v>
       </c>
@@ -28404,7 +28443,7 @@
         <v>1239</v>
       </c>
     </row>
-    <row r="770" spans="3:13" x14ac:dyDescent="0.3">
+    <row r="770" spans="3:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="C770" t="s">
         <v>45</v>
       </c>
@@ -28433,7 +28472,7 @@
         <v>1239</v>
       </c>
     </row>
-    <row r="771" spans="3:13" x14ac:dyDescent="0.3">
+    <row r="771" spans="3:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="C771" t="s">
         <v>45</v>
       </c>
@@ -28462,7 +28501,7 @@
         <v>1239</v>
       </c>
     </row>
-    <row r="772" spans="3:13" x14ac:dyDescent="0.3">
+    <row r="772" spans="3:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="C772" t="s">
         <v>635</v>
       </c>
@@ -28491,7 +28530,7 @@
         <v>1245</v>
       </c>
     </row>
-    <row r="773" spans="3:13" x14ac:dyDescent="0.3">
+    <row r="773" spans="3:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="C773" t="s">
         <v>635</v>
       </c>
@@ -28520,7 +28559,7 @@
         <v>1245</v>
       </c>
     </row>
-    <row r="774" spans="3:13" x14ac:dyDescent="0.3">
+    <row r="774" spans="3:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="C774" t="s">
         <v>635</v>
       </c>
@@ -28549,7 +28588,7 @@
         <v>1245</v>
       </c>
     </row>
-    <row r="775" spans="3:13" x14ac:dyDescent="0.3">
+    <row r="775" spans="3:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="C775" t="s">
         <v>635</v>
       </c>
@@ -28578,7 +28617,7 @@
         <v>1245</v>
       </c>
     </row>
-    <row r="776" spans="3:13" x14ac:dyDescent="0.3">
+    <row r="776" spans="3:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="C776" t="s">
         <v>90</v>
       </c>
@@ -28607,7 +28646,7 @@
         <v>1250</v>
       </c>
     </row>
-    <row r="777" spans="3:13" x14ac:dyDescent="0.3">
+    <row r="777" spans="3:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="C777" t="s">
         <v>90</v>
       </c>
@@ -28636,7 +28675,7 @@
         <v>1250</v>
       </c>
     </row>
-    <row r="778" spans="3:13" x14ac:dyDescent="0.3">
+    <row r="778" spans="3:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="C778" t="s">
         <v>90</v>
       </c>
@@ -28665,7 +28704,7 @@
         <v>1250</v>
       </c>
     </row>
-    <row r="779" spans="3:13" x14ac:dyDescent="0.3">
+    <row r="779" spans="3:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="C779" t="s">
         <v>90</v>
       </c>
@@ -28694,7 +28733,7 @@
         <v>1250</v>
       </c>
     </row>
-    <row r="780" spans="3:13" x14ac:dyDescent="0.3">
+    <row r="780" spans="3:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="C780" t="s">
         <v>90</v>
       </c>
@@ -28723,7 +28762,7 @@
         <v>1250</v>
       </c>
     </row>
-    <row r="781" spans="3:13" x14ac:dyDescent="0.3">
+    <row r="781" spans="3:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="C781" t="s">
         <v>90</v>
       </c>
@@ -28752,7 +28791,7 @@
         <v>1250</v>
       </c>
     </row>
-    <row r="782" spans="3:13" x14ac:dyDescent="0.3">
+    <row r="782" spans="3:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="C782" t="s">
         <v>90</v>
       </c>
@@ -28781,7 +28820,7 @@
         <v>1250</v>
       </c>
     </row>
-    <row r="783" spans="3:13" x14ac:dyDescent="0.3">
+    <row r="783" spans="3:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="C783" t="s">
         <v>90</v>
       </c>
@@ -28810,7 +28849,7 @@
         <v>1250</v>
       </c>
     </row>
-    <row r="784" spans="3:13" x14ac:dyDescent="0.3">
+    <row r="784" spans="3:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="C784" t="s">
         <v>69</v>
       </c>
@@ -28839,7 +28878,7 @@
         <v>1260</v>
       </c>
     </row>
-    <row r="785" spans="2:13" x14ac:dyDescent="0.3">
+    <row r="785" spans="2:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="C785" t="s">
         <v>69</v>
       </c>
@@ -28868,7 +28907,7 @@
         <v>1260</v>
       </c>
     </row>
-    <row r="786" spans="2:13" x14ac:dyDescent="0.3">
+    <row r="786" spans="2:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="C786" t="s">
         <v>69</v>
       </c>
@@ -28897,7 +28936,7 @@
         <v>1260</v>
       </c>
     </row>
-    <row r="787" spans="2:13" x14ac:dyDescent="0.3">
+    <row r="787" spans="2:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="C787" t="s">
         <v>69</v>
       </c>
@@ -28926,7 +28965,7 @@
         <v>1260</v>
       </c>
     </row>
-    <row r="788" spans="2:13" x14ac:dyDescent="0.3">
+    <row r="788" spans="2:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="C788" t="s">
         <v>69</v>
       </c>
@@ -28955,7 +28994,7 @@
         <v>1260</v>
       </c>
     </row>
-    <row r="789" spans="2:13" x14ac:dyDescent="0.3">
+    <row r="789" spans="2:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="C789" t="s">
         <v>69</v>
       </c>
@@ -28984,7 +29023,7 @@
         <v>1260</v>
       </c>
     </row>
-    <row r="790" spans="2:13" x14ac:dyDescent="0.3">
+    <row r="790" spans="2:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="C790" t="s">
         <v>69</v>
       </c>
@@ -29013,7 +29052,7 @@
         <v>1260</v>
       </c>
     </row>
-    <row r="791" spans="2:13" x14ac:dyDescent="0.3">
+    <row r="791" spans="2:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="C791" t="s">
         <v>372</v>
       </c>
@@ -29042,7 +29081,7 @@
         <v>1269</v>
       </c>
     </row>
-    <row r="792" spans="2:13" x14ac:dyDescent="0.3">
+    <row r="792" spans="2:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="C792" t="s">
         <v>372</v>
       </c>
@@ -29071,7 +29110,7 @@
         <v>1269</v>
       </c>
     </row>
-    <row r="793" spans="2:13" x14ac:dyDescent="0.3">
+    <row r="793" spans="2:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="C793" t="s">
         <v>372</v>
       </c>
@@ -29100,7 +29139,7 @@
         <v>1269</v>
       </c>
     </row>
-    <row r="794" spans="2:13" x14ac:dyDescent="0.3">
+    <row r="794" spans="2:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="C794" t="s">
         <v>372</v>
       </c>
@@ -29129,7 +29168,7 @@
         <v>1269</v>
       </c>
     </row>
-    <row r="795" spans="2:13" x14ac:dyDescent="0.3">
+    <row r="795" spans="2:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="C795" t="s">
         <v>1273</v>
       </c>
@@ -29158,7 +29197,7 @@
         <v>1276</v>
       </c>
     </row>
-    <row r="796" spans="2:13" x14ac:dyDescent="0.3">
+    <row r="796" spans="2:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="C796" t="s">
         <v>1273</v>
       </c>
@@ -29187,7 +29226,7 @@
         <v>1276</v>
       </c>
     </row>
-    <row r="797" spans="2:13" x14ac:dyDescent="0.3">
+    <row r="797" spans="2:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="B797" t="s">
         <v>162</v>
       </c>
@@ -29216,7 +29255,7 @@
         <v>1279</v>
       </c>
     </row>
-    <row r="798" spans="2:13" x14ac:dyDescent="0.3">
+    <row r="798" spans="2:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="B798" t="s">
         <v>162</v>
       </c>
@@ -29245,7 +29284,7 @@
         <v>1279</v>
       </c>
     </row>
-    <row r="799" spans="2:13" x14ac:dyDescent="0.3">
+    <row r="799" spans="2:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="B799" t="s">
         <v>162</v>
       </c>
@@ -29274,7 +29313,7 @@
         <v>1279</v>
       </c>
     </row>
-    <row r="800" spans="2:13" x14ac:dyDescent="0.3">
+    <row r="800" spans="2:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="B800" t="s">
         <v>162</v>
       </c>
@@ -29303,7 +29342,7 @@
         <v>1279</v>
       </c>
     </row>
-    <row r="801" spans="2:13" x14ac:dyDescent="0.3">
+    <row r="801" spans="2:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="B801" t="s">
         <v>162</v>
       </c>
@@ -29332,7 +29371,7 @@
         <v>1279</v>
       </c>
     </row>
-    <row r="802" spans="2:13" x14ac:dyDescent="0.3">
+    <row r="802" spans="2:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="B802" t="s">
         <v>162</v>
       </c>
@@ -29361,7 +29400,7 @@
         <v>1279</v>
       </c>
     </row>
-    <row r="803" spans="2:13" x14ac:dyDescent="0.3">
+    <row r="803" spans="2:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="B803" t="s">
         <v>137</v>
       </c>
@@ -29390,7 +29429,7 @@
         <v>1287</v>
       </c>
     </row>
-    <row r="804" spans="2:13" x14ac:dyDescent="0.3">
+    <row r="804" spans="2:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="B804" t="s">
         <v>137</v>
       </c>
@@ -29419,7 +29458,7 @@
         <v>1287</v>
       </c>
     </row>
-    <row r="805" spans="2:13" x14ac:dyDescent="0.3">
+    <row r="805" spans="2:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="B805" t="s">
         <v>137</v>
       </c>
@@ -29446,7 +29485,7 @@
         <v>1287</v>
       </c>
     </row>
-    <row r="806" spans="2:13" x14ac:dyDescent="0.3">
+    <row r="806" spans="2:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="C806" t="s">
         <v>101</v>
       </c>
@@ -29475,7 +29514,7 @@
         <v>1294</v>
       </c>
     </row>
-    <row r="807" spans="2:13" x14ac:dyDescent="0.3">
+    <row r="807" spans="2:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="C807" t="s">
         <v>101</v>
       </c>
@@ -29504,7 +29543,7 @@
         <v>1294</v>
       </c>
     </row>
-    <row r="808" spans="2:13" x14ac:dyDescent="0.3">
+    <row r="808" spans="2:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="C808" t="s">
         <v>101</v>
       </c>
@@ -29533,7 +29572,7 @@
         <v>1294</v>
       </c>
     </row>
-    <row r="809" spans="2:13" x14ac:dyDescent="0.3">
+    <row r="809" spans="2:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="C809" t="s">
         <v>101</v>
       </c>
@@ -29562,7 +29601,7 @@
         <v>1294</v>
       </c>
     </row>
-    <row r="810" spans="2:13" x14ac:dyDescent="0.3">
+    <row r="810" spans="2:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="C810" t="s">
         <v>101</v>
       </c>
@@ -29591,7 +29630,7 @@
         <v>1294</v>
       </c>
     </row>
-    <row r="811" spans="2:13" x14ac:dyDescent="0.3">
+    <row r="811" spans="2:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="C811" t="s">
         <v>101</v>
       </c>
@@ -29620,7 +29659,7 @@
         <v>1294</v>
       </c>
     </row>
-    <row r="812" spans="2:13" x14ac:dyDescent="0.3">
+    <row r="812" spans="2:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="C812" t="s">
         <v>399</v>
       </c>
@@ -29649,7 +29688,7 @@
         <v>1303</v>
       </c>
     </row>
-    <row r="813" spans="2:13" x14ac:dyDescent="0.3">
+    <row r="813" spans="2:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="C813" t="s">
         <v>399</v>
       </c>
@@ -29678,7 +29717,7 @@
         <v>1303</v>
       </c>
     </row>
-    <row r="814" spans="2:13" x14ac:dyDescent="0.3">
+    <row r="814" spans="2:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="C814" t="s">
         <v>180</v>
       </c>
@@ -29704,7 +29743,7 @@
         <v>1307</v>
       </c>
     </row>
-    <row r="815" spans="2:13" x14ac:dyDescent="0.3">
+    <row r="815" spans="2:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="C815" t="s">
         <v>180</v>
       </c>
@@ -29730,7 +29769,7 @@
         <v>1307</v>
       </c>
     </row>
-    <row r="816" spans="2:13" x14ac:dyDescent="0.3">
+    <row r="816" spans="2:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="C816" t="s">
         <v>180</v>
       </c>
@@ -29756,7 +29795,7 @@
         <v>1307</v>
       </c>
     </row>
-    <row r="817" spans="3:13" x14ac:dyDescent="0.3">
+    <row r="817" spans="3:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="C817" t="s">
         <v>180</v>
       </c>
@@ -29782,7 +29821,7 @@
         <v>1307</v>
       </c>
     </row>
-    <row r="818" spans="3:13" x14ac:dyDescent="0.3">
+    <row r="818" spans="3:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="C818" t="s">
         <v>180</v>
       </c>
@@ -29808,7 +29847,7 @@
         <v>1307</v>
       </c>
     </row>
-    <row r="819" spans="3:13" x14ac:dyDescent="0.3">
+    <row r="819" spans="3:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="C819" t="s">
         <v>180</v>
       </c>
@@ -29834,7 +29873,7 @@
         <v>1307</v>
       </c>
     </row>
-    <row r="820" spans="3:13" x14ac:dyDescent="0.3">
+    <row r="820" spans="3:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="C820" t="s">
         <v>129</v>
       </c>
@@ -29863,7 +29902,7 @@
         <v>1315</v>
       </c>
     </row>
-    <row r="821" spans="3:13" x14ac:dyDescent="0.3">
+    <row r="821" spans="3:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="C821" t="s">
         <v>129</v>
       </c>
@@ -29892,7 +29931,7 @@
         <v>1315</v>
       </c>
     </row>
-    <row r="822" spans="3:13" x14ac:dyDescent="0.3">
+    <row r="822" spans="3:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="C822" t="s">
         <v>129</v>
       </c>
@@ -29921,7 +29960,7 @@
         <v>1315</v>
       </c>
     </row>
-    <row r="823" spans="3:13" x14ac:dyDescent="0.3">
+    <row r="823" spans="3:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="C823" t="s">
         <v>129</v>
       </c>
@@ -29950,7 +29989,7 @@
         <v>1315</v>
       </c>
     </row>
-    <row r="824" spans="3:13" x14ac:dyDescent="0.3">
+    <row r="824" spans="3:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="C824" t="s">
         <v>129</v>
       </c>
@@ -29979,7 +30018,7 @@
         <v>1315</v>
       </c>
     </row>
-    <row r="825" spans="3:13" x14ac:dyDescent="0.3">
+    <row r="825" spans="3:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="C825" t="s">
         <v>129</v>
       </c>
@@ -30008,7 +30047,7 @@
         <v>1315</v>
       </c>
     </row>
-    <row r="826" spans="3:13" x14ac:dyDescent="0.3">
+    <row r="826" spans="3:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="C826" t="s">
         <v>129</v>
       </c>
@@ -30037,7 +30076,7 @@
         <v>1315</v>
       </c>
     </row>
-    <row r="827" spans="3:13" x14ac:dyDescent="0.3">
+    <row r="827" spans="3:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="C827" t="s">
         <v>129</v>
       </c>
@@ -30066,7 +30105,7 @@
         <v>1315</v>
       </c>
     </row>
-    <row r="828" spans="3:13" x14ac:dyDescent="0.3">
+    <row r="828" spans="3:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="C828" t="s">
         <v>150</v>
       </c>
@@ -30095,7 +30134,7 @@
         <v>1324</v>
       </c>
     </row>
-    <row r="829" spans="3:13" x14ac:dyDescent="0.3">
+    <row r="829" spans="3:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="C829" t="s">
         <v>150</v>
       </c>
@@ -30124,7 +30163,7 @@
         <v>1324</v>
       </c>
     </row>
-    <row r="830" spans="3:13" x14ac:dyDescent="0.3">
+    <row r="830" spans="3:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="C830" t="s">
         <v>150</v>
       </c>
@@ -30153,7 +30192,7 @@
         <v>1324</v>
       </c>
     </row>
-    <row r="831" spans="3:13" x14ac:dyDescent="0.3">
+    <row r="831" spans="3:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="C831" t="s">
         <v>150</v>
       </c>
@@ -30182,7 +30221,7 @@
         <v>1324</v>
       </c>
     </row>
-    <row r="832" spans="3:13" x14ac:dyDescent="0.3">
+    <row r="832" spans="3:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="C832" t="s">
         <v>150</v>
       </c>
@@ -30211,7 +30250,7 @@
         <v>1324</v>
       </c>
     </row>
-    <row r="833" spans="3:13" x14ac:dyDescent="0.3">
+    <row r="833" spans="3:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="C833" t="s">
         <v>150</v>
       </c>
@@ -30240,7 +30279,7 @@
         <v>1324</v>
       </c>
     </row>
-    <row r="834" spans="3:13" x14ac:dyDescent="0.3">
+    <row r="834" spans="3:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="C834" t="s">
         <v>150</v>
       </c>
@@ -30269,7 +30308,7 @@
         <v>1324</v>
       </c>
     </row>
-    <row r="835" spans="3:13" x14ac:dyDescent="0.3">
+    <row r="835" spans="3:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="C835" t="s">
         <v>150</v>
       </c>
@@ -30298,7 +30337,7 @@
         <v>1324</v>
       </c>
     </row>
-    <row r="836" spans="3:13" x14ac:dyDescent="0.3">
+    <row r="836" spans="3:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="C836" t="s">
         <v>303</v>
       </c>
@@ -30327,7 +30366,7 @@
         <v>1335</v>
       </c>
     </row>
-    <row r="837" spans="3:13" x14ac:dyDescent="0.3">
+    <row r="837" spans="3:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="C837" t="s">
         <v>303</v>
       </c>
@@ -30356,7 +30395,7 @@
         <v>1335</v>
       </c>
     </row>
-    <row r="838" spans="3:13" x14ac:dyDescent="0.3">
+    <row r="838" spans="3:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="C838" t="s">
         <v>303</v>
       </c>
@@ -30385,7 +30424,7 @@
         <v>1335</v>
       </c>
     </row>
-    <row r="839" spans="3:13" x14ac:dyDescent="0.3">
+    <row r="839" spans="3:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="C839" t="s">
         <v>303</v>
       </c>
@@ -30414,7 +30453,7 @@
         <v>1335</v>
       </c>
     </row>
-    <row r="840" spans="3:13" x14ac:dyDescent="0.3">
+    <row r="840" spans="3:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="C840" t="s">
         <v>303</v>
       </c>
@@ -30443,7 +30482,7 @@
         <v>1335</v>
       </c>
     </row>
-    <row r="841" spans="3:13" x14ac:dyDescent="0.3">
+    <row r="841" spans="3:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="D841" t="s">
         <v>1342</v>
       </c>
@@ -30466,7 +30505,7 @@
         <v>1345</v>
       </c>
     </row>
-    <row r="842" spans="3:13" x14ac:dyDescent="0.3">
+    <row r="842" spans="3:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="D842" t="s">
         <v>1342</v>
       </c>
@@ -30489,7 +30528,7 @@
         <v>1345</v>
       </c>
     </row>
-    <row r="843" spans="3:13" x14ac:dyDescent="0.3">
+    <row r="843" spans="3:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="D843" t="s">
         <v>1342</v>
       </c>
@@ -30512,7 +30551,7 @@
         <v>1345</v>
       </c>
     </row>
-    <row r="844" spans="3:13" x14ac:dyDescent="0.3">
+    <row r="844" spans="3:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="D844" t="s">
         <v>1342</v>
       </c>
@@ -30535,7 +30574,7 @@
         <v>1345</v>
       </c>
     </row>
-    <row r="845" spans="3:13" x14ac:dyDescent="0.3">
+    <row r="845" spans="3:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="D845" t="s">
         <v>1342</v>
       </c>
@@ -30558,7 +30597,7 @@
         <v>1345</v>
       </c>
     </row>
-    <row r="846" spans="3:13" x14ac:dyDescent="0.3">
+    <row r="846" spans="3:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="D846" t="s">
         <v>1342</v>
       </c>
@@ -30581,7 +30620,7 @@
         <v>1345</v>
       </c>
     </row>
-    <row r="847" spans="3:13" x14ac:dyDescent="0.3">
+    <row r="847" spans="3:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="C847" t="s">
         <v>154</v>
       </c>
@@ -30610,7 +30649,7 @@
         <v>1352</v>
       </c>
     </row>
-    <row r="848" spans="3:13" x14ac:dyDescent="0.3">
+    <row r="848" spans="3:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="C848" t="s">
         <v>154</v>
       </c>
@@ -30639,7 +30678,7 @@
         <v>1352</v>
       </c>
     </row>
-    <row r="849" spans="2:13" x14ac:dyDescent="0.3">
+    <row r="849" spans="2:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="C849" t="s">
         <v>154</v>
       </c>
@@ -30668,7 +30707,7 @@
         <v>1352</v>
       </c>
     </row>
-    <row r="850" spans="2:13" x14ac:dyDescent="0.3">
+    <row r="850" spans="2:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="C850" t="s">
         <v>154</v>
       </c>
@@ -30697,7 +30736,7 @@
         <v>1352</v>
       </c>
     </row>
-    <row r="851" spans="2:13" x14ac:dyDescent="0.3">
+    <row r="851" spans="2:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="B851" t="s">
         <v>137</v>
       </c>
@@ -30726,7 +30765,7 @@
         <v>1359</v>
       </c>
     </row>
-    <row r="852" spans="2:13" x14ac:dyDescent="0.3">
+    <row r="852" spans="2:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="B852" t="s">
         <v>137</v>
       </c>
@@ -30755,7 +30794,7 @@
         <v>1359</v>
       </c>
     </row>
-    <row r="853" spans="2:13" x14ac:dyDescent="0.3">
+    <row r="853" spans="2:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="C853" t="s">
         <v>27</v>
       </c>
@@ -30784,7 +30823,7 @@
         <v>1364</v>
       </c>
     </row>
-    <row r="854" spans="2:13" x14ac:dyDescent="0.3">
+    <row r="854" spans="2:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="C854" t="s">
         <v>27</v>
       </c>
@@ -30813,7 +30852,7 @@
         <v>1364</v>
       </c>
     </row>
-    <row r="855" spans="2:13" x14ac:dyDescent="0.3">
+    <row r="855" spans="2:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="C855" t="s">
         <v>27</v>
       </c>
@@ -30842,7 +30881,7 @@
         <v>1364</v>
       </c>
     </row>
-    <row r="856" spans="2:13" x14ac:dyDescent="0.3">
+    <row r="856" spans="2:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="C856" t="s">
         <v>27</v>
       </c>
@@ -30871,7 +30910,7 @@
         <v>1364</v>
       </c>
     </row>
-    <row r="857" spans="2:13" x14ac:dyDescent="0.3">
+    <row r="857" spans="2:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="C857" t="s">
         <v>45</v>
       </c>
@@ -30900,7 +30939,7 @@
         <v>1370</v>
       </c>
     </row>
-    <row r="858" spans="2:13" x14ac:dyDescent="0.3">
+    <row r="858" spans="2:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="C858" t="s">
         <v>45</v>
       </c>
@@ -30929,7 +30968,7 @@
         <v>1370</v>
       </c>
     </row>
-    <row r="859" spans="2:13" x14ac:dyDescent="0.3">
+    <row r="859" spans="2:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="C859" t="s">
         <v>45</v>
       </c>
@@ -30958,7 +30997,7 @@
         <v>1370</v>
       </c>
     </row>
-    <row r="860" spans="2:13" x14ac:dyDescent="0.3">
+    <row r="860" spans="2:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="C860" t="s">
         <v>45</v>
       </c>
@@ -30987,7 +31026,7 @@
         <v>1370</v>
       </c>
     </row>
-    <row r="861" spans="2:13" x14ac:dyDescent="0.3">
+    <row r="861" spans="2:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="C861" t="s">
         <v>1374</v>
       </c>
@@ -31013,7 +31052,7 @@
         <v>1376</v>
       </c>
     </row>
-    <row r="862" spans="2:13" x14ac:dyDescent="0.3">
+    <row r="862" spans="2:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="C862" t="s">
         <v>1374</v>
       </c>
@@ -31039,7 +31078,7 @@
         <v>1376</v>
       </c>
     </row>
-    <row r="863" spans="2:13" x14ac:dyDescent="0.3">
+    <row r="863" spans="2:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="C863" t="s">
         <v>1374</v>
       </c>
@@ -31065,7 +31104,7 @@
         <v>1376</v>
       </c>
     </row>
-    <row r="864" spans="2:13" x14ac:dyDescent="0.3">
+    <row r="864" spans="2:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="C864" t="s">
         <v>1374</v>
       </c>
@@ -31091,7 +31130,7 @@
         <v>1376</v>
       </c>
     </row>
-    <row r="865" spans="2:13" x14ac:dyDescent="0.3">
+    <row r="865" spans="2:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="C865" t="s">
         <v>1374</v>
       </c>
@@ -31117,7 +31156,7 @@
         <v>1376</v>
       </c>
     </row>
-    <row r="866" spans="2:13" x14ac:dyDescent="0.3">
+    <row r="866" spans="2:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="C866" t="s">
         <v>1374</v>
       </c>
@@ -31143,7 +31182,7 @@
         <v>1376</v>
       </c>
     </row>
-    <row r="867" spans="2:13" x14ac:dyDescent="0.3">
+    <row r="867" spans="2:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="C867" t="s">
         <v>90</v>
       </c>
@@ -31172,7 +31211,7 @@
         <v>1379</v>
       </c>
     </row>
-    <row r="868" spans="2:13" x14ac:dyDescent="0.3">
+    <row r="868" spans="2:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="C868" t="s">
         <v>90</v>
       </c>
@@ -31201,7 +31240,7 @@
         <v>1379</v>
       </c>
     </row>
-    <row r="869" spans="2:13" x14ac:dyDescent="0.3">
+    <row r="869" spans="2:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="C869" t="s">
         <v>90</v>
       </c>
@@ -31230,7 +31269,7 @@
         <v>1379</v>
       </c>
     </row>
-    <row r="870" spans="2:13" x14ac:dyDescent="0.3">
+    <row r="870" spans="2:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="C870" t="s">
         <v>90</v>
       </c>
@@ -31259,7 +31298,7 @@
         <v>1379</v>
       </c>
     </row>
-    <row r="871" spans="2:13" x14ac:dyDescent="0.3">
+    <row r="871" spans="2:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="C871" t="s">
         <v>90</v>
       </c>
@@ -31288,7 +31327,7 @@
         <v>1379</v>
       </c>
     </row>
-    <row r="872" spans="2:13" x14ac:dyDescent="0.3">
+    <row r="872" spans="2:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="C872" t="s">
         <v>90</v>
       </c>
@@ -31317,7 +31356,7 @@
         <v>1379</v>
       </c>
     </row>
-    <row r="873" spans="2:13" x14ac:dyDescent="0.3">
+    <row r="873" spans="2:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="C873" t="s">
         <v>90</v>
       </c>
@@ -31346,7 +31385,7 @@
         <v>1379</v>
       </c>
     </row>
-    <row r="874" spans="2:13" x14ac:dyDescent="0.3">
+    <row r="874" spans="2:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="C874" t="s">
         <v>90</v>
       </c>
@@ -31375,7 +31414,7 @@
         <v>1379</v>
       </c>
     </row>
-    <row r="875" spans="2:13" x14ac:dyDescent="0.3">
+    <row r="875" spans="2:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="B875" t="s">
         <v>137</v>
       </c>
@@ -31401,7 +31440,7 @@
         <v>1388</v>
       </c>
     </row>
-    <row r="876" spans="2:13" x14ac:dyDescent="0.3">
+    <row r="876" spans="2:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="B876" t="s">
         <v>137</v>
       </c>
@@ -31427,7 +31466,7 @@
         <v>1388</v>
       </c>
     </row>
-    <row r="877" spans="2:13" x14ac:dyDescent="0.3">
+    <row r="877" spans="2:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="B877" t="s">
         <v>137</v>
       </c>
@@ -31453,7 +31492,7 @@
         <v>1388</v>
       </c>
     </row>
-    <row r="878" spans="2:13" x14ac:dyDescent="0.3">
+    <row r="878" spans="2:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="B878" t="s">
         <v>137</v>
       </c>
@@ -31479,7 +31518,7 @@
         <v>1388</v>
       </c>
     </row>
-    <row r="879" spans="2:13" x14ac:dyDescent="0.3">
+    <row r="879" spans="2:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="C879" t="s">
         <v>69</v>
       </c>
@@ -31508,7 +31547,7 @@
         <v>1397</v>
       </c>
     </row>
-    <row r="880" spans="2:13" x14ac:dyDescent="0.3">
+    <row r="880" spans="2:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="C880" t="s">
         <v>69</v>
       </c>
@@ -31537,7 +31576,7 @@
         <v>1397</v>
       </c>
     </row>
-    <row r="881" spans="2:13" x14ac:dyDescent="0.3">
+    <row r="881" spans="2:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="C881" t="s">
         <v>69</v>
       </c>
@@ -31566,7 +31605,7 @@
         <v>1397</v>
       </c>
     </row>
-    <row r="882" spans="2:13" x14ac:dyDescent="0.3">
+    <row r="882" spans="2:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="C882" t="s">
         <v>69</v>
       </c>
@@ -31595,7 +31634,7 @@
         <v>1397</v>
       </c>
     </row>
-    <row r="883" spans="2:13" x14ac:dyDescent="0.3">
+    <row r="883" spans="2:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="C883" t="s">
         <v>69</v>
       </c>
@@ -31624,7 +31663,7 @@
         <v>1397</v>
       </c>
     </row>
-    <row r="884" spans="2:13" x14ac:dyDescent="0.3">
+    <row r="884" spans="2:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="C884" t="s">
         <v>69</v>
       </c>
@@ -31653,7 +31692,7 @@
         <v>1397</v>
       </c>
     </row>
-    <row r="885" spans="2:13" x14ac:dyDescent="0.3">
+    <row r="885" spans="2:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="B885" t="s">
         <v>162</v>
       </c>
@@ -31682,7 +31721,7 @@
         <v>1405</v>
       </c>
     </row>
-    <row r="886" spans="2:13" x14ac:dyDescent="0.3">
+    <row r="886" spans="2:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="B886" t="s">
         <v>162</v>
       </c>
@@ -31711,7 +31750,7 @@
         <v>1405</v>
       </c>
     </row>
-    <row r="887" spans="2:13" x14ac:dyDescent="0.3">
+    <row r="887" spans="2:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="B887" t="s">
         <v>162</v>
       </c>
@@ -31740,7 +31779,7 @@
         <v>1405</v>
       </c>
     </row>
-    <row r="888" spans="2:13" x14ac:dyDescent="0.3">
+    <row r="888" spans="2:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="B888" t="s">
         <v>162</v>
       </c>
@@ -31769,7 +31808,7 @@
         <v>1405</v>
       </c>
     </row>
-    <row r="889" spans="2:13" x14ac:dyDescent="0.3">
+    <row r="889" spans="2:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="B889" t="s">
         <v>162</v>
       </c>
@@ -31798,7 +31837,7 @@
         <v>1405</v>
       </c>
     </row>
-    <row r="890" spans="2:13" x14ac:dyDescent="0.3">
+    <row r="890" spans="2:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="B890" t="s">
         <v>162</v>
       </c>
@@ -31827,7 +31866,7 @@
         <v>1405</v>
       </c>
     </row>
-    <row r="891" spans="2:13" x14ac:dyDescent="0.3">
+    <row r="891" spans="2:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="C891" t="s">
         <v>1411</v>
       </c>
@@ -31856,7 +31895,7 @@
         <v>1414</v>
       </c>
     </row>
-    <row r="892" spans="2:13" x14ac:dyDescent="0.3">
+    <row r="892" spans="2:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="C892" t="s">
         <v>1411</v>
       </c>
@@ -31885,7 +31924,7 @@
         <v>1414</v>
       </c>
     </row>
-    <row r="893" spans="2:13" x14ac:dyDescent="0.3">
+    <row r="893" spans="2:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="C893" t="s">
         <v>1411</v>
       </c>
@@ -31914,7 +31953,7 @@
         <v>1414</v>
       </c>
     </row>
-    <row r="894" spans="2:13" x14ac:dyDescent="0.3">
+    <row r="894" spans="2:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="C894" t="s">
         <v>1411</v>
       </c>
@@ -31943,7 +31982,7 @@
         <v>1414</v>
       </c>
     </row>
-    <row r="895" spans="2:13" x14ac:dyDescent="0.3">
+    <row r="895" spans="2:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="C895" t="s">
         <v>1411</v>
       </c>
@@ -31972,7 +32011,7 @@
         <v>1414</v>
       </c>
     </row>
-    <row r="896" spans="2:13" x14ac:dyDescent="0.3">
+    <row r="896" spans="2:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="C896" t="s">
         <v>1411</v>
       </c>
@@ -32001,7 +32040,7 @@
         <v>1414</v>
       </c>
     </row>
-    <row r="897" spans="3:13" x14ac:dyDescent="0.3">
+    <row r="897" spans="3:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="C897" t="s">
         <v>1411</v>
       </c>
@@ -32030,7 +32069,7 @@
         <v>1414</v>
       </c>
     </row>
-    <row r="898" spans="3:13" x14ac:dyDescent="0.3">
+    <row r="898" spans="3:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="C898" t="s">
         <v>1411</v>
       </c>
@@ -32059,7 +32098,7 @@
         <v>1414</v>
       </c>
     </row>
-    <row r="899" spans="3:13" x14ac:dyDescent="0.3">
+    <row r="899" spans="3:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="C899" t="s">
         <v>1424</v>
       </c>
@@ -32088,7 +32127,7 @@
         <v>1427</v>
       </c>
     </row>
-    <row r="900" spans="3:13" x14ac:dyDescent="0.3">
+    <row r="900" spans="3:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="C900" t="s">
         <v>1424</v>
       </c>
@@ -32117,7 +32156,7 @@
         <v>1427</v>
       </c>
     </row>
-    <row r="901" spans="3:13" x14ac:dyDescent="0.3">
+    <row r="901" spans="3:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="C901" t="s">
         <v>1424</v>
       </c>
@@ -32146,7 +32185,7 @@
         <v>1427</v>
       </c>
     </row>
-    <row r="902" spans="3:13" x14ac:dyDescent="0.3">
+    <row r="902" spans="3:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="C902" t="s">
         <v>1424</v>
       </c>
@@ -32175,7 +32214,7 @@
         <v>1427</v>
       </c>
     </row>
-    <row r="903" spans="3:13" x14ac:dyDescent="0.3">
+    <row r="903" spans="3:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="C903" t="s">
         <v>1424</v>
       </c>
@@ -32204,7 +32243,7 @@
         <v>1427</v>
       </c>
     </row>
-    <row r="904" spans="3:13" x14ac:dyDescent="0.3">
+    <row r="904" spans="3:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="C904" t="s">
         <v>1424</v>
       </c>
@@ -32233,7 +32272,7 @@
         <v>1427</v>
       </c>
     </row>
-    <row r="905" spans="3:13" x14ac:dyDescent="0.3">
+    <row r="905" spans="3:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="C905" t="s">
         <v>1424</v>
       </c>
@@ -32262,7 +32301,7 @@
         <v>1427</v>
       </c>
     </row>
-    <row r="906" spans="3:13" x14ac:dyDescent="0.3">
+    <row r="906" spans="3:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="C906" t="s">
         <v>1424</v>
       </c>
@@ -32291,7 +32330,7 @@
         <v>1427</v>
       </c>
     </row>
-    <row r="907" spans="3:13" x14ac:dyDescent="0.3">
+    <row r="907" spans="3:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="C907" t="s">
         <v>101</v>
       </c>
@@ -32320,7 +32359,7 @@
         <v>1437</v>
       </c>
     </row>
-    <row r="908" spans="3:13" x14ac:dyDescent="0.3">
+    <row r="908" spans="3:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="C908" t="s">
         <v>101</v>
       </c>
@@ -32349,7 +32388,7 @@
         <v>1437</v>
       </c>
     </row>
-    <row r="909" spans="3:13" x14ac:dyDescent="0.3">
+    <row r="909" spans="3:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="C909" t="s">
         <v>101</v>
       </c>
@@ -32378,7 +32417,7 @@
         <v>1437</v>
       </c>
     </row>
-    <row r="910" spans="3:13" x14ac:dyDescent="0.3">
+    <row r="910" spans="3:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="C910" t="s">
         <v>101</v>
       </c>
@@ -32407,7 +32446,7 @@
         <v>1437</v>
       </c>
     </row>
-    <row r="911" spans="3:13" x14ac:dyDescent="0.3">
+    <row r="911" spans="3:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="C911" t="s">
         <v>101</v>
       </c>
@@ -32436,7 +32475,7 @@
         <v>1437</v>
       </c>
     </row>
-    <row r="912" spans="3:13" x14ac:dyDescent="0.3">
+    <row r="912" spans="3:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="C912" t="s">
         <v>101</v>
       </c>
@@ -32465,7 +32504,7 @@
         <v>1437</v>
       </c>
     </row>
-    <row r="913" spans="2:13" x14ac:dyDescent="0.3">
+    <row r="913" spans="2:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="C913" t="s">
         <v>399</v>
       </c>
@@ -32494,7 +32533,7 @@
         <v>1445</v>
       </c>
     </row>
-    <row r="914" spans="2:13" x14ac:dyDescent="0.3">
+    <row r="914" spans="2:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="C914" t="s">
         <v>399</v>
       </c>
@@ -32523,7 +32562,7 @@
         <v>1445</v>
       </c>
     </row>
-    <row r="915" spans="2:13" x14ac:dyDescent="0.3">
+    <row r="915" spans="2:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="D915" t="s">
         <v>1447</v>
       </c>
@@ -32549,7 +32588,7 @@
         <v>1449</v>
       </c>
     </row>
-    <row r="916" spans="2:13" x14ac:dyDescent="0.3">
+    <row r="916" spans="2:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="D916" t="s">
         <v>1447</v>
       </c>
@@ -32575,7 +32614,7 @@
         <v>1449</v>
       </c>
     </row>
-    <row r="917" spans="2:13" x14ac:dyDescent="0.3">
+    <row r="917" spans="2:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="D917" t="s">
         <v>1447</v>
       </c>
@@ -32601,7 +32640,7 @@
         <v>1449</v>
       </c>
     </row>
-    <row r="918" spans="2:13" x14ac:dyDescent="0.3">
+    <row r="918" spans="2:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="D918" t="s">
         <v>1447</v>
       </c>
@@ -32627,7 +32666,7 @@
         <v>1449</v>
       </c>
     </row>
-    <row r="919" spans="2:13" x14ac:dyDescent="0.3">
+    <row r="919" spans="2:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="D919" t="s">
         <v>1447</v>
       </c>
@@ -32653,7 +32692,7 @@
         <v>1449</v>
       </c>
     </row>
-    <row r="920" spans="2:13" x14ac:dyDescent="0.3">
+    <row r="920" spans="2:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="D920" t="s">
         <v>1447</v>
       </c>
@@ -32679,7 +32718,7 @@
         <v>1449</v>
       </c>
     </row>
-    <row r="921" spans="2:13" x14ac:dyDescent="0.3">
+    <row r="921" spans="2:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="D921" t="s">
         <v>1447</v>
       </c>
@@ -32705,7 +32744,7 @@
         <v>1449</v>
       </c>
     </row>
-    <row r="922" spans="2:13" x14ac:dyDescent="0.3">
+    <row r="922" spans="2:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="D922" t="s">
         <v>1447</v>
       </c>
@@ -32731,7 +32770,7 @@
         <v>1449</v>
       </c>
     </row>
-    <row r="923" spans="2:13" x14ac:dyDescent="0.3">
+    <row r="923" spans="2:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="B923" t="s">
         <v>162</v>
       </c>
@@ -32760,7 +32799,7 @@
         <v>1460</v>
       </c>
     </row>
-    <row r="924" spans="2:13" x14ac:dyDescent="0.3">
+    <row r="924" spans="2:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="B924" t="s">
         <v>162</v>
       </c>
@@ -32789,7 +32828,7 @@
         <v>1460</v>
       </c>
     </row>
-    <row r="925" spans="2:13" x14ac:dyDescent="0.3">
+    <row r="925" spans="2:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="B925" t="s">
         <v>162</v>
       </c>
@@ -32818,7 +32857,7 @@
         <v>1460</v>
       </c>
     </row>
-    <row r="926" spans="2:13" x14ac:dyDescent="0.3">
+    <row r="926" spans="2:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="B926" t="s">
         <v>162</v>
       </c>
@@ -32847,7 +32886,7 @@
         <v>1460</v>
       </c>
     </row>
-    <row r="927" spans="2:13" x14ac:dyDescent="0.3">
+    <row r="927" spans="2:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="B927" t="s">
         <v>162</v>
       </c>
@@ -32876,7 +32915,7 @@
         <v>1460</v>
       </c>
     </row>
-    <row r="928" spans="2:13" x14ac:dyDescent="0.3">
+    <row r="928" spans="2:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="B928" t="s">
         <v>162</v>
       </c>
@@ -32905,7 +32944,7 @@
         <v>1460</v>
       </c>
     </row>
-    <row r="929" spans="2:13" x14ac:dyDescent="0.3">
+    <row r="929" spans="2:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="B929" t="s">
         <v>593</v>
       </c>
@@ -32940,7 +32979,7 @@
         <v>1475</v>
       </c>
     </row>
-    <row r="930" spans="2:13" x14ac:dyDescent="0.3">
+    <row r="930" spans="2:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="B930" t="s">
         <v>593</v>
       </c>
@@ -32978,7 +33017,7 @@
         <v>1475</v>
       </c>
     </row>
-    <row r="931" spans="2:13" x14ac:dyDescent="0.3">
+    <row r="931" spans="2:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="B931" t="s">
         <v>593</v>
       </c>
@@ -33016,7 +33055,7 @@
         <v>1475</v>
       </c>
     </row>
-    <row r="932" spans="2:13" x14ac:dyDescent="0.3">
+    <row r="932" spans="2:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="B932" t="s">
         <v>593</v>
       </c>
@@ -33054,7 +33093,7 @@
         <v>1475</v>
       </c>
     </row>
-    <row r="933" spans="2:13" x14ac:dyDescent="0.3">
+    <row r="933" spans="2:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="B933" t="s">
         <v>593</v>
       </c>
@@ -33089,7 +33128,7 @@
         <v>1475</v>
       </c>
     </row>
-    <row r="934" spans="2:13" x14ac:dyDescent="0.3">
+    <row r="934" spans="2:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="B934" t="s">
         <v>593</v>
       </c>
@@ -33127,7 +33166,7 @@
         <v>1475</v>
       </c>
     </row>
-    <row r="935" spans="2:13" x14ac:dyDescent="0.3">
+    <row r="935" spans="2:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="B935" t="s">
         <v>593</v>
       </c>
@@ -33162,7 +33201,7 @@
         <v>1475</v>
       </c>
     </row>
-    <row r="936" spans="2:13" x14ac:dyDescent="0.3">
+    <row r="936" spans="2:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="B936" t="s">
         <v>593</v>
       </c>
@@ -33200,7 +33239,7 @@
         <v>1475</v>
       </c>
     </row>
-    <row r="937" spans="2:13" x14ac:dyDescent="0.3">
+    <row r="937" spans="2:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="C937" t="s">
         <v>150</v>
       </c>
@@ -33229,7 +33268,7 @@
         <v>1491</v>
       </c>
     </row>
-    <row r="938" spans="2:13" x14ac:dyDescent="0.3">
+    <row r="938" spans="2:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="C938" t="s">
         <v>150</v>
       </c>
@@ -33258,7 +33297,7 @@
         <v>1491</v>
       </c>
     </row>
-    <row r="939" spans="2:13" x14ac:dyDescent="0.3">
+    <row r="939" spans="2:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="C939" t="s">
         <v>150</v>
       </c>
@@ -33287,7 +33326,7 @@
         <v>1491</v>
       </c>
     </row>
-    <row r="940" spans="2:13" x14ac:dyDescent="0.3">
+    <row r="940" spans="2:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="C940" t="s">
         <v>150</v>
       </c>
@@ -33316,7 +33355,7 @@
         <v>1491</v>
       </c>
     </row>
-    <row r="941" spans="2:13" x14ac:dyDescent="0.3">
+    <row r="941" spans="2:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="C941" t="s">
         <v>150</v>
       </c>
@@ -33345,7 +33384,7 @@
         <v>1491</v>
       </c>
     </row>
-    <row r="942" spans="2:13" x14ac:dyDescent="0.3">
+    <row r="942" spans="2:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="C942" t="s">
         <v>150</v>
       </c>
@@ -33374,7 +33413,7 @@
         <v>1491</v>
       </c>
     </row>
-    <row r="943" spans="2:13" x14ac:dyDescent="0.3">
+    <row r="943" spans="2:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="C943" t="s">
         <v>150</v>
       </c>
@@ -33403,7 +33442,7 @@
         <v>1491</v>
       </c>
     </row>
-    <row r="944" spans="2:13" x14ac:dyDescent="0.3">
+    <row r="944" spans="2:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="C944" t="s">
         <v>150</v>
       </c>
@@ -33432,7 +33471,7 @@
         <v>1491</v>
       </c>
     </row>
-    <row r="945" spans="2:13" x14ac:dyDescent="0.3">
+    <row r="945" spans="2:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="C945" t="s">
         <v>129</v>
       </c>
@@ -33461,7 +33500,7 @@
         <v>1503</v>
       </c>
     </row>
-    <row r="946" spans="2:13" x14ac:dyDescent="0.3">
+    <row r="946" spans="2:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="C946" t="s">
         <v>129</v>
       </c>
@@ -33490,7 +33529,7 @@
         <v>1503</v>
       </c>
     </row>
-    <row r="947" spans="2:13" x14ac:dyDescent="0.3">
+    <row r="947" spans="2:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="C947" t="s">
         <v>129</v>
       </c>
@@ -33519,7 +33558,7 @@
         <v>1503</v>
       </c>
     </row>
-    <row r="948" spans="2:13" x14ac:dyDescent="0.3">
+    <row r="948" spans="2:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="C948" t="s">
         <v>129</v>
       </c>
@@ -33548,7 +33587,7 @@
         <v>1503</v>
       </c>
     </row>
-    <row r="949" spans="2:13" x14ac:dyDescent="0.3">
+    <row r="949" spans="2:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="C949" t="s">
         <v>129</v>
       </c>
@@ -33577,7 +33616,7 @@
         <v>1503</v>
       </c>
     </row>
-    <row r="950" spans="2:13" x14ac:dyDescent="0.3">
+    <row r="950" spans="2:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="C950" t="s">
         <v>129</v>
       </c>
@@ -33606,7 +33645,7 @@
         <v>1503</v>
       </c>
     </row>
-    <row r="951" spans="2:13" x14ac:dyDescent="0.3">
+    <row r="951" spans="2:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="C951" t="s">
         <v>129</v>
       </c>
@@ -33635,7 +33674,7 @@
         <v>1503</v>
       </c>
     </row>
-    <row r="952" spans="2:13" x14ac:dyDescent="0.3">
+    <row r="952" spans="2:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="C952" t="s">
         <v>129</v>
       </c>
@@ -33664,7 +33703,7 @@
         <v>1503</v>
       </c>
     </row>
-    <row r="953" spans="2:13" x14ac:dyDescent="0.3">
+    <row r="953" spans="2:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="C953" t="s">
         <v>303</v>
       </c>
@@ -33690,7 +33729,7 @@
         <v>1513</v>
       </c>
     </row>
-    <row r="954" spans="2:13" x14ac:dyDescent="0.3">
+    <row r="954" spans="2:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="C954" t="s">
         <v>303</v>
       </c>
@@ -33716,7 +33755,7 @@
         <v>1513</v>
       </c>
     </row>
-    <row r="955" spans="2:13" x14ac:dyDescent="0.3">
+    <row r="955" spans="2:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="C955" t="s">
         <v>303</v>
       </c>
@@ -33742,7 +33781,7 @@
         <v>1513</v>
       </c>
     </row>
-    <row r="956" spans="2:13" x14ac:dyDescent="0.3">
+    <row r="956" spans="2:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="C956" t="s">
         <v>303</v>
       </c>
@@ -33768,7 +33807,7 @@
         <v>1513</v>
       </c>
     </row>
-    <row r="957" spans="2:13" x14ac:dyDescent="0.3">
+    <row r="957" spans="2:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="B957" t="s">
         <v>593</v>
       </c>
@@ -33797,7 +33836,7 @@
         <v>1520</v>
       </c>
     </row>
-    <row r="958" spans="2:13" x14ac:dyDescent="0.3">
+    <row r="958" spans="2:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="B958" t="s">
         <v>593</v>
       </c>
@@ -33826,7 +33865,7 @@
         <v>1520</v>
       </c>
     </row>
-    <row r="959" spans="2:13" x14ac:dyDescent="0.3">
+    <row r="959" spans="2:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="B959" t="s">
         <v>593</v>
       </c>
@@ -33855,7 +33894,7 @@
         <v>1520</v>
       </c>
     </row>
-    <row r="960" spans="2:13" x14ac:dyDescent="0.3">
+    <row r="960" spans="2:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="B960" t="s">
         <v>593</v>
       </c>
@@ -33884,7 +33923,7 @@
         <v>1520</v>
       </c>
     </row>
-    <row r="961" spans="2:13" x14ac:dyDescent="0.3">
+    <row r="961" spans="2:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="B961" t="s">
         <v>593</v>
       </c>
@@ -33913,7 +33952,7 @@
         <v>1520</v>
       </c>
     </row>
-    <row r="962" spans="2:13" x14ac:dyDescent="0.3">
+    <row r="962" spans="2:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="B962" t="s">
         <v>593</v>
       </c>
@@ -33942,7 +33981,7 @@
         <v>1520</v>
       </c>
     </row>
-    <row r="963" spans="2:13" x14ac:dyDescent="0.3">
+    <row r="963" spans="2:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="B963" t="s">
         <v>593</v>
       </c>
@@ -33974,7 +34013,7 @@
         <v>1520</v>
       </c>
     </row>
-    <row r="964" spans="2:13" x14ac:dyDescent="0.3">
+    <row r="964" spans="2:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="B964" t="s">
         <v>593</v>
       </c>
@@ -34006,7 +34045,7 @@
         <v>1520</v>
       </c>
     </row>
-    <row r="965" spans="2:13" x14ac:dyDescent="0.3">
+    <row r="965" spans="2:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="B965" t="s">
         <v>593</v>
       </c>
@@ -34041,7 +34080,7 @@
         <v>1535</v>
       </c>
     </row>
-    <row r="966" spans="2:13" x14ac:dyDescent="0.3">
+    <row r="966" spans="2:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="C966" t="s">
         <v>1536</v>
       </c>
@@ -34070,7 +34109,7 @@
         <v>1540</v>
       </c>
     </row>
-    <row r="967" spans="2:13" x14ac:dyDescent="0.3">
+    <row r="967" spans="2:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="C967" t="s">
         <v>1536</v>
       </c>
@@ -34099,7 +34138,7 @@
         <v>1540</v>
       </c>
     </row>
-    <row r="968" spans="2:13" x14ac:dyDescent="0.3">
+    <row r="968" spans="2:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="C968" t="s">
         <v>1536</v>
       </c>
@@ -34128,7 +34167,7 @@
         <v>1540</v>
       </c>
     </row>
-    <row r="969" spans="2:13" x14ac:dyDescent="0.3">
+    <row r="969" spans="2:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="C969" t="s">
         <v>1536</v>
       </c>
@@ -34157,7 +34196,7 @@
         <v>1540</v>
       </c>
     </row>
-    <row r="970" spans="2:13" x14ac:dyDescent="0.3">
+    <row r="970" spans="2:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="C970" t="s">
         <v>1536</v>
       </c>
@@ -34186,7 +34225,7 @@
         <v>1540</v>
       </c>
     </row>
-    <row r="971" spans="2:13" x14ac:dyDescent="0.3">
+    <row r="971" spans="2:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="C971" t="s">
         <v>1536</v>
       </c>
@@ -34215,7 +34254,7 @@
         <v>1540</v>
       </c>
     </row>
-    <row r="972" spans="2:13" x14ac:dyDescent="0.3">
+    <row r="972" spans="2:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="C972" t="s">
         <v>1536</v>
       </c>
@@ -34244,7 +34283,7 @@
         <v>1540</v>
       </c>
     </row>
-    <row r="973" spans="2:13" x14ac:dyDescent="0.3">
+    <row r="973" spans="2:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="C973" t="s">
         <v>1536</v>
       </c>
@@ -34273,7 +34312,7 @@
         <v>1540</v>
       </c>
     </row>
-    <row r="974" spans="2:13" x14ac:dyDescent="0.3">
+    <row r="974" spans="2:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="C974" t="s">
         <v>1536</v>
       </c>
@@ -34302,7 +34341,7 @@
         <v>1540</v>
       </c>
     </row>
-    <row r="975" spans="2:13" x14ac:dyDescent="0.3">
+    <row r="975" spans="2:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="C975" t="s">
         <v>1411</v>
       </c>
@@ -34331,7 +34370,7 @@
         <v>1552</v>
       </c>
     </row>
-    <row r="976" spans="2:13" x14ac:dyDescent="0.3">
+    <row r="976" spans="2:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="C976" t="s">
         <v>1411</v>
       </c>
@@ -34360,7 +34399,7 @@
         <v>1552</v>
       </c>
     </row>
-    <row r="977" spans="2:13" x14ac:dyDescent="0.3">
+    <row r="977" spans="2:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="C977" t="s">
         <v>1411</v>
       </c>
@@ -34389,7 +34428,7 @@
         <v>1552</v>
       </c>
     </row>
-    <row r="978" spans="2:13" x14ac:dyDescent="0.3">
+    <row r="978" spans="2:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="C978" t="s">
         <v>1411</v>
       </c>
@@ -34418,7 +34457,7 @@
         <v>1552</v>
       </c>
     </row>
-    <row r="979" spans="2:13" x14ac:dyDescent="0.3">
+    <row r="979" spans="2:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="C979" t="s">
         <v>1411</v>
       </c>
@@ -34447,7 +34486,7 @@
         <v>1552</v>
       </c>
     </row>
-    <row r="980" spans="2:13" x14ac:dyDescent="0.3">
+    <row r="980" spans="2:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="C980" t="s">
         <v>1411</v>
       </c>
@@ -34476,7 +34515,7 @@
         <v>1552</v>
       </c>
     </row>
-    <row r="981" spans="2:13" x14ac:dyDescent="0.3">
+    <row r="981" spans="2:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="B981" t="s">
         <v>137</v>
       </c>
@@ -34493,7 +34532,7 @@
         <v>1559</v>
       </c>
       <c r="I981">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L981" t="s">
         <v>1560</v>
@@ -34502,7 +34541,7 @@
         <v>1561</v>
       </c>
     </row>
-    <row r="982" spans="2:13" x14ac:dyDescent="0.3">
+    <row r="982" spans="2:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="B982" t="s">
         <v>137</v>
       </c>
@@ -34519,7 +34558,7 @@
         <v>1559</v>
       </c>
       <c r="I982">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L982" t="s">
         <v>1562</v>
@@ -34528,7 +34567,7 @@
         <v>1561</v>
       </c>
     </row>
-    <row r="983" spans="2:13" x14ac:dyDescent="0.3">
+    <row r="983" spans="2:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="B983" t="s">
         <v>137</v>
       </c>
@@ -34545,7 +34584,7 @@
         <v>1559</v>
       </c>
       <c r="I983">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L983" t="s">
         <v>1563</v>
@@ -34554,7 +34593,7 @@
         <v>1561</v>
       </c>
     </row>
-    <row r="984" spans="2:13" x14ac:dyDescent="0.3">
+    <row r="984" spans="2:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="B984" t="s">
         <v>137</v>
       </c>
@@ -34580,7 +34619,7 @@
         <v>1561</v>
       </c>
     </row>
-    <row r="985" spans="2:13" x14ac:dyDescent="0.3">
+    <row r="985" spans="2:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="B985" t="s">
         <v>137</v>
       </c>
@@ -34606,7 +34645,7 @@
         <v>1561</v>
       </c>
     </row>
-    <row r="986" spans="2:13" x14ac:dyDescent="0.3">
+    <row r="986" spans="2:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="C986" t="s">
         <v>101</v>
       </c>
@@ -34635,7 +34674,7 @@
         <v>1569</v>
       </c>
     </row>
-    <row r="987" spans="2:13" x14ac:dyDescent="0.3">
+    <row r="987" spans="2:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="C987" t="s">
         <v>101</v>
       </c>
@@ -34664,7 +34703,7 @@
         <v>1569</v>
       </c>
     </row>
-    <row r="988" spans="2:13" x14ac:dyDescent="0.3">
+    <row r="988" spans="2:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="C988" t="s">
         <v>101</v>
       </c>
@@ -34693,7 +34732,7 @@
         <v>1569</v>
       </c>
     </row>
-    <row r="989" spans="2:13" x14ac:dyDescent="0.3">
+    <row r="989" spans="2:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="C989" t="s">
         <v>101</v>
       </c>
@@ -34722,7 +34761,7 @@
         <v>1569</v>
       </c>
     </row>
-    <row r="990" spans="2:13" x14ac:dyDescent="0.3">
+    <row r="990" spans="2:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="C990" t="s">
         <v>101</v>
       </c>
@@ -34751,7 +34790,7 @@
         <v>1569</v>
       </c>
     </row>
-    <row r="991" spans="2:13" x14ac:dyDescent="0.3">
+    <row r="991" spans="2:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="C991" t="s">
         <v>101</v>
       </c>
@@ -34780,7 +34819,7 @@
         <v>1569</v>
       </c>
     </row>
-    <row r="992" spans="2:13" x14ac:dyDescent="0.3">
+    <row r="992" spans="2:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="C992" t="s">
         <v>101</v>
       </c>
@@ -34809,7 +34848,7 @@
         <v>1569</v>
       </c>
     </row>
-    <row r="993" spans="3:13" x14ac:dyDescent="0.3">
+    <row r="993" spans="3:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="C993" t="s">
         <v>101</v>
       </c>
@@ -34838,7 +34877,7 @@
         <v>1569</v>
       </c>
     </row>
-    <row r="994" spans="3:13" x14ac:dyDescent="0.3">
+    <row r="994" spans="3:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="C994" t="s">
         <v>399</v>
       </c>
@@ -34867,7 +34906,7 @@
         <v>1581</v>
       </c>
     </row>
-    <row r="995" spans="3:13" x14ac:dyDescent="0.3">
+    <row r="995" spans="3:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="C995" t="s">
         <v>399</v>
       </c>
@@ -34896,7 +34935,7 @@
         <v>1581</v>
       </c>
     </row>
-    <row r="996" spans="3:13" x14ac:dyDescent="0.3">
+    <row r="996" spans="3:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="C996" t="s">
         <v>399</v>
       </c>
@@ -34925,7 +34964,7 @@
         <v>1581</v>
       </c>
     </row>
-    <row r="997" spans="3:13" x14ac:dyDescent="0.3">
+    <row r="997" spans="3:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="C997" t="s">
         <v>721</v>
       </c>
@@ -34954,7 +34993,7 @@
         <v>1587</v>
       </c>
     </row>
-    <row r="998" spans="3:13" x14ac:dyDescent="0.3">
+    <row r="998" spans="3:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="C998" t="s">
         <v>721</v>
       </c>
@@ -34983,7 +35022,7 @@
         <v>1587</v>
       </c>
     </row>
-    <row r="999" spans="3:13" x14ac:dyDescent="0.3">
+    <row r="999" spans="3:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="C999" t="s">
         <v>721</v>
       </c>
@@ -35012,7 +35051,7 @@
         <v>1587</v>
       </c>
     </row>
-    <row r="1000" spans="3:13" x14ac:dyDescent="0.3">
+    <row r="1000" spans="3:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="C1000" t="s">
         <v>721</v>
       </c>
@@ -35041,7 +35080,7 @@
         <v>1587</v>
       </c>
     </row>
-    <row r="1001" spans="3:13" x14ac:dyDescent="0.3">
+    <row r="1001" spans="3:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="C1001" t="s">
         <v>721</v>
       </c>
@@ -35070,7 +35109,7 @@
         <v>1587</v>
       </c>
     </row>
-    <row r="1002" spans="3:13" x14ac:dyDescent="0.3">
+    <row r="1002" spans="3:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="C1002" t="s">
         <v>721</v>
       </c>
@@ -35099,7 +35138,7 @@
         <v>1587</v>
       </c>
     </row>
-    <row r="1003" spans="3:13" x14ac:dyDescent="0.3">
+    <row r="1003" spans="3:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="C1003" t="s">
         <v>721</v>
       </c>
@@ -35128,7 +35167,7 @@
         <v>1587</v>
       </c>
     </row>
-    <row r="1004" spans="3:13" x14ac:dyDescent="0.3">
+    <row r="1004" spans="3:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="C1004" t="s">
         <v>721</v>
       </c>
@@ -35157,7 +35196,7 @@
         <v>1587</v>
       </c>
     </row>
-    <row r="1005" spans="3:13" x14ac:dyDescent="0.3">
+    <row r="1005" spans="3:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="C1005" t="s">
         <v>721</v>
       </c>
@@ -35186,7 +35225,7 @@
         <v>1587</v>
       </c>
     </row>
-    <row r="1006" spans="3:13" x14ac:dyDescent="0.3">
+    <row r="1006" spans="3:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="C1006" t="s">
         <v>180</v>
       </c>
@@ -35212,7 +35251,7 @@
         <v>1598</v>
       </c>
     </row>
-    <row r="1007" spans="3:13" x14ac:dyDescent="0.3">
+    <row r="1007" spans="3:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="C1007" t="s">
         <v>180</v>
       </c>
@@ -35238,7 +35277,7 @@
         <v>1598</v>
       </c>
     </row>
-    <row r="1008" spans="3:13" x14ac:dyDescent="0.3">
+    <row r="1008" spans="3:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="C1008" t="s">
         <v>180</v>
       </c>
@@ -35264,7 +35303,7 @@
         <v>1598</v>
       </c>
     </row>
-    <row r="1009" spans="2:13" x14ac:dyDescent="0.3">
+    <row r="1009" spans="2:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="C1009" t="s">
         <v>180</v>
       </c>
@@ -35290,7 +35329,7 @@
         <v>1598</v>
       </c>
     </row>
-    <row r="1010" spans="2:13" x14ac:dyDescent="0.3">
+    <row r="1010" spans="2:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="C1010" t="s">
         <v>180</v>
       </c>
@@ -35316,7 +35355,7 @@
         <v>1598</v>
       </c>
     </row>
-    <row r="1011" spans="2:13" x14ac:dyDescent="0.3">
+    <row r="1011" spans="2:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="C1011" t="s">
         <v>180</v>
       </c>
@@ -35342,7 +35381,7 @@
         <v>1598</v>
       </c>
     </row>
-    <row r="1012" spans="2:13" x14ac:dyDescent="0.3">
+    <row r="1012" spans="2:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="C1012" t="s">
         <v>180</v>
       </c>
@@ -35368,7 +35407,7 @@
         <v>1598</v>
       </c>
     </row>
-    <row r="1013" spans="2:13" x14ac:dyDescent="0.3">
+    <row r="1013" spans="2:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="C1013" t="s">
         <v>180</v>
       </c>
@@ -35394,7 +35433,7 @@
         <v>1598</v>
       </c>
     </row>
-    <row r="1014" spans="2:13" x14ac:dyDescent="0.3">
+    <row r="1014" spans="2:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="C1014" t="s">
         <v>180</v>
       </c>
@@ -35420,7 +35459,7 @@
         <v>1598</v>
       </c>
     </row>
-    <row r="1015" spans="2:13" x14ac:dyDescent="0.3">
+    <row r="1015" spans="2:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="B1015" t="s">
         <v>137</v>
       </c>
@@ -35440,7 +35479,7 @@
         <v>1609</v>
       </c>
       <c r="I1015">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L1015" t="s">
         <v>1610</v>
@@ -35449,7 +35488,7 @@
         <v>1598</v>
       </c>
     </row>
-    <row r="1016" spans="2:13" x14ac:dyDescent="0.3">
+    <row r="1016" spans="2:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="B1016" t="s">
         <v>137</v>
       </c>
@@ -35478,7 +35517,7 @@
         <v>1598</v>
       </c>
     </row>
-    <row r="1017" spans="2:13" x14ac:dyDescent="0.3">
+    <row r="1017" spans="2:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="B1017" t="s">
         <v>137</v>
       </c>
@@ -35507,7 +35546,7 @@
         <v>1598</v>
       </c>
     </row>
-    <row r="1018" spans="2:13" x14ac:dyDescent="0.3">
+    <row r="1018" spans="2:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="C1018" t="s">
         <v>150</v>
       </c>
@@ -35536,7 +35575,7 @@
         <v>1616</v>
       </c>
     </row>
-    <row r="1019" spans="2:13" x14ac:dyDescent="0.3">
+    <row r="1019" spans="2:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="C1019" t="s">
         <v>150</v>
       </c>
@@ -35565,7 +35604,7 @@
         <v>1616</v>
       </c>
     </row>
-    <row r="1020" spans="2:13" x14ac:dyDescent="0.3">
+    <row r="1020" spans="2:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="C1020" t="s">
         <v>150</v>
       </c>
@@ -35594,7 +35633,7 @@
         <v>1616</v>
       </c>
     </row>
-    <row r="1021" spans="2:13" x14ac:dyDescent="0.3">
+    <row r="1021" spans="2:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="C1021" t="s">
         <v>150</v>
       </c>
@@ -35623,7 +35662,7 @@
         <v>1616</v>
       </c>
     </row>
-    <row r="1022" spans="2:13" x14ac:dyDescent="0.3">
+    <row r="1022" spans="2:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="C1022" t="s">
         <v>150</v>
       </c>
@@ -35652,7 +35691,7 @@
         <v>1616</v>
       </c>
     </row>
-    <row r="1023" spans="2:13" x14ac:dyDescent="0.3">
+    <row r="1023" spans="2:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="C1023" t="s">
         <v>150</v>
       </c>
@@ -35681,7 +35720,7 @@
         <v>1616</v>
       </c>
     </row>
-    <row r="1024" spans="2:13" x14ac:dyDescent="0.3">
+    <row r="1024" spans="2:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="C1024" t="s">
         <v>150</v>
       </c>
@@ -35710,7 +35749,7 @@
         <v>1616</v>
       </c>
     </row>
-    <row r="1025" spans="3:13" x14ac:dyDescent="0.3">
+    <row r="1025" spans="3:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="C1025" t="s">
         <v>150</v>
       </c>
@@ -35739,7 +35778,7 @@
         <v>1616</v>
       </c>
     </row>
-    <row r="1026" spans="3:13" x14ac:dyDescent="0.3">
+    <row r="1026" spans="3:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="D1026" t="s">
         <v>1625</v>
       </c>
@@ -35753,7 +35792,7 @@
         <v>1626</v>
       </c>
       <c r="I1026">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L1026" t="s">
         <v>1627</v>
@@ -35762,7 +35801,7 @@
         <v>1628</v>
       </c>
     </row>
-    <row r="1027" spans="3:13" x14ac:dyDescent="0.3">
+    <row r="1027" spans="3:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="D1027" t="s">
         <v>1625</v>
       </c>
@@ -35776,7 +35815,7 @@
         <v>1559</v>
       </c>
       <c r="I1027">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L1027" t="s">
         <v>864</v>
@@ -35785,7 +35824,7 @@
         <v>1628</v>
       </c>
     </row>
-    <row r="1028" spans="3:13" x14ac:dyDescent="0.3">
+    <row r="1028" spans="3:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="D1028" t="s">
         <v>1625</v>
       </c>
@@ -35805,7 +35844,7 @@
         <v>1628</v>
       </c>
     </row>
-    <row r="1029" spans="3:13" x14ac:dyDescent="0.3">
+    <row r="1029" spans="3:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="D1029" t="s">
         <v>1625</v>
       </c>
@@ -35825,7 +35864,7 @@
         <v>1628</v>
       </c>
     </row>
-    <row r="1030" spans="3:13" x14ac:dyDescent="0.3">
+    <row r="1030" spans="3:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="C1030" t="s">
         <v>129</v>
       </c>
@@ -35851,7 +35890,7 @@
         <v>1632</v>
       </c>
     </row>
-    <row r="1031" spans="3:13" x14ac:dyDescent="0.3">
+    <row r="1031" spans="3:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="C1031" t="s">
         <v>129</v>
       </c>
@@ -35877,7 +35916,7 @@
         <v>1632</v>
       </c>
     </row>
-    <row r="1032" spans="3:13" x14ac:dyDescent="0.3">
+    <row r="1032" spans="3:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="C1032" t="s">
         <v>129</v>
       </c>
@@ -35903,7 +35942,7 @@
         <v>1632</v>
       </c>
     </row>
-    <row r="1033" spans="3:13" x14ac:dyDescent="0.3">
+    <row r="1033" spans="3:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="C1033" t="s">
         <v>129</v>
       </c>
@@ -35929,7 +35968,7 @@
         <v>1632</v>
       </c>
     </row>
-    <row r="1034" spans="3:13" x14ac:dyDescent="0.3">
+    <row r="1034" spans="3:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="C1034" t="s">
         <v>129</v>
       </c>
@@ -35955,7 +35994,7 @@
         <v>1632</v>
       </c>
     </row>
-    <row r="1035" spans="3:13" x14ac:dyDescent="0.3">
+    <row r="1035" spans="3:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="C1035" t="s">
         <v>129</v>
       </c>
@@ -35981,7 +36020,7 @@
         <v>1632</v>
       </c>
     </row>
-    <row r="1036" spans="3:13" x14ac:dyDescent="0.3">
+    <row r="1036" spans="3:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="C1036" t="s">
         <v>129</v>
       </c>
@@ -36007,7 +36046,7 @@
         <v>1632</v>
       </c>
     </row>
-    <row r="1037" spans="3:13" x14ac:dyDescent="0.3">
+    <row r="1037" spans="3:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="C1037" t="s">
         <v>129</v>
       </c>
@@ -36033,7 +36072,7 @@
         <v>1632</v>
       </c>
     </row>
-    <row r="1038" spans="3:13" x14ac:dyDescent="0.3">
+    <row r="1038" spans="3:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="C1038" t="s">
         <v>303</v>
       </c>
@@ -36059,7 +36098,7 @@
         <v>1634</v>
       </c>
     </row>
-    <row r="1039" spans="3:13" x14ac:dyDescent="0.3">
+    <row r="1039" spans="3:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="C1039" t="s">
         <v>303</v>
       </c>
@@ -36085,7 +36124,7 @@
         <v>1634</v>
       </c>
     </row>
-    <row r="1040" spans="3:13" x14ac:dyDescent="0.3">
+    <row r="1040" spans="3:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="C1040" t="s">
         <v>303</v>
       </c>
@@ -36111,7 +36150,7 @@
         <v>1634</v>
       </c>
     </row>
-    <row r="1041" spans="3:13" x14ac:dyDescent="0.3">
+    <row r="1041" spans="2:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="C1041" t="s">
         <v>303</v>
       </c>
@@ -36137,8 +36176,167 @@
         <v>1634</v>
       </c>
     </row>
+    <row r="1042" spans="2:13" hidden="1" x14ac:dyDescent="0.3">
+      <c r="B1042" t="s">
+        <v>137</v>
+      </c>
+      <c r="C1042" t="s">
+        <v>1424</v>
+      </c>
+      <c r="D1042" t="s">
+        <v>1688</v>
+      </c>
+      <c r="E1042" s="5">
+        <v>46298</v>
+      </c>
+      <c r="G1042" t="s">
+        <v>15</v>
+      </c>
+      <c r="H1042" t="s">
+        <v>417</v>
+      </c>
+      <c r="I1042">
+        <v>1</v>
+      </c>
+      <c r="K1042" t="s">
+        <v>1689</v>
+      </c>
+      <c r="L1042" t="s">
+        <v>1690</v>
+      </c>
+      <c r="M1042" t="s">
+        <v>1691</v>
+      </c>
+    </row>
+    <row r="1043" spans="2:13" hidden="1" x14ac:dyDescent="0.3">
+      <c r="B1043" t="s">
+        <v>137</v>
+      </c>
+      <c r="C1043" t="s">
+        <v>1424</v>
+      </c>
+      <c r="D1043" t="s">
+        <v>1688</v>
+      </c>
+      <c r="E1043" s="5">
+        <v>46298</v>
+      </c>
+      <c r="G1043" t="s">
+        <v>15</v>
+      </c>
+      <c r="H1043" t="s">
+        <v>421</v>
+      </c>
+      <c r="I1043">
+        <v>1</v>
+      </c>
+      <c r="K1043" t="s">
+        <v>1692</v>
+      </c>
+      <c r="L1043" t="s">
+        <v>1693</v>
+      </c>
+      <c r="M1043" t="s">
+        <v>1691</v>
+      </c>
+    </row>
+    <row r="1044" spans="2:13" hidden="1" x14ac:dyDescent="0.3">
+      <c r="B1044" t="s">
+        <v>137</v>
+      </c>
+      <c r="C1044" t="s">
+        <v>1424</v>
+      </c>
+      <c r="D1044" t="s">
+        <v>1688</v>
+      </c>
+      <c r="E1044" s="5">
+        <v>46298</v>
+      </c>
+      <c r="G1044" t="s">
+        <v>15</v>
+      </c>
+      <c r="H1044" t="s">
+        <v>1694</v>
+      </c>
+      <c r="I1044">
+        <v>0</v>
+      </c>
+      <c r="L1044" t="s">
+        <v>1699</v>
+      </c>
+      <c r="M1044" t="s">
+        <v>1691</v>
+      </c>
+    </row>
+    <row r="1045" spans="2:13" hidden="1" x14ac:dyDescent="0.3">
+      <c r="B1045" t="s">
+        <v>137</v>
+      </c>
+      <c r="C1045" t="s">
+        <v>1424</v>
+      </c>
+      <c r="D1045" t="s">
+        <v>1688</v>
+      </c>
+      <c r="E1045" s="5">
+        <v>46298</v>
+      </c>
+      <c r="G1045" t="s">
+        <v>15</v>
+      </c>
+      <c r="H1045" t="s">
+        <v>1695</v>
+      </c>
+      <c r="I1045">
+        <v>0</v>
+      </c>
+      <c r="L1045" t="s">
+        <v>1696</v>
+      </c>
+      <c r="M1045" t="s">
+        <v>1691</v>
+      </c>
+    </row>
+    <row r="1046" spans="2:13" hidden="1" x14ac:dyDescent="0.3">
+      <c r="B1046" t="s">
+        <v>137</v>
+      </c>
+      <c r="C1046" t="s">
+        <v>1424</v>
+      </c>
+      <c r="D1046" t="s">
+        <v>1688</v>
+      </c>
+      <c r="E1046" s="5">
+        <v>46298</v>
+      </c>
+      <c r="G1046" t="s">
+        <v>15</v>
+      </c>
+      <c r="H1046" t="s">
+        <v>1697</v>
+      </c>
+      <c r="I1046">
+        <v>0</v>
+      </c>
+      <c r="L1046" t="s">
+        <v>1698</v>
+      </c>
+      <c r="M1046" t="s">
+        <v>1691</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:M1041" xr:uid="{00000000-0009-0000-0000-000000000000}"/>
+  <autoFilter ref="A1:M1046" xr:uid="{00000000-0001-0000-0000-000000000000}">
+    <filterColumn colId="3">
+      <filters>
+        <filter val="Copa Konomi"/>
+        <filter val="Copa Konomi - Nuevos Valores"/>
+        <filter val="II Torneo Konomi"/>
+      </filters>
+    </filterColumn>
+  </autoFilter>
   <hyperlinks>
     <hyperlink ref="M14" r:id="rId1" xr:uid="{00000000-0004-0000-0000-000000000000}"/>
     <hyperlink ref="M15" r:id="rId2" xr:uid="{00000000-0004-0000-0000-000001000000}"/>

--- a/data/raw/copas_y_torneos.xlsx
+++ b/data/raw/copas_y_torneos.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Projects\gateball\kantokeando-data\data\raw\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AC7ACE5C-4C2C-4914-A25F-FBF63FEC39F2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{951D83D9-A38A-48DA-9FC9-41C9A06ECD19}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -48,7 +48,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="8210" uniqueCount="1707">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="8216" uniqueCount="1712">
   <si>
     <t>id_torneo</t>
   </si>
@@ -5169,6 +5169,21 @@
   </si>
   <si>
     <t>En curso</t>
+  </si>
+  <si>
+    <t>Gushiken Manuel, Tsukazan Sechan, Nagamine Taeko, Yoshiko Kanashiro, Kiyan Miyoko</t>
+  </si>
+  <si>
+    <t>Miyagui Haruko, Tsuhako Hiroshi, Sakihara Carlos, Yoshiko Takehara, Seiki Miyashiro, William Nakahodo</t>
+  </si>
+  <si>
+    <t>Miyagui Haruko, Sakihara Carlos, Tamanaha Haruko</t>
+  </si>
+  <si>
+    <t>Raul Tengan, Gaby Tokumori, Julia Nakayoshi, Gladys Tengan, Yamashiro Mercedes</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> </t>
   </si>
 </sst>
 </file>
@@ -5366,7 +5381,7 @@
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="29">
+  <cellXfs count="31">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -5424,6 +5439,8 @@
     <xf numFmtId="9" fontId="14" fillId="6" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="3">
     <cellStyle name="Hipervínculo" xfId="1" builtinId="8"/>
@@ -5741,7 +5758,6 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <sheetPr filterMode="1"/>
   <dimension ref="A1:M1049"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.88671875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
@@ -5800,7 +5816,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="2" spans="1:13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A2" s="6" t="s">
         <v>13</v>
       </c>
@@ -5833,7 +5849,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="3" spans="1:13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A3" s="6"/>
       <c r="B3" s="6"/>
       <c r="C3" s="6"/>
@@ -5864,7 +5880,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="4" spans="1:13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A4" s="6"/>
       <c r="B4" s="6"/>
       <c r="C4" s="6"/>
@@ -5895,7 +5911,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="5" spans="1:13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:13" x14ac:dyDescent="0.3">
       <c r="D5" s="6" t="s">
         <v>14</v>
       </c>
@@ -5922,7 +5938,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="6" spans="1:13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:13" x14ac:dyDescent="0.3">
       <c r="C6" t="s">
         <v>27</v>
       </c>
@@ -5952,7 +5968,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="7" spans="1:13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:13" x14ac:dyDescent="0.3">
       <c r="C7" t="s">
         <v>27</v>
       </c>
@@ -5982,7 +5998,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="8" spans="1:13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:13" x14ac:dyDescent="0.3">
       <c r="C8" t="s">
         <v>27</v>
       </c>
@@ -6012,7 +6028,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="9" spans="1:13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:13" x14ac:dyDescent="0.3">
       <c r="C9" t="s">
         <v>27</v>
       </c>
@@ -6042,7 +6058,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="10" spans="1:13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:13" x14ac:dyDescent="0.3">
       <c r="C10" t="s">
         <v>27</v>
       </c>
@@ -6072,7 +6088,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="11" spans="1:13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:13" x14ac:dyDescent="0.3">
       <c r="C11" t="s">
         <v>27</v>
       </c>
@@ -6102,7 +6118,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="12" spans="1:13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:13" x14ac:dyDescent="0.3">
       <c r="C12" t="s">
         <v>27</v>
       </c>
@@ -6132,7 +6148,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="13" spans="1:13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:13" x14ac:dyDescent="0.3">
       <c r="C13" t="s">
         <v>27</v>
       </c>
@@ -6162,7 +6178,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="14" spans="1:13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:13" x14ac:dyDescent="0.3">
       <c r="C14" t="s">
         <v>45</v>
       </c>
@@ -6192,7 +6208,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="15" spans="1:13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:13" x14ac:dyDescent="0.3">
       <c r="C15" t="s">
         <v>45</v>
       </c>
@@ -6222,7 +6238,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="16" spans="1:13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:13" x14ac:dyDescent="0.3">
       <c r="C16" t="s">
         <v>45</v>
       </c>
@@ -6252,7 +6268,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="17" spans="3:13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="17" spans="3:13" x14ac:dyDescent="0.3">
       <c r="C17" t="s">
         <v>45</v>
       </c>
@@ -6282,7 +6298,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="18" spans="3:13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="18" spans="3:13" x14ac:dyDescent="0.3">
       <c r="C18" t="s">
         <v>45</v>
       </c>
@@ -6312,7 +6328,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="19" spans="3:13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="19" spans="3:13" x14ac:dyDescent="0.3">
       <c r="C19" t="s">
         <v>45</v>
       </c>
@@ -6338,11 +6354,11 @@
       <c r="L19" s="9" t="s">
         <v>58</v>
       </c>
-      <c r="M19" s="11" t="s">
+      <c r="M19" s="3" t="s">
         <v>48</v>
       </c>
     </row>
-    <row r="20" spans="3:13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="20" spans="3:13" x14ac:dyDescent="0.3">
       <c r="C20" t="s">
         <v>59</v>
       </c>
@@ -6369,7 +6385,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="21" spans="3:13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="21" spans="3:13" x14ac:dyDescent="0.3">
       <c r="C21" t="s">
         <v>59</v>
       </c>
@@ -6396,7 +6412,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="22" spans="3:13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="22" spans="3:13" x14ac:dyDescent="0.3">
       <c r="C22" t="s">
         <v>59</v>
       </c>
@@ -6423,7 +6439,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="23" spans="3:13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="23" spans="3:13" x14ac:dyDescent="0.3">
       <c r="C23" t="s">
         <v>59</v>
       </c>
@@ -6450,7 +6466,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="24" spans="3:13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="24" spans="3:13" x14ac:dyDescent="0.3">
       <c r="C24" t="s">
         <v>69</v>
       </c>
@@ -6477,7 +6493,7 @@
         <v>74</v>
       </c>
     </row>
-    <row r="25" spans="3:13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="25" spans="3:13" x14ac:dyDescent="0.3">
       <c r="C25" t="s">
         <v>69</v>
       </c>
@@ -6504,7 +6520,7 @@
         <v>74</v>
       </c>
     </row>
-    <row r="26" spans="3:13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="26" spans="3:13" x14ac:dyDescent="0.3">
       <c r="C26" t="s">
         <v>69</v>
       </c>
@@ -6531,7 +6547,7 @@
         <v>74</v>
       </c>
     </row>
-    <row r="27" spans="3:13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="27" spans="3:13" x14ac:dyDescent="0.3">
       <c r="C27" t="s">
         <v>69</v>
       </c>
@@ -6558,7 +6574,7 @@
         <v>74</v>
       </c>
     </row>
-    <row r="28" spans="3:13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="28" spans="3:13" x14ac:dyDescent="0.3">
       <c r="C28" t="s">
         <v>79</v>
       </c>
@@ -6585,7 +6601,7 @@
         <v>83</v>
       </c>
     </row>
-    <row r="29" spans="3:13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="29" spans="3:13" x14ac:dyDescent="0.3">
       <c r="C29" t="s">
         <v>79</v>
       </c>
@@ -6612,7 +6628,7 @@
         <v>83</v>
       </c>
     </row>
-    <row r="30" spans="3:13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="30" spans="3:13" x14ac:dyDescent="0.3">
       <c r="C30" t="s">
         <v>79</v>
       </c>
@@ -6639,7 +6655,7 @@
         <v>83</v>
       </c>
     </row>
-    <row r="31" spans="3:13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="31" spans="3:13" x14ac:dyDescent="0.3">
       <c r="C31" t="s">
         <v>79</v>
       </c>
@@ -6666,7 +6682,7 @@
         <v>83</v>
       </c>
     </row>
-    <row r="32" spans="3:13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="32" spans="3:13" x14ac:dyDescent="0.3">
       <c r="C32" t="s">
         <v>90</v>
       </c>
@@ -6693,7 +6709,7 @@
         <v>94</v>
       </c>
     </row>
-    <row r="33" spans="3:13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="33" spans="3:13" x14ac:dyDescent="0.3">
       <c r="C33" t="s">
         <v>90</v>
       </c>
@@ -6720,7 +6736,7 @@
         <v>94</v>
       </c>
     </row>
-    <row r="34" spans="3:13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="34" spans="3:13" x14ac:dyDescent="0.3">
       <c r="C34" t="s">
         <v>90</v>
       </c>
@@ -6747,7 +6763,7 @@
         <v>94</v>
       </c>
     </row>
-    <row r="35" spans="3:13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="35" spans="3:13" x14ac:dyDescent="0.3">
       <c r="C35" t="s">
         <v>90</v>
       </c>
@@ -6774,7 +6790,7 @@
         <v>94</v>
       </c>
     </row>
-    <row r="36" spans="3:13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="36" spans="3:13" x14ac:dyDescent="0.3">
       <c r="C36" t="s">
         <v>101</v>
       </c>
@@ -6801,7 +6817,7 @@
         <v>105</v>
       </c>
     </row>
-    <row r="37" spans="3:13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="37" spans="3:13" x14ac:dyDescent="0.3">
       <c r="C37" t="s">
         <v>101</v>
       </c>
@@ -6828,7 +6844,7 @@
         <v>105</v>
       </c>
     </row>
-    <row r="38" spans="3:13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="38" spans="3:13" x14ac:dyDescent="0.3">
       <c r="C38" t="s">
         <v>101</v>
       </c>
@@ -6855,7 +6871,7 @@
         <v>105</v>
       </c>
     </row>
-    <row r="39" spans="3:13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="39" spans="3:13" x14ac:dyDescent="0.3">
       <c r="C39" t="s">
         <v>101</v>
       </c>
@@ -6882,7 +6898,7 @@
         <v>105</v>
       </c>
     </row>
-    <row r="40" spans="3:13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="40" spans="3:13" x14ac:dyDescent="0.3">
       <c r="C40" t="s">
         <v>110</v>
       </c>
@@ -6909,7 +6925,7 @@
         <v>114</v>
       </c>
     </row>
-    <row r="41" spans="3:13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="41" spans="3:13" x14ac:dyDescent="0.3">
       <c r="C41" t="s">
         <v>110</v>
       </c>
@@ -6936,7 +6952,7 @@
         <v>114</v>
       </c>
     </row>
-    <row r="42" spans="3:13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="42" spans="3:13" x14ac:dyDescent="0.3">
       <c r="C42" t="s">
         <v>110</v>
       </c>
@@ -6963,7 +6979,7 @@
         <v>114</v>
       </c>
     </row>
-    <row r="43" spans="3:13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="43" spans="3:13" x14ac:dyDescent="0.3">
       <c r="C43" t="s">
         <v>110</v>
       </c>
@@ -6990,7 +7006,7 @@
         <v>114</v>
       </c>
     </row>
-    <row r="44" spans="3:13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="44" spans="3:13" x14ac:dyDescent="0.3">
       <c r="C44" t="s">
         <v>110</v>
       </c>
@@ -7017,7 +7033,7 @@
         <v>124</v>
       </c>
     </row>
-    <row r="45" spans="3:13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="45" spans="3:13" x14ac:dyDescent="0.3">
       <c r="C45" t="s">
         <v>110</v>
       </c>
@@ -7044,7 +7060,7 @@
         <v>124</v>
       </c>
     </row>
-    <row r="46" spans="3:13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="46" spans="3:13" x14ac:dyDescent="0.3">
       <c r="C46" t="s">
         <v>110</v>
       </c>
@@ -7071,7 +7087,7 @@
         <v>124</v>
       </c>
     </row>
-    <row r="47" spans="3:13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="47" spans="3:13" x14ac:dyDescent="0.3">
       <c r="C47" t="s">
         <v>110</v>
       </c>
@@ -7098,7 +7114,7 @@
         <v>124</v>
       </c>
     </row>
-    <row r="48" spans="3:13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="48" spans="3:13" x14ac:dyDescent="0.3">
       <c r="C48" t="s">
         <v>129</v>
       </c>
@@ -7125,7 +7141,7 @@
         <v>132</v>
       </c>
     </row>
-    <row r="49" spans="2:13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="49" spans="2:13" x14ac:dyDescent="0.3">
       <c r="C49" t="s">
         <v>129</v>
       </c>
@@ -7152,7 +7168,7 @@
         <v>132</v>
       </c>
     </row>
-    <row r="50" spans="2:13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="50" spans="2:13" x14ac:dyDescent="0.3">
       <c r="C50" t="s">
         <v>129</v>
       </c>
@@ -7179,7 +7195,7 @@
         <v>132</v>
       </c>
     </row>
-    <row r="51" spans="2:13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="51" spans="2:13" x14ac:dyDescent="0.3">
       <c r="C51" t="s">
         <v>129</v>
       </c>
@@ -7206,7 +7222,7 @@
         <v>132</v>
       </c>
     </row>
-    <row r="52" spans="2:13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="52" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B52" t="s">
         <v>137</v>
       </c>
@@ -7233,7 +7249,7 @@
         <v>141</v>
       </c>
     </row>
-    <row r="53" spans="2:13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="53" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B53" t="s">
         <v>137</v>
       </c>
@@ -7260,7 +7276,7 @@
         <v>141</v>
       </c>
     </row>
-    <row r="54" spans="2:13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="54" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B54" t="s">
         <v>137</v>
       </c>
@@ -7287,7 +7303,7 @@
         <v>147</v>
       </c>
     </row>
-    <row r="55" spans="2:13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="55" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B55" t="s">
         <v>137</v>
       </c>
@@ -7314,7 +7330,7 @@
         <v>147</v>
       </c>
     </row>
-    <row r="56" spans="2:13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="56" spans="2:13" x14ac:dyDescent="0.3">
       <c r="C56" t="s">
         <v>150</v>
       </c>
@@ -7341,7 +7357,7 @@
         <v>153</v>
       </c>
     </row>
-    <row r="57" spans="2:13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="57" spans="2:13" x14ac:dyDescent="0.3">
       <c r="C57" t="s">
         <v>154</v>
       </c>
@@ -7368,7 +7384,7 @@
         <v>157</v>
       </c>
     </row>
-    <row r="58" spans="2:13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="58" spans="2:13" x14ac:dyDescent="0.3">
       <c r="C58" t="s">
         <v>154</v>
       </c>
@@ -7395,7 +7411,7 @@
         <v>157</v>
       </c>
     </row>
-    <row r="59" spans="2:13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="59" spans="2:13" x14ac:dyDescent="0.3">
       <c r="C59" t="s">
         <v>154</v>
       </c>
@@ -7422,7 +7438,7 @@
         <v>157</v>
       </c>
     </row>
-    <row r="60" spans="2:13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="60" spans="2:13" x14ac:dyDescent="0.3">
       <c r="C60" t="s">
         <v>154</v>
       </c>
@@ -7449,7 +7465,7 @@
         <v>157</v>
       </c>
     </row>
-    <row r="61" spans="2:13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="61" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B61" t="s">
         <v>162</v>
       </c>
@@ -7479,7 +7495,7 @@
         <v>167</v>
       </c>
     </row>
-    <row r="62" spans="2:13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="62" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B62" t="s">
         <v>162</v>
       </c>
@@ -7509,7 +7525,7 @@
         <v>167</v>
       </c>
     </row>
-    <row r="63" spans="2:13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="63" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B63" t="s">
         <v>162</v>
       </c>
@@ -7539,7 +7555,7 @@
         <v>167</v>
       </c>
     </row>
-    <row r="64" spans="2:13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="64" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B64" t="s">
         <v>162</v>
       </c>
@@ -7569,7 +7585,7 @@
         <v>167</v>
       </c>
     </row>
-    <row r="65" spans="2:13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="65" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B65" t="s">
         <v>162</v>
       </c>
@@ -7599,7 +7615,7 @@
         <v>167</v>
       </c>
     </row>
-    <row r="66" spans="2:13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="66" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B66" t="s">
         <v>162</v>
       </c>
@@ -7629,7 +7645,7 @@
         <v>167</v>
       </c>
     </row>
-    <row r="67" spans="2:13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="67" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B67" t="s">
         <v>162</v>
       </c>
@@ -7659,7 +7675,7 @@
         <v>167</v>
       </c>
     </row>
-    <row r="68" spans="2:13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="68" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B68" t="s">
         <v>162</v>
       </c>
@@ -7689,7 +7705,7 @@
         <v>167</v>
       </c>
     </row>
-    <row r="69" spans="2:13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="69" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B69" t="s">
         <v>162</v>
       </c>
@@ -7719,7 +7735,7 @@
         <v>167</v>
       </c>
     </row>
-    <row r="70" spans="2:13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="70" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B70" t="s">
         <v>162</v>
       </c>
@@ -7749,7 +7765,7 @@
         <v>184</v>
       </c>
     </row>
-    <row r="71" spans="2:13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="71" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B71" t="s">
         <v>162</v>
       </c>
@@ -7779,7 +7795,7 @@
         <v>184</v>
       </c>
     </row>
-    <row r="72" spans="2:13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="72" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B72" t="s">
         <v>162</v>
       </c>
@@ -7809,7 +7825,7 @@
         <v>184</v>
       </c>
     </row>
-    <row r="73" spans="2:13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="73" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B73" t="s">
         <v>162</v>
       </c>
@@ -7839,7 +7855,7 @@
         <v>184</v>
       </c>
     </row>
-    <row r="74" spans="2:13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="74" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B74" t="s">
         <v>162</v>
       </c>
@@ -7869,7 +7885,7 @@
         <v>184</v>
       </c>
     </row>
-    <row r="75" spans="2:13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="75" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B75" t="s">
         <v>162</v>
       </c>
@@ -7899,7 +7915,7 @@
         <v>184</v>
       </c>
     </row>
-    <row r="76" spans="2:13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="76" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B76" t="s">
         <v>162</v>
       </c>
@@ -7929,7 +7945,7 @@
         <v>184</v>
       </c>
     </row>
-    <row r="77" spans="2:13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="77" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B77" t="s">
         <v>162</v>
       </c>
@@ -7959,7 +7975,7 @@
         <v>184</v>
       </c>
     </row>
-    <row r="78" spans="2:13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="78" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B78" t="s">
         <v>162</v>
       </c>
@@ -7989,7 +8005,7 @@
         <v>184</v>
       </c>
     </row>
-    <row r="79" spans="2:13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="79" spans="2:13" x14ac:dyDescent="0.3">
       <c r="C79" t="s">
         <v>79</v>
       </c>
@@ -8016,7 +8032,7 @@
         <v>198</v>
       </c>
     </row>
-    <row r="80" spans="2:13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="80" spans="2:13" x14ac:dyDescent="0.3">
       <c r="C80" t="s">
         <v>79</v>
       </c>
@@ -8043,7 +8059,7 @@
         <v>198</v>
       </c>
     </row>
-    <row r="81" spans="3:13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="81" spans="3:13" x14ac:dyDescent="0.3">
       <c r="C81" t="s">
         <v>79</v>
       </c>
@@ -8070,7 +8086,7 @@
         <v>198</v>
       </c>
     </row>
-    <row r="82" spans="3:13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="82" spans="3:13" x14ac:dyDescent="0.3">
       <c r="C82" t="s">
         <v>79</v>
       </c>
@@ -8097,7 +8113,7 @@
         <v>198</v>
       </c>
     </row>
-    <row r="83" spans="3:13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="83" spans="3:13" x14ac:dyDescent="0.3">
       <c r="C83" t="s">
         <v>45</v>
       </c>
@@ -8127,7 +8143,7 @@
         <v>207</v>
       </c>
     </row>
-    <row r="84" spans="3:13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="84" spans="3:13" x14ac:dyDescent="0.3">
       <c r="C84" t="s">
         <v>45</v>
       </c>
@@ -8157,7 +8173,7 @@
         <v>207</v>
       </c>
     </row>
-    <row r="85" spans="3:13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="85" spans="3:13" x14ac:dyDescent="0.3">
       <c r="C85" t="s">
         <v>45</v>
       </c>
@@ -8187,7 +8203,7 @@
         <v>207</v>
       </c>
     </row>
-    <row r="86" spans="3:13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="86" spans="3:13" x14ac:dyDescent="0.3">
       <c r="C86" t="s">
         <v>45</v>
       </c>
@@ -8217,7 +8233,7 @@
         <v>207</v>
       </c>
     </row>
-    <row r="87" spans="3:13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="87" spans="3:13" x14ac:dyDescent="0.3">
       <c r="C87" t="s">
         <v>45</v>
       </c>
@@ -8247,7 +8263,7 @@
         <v>207</v>
       </c>
     </row>
-    <row r="88" spans="3:13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="88" spans="3:13" x14ac:dyDescent="0.3">
       <c r="C88" t="s">
         <v>45</v>
       </c>
@@ -8277,7 +8293,7 @@
         <v>207</v>
       </c>
     </row>
-    <row r="89" spans="3:13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="89" spans="3:13" x14ac:dyDescent="0.3">
       <c r="C89" t="s">
         <v>59</v>
       </c>
@@ -8304,7 +8320,7 @@
         <v>214</v>
       </c>
     </row>
-    <row r="90" spans="3:13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="90" spans="3:13" x14ac:dyDescent="0.3">
       <c r="C90" t="s">
         <v>59</v>
       </c>
@@ -8331,7 +8347,7 @@
         <v>214</v>
       </c>
     </row>
-    <row r="91" spans="3:13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="91" spans="3:13" x14ac:dyDescent="0.3">
       <c r="C91" t="s">
         <v>59</v>
       </c>
@@ -8358,7 +8374,7 @@
         <v>214</v>
       </c>
     </row>
-    <row r="92" spans="3:13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="92" spans="3:13" x14ac:dyDescent="0.3">
       <c r="C92" t="s">
         <v>59</v>
       </c>
@@ -8385,7 +8401,7 @@
         <v>214</v>
       </c>
     </row>
-    <row r="93" spans="3:13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="93" spans="3:13" x14ac:dyDescent="0.3">
       <c r="C93" t="s">
         <v>69</v>
       </c>
@@ -8412,7 +8428,7 @@
         <v>219</v>
       </c>
     </row>
-    <row r="94" spans="3:13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="94" spans="3:13" x14ac:dyDescent="0.3">
       <c r="C94" t="s">
         <v>69</v>
       </c>
@@ -8439,7 +8455,7 @@
         <v>219</v>
       </c>
     </row>
-    <row r="95" spans="3:13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="95" spans="3:13" x14ac:dyDescent="0.3">
       <c r="C95" t="s">
         <v>69</v>
       </c>
@@ -8466,7 +8482,7 @@
         <v>219</v>
       </c>
     </row>
-    <row r="96" spans="3:13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="96" spans="3:13" x14ac:dyDescent="0.3">
       <c r="C96" t="s">
         <v>69</v>
       </c>
@@ -8493,7 +8509,7 @@
         <v>219</v>
       </c>
     </row>
-    <row r="97" spans="2:13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="97" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B97" t="s">
         <v>137</v>
       </c>
@@ -8523,7 +8539,7 @@
         <v>229</v>
       </c>
     </row>
-    <row r="98" spans="2:13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="98" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B98" t="s">
         <v>137</v>
       </c>
@@ -8553,7 +8569,7 @@
         <v>229</v>
       </c>
     </row>
-    <row r="99" spans="2:13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="99" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B99" t="s">
         <v>137</v>
       </c>
@@ -8583,7 +8599,7 @@
         <v>229</v>
       </c>
     </row>
-    <row r="100" spans="2:13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="100" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B100" t="s">
         <v>162</v>
       </c>
@@ -8613,7 +8629,7 @@
         <v>237</v>
       </c>
     </row>
-    <row r="101" spans="2:13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="101" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B101" t="s">
         <v>162</v>
       </c>
@@ -8636,11 +8652,14 @@
       <c r="K101" s="9" t="s">
         <v>238</v>
       </c>
+      <c r="L101" s="29" t="s">
+        <v>1707</v>
+      </c>
       <c r="M101" s="3" t="s">
         <v>237</v>
       </c>
     </row>
-    <row r="102" spans="2:13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="102" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B102" t="s">
         <v>162</v>
       </c>
@@ -8663,11 +8682,14 @@
       <c r="K102" s="9" t="s">
         <v>239</v>
       </c>
+      <c r="L102" t="s">
+        <v>1708</v>
+      </c>
       <c r="M102" s="3" t="s">
         <v>237</v>
       </c>
     </row>
-    <row r="103" spans="2:13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="103" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B103" t="s">
         <v>162</v>
       </c>
@@ -8697,7 +8719,7 @@
         <v>237</v>
       </c>
     </row>
-    <row r="104" spans="2:13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="104" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B104" t="s">
         <v>162</v>
       </c>
@@ -8720,11 +8742,14 @@
       <c r="K104" s="9" t="s">
         <v>205</v>
       </c>
+      <c r="L104" s="30" t="s">
+        <v>1710</v>
+      </c>
       <c r="M104" s="3" t="s">
         <v>237</v>
       </c>
     </row>
-    <row r="105" spans="2:13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="105" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B105" t="s">
         <v>162</v>
       </c>
@@ -8747,11 +8772,14 @@
       <c r="K105" s="9" t="s">
         <v>241</v>
       </c>
+      <c r="L105" s="30" t="s">
+        <v>1711</v>
+      </c>
       <c r="M105" s="3" t="s">
         <v>237</v>
       </c>
     </row>
-    <row r="106" spans="2:13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="106" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B106" t="s">
         <v>162</v>
       </c>
@@ -8778,7 +8806,7 @@
         <v>237</v>
       </c>
     </row>
-    <row r="107" spans="2:13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="107" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B107" t="s">
         <v>162</v>
       </c>
@@ -8805,7 +8833,7 @@
         <v>237</v>
       </c>
     </row>
-    <row r="108" spans="2:13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="108" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B108" t="s">
         <v>162</v>
       </c>
@@ -8828,11 +8856,14 @@
       <c r="K108" s="9" t="s">
         <v>43</v>
       </c>
+      <c r="L108" t="s">
+        <v>281</v>
+      </c>
       <c r="M108" s="3" t="s">
         <v>237</v>
       </c>
     </row>
-    <row r="109" spans="2:13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="109" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B109" t="s">
         <v>162</v>
       </c>
@@ -8859,7 +8890,7 @@
         <v>237</v>
       </c>
     </row>
-    <row r="110" spans="2:13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="110" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B110" t="s">
         <v>162</v>
       </c>
@@ -8886,7 +8917,7 @@
         <v>237</v>
       </c>
     </row>
-    <row r="111" spans="2:13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="111" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B111" t="s">
         <v>162</v>
       </c>
@@ -8913,7 +8944,7 @@
         <v>237</v>
       </c>
     </row>
-    <row r="112" spans="2:13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="112" spans="2:13" x14ac:dyDescent="0.3">
       <c r="C112" t="s">
         <v>90</v>
       </c>
@@ -8940,7 +8971,7 @@
         <v>247</v>
       </c>
     </row>
-    <row r="113" spans="2:13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="113" spans="2:13" x14ac:dyDescent="0.3">
       <c r="C113" t="s">
         <v>90</v>
       </c>
@@ -8967,7 +8998,7 @@
         <v>247</v>
       </c>
     </row>
-    <row r="114" spans="2:13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="114" spans="2:13" x14ac:dyDescent="0.3">
       <c r="C114" t="s">
         <v>90</v>
       </c>
@@ -8994,7 +9025,7 @@
         <v>247</v>
       </c>
     </row>
-    <row r="115" spans="2:13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="115" spans="2:13" x14ac:dyDescent="0.3">
       <c r="C115" t="s">
         <v>90</v>
       </c>
@@ -9021,7 +9052,7 @@
         <v>247</v>
       </c>
     </row>
-    <row r="116" spans="2:13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="116" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B116" t="s">
         <v>137</v>
       </c>
@@ -9048,7 +9079,7 @@
         <v>255</v>
       </c>
     </row>
-    <row r="117" spans="2:13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="117" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B117" t="s">
         <v>137</v>
       </c>
@@ -9075,7 +9106,7 @@
         <v>255</v>
       </c>
     </row>
-    <row r="118" spans="2:13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="118" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B118" t="s">
         <v>137</v>
       </c>
@@ -9102,7 +9133,7 @@
         <v>255</v>
       </c>
     </row>
-    <row r="119" spans="2:13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="119" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B119" t="s">
         <v>137</v>
       </c>
@@ -9129,7 +9160,7 @@
         <v>255</v>
       </c>
     </row>
-    <row r="120" spans="2:13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="120" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B120" t="s">
         <v>137</v>
       </c>
@@ -9156,7 +9187,7 @@
         <v>265</v>
       </c>
     </row>
-    <row r="121" spans="2:13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="121" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B121" t="s">
         <v>137</v>
       </c>
@@ -9183,7 +9214,7 @@
         <v>265</v>
       </c>
     </row>
-    <row r="122" spans="2:13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="122" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B122" t="s">
         <v>137</v>
       </c>
@@ -9210,7 +9241,7 @@
         <v>265</v>
       </c>
     </row>
-    <row r="123" spans="2:13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="123" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B123" t="s">
         <v>137</v>
       </c>
@@ -9237,7 +9268,7 @@
         <v>265</v>
       </c>
     </row>
-    <row r="124" spans="2:13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="124" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B124" t="s">
         <v>162</v>
       </c>
@@ -9267,7 +9298,7 @@
         <v>273</v>
       </c>
     </row>
-    <row r="125" spans="2:13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="125" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B125" t="s">
         <v>162</v>
       </c>
@@ -9297,7 +9328,7 @@
         <v>273</v>
       </c>
     </row>
-    <row r="126" spans="2:13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="126" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B126" t="s">
         <v>162</v>
       </c>
@@ -9327,7 +9358,7 @@
         <v>273</v>
       </c>
     </row>
-    <row r="127" spans="2:13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="127" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B127" t="s">
         <v>162</v>
       </c>
@@ -9357,7 +9388,7 @@
         <v>273</v>
       </c>
     </row>
-    <row r="128" spans="2:13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="128" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B128" t="s">
         <v>162</v>
       </c>
@@ -9387,7 +9418,7 @@
         <v>273</v>
       </c>
     </row>
-    <row r="129" spans="2:13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="129" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B129" t="s">
         <v>162</v>
       </c>
@@ -9417,7 +9448,7 @@
         <v>273</v>
       </c>
     </row>
-    <row r="130" spans="2:13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="130" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B130" t="s">
         <v>162</v>
       </c>
@@ -9447,7 +9478,7 @@
         <v>273</v>
       </c>
     </row>
-    <row r="131" spans="2:13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="131" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B131" t="s">
         <v>162</v>
       </c>
@@ -9477,7 +9508,7 @@
         <v>273</v>
       </c>
     </row>
-    <row r="132" spans="2:13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="132" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B132" t="s">
         <v>162</v>
       </c>
@@ -9507,7 +9538,7 @@
         <v>273</v>
       </c>
     </row>
-    <row r="133" spans="2:13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="133" spans="2:13" x14ac:dyDescent="0.3">
       <c r="C133" t="s">
         <v>129</v>
       </c>
@@ -9534,7 +9565,7 @@
         <v>284</v>
       </c>
     </row>
-    <row r="134" spans="2:13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="134" spans="2:13" x14ac:dyDescent="0.3">
       <c r="C134" t="s">
         <v>129</v>
       </c>
@@ -9561,7 +9592,7 @@
         <v>284</v>
       </c>
     </row>
-    <row r="135" spans="2:13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="135" spans="2:13" x14ac:dyDescent="0.3">
       <c r="C135" t="s">
         <v>129</v>
       </c>
@@ -9588,7 +9619,7 @@
         <v>284</v>
       </c>
     </row>
-    <row r="136" spans="2:13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="136" spans="2:13" x14ac:dyDescent="0.3">
       <c r="C136" t="s">
         <v>129</v>
       </c>
@@ -9615,7 +9646,7 @@
         <v>284</v>
       </c>
     </row>
-    <row r="137" spans="2:13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="137" spans="2:13" x14ac:dyDescent="0.3">
       <c r="C137" t="s">
         <v>150</v>
       </c>
@@ -9642,7 +9673,7 @@
         <v>290</v>
       </c>
     </row>
-    <row r="138" spans="2:13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="138" spans="2:13" x14ac:dyDescent="0.3">
       <c r="C138" t="s">
         <v>150</v>
       </c>
@@ -9669,7 +9700,7 @@
         <v>290</v>
       </c>
     </row>
-    <row r="139" spans="2:13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="139" spans="2:13" x14ac:dyDescent="0.3">
       <c r="C139" t="s">
         <v>150</v>
       </c>
@@ -9696,7 +9727,7 @@
         <v>290</v>
       </c>
     </row>
-    <row r="140" spans="2:13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="140" spans="2:13" x14ac:dyDescent="0.3">
       <c r="C140" t="s">
         <v>150</v>
       </c>
@@ -9723,7 +9754,7 @@
         <v>290</v>
       </c>
     </row>
-    <row r="141" spans="2:13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="141" spans="2:13" x14ac:dyDescent="0.3">
       <c r="C141" t="s">
         <v>294</v>
       </c>
@@ -9753,7 +9784,7 @@
         <v>297</v>
       </c>
     </row>
-    <row r="142" spans="2:13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="142" spans="2:13" x14ac:dyDescent="0.3">
       <c r="C142" t="s">
         <v>294</v>
       </c>
@@ -9783,7 +9814,7 @@
         <v>297</v>
       </c>
     </row>
-    <row r="143" spans="2:13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="143" spans="2:13" x14ac:dyDescent="0.3">
       <c r="C143" t="s">
         <v>294</v>
       </c>
@@ -9813,7 +9844,7 @@
         <v>297</v>
       </c>
     </row>
-    <row r="144" spans="2:13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="144" spans="2:13" x14ac:dyDescent="0.3">
       <c r="C144" t="s">
         <v>294</v>
       </c>
@@ -9843,7 +9874,7 @@
         <v>297</v>
       </c>
     </row>
-    <row r="145" spans="2:13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="145" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B145" t="s">
         <v>302</v>
       </c>
@@ -9873,7 +9904,7 @@
         <v>307</v>
       </c>
     </row>
-    <row r="146" spans="2:13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="146" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B146" t="s">
         <v>302</v>
       </c>
@@ -9903,7 +9934,7 @@
         <v>307</v>
       </c>
     </row>
-    <row r="147" spans="2:13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="147" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B147" t="s">
         <v>302</v>
       </c>
@@ -9933,7 +9964,7 @@
         <v>307</v>
       </c>
     </row>
-    <row r="148" spans="2:13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="148" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B148" t="s">
         <v>302</v>
       </c>
@@ -9963,7 +9994,7 @@
         <v>307</v>
       </c>
     </row>
-    <row r="149" spans="2:13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="149" spans="2:13" x14ac:dyDescent="0.3">
       <c r="D149" t="s">
         <v>312</v>
       </c>
@@ -9990,7 +10021,7 @@
         <v>314</v>
       </c>
     </row>
-    <row r="150" spans="2:13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="150" spans="2:13" x14ac:dyDescent="0.3">
       <c r="D150" t="s">
         <v>312</v>
       </c>
@@ -10017,7 +10048,7 @@
         <v>314</v>
       </c>
     </row>
-    <row r="151" spans="2:13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="151" spans="2:13" x14ac:dyDescent="0.3">
       <c r="D151" t="s">
         <v>312</v>
       </c>
@@ -10044,7 +10075,7 @@
         <v>314</v>
       </c>
     </row>
-    <row r="152" spans="2:13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="152" spans="2:13" x14ac:dyDescent="0.3">
       <c r="D152" t="s">
         <v>312</v>
       </c>
@@ -10071,7 +10102,7 @@
         <v>314</v>
       </c>
     </row>
-    <row r="153" spans="2:13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="153" spans="2:13" x14ac:dyDescent="0.3">
       <c r="D153" t="s">
         <v>312</v>
       </c>
@@ -10098,7 +10129,7 @@
         <v>314</v>
       </c>
     </row>
-    <row r="154" spans="2:13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="154" spans="2:13" x14ac:dyDescent="0.3">
       <c r="D154" t="s">
         <v>312</v>
       </c>
@@ -10125,7 +10156,7 @@
         <v>314</v>
       </c>
     </row>
-    <row r="155" spans="2:13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="155" spans="2:13" x14ac:dyDescent="0.3">
       <c r="C155" t="s">
         <v>27</v>
       </c>
@@ -10155,7 +10186,7 @@
         <v>327</v>
       </c>
     </row>
-    <row r="156" spans="2:13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="156" spans="2:13" x14ac:dyDescent="0.3">
       <c r="C156" t="s">
         <v>27</v>
       </c>
@@ -10185,7 +10216,7 @@
         <v>327</v>
       </c>
     </row>
-    <row r="157" spans="2:13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="157" spans="2:13" x14ac:dyDescent="0.3">
       <c r="C157" t="s">
         <v>27</v>
       </c>
@@ -10215,7 +10246,7 @@
         <v>327</v>
       </c>
     </row>
-    <row r="158" spans="2:13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="158" spans="2:13" x14ac:dyDescent="0.3">
       <c r="C158" t="s">
         <v>27</v>
       </c>
@@ -10245,7 +10276,7 @@
         <v>327</v>
       </c>
     </row>
-    <row r="159" spans="2:13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="159" spans="2:13" x14ac:dyDescent="0.3">
       <c r="C159" t="s">
         <v>27</v>
       </c>
@@ -10275,7 +10306,7 @@
         <v>327</v>
       </c>
     </row>
-    <row r="160" spans="2:13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="160" spans="2:13" x14ac:dyDescent="0.3">
       <c r="C160" t="s">
         <v>27</v>
       </c>
@@ -10305,7 +10336,7 @@
         <v>327</v>
       </c>
     </row>
-    <row r="161" spans="3:13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="161" spans="3:13" x14ac:dyDescent="0.3">
       <c r="C161" t="s">
         <v>27</v>
       </c>
@@ -10335,7 +10366,7 @@
         <v>327</v>
       </c>
     </row>
-    <row r="162" spans="3:13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="162" spans="3:13" x14ac:dyDescent="0.3">
       <c r="C162" t="s">
         <v>27</v>
       </c>
@@ -10365,7 +10396,7 @@
         <v>327</v>
       </c>
     </row>
-    <row r="163" spans="3:13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="163" spans="3:13" x14ac:dyDescent="0.3">
       <c r="C163" t="s">
         <v>45</v>
       </c>
@@ -10395,7 +10426,7 @@
         <v>339</v>
       </c>
     </row>
-    <row r="164" spans="3:13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="164" spans="3:13" x14ac:dyDescent="0.3">
       <c r="C164" t="s">
         <v>45</v>
       </c>
@@ -10425,7 +10456,7 @@
         <v>339</v>
       </c>
     </row>
-    <row r="165" spans="3:13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="165" spans="3:13" x14ac:dyDescent="0.3">
       <c r="C165" t="s">
         <v>45</v>
       </c>
@@ -10455,7 +10486,7 @@
         <v>339</v>
       </c>
     </row>
-    <row r="166" spans="3:13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="166" spans="3:13" x14ac:dyDescent="0.3">
       <c r="C166" t="s">
         <v>45</v>
       </c>
@@ -10485,7 +10516,7 @@
         <v>339</v>
       </c>
     </row>
-    <row r="167" spans="3:13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="167" spans="3:13" x14ac:dyDescent="0.3">
       <c r="C167" t="s">
         <v>45</v>
       </c>
@@ -10515,7 +10546,7 @@
         <v>339</v>
       </c>
     </row>
-    <row r="168" spans="3:13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="168" spans="3:13" x14ac:dyDescent="0.3">
       <c r="C168" t="s">
         <v>45</v>
       </c>
@@ -10545,7 +10576,7 @@
         <v>339</v>
       </c>
     </row>
-    <row r="169" spans="3:13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="169" spans="3:13" x14ac:dyDescent="0.3">
       <c r="C169" t="s">
         <v>79</v>
       </c>
@@ -10575,7 +10606,7 @@
         <v>347</v>
       </c>
     </row>
-    <row r="170" spans="3:13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="170" spans="3:13" x14ac:dyDescent="0.3">
       <c r="C170" t="s">
         <v>79</v>
       </c>
@@ -10605,7 +10636,7 @@
         <v>347</v>
       </c>
     </row>
-    <row r="171" spans="3:13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="171" spans="3:13" x14ac:dyDescent="0.3">
       <c r="C171" t="s">
         <v>79</v>
       </c>
@@ -10635,7 +10666,7 @@
         <v>347</v>
       </c>
     </row>
-    <row r="172" spans="3:13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="172" spans="3:13" x14ac:dyDescent="0.3">
       <c r="C172" t="s">
         <v>79</v>
       </c>
@@ -10665,7 +10696,7 @@
         <v>347</v>
       </c>
     </row>
-    <row r="173" spans="3:13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="173" spans="3:13" x14ac:dyDescent="0.3">
       <c r="C173" t="s">
         <v>69</v>
       </c>
@@ -10695,7 +10726,7 @@
         <v>354</v>
       </c>
     </row>
-    <row r="174" spans="3:13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="174" spans="3:13" x14ac:dyDescent="0.3">
       <c r="C174" t="s">
         <v>69</v>
       </c>
@@ -10725,7 +10756,7 @@
         <v>354</v>
       </c>
     </row>
-    <row r="175" spans="3:13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="175" spans="3:13" x14ac:dyDescent="0.3">
       <c r="C175" t="s">
         <v>69</v>
       </c>
@@ -10755,7 +10786,7 @@
         <v>354</v>
       </c>
     </row>
-    <row r="176" spans="3:13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="176" spans="3:13" x14ac:dyDescent="0.3">
       <c r="C176" t="s">
         <v>69</v>
       </c>
@@ -10785,7 +10816,7 @@
         <v>354</v>
       </c>
     </row>
-    <row r="177" spans="2:13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="177" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B177" t="s">
         <v>162</v>
       </c>
@@ -10815,7 +10846,7 @@
         <v>358</v>
       </c>
     </row>
-    <row r="178" spans="2:13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="178" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B178" t="s">
         <v>162</v>
       </c>
@@ -10845,7 +10876,7 @@
         <v>358</v>
       </c>
     </row>
-    <row r="179" spans="2:13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="179" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B179" t="s">
         <v>162</v>
       </c>
@@ -10875,7 +10906,7 @@
         <v>358</v>
       </c>
     </row>
-    <row r="180" spans="2:13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="180" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B180" t="s">
         <v>162</v>
       </c>
@@ -10905,7 +10936,7 @@
         <v>358</v>
       </c>
     </row>
-    <row r="181" spans="2:13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="181" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B181" t="s">
         <v>162</v>
       </c>
@@ -10935,7 +10966,7 @@
         <v>358</v>
       </c>
     </row>
-    <row r="182" spans="2:13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="182" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B182" t="s">
         <v>162</v>
       </c>
@@ -10965,7 +10996,7 @@
         <v>358</v>
       </c>
     </row>
-    <row r="183" spans="2:13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="183" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B183" t="s">
         <v>162</v>
       </c>
@@ -10995,7 +11026,7 @@
         <v>358</v>
       </c>
     </row>
-    <row r="184" spans="2:13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="184" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B184" t="s">
         <v>162</v>
       </c>
@@ -11025,7 +11056,7 @@
         <v>358</v>
       </c>
     </row>
-    <row r="185" spans="2:13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="185" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B185" t="s">
         <v>162</v>
       </c>
@@ -11055,7 +11086,7 @@
         <v>358</v>
       </c>
     </row>
-    <row r="186" spans="2:13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="186" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B186" t="s">
         <v>162</v>
       </c>
@@ -11085,7 +11116,7 @@
         <v>358</v>
       </c>
     </row>
-    <row r="187" spans="2:13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="187" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B187" t="s">
         <v>162</v>
       </c>
@@ -11115,7 +11146,7 @@
         <v>358</v>
       </c>
     </row>
-    <row r="188" spans="2:13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="188" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B188" t="s">
         <v>162</v>
       </c>
@@ -11145,7 +11176,7 @@
         <v>358</v>
       </c>
     </row>
-    <row r="189" spans="2:13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="189" spans="2:13" x14ac:dyDescent="0.3">
       <c r="C189" t="s">
         <v>372</v>
       </c>
@@ -11172,7 +11203,7 @@
         <v>375</v>
       </c>
     </row>
-    <row r="190" spans="2:13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="190" spans="2:13" x14ac:dyDescent="0.3">
       <c r="C190" t="s">
         <v>372</v>
       </c>
@@ -11199,7 +11230,7 @@
         <v>375</v>
       </c>
     </row>
-    <row r="191" spans="2:13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="191" spans="2:13" x14ac:dyDescent="0.3">
       <c r="C191" t="s">
         <v>372</v>
       </c>
@@ -11226,7 +11257,7 @@
         <v>375</v>
       </c>
     </row>
-    <row r="192" spans="2:13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="192" spans="2:13" x14ac:dyDescent="0.3">
       <c r="C192" t="s">
         <v>372</v>
       </c>
@@ -11253,7 +11284,7 @@
         <v>375</v>
       </c>
     </row>
-    <row r="193" spans="3:13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="193" spans="3:13" x14ac:dyDescent="0.3">
       <c r="C193" t="s">
         <v>101</v>
       </c>
@@ -11280,7 +11311,7 @@
         <v>380</v>
       </c>
     </row>
-    <row r="194" spans="3:13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="194" spans="3:13" x14ac:dyDescent="0.3">
       <c r="C194" t="s">
         <v>101</v>
       </c>
@@ -11307,7 +11338,7 @@
         <v>380</v>
       </c>
     </row>
-    <row r="195" spans="3:13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="195" spans="3:13" x14ac:dyDescent="0.3">
       <c r="C195" t="s">
         <v>101</v>
       </c>
@@ -11334,7 +11365,7 @@
         <v>380</v>
       </c>
     </row>
-    <row r="196" spans="3:13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="196" spans="3:13" x14ac:dyDescent="0.3">
       <c r="C196" t="s">
         <v>101</v>
       </c>
@@ -11361,7 +11392,7 @@
         <v>380</v>
       </c>
     </row>
-    <row r="197" spans="3:13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="197" spans="3:13" x14ac:dyDescent="0.3">
       <c r="C197" t="s">
         <v>382</v>
       </c>
@@ -11391,7 +11422,7 @@
         <v>386</v>
       </c>
     </row>
-    <row r="198" spans="3:13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="198" spans="3:13" x14ac:dyDescent="0.3">
       <c r="C198" t="s">
         <v>382</v>
       </c>
@@ -11421,7 +11452,7 @@
         <v>386</v>
       </c>
     </row>
-    <row r="199" spans="3:13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="199" spans="3:13" x14ac:dyDescent="0.3">
       <c r="C199" t="s">
         <v>382</v>
       </c>
@@ -11451,7 +11482,7 @@
         <v>386</v>
       </c>
     </row>
-    <row r="200" spans="3:13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="200" spans="3:13" x14ac:dyDescent="0.3">
       <c r="C200" t="s">
         <v>382</v>
       </c>
@@ -11481,7 +11512,7 @@
         <v>386</v>
       </c>
     </row>
-    <row r="201" spans="3:13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="201" spans="3:13" x14ac:dyDescent="0.3">
       <c r="C201" t="s">
         <v>382</v>
       </c>
@@ -11511,7 +11542,7 @@
         <v>386</v>
       </c>
     </row>
-    <row r="202" spans="3:13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="202" spans="3:13" x14ac:dyDescent="0.3">
       <c r="C202" t="s">
         <v>110</v>
       </c>
@@ -11538,7 +11569,7 @@
         <v>396</v>
       </c>
     </row>
-    <row r="203" spans="3:13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="203" spans="3:13" x14ac:dyDescent="0.3">
       <c r="C203" t="s">
         <v>110</v>
       </c>
@@ -11565,7 +11596,7 @@
         <v>396</v>
       </c>
     </row>
-    <row r="204" spans="3:13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="204" spans="3:13" x14ac:dyDescent="0.3">
       <c r="C204" t="s">
         <v>110</v>
       </c>
@@ -11592,7 +11623,7 @@
         <v>396</v>
       </c>
     </row>
-    <row r="205" spans="3:13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="205" spans="3:13" x14ac:dyDescent="0.3">
       <c r="C205" t="s">
         <v>110</v>
       </c>
@@ -11619,7 +11650,7 @@
         <v>396</v>
       </c>
     </row>
-    <row r="206" spans="3:13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="206" spans="3:13" x14ac:dyDescent="0.3">
       <c r="C206" t="s">
         <v>399</v>
       </c>
@@ -11646,7 +11677,7 @@
         <v>402</v>
       </c>
     </row>
-    <row r="207" spans="3:13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="207" spans="3:13" x14ac:dyDescent="0.3">
       <c r="C207" t="s">
         <v>399</v>
       </c>
@@ -11673,7 +11704,7 @@
         <v>402</v>
       </c>
     </row>
-    <row r="208" spans="3:13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="208" spans="3:13" x14ac:dyDescent="0.3">
       <c r="C208" t="s">
         <v>399</v>
       </c>
@@ -11700,7 +11731,7 @@
         <v>402</v>
       </c>
     </row>
-    <row r="209" spans="2:13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="209" spans="2:13" x14ac:dyDescent="0.3">
       <c r="C209" t="s">
         <v>399</v>
       </c>
@@ -11727,7 +11758,7 @@
         <v>402</v>
       </c>
     </row>
-    <row r="210" spans="2:13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="210" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B210" t="s">
         <v>162</v>
       </c>
@@ -11757,7 +11788,7 @@
         <v>407</v>
       </c>
     </row>
-    <row r="211" spans="2:13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="211" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B211" t="s">
         <v>162</v>
       </c>
@@ -11787,7 +11818,7 @@
         <v>407</v>
       </c>
     </row>
-    <row r="212" spans="2:13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="212" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B212" t="s">
         <v>162</v>
       </c>
@@ -11810,11 +11841,14 @@
       <c r="K212" s="9" t="s">
         <v>112</v>
       </c>
-      <c r="M212" t="s">
+      <c r="L212" t="s">
+        <v>1709</v>
+      </c>
+      <c r="M212" s="3" t="s">
         <v>407</v>
       </c>
     </row>
-    <row r="213" spans="2:13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="213" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B213" t="s">
         <v>162</v>
       </c>
@@ -11844,7 +11878,7 @@
         <v>407</v>
       </c>
     </row>
-    <row r="214" spans="2:13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="214" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B214" t="s">
         <v>162</v>
       </c>
@@ -11871,7 +11905,7 @@
         <v>407</v>
       </c>
     </row>
-    <row r="215" spans="2:13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="215" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B215" t="s">
         <v>162</v>
       </c>
@@ -11901,7 +11935,7 @@
         <v>407</v>
       </c>
     </row>
-    <row r="216" spans="2:13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="216" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B216" t="s">
         <v>162</v>
       </c>
@@ -11928,7 +11962,7 @@
         <v>407</v>
       </c>
     </row>
-    <row r="217" spans="2:13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="217" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B217" t="s">
         <v>162</v>
       </c>
@@ -11955,7 +11989,7 @@
         <v>407</v>
       </c>
     </row>
-    <row r="218" spans="2:13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="218" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B218" t="s">
         <v>162</v>
       </c>
@@ -11985,7 +12019,7 @@
         <v>407</v>
       </c>
     </row>
-    <row r="219" spans="2:13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="219" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B219" t="s">
         <v>162</v>
       </c>
@@ -12012,7 +12046,7 @@
         <v>407</v>
       </c>
     </row>
-    <row r="220" spans="2:13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="220" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B220" t="s">
         <v>162</v>
       </c>
@@ -12042,7 +12076,7 @@
         <v>407</v>
       </c>
     </row>
-    <row r="221" spans="2:13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="221" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B221" t="s">
         <v>162</v>
       </c>
@@ -12072,7 +12106,7 @@
         <v>407</v>
       </c>
     </row>
-    <row r="222" spans="2:13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="222" spans="2:13" x14ac:dyDescent="0.3">
       <c r="C222" t="s">
         <v>129</v>
       </c>
@@ -12099,7 +12133,7 @@
         <v>412</v>
       </c>
     </row>
-    <row r="223" spans="2:13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="223" spans="2:13" x14ac:dyDescent="0.3">
       <c r="C223" t="s">
         <v>129</v>
       </c>
@@ -12126,7 +12160,7 @@
         <v>412</v>
       </c>
     </row>
-    <row r="224" spans="2:13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="224" spans="2:13" x14ac:dyDescent="0.3">
       <c r="C224" t="s">
         <v>129</v>
       </c>
@@ -12153,7 +12187,7 @@
         <v>412</v>
       </c>
     </row>
-    <row r="225" spans="2:13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="225" spans="2:13" x14ac:dyDescent="0.3">
       <c r="C225" t="s">
         <v>129</v>
       </c>
@@ -12180,7 +12214,7 @@
         <v>412</v>
       </c>
     </row>
-    <row r="226" spans="2:13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="226" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B226" t="s">
         <v>137</v>
       </c>
@@ -12210,7 +12244,7 @@
         <v>420</v>
       </c>
     </row>
-    <row r="227" spans="2:13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="227" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B227" t="s">
         <v>137</v>
       </c>
@@ -12240,7 +12274,7 @@
         <v>420</v>
       </c>
     </row>
-    <row r="228" spans="2:13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="228" spans="2:13" x14ac:dyDescent="0.3">
       <c r="C228" t="s">
         <v>150</v>
       </c>
@@ -12267,7 +12301,7 @@
         <v>425</v>
       </c>
     </row>
-    <row r="229" spans="2:13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="229" spans="2:13" x14ac:dyDescent="0.3">
       <c r="C229" t="s">
         <v>150</v>
       </c>
@@ -12294,7 +12328,7 @@
         <v>425</v>
       </c>
     </row>
-    <row r="230" spans="2:13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="230" spans="2:13" x14ac:dyDescent="0.3">
       <c r="C230" t="s">
         <v>150</v>
       </c>
@@ -12321,7 +12355,7 @@
         <v>425</v>
       </c>
     </row>
-    <row r="231" spans="2:13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="231" spans="2:13" x14ac:dyDescent="0.3">
       <c r="C231" t="s">
         <v>150</v>
       </c>
@@ -12348,7 +12382,7 @@
         <v>425</v>
       </c>
     </row>
-    <row r="232" spans="2:13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="232" spans="2:13" x14ac:dyDescent="0.3">
       <c r="C232" t="s">
         <v>294</v>
       </c>
@@ -12378,7 +12412,7 @@
         <v>432</v>
       </c>
     </row>
-    <row r="233" spans="2:13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="233" spans="2:13" x14ac:dyDescent="0.3">
       <c r="C233" t="s">
         <v>294</v>
       </c>
@@ -12408,7 +12442,7 @@
         <v>432</v>
       </c>
     </row>
-    <row r="234" spans="2:13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="234" spans="2:13" x14ac:dyDescent="0.3">
       <c r="C234" t="s">
         <v>294</v>
       </c>
@@ -12438,7 +12472,7 @@
         <v>432</v>
       </c>
     </row>
-    <row r="235" spans="2:13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="235" spans="2:13" x14ac:dyDescent="0.3">
       <c r="C235" t="s">
         <v>294</v>
       </c>
@@ -12468,7 +12502,7 @@
         <v>432</v>
       </c>
     </row>
-    <row r="236" spans="2:13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="236" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B236" t="s">
         <v>302</v>
       </c>
@@ -12498,7 +12532,7 @@
         <v>439</v>
       </c>
     </row>
-    <row r="237" spans="2:13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="237" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B237" t="s">
         <v>302</v>
       </c>
@@ -12528,7 +12562,7 @@
         <v>439</v>
       </c>
     </row>
-    <row r="238" spans="2:13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="238" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B238" t="s">
         <v>302</v>
       </c>
@@ -12558,7 +12592,7 @@
         <v>439</v>
       </c>
     </row>
-    <row r="239" spans="2:13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="239" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B239" t="s">
         <v>302</v>
       </c>
@@ -12588,7 +12622,7 @@
         <v>439</v>
       </c>
     </row>
-    <row r="240" spans="2:13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="240" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B240" t="s">
         <v>137</v>
       </c>
@@ -12618,7 +12652,7 @@
         <v>448</v>
       </c>
     </row>
-    <row r="241" spans="2:13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="241" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B241" t="s">
         <v>137</v>
       </c>
@@ -12648,7 +12682,7 @@
         <v>448</v>
       </c>
     </row>
-    <row r="242" spans="2:13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="242" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B242" t="s">
         <v>137</v>
       </c>
@@ -12678,7 +12712,7 @@
         <v>448</v>
       </c>
     </row>
-    <row r="243" spans="2:13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="243" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B243" t="s">
         <v>137</v>
       </c>
@@ -12704,11 +12738,11 @@
       <c r="L243" t="s">
         <v>452</v>
       </c>
-      <c r="M243" t="s">
+      <c r="M243" s="3" t="s">
         <v>448</v>
       </c>
     </row>
-    <row r="244" spans="2:13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="244" spans="2:13" x14ac:dyDescent="0.3">
       <c r="C244" t="s">
         <v>27</v>
       </c>
@@ -12738,7 +12772,7 @@
         <v>455</v>
       </c>
     </row>
-    <row r="245" spans="2:13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="245" spans="2:13" x14ac:dyDescent="0.3">
       <c r="C245" t="s">
         <v>27</v>
       </c>
@@ -12768,7 +12802,7 @@
         <v>455</v>
       </c>
     </row>
-    <row r="246" spans="2:13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="246" spans="2:13" x14ac:dyDescent="0.3">
       <c r="C246" t="s">
         <v>27</v>
       </c>
@@ -12798,7 +12832,7 @@
         <v>455</v>
       </c>
     </row>
-    <row r="247" spans="2:13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="247" spans="2:13" x14ac:dyDescent="0.3">
       <c r="C247" t="s">
         <v>27</v>
       </c>
@@ -12828,7 +12862,7 @@
         <v>455</v>
       </c>
     </row>
-    <row r="248" spans="2:13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="248" spans="2:13" x14ac:dyDescent="0.3">
       <c r="C248" t="s">
         <v>45</v>
       </c>
@@ -12858,7 +12892,7 @@
         <v>460</v>
       </c>
     </row>
-    <row r="249" spans="2:13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="249" spans="2:13" x14ac:dyDescent="0.3">
       <c r="C249" t="s">
         <v>45</v>
       </c>
@@ -12888,7 +12922,7 @@
         <v>460</v>
       </c>
     </row>
-    <row r="250" spans="2:13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="250" spans="2:13" x14ac:dyDescent="0.3">
       <c r="C250" t="s">
         <v>45</v>
       </c>
@@ -12918,7 +12952,7 @@
         <v>460</v>
       </c>
     </row>
-    <row r="251" spans="2:13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="251" spans="2:13" x14ac:dyDescent="0.3">
       <c r="C251" t="s">
         <v>45</v>
       </c>
@@ -12948,7 +12982,7 @@
         <v>460</v>
       </c>
     </row>
-    <row r="252" spans="2:13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="252" spans="2:13" x14ac:dyDescent="0.3">
       <c r="C252" t="s">
         <v>45</v>
       </c>
@@ -12978,7 +13012,7 @@
         <v>460</v>
       </c>
     </row>
-    <row r="253" spans="2:13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="253" spans="2:13" x14ac:dyDescent="0.3">
       <c r="C253" t="s">
         <v>45</v>
       </c>
@@ -13008,7 +13042,7 @@
         <v>460</v>
       </c>
     </row>
-    <row r="254" spans="2:13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="254" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B254" t="s">
         <v>137</v>
       </c>
@@ -13038,7 +13072,7 @@
         <v>470</v>
       </c>
     </row>
-    <row r="255" spans="2:13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="255" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B255" t="s">
         <v>137</v>
       </c>
@@ -13068,7 +13102,7 @@
         <v>470</v>
       </c>
     </row>
-    <row r="256" spans="2:13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="256" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B256" t="s">
         <v>137</v>
       </c>
@@ -13098,7 +13132,7 @@
         <v>470</v>
       </c>
     </row>
-    <row r="257" spans="2:13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="257" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B257" t="s">
         <v>137</v>
       </c>
@@ -13128,7 +13162,7 @@
         <v>470</v>
       </c>
     </row>
-    <row r="258" spans="2:13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="258" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B258" t="s">
         <v>137</v>
       </c>
@@ -13158,7 +13192,7 @@
         <v>470</v>
       </c>
     </row>
-    <row r="259" spans="2:13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="259" spans="2:13" x14ac:dyDescent="0.3">
       <c r="C259" t="s">
         <v>69</v>
       </c>
@@ -13188,7 +13222,7 @@
         <v>483</v>
       </c>
     </row>
-    <row r="260" spans="2:13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="260" spans="2:13" x14ac:dyDescent="0.3">
       <c r="C260" t="s">
         <v>69</v>
       </c>
@@ -13218,7 +13252,7 @@
         <v>483</v>
       </c>
     </row>
-    <row r="261" spans="2:13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="261" spans="2:13" x14ac:dyDescent="0.3">
       <c r="C261" t="s">
         <v>69</v>
       </c>
@@ -13248,7 +13282,7 @@
         <v>483</v>
       </c>
     </row>
-    <row r="262" spans="2:13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="262" spans="2:13" x14ac:dyDescent="0.3">
       <c r="C262" t="s">
         <v>69</v>
       </c>
@@ -13278,7 +13312,7 @@
         <v>483</v>
       </c>
     </row>
-    <row r="263" spans="2:13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="263" spans="2:13" x14ac:dyDescent="0.3">
       <c r="C263" t="s">
         <v>69</v>
       </c>
@@ -13308,7 +13342,7 @@
         <v>483</v>
       </c>
     </row>
-    <row r="264" spans="2:13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="264" spans="2:13" x14ac:dyDescent="0.3">
       <c r="C264" t="s">
         <v>69</v>
       </c>
@@ -13338,7 +13372,7 @@
         <v>483</v>
       </c>
     </row>
-    <row r="265" spans="2:13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="265" spans="2:13" x14ac:dyDescent="0.3">
       <c r="C265" t="s">
         <v>69</v>
       </c>
@@ -13368,7 +13402,7 @@
         <v>483</v>
       </c>
     </row>
-    <row r="266" spans="2:13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="266" spans="2:13" x14ac:dyDescent="0.3">
       <c r="C266" t="s">
         <v>69</v>
       </c>
@@ -13398,7 +13432,7 @@
         <v>483</v>
       </c>
     </row>
-    <row r="267" spans="2:13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="267" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B267" t="s">
         <v>162</v>
       </c>
@@ -13428,7 +13462,7 @@
         <v>493</v>
       </c>
     </row>
-    <row r="268" spans="2:13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="268" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B268" t="s">
         <v>162</v>
       </c>
@@ -13458,7 +13492,7 @@
         <v>493</v>
       </c>
     </row>
-    <row r="269" spans="2:13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="269" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B269" t="s">
         <v>162</v>
       </c>
@@ -13488,7 +13522,7 @@
         <v>493</v>
       </c>
     </row>
-    <row r="270" spans="2:13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="270" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B270" t="s">
         <v>162</v>
       </c>
@@ -13518,7 +13552,7 @@
         <v>493</v>
       </c>
     </row>
-    <row r="271" spans="2:13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="271" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B271" t="s">
         <v>162</v>
       </c>
@@ -13548,7 +13582,7 @@
         <v>493</v>
       </c>
     </row>
-    <row r="272" spans="2:13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="272" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B272" t="s">
         <v>162</v>
       </c>
@@ -13578,7 +13612,7 @@
         <v>493</v>
       </c>
     </row>
-    <row r="273" spans="2:13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="273" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B273" t="s">
         <v>162</v>
       </c>
@@ -13608,7 +13642,7 @@
         <v>493</v>
       </c>
     </row>
-    <row r="274" spans="2:13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="274" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B274" t="s">
         <v>162</v>
       </c>
@@ -13638,7 +13672,7 @@
         <v>493</v>
       </c>
     </row>
-    <row r="275" spans="2:13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="275" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B275" t="s">
         <v>162</v>
       </c>
@@ -13668,7 +13702,7 @@
         <v>493</v>
       </c>
     </row>
-    <row r="276" spans="2:13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="276" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B276" t="s">
         <v>162</v>
       </c>
@@ -13698,7 +13732,7 @@
         <v>493</v>
       </c>
     </row>
-    <row r="277" spans="2:13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="277" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B277" t="s">
         <v>162</v>
       </c>
@@ -13728,7 +13762,7 @@
         <v>493</v>
       </c>
     </row>
-    <row r="278" spans="2:13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="278" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B278" t="s">
         <v>162</v>
       </c>
@@ -13758,7 +13792,7 @@
         <v>493</v>
       </c>
     </row>
-    <row r="279" spans="2:13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="279" spans="2:13" x14ac:dyDescent="0.3">
       <c r="C279" t="s">
         <v>90</v>
       </c>
@@ -13788,7 +13822,7 @@
         <v>507</v>
       </c>
     </row>
-    <row r="280" spans="2:13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="280" spans="2:13" x14ac:dyDescent="0.3">
       <c r="C280" t="s">
         <v>90</v>
       </c>
@@ -13818,7 +13852,7 @@
         <v>507</v>
       </c>
     </row>
-    <row r="281" spans="2:13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="281" spans="2:13" x14ac:dyDescent="0.3">
       <c r="C281" t="s">
         <v>90</v>
       </c>
@@ -13848,7 +13882,7 @@
         <v>507</v>
       </c>
     </row>
-    <row r="282" spans="2:13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="282" spans="2:13" x14ac:dyDescent="0.3">
       <c r="C282" t="s">
         <v>90</v>
       </c>
@@ -13878,7 +13912,7 @@
         <v>507</v>
       </c>
     </row>
-    <row r="283" spans="2:13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="283" spans="2:13" x14ac:dyDescent="0.3">
       <c r="C283" t="s">
         <v>90</v>
       </c>
@@ -13908,7 +13942,7 @@
         <v>507</v>
       </c>
     </row>
-    <row r="284" spans="2:13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="284" spans="2:13" x14ac:dyDescent="0.3">
       <c r="C284" t="s">
         <v>90</v>
       </c>
@@ -13938,7 +13972,7 @@
         <v>507</v>
       </c>
     </row>
-    <row r="285" spans="2:13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="285" spans="2:13" x14ac:dyDescent="0.3">
       <c r="C285" t="s">
         <v>90</v>
       </c>
@@ -13968,7 +14002,7 @@
         <v>507</v>
       </c>
     </row>
-    <row r="286" spans="2:13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="286" spans="2:13" x14ac:dyDescent="0.3">
       <c r="C286" t="s">
         <v>90</v>
       </c>
@@ -13998,7 +14032,7 @@
         <v>507</v>
       </c>
     </row>
-    <row r="287" spans="2:13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="287" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B287" t="s">
         <v>137</v>
       </c>
@@ -14031,7 +14065,7 @@
         <v>520</v>
       </c>
     </row>
-    <row r="288" spans="2:13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="288" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B288" t="s">
         <v>137</v>
       </c>
@@ -14064,7 +14098,7 @@
         <v>520</v>
       </c>
     </row>
-    <row r="289" spans="2:13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="289" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B289" t="s">
         <v>137</v>
       </c>
@@ -14097,7 +14131,7 @@
         <v>520</v>
       </c>
     </row>
-    <row r="290" spans="2:13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="290" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B290" t="s">
         <v>137</v>
       </c>
@@ -14130,7 +14164,7 @@
         <v>520</v>
       </c>
     </row>
-    <row r="291" spans="2:13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="291" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B291" t="s">
         <v>137</v>
       </c>
@@ -14163,7 +14197,7 @@
         <v>520</v>
       </c>
     </row>
-    <row r="292" spans="2:13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="292" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B292" t="s">
         <v>137</v>
       </c>
@@ -14196,7 +14230,7 @@
         <v>520</v>
       </c>
     </row>
-    <row r="293" spans="2:13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="293" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B293" t="s">
         <v>137</v>
       </c>
@@ -14229,7 +14263,7 @@
         <v>520</v>
       </c>
     </row>
-    <row r="294" spans="2:13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="294" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B294" t="s">
         <v>137</v>
       </c>
@@ -14262,7 +14296,7 @@
         <v>520</v>
       </c>
     </row>
-    <row r="295" spans="2:13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="295" spans="2:13" x14ac:dyDescent="0.3">
       <c r="C295" t="s">
         <v>101</v>
       </c>
@@ -14292,7 +14326,7 @@
         <v>537</v>
       </c>
     </row>
-    <row r="296" spans="2:13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="296" spans="2:13" x14ac:dyDescent="0.3">
       <c r="C296" t="s">
         <v>101</v>
       </c>
@@ -14322,7 +14356,7 @@
         <v>537</v>
       </c>
     </row>
-    <row r="297" spans="2:13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="297" spans="2:13" x14ac:dyDescent="0.3">
       <c r="C297" t="s">
         <v>101</v>
       </c>
@@ -14352,7 +14386,7 @@
         <v>537</v>
       </c>
     </row>
-    <row r="298" spans="2:13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="298" spans="2:13" x14ac:dyDescent="0.3">
       <c r="C298" t="s">
         <v>101</v>
       </c>
@@ -14382,7 +14416,7 @@
         <v>537</v>
       </c>
     </row>
-    <row r="299" spans="2:13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="299" spans="2:13" x14ac:dyDescent="0.3">
       <c r="C299" t="s">
         <v>110</v>
       </c>
@@ -14412,7 +14446,7 @@
         <v>543</v>
       </c>
     </row>
-    <row r="300" spans="2:13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="300" spans="2:13" x14ac:dyDescent="0.3">
       <c r="C300" t="s">
         <v>110</v>
       </c>
@@ -14442,7 +14476,7 @@
         <v>543</v>
       </c>
     </row>
-    <row r="301" spans="2:13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="301" spans="2:13" x14ac:dyDescent="0.3">
       <c r="C301" t="s">
         <v>110</v>
       </c>
@@ -14472,7 +14506,7 @@
         <v>543</v>
       </c>
     </row>
-    <row r="302" spans="2:13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="302" spans="2:13" x14ac:dyDescent="0.3">
       <c r="C302" t="s">
         <v>110</v>
       </c>
@@ -14502,7 +14536,7 @@
         <v>543</v>
       </c>
     </row>
-    <row r="303" spans="2:13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="303" spans="2:13" x14ac:dyDescent="0.3">
       <c r="C303" t="s">
         <v>399</v>
       </c>
@@ -14532,7 +14566,7 @@
         <v>548</v>
       </c>
     </row>
-    <row r="304" spans="2:13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="304" spans="2:13" x14ac:dyDescent="0.3">
       <c r="C304" t="s">
         <v>399</v>
       </c>
@@ -14562,7 +14596,7 @@
         <v>548</v>
       </c>
     </row>
-    <row r="305" spans="2:13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="305" spans="2:13" x14ac:dyDescent="0.3">
       <c r="C305" t="s">
         <v>399</v>
       </c>
@@ -14592,7 +14626,7 @@
         <v>548</v>
       </c>
     </row>
-    <row r="306" spans="2:13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="306" spans="2:13" x14ac:dyDescent="0.3">
       <c r="C306" t="s">
         <v>399</v>
       </c>
@@ -14622,7 +14656,7 @@
         <v>548</v>
       </c>
     </row>
-    <row r="307" spans="2:13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="307" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B307" t="s">
         <v>162</v>
       </c>
@@ -14652,7 +14686,7 @@
         <v>553</v>
       </c>
     </row>
-    <row r="308" spans="2:13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="308" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B308" t="s">
         <v>162</v>
       </c>
@@ -14682,7 +14716,7 @@
         <v>553</v>
       </c>
     </row>
-    <row r="309" spans="2:13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="309" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B309" t="s">
         <v>162</v>
       </c>
@@ -14712,7 +14746,7 @@
         <v>553</v>
       </c>
     </row>
-    <row r="310" spans="2:13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="310" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B310" t="s">
         <v>162</v>
       </c>
@@ -14742,7 +14776,7 @@
         <v>553</v>
       </c>
     </row>
-    <row r="311" spans="2:13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="311" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B311" t="s">
         <v>162</v>
       </c>
@@ -14772,7 +14806,7 @@
         <v>553</v>
       </c>
     </row>
-    <row r="312" spans="2:13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="312" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B312" t="s">
         <v>162</v>
       </c>
@@ -14802,7 +14836,7 @@
         <v>553</v>
       </c>
     </row>
-    <row r="313" spans="2:13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="313" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B313" t="s">
         <v>162</v>
       </c>
@@ -14832,7 +14866,7 @@
         <v>553</v>
       </c>
     </row>
-    <row r="314" spans="2:13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="314" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B314" t="s">
         <v>162</v>
       </c>
@@ -14862,7 +14896,7 @@
         <v>553</v>
       </c>
     </row>
-    <row r="315" spans="2:13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="315" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B315" t="s">
         <v>162</v>
       </c>
@@ -14892,7 +14926,7 @@
         <v>553</v>
       </c>
     </row>
-    <row r="316" spans="2:13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="316" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B316" t="s">
         <v>162</v>
       </c>
@@ -14922,7 +14956,7 @@
         <v>553</v>
       </c>
     </row>
-    <row r="317" spans="2:13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="317" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B317" t="s">
         <v>162</v>
       </c>
@@ -14952,7 +14986,7 @@
         <v>553</v>
       </c>
     </row>
-    <row r="318" spans="2:13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="318" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B318" t="s">
         <v>162</v>
       </c>
@@ -14982,7 +15016,7 @@
         <v>553</v>
       </c>
     </row>
-    <row r="319" spans="2:13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="319" spans="2:13" x14ac:dyDescent="0.3">
       <c r="C319" t="s">
         <v>129</v>
       </c>
@@ -15012,7 +15046,7 @@
         <v>568</v>
       </c>
     </row>
-    <row r="320" spans="2:13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="320" spans="2:13" x14ac:dyDescent="0.3">
       <c r="C320" t="s">
         <v>129</v>
       </c>
@@ -15042,7 +15076,7 @@
         <v>568</v>
       </c>
     </row>
-    <row r="321" spans="2:13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="321" spans="2:13" x14ac:dyDescent="0.3">
       <c r="C321" t="s">
         <v>129</v>
       </c>
@@ -15072,7 +15106,7 @@
         <v>568</v>
       </c>
     </row>
-    <row r="322" spans="2:13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="322" spans="2:13" x14ac:dyDescent="0.3">
       <c r="C322" t="s">
         <v>129</v>
       </c>
@@ -15102,7 +15136,7 @@
         <v>568</v>
       </c>
     </row>
-    <row r="323" spans="2:13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="323" spans="2:13" x14ac:dyDescent="0.3">
       <c r="C323" t="s">
         <v>154</v>
       </c>
@@ -15135,7 +15169,7 @@
         <v>578</v>
       </c>
     </row>
-    <row r="324" spans="2:13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="324" spans="2:13" x14ac:dyDescent="0.3">
       <c r="C324" t="s">
         <v>154</v>
       </c>
@@ -15165,7 +15199,7 @@
         <v>578</v>
       </c>
     </row>
-    <row r="325" spans="2:13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="325" spans="2:13" x14ac:dyDescent="0.3">
       <c r="C325" t="s">
         <v>154</v>
       </c>
@@ -15198,7 +15232,7 @@
         <v>578</v>
       </c>
     </row>
-    <row r="326" spans="2:13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="326" spans="2:13" x14ac:dyDescent="0.3">
       <c r="C326" t="s">
         <v>154</v>
       </c>
@@ -15228,7 +15262,7 @@
         <v>578</v>
       </c>
     </row>
-    <row r="327" spans="2:13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="327" spans="2:13" x14ac:dyDescent="0.3">
       <c r="C327" t="s">
         <v>154</v>
       </c>
@@ -15261,7 +15295,7 @@
         <v>578</v>
       </c>
     </row>
-    <row r="328" spans="2:13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="328" spans="2:13" x14ac:dyDescent="0.3">
       <c r="C328" t="s">
         <v>154</v>
       </c>
@@ -15294,7 +15328,7 @@
         <v>578</v>
       </c>
     </row>
-    <row r="329" spans="2:13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="329" spans="2:13" x14ac:dyDescent="0.3">
       <c r="C329" t="s">
         <v>154</v>
       </c>
@@ -15327,7 +15361,7 @@
         <v>578</v>
       </c>
     </row>
-    <row r="330" spans="2:13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="330" spans="2:13" x14ac:dyDescent="0.3">
       <c r="C330" t="s">
         <v>154</v>
       </c>
@@ -15357,7 +15391,7 @@
         <v>578</v>
       </c>
     </row>
-    <row r="331" spans="2:13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="331" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B331" t="s">
         <v>593</v>
       </c>
@@ -15393,7 +15427,7 @@
         <v>597</v>
       </c>
     </row>
-    <row r="332" spans="2:13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="332" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B332" t="s">
         <v>593</v>
       </c>
@@ -15429,7 +15463,7 @@
         <v>597</v>
       </c>
     </row>
-    <row r="333" spans="2:13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="333" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B333" t="s">
         <v>593</v>
       </c>
@@ -15462,7 +15496,7 @@
         <v>597</v>
       </c>
     </row>
-    <row r="334" spans="2:13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="334" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B334" t="s">
         <v>593</v>
       </c>
@@ -15498,7 +15532,7 @@
         <v>597</v>
       </c>
     </row>
-    <row r="335" spans="2:13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="335" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B335" t="s">
         <v>593</v>
       </c>
@@ -15534,7 +15568,7 @@
         <v>597</v>
       </c>
     </row>
-    <row r="336" spans="2:13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="336" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B336" t="s">
         <v>593</v>
       </c>
@@ -15570,7 +15604,7 @@
         <v>597</v>
       </c>
     </row>
-    <row r="337" spans="2:13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="337" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B337" t="s">
         <v>593</v>
       </c>
@@ -15603,7 +15637,7 @@
         <v>597</v>
       </c>
     </row>
-    <row r="338" spans="2:13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="338" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B338" t="s">
         <v>593</v>
       </c>
@@ -15636,7 +15670,7 @@
         <v>597</v>
       </c>
     </row>
-    <row r="339" spans="2:13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="339" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B339" t="s">
         <v>593</v>
       </c>
@@ -15667,7 +15701,7 @@
         <v>613</v>
       </c>
     </row>
-    <row r="340" spans="2:13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="340" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B340" t="s">
         <v>593</v>
       </c>
@@ -15698,7 +15732,7 @@
         <v>613</v>
       </c>
     </row>
-    <row r="341" spans="2:13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="341" spans="2:13" x14ac:dyDescent="0.3">
       <c r="C341" t="s">
         <v>150</v>
       </c>
@@ -15728,7 +15762,7 @@
         <v>618</v>
       </c>
     </row>
-    <row r="342" spans="2:13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="342" spans="2:13" x14ac:dyDescent="0.3">
       <c r="C342" t="s">
         <v>150</v>
       </c>
@@ -15758,7 +15792,7 @@
         <v>618</v>
       </c>
     </row>
-    <row r="343" spans="2:13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="343" spans="2:13" x14ac:dyDescent="0.3">
       <c r="C343" t="s">
         <v>150</v>
       </c>
@@ -15788,7 +15822,7 @@
         <v>618</v>
       </c>
     </row>
-    <row r="344" spans="2:13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="344" spans="2:13" x14ac:dyDescent="0.3">
       <c r="C344" t="s">
         <v>150</v>
       </c>
@@ -15818,7 +15852,7 @@
         <v>618</v>
       </c>
     </row>
-    <row r="345" spans="2:13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="345" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B345" t="s">
         <v>302</v>
       </c>
@@ -15848,7 +15882,7 @@
         <v>624</v>
       </c>
     </row>
-    <row r="346" spans="2:13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="346" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B346" t="s">
         <v>302</v>
       </c>
@@ -15878,7 +15912,7 @@
         <v>624</v>
       </c>
     </row>
-    <row r="347" spans="2:13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="347" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B347" t="s">
         <v>302</v>
       </c>
@@ -15908,7 +15942,7 @@
         <v>624</v>
       </c>
     </row>
-    <row r="348" spans="2:13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="348" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B348" t="s">
         <v>302</v>
       </c>
@@ -15938,7 +15972,7 @@
         <v>624</v>
       </c>
     </row>
-    <row r="349" spans="2:13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="349" spans="2:13" x14ac:dyDescent="0.3">
       <c r="C349" t="s">
         <v>154</v>
       </c>
@@ -15968,7 +16002,7 @@
         <v>632</v>
       </c>
     </row>
-    <row r="350" spans="2:13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="350" spans="2:13" x14ac:dyDescent="0.3">
       <c r="C350" t="s">
         <v>154</v>
       </c>
@@ -15998,7 +16032,7 @@
         <v>632</v>
       </c>
     </row>
-    <row r="351" spans="2:13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="351" spans="2:13" x14ac:dyDescent="0.3">
       <c r="C351" t="s">
         <v>154</v>
       </c>
@@ -16028,7 +16062,7 @@
         <v>632</v>
       </c>
     </row>
-    <row r="352" spans="2:13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="352" spans="2:13" x14ac:dyDescent="0.3">
       <c r="C352" t="s">
         <v>154</v>
       </c>
@@ -16058,7 +16092,7 @@
         <v>632</v>
       </c>
     </row>
-    <row r="353" spans="2:13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="353" spans="2:13" x14ac:dyDescent="0.3">
       <c r="C353" t="s">
         <v>154</v>
       </c>
@@ -16088,7 +16122,7 @@
         <v>632</v>
       </c>
     </row>
-    <row r="354" spans="2:13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="354" spans="2:13" x14ac:dyDescent="0.3">
       <c r="C354" t="s">
         <v>154</v>
       </c>
@@ -16118,7 +16152,7 @@
         <v>632</v>
       </c>
     </row>
-    <row r="355" spans="2:13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="355" spans="2:13" x14ac:dyDescent="0.3">
       <c r="C355" t="s">
         <v>154</v>
       </c>
@@ -16148,7 +16182,7 @@
         <v>632</v>
       </c>
     </row>
-    <row r="356" spans="2:13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="356" spans="2:13" x14ac:dyDescent="0.3">
       <c r="C356" t="s">
         <v>154</v>
       </c>
@@ -16178,7 +16212,7 @@
         <v>632</v>
       </c>
     </row>
-    <row r="357" spans="2:13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="357" spans="2:13" x14ac:dyDescent="0.3">
       <c r="C357" t="s">
         <v>640</v>
       </c>
@@ -16208,7 +16242,7 @@
         <v>643</v>
       </c>
     </row>
-    <row r="358" spans="2:13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="358" spans="2:13" x14ac:dyDescent="0.3">
       <c r="C358" t="s">
         <v>640</v>
       </c>
@@ -16238,7 +16272,7 @@
         <v>643</v>
       </c>
     </row>
-    <row r="359" spans="2:13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="359" spans="2:13" x14ac:dyDescent="0.3">
       <c r="C359" t="s">
         <v>640</v>
       </c>
@@ -16268,7 +16302,7 @@
         <v>643</v>
       </c>
     </row>
-    <row r="360" spans="2:13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="360" spans="2:13" x14ac:dyDescent="0.3">
       <c r="C360" t="s">
         <v>640</v>
       </c>
@@ -16298,7 +16332,7 @@
         <v>643</v>
       </c>
     </row>
-    <row r="361" spans="2:13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="361" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B361" t="s">
         <v>137</v>
       </c>
@@ -16328,7 +16362,7 @@
         <v>650</v>
       </c>
     </row>
-    <row r="362" spans="2:13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="362" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B362" t="s">
         <v>137</v>
       </c>
@@ -16358,7 +16392,7 @@
         <v>650</v>
       </c>
     </row>
-    <row r="363" spans="2:13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="363" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B363" t="s">
         <v>137</v>
       </c>
@@ -16388,7 +16422,7 @@
         <v>650</v>
       </c>
     </row>
-    <row r="364" spans="2:13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="364" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B364" t="s">
         <v>137</v>
       </c>
@@ -16418,7 +16452,7 @@
         <v>650</v>
       </c>
     </row>
-    <row r="365" spans="2:13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="365" spans="2:13" x14ac:dyDescent="0.3">
       <c r="C365" t="s">
         <v>27</v>
       </c>
@@ -16448,7 +16482,7 @@
         <v>658</v>
       </c>
     </row>
-    <row r="366" spans="2:13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="366" spans="2:13" x14ac:dyDescent="0.3">
       <c r="C366" t="s">
         <v>27</v>
       </c>
@@ -16478,7 +16512,7 @@
         <v>658</v>
       </c>
     </row>
-    <row r="367" spans="2:13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="367" spans="2:13" x14ac:dyDescent="0.3">
       <c r="C367" t="s">
         <v>27</v>
       </c>
@@ -16508,7 +16542,7 @@
         <v>658</v>
       </c>
     </row>
-    <row r="368" spans="2:13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="368" spans="2:13" x14ac:dyDescent="0.3">
       <c r="C368" t="s">
         <v>27</v>
       </c>
@@ -16538,7 +16572,7 @@
         <v>658</v>
       </c>
     </row>
-    <row r="369" spans="3:13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="369" spans="3:13" x14ac:dyDescent="0.3">
       <c r="C369" t="s">
         <v>45</v>
       </c>
@@ -16568,7 +16602,7 @@
         <v>664</v>
       </c>
     </row>
-    <row r="370" spans="3:13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="370" spans="3:13" x14ac:dyDescent="0.3">
       <c r="C370" t="s">
         <v>45</v>
       </c>
@@ -16598,7 +16632,7 @@
         <v>664</v>
       </c>
     </row>
-    <row r="371" spans="3:13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="371" spans="3:13" x14ac:dyDescent="0.3">
       <c r="C371" t="s">
         <v>45</v>
       </c>
@@ -16628,7 +16662,7 @@
         <v>664</v>
       </c>
     </row>
-    <row r="372" spans="3:13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="372" spans="3:13" x14ac:dyDescent="0.3">
       <c r="C372" t="s">
         <v>45</v>
       </c>
@@ -16658,7 +16692,7 @@
         <v>664</v>
       </c>
     </row>
-    <row r="373" spans="3:13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="373" spans="3:13" x14ac:dyDescent="0.3">
       <c r="C373" t="s">
         <v>45</v>
       </c>
@@ -16688,7 +16722,7 @@
         <v>664</v>
       </c>
     </row>
-    <row r="374" spans="3:13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="374" spans="3:13" x14ac:dyDescent="0.3">
       <c r="C374" t="s">
         <v>45</v>
       </c>
@@ -16718,7 +16752,7 @@
         <v>664</v>
       </c>
     </row>
-    <row r="375" spans="3:13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="375" spans="3:13" x14ac:dyDescent="0.3">
       <c r="C375" t="s">
         <v>69</v>
       </c>
@@ -16748,7 +16782,7 @@
         <v>671</v>
       </c>
     </row>
-    <row r="376" spans="3:13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="376" spans="3:13" x14ac:dyDescent="0.3">
       <c r="C376" t="s">
         <v>69</v>
       </c>
@@ -16778,7 +16812,7 @@
         <v>671</v>
       </c>
     </row>
-    <row r="377" spans="3:13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="377" spans="3:13" x14ac:dyDescent="0.3">
       <c r="C377" t="s">
         <v>69</v>
       </c>
@@ -16808,7 +16842,7 @@
         <v>671</v>
       </c>
     </row>
-    <row r="378" spans="3:13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="378" spans="3:13" x14ac:dyDescent="0.3">
       <c r="C378" t="s">
         <v>69</v>
       </c>
@@ -16838,7 +16872,7 @@
         <v>671</v>
       </c>
     </row>
-    <row r="379" spans="3:13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="379" spans="3:13" x14ac:dyDescent="0.3">
       <c r="C379" t="s">
         <v>675</v>
       </c>
@@ -16868,7 +16902,7 @@
         <v>678</v>
       </c>
     </row>
-    <row r="380" spans="3:13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="380" spans="3:13" x14ac:dyDescent="0.3">
       <c r="C380" t="s">
         <v>675</v>
       </c>
@@ -16898,7 +16932,7 @@
         <v>678</v>
       </c>
     </row>
-    <row r="381" spans="3:13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="381" spans="3:13" x14ac:dyDescent="0.3">
       <c r="C381" t="s">
         <v>675</v>
       </c>
@@ -16928,7 +16962,7 @@
         <v>678</v>
       </c>
     </row>
-    <row r="382" spans="3:13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="382" spans="3:13" x14ac:dyDescent="0.3">
       <c r="C382" t="s">
         <v>675</v>
       </c>
@@ -16958,7 +16992,7 @@
         <v>678</v>
       </c>
     </row>
-    <row r="383" spans="3:13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="383" spans="3:13" x14ac:dyDescent="0.3">
       <c r="C383" t="s">
         <v>90</v>
       </c>
@@ -16988,7 +17022,7 @@
         <v>684</v>
       </c>
     </row>
-    <row r="384" spans="3:13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="384" spans="3:13" x14ac:dyDescent="0.3">
       <c r="C384" t="s">
         <v>90</v>
       </c>
@@ -17018,7 +17052,7 @@
         <v>684</v>
       </c>
     </row>
-    <row r="385" spans="2:13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="385" spans="2:13" x14ac:dyDescent="0.3">
       <c r="C385" t="s">
         <v>90</v>
       </c>
@@ -17048,7 +17082,7 @@
         <v>684</v>
       </c>
     </row>
-    <row r="386" spans="2:13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="386" spans="2:13" x14ac:dyDescent="0.3">
       <c r="C386" t="s">
         <v>90</v>
       </c>
@@ -17078,7 +17112,7 @@
         <v>684</v>
       </c>
     </row>
-    <row r="387" spans="2:13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="387" spans="2:13" x14ac:dyDescent="0.3">
       <c r="C387" t="s">
         <v>90</v>
       </c>
@@ -17108,7 +17142,7 @@
         <v>684</v>
       </c>
     </row>
-    <row r="388" spans="2:13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="388" spans="2:13" x14ac:dyDescent="0.3">
       <c r="C388" t="s">
         <v>90</v>
       </c>
@@ -17138,7 +17172,7 @@
         <v>684</v>
       </c>
     </row>
-    <row r="389" spans="2:13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="389" spans="2:13" x14ac:dyDescent="0.3">
       <c r="C389" t="s">
         <v>90</v>
       </c>
@@ -17168,7 +17202,7 @@
         <v>684</v>
       </c>
     </row>
-    <row r="390" spans="2:13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="390" spans="2:13" x14ac:dyDescent="0.3">
       <c r="C390" t="s">
         <v>90</v>
       </c>
@@ -17198,7 +17232,7 @@
         <v>684</v>
       </c>
     </row>
-    <row r="391" spans="2:13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="391" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B391" t="s">
         <v>162</v>
       </c>
@@ -17228,7 +17262,7 @@
         <v>692</v>
       </c>
     </row>
-    <row r="392" spans="2:13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="392" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B392" t="s">
         <v>162</v>
       </c>
@@ -17258,7 +17292,7 @@
         <v>692</v>
       </c>
     </row>
-    <row r="393" spans="2:13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="393" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B393" t="s">
         <v>162</v>
       </c>
@@ -17288,7 +17322,7 @@
         <v>692</v>
       </c>
     </row>
-    <row r="394" spans="2:13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="394" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B394" t="s">
         <v>162</v>
       </c>
@@ -17318,7 +17352,7 @@
         <v>692</v>
       </c>
     </row>
-    <row r="395" spans="2:13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="395" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B395" t="s">
         <v>162</v>
       </c>
@@ -17348,7 +17382,7 @@
         <v>692</v>
       </c>
     </row>
-    <row r="396" spans="2:13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="396" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B396" t="s">
         <v>162</v>
       </c>
@@ -17378,7 +17412,7 @@
         <v>692</v>
       </c>
     </row>
-    <row r="397" spans="2:13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="397" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B397" t="s">
         <v>162</v>
       </c>
@@ -17408,7 +17442,7 @@
         <v>692</v>
       </c>
     </row>
-    <row r="398" spans="2:13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="398" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B398" t="s">
         <v>162</v>
       </c>
@@ -17438,7 +17472,7 @@
         <v>692</v>
       </c>
     </row>
-    <row r="399" spans="2:13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="399" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B399" t="s">
         <v>162</v>
       </c>
@@ -17468,7 +17502,7 @@
         <v>692</v>
       </c>
     </row>
-    <row r="400" spans="2:13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="400" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B400" t="s">
         <v>162</v>
       </c>
@@ -17498,7 +17532,7 @@
         <v>692</v>
       </c>
     </row>
-    <row r="401" spans="2:13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="401" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B401" t="s">
         <v>162</v>
       </c>
@@ -17528,7 +17562,7 @@
         <v>692</v>
       </c>
     </row>
-    <row r="402" spans="2:13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="402" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B402" t="s">
         <v>162</v>
       </c>
@@ -17558,7 +17592,7 @@
         <v>692</v>
       </c>
     </row>
-    <row r="403" spans="2:13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="403" spans="2:13" x14ac:dyDescent="0.3">
       <c r="C403" t="s">
         <v>101</v>
       </c>
@@ -17588,7 +17622,7 @@
         <v>704</v>
       </c>
     </row>
-    <row r="404" spans="2:13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="404" spans="2:13" x14ac:dyDescent="0.3">
       <c r="C404" t="s">
         <v>101</v>
       </c>
@@ -17618,7 +17652,7 @@
         <v>704</v>
       </c>
     </row>
-    <row r="405" spans="2:13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="405" spans="2:13" x14ac:dyDescent="0.3">
       <c r="C405" t="s">
         <v>101</v>
       </c>
@@ -17648,7 +17682,7 @@
         <v>704</v>
       </c>
     </row>
-    <row r="406" spans="2:13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="406" spans="2:13" x14ac:dyDescent="0.3">
       <c r="C406" t="s">
         <v>101</v>
       </c>
@@ -17678,7 +17712,7 @@
         <v>704</v>
       </c>
     </row>
-    <row r="407" spans="2:13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="407" spans="2:13" x14ac:dyDescent="0.3">
       <c r="C407" t="s">
         <v>110</v>
       </c>
@@ -17708,7 +17742,7 @@
         <v>709</v>
       </c>
     </row>
-    <row r="408" spans="2:13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="408" spans="2:13" x14ac:dyDescent="0.3">
       <c r="C408" t="s">
         <v>110</v>
       </c>
@@ -17738,7 +17772,7 @@
         <v>709</v>
       </c>
     </row>
-    <row r="409" spans="2:13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="409" spans="2:13" x14ac:dyDescent="0.3">
       <c r="C409" t="s">
         <v>110</v>
       </c>
@@ -17768,7 +17802,7 @@
         <v>709</v>
       </c>
     </row>
-    <row r="410" spans="2:13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="410" spans="2:13" x14ac:dyDescent="0.3">
       <c r="C410" t="s">
         <v>110</v>
       </c>
@@ -17798,7 +17832,7 @@
         <v>709</v>
       </c>
     </row>
-    <row r="411" spans="2:13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="411" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B411" t="s">
         <v>162</v>
       </c>
@@ -17828,7 +17862,7 @@
         <v>714</v>
       </c>
     </row>
-    <row r="412" spans="2:13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="412" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B412" t="s">
         <v>162</v>
       </c>
@@ -17858,7 +17892,7 @@
         <v>714</v>
       </c>
     </row>
-    <row r="413" spans="2:13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="413" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B413" t="s">
         <v>162</v>
       </c>
@@ -17888,7 +17922,7 @@
         <v>714</v>
       </c>
     </row>
-    <row r="414" spans="2:13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="414" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B414" t="s">
         <v>162</v>
       </c>
@@ -17918,7 +17952,7 @@
         <v>714</v>
       </c>
     </row>
-    <row r="415" spans="2:13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="415" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B415" t="s">
         <v>162</v>
       </c>
@@ -17948,7 +17982,7 @@
         <v>714</v>
       </c>
     </row>
-    <row r="416" spans="2:13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="416" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B416" t="s">
         <v>162</v>
       </c>
@@ -17978,7 +18012,7 @@
         <v>714</v>
       </c>
     </row>
-    <row r="417" spans="2:13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="417" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B417" t="s">
         <v>162</v>
       </c>
@@ -18008,7 +18042,7 @@
         <v>714</v>
       </c>
     </row>
-    <row r="418" spans="2:13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="418" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B418" t="s">
         <v>162</v>
       </c>
@@ -18038,7 +18072,7 @@
         <v>714</v>
       </c>
     </row>
-    <row r="419" spans="2:13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="419" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B419" t="s">
         <v>162</v>
       </c>
@@ -18068,7 +18102,7 @@
         <v>714</v>
       </c>
     </row>
-    <row r="420" spans="2:13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="420" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B420" t="s">
         <v>162</v>
       </c>
@@ -18098,7 +18132,7 @@
         <v>714</v>
       </c>
     </row>
-    <row r="421" spans="2:13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="421" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B421" t="s">
         <v>162</v>
       </c>
@@ -18128,7 +18162,7 @@
         <v>714</v>
       </c>
     </row>
-    <row r="422" spans="2:13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="422" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B422" t="s">
         <v>162</v>
       </c>
@@ -18158,7 +18192,7 @@
         <v>714</v>
       </c>
     </row>
-    <row r="423" spans="2:13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="423" spans="2:13" x14ac:dyDescent="0.3">
       <c r="C423" t="s">
         <v>726</v>
       </c>
@@ -18188,7 +18222,7 @@
         <v>730</v>
       </c>
     </row>
-    <row r="424" spans="2:13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="424" spans="2:13" x14ac:dyDescent="0.3">
       <c r="C424" t="s">
         <v>726</v>
       </c>
@@ -18218,7 +18252,7 @@
         <v>730</v>
       </c>
     </row>
-    <row r="425" spans="2:13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="425" spans="2:13" x14ac:dyDescent="0.3">
       <c r="C425" t="s">
         <v>726</v>
       </c>
@@ -18248,7 +18282,7 @@
         <v>730</v>
       </c>
     </row>
-    <row r="426" spans="2:13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="426" spans="2:13" x14ac:dyDescent="0.3">
       <c r="C426" t="s">
         <v>726</v>
       </c>
@@ -18278,7 +18312,7 @@
         <v>730</v>
       </c>
     </row>
-    <row r="427" spans="2:13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="427" spans="2:13" x14ac:dyDescent="0.3">
       <c r="C427" t="s">
         <v>129</v>
       </c>
@@ -18308,7 +18342,7 @@
         <v>735</v>
       </c>
     </row>
-    <row r="428" spans="2:13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="428" spans="2:13" x14ac:dyDescent="0.3">
       <c r="C428" t="s">
         <v>129</v>
       </c>
@@ -18338,7 +18372,7 @@
         <v>735</v>
       </c>
     </row>
-    <row r="429" spans="2:13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="429" spans="2:13" x14ac:dyDescent="0.3">
       <c r="C429" t="s">
         <v>129</v>
       </c>
@@ -18368,7 +18402,7 @@
         <v>735</v>
       </c>
     </row>
-    <row r="430" spans="2:13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="430" spans="2:13" x14ac:dyDescent="0.3">
       <c r="C430" t="s">
         <v>129</v>
       </c>
@@ -18398,7 +18432,7 @@
         <v>735</v>
       </c>
     </row>
-    <row r="431" spans="2:13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="431" spans="2:13" x14ac:dyDescent="0.3">
       <c r="C431" t="s">
         <v>150</v>
       </c>
@@ -18428,7 +18462,7 @@
         <v>741</v>
       </c>
     </row>
-    <row r="432" spans="2:13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="432" spans="2:13" x14ac:dyDescent="0.3">
       <c r="C432" t="s">
         <v>150</v>
       </c>
@@ -18458,7 +18492,7 @@
         <v>741</v>
       </c>
     </row>
-    <row r="433" spans="3:13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="433" spans="3:13" x14ac:dyDescent="0.3">
       <c r="C433" t="s">
         <v>150</v>
       </c>
@@ -18488,7 +18522,7 @@
         <v>741</v>
       </c>
     </row>
-    <row r="434" spans="3:13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="434" spans="3:13" x14ac:dyDescent="0.3">
       <c r="C434" t="s">
         <v>150</v>
       </c>
@@ -18518,7 +18552,7 @@
         <v>741</v>
       </c>
     </row>
-    <row r="435" spans="3:13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="435" spans="3:13" x14ac:dyDescent="0.3">
       <c r="C435" t="s">
         <v>303</v>
       </c>
@@ -18545,7 +18579,7 @@
         <v>747</v>
       </c>
     </row>
-    <row r="436" spans="3:13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="436" spans="3:13" x14ac:dyDescent="0.3">
       <c r="C436" t="s">
         <v>303</v>
       </c>
@@ -18572,7 +18606,7 @@
         <v>747</v>
       </c>
     </row>
-    <row r="437" spans="3:13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="437" spans="3:13" x14ac:dyDescent="0.3">
       <c r="C437" t="s">
         <v>303</v>
       </c>
@@ -18599,7 +18633,7 @@
         <v>747</v>
       </c>
     </row>
-    <row r="438" spans="3:13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="438" spans="3:13" x14ac:dyDescent="0.3">
       <c r="C438" t="s">
         <v>303</v>
       </c>
@@ -19031,7 +19065,7 @@
         <v>757</v>
       </c>
     </row>
-    <row r="454" spans="3:13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="454" spans="3:13" x14ac:dyDescent="0.3">
       <c r="C454" t="s">
         <v>154</v>
       </c>
@@ -19061,7 +19095,7 @@
         <v>775</v>
       </c>
     </row>
-    <row r="455" spans="3:13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="455" spans="3:13" x14ac:dyDescent="0.3">
       <c r="C455" t="s">
         <v>154</v>
       </c>
@@ -19091,7 +19125,7 @@
         <v>775</v>
       </c>
     </row>
-    <row r="456" spans="3:13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="456" spans="3:13" x14ac:dyDescent="0.3">
       <c r="C456" t="s">
         <v>154</v>
       </c>
@@ -19121,7 +19155,7 @@
         <v>775</v>
       </c>
     </row>
-    <row r="457" spans="3:13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="457" spans="3:13" x14ac:dyDescent="0.3">
       <c r="C457" t="s">
         <v>154</v>
       </c>
@@ -19151,7 +19185,7 @@
         <v>775</v>
       </c>
     </row>
-    <row r="458" spans="3:13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="458" spans="3:13" x14ac:dyDescent="0.3">
       <c r="C458" t="s">
         <v>154</v>
       </c>
@@ -19181,7 +19215,7 @@
         <v>775</v>
       </c>
     </row>
-    <row r="459" spans="3:13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="459" spans="3:13" x14ac:dyDescent="0.3">
       <c r="C459" t="s">
         <v>154</v>
       </c>
@@ -19211,7 +19245,7 @@
         <v>775</v>
       </c>
     </row>
-    <row r="460" spans="3:13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="460" spans="3:13" x14ac:dyDescent="0.3">
       <c r="C460" t="s">
         <v>154</v>
       </c>
@@ -19241,7 +19275,7 @@
         <v>775</v>
       </c>
     </row>
-    <row r="461" spans="3:13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="461" spans="3:13" x14ac:dyDescent="0.3">
       <c r="C461" t="s">
         <v>154</v>
       </c>
@@ -19271,7 +19305,7 @@
         <v>775</v>
       </c>
     </row>
-    <row r="462" spans="3:13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="462" spans="3:13" x14ac:dyDescent="0.3">
       <c r="C462" t="s">
         <v>27</v>
       </c>
@@ -19301,7 +19335,7 @@
         <v>785</v>
       </c>
     </row>
-    <row r="463" spans="3:13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="463" spans="3:13" x14ac:dyDescent="0.3">
       <c r="C463" t="s">
         <v>27</v>
       </c>
@@ -19331,7 +19365,7 @@
         <v>785</v>
       </c>
     </row>
-    <row r="464" spans="3:13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="464" spans="3:13" x14ac:dyDescent="0.3">
       <c r="C464" t="s">
         <v>27</v>
       </c>
@@ -19361,7 +19395,7 @@
         <v>785</v>
       </c>
     </row>
-    <row r="465" spans="3:13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="465" spans="3:13" x14ac:dyDescent="0.3">
       <c r="C465" t="s">
         <v>27</v>
       </c>
@@ -19391,7 +19425,7 @@
         <v>785</v>
       </c>
     </row>
-    <row r="466" spans="3:13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="466" spans="3:13" x14ac:dyDescent="0.3">
       <c r="C466" t="s">
         <v>45</v>
       </c>
@@ -19421,7 +19455,7 @@
         <v>791</v>
       </c>
     </row>
-    <row r="467" spans="3:13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="467" spans="3:13" x14ac:dyDescent="0.3">
       <c r="C467" t="s">
         <v>45</v>
       </c>
@@ -19451,7 +19485,7 @@
         <v>791</v>
       </c>
     </row>
-    <row r="468" spans="3:13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="468" spans="3:13" x14ac:dyDescent="0.3">
       <c r="C468" t="s">
         <v>45</v>
       </c>
@@ -19481,7 +19515,7 @@
         <v>791</v>
       </c>
     </row>
-    <row r="469" spans="3:13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="469" spans="3:13" x14ac:dyDescent="0.3">
       <c r="C469" t="s">
         <v>45</v>
       </c>
@@ -19511,7 +19545,7 @@
         <v>791</v>
       </c>
     </row>
-    <row r="470" spans="3:13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="470" spans="3:13" x14ac:dyDescent="0.3">
       <c r="C470" t="s">
         <v>69</v>
       </c>
@@ -19541,7 +19575,7 @@
         <v>796</v>
       </c>
     </row>
-    <row r="471" spans="3:13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="471" spans="3:13" x14ac:dyDescent="0.3">
       <c r="C471" t="s">
         <v>69</v>
       </c>
@@ -19571,7 +19605,7 @@
         <v>796</v>
       </c>
     </row>
-    <row r="472" spans="3:13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="472" spans="3:13" x14ac:dyDescent="0.3">
       <c r="C472" t="s">
         <v>69</v>
       </c>
@@ -19601,7 +19635,7 @@
         <v>796</v>
       </c>
     </row>
-    <row r="473" spans="3:13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="473" spans="3:13" x14ac:dyDescent="0.3">
       <c r="C473" t="s">
         <v>69</v>
       </c>
@@ -19631,7 +19665,7 @@
         <v>796</v>
       </c>
     </row>
-    <row r="474" spans="3:13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="474" spans="3:13" x14ac:dyDescent="0.3">
       <c r="C474" t="s">
         <v>69</v>
       </c>
@@ -19661,7 +19695,7 @@
         <v>796</v>
       </c>
     </row>
-    <row r="475" spans="3:13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="475" spans="3:13" x14ac:dyDescent="0.3">
       <c r="C475" t="s">
         <v>69</v>
       </c>
@@ -19691,7 +19725,7 @@
         <v>796</v>
       </c>
     </row>
-    <row r="476" spans="3:13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="476" spans="3:13" x14ac:dyDescent="0.3">
       <c r="C476" t="s">
         <v>69</v>
       </c>
@@ -19721,7 +19755,7 @@
         <v>796</v>
       </c>
     </row>
-    <row r="477" spans="3:13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="477" spans="3:13" x14ac:dyDescent="0.3">
       <c r="C477" t="s">
         <v>69</v>
       </c>
@@ -19751,7 +19785,7 @@
         <v>796</v>
       </c>
     </row>
-    <row r="478" spans="3:13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="478" spans="3:13" x14ac:dyDescent="0.3">
       <c r="C478" t="s">
         <v>675</v>
       </c>
@@ -19781,7 +19815,7 @@
         <v>807</v>
       </c>
     </row>
-    <row r="479" spans="3:13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="479" spans="3:13" x14ac:dyDescent="0.3">
       <c r="C479" t="s">
         <v>675</v>
       </c>
@@ -19811,7 +19845,7 @@
         <v>807</v>
       </c>
     </row>
-    <row r="480" spans="3:13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="480" spans="3:13" x14ac:dyDescent="0.3">
       <c r="C480" t="s">
         <v>675</v>
       </c>
@@ -19841,7 +19875,7 @@
         <v>807</v>
       </c>
     </row>
-    <row r="481" spans="2:13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="481" spans="2:13" x14ac:dyDescent="0.3">
       <c r="C481" t="s">
         <v>675</v>
       </c>
@@ -19871,7 +19905,7 @@
         <v>807</v>
       </c>
     </row>
-    <row r="482" spans="2:13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="482" spans="2:13" x14ac:dyDescent="0.3">
       <c r="C482" t="s">
         <v>675</v>
       </c>
@@ -19901,7 +19935,7 @@
         <v>807</v>
       </c>
     </row>
-    <row r="483" spans="2:13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="483" spans="2:13" x14ac:dyDescent="0.3">
       <c r="C483" t="s">
         <v>675</v>
       </c>
@@ -19931,7 +19965,7 @@
         <v>807</v>
       </c>
     </row>
-    <row r="484" spans="2:13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="484" spans="2:13" x14ac:dyDescent="0.3">
       <c r="C484" t="s">
         <v>675</v>
       </c>
@@ -19961,7 +19995,7 @@
         <v>807</v>
       </c>
     </row>
-    <row r="485" spans="2:13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="485" spans="2:13" x14ac:dyDescent="0.3">
       <c r="C485" t="s">
         <v>675</v>
       </c>
@@ -19991,7 +20025,7 @@
         <v>807</v>
       </c>
     </row>
-    <row r="486" spans="2:13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="486" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B486" t="s">
         <v>162</v>
       </c>
@@ -20021,7 +20055,7 @@
         <v>816</v>
       </c>
     </row>
-    <row r="487" spans="2:13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="487" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B487" t="s">
         <v>162</v>
       </c>
@@ -20051,7 +20085,7 @@
         <v>816</v>
       </c>
     </row>
-    <row r="488" spans="2:13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="488" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B488" t="s">
         <v>162</v>
       </c>
@@ -20081,7 +20115,7 @@
         <v>816</v>
       </c>
     </row>
-    <row r="489" spans="2:13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="489" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B489" t="s">
         <v>162</v>
       </c>
@@ -20111,7 +20145,7 @@
         <v>816</v>
       </c>
     </row>
-    <row r="490" spans="2:13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="490" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B490" t="s">
         <v>162</v>
       </c>
@@ -20141,7 +20175,7 @@
         <v>816</v>
       </c>
     </row>
-    <row r="491" spans="2:13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="491" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B491" t="s">
         <v>162</v>
       </c>
@@ -20171,7 +20205,7 @@
         <v>816</v>
       </c>
     </row>
-    <row r="492" spans="2:13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="492" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B492" t="s">
         <v>162</v>
       </c>
@@ -20201,7 +20235,7 @@
         <v>816</v>
       </c>
     </row>
-    <row r="493" spans="2:13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="493" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B493" t="s">
         <v>162</v>
       </c>
@@ -20231,7 +20265,7 @@
         <v>816</v>
       </c>
     </row>
-    <row r="494" spans="2:13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="494" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B494" t="s">
         <v>162</v>
       </c>
@@ -20261,7 +20295,7 @@
         <v>816</v>
       </c>
     </row>
-    <row r="495" spans="2:13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="495" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B495" t="s">
         <v>162</v>
       </c>
@@ -20291,7 +20325,7 @@
         <v>816</v>
       </c>
     </row>
-    <row r="496" spans="2:13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="496" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B496" t="s">
         <v>162</v>
       </c>
@@ -20321,7 +20355,7 @@
         <v>816</v>
       </c>
     </row>
-    <row r="497" spans="2:13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="497" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B497" t="s">
         <v>162</v>
       </c>
@@ -20351,7 +20385,7 @@
         <v>816</v>
       </c>
     </row>
-    <row r="498" spans="2:13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="498" spans="2:13" x14ac:dyDescent="0.3">
       <c r="C498" t="s">
         <v>101</v>
       </c>
@@ -20381,7 +20415,7 @@
         <v>830</v>
       </c>
     </row>
-    <row r="499" spans="2:13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="499" spans="2:13" x14ac:dyDescent="0.3">
       <c r="C499" t="s">
         <v>101</v>
       </c>
@@ -20411,7 +20445,7 @@
         <v>830</v>
       </c>
     </row>
-    <row r="500" spans="2:13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="500" spans="2:13" x14ac:dyDescent="0.3">
       <c r="C500" t="s">
         <v>101</v>
       </c>
@@ -20441,7 +20475,7 @@
         <v>830</v>
       </c>
     </row>
-    <row r="501" spans="2:13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="501" spans="2:13" x14ac:dyDescent="0.3">
       <c r="C501" t="s">
         <v>101</v>
       </c>
@@ -20471,7 +20505,7 @@
         <v>830</v>
       </c>
     </row>
-    <row r="502" spans="2:13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="502" spans="2:13" x14ac:dyDescent="0.3">
       <c r="C502" t="s">
         <v>101</v>
       </c>
@@ -20501,7 +20535,7 @@
         <v>830</v>
       </c>
     </row>
-    <row r="503" spans="2:13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="503" spans="2:13" x14ac:dyDescent="0.3">
       <c r="C503" t="s">
         <v>101</v>
       </c>
@@ -20531,7 +20565,7 @@
         <v>830</v>
       </c>
     </row>
-    <row r="504" spans="2:13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="504" spans="2:13" x14ac:dyDescent="0.3">
       <c r="C504" t="s">
         <v>110</v>
       </c>
@@ -20561,7 +20595,7 @@
         <v>837</v>
       </c>
     </row>
-    <row r="505" spans="2:13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="505" spans="2:13" x14ac:dyDescent="0.3">
       <c r="C505" t="s">
         <v>110</v>
       </c>
@@ -20591,7 +20625,7 @@
         <v>837</v>
       </c>
     </row>
-    <row r="506" spans="2:13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="506" spans="2:13" x14ac:dyDescent="0.3">
       <c r="C506" t="s">
         <v>110</v>
       </c>
@@ -20621,7 +20655,7 @@
         <v>837</v>
       </c>
     </row>
-    <row r="507" spans="2:13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="507" spans="2:13" x14ac:dyDescent="0.3">
       <c r="C507" t="s">
         <v>110</v>
       </c>
@@ -20651,7 +20685,7 @@
         <v>837</v>
       </c>
     </row>
-    <row r="508" spans="2:13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="508" spans="2:13" x14ac:dyDescent="0.3">
       <c r="C508" t="s">
         <v>110</v>
       </c>
@@ -20681,7 +20715,7 @@
         <v>842</v>
       </c>
     </row>
-    <row r="509" spans="2:13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="509" spans="2:13" x14ac:dyDescent="0.3">
       <c r="C509" t="s">
         <v>110</v>
       </c>
@@ -20711,7 +20745,7 @@
         <v>842</v>
       </c>
     </row>
-    <row r="510" spans="2:13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="510" spans="2:13" x14ac:dyDescent="0.3">
       <c r="C510" t="s">
         <v>110</v>
       </c>
@@ -20741,7 +20775,7 @@
         <v>842</v>
       </c>
     </row>
-    <row r="511" spans="2:13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="511" spans="2:13" x14ac:dyDescent="0.3">
       <c r="C511" t="s">
         <v>110</v>
       </c>
@@ -20771,7 +20805,7 @@
         <v>842</v>
       </c>
     </row>
-    <row r="512" spans="2:13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="512" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B512" t="s">
         <v>162</v>
       </c>
@@ -20801,7 +20835,7 @@
         <v>847</v>
       </c>
     </row>
-    <row r="513" spans="2:13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="513" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B513" t="s">
         <v>162</v>
       </c>
@@ -20831,7 +20865,7 @@
         <v>847</v>
       </c>
     </row>
-    <row r="514" spans="2:13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="514" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B514" t="s">
         <v>162</v>
       </c>
@@ -20861,7 +20895,7 @@
         <v>847</v>
       </c>
     </row>
-    <row r="515" spans="2:13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="515" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B515" t="s">
         <v>162</v>
       </c>
@@ -20891,7 +20925,7 @@
         <v>847</v>
       </c>
     </row>
-    <row r="516" spans="2:13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="516" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B516" t="s">
         <v>162</v>
       </c>
@@ -20921,7 +20955,7 @@
         <v>847</v>
       </c>
     </row>
-    <row r="517" spans="2:13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="517" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B517" t="s">
         <v>162</v>
       </c>
@@ -20951,7 +20985,7 @@
         <v>847</v>
       </c>
     </row>
-    <row r="518" spans="2:13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="518" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B518" t="s">
         <v>162</v>
       </c>
@@ -20981,7 +21015,7 @@
         <v>847</v>
       </c>
     </row>
-    <row r="519" spans="2:13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="519" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B519" t="s">
         <v>162</v>
       </c>
@@ -21011,7 +21045,7 @@
         <v>847</v>
       </c>
     </row>
-    <row r="520" spans="2:13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="520" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B520" t="s">
         <v>162</v>
       </c>
@@ -21041,7 +21075,7 @@
         <v>847</v>
       </c>
     </row>
-    <row r="521" spans="2:13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="521" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B521" t="s">
         <v>162</v>
       </c>
@@ -21071,7 +21105,7 @@
         <v>847</v>
       </c>
     </row>
-    <row r="522" spans="2:13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="522" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B522" t="s">
         <v>162</v>
       </c>
@@ -21101,7 +21135,7 @@
         <v>847</v>
       </c>
     </row>
-    <row r="523" spans="2:13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="523" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B523" t="s">
         <v>162</v>
       </c>
@@ -21671,7 +21705,7 @@
         <v>861</v>
       </c>
     </row>
-    <row r="544" spans="2:13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="544" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B544" t="s">
         <v>137</v>
       </c>
@@ -21701,7 +21735,7 @@
         <v>882</v>
       </c>
     </row>
-    <row r="545" spans="2:13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="545" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B545" t="s">
         <v>137</v>
       </c>
@@ -21731,7 +21765,7 @@
         <v>882</v>
       </c>
     </row>
-    <row r="546" spans="2:13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="546" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B546" t="s">
         <v>137</v>
       </c>
@@ -21761,7 +21795,7 @@
         <v>882</v>
       </c>
     </row>
-    <row r="547" spans="2:13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="547" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B547" t="s">
         <v>137</v>
       </c>
@@ -21791,7 +21825,7 @@
         <v>882</v>
       </c>
     </row>
-    <row r="548" spans="2:13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="548" spans="2:13" x14ac:dyDescent="0.3">
       <c r="C548" t="s">
         <v>150</v>
       </c>
@@ -21821,7 +21855,7 @@
         <v>890</v>
       </c>
     </row>
-    <row r="549" spans="2:13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="549" spans="2:13" x14ac:dyDescent="0.3">
       <c r="C549" t="s">
         <v>150</v>
       </c>
@@ -21851,7 +21885,7 @@
         <v>890</v>
       </c>
     </row>
-    <row r="550" spans="2:13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="550" spans="2:13" x14ac:dyDescent="0.3">
       <c r="C550" t="s">
         <v>150</v>
       </c>
@@ -21881,7 +21915,7 @@
         <v>890</v>
       </c>
     </row>
-    <row r="551" spans="2:13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="551" spans="2:13" x14ac:dyDescent="0.3">
       <c r="C551" t="s">
         <v>150</v>
       </c>
@@ -21911,7 +21945,7 @@
         <v>890</v>
       </c>
     </row>
-    <row r="552" spans="2:13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="552" spans="2:13" x14ac:dyDescent="0.3">
       <c r="C552" t="s">
         <v>303</v>
       </c>
@@ -21938,7 +21972,7 @@
         <v>895</v>
       </c>
     </row>
-    <row r="553" spans="2:13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="553" spans="2:13" x14ac:dyDescent="0.3">
       <c r="C553" t="s">
         <v>303</v>
       </c>
@@ -21965,7 +21999,7 @@
         <v>895</v>
       </c>
     </row>
-    <row r="554" spans="2:13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="554" spans="2:13" x14ac:dyDescent="0.3">
       <c r="C554" t="s">
         <v>303</v>
       </c>
@@ -21992,7 +22026,7 @@
         <v>895</v>
       </c>
     </row>
-    <row r="555" spans="2:13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="555" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B555" t="s">
         <v>137</v>
       </c>
@@ -22022,7 +22056,7 @@
         <v>901</v>
       </c>
     </row>
-    <row r="556" spans="2:13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="556" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B556" t="s">
         <v>137</v>
       </c>
@@ -22052,7 +22086,7 @@
         <v>901</v>
       </c>
     </row>
-    <row r="557" spans="2:13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="557" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B557" t="s">
         <v>137</v>
       </c>
@@ -22082,7 +22116,7 @@
         <v>901</v>
       </c>
     </row>
-    <row r="558" spans="2:13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="558" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B558" t="s">
         <v>137</v>
       </c>
@@ -22112,7 +22146,7 @@
         <v>901</v>
       </c>
     </row>
-    <row r="559" spans="2:13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="559" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B559" t="s">
         <v>137</v>
       </c>
@@ -22142,7 +22176,7 @@
         <v>910</v>
       </c>
     </row>
-    <row r="560" spans="2:13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="560" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B560" t="s">
         <v>137</v>
       </c>
@@ -22172,7 +22206,7 @@
         <v>910</v>
       </c>
     </row>
-    <row r="561" spans="2:13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="561" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B561" t="s">
         <v>137</v>
       </c>
@@ -22202,7 +22236,7 @@
         <v>910</v>
       </c>
     </row>
-    <row r="562" spans="2:13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="562" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B562" t="s">
         <v>137</v>
       </c>
@@ -22232,7 +22266,7 @@
         <v>910</v>
       </c>
     </row>
-    <row r="563" spans="2:13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="563" spans="2:13" x14ac:dyDescent="0.3">
       <c r="C563" t="s">
         <v>154</v>
       </c>
@@ -22262,7 +22296,7 @@
         <v>918</v>
       </c>
     </row>
-    <row r="564" spans="2:13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="564" spans="2:13" x14ac:dyDescent="0.3">
       <c r="C564" t="s">
         <v>154</v>
       </c>
@@ -22292,7 +22326,7 @@
         <v>918</v>
       </c>
     </row>
-    <row r="565" spans="2:13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="565" spans="2:13" x14ac:dyDescent="0.3">
       <c r="C565" t="s">
         <v>154</v>
       </c>
@@ -22322,7 +22356,7 @@
         <v>918</v>
       </c>
     </row>
-    <row r="566" spans="2:13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="566" spans="2:13" x14ac:dyDescent="0.3">
       <c r="C566" t="s">
         <v>154</v>
       </c>
@@ -22352,7 +22386,7 @@
         <v>918</v>
       </c>
     </row>
-    <row r="567" spans="2:13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="567" spans="2:13" x14ac:dyDescent="0.3">
       <c r="C567" t="s">
         <v>154</v>
       </c>
@@ -22382,7 +22416,7 @@
         <v>918</v>
       </c>
     </row>
-    <row r="568" spans="2:13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="568" spans="2:13" x14ac:dyDescent="0.3">
       <c r="C568" t="s">
         <v>154</v>
       </c>
@@ -22412,7 +22446,7 @@
         <v>918</v>
       </c>
     </row>
-    <row r="569" spans="2:13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="569" spans="2:13" x14ac:dyDescent="0.3">
       <c r="C569" t="s">
         <v>154</v>
       </c>
@@ -22442,7 +22476,7 @@
         <v>918</v>
       </c>
     </row>
-    <row r="570" spans="2:13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="570" spans="2:13" x14ac:dyDescent="0.3">
       <c r="C570" t="s">
         <v>154</v>
       </c>
@@ -22472,7 +22506,7 @@
         <v>918</v>
       </c>
     </row>
-    <row r="571" spans="2:13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="571" spans="2:13" x14ac:dyDescent="0.3">
       <c r="C571" t="s">
         <v>45</v>
       </c>
@@ -22502,7 +22536,7 @@
         <v>929</v>
       </c>
     </row>
-    <row r="572" spans="2:13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="572" spans="2:13" x14ac:dyDescent="0.3">
       <c r="C572" t="s">
         <v>45</v>
       </c>
@@ -22532,7 +22566,7 @@
         <v>929</v>
       </c>
     </row>
-    <row r="573" spans="2:13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="573" spans="2:13" x14ac:dyDescent="0.3">
       <c r="C573" t="s">
         <v>45</v>
       </c>
@@ -22562,7 +22596,7 @@
         <v>929</v>
       </c>
     </row>
-    <row r="574" spans="2:13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="574" spans="2:13" x14ac:dyDescent="0.3">
       <c r="C574" t="s">
         <v>45</v>
       </c>
@@ -22592,7 +22626,7 @@
         <v>929</v>
       </c>
     </row>
-    <row r="575" spans="2:13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="575" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B575" t="s">
         <v>137</v>
       </c>
@@ -22622,7 +22656,7 @@
         <v>935</v>
       </c>
     </row>
-    <row r="576" spans="2:13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="576" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B576" t="s">
         <v>137</v>
       </c>
@@ -22652,7 +22686,7 @@
         <v>935</v>
       </c>
     </row>
-    <row r="577" spans="2:13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="577" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B577" t="s">
         <v>137</v>
       </c>
@@ -22682,7 +22716,7 @@
         <v>941</v>
       </c>
     </row>
-    <row r="578" spans="2:13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="578" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B578" t="s">
         <v>137</v>
       </c>
@@ -22712,7 +22746,7 @@
         <v>941</v>
       </c>
     </row>
-    <row r="579" spans="2:13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="579" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B579" t="s">
         <v>137</v>
       </c>
@@ -22742,7 +22776,7 @@
         <v>947</v>
       </c>
     </row>
-    <row r="580" spans="2:13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="580" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B580" t="s">
         <v>137</v>
       </c>
@@ -22772,7 +22806,7 @@
         <v>947</v>
       </c>
     </row>
-    <row r="581" spans="2:13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="581" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B581" t="s">
         <v>137</v>
       </c>
@@ -22802,7 +22836,7 @@
         <v>952</v>
       </c>
     </row>
-    <row r="582" spans="2:13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="582" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B582" t="s">
         <v>137</v>
       </c>
@@ -22832,7 +22866,7 @@
         <v>952</v>
       </c>
     </row>
-    <row r="583" spans="2:13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="583" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B583" t="s">
         <v>137</v>
       </c>
@@ -22862,7 +22896,7 @@
         <v>952</v>
       </c>
     </row>
-    <row r="584" spans="2:13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="584" spans="2:13" x14ac:dyDescent="0.3">
       <c r="C584" t="s">
         <v>154</v>
       </c>
@@ -22892,7 +22926,7 @@
         <v>959</v>
       </c>
     </row>
-    <row r="585" spans="2:13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="585" spans="2:13" x14ac:dyDescent="0.3">
       <c r="C585" t="s">
         <v>154</v>
       </c>
@@ -22922,7 +22956,7 @@
         <v>959</v>
       </c>
     </row>
-    <row r="586" spans="2:13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="586" spans="2:13" x14ac:dyDescent="0.3">
       <c r="C586" t="s">
         <v>154</v>
       </c>
@@ -22952,7 +22986,7 @@
         <v>959</v>
       </c>
     </row>
-    <row r="587" spans="2:13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="587" spans="2:13" x14ac:dyDescent="0.3">
       <c r="C587" t="s">
         <v>154</v>
       </c>
@@ -22982,7 +23016,7 @@
         <v>959</v>
       </c>
     </row>
-    <row r="588" spans="2:13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="588" spans="2:13" x14ac:dyDescent="0.3">
       <c r="C588" t="s">
         <v>27</v>
       </c>
@@ -23012,7 +23046,7 @@
         <v>965</v>
       </c>
     </row>
-    <row r="589" spans="2:13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="589" spans="2:13" x14ac:dyDescent="0.3">
       <c r="C589" t="s">
         <v>27</v>
       </c>
@@ -23042,7 +23076,7 @@
         <v>965</v>
       </c>
     </row>
-    <row r="590" spans="2:13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="590" spans="2:13" x14ac:dyDescent="0.3">
       <c r="C590" t="s">
         <v>27</v>
       </c>
@@ -23072,7 +23106,7 @@
         <v>965</v>
       </c>
     </row>
-    <row r="591" spans="2:13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="591" spans="2:13" x14ac:dyDescent="0.3">
       <c r="C591" t="s">
         <v>27</v>
       </c>
@@ -23102,7 +23136,7 @@
         <v>965</v>
       </c>
     </row>
-    <row r="592" spans="2:13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="592" spans="2:13" x14ac:dyDescent="0.3">
       <c r="C592" t="s">
         <v>45</v>
       </c>
@@ -23132,7 +23166,7 @@
         <v>971</v>
       </c>
     </row>
-    <row r="593" spans="2:13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="593" spans="2:13" x14ac:dyDescent="0.3">
       <c r="C593" t="s">
         <v>45</v>
       </c>
@@ -23162,7 +23196,7 @@
         <v>971</v>
       </c>
     </row>
-    <row r="594" spans="2:13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="594" spans="2:13" x14ac:dyDescent="0.3">
       <c r="C594" t="s">
         <v>45</v>
       </c>
@@ -23192,7 +23226,7 @@
         <v>971</v>
       </c>
     </row>
-    <row r="595" spans="2:13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="595" spans="2:13" x14ac:dyDescent="0.3">
       <c r="C595" t="s">
         <v>45</v>
       </c>
@@ -23222,7 +23256,7 @@
         <v>971</v>
       </c>
     </row>
-    <row r="596" spans="2:13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="596" spans="2:13" x14ac:dyDescent="0.3">
       <c r="C596" t="s">
         <v>69</v>
       </c>
@@ -23252,7 +23286,7 @@
         <v>976</v>
       </c>
     </row>
-    <row r="597" spans="2:13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="597" spans="2:13" x14ac:dyDescent="0.3">
       <c r="C597" t="s">
         <v>69</v>
       </c>
@@ -23282,7 +23316,7 @@
         <v>976</v>
       </c>
     </row>
-    <row r="598" spans="2:13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="598" spans="2:13" x14ac:dyDescent="0.3">
       <c r="C598" t="s">
         <v>69</v>
       </c>
@@ -23312,7 +23346,7 @@
         <v>976</v>
       </c>
     </row>
-    <row r="599" spans="2:13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="599" spans="2:13" x14ac:dyDescent="0.3">
       <c r="C599" t="s">
         <v>69</v>
       </c>
@@ -23342,7 +23376,7 @@
         <v>976</v>
       </c>
     </row>
-    <row r="600" spans="2:13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="600" spans="2:13" x14ac:dyDescent="0.3">
       <c r="C600" t="s">
         <v>69</v>
       </c>
@@ -23372,7 +23406,7 @@
         <v>976</v>
       </c>
     </row>
-    <row r="601" spans="2:13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="601" spans="2:13" x14ac:dyDescent="0.3">
       <c r="C601" t="s">
         <v>69</v>
       </c>
@@ -23402,7 +23436,7 @@
         <v>976</v>
       </c>
     </row>
-    <row r="602" spans="2:13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="602" spans="2:13" x14ac:dyDescent="0.3">
       <c r="C602" t="s">
         <v>69</v>
       </c>
@@ -23432,7 +23466,7 @@
         <v>976</v>
       </c>
     </row>
-    <row r="603" spans="2:13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="603" spans="2:13" x14ac:dyDescent="0.3">
       <c r="C603" t="s">
         <v>69</v>
       </c>
@@ -23462,7 +23496,7 @@
         <v>976</v>
       </c>
     </row>
-    <row r="604" spans="2:13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="604" spans="2:13" x14ac:dyDescent="0.3">
       <c r="C604" t="s">
         <v>90</v>
       </c>
@@ -23492,7 +23526,7 @@
         <v>985</v>
       </c>
     </row>
-    <row r="605" spans="2:13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="605" spans="2:13" x14ac:dyDescent="0.3">
       <c r="C605" t="s">
         <v>90</v>
       </c>
@@ -23522,7 +23556,7 @@
         <v>985</v>
       </c>
     </row>
-    <row r="606" spans="2:13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="606" spans="2:13" x14ac:dyDescent="0.3">
       <c r="C606" t="s">
         <v>90</v>
       </c>
@@ -23552,7 +23586,7 @@
         <v>985</v>
       </c>
     </row>
-    <row r="607" spans="2:13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="607" spans="2:13" x14ac:dyDescent="0.3">
       <c r="C607" t="s">
         <v>90</v>
       </c>
@@ -23582,7 +23616,7 @@
         <v>985</v>
       </c>
     </row>
-    <row r="608" spans="2:13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="608" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B608" t="s">
         <v>162</v>
       </c>
@@ -23612,7 +23646,7 @@
         <v>990</v>
       </c>
     </row>
-    <row r="609" spans="2:13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="609" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B609" t="s">
         <v>162</v>
       </c>
@@ -23642,7 +23676,7 @@
         <v>990</v>
       </c>
     </row>
-    <row r="610" spans="2:13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="610" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B610" t="s">
         <v>162</v>
       </c>
@@ -23672,7 +23706,7 @@
         <v>990</v>
       </c>
     </row>
-    <row r="611" spans="2:13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="611" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B611" t="s">
         <v>162</v>
       </c>
@@ -23702,7 +23736,7 @@
         <v>990</v>
       </c>
     </row>
-    <row r="612" spans="2:13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="612" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B612" t="s">
         <v>162</v>
       </c>
@@ -23732,7 +23766,7 @@
         <v>990</v>
       </c>
     </row>
-    <row r="613" spans="2:13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="613" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B613" t="s">
         <v>162</v>
       </c>
@@ -23762,7 +23796,7 @@
         <v>990</v>
       </c>
     </row>
-    <row r="614" spans="2:13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="614" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B614" t="s">
         <v>162</v>
       </c>
@@ -23792,7 +23826,7 @@
         <v>990</v>
       </c>
     </row>
-    <row r="615" spans="2:13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="615" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B615" t="s">
         <v>162</v>
       </c>
@@ -23822,7 +23856,7 @@
         <v>990</v>
       </c>
     </row>
-    <row r="616" spans="2:13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="616" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B616" t="s">
         <v>162</v>
       </c>
@@ -23852,7 +23886,7 @@
         <v>990</v>
       </c>
     </row>
-    <row r="617" spans="2:13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="617" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B617" t="s">
         <v>137</v>
       </c>
@@ -23885,7 +23919,7 @@
         <v>1001</v>
       </c>
     </row>
-    <row r="618" spans="2:13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="618" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B618" t="s">
         <v>137</v>
       </c>
@@ -23918,7 +23952,7 @@
         <v>1001</v>
       </c>
     </row>
-    <row r="619" spans="2:13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="619" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B619" t="s">
         <v>137</v>
       </c>
@@ -23951,7 +23985,7 @@
         <v>1001</v>
       </c>
     </row>
-    <row r="620" spans="2:13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="620" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B620" t="s">
         <v>137</v>
       </c>
@@ -23984,7 +24018,7 @@
         <v>1001</v>
       </c>
     </row>
-    <row r="621" spans="2:13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="621" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B621" t="s">
         <v>137</v>
       </c>
@@ -24017,7 +24051,7 @@
         <v>1001</v>
       </c>
     </row>
-    <row r="622" spans="2:13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="622" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B622" t="s">
         <v>137</v>
       </c>
@@ -24050,7 +24084,7 @@
         <v>1001</v>
       </c>
     </row>
-    <row r="623" spans="2:13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="623" spans="2:13" x14ac:dyDescent="0.3">
       <c r="C623" t="s">
         <v>101</v>
       </c>
@@ -24080,7 +24114,7 @@
         <v>1014</v>
       </c>
     </row>
-    <row r="624" spans="2:13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="624" spans="2:13" x14ac:dyDescent="0.3">
       <c r="C624" t="s">
         <v>101</v>
       </c>
@@ -24110,7 +24144,7 @@
         <v>1014</v>
       </c>
     </row>
-    <row r="625" spans="2:13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="625" spans="2:13" x14ac:dyDescent="0.3">
       <c r="C625" t="s">
         <v>101</v>
       </c>
@@ -24140,7 +24174,7 @@
         <v>1014</v>
       </c>
     </row>
-    <row r="626" spans="2:13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="626" spans="2:13" x14ac:dyDescent="0.3">
       <c r="C626" t="s">
         <v>101</v>
       </c>
@@ -24170,7 +24204,7 @@
         <v>1014</v>
       </c>
     </row>
-    <row r="627" spans="2:13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="627" spans="2:13" x14ac:dyDescent="0.3">
       <c r="C627" t="s">
         <v>101</v>
       </c>
@@ -24200,7 +24234,7 @@
         <v>1014</v>
       </c>
     </row>
-    <row r="628" spans="2:13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="628" spans="2:13" x14ac:dyDescent="0.3">
       <c r="C628" t="s">
         <v>101</v>
       </c>
@@ -24230,7 +24264,7 @@
         <v>1014</v>
       </c>
     </row>
-    <row r="629" spans="2:13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="629" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B629" t="s">
         <v>137</v>
       </c>
@@ -24260,7 +24294,7 @@
         <v>1021</v>
       </c>
     </row>
-    <row r="630" spans="2:13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="630" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B630" t="s">
         <v>137</v>
       </c>
@@ -24290,7 +24324,7 @@
         <v>1021</v>
       </c>
     </row>
-    <row r="631" spans="2:13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="631" spans="2:13" x14ac:dyDescent="0.3">
       <c r="C631" t="s">
         <v>399</v>
       </c>
@@ -24320,7 +24354,7 @@
         <v>1026</v>
       </c>
     </row>
-    <row r="632" spans="2:13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="632" spans="2:13" x14ac:dyDescent="0.3">
       <c r="C632" t="s">
         <v>399</v>
       </c>
@@ -24350,7 +24384,7 @@
         <v>1026</v>
       </c>
     </row>
-    <row r="633" spans="2:13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="633" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B633" t="s">
         <v>162</v>
       </c>
@@ -24380,7 +24414,7 @@
         <v>1030</v>
       </c>
     </row>
-    <row r="634" spans="2:13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="634" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B634" t="s">
         <v>162</v>
       </c>
@@ -24410,7 +24444,7 @@
         <v>1030</v>
       </c>
     </row>
-    <row r="635" spans="2:13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="635" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B635" t="s">
         <v>162</v>
       </c>
@@ -24440,7 +24474,7 @@
         <v>1030</v>
       </c>
     </row>
-    <row r="636" spans="2:13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="636" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B636" t="s">
         <v>162</v>
       </c>
@@ -24470,7 +24504,7 @@
         <v>1030</v>
       </c>
     </row>
-    <row r="637" spans="2:13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="637" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B637" t="s">
         <v>162</v>
       </c>
@@ -24500,7 +24534,7 @@
         <v>1030</v>
       </c>
     </row>
-    <row r="638" spans="2:13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="638" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B638" t="s">
         <v>162</v>
       </c>
@@ -24530,7 +24564,7 @@
         <v>1030</v>
       </c>
     </row>
-    <row r="639" spans="2:13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="639" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B639" t="s">
         <v>162</v>
       </c>
@@ -24560,7 +24594,7 @@
         <v>1030</v>
       </c>
     </row>
-    <row r="640" spans="2:13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="640" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B640" t="s">
         <v>162</v>
       </c>
@@ -24590,7 +24624,7 @@
         <v>1030</v>
       </c>
     </row>
-    <row r="641" spans="2:13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="641" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B641" t="s">
         <v>162</v>
       </c>
@@ -24620,7 +24654,7 @@
         <v>1030</v>
       </c>
     </row>
-    <row r="642" spans="2:13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="642" spans="2:13" x14ac:dyDescent="0.3">
       <c r="C642" t="s">
         <v>129</v>
       </c>
@@ -24650,7 +24684,7 @@
         <v>1038</v>
       </c>
     </row>
-    <row r="643" spans="2:13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="643" spans="2:13" x14ac:dyDescent="0.3">
       <c r="C643" t="s">
         <v>129</v>
       </c>
@@ -24680,7 +24714,7 @@
         <v>1038</v>
       </c>
     </row>
-    <row r="644" spans="2:13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="644" spans="2:13" x14ac:dyDescent="0.3">
       <c r="C644" t="s">
         <v>129</v>
       </c>
@@ -24710,7 +24744,7 @@
         <v>1038</v>
       </c>
     </row>
-    <row r="645" spans="2:13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="645" spans="2:13" x14ac:dyDescent="0.3">
       <c r="C645" t="s">
         <v>129</v>
       </c>
@@ -24740,7 +24774,7 @@
         <v>1038</v>
       </c>
     </row>
-    <row r="646" spans="2:13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="646" spans="2:13" x14ac:dyDescent="0.3">
       <c r="D646" t="s">
         <v>1041</v>
       </c>
@@ -24767,7 +24801,7 @@
         <v>1043</v>
       </c>
     </row>
-    <row r="647" spans="2:13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="647" spans="2:13" x14ac:dyDescent="0.3">
       <c r="D647" t="s">
         <v>1041</v>
       </c>
@@ -24794,7 +24828,7 @@
         <v>1043</v>
       </c>
     </row>
-    <row r="648" spans="2:13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="648" spans="2:13" x14ac:dyDescent="0.3">
       <c r="D648" t="s">
         <v>1041</v>
       </c>
@@ -24821,7 +24855,7 @@
         <v>1043</v>
       </c>
     </row>
-    <row r="649" spans="2:13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="649" spans="2:13" x14ac:dyDescent="0.3">
       <c r="D649" t="s">
         <v>1041</v>
       </c>
@@ -24908,7 +24942,7 @@
         <v>1050</v>
       </c>
     </row>
-    <row r="652" spans="2:13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="652" spans="2:13" x14ac:dyDescent="0.3">
       <c r="C652" t="s">
         <v>154</v>
       </c>
@@ -24938,7 +24972,7 @@
         <v>1055</v>
       </c>
     </row>
-    <row r="653" spans="2:13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="653" spans="2:13" x14ac:dyDescent="0.3">
       <c r="C653" t="s">
         <v>154</v>
       </c>
@@ -24968,7 +25002,7 @@
         <v>1055</v>
       </c>
     </row>
-    <row r="654" spans="2:13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="654" spans="2:13" x14ac:dyDescent="0.3">
       <c r="C654" t="s">
         <v>154</v>
       </c>
@@ -24998,7 +25032,7 @@
         <v>1055</v>
       </c>
     </row>
-    <row r="655" spans="2:13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="655" spans="2:13" x14ac:dyDescent="0.3">
       <c r="C655" t="s">
         <v>154</v>
       </c>
@@ -25028,7 +25062,7 @@
         <v>1055</v>
       </c>
     </row>
-    <row r="656" spans="2:13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="656" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B656" t="s">
         <v>137</v>
       </c>
@@ -25055,7 +25089,7 @@
         <v>1061</v>
       </c>
     </row>
-    <row r="657" spans="2:13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="657" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B657" t="s">
         <v>137</v>
       </c>
@@ -25085,7 +25119,7 @@
         <v>1061</v>
       </c>
     </row>
-    <row r="658" spans="2:13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="658" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B658" t="s">
         <v>137</v>
       </c>
@@ -25115,7 +25149,7 @@
         <v>1061</v>
       </c>
     </row>
-    <row r="659" spans="2:13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="659" spans="2:13" x14ac:dyDescent="0.3">
       <c r="C659" t="s">
         <v>45</v>
       </c>
@@ -25145,7 +25179,7 @@
         <v>1069</v>
       </c>
     </row>
-    <row r="660" spans="2:13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="660" spans="2:13" x14ac:dyDescent="0.3">
       <c r="C660" t="s">
         <v>45</v>
       </c>
@@ -25175,7 +25209,7 @@
         <v>1069</v>
       </c>
     </row>
-    <row r="661" spans="2:13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="661" spans="2:13" x14ac:dyDescent="0.3">
       <c r="C661" t="s">
         <v>45</v>
       </c>
@@ -25208,7 +25242,7 @@
         <v>1069</v>
       </c>
     </row>
-    <row r="662" spans="2:13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="662" spans="2:13" x14ac:dyDescent="0.3">
       <c r="C662" t="s">
         <v>45</v>
       </c>
@@ -25238,7 +25272,7 @@
         <v>1069</v>
       </c>
     </row>
-    <row r="663" spans="2:13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="663" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B663" t="s">
         <v>593</v>
       </c>
@@ -25271,7 +25305,7 @@
         <v>1077</v>
       </c>
     </row>
-    <row r="664" spans="2:13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="664" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B664" t="s">
         <v>593</v>
       </c>
@@ -25304,7 +25338,7 @@
         <v>1077</v>
       </c>
     </row>
-    <row r="665" spans="2:13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="665" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B665" t="s">
         <v>593</v>
       </c>
@@ -25337,7 +25371,7 @@
         <v>1077</v>
       </c>
     </row>
-    <row r="666" spans="2:13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="666" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B666" t="s">
         <v>593</v>
       </c>
@@ -25373,7 +25407,7 @@
         <v>1077</v>
       </c>
     </row>
-    <row r="667" spans="2:13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="667" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B667" t="s">
         <v>593</v>
       </c>
@@ -25406,7 +25440,7 @@
         <v>1077</v>
       </c>
     </row>
-    <row r="668" spans="2:13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="668" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B668" t="s">
         <v>593</v>
       </c>
@@ -25442,7 +25476,7 @@
         <v>1077</v>
       </c>
     </row>
-    <row r="669" spans="2:13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="669" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B669" t="s">
         <v>593</v>
       </c>
@@ -25478,7 +25512,7 @@
         <v>1077</v>
       </c>
     </row>
-    <row r="670" spans="2:13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="670" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B670" t="s">
         <v>593</v>
       </c>
@@ -25511,7 +25545,7 @@
         <v>1077</v>
       </c>
     </row>
-    <row r="671" spans="2:13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="671" spans="2:13" x14ac:dyDescent="0.3">
       <c r="D671" t="s">
         <v>1088</v>
       </c>
@@ -25538,7 +25572,7 @@
         <v>1090</v>
       </c>
     </row>
-    <row r="672" spans="2:13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="672" spans="2:13" x14ac:dyDescent="0.3">
       <c r="D672" t="s">
         <v>1088</v>
       </c>
@@ -25565,7 +25599,7 @@
         <v>1090</v>
       </c>
     </row>
-    <row r="673" spans="3:13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="673" spans="3:13" x14ac:dyDescent="0.3">
       <c r="D673" t="s">
         <v>1088</v>
       </c>
@@ -25592,7 +25626,7 @@
         <v>1090</v>
       </c>
     </row>
-    <row r="674" spans="3:13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="674" spans="3:13" x14ac:dyDescent="0.3">
       <c r="D674" t="s">
         <v>1088</v>
       </c>
@@ -25619,7 +25653,7 @@
         <v>1090</v>
       </c>
     </row>
-    <row r="675" spans="3:13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="675" spans="3:13" x14ac:dyDescent="0.3">
       <c r="C675" t="s">
         <v>1094</v>
       </c>
@@ -25649,7 +25683,7 @@
         <v>1096</v>
       </c>
     </row>
-    <row r="676" spans="3:13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="676" spans="3:13" x14ac:dyDescent="0.3">
       <c r="C676" t="s">
         <v>1094</v>
       </c>
@@ -25679,7 +25713,7 @@
         <v>1096</v>
       </c>
     </row>
-    <row r="677" spans="3:13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="677" spans="3:13" x14ac:dyDescent="0.3">
       <c r="C677" t="s">
         <v>1094</v>
       </c>
@@ -25709,7 +25743,7 @@
         <v>1096</v>
       </c>
     </row>
-    <row r="678" spans="3:13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="678" spans="3:13" x14ac:dyDescent="0.3">
       <c r="C678" t="s">
         <v>1094</v>
       </c>
@@ -25739,7 +25773,7 @@
         <v>1096</v>
       </c>
     </row>
-    <row r="679" spans="3:13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="679" spans="3:13" x14ac:dyDescent="0.3">
       <c r="C679" t="s">
         <v>1094</v>
       </c>
@@ -25769,7 +25803,7 @@
         <v>1096</v>
       </c>
     </row>
-    <row r="680" spans="3:13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="680" spans="3:13" x14ac:dyDescent="0.3">
       <c r="C680" t="s">
         <v>1094</v>
       </c>
@@ -25799,7 +25833,7 @@
         <v>1096</v>
       </c>
     </row>
-    <row r="681" spans="3:13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="681" spans="3:13" x14ac:dyDescent="0.3">
       <c r="C681" t="s">
         <v>1094</v>
       </c>
@@ -25829,7 +25863,7 @@
         <v>1096</v>
       </c>
     </row>
-    <row r="682" spans="3:13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="682" spans="3:13" x14ac:dyDescent="0.3">
       <c r="C682" t="s">
         <v>1094</v>
       </c>
@@ -25859,7 +25893,7 @@
         <v>1096</v>
       </c>
     </row>
-    <row r="683" spans="3:13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="683" spans="3:13" x14ac:dyDescent="0.3">
       <c r="C683" t="s">
         <v>69</v>
       </c>
@@ -25889,7 +25923,7 @@
         <v>1105</v>
       </c>
     </row>
-    <row r="684" spans="3:13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="684" spans="3:13" x14ac:dyDescent="0.3">
       <c r="C684" t="s">
         <v>69</v>
       </c>
@@ -25919,7 +25953,7 @@
         <v>1105</v>
       </c>
     </row>
-    <row r="685" spans="3:13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="685" spans="3:13" x14ac:dyDescent="0.3">
       <c r="C685" t="s">
         <v>69</v>
       </c>
@@ -25949,7 +25983,7 @@
         <v>1105</v>
       </c>
     </row>
-    <row r="686" spans="3:13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="686" spans="3:13" x14ac:dyDescent="0.3">
       <c r="C686" t="s">
         <v>69</v>
       </c>
@@ -25979,7 +26013,7 @@
         <v>1105</v>
       </c>
     </row>
-    <row r="687" spans="3:13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="687" spans="3:13" x14ac:dyDescent="0.3">
       <c r="C687" t="s">
         <v>69</v>
       </c>
@@ -26009,7 +26043,7 @@
         <v>1105</v>
       </c>
     </row>
-    <row r="688" spans="3:13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="688" spans="3:13" x14ac:dyDescent="0.3">
       <c r="C688" t="s">
         <v>69</v>
       </c>
@@ -26039,7 +26073,7 @@
         <v>1105</v>
       </c>
     </row>
-    <row r="689" spans="2:13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="689" spans="2:13" x14ac:dyDescent="0.3">
       <c r="C689" t="s">
         <v>69</v>
       </c>
@@ -26069,7 +26103,7 @@
         <v>1105</v>
       </c>
     </row>
-    <row r="690" spans="2:13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="690" spans="2:13" x14ac:dyDescent="0.3">
       <c r="C690" t="s">
         <v>69</v>
       </c>
@@ -26099,7 +26133,7 @@
         <v>1105</v>
       </c>
     </row>
-    <row r="691" spans="2:13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="691" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B691" t="s">
         <v>162</v>
       </c>
@@ -26129,7 +26163,7 @@
         <v>1115</v>
       </c>
     </row>
-    <row r="692" spans="2:13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="692" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B692" t="s">
         <v>162</v>
       </c>
@@ -26159,7 +26193,7 @@
         <v>1115</v>
       </c>
     </row>
-    <row r="693" spans="2:13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="693" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B693" t="s">
         <v>162</v>
       </c>
@@ -26189,7 +26223,7 @@
         <v>1115</v>
       </c>
     </row>
-    <row r="694" spans="2:13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="694" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B694" t="s">
         <v>162</v>
       </c>
@@ -26219,7 +26253,7 @@
         <v>1115</v>
       </c>
     </row>
-    <row r="695" spans="2:13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="695" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B695" t="s">
         <v>162</v>
       </c>
@@ -26249,7 +26283,7 @@
         <v>1115</v>
       </c>
     </row>
-    <row r="696" spans="2:13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="696" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B696" t="s">
         <v>162</v>
       </c>
@@ -26279,7 +26313,7 @@
         <v>1115</v>
       </c>
     </row>
-    <row r="697" spans="2:13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="697" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B697" t="s">
         <v>162</v>
       </c>
@@ -26309,7 +26343,7 @@
         <v>1115</v>
       </c>
     </row>
-    <row r="698" spans="2:13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="698" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B698" t="s">
         <v>162</v>
       </c>
@@ -26339,7 +26373,7 @@
         <v>1115</v>
       </c>
     </row>
-    <row r="699" spans="2:13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="699" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B699" t="s">
         <v>162</v>
       </c>
@@ -26369,7 +26403,7 @@
         <v>1115</v>
       </c>
     </row>
-    <row r="700" spans="2:13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="700" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B700" t="s">
         <v>137</v>
       </c>
@@ -26402,7 +26436,7 @@
         <v>1125</v>
       </c>
     </row>
-    <row r="701" spans="2:13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="701" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B701" t="s">
         <v>137</v>
       </c>
@@ -26435,7 +26469,7 @@
         <v>1125</v>
       </c>
     </row>
-    <row r="702" spans="2:13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="702" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B702" t="s">
         <v>137</v>
       </c>
@@ -26468,7 +26502,7 @@
         <v>1125</v>
       </c>
     </row>
-    <row r="703" spans="2:13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="703" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B703" t="s">
         <v>137</v>
       </c>
@@ -26501,7 +26535,7 @@
         <v>1125</v>
       </c>
     </row>
-    <row r="704" spans="2:13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="704" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B704" t="s">
         <v>137</v>
       </c>
@@ -26534,7 +26568,7 @@
         <v>1125</v>
       </c>
     </row>
-    <row r="705" spans="2:13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="705" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B705" t="s">
         <v>137</v>
       </c>
@@ -26567,7 +26601,7 @@
         <v>1125</v>
       </c>
     </row>
-    <row r="706" spans="2:13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="706" spans="2:13" x14ac:dyDescent="0.3">
       <c r="C706" t="s">
         <v>101</v>
       </c>
@@ -26597,7 +26631,7 @@
         <v>1136</v>
       </c>
     </row>
-    <row r="707" spans="2:13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="707" spans="2:13" x14ac:dyDescent="0.3">
       <c r="C707" t="s">
         <v>101</v>
       </c>
@@ -26627,7 +26661,7 @@
         <v>1136</v>
       </c>
     </row>
-    <row r="708" spans="2:13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="708" spans="2:13" x14ac:dyDescent="0.3">
       <c r="C708" t="s">
         <v>101</v>
       </c>
@@ -26657,7 +26691,7 @@
         <v>1136</v>
       </c>
     </row>
-    <row r="709" spans="2:13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="709" spans="2:13" x14ac:dyDescent="0.3">
       <c r="C709" t="s">
         <v>101</v>
       </c>
@@ -26687,7 +26721,7 @@
         <v>1136</v>
       </c>
     </row>
-    <row r="710" spans="2:13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="710" spans="2:13" x14ac:dyDescent="0.3">
       <c r="C710" t="s">
         <v>101</v>
       </c>
@@ -26717,7 +26751,7 @@
         <v>1136</v>
       </c>
     </row>
-    <row r="711" spans="2:13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="711" spans="2:13" x14ac:dyDescent="0.3">
       <c r="C711" t="s">
         <v>101</v>
       </c>
@@ -26747,7 +26781,7 @@
         <v>1136</v>
       </c>
     </row>
-    <row r="712" spans="2:13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="712" spans="2:13" x14ac:dyDescent="0.3">
       <c r="C712" t="s">
         <v>399</v>
       </c>
@@ -26777,7 +26811,7 @@
         <v>1144</v>
       </c>
     </row>
-    <row r="713" spans="2:13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="713" spans="2:13" x14ac:dyDescent="0.3">
       <c r="C713" t="s">
         <v>399</v>
       </c>
@@ -26807,7 +26841,7 @@
         <v>1144</v>
       </c>
     </row>
-    <row r="714" spans="2:13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="714" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B714" t="s">
         <v>162</v>
       </c>
@@ -26837,7 +26871,7 @@
         <v>1148</v>
       </c>
     </row>
-    <row r="715" spans="2:13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="715" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B715" t="s">
         <v>162</v>
       </c>
@@ -26867,7 +26901,7 @@
         <v>1148</v>
       </c>
     </row>
-    <row r="716" spans="2:13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="716" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B716" t="s">
         <v>162</v>
       </c>
@@ -26897,7 +26931,7 @@
         <v>1148</v>
       </c>
     </row>
-    <row r="717" spans="2:13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="717" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B717" t="s">
         <v>162</v>
       </c>
@@ -26927,7 +26961,7 @@
         <v>1148</v>
       </c>
     </row>
-    <row r="718" spans="2:13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="718" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B718" t="s">
         <v>162</v>
       </c>
@@ -26957,7 +26991,7 @@
         <v>1148</v>
       </c>
     </row>
-    <row r="719" spans="2:13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="719" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B719" t="s">
         <v>162</v>
       </c>
@@ -26987,7 +27021,7 @@
         <v>1148</v>
       </c>
     </row>
-    <row r="720" spans="2:13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="720" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B720" t="s">
         <v>162</v>
       </c>
@@ -27017,7 +27051,7 @@
         <v>1148</v>
       </c>
     </row>
-    <row r="721" spans="2:13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="721" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B721" t="s">
         <v>162</v>
       </c>
@@ -27047,7 +27081,7 @@
         <v>1148</v>
       </c>
     </row>
-    <row r="722" spans="2:13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="722" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B722" t="s">
         <v>162</v>
       </c>
@@ -27077,7 +27111,7 @@
         <v>1148</v>
       </c>
     </row>
-    <row r="723" spans="2:13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="723" spans="2:13" x14ac:dyDescent="0.3">
       <c r="C723" t="s">
         <v>129</v>
       </c>
@@ -27107,7 +27141,7 @@
         <v>1158</v>
       </c>
     </row>
-    <row r="724" spans="2:13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="724" spans="2:13" x14ac:dyDescent="0.3">
       <c r="C724" t="s">
         <v>129</v>
       </c>
@@ -27137,7 +27171,7 @@
         <v>1158</v>
       </c>
     </row>
-    <row r="725" spans="2:13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="725" spans="2:13" x14ac:dyDescent="0.3">
       <c r="C725" t="s">
         <v>129</v>
       </c>
@@ -27167,7 +27201,7 @@
         <v>1158</v>
       </c>
     </row>
-    <row r="726" spans="2:13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="726" spans="2:13" x14ac:dyDescent="0.3">
       <c r="C726" t="s">
         <v>129</v>
       </c>
@@ -27197,7 +27231,7 @@
         <v>1158</v>
       </c>
     </row>
-    <row r="727" spans="2:13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="727" spans="2:13" x14ac:dyDescent="0.3">
       <c r="C727" t="s">
         <v>129</v>
       </c>
@@ -27227,7 +27261,7 @@
         <v>1158</v>
       </c>
     </row>
-    <row r="728" spans="2:13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="728" spans="2:13" x14ac:dyDescent="0.3">
       <c r="C728" t="s">
         <v>129</v>
       </c>
@@ -27257,7 +27291,7 @@
         <v>1158</v>
       </c>
     </row>
-    <row r="729" spans="2:13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="729" spans="2:13" x14ac:dyDescent="0.3">
       <c r="C729" t="s">
         <v>129</v>
       </c>
@@ -27287,7 +27321,7 @@
         <v>1158</v>
       </c>
     </row>
-    <row r="730" spans="2:13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="730" spans="2:13" x14ac:dyDescent="0.3">
       <c r="C730" t="s">
         <v>129</v>
       </c>
@@ -27317,7 +27351,7 @@
         <v>1158</v>
       </c>
     </row>
-    <row r="731" spans="2:13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="731" spans="2:13" x14ac:dyDescent="0.3">
       <c r="C731" t="s">
         <v>129</v>
       </c>
@@ -27344,7 +27378,7 @@
         <v>1158</v>
       </c>
     </row>
-    <row r="732" spans="2:13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="732" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B732" t="s">
         <v>137</v>
       </c>
@@ -27374,7 +27408,7 @@
         <v>1169</v>
       </c>
     </row>
-    <row r="733" spans="2:13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="733" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B733" t="s">
         <v>137</v>
       </c>
@@ -27404,7 +27438,7 @@
         <v>1169</v>
       </c>
     </row>
-    <row r="734" spans="2:13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="734" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B734" t="s">
         <v>137</v>
       </c>
@@ -27434,7 +27468,7 @@
         <v>1169</v>
       </c>
     </row>
-    <row r="735" spans="2:13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="735" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B735" t="s">
         <v>137</v>
       </c>
@@ -27461,7 +27495,7 @@
         <v>1177</v>
       </c>
     </row>
-    <row r="736" spans="2:13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="736" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B736" t="s">
         <v>137</v>
       </c>
@@ -27488,7 +27522,7 @@
         <v>1177</v>
       </c>
     </row>
-    <row r="737" spans="2:13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="737" spans="2:13" x14ac:dyDescent="0.3">
       <c r="C737" t="s">
         <v>150</v>
       </c>
@@ -27518,7 +27552,7 @@
         <v>1181</v>
       </c>
     </row>
-    <row r="738" spans="2:13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="738" spans="2:13" x14ac:dyDescent="0.3">
       <c r="C738" t="s">
         <v>150</v>
       </c>
@@ -27548,7 +27582,7 @@
         <v>1181</v>
       </c>
     </row>
-    <row r="739" spans="2:13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="739" spans="2:13" x14ac:dyDescent="0.3">
       <c r="C739" t="s">
         <v>150</v>
       </c>
@@ -27578,7 +27612,7 @@
         <v>1181</v>
       </c>
     </row>
-    <row r="740" spans="2:13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="740" spans="2:13" x14ac:dyDescent="0.3">
       <c r="C740" t="s">
         <v>150</v>
       </c>
@@ -27608,7 +27642,7 @@
         <v>1181</v>
       </c>
     </row>
-    <row r="741" spans="2:13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="741" spans="2:13" x14ac:dyDescent="0.3">
       <c r="C741" t="s">
         <v>303</v>
       </c>
@@ -27638,7 +27672,7 @@
         <v>1187</v>
       </c>
     </row>
-    <row r="742" spans="2:13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="742" spans="2:13" x14ac:dyDescent="0.3">
       <c r="C742" t="s">
         <v>303</v>
       </c>
@@ -27668,7 +27702,7 @@
         <v>1187</v>
       </c>
     </row>
-    <row r="743" spans="2:13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="743" spans="2:13" x14ac:dyDescent="0.3">
       <c r="C743" t="s">
         <v>303</v>
       </c>
@@ -27698,7 +27732,7 @@
         <v>1187</v>
       </c>
     </row>
-    <row r="744" spans="2:13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="744" spans="2:13" x14ac:dyDescent="0.3">
       <c r="C744" t="s">
         <v>303</v>
       </c>
@@ -27728,7 +27762,7 @@
         <v>1187</v>
       </c>
     </row>
-    <row r="745" spans="2:13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="745" spans="2:13" x14ac:dyDescent="0.3">
       <c r="C745" t="s">
         <v>640</v>
       </c>
@@ -27758,7 +27792,7 @@
         <v>1195</v>
       </c>
     </row>
-    <row r="746" spans="2:13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="746" spans="2:13" x14ac:dyDescent="0.3">
       <c r="C746" t="s">
         <v>640</v>
       </c>
@@ -27788,7 +27822,7 @@
         <v>1195</v>
       </c>
     </row>
-    <row r="747" spans="2:13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="747" spans="2:13" x14ac:dyDescent="0.3">
       <c r="C747" t="s">
         <v>640</v>
       </c>
@@ -27818,7 +27852,7 @@
         <v>1195</v>
       </c>
     </row>
-    <row r="748" spans="2:13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="748" spans="2:13" x14ac:dyDescent="0.3">
       <c r="C748" t="s">
         <v>640</v>
       </c>
@@ -27848,7 +27882,7 @@
         <v>1195</v>
       </c>
     </row>
-    <row r="749" spans="2:13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="749" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B749" t="s">
         <v>593</v>
       </c>
@@ -27877,7 +27911,7 @@
         <v>1195</v>
       </c>
     </row>
-    <row r="750" spans="2:13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="750" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B750" t="s">
         <v>593</v>
       </c>
@@ -27909,7 +27943,7 @@
         <v>1195</v>
       </c>
     </row>
-    <row r="751" spans="2:13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="751" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B751" t="s">
         <v>593</v>
       </c>
@@ -27941,7 +27975,7 @@
         <v>1195</v>
       </c>
     </row>
-    <row r="752" spans="2:13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="752" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B752" t="s">
         <v>593</v>
       </c>
@@ -27973,7 +28007,7 @@
         <v>1195</v>
       </c>
     </row>
-    <row r="753" spans="2:13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="753" spans="2:13" x14ac:dyDescent="0.3">
       <c r="C753" t="s">
         <v>1209</v>
       </c>
@@ -28002,7 +28036,7 @@
         <v>1212</v>
       </c>
     </row>
-    <row r="754" spans="2:13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="754" spans="2:13" x14ac:dyDescent="0.3">
       <c r="C754" t="s">
         <v>1209</v>
       </c>
@@ -28031,7 +28065,7 @@
         <v>1212</v>
       </c>
     </row>
-    <row r="755" spans="2:13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="755" spans="2:13" x14ac:dyDescent="0.3">
       <c r="C755" t="s">
         <v>1209</v>
       </c>
@@ -28060,7 +28094,7 @@
         <v>1212</v>
       </c>
     </row>
-    <row r="756" spans="2:13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="756" spans="2:13" x14ac:dyDescent="0.3">
       <c r="C756" t="s">
         <v>1209</v>
       </c>
@@ -28089,7 +28123,7 @@
         <v>1212</v>
       </c>
     </row>
-    <row r="757" spans="2:13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="757" spans="2:13" x14ac:dyDescent="0.3">
       <c r="C757" t="s">
         <v>1209</v>
       </c>
@@ -28118,7 +28152,7 @@
         <v>1212</v>
       </c>
     </row>
-    <row r="758" spans="2:13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="758" spans="2:13" x14ac:dyDescent="0.3">
       <c r="C758" t="s">
         <v>1209</v>
       </c>
@@ -28147,7 +28181,7 @@
         <v>1212</v>
       </c>
     </row>
-    <row r="759" spans="2:13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="759" spans="2:13" x14ac:dyDescent="0.3">
       <c r="C759" t="s">
         <v>154</v>
       </c>
@@ -28176,7 +28210,7 @@
         <v>1222</v>
       </c>
     </row>
-    <row r="760" spans="2:13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="760" spans="2:13" x14ac:dyDescent="0.3">
       <c r="C760" t="s">
         <v>154</v>
       </c>
@@ -28205,7 +28239,7 @@
         <v>1222</v>
       </c>
     </row>
-    <row r="761" spans="2:13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="761" spans="2:13" x14ac:dyDescent="0.3">
       <c r="C761" t="s">
         <v>154</v>
       </c>
@@ -28234,7 +28268,7 @@
         <v>1222</v>
       </c>
     </row>
-    <row r="762" spans="2:13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="762" spans="2:13" x14ac:dyDescent="0.3">
       <c r="C762" t="s">
         <v>154</v>
       </c>
@@ -28263,7 +28297,7 @@
         <v>1222</v>
       </c>
     </row>
-    <row r="763" spans="2:13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="763" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B763" t="s">
         <v>137</v>
       </c>
@@ -28292,7 +28326,7 @@
         <v>1229</v>
       </c>
     </row>
-    <row r="764" spans="2:13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="764" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B764" t="s">
         <v>137</v>
       </c>
@@ -28321,7 +28355,7 @@
         <v>1229</v>
       </c>
     </row>
-    <row r="765" spans="2:13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="765" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B765" t="s">
         <v>137</v>
       </c>
@@ -28350,7 +28384,7 @@
         <v>1229</v>
       </c>
     </row>
-    <row r="766" spans="2:13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="766" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B766" t="s">
         <v>137</v>
       </c>
@@ -28379,7 +28413,7 @@
         <v>1229</v>
       </c>
     </row>
-    <row r="767" spans="2:13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="767" spans="2:13" x14ac:dyDescent="0.3">
       <c r="C767" t="s">
         <v>27</v>
       </c>
@@ -28408,7 +28442,7 @@
         <v>1238</v>
       </c>
     </row>
-    <row r="768" spans="2:13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="768" spans="2:13" x14ac:dyDescent="0.3">
       <c r="C768" t="s">
         <v>27</v>
       </c>
@@ -28437,7 +28471,7 @@
         <v>1238</v>
       </c>
     </row>
-    <row r="769" spans="3:13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="769" spans="3:13" x14ac:dyDescent="0.3">
       <c r="C769" t="s">
         <v>27</v>
       </c>
@@ -28466,7 +28500,7 @@
         <v>1238</v>
       </c>
     </row>
-    <row r="770" spans="3:13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="770" spans="3:13" x14ac:dyDescent="0.3">
       <c r="C770" t="s">
         <v>27</v>
       </c>
@@ -28495,7 +28529,7 @@
         <v>1238</v>
       </c>
     </row>
-    <row r="771" spans="3:13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="771" spans="3:13" x14ac:dyDescent="0.3">
       <c r="C771" t="s">
         <v>45</v>
       </c>
@@ -28524,7 +28558,7 @@
         <v>1245</v>
       </c>
     </row>
-    <row r="772" spans="3:13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="772" spans="3:13" x14ac:dyDescent="0.3">
       <c r="C772" t="s">
         <v>45</v>
       </c>
@@ -28553,7 +28587,7 @@
         <v>1245</v>
       </c>
     </row>
-    <row r="773" spans="3:13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="773" spans="3:13" x14ac:dyDescent="0.3">
       <c r="C773" t="s">
         <v>45</v>
       </c>
@@ -28582,7 +28616,7 @@
         <v>1245</v>
       </c>
     </row>
-    <row r="774" spans="3:13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="774" spans="3:13" x14ac:dyDescent="0.3">
       <c r="C774" t="s">
         <v>45</v>
       </c>
@@ -28611,7 +28645,7 @@
         <v>1245</v>
       </c>
     </row>
-    <row r="775" spans="3:13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="775" spans="3:13" x14ac:dyDescent="0.3">
       <c r="C775" t="s">
         <v>640</v>
       </c>
@@ -28640,7 +28674,7 @@
         <v>1251</v>
       </c>
     </row>
-    <row r="776" spans="3:13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="776" spans="3:13" x14ac:dyDescent="0.3">
       <c r="C776" t="s">
         <v>640</v>
       </c>
@@ -28669,7 +28703,7 @@
         <v>1251</v>
       </c>
     </row>
-    <row r="777" spans="3:13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="777" spans="3:13" x14ac:dyDescent="0.3">
       <c r="C777" t="s">
         <v>640</v>
       </c>
@@ -28698,7 +28732,7 @@
         <v>1251</v>
       </c>
     </row>
-    <row r="778" spans="3:13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="778" spans="3:13" x14ac:dyDescent="0.3">
       <c r="C778" t="s">
         <v>640</v>
       </c>
@@ -28727,7 +28761,7 @@
         <v>1251</v>
       </c>
     </row>
-    <row r="779" spans="3:13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="779" spans="3:13" x14ac:dyDescent="0.3">
       <c r="C779" t="s">
         <v>90</v>
       </c>
@@ -28756,7 +28790,7 @@
         <v>1256</v>
       </c>
     </row>
-    <row r="780" spans="3:13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="780" spans="3:13" x14ac:dyDescent="0.3">
       <c r="C780" t="s">
         <v>90</v>
       </c>
@@ -28785,7 +28819,7 @@
         <v>1256</v>
       </c>
     </row>
-    <row r="781" spans="3:13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="781" spans="3:13" x14ac:dyDescent="0.3">
       <c r="C781" t="s">
         <v>90</v>
       </c>
@@ -28814,7 +28848,7 @@
         <v>1256</v>
       </c>
     </row>
-    <row r="782" spans="3:13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="782" spans="3:13" x14ac:dyDescent="0.3">
       <c r="C782" t="s">
         <v>90</v>
       </c>
@@ -28843,7 +28877,7 @@
         <v>1256</v>
       </c>
     </row>
-    <row r="783" spans="3:13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="783" spans="3:13" x14ac:dyDescent="0.3">
       <c r="C783" t="s">
         <v>90</v>
       </c>
@@ -28872,7 +28906,7 @@
         <v>1256</v>
       </c>
     </row>
-    <row r="784" spans="3:13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="784" spans="3:13" x14ac:dyDescent="0.3">
       <c r="C784" t="s">
         <v>90</v>
       </c>
@@ -28901,7 +28935,7 @@
         <v>1256</v>
       </c>
     </row>
-    <row r="785" spans="2:13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="785" spans="2:13" x14ac:dyDescent="0.3">
       <c r="C785" t="s">
         <v>90</v>
       </c>
@@ -28930,7 +28964,7 @@
         <v>1256</v>
       </c>
     </row>
-    <row r="786" spans="2:13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="786" spans="2:13" x14ac:dyDescent="0.3">
       <c r="C786" t="s">
         <v>90</v>
       </c>
@@ -28959,7 +28993,7 @@
         <v>1256</v>
       </c>
     </row>
-    <row r="787" spans="2:13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="787" spans="2:13" x14ac:dyDescent="0.3">
       <c r="C787" t="s">
         <v>69</v>
       </c>
@@ -28988,7 +29022,7 @@
         <v>1266</v>
       </c>
     </row>
-    <row r="788" spans="2:13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="788" spans="2:13" x14ac:dyDescent="0.3">
       <c r="C788" t="s">
         <v>69</v>
       </c>
@@ -29017,7 +29051,7 @@
         <v>1266</v>
       </c>
     </row>
-    <row r="789" spans="2:13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="789" spans="2:13" x14ac:dyDescent="0.3">
       <c r="C789" t="s">
         <v>69</v>
       </c>
@@ -29046,7 +29080,7 @@
         <v>1266</v>
       </c>
     </row>
-    <row r="790" spans="2:13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="790" spans="2:13" x14ac:dyDescent="0.3">
       <c r="C790" t="s">
         <v>69</v>
       </c>
@@ -29075,7 +29109,7 @@
         <v>1266</v>
       </c>
     </row>
-    <row r="791" spans="2:13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="791" spans="2:13" x14ac:dyDescent="0.3">
       <c r="C791" t="s">
         <v>69</v>
       </c>
@@ -29104,7 +29138,7 @@
         <v>1266</v>
       </c>
     </row>
-    <row r="792" spans="2:13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="792" spans="2:13" x14ac:dyDescent="0.3">
       <c r="C792" t="s">
         <v>69</v>
       </c>
@@ -29133,7 +29167,7 @@
         <v>1266</v>
       </c>
     </row>
-    <row r="793" spans="2:13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="793" spans="2:13" x14ac:dyDescent="0.3">
       <c r="C793" t="s">
         <v>69</v>
       </c>
@@ -29162,7 +29196,7 @@
         <v>1266</v>
       </c>
     </row>
-    <row r="794" spans="2:13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="794" spans="2:13" x14ac:dyDescent="0.3">
       <c r="C794" t="s">
         <v>372</v>
       </c>
@@ -29191,7 +29225,7 @@
         <v>1275</v>
       </c>
     </row>
-    <row r="795" spans="2:13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="795" spans="2:13" x14ac:dyDescent="0.3">
       <c r="C795" t="s">
         <v>372</v>
       </c>
@@ -29220,7 +29254,7 @@
         <v>1275</v>
       </c>
     </row>
-    <row r="796" spans="2:13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="796" spans="2:13" x14ac:dyDescent="0.3">
       <c r="C796" t="s">
         <v>372</v>
       </c>
@@ -29249,7 +29283,7 @@
         <v>1275</v>
       </c>
     </row>
-    <row r="797" spans="2:13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="797" spans="2:13" x14ac:dyDescent="0.3">
       <c r="C797" t="s">
         <v>372</v>
       </c>
@@ -29278,7 +29312,7 @@
         <v>1275</v>
       </c>
     </row>
-    <row r="798" spans="2:13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="798" spans="2:13" x14ac:dyDescent="0.3">
       <c r="C798" t="s">
         <v>1279</v>
       </c>
@@ -29307,7 +29341,7 @@
         <v>1282</v>
       </c>
     </row>
-    <row r="799" spans="2:13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="799" spans="2:13" x14ac:dyDescent="0.3">
       <c r="C799" t="s">
         <v>1279</v>
       </c>
@@ -29336,7 +29370,7 @@
         <v>1282</v>
       </c>
     </row>
-    <row r="800" spans="2:13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="800" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B800" t="s">
         <v>162</v>
       </c>
@@ -29365,7 +29399,7 @@
         <v>1285</v>
       </c>
     </row>
-    <row r="801" spans="2:13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="801" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B801" t="s">
         <v>162</v>
       </c>
@@ -29394,7 +29428,7 @@
         <v>1285</v>
       </c>
     </row>
-    <row r="802" spans="2:13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="802" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B802" t="s">
         <v>162</v>
       </c>
@@ -29423,7 +29457,7 @@
         <v>1285</v>
       </c>
     </row>
-    <row r="803" spans="2:13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="803" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B803" t="s">
         <v>162</v>
       </c>
@@ -29452,7 +29486,7 @@
         <v>1285</v>
       </c>
     </row>
-    <row r="804" spans="2:13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="804" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B804" t="s">
         <v>162</v>
       </c>
@@ -29481,7 +29515,7 @@
         <v>1285</v>
       </c>
     </row>
-    <row r="805" spans="2:13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="805" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B805" t="s">
         <v>162</v>
       </c>
@@ -29510,7 +29544,7 @@
         <v>1285</v>
       </c>
     </row>
-    <row r="806" spans="2:13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="806" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B806" t="s">
         <v>137</v>
       </c>
@@ -29539,7 +29573,7 @@
         <v>1293</v>
       </c>
     </row>
-    <row r="807" spans="2:13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="807" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B807" t="s">
         <v>137</v>
       </c>
@@ -29568,7 +29602,7 @@
         <v>1293</v>
       </c>
     </row>
-    <row r="808" spans="2:13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="808" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B808" t="s">
         <v>137</v>
       </c>
@@ -29595,7 +29629,7 @@
         <v>1293</v>
       </c>
     </row>
-    <row r="809" spans="2:13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="809" spans="2:13" x14ac:dyDescent="0.3">
       <c r="C809" t="s">
         <v>101</v>
       </c>
@@ -29624,7 +29658,7 @@
         <v>1300</v>
       </c>
     </row>
-    <row r="810" spans="2:13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="810" spans="2:13" x14ac:dyDescent="0.3">
       <c r="C810" t="s">
         <v>101</v>
       </c>
@@ -29653,7 +29687,7 @@
         <v>1300</v>
       </c>
     </row>
-    <row r="811" spans="2:13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="811" spans="2:13" x14ac:dyDescent="0.3">
       <c r="C811" t="s">
         <v>101</v>
       </c>
@@ -29682,7 +29716,7 @@
         <v>1300</v>
       </c>
     </row>
-    <row r="812" spans="2:13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="812" spans="2:13" x14ac:dyDescent="0.3">
       <c r="C812" t="s">
         <v>101</v>
       </c>
@@ -29711,7 +29745,7 @@
         <v>1300</v>
       </c>
     </row>
-    <row r="813" spans="2:13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="813" spans="2:13" x14ac:dyDescent="0.3">
       <c r="C813" t="s">
         <v>101</v>
       </c>
@@ -29740,7 +29774,7 @@
         <v>1300</v>
       </c>
     </row>
-    <row r="814" spans="2:13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="814" spans="2:13" x14ac:dyDescent="0.3">
       <c r="C814" t="s">
         <v>101</v>
       </c>
@@ -29769,7 +29803,7 @@
         <v>1300</v>
       </c>
     </row>
-    <row r="815" spans="2:13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="815" spans="2:13" x14ac:dyDescent="0.3">
       <c r="C815" t="s">
         <v>399</v>
       </c>
@@ -29798,7 +29832,7 @@
         <v>1309</v>
       </c>
     </row>
-    <row r="816" spans="2:13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="816" spans="2:13" x14ac:dyDescent="0.3">
       <c r="C816" t="s">
         <v>399</v>
       </c>
@@ -29827,7 +29861,7 @@
         <v>1309</v>
       </c>
     </row>
-    <row r="817" spans="3:13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="817" spans="3:13" x14ac:dyDescent="0.3">
       <c r="C817" t="s">
         <v>180</v>
       </c>
@@ -29853,7 +29887,7 @@
         <v>1313</v>
       </c>
     </row>
-    <row r="818" spans="3:13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="818" spans="3:13" x14ac:dyDescent="0.3">
       <c r="C818" t="s">
         <v>180</v>
       </c>
@@ -29879,7 +29913,7 @@
         <v>1313</v>
       </c>
     </row>
-    <row r="819" spans="3:13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="819" spans="3:13" x14ac:dyDescent="0.3">
       <c r="C819" t="s">
         <v>180</v>
       </c>
@@ -29905,7 +29939,7 @@
         <v>1313</v>
       </c>
     </row>
-    <row r="820" spans="3:13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="820" spans="3:13" x14ac:dyDescent="0.3">
       <c r="C820" t="s">
         <v>180</v>
       </c>
@@ -29931,7 +29965,7 @@
         <v>1313</v>
       </c>
     </row>
-    <row r="821" spans="3:13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="821" spans="3:13" x14ac:dyDescent="0.3">
       <c r="C821" t="s">
         <v>180</v>
       </c>
@@ -29957,7 +29991,7 @@
         <v>1313</v>
       </c>
     </row>
-    <row r="822" spans="3:13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="822" spans="3:13" x14ac:dyDescent="0.3">
       <c r="C822" t="s">
         <v>180</v>
       </c>
@@ -29983,7 +30017,7 @@
         <v>1313</v>
       </c>
     </row>
-    <row r="823" spans="3:13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="823" spans="3:13" x14ac:dyDescent="0.3">
       <c r="C823" t="s">
         <v>129</v>
       </c>
@@ -30012,7 +30046,7 @@
         <v>1321</v>
       </c>
     </row>
-    <row r="824" spans="3:13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="824" spans="3:13" x14ac:dyDescent="0.3">
       <c r="C824" t="s">
         <v>129</v>
       </c>
@@ -30041,7 +30075,7 @@
         <v>1321</v>
       </c>
     </row>
-    <row r="825" spans="3:13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="825" spans="3:13" x14ac:dyDescent="0.3">
       <c r="C825" t="s">
         <v>129</v>
       </c>
@@ -30070,7 +30104,7 @@
         <v>1321</v>
       </c>
     </row>
-    <row r="826" spans="3:13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="826" spans="3:13" x14ac:dyDescent="0.3">
       <c r="C826" t="s">
         <v>129</v>
       </c>
@@ -30099,7 +30133,7 @@
         <v>1321</v>
       </c>
     </row>
-    <row r="827" spans="3:13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="827" spans="3:13" x14ac:dyDescent="0.3">
       <c r="C827" t="s">
         <v>129</v>
       </c>
@@ -30128,7 +30162,7 @@
         <v>1321</v>
       </c>
     </row>
-    <row r="828" spans="3:13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="828" spans="3:13" x14ac:dyDescent="0.3">
       <c r="C828" t="s">
         <v>129</v>
       </c>
@@ -30157,7 +30191,7 @@
         <v>1321</v>
       </c>
     </row>
-    <row r="829" spans="3:13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="829" spans="3:13" x14ac:dyDescent="0.3">
       <c r="C829" t="s">
         <v>129</v>
       </c>
@@ -30186,7 +30220,7 @@
         <v>1321</v>
       </c>
     </row>
-    <row r="830" spans="3:13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="830" spans="3:13" x14ac:dyDescent="0.3">
       <c r="C830" t="s">
         <v>129</v>
       </c>
@@ -30215,7 +30249,7 @@
         <v>1321</v>
       </c>
     </row>
-    <row r="831" spans="3:13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="831" spans="3:13" x14ac:dyDescent="0.3">
       <c r="C831" t="s">
         <v>150</v>
       </c>
@@ -30244,7 +30278,7 @@
         <v>1330</v>
       </c>
     </row>
-    <row r="832" spans="3:13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="832" spans="3:13" x14ac:dyDescent="0.3">
       <c r="C832" t="s">
         <v>150</v>
       </c>
@@ -30273,7 +30307,7 @@
         <v>1330</v>
       </c>
     </row>
-    <row r="833" spans="3:13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="833" spans="3:13" x14ac:dyDescent="0.3">
       <c r="C833" t="s">
         <v>150</v>
       </c>
@@ -30302,7 +30336,7 @@
         <v>1330</v>
       </c>
     </row>
-    <row r="834" spans="3:13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="834" spans="3:13" x14ac:dyDescent="0.3">
       <c r="C834" t="s">
         <v>150</v>
       </c>
@@ -30331,7 +30365,7 @@
         <v>1330</v>
       </c>
     </row>
-    <row r="835" spans="3:13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="835" spans="3:13" x14ac:dyDescent="0.3">
       <c r="C835" t="s">
         <v>150</v>
       </c>
@@ -30360,7 +30394,7 @@
         <v>1330</v>
       </c>
     </row>
-    <row r="836" spans="3:13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="836" spans="3:13" x14ac:dyDescent="0.3">
       <c r="C836" t="s">
         <v>150</v>
       </c>
@@ -30389,7 +30423,7 @@
         <v>1330</v>
       </c>
     </row>
-    <row r="837" spans="3:13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="837" spans="3:13" x14ac:dyDescent="0.3">
       <c r="C837" t="s">
         <v>150</v>
       </c>
@@ -30418,7 +30452,7 @@
         <v>1330</v>
       </c>
     </row>
-    <row r="838" spans="3:13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="838" spans="3:13" x14ac:dyDescent="0.3">
       <c r="C838" t="s">
         <v>150</v>
       </c>
@@ -30447,7 +30481,7 @@
         <v>1330</v>
       </c>
     </row>
-    <row r="839" spans="3:13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="839" spans="3:13" x14ac:dyDescent="0.3">
       <c r="C839" t="s">
         <v>303</v>
       </c>
@@ -30476,7 +30510,7 @@
         <v>1341</v>
       </c>
     </row>
-    <row r="840" spans="3:13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="840" spans="3:13" x14ac:dyDescent="0.3">
       <c r="C840" t="s">
         <v>303</v>
       </c>
@@ -30505,7 +30539,7 @@
         <v>1341</v>
       </c>
     </row>
-    <row r="841" spans="3:13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="841" spans="3:13" x14ac:dyDescent="0.3">
       <c r="C841" t="s">
         <v>303</v>
       </c>
@@ -30534,7 +30568,7 @@
         <v>1341</v>
       </c>
     </row>
-    <row r="842" spans="3:13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="842" spans="3:13" x14ac:dyDescent="0.3">
       <c r="C842" t="s">
         <v>303</v>
       </c>
@@ -30563,7 +30597,7 @@
         <v>1341</v>
       </c>
     </row>
-    <row r="843" spans="3:13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="843" spans="3:13" x14ac:dyDescent="0.3">
       <c r="C843" t="s">
         <v>303</v>
       </c>
@@ -30592,7 +30626,7 @@
         <v>1341</v>
       </c>
     </row>
-    <row r="844" spans="3:13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="844" spans="3:13" x14ac:dyDescent="0.3">
       <c r="D844" t="s">
         <v>1348</v>
       </c>
@@ -30615,7 +30649,7 @@
         <v>1351</v>
       </c>
     </row>
-    <row r="845" spans="3:13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="845" spans="3:13" x14ac:dyDescent="0.3">
       <c r="D845" t="s">
         <v>1348</v>
       </c>
@@ -30638,7 +30672,7 @@
         <v>1351</v>
       </c>
     </row>
-    <row r="846" spans="3:13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="846" spans="3:13" x14ac:dyDescent="0.3">
       <c r="D846" t="s">
         <v>1348</v>
       </c>
@@ -30661,7 +30695,7 @@
         <v>1351</v>
       </c>
     </row>
-    <row r="847" spans="3:13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="847" spans="3:13" x14ac:dyDescent="0.3">
       <c r="D847" t="s">
         <v>1348</v>
       </c>
@@ -30684,7 +30718,7 @@
         <v>1351</v>
       </c>
     </row>
-    <row r="848" spans="3:13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="848" spans="3:13" x14ac:dyDescent="0.3">
       <c r="D848" t="s">
         <v>1348</v>
       </c>
@@ -30707,7 +30741,7 @@
         <v>1351</v>
       </c>
     </row>
-    <row r="849" spans="2:13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="849" spans="2:13" x14ac:dyDescent="0.3">
       <c r="D849" t="s">
         <v>1348</v>
       </c>
@@ -30730,7 +30764,7 @@
         <v>1351</v>
       </c>
     </row>
-    <row r="850" spans="2:13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="850" spans="2:13" x14ac:dyDescent="0.3">
       <c r="C850" t="s">
         <v>154</v>
       </c>
@@ -30759,7 +30793,7 @@
         <v>1358</v>
       </c>
     </row>
-    <row r="851" spans="2:13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="851" spans="2:13" x14ac:dyDescent="0.3">
       <c r="C851" t="s">
         <v>154</v>
       </c>
@@ -30788,7 +30822,7 @@
         <v>1358</v>
       </c>
     </row>
-    <row r="852" spans="2:13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="852" spans="2:13" x14ac:dyDescent="0.3">
       <c r="C852" t="s">
         <v>154</v>
       </c>
@@ -30817,7 +30851,7 @@
         <v>1358</v>
       </c>
     </row>
-    <row r="853" spans="2:13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="853" spans="2:13" x14ac:dyDescent="0.3">
       <c r="C853" t="s">
         <v>154</v>
       </c>
@@ -30846,7 +30880,7 @@
         <v>1358</v>
       </c>
     </row>
-    <row r="854" spans="2:13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="854" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B854" t="s">
         <v>137</v>
       </c>
@@ -30875,7 +30909,7 @@
         <v>1365</v>
       </c>
     </row>
-    <row r="855" spans="2:13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="855" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B855" t="s">
         <v>137</v>
       </c>
@@ -30904,7 +30938,7 @@
         <v>1365</v>
       </c>
     </row>
-    <row r="856" spans="2:13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="856" spans="2:13" x14ac:dyDescent="0.3">
       <c r="C856" t="s">
         <v>27</v>
       </c>
@@ -30933,7 +30967,7 @@
         <v>1370</v>
       </c>
     </row>
-    <row r="857" spans="2:13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="857" spans="2:13" x14ac:dyDescent="0.3">
       <c r="C857" t="s">
         <v>27</v>
       </c>
@@ -30962,7 +30996,7 @@
         <v>1370</v>
       </c>
     </row>
-    <row r="858" spans="2:13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="858" spans="2:13" x14ac:dyDescent="0.3">
       <c r="C858" t="s">
         <v>27</v>
       </c>
@@ -30991,7 +31025,7 @@
         <v>1370</v>
       </c>
     </row>
-    <row r="859" spans="2:13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="859" spans="2:13" x14ac:dyDescent="0.3">
       <c r="C859" t="s">
         <v>27</v>
       </c>
@@ -31020,7 +31054,7 @@
         <v>1370</v>
       </c>
     </row>
-    <row r="860" spans="2:13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="860" spans="2:13" x14ac:dyDescent="0.3">
       <c r="C860" t="s">
         <v>45</v>
       </c>
@@ -31049,7 +31083,7 @@
         <v>1376</v>
       </c>
     </row>
-    <row r="861" spans="2:13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="861" spans="2:13" x14ac:dyDescent="0.3">
       <c r="C861" t="s">
         <v>45</v>
       </c>
@@ -31078,7 +31112,7 @@
         <v>1376</v>
       </c>
     </row>
-    <row r="862" spans="2:13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="862" spans="2:13" x14ac:dyDescent="0.3">
       <c r="C862" t="s">
         <v>45</v>
       </c>
@@ -31107,7 +31141,7 @@
         <v>1376</v>
       </c>
     </row>
-    <row r="863" spans="2:13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="863" spans="2:13" x14ac:dyDescent="0.3">
       <c r="C863" t="s">
         <v>45</v>
       </c>
@@ -31136,7 +31170,7 @@
         <v>1376</v>
       </c>
     </row>
-    <row r="864" spans="2:13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="864" spans="2:13" x14ac:dyDescent="0.3">
       <c r="C864" t="s">
         <v>1380</v>
       </c>
@@ -31162,7 +31196,7 @@
         <v>1382</v>
       </c>
     </row>
-    <row r="865" spans="2:13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="865" spans="2:13" x14ac:dyDescent="0.3">
       <c r="C865" t="s">
         <v>1380</v>
       </c>
@@ -31188,7 +31222,7 @@
         <v>1382</v>
       </c>
     </row>
-    <row r="866" spans="2:13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="866" spans="2:13" x14ac:dyDescent="0.3">
       <c r="C866" t="s">
         <v>1380</v>
       </c>
@@ -31214,7 +31248,7 @@
         <v>1382</v>
       </c>
     </row>
-    <row r="867" spans="2:13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="867" spans="2:13" x14ac:dyDescent="0.3">
       <c r="C867" t="s">
         <v>1380</v>
       </c>
@@ -31236,11 +31270,11 @@
       <c r="K867" t="s">
         <v>76</v>
       </c>
-      <c r="M867" t="s">
+      <c r="M867" s="3" t="s">
         <v>1382</v>
       </c>
     </row>
-    <row r="868" spans="2:13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="868" spans="2:13" x14ac:dyDescent="0.3">
       <c r="C868" t="s">
         <v>1380</v>
       </c>
@@ -31266,7 +31300,7 @@
         <v>1382</v>
       </c>
     </row>
-    <row r="869" spans="2:13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="869" spans="2:13" x14ac:dyDescent="0.3">
       <c r="C869" t="s">
         <v>1380</v>
       </c>
@@ -31292,7 +31326,7 @@
         <v>1382</v>
       </c>
     </row>
-    <row r="870" spans="2:13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="870" spans="2:13" x14ac:dyDescent="0.3">
       <c r="C870" t="s">
         <v>90</v>
       </c>
@@ -31321,7 +31355,7 @@
         <v>1385</v>
       </c>
     </row>
-    <row r="871" spans="2:13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="871" spans="2:13" x14ac:dyDescent="0.3">
       <c r="C871" t="s">
         <v>90</v>
       </c>
@@ -31350,7 +31384,7 @@
         <v>1385</v>
       </c>
     </row>
-    <row r="872" spans="2:13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="872" spans="2:13" x14ac:dyDescent="0.3">
       <c r="C872" t="s">
         <v>90</v>
       </c>
@@ -31379,7 +31413,7 @@
         <v>1385</v>
       </c>
     </row>
-    <row r="873" spans="2:13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="873" spans="2:13" x14ac:dyDescent="0.3">
       <c r="C873" t="s">
         <v>90</v>
       </c>
@@ -31408,7 +31442,7 @@
         <v>1385</v>
       </c>
     </row>
-    <row r="874" spans="2:13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="874" spans="2:13" x14ac:dyDescent="0.3">
       <c r="C874" t="s">
         <v>90</v>
       </c>
@@ -31437,7 +31471,7 @@
         <v>1385</v>
       </c>
     </row>
-    <row r="875" spans="2:13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="875" spans="2:13" x14ac:dyDescent="0.3">
       <c r="C875" t="s">
         <v>90</v>
       </c>
@@ -31466,7 +31500,7 @@
         <v>1385</v>
       </c>
     </row>
-    <row r="876" spans="2:13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="876" spans="2:13" x14ac:dyDescent="0.3">
       <c r="C876" t="s">
         <v>90</v>
       </c>
@@ -31495,7 +31529,7 @@
         <v>1385</v>
       </c>
     </row>
-    <row r="877" spans="2:13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="877" spans="2:13" x14ac:dyDescent="0.3">
       <c r="C877" t="s">
         <v>90</v>
       </c>
@@ -31524,7 +31558,7 @@
         <v>1385</v>
       </c>
     </row>
-    <row r="878" spans="2:13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="878" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B878" t="s">
         <v>137</v>
       </c>
@@ -31550,7 +31584,7 @@
         <v>1394</v>
       </c>
     </row>
-    <row r="879" spans="2:13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="879" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B879" t="s">
         <v>137</v>
       </c>
@@ -31576,7 +31610,7 @@
         <v>1394</v>
       </c>
     </row>
-    <row r="880" spans="2:13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="880" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B880" t="s">
         <v>137</v>
       </c>
@@ -31602,7 +31636,7 @@
         <v>1394</v>
       </c>
     </row>
-    <row r="881" spans="2:13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="881" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B881" t="s">
         <v>137</v>
       </c>
@@ -31628,7 +31662,7 @@
         <v>1394</v>
       </c>
     </row>
-    <row r="882" spans="2:13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="882" spans="2:13" x14ac:dyDescent="0.3">
       <c r="C882" t="s">
         <v>69</v>
       </c>
@@ -31657,7 +31691,7 @@
         <v>1403</v>
       </c>
     </row>
-    <row r="883" spans="2:13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="883" spans="2:13" x14ac:dyDescent="0.3">
       <c r="C883" t="s">
         <v>69</v>
       </c>
@@ -31686,7 +31720,7 @@
         <v>1403</v>
       </c>
     </row>
-    <row r="884" spans="2:13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="884" spans="2:13" x14ac:dyDescent="0.3">
       <c r="C884" t="s">
         <v>69</v>
       </c>
@@ -31715,7 +31749,7 @@
         <v>1403</v>
       </c>
     </row>
-    <row r="885" spans="2:13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="885" spans="2:13" x14ac:dyDescent="0.3">
       <c r="C885" t="s">
         <v>69</v>
       </c>
@@ -31744,7 +31778,7 @@
         <v>1403</v>
       </c>
     </row>
-    <row r="886" spans="2:13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="886" spans="2:13" x14ac:dyDescent="0.3">
       <c r="C886" t="s">
         <v>69</v>
       </c>
@@ -31773,7 +31807,7 @@
         <v>1403</v>
       </c>
     </row>
-    <row r="887" spans="2:13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="887" spans="2:13" x14ac:dyDescent="0.3">
       <c r="C887" t="s">
         <v>69</v>
       </c>
@@ -31802,7 +31836,7 @@
         <v>1403</v>
       </c>
     </row>
-    <row r="888" spans="2:13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="888" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B888" t="s">
         <v>162</v>
       </c>
@@ -31831,7 +31865,7 @@
         <v>1411</v>
       </c>
     </row>
-    <row r="889" spans="2:13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="889" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B889" t="s">
         <v>162</v>
       </c>
@@ -31860,7 +31894,7 @@
         <v>1411</v>
       </c>
     </row>
-    <row r="890" spans="2:13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="890" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B890" t="s">
         <v>162</v>
       </c>
@@ -31889,7 +31923,7 @@
         <v>1411</v>
       </c>
     </row>
-    <row r="891" spans="2:13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="891" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B891" t="s">
         <v>162</v>
       </c>
@@ -31918,7 +31952,7 @@
         <v>1411</v>
       </c>
     </row>
-    <row r="892" spans="2:13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="892" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B892" t="s">
         <v>162</v>
       </c>
@@ -31947,7 +31981,7 @@
         <v>1411</v>
       </c>
     </row>
-    <row r="893" spans="2:13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="893" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B893" t="s">
         <v>162</v>
       </c>
@@ -31976,7 +32010,7 @@
         <v>1411</v>
       </c>
     </row>
-    <row r="894" spans="2:13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="894" spans="2:13" x14ac:dyDescent="0.3">
       <c r="C894" t="s">
         <v>1417</v>
       </c>
@@ -32005,7 +32039,7 @@
         <v>1420</v>
       </c>
     </row>
-    <row r="895" spans="2:13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="895" spans="2:13" x14ac:dyDescent="0.3">
       <c r="C895" t="s">
         <v>1417</v>
       </c>
@@ -32034,7 +32068,7 @@
         <v>1420</v>
       </c>
     </row>
-    <row r="896" spans="2:13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="896" spans="2:13" x14ac:dyDescent="0.3">
       <c r="C896" t="s">
         <v>1417</v>
       </c>
@@ -32063,7 +32097,7 @@
         <v>1420</v>
       </c>
     </row>
-    <row r="897" spans="3:13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="897" spans="3:13" x14ac:dyDescent="0.3">
       <c r="C897" t="s">
         <v>1417</v>
       </c>
@@ -32092,7 +32126,7 @@
         <v>1420</v>
       </c>
     </row>
-    <row r="898" spans="3:13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="898" spans="3:13" x14ac:dyDescent="0.3">
       <c r="C898" t="s">
         <v>1417</v>
       </c>
@@ -32121,7 +32155,7 @@
         <v>1420</v>
       </c>
     </row>
-    <row r="899" spans="3:13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="899" spans="3:13" x14ac:dyDescent="0.3">
       <c r="C899" t="s">
         <v>1417</v>
       </c>
@@ -32150,7 +32184,7 @@
         <v>1420</v>
       </c>
     </row>
-    <row r="900" spans="3:13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="900" spans="3:13" x14ac:dyDescent="0.3">
       <c r="C900" t="s">
         <v>1417</v>
       </c>
@@ -32179,7 +32213,7 @@
         <v>1420</v>
       </c>
     </row>
-    <row r="901" spans="3:13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="901" spans="3:13" x14ac:dyDescent="0.3">
       <c r="C901" t="s">
         <v>1417</v>
       </c>
@@ -32208,7 +32242,7 @@
         <v>1420</v>
       </c>
     </row>
-    <row r="902" spans="3:13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="902" spans="3:13" x14ac:dyDescent="0.3">
       <c r="C902" t="s">
         <v>1430</v>
       </c>
@@ -32237,7 +32271,7 @@
         <v>1433</v>
       </c>
     </row>
-    <row r="903" spans="3:13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="903" spans="3:13" x14ac:dyDescent="0.3">
       <c r="C903" t="s">
         <v>1430</v>
       </c>
@@ -32266,7 +32300,7 @@
         <v>1433</v>
       </c>
     </row>
-    <row r="904" spans="3:13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="904" spans="3:13" x14ac:dyDescent="0.3">
       <c r="C904" t="s">
         <v>1430</v>
       </c>
@@ -32295,7 +32329,7 @@
         <v>1433</v>
       </c>
     </row>
-    <row r="905" spans="3:13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="905" spans="3:13" x14ac:dyDescent="0.3">
       <c r="C905" t="s">
         <v>1430</v>
       </c>
@@ -32324,7 +32358,7 @@
         <v>1433</v>
       </c>
     </row>
-    <row r="906" spans="3:13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="906" spans="3:13" x14ac:dyDescent="0.3">
       <c r="C906" t="s">
         <v>1430</v>
       </c>
@@ -32353,7 +32387,7 @@
         <v>1433</v>
       </c>
     </row>
-    <row r="907" spans="3:13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="907" spans="3:13" x14ac:dyDescent="0.3">
       <c r="C907" t="s">
         <v>1430</v>
       </c>
@@ -32382,7 +32416,7 @@
         <v>1433</v>
       </c>
     </row>
-    <row r="908" spans="3:13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="908" spans="3:13" x14ac:dyDescent="0.3">
       <c r="C908" t="s">
         <v>1430</v>
       </c>
@@ -32411,7 +32445,7 @@
         <v>1433</v>
       </c>
     </row>
-    <row r="909" spans="3:13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="909" spans="3:13" x14ac:dyDescent="0.3">
       <c r="C909" t="s">
         <v>1430</v>
       </c>
@@ -32440,7 +32474,7 @@
         <v>1433</v>
       </c>
     </row>
-    <row r="910" spans="3:13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="910" spans="3:13" x14ac:dyDescent="0.3">
       <c r="C910" t="s">
         <v>101</v>
       </c>
@@ -32469,7 +32503,7 @@
         <v>1443</v>
       </c>
     </row>
-    <row r="911" spans="3:13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="911" spans="3:13" x14ac:dyDescent="0.3">
       <c r="C911" t="s">
         <v>101</v>
       </c>
@@ -32498,7 +32532,7 @@
         <v>1443</v>
       </c>
     </row>
-    <row r="912" spans="3:13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="912" spans="3:13" x14ac:dyDescent="0.3">
       <c r="C912" t="s">
         <v>101</v>
       </c>
@@ -32527,7 +32561,7 @@
         <v>1443</v>
       </c>
     </row>
-    <row r="913" spans="2:13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="913" spans="2:13" x14ac:dyDescent="0.3">
       <c r="C913" t="s">
         <v>101</v>
       </c>
@@ -32556,7 +32590,7 @@
         <v>1443</v>
       </c>
     </row>
-    <row r="914" spans="2:13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="914" spans="2:13" x14ac:dyDescent="0.3">
       <c r="C914" t="s">
         <v>101</v>
       </c>
@@ -32585,7 +32619,7 @@
         <v>1443</v>
       </c>
     </row>
-    <row r="915" spans="2:13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="915" spans="2:13" x14ac:dyDescent="0.3">
       <c r="C915" t="s">
         <v>101</v>
       </c>
@@ -32614,7 +32648,7 @@
         <v>1443</v>
       </c>
     </row>
-    <row r="916" spans="2:13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="916" spans="2:13" x14ac:dyDescent="0.3">
       <c r="C916" t="s">
         <v>399</v>
       </c>
@@ -32643,7 +32677,7 @@
         <v>1451</v>
       </c>
     </row>
-    <row r="917" spans="2:13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="917" spans="2:13" x14ac:dyDescent="0.3">
       <c r="C917" t="s">
         <v>399</v>
       </c>
@@ -32672,7 +32706,7 @@
         <v>1451</v>
       </c>
     </row>
-    <row r="918" spans="2:13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="918" spans="2:13" x14ac:dyDescent="0.3">
       <c r="D918" t="s">
         <v>1453</v>
       </c>
@@ -32698,7 +32732,7 @@
         <v>1455</v>
       </c>
     </row>
-    <row r="919" spans="2:13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="919" spans="2:13" x14ac:dyDescent="0.3">
       <c r="D919" t="s">
         <v>1453</v>
       </c>
@@ -32724,7 +32758,7 @@
         <v>1455</v>
       </c>
     </row>
-    <row r="920" spans="2:13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="920" spans="2:13" x14ac:dyDescent="0.3">
       <c r="D920" t="s">
         <v>1453</v>
       </c>
@@ -32750,7 +32784,7 @@
         <v>1455</v>
       </c>
     </row>
-    <row r="921" spans="2:13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="921" spans="2:13" x14ac:dyDescent="0.3">
       <c r="D921" t="s">
         <v>1453</v>
       </c>
@@ -32776,7 +32810,7 @@
         <v>1455</v>
       </c>
     </row>
-    <row r="922" spans="2:13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="922" spans="2:13" x14ac:dyDescent="0.3">
       <c r="D922" t="s">
         <v>1453</v>
       </c>
@@ -32802,7 +32836,7 @@
         <v>1455</v>
       </c>
     </row>
-    <row r="923" spans="2:13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="923" spans="2:13" x14ac:dyDescent="0.3">
       <c r="D923" t="s">
         <v>1453</v>
       </c>
@@ -32828,7 +32862,7 @@
         <v>1455</v>
       </c>
     </row>
-    <row r="924" spans="2:13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="924" spans="2:13" x14ac:dyDescent="0.3">
       <c r="D924" t="s">
         <v>1453</v>
       </c>
@@ -32854,7 +32888,7 @@
         <v>1455</v>
       </c>
     </row>
-    <row r="925" spans="2:13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="925" spans="2:13" x14ac:dyDescent="0.3">
       <c r="D925" t="s">
         <v>1453</v>
       </c>
@@ -32880,7 +32914,7 @@
         <v>1455</v>
       </c>
     </row>
-    <row r="926" spans="2:13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="926" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B926" t="s">
         <v>162</v>
       </c>
@@ -32909,7 +32943,7 @@
         <v>1466</v>
       </c>
     </row>
-    <row r="927" spans="2:13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="927" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B927" t="s">
         <v>162</v>
       </c>
@@ -32938,7 +32972,7 @@
         <v>1466</v>
       </c>
     </row>
-    <row r="928" spans="2:13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="928" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B928" t="s">
         <v>162</v>
       </c>
@@ -32967,7 +33001,7 @@
         <v>1466</v>
       </c>
     </row>
-    <row r="929" spans="2:13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="929" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B929" t="s">
         <v>162</v>
       </c>
@@ -32996,7 +33030,7 @@
         <v>1466</v>
       </c>
     </row>
-    <row r="930" spans="2:13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="930" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B930" t="s">
         <v>162</v>
       </c>
@@ -33025,7 +33059,7 @@
         <v>1466</v>
       </c>
     </row>
-    <row r="931" spans="2:13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="931" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B931" t="s">
         <v>162</v>
       </c>
@@ -33054,7 +33088,7 @@
         <v>1466</v>
       </c>
     </row>
-    <row r="932" spans="2:13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="932" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B932" t="s">
         <v>593</v>
       </c>
@@ -33089,7 +33123,7 @@
         <v>1481</v>
       </c>
     </row>
-    <row r="933" spans="2:13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="933" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B933" t="s">
         <v>593</v>
       </c>
@@ -33127,7 +33161,7 @@
         <v>1481</v>
       </c>
     </row>
-    <row r="934" spans="2:13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="934" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B934" t="s">
         <v>593</v>
       </c>
@@ -33165,7 +33199,7 @@
         <v>1481</v>
       </c>
     </row>
-    <row r="935" spans="2:13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="935" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B935" t="s">
         <v>593</v>
       </c>
@@ -33203,7 +33237,7 @@
         <v>1481</v>
       </c>
     </row>
-    <row r="936" spans="2:13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="936" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B936" t="s">
         <v>593</v>
       </c>
@@ -33238,7 +33272,7 @@
         <v>1481</v>
       </c>
     </row>
-    <row r="937" spans="2:13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="937" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B937" t="s">
         <v>593</v>
       </c>
@@ -33276,7 +33310,7 @@
         <v>1481</v>
       </c>
     </row>
-    <row r="938" spans="2:13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="938" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B938" t="s">
         <v>593</v>
       </c>
@@ -33311,7 +33345,7 @@
         <v>1481</v>
       </c>
     </row>
-    <row r="939" spans="2:13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="939" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B939" t="s">
         <v>593</v>
       </c>
@@ -33349,7 +33383,7 @@
         <v>1481</v>
       </c>
     </row>
-    <row r="940" spans="2:13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="940" spans="2:13" x14ac:dyDescent="0.3">
       <c r="C940" t="s">
         <v>150</v>
       </c>
@@ -33378,7 +33412,7 @@
         <v>1497</v>
       </c>
     </row>
-    <row r="941" spans="2:13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="941" spans="2:13" x14ac:dyDescent="0.3">
       <c r="C941" t="s">
         <v>150</v>
       </c>
@@ -33407,7 +33441,7 @@
         <v>1497</v>
       </c>
     </row>
-    <row r="942" spans="2:13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="942" spans="2:13" x14ac:dyDescent="0.3">
       <c r="C942" t="s">
         <v>150</v>
       </c>
@@ -33436,7 +33470,7 @@
         <v>1497</v>
       </c>
     </row>
-    <row r="943" spans="2:13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="943" spans="2:13" x14ac:dyDescent="0.3">
       <c r="C943" t="s">
         <v>150</v>
       </c>
@@ -33465,7 +33499,7 @@
         <v>1497</v>
       </c>
     </row>
-    <row r="944" spans="2:13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="944" spans="2:13" x14ac:dyDescent="0.3">
       <c r="C944" t="s">
         <v>150</v>
       </c>
@@ -33494,7 +33528,7 @@
         <v>1497</v>
       </c>
     </row>
-    <row r="945" spans="2:13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="945" spans="2:13" x14ac:dyDescent="0.3">
       <c r="C945" t="s">
         <v>150</v>
       </c>
@@ -33523,7 +33557,7 @@
         <v>1497</v>
       </c>
     </row>
-    <row r="946" spans="2:13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="946" spans="2:13" x14ac:dyDescent="0.3">
       <c r="C946" t="s">
         <v>150</v>
       </c>
@@ -33552,7 +33586,7 @@
         <v>1497</v>
       </c>
     </row>
-    <row r="947" spans="2:13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="947" spans="2:13" x14ac:dyDescent="0.3">
       <c r="C947" t="s">
         <v>150</v>
       </c>
@@ -33581,7 +33615,7 @@
         <v>1497</v>
       </c>
     </row>
-    <row r="948" spans="2:13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="948" spans="2:13" x14ac:dyDescent="0.3">
       <c r="C948" t="s">
         <v>129</v>
       </c>
@@ -33610,7 +33644,7 @@
         <v>1509</v>
       </c>
     </row>
-    <row r="949" spans="2:13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="949" spans="2:13" x14ac:dyDescent="0.3">
       <c r="C949" t="s">
         <v>129</v>
       </c>
@@ -33639,7 +33673,7 @@
         <v>1509</v>
       </c>
     </row>
-    <row r="950" spans="2:13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="950" spans="2:13" x14ac:dyDescent="0.3">
       <c r="C950" t="s">
         <v>129</v>
       </c>
@@ -33668,7 +33702,7 @@
         <v>1509</v>
       </c>
     </row>
-    <row r="951" spans="2:13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="951" spans="2:13" x14ac:dyDescent="0.3">
       <c r="C951" t="s">
         <v>129</v>
       </c>
@@ -33697,7 +33731,7 @@
         <v>1509</v>
       </c>
     </row>
-    <row r="952" spans="2:13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="952" spans="2:13" x14ac:dyDescent="0.3">
       <c r="C952" t="s">
         <v>129</v>
       </c>
@@ -33726,7 +33760,7 @@
         <v>1509</v>
       </c>
     </row>
-    <row r="953" spans="2:13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="953" spans="2:13" x14ac:dyDescent="0.3">
       <c r="C953" t="s">
         <v>129</v>
       </c>
@@ -33755,7 +33789,7 @@
         <v>1509</v>
       </c>
     </row>
-    <row r="954" spans="2:13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="954" spans="2:13" x14ac:dyDescent="0.3">
       <c r="C954" t="s">
         <v>129</v>
       </c>
@@ -33784,7 +33818,7 @@
         <v>1509</v>
       </c>
     </row>
-    <row r="955" spans="2:13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="955" spans="2:13" x14ac:dyDescent="0.3">
       <c r="C955" t="s">
         <v>129</v>
       </c>
@@ -33813,7 +33847,7 @@
         <v>1509</v>
       </c>
     </row>
-    <row r="956" spans="2:13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="956" spans="2:13" x14ac:dyDescent="0.3">
       <c r="C956" t="s">
         <v>303</v>
       </c>
@@ -33839,7 +33873,7 @@
         <v>1519</v>
       </c>
     </row>
-    <row r="957" spans="2:13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="957" spans="2:13" x14ac:dyDescent="0.3">
       <c r="C957" t="s">
         <v>303</v>
       </c>
@@ -33865,7 +33899,7 @@
         <v>1519</v>
       </c>
     </row>
-    <row r="958" spans="2:13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="958" spans="2:13" x14ac:dyDescent="0.3">
       <c r="C958" t="s">
         <v>303</v>
       </c>
@@ -33891,7 +33925,7 @@
         <v>1519</v>
       </c>
     </row>
-    <row r="959" spans="2:13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="959" spans="2:13" x14ac:dyDescent="0.3">
       <c r="C959" t="s">
         <v>303</v>
       </c>
@@ -33917,7 +33951,7 @@
         <v>1519</v>
       </c>
     </row>
-    <row r="960" spans="2:13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="960" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B960" t="s">
         <v>593</v>
       </c>
@@ -33946,7 +33980,7 @@
         <v>1526</v>
       </c>
     </row>
-    <row r="961" spans="2:13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="961" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B961" t="s">
         <v>593</v>
       </c>
@@ -33975,7 +34009,7 @@
         <v>1526</v>
       </c>
     </row>
-    <row r="962" spans="2:13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="962" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B962" t="s">
         <v>593</v>
       </c>
@@ -34004,7 +34038,7 @@
         <v>1526</v>
       </c>
     </row>
-    <row r="963" spans="2:13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="963" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B963" t="s">
         <v>593</v>
       </c>
@@ -34033,7 +34067,7 @@
         <v>1526</v>
       </c>
     </row>
-    <row r="964" spans="2:13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="964" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B964" t="s">
         <v>593</v>
       </c>
@@ -34062,7 +34096,7 @@
         <v>1526</v>
       </c>
     </row>
-    <row r="965" spans="2:13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="965" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B965" t="s">
         <v>593</v>
       </c>
@@ -34091,7 +34125,7 @@
         <v>1526</v>
       </c>
     </row>
-    <row r="966" spans="2:13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="966" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B966" t="s">
         <v>593</v>
       </c>
@@ -34123,7 +34157,7 @@
         <v>1526</v>
       </c>
     </row>
-    <row r="967" spans="2:13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="967" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B967" t="s">
         <v>593</v>
       </c>
@@ -34155,7 +34189,7 @@
         <v>1526</v>
       </c>
     </row>
-    <row r="968" spans="2:13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="968" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B968" t="s">
         <v>593</v>
       </c>
@@ -34190,7 +34224,7 @@
         <v>1541</v>
       </c>
     </row>
-    <row r="969" spans="2:13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="969" spans="2:13" x14ac:dyDescent="0.3">
       <c r="C969" t="s">
         <v>1542</v>
       </c>
@@ -34219,7 +34253,7 @@
         <v>1546</v>
       </c>
     </row>
-    <row r="970" spans="2:13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="970" spans="2:13" x14ac:dyDescent="0.3">
       <c r="C970" t="s">
         <v>1542</v>
       </c>
@@ -34248,7 +34282,7 @@
         <v>1546</v>
       </c>
     </row>
-    <row r="971" spans="2:13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="971" spans="2:13" x14ac:dyDescent="0.3">
       <c r="C971" t="s">
         <v>1542</v>
       </c>
@@ -34277,7 +34311,7 @@
         <v>1546</v>
       </c>
     </row>
-    <row r="972" spans="2:13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="972" spans="2:13" x14ac:dyDescent="0.3">
       <c r="C972" t="s">
         <v>1542</v>
       </c>
@@ -34306,7 +34340,7 @@
         <v>1546</v>
       </c>
     </row>
-    <row r="973" spans="2:13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="973" spans="2:13" x14ac:dyDescent="0.3">
       <c r="C973" t="s">
         <v>1542</v>
       </c>
@@ -34335,7 +34369,7 @@
         <v>1546</v>
       </c>
     </row>
-    <row r="974" spans="2:13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="974" spans="2:13" x14ac:dyDescent="0.3">
       <c r="C974" t="s">
         <v>1542</v>
       </c>
@@ -34364,7 +34398,7 @@
         <v>1546</v>
       </c>
     </row>
-    <row r="975" spans="2:13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="975" spans="2:13" x14ac:dyDescent="0.3">
       <c r="C975" t="s">
         <v>1542</v>
       </c>
@@ -34393,7 +34427,7 @@
         <v>1546</v>
       </c>
     </row>
-    <row r="976" spans="2:13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="976" spans="2:13" x14ac:dyDescent="0.3">
       <c r="C976" t="s">
         <v>1542</v>
       </c>
@@ -34422,7 +34456,7 @@
         <v>1546</v>
       </c>
     </row>
-    <row r="977" spans="2:13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="977" spans="2:13" x14ac:dyDescent="0.3">
       <c r="C977" t="s">
         <v>1542</v>
       </c>
@@ -34451,7 +34485,7 @@
         <v>1546</v>
       </c>
     </row>
-    <row r="978" spans="2:13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="978" spans="2:13" x14ac:dyDescent="0.3">
       <c r="C978" t="s">
         <v>1417</v>
       </c>
@@ -34480,7 +34514,7 @@
         <v>1558</v>
       </c>
     </row>
-    <row r="979" spans="2:13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="979" spans="2:13" x14ac:dyDescent="0.3">
       <c r="C979" t="s">
         <v>1417</v>
       </c>
@@ -34509,7 +34543,7 @@
         <v>1558</v>
       </c>
     </row>
-    <row r="980" spans="2:13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="980" spans="2:13" x14ac:dyDescent="0.3">
       <c r="C980" t="s">
         <v>1417</v>
       </c>
@@ -34538,7 +34572,7 @@
         <v>1558</v>
       </c>
     </row>
-    <row r="981" spans="2:13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="981" spans="2:13" x14ac:dyDescent="0.3">
       <c r="C981" t="s">
         <v>1417</v>
       </c>
@@ -34567,7 +34601,7 @@
         <v>1558</v>
       </c>
     </row>
-    <row r="982" spans="2:13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="982" spans="2:13" x14ac:dyDescent="0.3">
       <c r="C982" t="s">
         <v>1417</v>
       </c>
@@ -34596,7 +34630,7 @@
         <v>1558</v>
       </c>
     </row>
-    <row r="983" spans="2:13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="983" spans="2:13" x14ac:dyDescent="0.3">
       <c r="C983" t="s">
         <v>1417</v>
       </c>
@@ -34625,7 +34659,7 @@
         <v>1558</v>
       </c>
     </row>
-    <row r="984" spans="2:13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="984" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B984" t="s">
         <v>137</v>
       </c>
@@ -34651,7 +34685,7 @@
         <v>1567</v>
       </c>
     </row>
-    <row r="985" spans="2:13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="985" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B985" t="s">
         <v>137</v>
       </c>
@@ -34677,7 +34711,7 @@
         <v>1567</v>
       </c>
     </row>
-    <row r="986" spans="2:13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="986" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B986" t="s">
         <v>137</v>
       </c>
@@ -34703,7 +34737,7 @@
         <v>1567</v>
       </c>
     </row>
-    <row r="987" spans="2:13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="987" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B987" t="s">
         <v>137</v>
       </c>
@@ -34729,7 +34763,7 @@
         <v>1567</v>
       </c>
     </row>
-    <row r="988" spans="2:13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="988" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B988" t="s">
         <v>137</v>
       </c>
@@ -34755,7 +34789,7 @@
         <v>1567</v>
       </c>
     </row>
-    <row r="989" spans="2:13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="989" spans="2:13" x14ac:dyDescent="0.3">
       <c r="C989" t="s">
         <v>101</v>
       </c>
@@ -34784,7 +34818,7 @@
         <v>1575</v>
       </c>
     </row>
-    <row r="990" spans="2:13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="990" spans="2:13" x14ac:dyDescent="0.3">
       <c r="C990" t="s">
         <v>101</v>
       </c>
@@ -34813,7 +34847,7 @@
         <v>1575</v>
       </c>
     </row>
-    <row r="991" spans="2:13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="991" spans="2:13" x14ac:dyDescent="0.3">
       <c r="C991" t="s">
         <v>101</v>
       </c>
@@ -34842,7 +34876,7 @@
         <v>1575</v>
       </c>
     </row>
-    <row r="992" spans="2:13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="992" spans="2:13" x14ac:dyDescent="0.3">
       <c r="C992" t="s">
         <v>101</v>
       </c>
@@ -34871,7 +34905,7 @@
         <v>1575</v>
       </c>
     </row>
-    <row r="993" spans="3:13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="993" spans="3:13" x14ac:dyDescent="0.3">
       <c r="C993" t="s">
         <v>101</v>
       </c>
@@ -34900,7 +34934,7 @@
         <v>1575</v>
       </c>
     </row>
-    <row r="994" spans="3:13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="994" spans="3:13" x14ac:dyDescent="0.3">
       <c r="C994" t="s">
         <v>101</v>
       </c>
@@ -34929,7 +34963,7 @@
         <v>1575</v>
       </c>
     </row>
-    <row r="995" spans="3:13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="995" spans="3:13" x14ac:dyDescent="0.3">
       <c r="C995" t="s">
         <v>101</v>
       </c>
@@ -34958,7 +34992,7 @@
         <v>1575</v>
       </c>
     </row>
-    <row r="996" spans="3:13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="996" spans="3:13" x14ac:dyDescent="0.3">
       <c r="C996" t="s">
         <v>101</v>
       </c>
@@ -34987,7 +35021,7 @@
         <v>1575</v>
       </c>
     </row>
-    <row r="997" spans="3:13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="997" spans="3:13" x14ac:dyDescent="0.3">
       <c r="C997" t="s">
         <v>399</v>
       </c>
@@ -35016,7 +35050,7 @@
         <v>1587</v>
       </c>
     </row>
-    <row r="998" spans="3:13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="998" spans="3:13" x14ac:dyDescent="0.3">
       <c r="C998" t="s">
         <v>399</v>
       </c>
@@ -35045,7 +35079,7 @@
         <v>1587</v>
       </c>
     </row>
-    <row r="999" spans="3:13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="999" spans="3:13" x14ac:dyDescent="0.3">
       <c r="C999" t="s">
         <v>399</v>
       </c>
@@ -35074,7 +35108,7 @@
         <v>1587</v>
       </c>
     </row>
-    <row r="1000" spans="3:13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="1000" spans="3:13" x14ac:dyDescent="0.3">
       <c r="C1000" t="s">
         <v>726</v>
       </c>
@@ -35103,7 +35137,7 @@
         <v>1593</v>
       </c>
     </row>
-    <row r="1001" spans="3:13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="1001" spans="3:13" x14ac:dyDescent="0.3">
       <c r="C1001" t="s">
         <v>726</v>
       </c>
@@ -35132,7 +35166,7 @@
         <v>1593</v>
       </c>
     </row>
-    <row r="1002" spans="3:13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="1002" spans="3:13" x14ac:dyDescent="0.3">
       <c r="C1002" t="s">
         <v>726</v>
       </c>
@@ -35161,7 +35195,7 @@
         <v>1593</v>
       </c>
     </row>
-    <row r="1003" spans="3:13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="1003" spans="3:13" x14ac:dyDescent="0.3">
       <c r="C1003" t="s">
         <v>726</v>
       </c>
@@ -35190,7 +35224,7 @@
         <v>1593</v>
       </c>
     </row>
-    <row r="1004" spans="3:13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="1004" spans="3:13" x14ac:dyDescent="0.3">
       <c r="C1004" t="s">
         <v>726</v>
       </c>
@@ -35219,7 +35253,7 @@
         <v>1593</v>
       </c>
     </row>
-    <row r="1005" spans="3:13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="1005" spans="3:13" x14ac:dyDescent="0.3">
       <c r="C1005" t="s">
         <v>726</v>
       </c>
@@ -35248,7 +35282,7 @@
         <v>1593</v>
       </c>
     </row>
-    <row r="1006" spans="3:13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="1006" spans="3:13" x14ac:dyDescent="0.3">
       <c r="C1006" t="s">
         <v>726</v>
       </c>
@@ -35277,7 +35311,7 @@
         <v>1593</v>
       </c>
     </row>
-    <row r="1007" spans="3:13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="1007" spans="3:13" x14ac:dyDescent="0.3">
       <c r="C1007" t="s">
         <v>726</v>
       </c>
@@ -35306,7 +35340,7 @@
         <v>1593</v>
       </c>
     </row>
-    <row r="1008" spans="3:13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="1008" spans="3:13" x14ac:dyDescent="0.3">
       <c r="C1008" t="s">
         <v>726</v>
       </c>
@@ -35335,7 +35369,7 @@
         <v>1593</v>
       </c>
     </row>
-    <row r="1009" spans="2:13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="1009" spans="2:13" x14ac:dyDescent="0.3">
       <c r="C1009" t="s">
         <v>180</v>
       </c>
@@ -35361,7 +35395,7 @@
         <v>1604</v>
       </c>
     </row>
-    <row r="1010" spans="2:13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="1010" spans="2:13" x14ac:dyDescent="0.3">
       <c r="C1010" t="s">
         <v>180</v>
       </c>
@@ -35387,7 +35421,7 @@
         <v>1604</v>
       </c>
     </row>
-    <row r="1011" spans="2:13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="1011" spans="2:13" x14ac:dyDescent="0.3">
       <c r="C1011" t="s">
         <v>180</v>
       </c>
@@ -35413,7 +35447,7 @@
         <v>1604</v>
       </c>
     </row>
-    <row r="1012" spans="2:13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="1012" spans="2:13" x14ac:dyDescent="0.3">
       <c r="C1012" t="s">
         <v>180</v>
       </c>
@@ -35439,7 +35473,7 @@
         <v>1604</v>
       </c>
     </row>
-    <row r="1013" spans="2:13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="1013" spans="2:13" x14ac:dyDescent="0.3">
       <c r="C1013" t="s">
         <v>180</v>
       </c>
@@ -35465,7 +35499,7 @@
         <v>1604</v>
       </c>
     </row>
-    <row r="1014" spans="2:13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="1014" spans="2:13" x14ac:dyDescent="0.3">
       <c r="C1014" t="s">
         <v>180</v>
       </c>
@@ -35491,7 +35525,7 @@
         <v>1604</v>
       </c>
     </row>
-    <row r="1015" spans="2:13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="1015" spans="2:13" x14ac:dyDescent="0.3">
       <c r="C1015" t="s">
         <v>180</v>
       </c>
@@ -35517,7 +35551,7 @@
         <v>1604</v>
       </c>
     </row>
-    <row r="1016" spans="2:13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="1016" spans="2:13" x14ac:dyDescent="0.3">
       <c r="C1016" t="s">
         <v>180</v>
       </c>
@@ -35543,7 +35577,7 @@
         <v>1604</v>
       </c>
     </row>
-    <row r="1017" spans="2:13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="1017" spans="2:13" x14ac:dyDescent="0.3">
       <c r="C1017" t="s">
         <v>180</v>
       </c>
@@ -35569,7 +35603,7 @@
         <v>1604</v>
       </c>
     </row>
-    <row r="1018" spans="2:13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="1018" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B1018" t="s">
         <v>137</v>
       </c>
@@ -35598,7 +35632,7 @@
         <v>1617</v>
       </c>
     </row>
-    <row r="1019" spans="2:13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="1019" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B1019" t="s">
         <v>137</v>
       </c>
@@ -35627,7 +35661,7 @@
         <v>1617</v>
       </c>
     </row>
-    <row r="1020" spans="2:13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="1020" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B1020" t="s">
         <v>137</v>
       </c>
@@ -35656,7 +35690,7 @@
         <v>1617</v>
       </c>
     </row>
-    <row r="1021" spans="2:13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="1021" spans="2:13" x14ac:dyDescent="0.3">
       <c r="C1021" t="s">
         <v>150</v>
       </c>
@@ -35685,7 +35719,7 @@
         <v>1623</v>
       </c>
     </row>
-    <row r="1022" spans="2:13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="1022" spans="2:13" x14ac:dyDescent="0.3">
       <c r="C1022" t="s">
         <v>150</v>
       </c>
@@ -35714,7 +35748,7 @@
         <v>1623</v>
       </c>
     </row>
-    <row r="1023" spans="2:13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="1023" spans="2:13" x14ac:dyDescent="0.3">
       <c r="C1023" t="s">
         <v>150</v>
       </c>
@@ -35743,7 +35777,7 @@
         <v>1623</v>
       </c>
     </row>
-    <row r="1024" spans="2:13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="1024" spans="2:13" x14ac:dyDescent="0.3">
       <c r="C1024" t="s">
         <v>150</v>
       </c>
@@ -35772,7 +35806,7 @@
         <v>1623</v>
       </c>
     </row>
-    <row r="1025" spans="3:13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="1025" spans="3:13" x14ac:dyDescent="0.3">
       <c r="C1025" t="s">
         <v>150</v>
       </c>
@@ -35801,7 +35835,7 @@
         <v>1623</v>
       </c>
     </row>
-    <row r="1026" spans="3:13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="1026" spans="3:13" x14ac:dyDescent="0.3">
       <c r="C1026" t="s">
         <v>150</v>
       </c>
@@ -35830,7 +35864,7 @@
         <v>1623</v>
       </c>
     </row>
-    <row r="1027" spans="3:13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="1027" spans="3:13" x14ac:dyDescent="0.3">
       <c r="C1027" t="s">
         <v>150</v>
       </c>
@@ -35859,7 +35893,7 @@
         <v>1623</v>
       </c>
     </row>
-    <row r="1028" spans="3:13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="1028" spans="3:13" x14ac:dyDescent="0.3">
       <c r="C1028" t="s">
         <v>150</v>
       </c>
@@ -35888,7 +35922,7 @@
         <v>1623</v>
       </c>
     </row>
-    <row r="1029" spans="3:13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="1029" spans="3:13" x14ac:dyDescent="0.3">
       <c r="D1029" t="s">
         <v>1632</v>
       </c>
@@ -35911,7 +35945,7 @@
         <v>1635</v>
       </c>
     </row>
-    <row r="1030" spans="3:13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="1030" spans="3:13" x14ac:dyDescent="0.3">
       <c r="D1030" t="s">
         <v>1632</v>
       </c>
@@ -35934,7 +35968,7 @@
         <v>1635</v>
       </c>
     </row>
-    <row r="1031" spans="3:13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="1031" spans="3:13" x14ac:dyDescent="0.3">
       <c r="D1031" t="s">
         <v>1632</v>
       </c>
@@ -35954,7 +35988,7 @@
         <v>1635</v>
       </c>
     </row>
-    <row r="1032" spans="3:13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="1032" spans="3:13" x14ac:dyDescent="0.3">
       <c r="D1032" t="s">
         <v>1632</v>
       </c>
@@ -35974,7 +36008,7 @@
         <v>1635</v>
       </c>
     </row>
-    <row r="1033" spans="3:13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="1033" spans="3:13" x14ac:dyDescent="0.3">
       <c r="C1033" t="s">
         <v>129</v>
       </c>
@@ -36000,7 +36034,7 @@
         <v>1639</v>
       </c>
     </row>
-    <row r="1034" spans="3:13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="1034" spans="3:13" x14ac:dyDescent="0.3">
       <c r="C1034" t="s">
         <v>129</v>
       </c>
@@ -36026,7 +36060,7 @@
         <v>1639</v>
       </c>
     </row>
-    <row r="1035" spans="3:13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="1035" spans="3:13" x14ac:dyDescent="0.3">
       <c r="C1035" t="s">
         <v>129</v>
       </c>
@@ -36052,7 +36086,7 @@
         <v>1639</v>
       </c>
     </row>
-    <row r="1036" spans="3:13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="1036" spans="3:13" x14ac:dyDescent="0.3">
       <c r="C1036" t="s">
         <v>129</v>
       </c>
@@ -36078,7 +36112,7 @@
         <v>1639</v>
       </c>
     </row>
-    <row r="1037" spans="3:13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="1037" spans="3:13" x14ac:dyDescent="0.3">
       <c r="C1037" t="s">
         <v>129</v>
       </c>
@@ -36104,7 +36138,7 @@
         <v>1639</v>
       </c>
     </row>
-    <row r="1038" spans="3:13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="1038" spans="3:13" x14ac:dyDescent="0.3">
       <c r="C1038" t="s">
         <v>129</v>
       </c>
@@ -36130,7 +36164,7 @@
         <v>1639</v>
       </c>
     </row>
-    <row r="1039" spans="3:13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="1039" spans="3:13" x14ac:dyDescent="0.3">
       <c r="C1039" t="s">
         <v>129</v>
       </c>
@@ -36156,7 +36190,7 @@
         <v>1639</v>
       </c>
     </row>
-    <row r="1040" spans="3:13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="1040" spans="3:13" x14ac:dyDescent="0.3">
       <c r="C1040" t="s">
         <v>129</v>
       </c>
@@ -36182,7 +36216,7 @@
         <v>1639</v>
       </c>
     </row>
-    <row r="1041" spans="2:13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="1041" spans="2:13" x14ac:dyDescent="0.3">
       <c r="C1041" t="s">
         <v>303</v>
       </c>
@@ -36208,7 +36242,7 @@
         <v>1641</v>
       </c>
     </row>
-    <row r="1042" spans="2:13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="1042" spans="2:13" x14ac:dyDescent="0.3">
       <c r="C1042" t="s">
         <v>303</v>
       </c>
@@ -36234,7 +36268,7 @@
         <v>1641</v>
       </c>
     </row>
-    <row r="1043" spans="2:13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="1043" spans="2:13" x14ac:dyDescent="0.3">
       <c r="C1043" t="s">
         <v>303</v>
       </c>
@@ -36260,7 +36294,7 @@
         <v>1641</v>
       </c>
     </row>
-    <row r="1044" spans="2:13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="1044" spans="2:13" x14ac:dyDescent="0.3">
       <c r="C1044" t="s">
         <v>303</v>
       </c>
@@ -36286,7 +36320,7 @@
         <v>1641</v>
       </c>
     </row>
-    <row r="1045" spans="2:13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="1045" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B1045" t="s">
         <v>137</v>
       </c>
@@ -36318,7 +36352,7 @@
         <v>1648</v>
       </c>
     </row>
-    <row r="1046" spans="2:13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="1046" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B1046" t="s">
         <v>137</v>
       </c>
@@ -36350,7 +36384,7 @@
         <v>1648</v>
       </c>
     </row>
-    <row r="1047" spans="2:13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="1047" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B1047" t="s">
         <v>137</v>
       </c>
@@ -36379,7 +36413,7 @@
         <v>1648</v>
       </c>
     </row>
-    <row r="1048" spans="2:13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="1048" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B1048" t="s">
         <v>137</v>
       </c>
@@ -36408,7 +36442,7 @@
         <v>1648</v>
       </c>
     </row>
-    <row r="1049" spans="2:13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="1049" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B1049" t="s">
         <v>137</v>
       </c>
@@ -36438,15 +36472,7 @@
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:M1049" xr:uid="{00000000-0009-0000-0000-000000000000}">
-    <filterColumn colId="3">
-      <filters>
-        <filter val="Copa Konomi"/>
-        <filter val="Copa Konomi - Nuevos Valores"/>
-        <filter val="II Torneo Konomi"/>
-      </filters>
-    </filterColumn>
-  </autoFilter>
+  <autoFilter ref="A1:M1049" xr:uid="{00000000-0009-0000-0000-000000000000}"/>
   <hyperlinks>
     <hyperlink ref="M14" r:id="rId1" xr:uid="{00000000-0004-0000-0000-000000000000}"/>
     <hyperlink ref="M15" r:id="rId2" xr:uid="{00000000-0004-0000-0000-000001000000}"/>
@@ -36984,9 +37010,12 @@
     <hyperlink ref="M1038" r:id="rId534" xr:uid="{00000000-0004-0000-0000-000015020000}"/>
     <hyperlink ref="M1039" r:id="rId535" xr:uid="{00000000-0004-0000-0000-000016020000}"/>
     <hyperlink ref="M1040" r:id="rId536" xr:uid="{00000000-0004-0000-0000-000017020000}"/>
+    <hyperlink ref="M212" r:id="rId537" xr:uid="{516292F0-1A94-400B-A993-81F88F867B04}"/>
+    <hyperlink ref="M243" r:id="rId538" xr:uid="{E7DFA6B8-E2C0-420F-8AEA-E53722F06A5E}"/>
+    <hyperlink ref="M867" r:id="rId539" xr:uid="{772A65B7-BE22-4D44-9CE5-D0E0922EF212}"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-  <legacyDrawing r:id="rId537"/>
+  <legacyDrawing r:id="rId540"/>
 </worksheet>
 </file>
 

--- a/data/raw/copas_y_torneos.xlsx
+++ b/data/raw/copas_y_torneos.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Projects\gateball\kantokeando-data\data\raw\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2E1EE6E5-F7C5-4A0D-93DD-6E5A5411C9BA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A62F31FB-B13C-403E-AC98-877D5C952347}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="360" windowWidth="23256" windowHeight="12456" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Resultados" sheetId="1" r:id="rId1"/>
@@ -35251,7 +35251,7 @@
         <v>2</v>
       </c>
       <c r="K1004" t="s">
-        <v>514</v>
+        <v>639</v>
       </c>
       <c r="L1004" t="s">
         <v>1603</v>

--- a/data/raw/copas_y_torneos.xlsx
+++ b/data/raw/copas_y_torneos.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Projects\gateball\kantokeando-data\data\raw\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A62F31FB-B13C-403E-AC98-877D5C952347}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{801F71AE-05BD-4BEB-9DB1-17853D6D06D9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -48,7 +48,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="8241" uniqueCount="1712">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="8245" uniqueCount="1712">
   <si>
     <t>id_torneo</t>
   </si>
@@ -5387,7 +5387,7 @@
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="30">
+  <cellXfs count="31">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -5448,6 +5448,7 @@
     <xf numFmtId="0" fontId="15" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="3">
     <cellStyle name="Hipervínculo" xfId="1" builtinId="8"/>
@@ -31569,6 +31570,9 @@
       <c r="B878" t="s">
         <v>137</v>
       </c>
+      <c r="C878" t="s">
+        <v>521</v>
+      </c>
       <c r="D878" t="s">
         <v>1397</v>
       </c>
@@ -31595,6 +31599,9 @@
       <c r="B879" t="s">
         <v>137</v>
       </c>
+      <c r="C879" t="s">
+        <v>521</v>
+      </c>
       <c r="D879" t="s">
         <v>1397</v>
       </c>
@@ -31621,6 +31628,9 @@
       <c r="B880" t="s">
         <v>137</v>
       </c>
+      <c r="C880" s="30" t="s">
+        <v>521</v>
+      </c>
       <c r="D880" t="s">
         <v>1397</v>
       </c>
@@ -31646,6 +31656,9 @@
     <row r="881" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B881" t="s">
         <v>137</v>
+      </c>
+      <c r="C881" t="s">
+        <v>521</v>
       </c>
       <c r="D881" t="s">
         <v>1397</v>
